--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Job Matches" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Matches'!$A$1:$M$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Matches'!$A$1:$M$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -49,7 +49,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -81,6 +81,11 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -108,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -141,6 +146,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -508,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1286,8 +1303,1394 @@
       </c>
       <c r="M12" s="2" t="inlineStr"/>
     </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>4401686051</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Front End Software Engineer</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Saronic Technologies</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, react, node, aws, api, Location: Austin, TX, Title match: Front End Software Engineer</t>
+        </is>
+      </c>
+      <c r="K13" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L13" s="12" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M13" s="12" t="inlineStr"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>4309696652</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>DataAnnotation</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>Rhode Island, United States</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, html, sql, full stack, c++, Title match: Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L14" s="13" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M14" s="13" t="inlineStr"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>4309804319</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>DataAnnotation</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>Colorado, United States</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, html, sql, full stack, c++, Title match: Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="K15" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L15" s="12" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M15" s="12" t="inlineStr"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>4410271532</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Associate Developer</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>HealthStream</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>Nashville, TN</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>Very Low</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Skills: aws, api, c, ci/cd</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L16" s="13" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M16" s="13" t="inlineStr"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>4304445726</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>DataAnnotation</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>Oregon, United States</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, html, sql, c++, c, Title match: Software Developer</t>
+        </is>
+      </c>
+      <c r="K17" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L17" s="12" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M17" s="12" t="inlineStr"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>4342036151</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Modern Treasury</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Skills: react, aws, rest, api, git, full-stack, Title match: Software Engineer</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L18" s="13" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M18" s="13" t="inlineStr"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>4304441843</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>DataAnnotation</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>Idaho, United States</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, html, sql, c++, c, Title match: Software Developer</t>
+        </is>
+      </c>
+      <c r="K19" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L19" s="12" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M19" s="12" t="inlineStr"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>4408047047</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Computer Sciences - Graduates - AI Training - Las Vegas, US</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>Prolific</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>Very Low</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>Temporary</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Skills: aws, c, llm, algorithms</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L20" s="13" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M20" s="13" t="inlineStr"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>4304444837</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>DataAnnotation</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>New Jersey, United States</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, html, sql, c++, c, Title match: Software Developer</t>
+        </is>
+      </c>
+      <c r="K21" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L21" s="12" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M21" s="12" t="inlineStr"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>4405641326</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>PartnerTap</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>Skills: javascript, react, rest, api, html, css, Location: Seattle, WA</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L22" s="13" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M22" s="13" t="inlineStr"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>4341020900</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>PlanIT Group, LLC</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, react, node, api, html, Title match: Software Engineer</t>
+        </is>
+      </c>
+      <c r="K23" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L23" s="12" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M23" s="12" t="inlineStr"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>4304450637</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>DataAnnotation</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>New York, United States</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, html, sql, c++, c, Title match: Software Developer</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L24" s="13" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M24" s="13" t="inlineStr"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>4304451654</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>DataAnnotation</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>Utah, United States</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, html, sql, c++, c, Title match: Software Developer</t>
+        </is>
+      </c>
+      <c r="K25" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L25" s="12" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M25" s="12" t="inlineStr"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>4413745880</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Crate &amp; Barrel</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>Northbrook, IL</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, git, sql, c++, c, Title match: Software Engineer</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L26" s="13" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M26" s="13" t="inlineStr"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>4304438841</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>DataAnnotation</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>Connecticut, United States</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, html, sql, c++, c, Title match: Software Developer</t>
+        </is>
+      </c>
+      <c r="K27" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L27" s="12" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M27" s="12" t="inlineStr"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>4393215930</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>Transcend</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>California, United States</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>Skills: react, node, aws, rest, api, sql, Title match: Software Engineer</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L28" s="13" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M28" s="13" t="inlineStr"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>4304445723</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>DataAnnotation</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>Illinois, United States</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, html, sql, c++, c, Title match: Software Developer</t>
+        </is>
+      </c>
+      <c r="K29" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M29" s="12" t="inlineStr"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>4396380649</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Full-Stack Developer Intern, Music &amp; Audio</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>Melotech</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>Skills: node, api, full stack, full-stack, backend, frontend, Title match: Full-Stack Developer Intern, Music &amp; Audio</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L30" s="13" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M30" s="13" t="inlineStr"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>4304454025</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>DataAnnotation</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>Washington, DC</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, html, sql, c++, c, Location: Washington, DC, Title match: Software Developer</t>
+        </is>
+      </c>
+      <c r="K31" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L31" s="12" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M31" s="12" t="inlineStr"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>4309802287</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>DataAnnotation</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>New Jersey, United States</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, html, sql, full stack, c++, Title match: Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L32" s="13" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M32" s="13" t="inlineStr"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>4309694880</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>DataAnnotation</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>New York, United States</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, html, sql, full stack, c++, Title match: Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="K33" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L33" s="12" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M33" s="12" t="inlineStr"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>4411274012</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Junior UI Developer</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>General Dynamics Information Technology</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="inlineStr">
+        <is>
+          <t>Very Low</t>
+        </is>
+      </c>
+      <c r="H34" s="13" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>Skills: react, git, c, agile</t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L34" s="13" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M34" s="13" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M12"/>
+  <autoFilter ref="A1:M34"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1300,6 +2703,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Job Matches" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Matches'!$A$1:$M$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Matches'!$A$1:$M$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -49,7 +49,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -86,6 +86,11 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCC99"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -113,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -158,6 +163,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -525,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -611,12 +628,12 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>4406952064</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -626,12 +643,12 @@
           <t>DevSecOps Intern</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>Modern Technology Solutions, Inc. (MTSI)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>Huntsville, AL</t>
         </is>
@@ -646,12 +663,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="13" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -666,20 +683,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+      <c r="L2" s="13" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M2" s="13" t="inlineStr"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>4405630173</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -689,12 +706,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>DLRdmv®</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>Dallas, TX</t>
         </is>
@@ -709,12 +726,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -729,20 +746,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L3" s="7" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M3" s="7" t="inlineStr"/>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M3" s="12" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>4287414862</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -752,12 +769,12 @@
           <t>[Online Assessment]Software Development Engineer Intern (Network Automation)- 2026 Summer (BS/ MS)</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>ByteDance</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -772,12 +789,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="13" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="13" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -792,20 +809,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>4309805269</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -815,12 +832,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Delaware, United States</t>
         </is>
@@ -835,12 +852,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -855,20 +872,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="inlineStr"/>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>4371812987</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -878,12 +895,12 @@
           <t>Software Development Engineer Fall Intern - Military Veteran</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -898,12 +915,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -918,20 +935,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M6" s="13" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>4274682122</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -941,12 +958,12 @@
           <t>Software Engineer Intern (Data Ecosystem) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -961,12 +978,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -981,20 +998,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="inlineStr"/>
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>4283848614</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1004,12 +1021,12 @@
           <t>[Online Assessment] Software Engineer Intern (Recommendation Infrastructure) - 2026 Fall (BS/ MS)</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1024,12 +1041,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1044,20 +1061,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+      <c r="L8" s="13" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M8" s="13" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>4411790844</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1067,12 +1084,12 @@
           <t>Software Engineer Intern (Infrastructure Automation) - Fall 2026</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -1087,12 +1104,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="12" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1107,20 +1124,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L9" s="7" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="inlineStr"/>
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M9" s="12" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>4332425058</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1130,12 +1147,12 @@
           <t>Software Development Engineer Internship - Fall 2026 (US)</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1150,12 +1167,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="13" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="13" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1170,20 +1187,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+      <c r="L10" s="13" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M10" s="13" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>4323643644</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1193,12 +1210,12 @@
           <t>[Online Assessment] Software Engineer Intern (Recommendation Infrastructure) - 2026 Summer (BS/ MS)</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1213,12 +1230,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="12" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1233,20 +1250,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L11" s="7" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="inlineStr"/>
+      <c r="L11" s="12" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M11" s="12" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>4320849104</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1256,12 +1273,12 @@
           <t>Software Engineer Intern (Commerce Ads) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1276,12 +1293,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="13" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="13" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1296,12 +1313,12 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+      <c r="L12" s="13" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M12" s="13" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
@@ -2689,8 +2706,197 @@
       </c>
       <c r="M34" s="13" t="inlineStr"/>
     </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>4264562292</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>Cymertek Corporation</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>San Antonio, TX</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H35" s="16" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="I35" s="16" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, aws, docker, git, sql, full stack, Title match: Software Developer</t>
+        </is>
+      </c>
+      <c r="K35" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L35" s="16" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M35" s="16" t="inlineStr"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>4417482675</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Software Developer I</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>El Paso Water</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>El Paso, TX</t>
+        </is>
+      </c>
+      <c r="F36" s="18" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="G36" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H36" s="17" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="I36" s="17" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, rest, c, Title match: Software Developer I</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L36" s="17" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M36" s="17" t="inlineStr"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>4416508200</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test Intern (Global E-Commerce) - 2026 Summer (BS/MS)</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H37" s="16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I37" s="16" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>Skills: aws, rest, api, c, express, agile, Location: Seattle, WA, Title match: Software Development Engineer in Test Intern (Global E-Commerce) - 2026 Summer (BS/MS)</t>
+        </is>
+      </c>
+      <c r="K37" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L37" s="16" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M37" s="16" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M34"/>
+  <autoFilter ref="A1:M37"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -2725,6 +2931,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Job Matches" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Matches'!$A$1:$M$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Matches'!$A$1:$M$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -176,6 +176,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -542,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -628,12 +634,12 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>4406952064</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -643,12 +649,12 @@
           <t>DevSecOps Intern</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>Modern Technology Solutions, Inc. (MTSI)</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>Huntsville, AL</t>
         </is>
@@ -663,12 +669,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H2" s="13" t="inlineStr">
+      <c r="H2" s="17" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="I2" s="13" t="inlineStr">
+      <c r="I2" s="17" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -683,20 +689,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L2" s="13" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M2" s="13" t="inlineStr"/>
+      <c r="L2" s="17" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M2" s="17" t="inlineStr"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>4405630173</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -706,12 +712,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>DLRdmv®</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>Dallas, TX</t>
         </is>
@@ -726,12 +732,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I3" s="12" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -746,20 +752,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L3" s="12" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M3" s="12" t="inlineStr"/>
+      <c r="L3" s="16" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M3" s="16" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>4287414862</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -769,12 +775,12 @@
           <t>[Online Assessment]Software Development Engineer Intern (Network Automation)- 2026 Summer (BS/ MS)</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>ByteDance</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -789,12 +795,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -809,20 +815,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M4" s="13" t="inlineStr"/>
+      <c r="L4" s="17" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M4" s="17" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>4309805269</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -832,12 +838,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>Delaware, United States</t>
         </is>
@@ -852,12 +858,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="H5" s="16" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="I5" s="12" t="inlineStr">
+      <c r="I5" s="16" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -872,20 +878,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M5" s="12" t="inlineStr"/>
+      <c r="L5" s="16" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M5" s="16" t="inlineStr"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>4371812987</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -895,12 +901,12 @@
           <t>Software Development Engineer Fall Intern - Military Veteran</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -915,12 +921,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -935,20 +941,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L6" s="13" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M6" s="13" t="inlineStr"/>
+      <c r="L6" s="17" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M6" s="17" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>4274682122</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -958,12 +964,12 @@
           <t>Software Engineer Intern (Data Ecosystem) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -978,12 +984,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I7" s="12" t="inlineStr">
+      <c r="I7" s="16" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -998,20 +1004,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M7" s="12" t="inlineStr"/>
+      <c r="L7" s="16" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M7" s="16" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>4283848614</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1021,12 +1027,12 @@
           <t>[Online Assessment] Software Engineer Intern (Recommendation Infrastructure) - 2026 Fall (BS/ MS)</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1041,12 +1047,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I8" s="13" t="inlineStr">
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1061,20 +1067,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L8" s="13" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M8" s="13" t="inlineStr"/>
+      <c r="L8" s="17" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M8" s="17" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>4411790844</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1084,12 +1090,12 @@
           <t>Software Engineer Intern (Infrastructure Automation) - Fall 2026</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -1104,12 +1110,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="H9" s="16" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I9" s="12" t="inlineStr">
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1124,20 +1130,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L9" s="12" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M9" s="12" t="inlineStr"/>
+      <c r="L9" s="16" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M9" s="16" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>4332425058</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1147,12 +1153,12 @@
           <t>Software Development Engineer Internship - Fall 2026 (US)</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1167,12 +1173,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H10" s="13" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1187,20 +1193,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L10" s="13" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M10" s="13" t="inlineStr"/>
+      <c r="L10" s="17" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M10" s="17" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>4323643644</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1210,12 +1216,12 @@
           <t>[Online Assessment] Software Engineer Intern (Recommendation Infrastructure) - 2026 Summer (BS/ MS)</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1230,12 +1236,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
+      <c r="H11" s="16" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I11" s="12" t="inlineStr">
+      <c r="I11" s="16" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1250,20 +1256,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L11" s="12" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M11" s="12" t="inlineStr"/>
+      <c r="L11" s="16" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M11" s="16" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>4320849104</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1273,12 +1279,12 @@
           <t>Software Engineer Intern (Commerce Ads) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1293,12 +1299,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H12" s="13" t="inlineStr">
+      <c r="H12" s="17" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I12" s="13" t="inlineStr">
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1313,20 +1319,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L12" s="13" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M12" s="13" t="inlineStr"/>
+      <c r="L12" s="17" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M12" s="17" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>4401686051</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1336,12 +1342,12 @@
           <t>Front End Software Engineer</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>Saronic Technologies</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -1356,12 +1362,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="H13" s="16" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I13" s="12" t="inlineStr">
+      <c r="I13" s="16" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1376,20 +1382,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L13" s="12" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M13" s="12" t="inlineStr"/>
+      <c r="L13" s="16" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M13" s="16" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>4309696652</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1399,12 +1405,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>Rhode Island, United States</t>
         </is>
@@ -1419,12 +1425,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H14" s="13" t="inlineStr">
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="I14" s="13" t="inlineStr">
+      <c r="I14" s="17" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1439,20 +1445,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L14" s="13" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M14" s="13" t="inlineStr"/>
+      <c r="L14" s="17" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M14" s="17" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>4309804319</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1462,12 +1468,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>Colorado, United States</t>
         </is>
@@ -1482,12 +1488,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H15" s="12" t="inlineStr">
+      <c r="H15" s="16" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="I15" s="12" t="inlineStr">
+      <c r="I15" s="16" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1502,20 +1508,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L15" s="12" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M15" s="12" t="inlineStr"/>
+      <c r="L15" s="16" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M15" s="16" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>4410271532</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1525,12 +1531,12 @@
           <t>Associate Developer</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>HealthStream</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>Nashville, TN</t>
         </is>
@@ -1545,12 +1551,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H16" s="13" t="inlineStr">
+      <c r="H16" s="17" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I16" s="13" t="inlineStr">
+      <c r="I16" s="17" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1565,20 +1571,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L16" s="13" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M16" s="13" t="inlineStr"/>
+      <c r="L16" s="17" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M16" s="17" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>4304445726</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1588,12 +1594,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>Oregon, United States</t>
         </is>
@@ -1608,12 +1614,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H17" s="12" t="inlineStr">
+      <c r="H17" s="16" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="I17" s="12" t="inlineStr">
+      <c r="I17" s="16" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1628,20 +1634,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L17" s="12" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M17" s="12" t="inlineStr"/>
+      <c r="L17" s="16" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M17" s="16" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>4342036151</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1651,12 +1657,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>Modern Treasury</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
@@ -1671,12 +1677,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H18" s="13" t="inlineStr">
+      <c r="H18" s="17" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I18" s="13" t="inlineStr">
+      <c r="I18" s="17" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1691,20 +1697,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L18" s="13" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M18" s="13" t="inlineStr"/>
+      <c r="L18" s="17" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M18" s="17" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>4304441843</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1714,12 +1720,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>Idaho, United States</t>
         </is>
@@ -1734,12 +1740,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H19" s="12" t="inlineStr">
+      <c r="H19" s="16" t="inlineStr">
         <is>
           <t>157</t>
         </is>
       </c>
-      <c r="I19" s="12" t="inlineStr">
+      <c r="I19" s="16" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1754,20 +1760,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L19" s="12" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M19" s="12" t="inlineStr"/>
+      <c r="L19" s="16" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M19" s="16" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>4408047047</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1777,12 +1783,12 @@
           <t>Computer Sciences - Graduates - AI Training - Las Vegas, US</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>Prolific</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>Las Vegas, NV</t>
         </is>
@@ -1797,12 +1803,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H20" s="13" t="inlineStr">
+      <c r="H20" s="17" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I20" s="13" t="inlineStr">
+      <c r="I20" s="17" t="inlineStr">
         <is>
           <t>Temporary</t>
         </is>
@@ -1817,20 +1823,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L20" s="13" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M20" s="13" t="inlineStr"/>
+      <c r="L20" s="17" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M20" s="17" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>4304444837</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1840,12 +1846,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>New Jersey, United States</t>
         </is>
@@ -1860,12 +1866,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H21" s="12" t="inlineStr">
+      <c r="H21" s="16" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I21" s="12" t="inlineStr">
+      <c r="I21" s="16" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1880,20 +1886,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L21" s="12" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M21" s="12" t="inlineStr"/>
+      <c r="L21" s="16" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M21" s="16" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>4405641326</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1903,12 +1909,12 @@
           <t>Full-stack Engineer</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>PartnerTap</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1923,12 +1929,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H22" s="13" t="inlineStr">
+      <c r="H22" s="17" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I22" s="13" t="inlineStr">
+      <c r="I22" s="17" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1943,20 +1949,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L22" s="13" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M22" s="13" t="inlineStr"/>
+      <c r="L22" s="17" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M22" s="17" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>4341020900</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1966,12 +1972,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>PlanIT Group, LLC</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -1986,12 +1992,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H23" s="12" t="inlineStr">
+      <c r="H23" s="16" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I23" s="12" t="inlineStr">
+      <c r="I23" s="16" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
@@ -2006,20 +2012,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L23" s="12" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M23" s="12" t="inlineStr"/>
+      <c r="L23" s="16" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M23" s="16" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>4304450637</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2029,12 +2035,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -2049,12 +2055,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H24" s="13" t="inlineStr">
+      <c r="H24" s="17" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I24" s="13" t="inlineStr">
+      <c r="I24" s="17" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2069,20 +2075,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L24" s="13" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M24" s="13" t="inlineStr"/>
+      <c r="L24" s="17" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M24" s="17" t="inlineStr"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>4304451654</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2092,12 +2098,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="16" t="inlineStr">
         <is>
           <t>Utah, United States</t>
         </is>
@@ -2112,12 +2118,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H25" s="12" t="inlineStr">
+      <c r="H25" s="16" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I25" s="12" t="inlineStr">
+      <c r="I25" s="16" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2132,20 +2138,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L25" s="12" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M25" s="12" t="inlineStr"/>
+      <c r="L25" s="16" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M25" s="16" t="inlineStr"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>4413745880</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2155,12 +2161,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>Crate &amp; Barrel</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>Northbrook, IL</t>
         </is>
@@ -2175,12 +2181,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H26" s="13" t="inlineStr">
+      <c r="H26" s="17" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I26" s="13" t="inlineStr">
+      <c r="I26" s="17" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2195,20 +2201,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L26" s="13" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M26" s="13" t="inlineStr"/>
+      <c r="L26" s="17" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M26" s="17" t="inlineStr"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>4304438841</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2218,12 +2224,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>Connecticut, United States</t>
         </is>
@@ -2238,12 +2244,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H27" s="12" t="inlineStr">
+      <c r="H27" s="16" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I27" s="12" t="inlineStr">
+      <c r="I27" s="16" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2258,20 +2264,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L27" s="12" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M27" s="12" t="inlineStr"/>
+      <c r="L27" s="16" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M27" s="16" t="inlineStr"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>4393215930</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2281,12 +2287,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>Transcend</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>California, United States</t>
         </is>
@@ -2301,12 +2307,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H28" s="13" t="inlineStr">
+      <c r="H28" s="17" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I28" s="13" t="inlineStr">
+      <c r="I28" s="17" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2321,20 +2327,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L28" s="13" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M28" s="13" t="inlineStr"/>
+      <c r="L28" s="17" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M28" s="17" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>4304445723</t>
         </is>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2344,12 +2350,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E29" s="16" t="inlineStr">
         <is>
           <t>Illinois, United States</t>
         </is>
@@ -2364,12 +2370,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H29" s="12" t="inlineStr">
+      <c r="H29" s="16" t="inlineStr">
         <is>
           <t>198</t>
         </is>
       </c>
-      <c r="I29" s="12" t="inlineStr">
+      <c r="I29" s="16" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2384,20 +2390,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L29" s="12" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M29" s="12" t="inlineStr"/>
+      <c r="L29" s="16" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M29" s="16" t="inlineStr"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>4396380649</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2407,12 +2413,12 @@
           <t>Full-Stack Developer Intern, Music &amp; Audio</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>Melotech</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
@@ -2427,12 +2433,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H30" s="13" t="inlineStr">
+      <c r="H30" s="17" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I30" s="13" t="inlineStr">
+      <c r="I30" s="17" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -2447,20 +2453,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L30" s="13" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M30" s="13" t="inlineStr"/>
+      <c r="L30" s="17" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M30" s="17" t="inlineStr"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>4304454025</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2470,12 +2476,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E31" s="16" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -2490,12 +2496,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H31" s="12" t="inlineStr">
+      <c r="H31" s="16" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I31" s="12" t="inlineStr">
+      <c r="I31" s="16" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2510,20 +2516,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L31" s="12" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M31" s="12" t="inlineStr"/>
+      <c r="L31" s="16" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M31" s="16" t="inlineStr"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>4309802287</t>
         </is>
       </c>
-      <c r="B32" s="13" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2533,12 +2539,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
         <is>
           <t>New Jersey, United States</t>
         </is>
@@ -2553,12 +2559,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H32" s="13" t="inlineStr">
+      <c r="H32" s="17" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I32" s="13" t="inlineStr">
+      <c r="I32" s="17" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2573,20 +2579,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L32" s="13" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M32" s="13" t="inlineStr"/>
+      <c r="L32" s="17" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M32" s="17" t="inlineStr"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>4309694880</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2596,12 +2602,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E33" s="16" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -2616,12 +2622,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H33" s="12" t="inlineStr">
+      <c r="H33" s="16" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I33" s="12" t="inlineStr">
+      <c r="I33" s="16" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2636,20 +2642,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L33" s="12" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M33" s="12" t="inlineStr"/>
+      <c r="L33" s="16" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M33" s="16" t="inlineStr"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>4411274012</t>
         </is>
       </c>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2659,12 +2665,12 @@
           <t>Junior UI Developer</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>General Dynamics Information Technology</t>
         </is>
       </c>
-      <c r="E34" s="13" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -2679,12 +2685,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H34" s="13" t="inlineStr">
+      <c r="H34" s="17" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I34" s="13" t="inlineStr">
+      <c r="I34" s="17" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2699,12 +2705,12 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L34" s="13" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M34" s="13" t="inlineStr"/>
+      <c r="L34" s="17" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M34" s="17" t="inlineStr"/>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="16" t="inlineStr">
@@ -2895,8 +2901,134 @@
       </c>
       <c r="M37" s="16" t="inlineStr"/>
     </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>4309809191</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>DataAnnotation</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>Ohio, United States</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H38" s="20" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="I38" s="20" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, html, sql, full stack, c++, Title match: Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L38" s="20" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M38" s="20" t="inlineStr"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="21" t="inlineStr">
+        <is>
+          <t>3986118096</t>
+        </is>
+      </c>
+      <c r="B39" s="21" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D39" s="21" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="E39" s="21" t="inlineStr">
+        <is>
+          <t>Irving, TX</t>
+        </is>
+      </c>
+      <c r="F39" s="18" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="G39" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H39" s="21" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I39" s="21" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J39" s="8" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, machine learning, c, Title match: Software Engineer</t>
+        </is>
+      </c>
+      <c r="K39" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L39" s="21" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M39" s="21" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M37"/>
+  <autoFilter ref="A1:M39"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -2934,6 +3066,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Job Matches" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Matches'!$A$1:$M$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Matches'!$A$1:$M$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -176,6 +176,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -548,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -634,12 +640,12 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>4406952064</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -649,12 +655,12 @@
           <t>DevSecOps Intern</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="20" t="inlineStr">
         <is>
           <t>Modern Technology Solutions, Inc. (MTSI)</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="20" t="inlineStr">
         <is>
           <t>Huntsville, AL</t>
         </is>
@@ -669,12 +675,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H2" s="17" t="inlineStr">
+      <c r="H2" s="20" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="I2" s="17" t="inlineStr">
+      <c r="I2" s="20" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -689,20 +695,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L2" s="17" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M2" s="17" t="inlineStr"/>
+      <c r="L2" s="20" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M2" s="20" t="inlineStr"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>4405630173</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -712,12 +718,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t>DLRdmv®</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="21" t="inlineStr">
         <is>
           <t>Dallas, TX</t>
         </is>
@@ -732,12 +738,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H3" s="16" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I3" s="16" t="inlineStr">
+      <c r="I3" s="21" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -752,20 +758,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L3" s="16" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M3" s="16" t="inlineStr"/>
+      <c r="L3" s="21" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M3" s="21" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>4287414862</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -775,12 +781,12 @@
           <t>[Online Assessment]Software Development Engineer Intern (Network Automation)- 2026 Summer (BS/ MS)</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>ByteDance</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -795,12 +801,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="20" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I4" s="17" t="inlineStr">
+      <c r="I4" s="20" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -815,20 +821,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M4" s="17" t="inlineStr"/>
+      <c r="L4" s="20" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M4" s="20" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>4309805269</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -838,12 +844,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>Delaware, United States</t>
         </is>
@@ -858,12 +864,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H5" s="16" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="I5" s="16" t="inlineStr">
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -878,20 +884,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L5" s="16" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M5" s="16" t="inlineStr"/>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M5" s="21" t="inlineStr"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>4371812987</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -901,12 +907,12 @@
           <t>Software Development Engineer Fall Intern - Military Veteran</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -921,12 +927,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -941,20 +947,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M6" s="17" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>4274682122</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -964,12 +970,12 @@
           <t>Software Engineer Intern (Data Ecosystem) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -984,12 +990,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1004,20 +1010,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L7" s="16" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M7" s="16" t="inlineStr"/>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>4283848614</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1027,12 +1033,12 @@
           <t>[Online Assessment] Software Engineer Intern (Recommendation Infrastructure) - 2026 Fall (BS/ MS)</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1047,12 +1053,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I8" s="17" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1067,20 +1073,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M8" s="17" t="inlineStr"/>
+      <c r="L8" s="20" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M8" s="20" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>4411790844</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1090,12 +1096,12 @@
           <t>Software Engineer Intern (Infrastructure Automation) - Fall 2026</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -1110,12 +1116,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I9" s="16" t="inlineStr">
+      <c r="I9" s="21" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1130,20 +1136,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L9" s="16" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M9" s="16" t="inlineStr"/>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M9" s="21" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>4332425058</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1153,12 +1159,12 @@
           <t>Software Development Engineer Internship - Fall 2026 (US)</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1173,12 +1179,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1193,20 +1199,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L10" s="17" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M10" s="17" t="inlineStr"/>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>4323643644</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1216,12 +1222,12 @@
           <t>[Online Assessment] Software Engineer Intern (Recommendation Infrastructure) - 2026 Summer (BS/ MS)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1236,12 +1242,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I11" s="16" t="inlineStr">
+      <c r="I11" s="21" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1256,20 +1262,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L11" s="16" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M11" s="16" t="inlineStr"/>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M11" s="21" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>4320849104</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1279,12 +1285,12 @@
           <t>Software Engineer Intern (Commerce Ads) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1299,12 +1305,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1319,20 +1325,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M12" s="17" t="inlineStr"/>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>4401686051</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1342,12 +1348,12 @@
           <t>Front End Software Engineer</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>Saronic Technologies</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -1362,12 +1368,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I13" s="16" t="inlineStr">
+      <c r="I13" s="21" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1382,20 +1388,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L13" s="16" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M13" s="16" t="inlineStr"/>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M13" s="21" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>4309696652</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1405,12 +1411,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>Rhode Island, United States</t>
         </is>
@@ -1425,12 +1431,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="I14" s="17" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1445,20 +1451,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L14" s="17" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M14" s="17" t="inlineStr"/>
+      <c r="L14" s="20" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M14" s="20" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>4309804319</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1468,12 +1474,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>Colorado, United States</t>
         </is>
@@ -1488,12 +1494,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="I15" s="16" t="inlineStr">
+      <c r="I15" s="21" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1508,20 +1514,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M15" s="16" t="inlineStr"/>
+      <c r="L15" s="21" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M15" s="21" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>4410271532</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1531,12 +1537,12 @@
           <t>Associate Developer</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>HealthStream</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>Nashville, TN</t>
         </is>
@@ -1551,12 +1557,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1571,20 +1577,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L16" s="17" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M16" s="17" t="inlineStr"/>
+      <c r="L16" s="20" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M16" s="20" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>4304445726</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1594,12 +1600,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>Oregon, United States</t>
         </is>
@@ -1614,12 +1620,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="I17" s="21" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1634,20 +1640,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L17" s="16" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M17" s="16" t="inlineStr"/>
+      <c r="L17" s="21" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M17" s="21" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>4342036151</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1657,12 +1663,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>Modern Treasury</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
@@ -1677,12 +1683,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I18" s="17" t="inlineStr">
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1697,20 +1703,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L18" s="17" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M18" s="17" t="inlineStr"/>
+      <c r="L18" s="20" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M18" s="20" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>4304441843</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1720,12 +1726,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>Idaho, United States</t>
         </is>
@@ -1740,12 +1746,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>157</t>
         </is>
       </c>
-      <c r="I19" s="16" t="inlineStr">
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1760,20 +1766,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L19" s="16" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M19" s="16" t="inlineStr"/>
+      <c r="L19" s="21" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M19" s="21" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>4408047047</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1783,12 +1789,12 @@
           <t>Computer Sciences - Graduates - AI Training - Las Vegas, US</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>Prolific</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>Las Vegas, NV</t>
         </is>
@@ -1803,12 +1809,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H20" s="17" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I20" s="17" t="inlineStr">
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>Temporary</t>
         </is>
@@ -1823,20 +1829,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L20" s="17" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M20" s="17" t="inlineStr"/>
+      <c r="L20" s="20" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M20" s="20" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>4304444837</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1846,12 +1852,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>New Jersey, United States</t>
         </is>
@@ -1866,12 +1872,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I21" s="16" t="inlineStr">
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1886,20 +1892,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L21" s="16" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M21" s="16" t="inlineStr"/>
+      <c r="L21" s="21" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M21" s="21" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>4405641326</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1909,12 +1915,12 @@
           <t>Full-stack Engineer</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>PartnerTap</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1929,12 +1935,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H22" s="17" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I22" s="17" t="inlineStr">
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1949,20 +1955,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L22" s="17" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M22" s="17" t="inlineStr"/>
+      <c r="L22" s="20" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M22" s="20" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>4341020900</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1972,12 +1978,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>PlanIT Group, LLC</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -1992,12 +1998,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I23" s="16" t="inlineStr">
+      <c r="I23" s="21" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
@@ -2012,20 +2018,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L23" s="16" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M23" s="16" t="inlineStr"/>
+      <c r="L23" s="21" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M23" s="21" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>4304450637</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2035,12 +2041,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -2055,12 +2061,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H24" s="17" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I24" s="17" t="inlineStr">
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2075,20 +2081,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L24" s="17" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M24" s="17" t="inlineStr"/>
+      <c r="L24" s="20" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M24" s="20" t="inlineStr"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>4304451654</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2098,12 +2104,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>Utah, United States</t>
         </is>
@@ -2118,12 +2124,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I25" s="16" t="inlineStr">
+      <c r="I25" s="21" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2138,20 +2144,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L25" s="16" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M25" s="16" t="inlineStr"/>
+      <c r="L25" s="21" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M25" s="21" t="inlineStr"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>4413745880</t>
         </is>
       </c>
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2161,12 +2167,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>Crate &amp; Barrel</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>Northbrook, IL</t>
         </is>
@@ -2181,12 +2187,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H26" s="17" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I26" s="17" t="inlineStr">
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2201,20 +2207,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L26" s="17" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M26" s="17" t="inlineStr"/>
+      <c r="L26" s="20" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M26" s="20" t="inlineStr"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>4304438841</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2224,12 +2230,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>Connecticut, United States</t>
         </is>
@@ -2244,12 +2250,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H27" s="16" t="inlineStr">
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I27" s="16" t="inlineStr">
+      <c r="I27" s="21" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2264,20 +2270,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L27" s="16" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M27" s="16" t="inlineStr"/>
+      <c r="L27" s="21" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M27" s="21" t="inlineStr"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>4393215930</t>
         </is>
       </c>
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2287,12 +2293,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D28" s="17" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>Transcend</t>
         </is>
       </c>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>California, United States</t>
         </is>
@@ -2307,12 +2313,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H28" s="17" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I28" s="17" t="inlineStr">
+      <c r="I28" s="20" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2327,20 +2333,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L28" s="17" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M28" s="17" t="inlineStr"/>
+      <c r="L28" s="20" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M28" s="20" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>4304445723</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2350,12 +2356,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>Illinois, United States</t>
         </is>
@@ -2370,12 +2376,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H29" s="16" t="inlineStr">
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>198</t>
         </is>
       </c>
-      <c r="I29" s="16" t="inlineStr">
+      <c r="I29" s="21" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2390,20 +2396,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L29" s="16" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M29" s="16" t="inlineStr"/>
+      <c r="L29" s="21" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M29" s="21" t="inlineStr"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>4396380649</t>
         </is>
       </c>
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2413,12 +2419,12 @@
           <t>Full-Stack Developer Intern, Music &amp; Audio</t>
         </is>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>Melotech</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
@@ -2433,12 +2439,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H30" s="17" t="inlineStr">
+      <c r="H30" s="20" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I30" s="17" t="inlineStr">
+      <c r="I30" s="20" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -2453,20 +2459,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L30" s="17" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M30" s="17" t="inlineStr"/>
+      <c r="L30" s="20" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M30" s="20" t="inlineStr"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>4304454025</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2476,12 +2482,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -2496,12 +2502,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H31" s="16" t="inlineStr">
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I31" s="16" t="inlineStr">
+      <c r="I31" s="21" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2516,20 +2522,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L31" s="16" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M31" s="16" t="inlineStr"/>
+      <c r="L31" s="21" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M31" s="21" t="inlineStr"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>4309802287</t>
         </is>
       </c>
-      <c r="B32" s="17" t="inlineStr">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2539,12 +2545,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D32" s="17" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E32" s="17" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>New Jersey, United States</t>
         </is>
@@ -2559,12 +2565,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H32" s="17" t="inlineStr">
+      <c r="H32" s="20" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I32" s="17" t="inlineStr">
+      <c r="I32" s="20" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2579,20 +2585,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L32" s="17" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M32" s="17" t="inlineStr"/>
+      <c r="L32" s="20" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M32" s="20" t="inlineStr"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>4309694880</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2602,12 +2608,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D33" s="21" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="E33" s="21" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -2622,12 +2628,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H33" s="16" t="inlineStr">
+      <c r="H33" s="21" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I33" s="16" t="inlineStr">
+      <c r="I33" s="21" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2642,20 +2648,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L33" s="16" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M33" s="16" t="inlineStr"/>
+      <c r="L33" s="21" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M33" s="21" t="inlineStr"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>4411274012</t>
         </is>
       </c>
-      <c r="B34" s="17" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2665,12 +2671,12 @@
           <t>Junior UI Developer</t>
         </is>
       </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>General Dynamics Information Technology</t>
         </is>
       </c>
-      <c r="E34" s="17" t="inlineStr">
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -2685,12 +2691,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H34" s="17" t="inlineStr">
+      <c r="H34" s="20" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I34" s="17" t="inlineStr">
+      <c r="I34" s="20" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2705,20 +2711,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L34" s="17" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M34" s="17" t="inlineStr"/>
+      <c r="L34" s="20" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M34" s="20" t="inlineStr"/>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>4264562292</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2728,12 +2734,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D35" s="21" t="inlineStr">
         <is>
           <t>Cymertek Corporation</t>
         </is>
       </c>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="E35" s="21" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
@@ -2748,12 +2754,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H35" s="16" t="inlineStr">
+      <c r="H35" s="21" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="I35" s="16" t="inlineStr">
+      <c r="I35" s="21" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2768,20 +2774,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L35" s="16" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M35" s="16" t="inlineStr"/>
+      <c r="L35" s="21" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M35" s="21" t="inlineStr"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>4417482675</t>
         </is>
       </c>
-      <c r="B36" s="17" t="inlineStr">
+      <c r="B36" s="20" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2791,12 +2797,12 @@
           <t>Software Developer I</t>
         </is>
       </c>
-      <c r="D36" s="17" t="inlineStr">
+      <c r="D36" s="20" t="inlineStr">
         <is>
           <t>El Paso Water</t>
         </is>
       </c>
-      <c r="E36" s="17" t="inlineStr">
+      <c r="E36" s="20" t="inlineStr">
         <is>
           <t>El Paso, TX</t>
         </is>
@@ -2811,12 +2817,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H36" s="17" t="inlineStr">
+      <c r="H36" s="20" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="I36" s="17" t="inlineStr">
+      <c r="I36" s="20" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2831,20 +2837,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L36" s="17" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M36" s="17" t="inlineStr"/>
+      <c r="L36" s="20" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M36" s="20" t="inlineStr"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>4416508200</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2854,12 +2860,12 @@
           <t>Software Development Engineer in Test Intern (Global E-Commerce) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D37" s="21" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="E37" s="21" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -2874,12 +2880,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H37" s="16" t="inlineStr">
+      <c r="H37" s="21" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I37" s="16" t="inlineStr">
+      <c r="I37" s="21" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -2894,12 +2900,12 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L37" s="16" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M37" s="16" t="inlineStr"/>
+      <c r="L37" s="21" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M37" s="21" t="inlineStr"/>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
@@ -3027,8 +3033,638 @@
       </c>
       <c r="M39" s="21" t="inlineStr"/>
     </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="22" t="inlineStr">
+        <is>
+          <t>4309808244</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D40" s="22" t="inlineStr">
+        <is>
+          <t>DataAnnotation</t>
+        </is>
+      </c>
+      <c r="E40" s="22" t="inlineStr">
+        <is>
+          <t>Massachusetts, United States</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H40" s="22" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="I40" s="22" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, html, sql, full stack, c++, Title match: Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L40" s="22" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M40" s="22" t="inlineStr"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="23" t="inlineStr">
+        <is>
+          <t>4362173625</t>
+        </is>
+      </c>
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="inlineStr">
+        <is>
+          <t>Empower Sleep</t>
+        </is>
+      </c>
+      <c r="E41" s="23" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H41" s="23" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I41" s="23" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J41" s="8" t="inlineStr">
+        <is>
+          <t>Skills: react, aws, api, git, full stack, backend, Title match: Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="K41" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L41" s="23" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M41" s="23" t="inlineStr"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t>4309812093</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D42" s="22" t="inlineStr">
+        <is>
+          <t>DataAnnotation</t>
+        </is>
+      </c>
+      <c r="E42" s="22" t="inlineStr">
+        <is>
+          <t>Florida, United States</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H42" s="22" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="I42" s="22" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, html, sql, full stack, c++, Title match: Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L42" s="22" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M42" s="22" t="inlineStr"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="23" t="inlineStr">
+        <is>
+          <t>4391759914</t>
+        </is>
+      </c>
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>QA Engineering Internship</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="inlineStr">
+        <is>
+          <t>Chartbeat</t>
+        </is>
+      </c>
+      <c r="E43" s="23" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H43" s="23" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="I43" s="23" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="J43" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, react, rest, api, git, Location: Austin, TX, Title match: QA Engineering Internship</t>
+        </is>
+      </c>
+      <c r="K43" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L43" s="23" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M43" s="23" t="inlineStr"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>4412855678</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer</t>
+        </is>
+      </c>
+      <c r="D44" s="22" t="inlineStr">
+        <is>
+          <t>UST</t>
+        </is>
+      </c>
+      <c r="E44" s="22" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA</t>
+        </is>
+      </c>
+      <c r="F44" s="18" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="G44" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H44" s="22" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I44" s="22" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, aws, rest, api, git, sql</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L44" s="22" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M44" s="22" t="inlineStr"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="23" t="inlineStr">
+        <is>
+          <t>4309805219</t>
+        </is>
+      </c>
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D45" s="23" t="inlineStr">
+        <is>
+          <t>DataAnnotation</t>
+        </is>
+      </c>
+      <c r="E45" s="23" t="inlineStr">
+        <is>
+          <t>Washington, DC</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H45" s="23" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I45" s="23" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J45" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, html, sql, full stack, c++, Location: Washington, DC, Title match: Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="K45" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L45" s="23" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M45" s="23" t="inlineStr"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>4409726429</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Data Science Intern</t>
+        </is>
+      </c>
+      <c r="D46" s="22" t="inlineStr">
+        <is>
+          <t>Rundoo</t>
+        </is>
+      </c>
+      <c r="E46" s="22" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F46" s="18" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="G46" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H46" s="22" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I46" s="22" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, api, git, c, Title match: Data Science Intern</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L46" s="22" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M46" s="22" t="inlineStr"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="23" t="inlineStr">
+        <is>
+          <t>4305671729</t>
+        </is>
+      </c>
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>DoD SkillBridge Internship/Fellowship Opportunity Application (U.S. Military Only)</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="inlineStr">
+        <is>
+          <t>Onsights</t>
+        </is>
+      </c>
+      <c r="E47" s="23" t="inlineStr">
+        <is>
+          <t>Washington, DC</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="G47" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H47" s="23" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I47" s="23" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="J47" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, react, sql, machine learning, c++, c, Location: Washington, DC, Title match: DoD SkillBridge Internship/Fellowship Opportunity Application (U.S. Military Only)</t>
+        </is>
+      </c>
+      <c r="K47" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L47" s="23" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M47" s="23" t="inlineStr"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>4414096220</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Visualization Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D48" s="22" t="inlineStr">
+        <is>
+          <t>Leidos</t>
+        </is>
+      </c>
+      <c r="E48" s="22" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H48" s="22" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I48" s="22" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, aws, rest, api, git, c++, Title match: Visualization Engineer Intern</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L48" s="22" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M48" s="22" t="inlineStr"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="23" t="inlineStr">
+        <is>
+          <t>4361076044</t>
+        </is>
+      </c>
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>GenAI Engineering Intern  - SkillBridge (Remote)</t>
+        </is>
+      </c>
+      <c r="D49" s="23" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="E49" s="23" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H49" s="23" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I49" s="23" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J49" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, aws, rest, api, full stack, c, Title match: GenAI Engineering Intern  - SkillBridge (Remote)</t>
+        </is>
+      </c>
+      <c r="K49" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L49" s="23" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M49" s="23" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M39"/>
+  <autoFilter ref="A1:M49"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -3068,6 +3704,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Job Matches" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Matches'!$A$1:$M$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Matches'!$A$1:$M$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -176,6 +176,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -554,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -640,12 +646,12 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="20" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>4406952064</t>
         </is>
       </c>
-      <c r="B2" s="20" t="inlineStr">
+      <c r="B2" s="22" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -655,12 +661,12 @@
           <t>DevSecOps Intern</t>
         </is>
       </c>
-      <c r="D2" s="20" t="inlineStr">
+      <c r="D2" s="22" t="inlineStr">
         <is>
           <t>Modern Technology Solutions, Inc. (MTSI)</t>
         </is>
       </c>
-      <c r="E2" s="20" t="inlineStr">
+      <c r="E2" s="22" t="inlineStr">
         <is>
           <t>Huntsville, AL</t>
         </is>
@@ -675,12 +681,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H2" s="20" t="inlineStr">
+      <c r="H2" s="22" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="I2" s="20" t="inlineStr">
+      <c r="I2" s="22" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -695,20 +701,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L2" s="20" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M2" s="20" t="inlineStr"/>
+      <c r="L2" s="22" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M2" s="22" t="inlineStr"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>4405630173</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -718,12 +724,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D3" s="21" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t>DLRdmv®</t>
         </is>
       </c>
-      <c r="E3" s="21" t="inlineStr">
+      <c r="E3" s="23" t="inlineStr">
         <is>
           <t>Dallas, TX</t>
         </is>
@@ -738,12 +744,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H3" s="21" t="inlineStr">
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I3" s="21" t="inlineStr">
+      <c r="I3" s="23" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -758,20 +764,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L3" s="21" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M3" s="21" t="inlineStr"/>
+      <c r="L3" s="23" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M3" s="23" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>4287414862</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -781,12 +787,12 @@
           <t>[Online Assessment]Software Development Engineer Intern (Network Automation)- 2026 Summer (BS/ MS)</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="22" t="inlineStr">
         <is>
           <t>ByteDance</t>
         </is>
       </c>
-      <c r="E4" s="20" t="inlineStr">
+      <c r="E4" s="22" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -801,12 +807,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H4" s="20" t="inlineStr">
+      <c r="H4" s="22" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I4" s="20" t="inlineStr">
+      <c r="I4" s="22" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -821,20 +827,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L4" s="20" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M4" s="20" t="inlineStr"/>
+      <c r="L4" s="22" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M4" s="22" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>4309805269</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -844,12 +850,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>Delaware, United States</t>
         </is>
@@ -864,12 +870,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H5" s="21" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="I5" s="21" t="inlineStr">
+      <c r="I5" s="23" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -884,20 +890,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M5" s="21" t="inlineStr"/>
+      <c r="L5" s="23" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M5" s="23" t="inlineStr"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>4371812987</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -907,12 +913,12 @@
           <t>Software Development Engineer Fall Intern - Military Veteran</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -927,12 +933,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="H6" s="22" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="I6" s="20" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -947,20 +953,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L6" s="20" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M6" s="20" t="inlineStr"/>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M6" s="22" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>4274682122</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -970,12 +976,12 @@
           <t>Software Engineer Intern (Data Ecosystem) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -990,12 +996,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I7" s="21" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1010,20 +1016,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L7" s="21" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M7" s="21" t="inlineStr"/>
+      <c r="L7" s="23" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M7" s="23" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>4283848614</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1033,12 +1039,12 @@
           <t>[Online Assessment] Software Engineer Intern (Recommendation Infrastructure) - 2026 Fall (BS/ MS)</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1053,12 +1059,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr">
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1073,20 +1079,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L8" s="20" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M8" s="20" t="inlineStr"/>
+      <c r="L8" s="22" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M8" s="22" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>4411790844</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1096,12 +1102,12 @@
           <t>Software Engineer Intern (Infrastructure Automation) - Fall 2026</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -1116,12 +1122,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I9" s="21" t="inlineStr">
+      <c r="I9" s="23" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1136,20 +1142,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M9" s="21" t="inlineStr"/>
+      <c r="L9" s="23" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M9" s="23" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>4332425058</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1159,12 +1165,12 @@
           <t>Software Development Engineer Internship - Fall 2026 (US)</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1179,12 +1185,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I10" s="20" t="inlineStr">
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1199,20 +1205,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L10" s="20" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M10" s="20" t="inlineStr"/>
+      <c r="L10" s="22" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M10" s="22" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>4323643644</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1222,12 +1228,12 @@
           <t>[Online Assessment] Software Engineer Intern (Recommendation Infrastructure) - 2026 Summer (BS/ MS)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1242,12 +1248,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I11" s="21" t="inlineStr">
+      <c r="I11" s="23" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1262,20 +1268,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L11" s="21" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M11" s="21" t="inlineStr"/>
+      <c r="L11" s="23" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M11" s="23" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>4320849104</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1285,12 +1291,12 @@
           <t>Software Engineer Intern (Commerce Ads) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1305,12 +1311,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr">
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1325,20 +1331,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L12" s="20" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M12" s="20" t="inlineStr"/>
+      <c r="L12" s="22" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M12" s="22" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>4401686051</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1348,12 +1354,12 @@
           <t>Front End Software Engineer</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>Saronic Technologies</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -1368,12 +1374,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="H13" s="23" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I13" s="21" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1388,20 +1394,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M13" s="21" t="inlineStr"/>
+      <c r="L13" s="23" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M13" s="23" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>4309696652</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1411,12 +1417,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>Rhode Island, United States</t>
         </is>
@@ -1431,12 +1437,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="I14" s="20" t="inlineStr">
+      <c r="I14" s="22" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1451,20 +1457,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L14" s="20" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M14" s="20" t="inlineStr"/>
+      <c r="L14" s="22" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M14" s="22" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>4309804319</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1474,12 +1480,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>Colorado, United States</t>
         </is>
@@ -1494,12 +1500,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H15" s="21" t="inlineStr">
+      <c r="H15" s="23" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="I15" s="21" t="inlineStr">
+      <c r="I15" s="23" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1514,20 +1520,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L15" s="21" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M15" s="21" t="inlineStr"/>
+      <c r="L15" s="23" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M15" s="23" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>4410271532</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1537,12 +1543,12 @@
           <t>Associate Developer</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>HealthStream</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>Nashville, TN</t>
         </is>
@@ -1557,12 +1563,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H16" s="20" t="inlineStr">
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I16" s="20" t="inlineStr">
+      <c r="I16" s="22" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1577,20 +1583,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L16" s="20" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M16" s="20" t="inlineStr"/>
+      <c r="L16" s="22" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M16" s="22" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t>4304445726</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1600,12 +1606,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>Oregon, United States</t>
         </is>
@@ -1620,12 +1626,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H17" s="21" t="inlineStr">
+      <c r="H17" s="23" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="I17" s="21" t="inlineStr">
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1640,20 +1646,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L17" s="21" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M17" s="21" t="inlineStr"/>
+      <c r="L17" s="23" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M17" s="23" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>4342036151</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1663,12 +1669,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>Modern Treasury</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
@@ -1683,12 +1689,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H18" s="20" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I18" s="20" t="inlineStr">
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1703,20 +1709,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L18" s="20" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M18" s="20" t="inlineStr"/>
+      <c r="L18" s="22" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M18" s="22" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="21" t="inlineStr">
+      <c r="A19" s="23" t="inlineStr">
         <is>
           <t>4304441843</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1726,12 +1732,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>Idaho, United States</t>
         </is>
@@ -1746,12 +1752,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H19" s="21" t="inlineStr">
+      <c r="H19" s="23" t="inlineStr">
         <is>
           <t>157</t>
         </is>
       </c>
-      <c r="I19" s="21" t="inlineStr">
+      <c r="I19" s="23" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1766,20 +1772,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L19" s="21" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M19" s="21" t="inlineStr"/>
+      <c r="L19" s="23" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M19" s="23" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="22" t="inlineStr">
         <is>
           <t>4408047047</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1789,12 +1795,12 @@
           <t>Computer Sciences - Graduates - AI Training - Las Vegas, US</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>Prolific</t>
         </is>
       </c>
-      <c r="E20" s="20" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>Las Vegas, NV</t>
         </is>
@@ -1809,12 +1815,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H20" s="20" t="inlineStr">
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I20" s="20" t="inlineStr">
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>Temporary</t>
         </is>
@@ -1829,20 +1835,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L20" s="20" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M20" s="20" t="inlineStr"/>
+      <c r="L20" s="22" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M20" s="22" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t>4304444837</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1852,12 +1858,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>New Jersey, United States</t>
         </is>
@@ -1872,12 +1878,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="H21" s="23" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I21" s="21" t="inlineStr">
+      <c r="I21" s="23" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1892,20 +1898,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L21" s="21" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M21" s="21" t="inlineStr"/>
+      <c r="L21" s="23" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M21" s="23" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>4405641326</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1915,12 +1921,12 @@
           <t>Full-stack Engineer</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>PartnerTap</t>
         </is>
       </c>
-      <c r="E22" s="20" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1935,12 +1941,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H22" s="20" t="inlineStr">
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I22" s="20" t="inlineStr">
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1955,20 +1961,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L22" s="20" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M22" s="20" t="inlineStr"/>
+      <c r="L22" s="22" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M22" s="22" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="23" t="inlineStr">
         <is>
           <t>4341020900</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1978,12 +1984,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>PlanIT Group, LLC</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -1998,12 +2004,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H23" s="21" t="inlineStr">
+      <c r="H23" s="23" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I23" s="21" t="inlineStr">
+      <c r="I23" s="23" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
@@ -2018,20 +2024,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L23" s="21" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M23" s="21" t="inlineStr"/>
+      <c r="L23" s="23" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M23" s="23" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>4304450637</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2041,12 +2047,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E24" s="20" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -2061,12 +2067,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H24" s="20" t="inlineStr">
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I24" s="20" t="inlineStr">
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2081,20 +2087,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L24" s="20" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M24" s="20" t="inlineStr"/>
+      <c r="L24" s="22" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M24" s="22" t="inlineStr"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="A25" s="23" t="inlineStr">
         <is>
           <t>4304451654</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2104,12 +2110,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>Utah, United States</t>
         </is>
@@ -2124,12 +2130,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H25" s="21" t="inlineStr">
+      <c r="H25" s="23" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I25" s="21" t="inlineStr">
+      <c r="I25" s="23" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2144,20 +2150,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L25" s="21" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M25" s="21" t="inlineStr"/>
+      <c r="L25" s="23" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M25" s="23" t="inlineStr"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>4413745880</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2167,12 +2173,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>Crate &amp; Barrel</t>
         </is>
       </c>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>Northbrook, IL</t>
         </is>
@@ -2187,12 +2193,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H26" s="20" t="inlineStr">
+      <c r="H26" s="22" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I26" s="20" t="inlineStr">
+      <c r="I26" s="22" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2207,20 +2213,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L26" s="20" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M26" s="20" t="inlineStr"/>
+      <c r="L26" s="22" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M26" s="22" t="inlineStr"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="21" t="inlineStr">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>4304438841</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2230,12 +2236,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>Connecticut, United States</t>
         </is>
@@ -2250,12 +2256,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H27" s="21" t="inlineStr">
+      <c r="H27" s="23" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I27" s="21" t="inlineStr">
+      <c r="I27" s="23" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2270,20 +2276,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L27" s="21" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M27" s="21" t="inlineStr"/>
+      <c r="L27" s="23" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M27" s="23" t="inlineStr"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="22" t="inlineStr">
         <is>
           <t>4393215930</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2293,12 +2299,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>Transcend</t>
         </is>
       </c>
-      <c r="E28" s="20" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>California, United States</t>
         </is>
@@ -2313,12 +2319,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H28" s="20" t="inlineStr">
+      <c r="H28" s="22" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I28" s="20" t="inlineStr">
+      <c r="I28" s="22" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2333,20 +2339,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L28" s="20" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M28" s="20" t="inlineStr"/>
+      <c r="L28" s="22" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M28" s="22" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="21" t="inlineStr">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>4304445723</t>
         </is>
       </c>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2356,12 +2362,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>Illinois, United States</t>
         </is>
@@ -2376,12 +2382,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H29" s="21" t="inlineStr">
+      <c r="H29" s="23" t="inlineStr">
         <is>
           <t>198</t>
         </is>
       </c>
-      <c r="I29" s="21" t="inlineStr">
+      <c r="I29" s="23" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2396,20 +2402,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L29" s="21" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M29" s="21" t="inlineStr"/>
+      <c r="L29" s="23" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M29" s="23" t="inlineStr"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="22" t="inlineStr">
         <is>
           <t>4396380649</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2419,12 +2425,12 @@
           <t>Full-Stack Developer Intern, Music &amp; Audio</t>
         </is>
       </c>
-      <c r="D30" s="20" t="inlineStr">
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>Melotech</t>
         </is>
       </c>
-      <c r="E30" s="20" t="inlineStr">
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
@@ -2439,12 +2445,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H30" s="20" t="inlineStr">
+      <c r="H30" s="22" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I30" s="20" t="inlineStr">
+      <c r="I30" s="22" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -2459,20 +2465,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L30" s="20" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M30" s="20" t="inlineStr"/>
+      <c r="L30" s="22" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M30" s="22" t="inlineStr"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="21" t="inlineStr">
+      <c r="A31" s="23" t="inlineStr">
         <is>
           <t>4304454025</t>
         </is>
       </c>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2482,12 +2488,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D31" s="21" t="inlineStr">
+      <c r="D31" s="23" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E31" s="21" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -2502,12 +2508,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H31" s="21" t="inlineStr">
+      <c r="H31" s="23" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I31" s="21" t="inlineStr">
+      <c r="I31" s="23" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2522,20 +2528,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L31" s="21" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M31" s="21" t="inlineStr"/>
+      <c r="L31" s="23" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M31" s="23" t="inlineStr"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="A32" s="22" t="inlineStr">
         <is>
           <t>4309802287</t>
         </is>
       </c>
-      <c r="B32" s="20" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2545,12 +2551,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D32" s="20" t="inlineStr">
+      <c r="D32" s="22" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E32" s="20" t="inlineStr">
+      <c r="E32" s="22" t="inlineStr">
         <is>
           <t>New Jersey, United States</t>
         </is>
@@ -2565,12 +2571,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H32" s="20" t="inlineStr">
+      <c r="H32" s="22" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I32" s="20" t="inlineStr">
+      <c r="I32" s="22" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2585,20 +2591,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L32" s="20" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M32" s="20" t="inlineStr"/>
+      <c r="L32" s="22" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M32" s="22" t="inlineStr"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="21" t="inlineStr">
+      <c r="A33" s="23" t="inlineStr">
         <is>
           <t>4309694880</t>
         </is>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2608,12 +2614,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D33" s="21" t="inlineStr">
+      <c r="D33" s="23" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E33" s="21" t="inlineStr">
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -2628,12 +2634,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H33" s="21" t="inlineStr">
+      <c r="H33" s="23" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I33" s="21" t="inlineStr">
+      <c r="I33" s="23" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2648,20 +2654,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L33" s="21" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M33" s="21" t="inlineStr"/>
+      <c r="L33" s="23" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M33" s="23" t="inlineStr"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>4411274012</t>
         </is>
       </c>
-      <c r="B34" s="20" t="inlineStr">
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2671,12 +2677,12 @@
           <t>Junior UI Developer</t>
         </is>
       </c>
-      <c r="D34" s="20" t="inlineStr">
+      <c r="D34" s="22" t="inlineStr">
         <is>
           <t>General Dynamics Information Technology</t>
         </is>
       </c>
-      <c r="E34" s="20" t="inlineStr">
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -2691,12 +2697,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H34" s="20" t="inlineStr">
+      <c r="H34" s="22" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I34" s="20" t="inlineStr">
+      <c r="I34" s="22" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2711,20 +2717,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L34" s="20" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M34" s="20" t="inlineStr"/>
+      <c r="L34" s="22" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M34" s="22" t="inlineStr"/>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="21" t="inlineStr">
+      <c r="A35" s="23" t="inlineStr">
         <is>
           <t>4264562292</t>
         </is>
       </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2734,12 +2740,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D35" s="21" t="inlineStr">
+      <c r="D35" s="23" t="inlineStr">
         <is>
           <t>Cymertek Corporation</t>
         </is>
       </c>
-      <c r="E35" s="21" t="inlineStr">
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
@@ -2754,12 +2760,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H35" s="21" t="inlineStr">
+      <c r="H35" s="23" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="I35" s="21" t="inlineStr">
+      <c r="I35" s="23" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2774,20 +2780,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L35" s="21" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M35" s="21" t="inlineStr"/>
+      <c r="L35" s="23" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M35" s="23" t="inlineStr"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="20" t="inlineStr">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>4417482675</t>
         </is>
       </c>
-      <c r="B36" s="20" t="inlineStr">
+      <c r="B36" s="22" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2797,12 +2803,12 @@
           <t>Software Developer I</t>
         </is>
       </c>
-      <c r="D36" s="20" t="inlineStr">
+      <c r="D36" s="22" t="inlineStr">
         <is>
           <t>El Paso Water</t>
         </is>
       </c>
-      <c r="E36" s="20" t="inlineStr">
+      <c r="E36" s="22" t="inlineStr">
         <is>
           <t>El Paso, TX</t>
         </is>
@@ -2817,12 +2823,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H36" s="20" t="inlineStr">
+      <c r="H36" s="22" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="I36" s="20" t="inlineStr">
+      <c r="I36" s="22" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2837,20 +2843,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L36" s="20" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M36" s="20" t="inlineStr"/>
+      <c r="L36" s="22" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M36" s="22" t="inlineStr"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="21" t="inlineStr">
+      <c r="A37" s="23" t="inlineStr">
         <is>
           <t>4416508200</t>
         </is>
       </c>
-      <c r="B37" s="21" t="inlineStr">
+      <c r="B37" s="23" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2860,12 +2866,12 @@
           <t>Software Development Engineer in Test Intern (Global E-Commerce) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D37" s="21" t="inlineStr">
+      <c r="D37" s="23" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E37" s="21" t="inlineStr">
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -2880,12 +2886,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H37" s="21" t="inlineStr">
+      <c r="H37" s="23" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I37" s="21" t="inlineStr">
+      <c r="I37" s="23" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -2900,20 +2906,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L37" s="21" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M37" s="21" t="inlineStr"/>
+      <c r="L37" s="23" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M37" s="23" t="inlineStr"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="20" t="inlineStr">
+      <c r="A38" s="22" t="inlineStr">
         <is>
           <t>4309809191</t>
         </is>
       </c>
-      <c r="B38" s="20" t="inlineStr">
+      <c r="B38" s="22" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
@@ -2923,12 +2929,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D38" s="20" t="inlineStr">
+      <c r="D38" s="22" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E38" s="20" t="inlineStr">
+      <c r="E38" s="22" t="inlineStr">
         <is>
           <t>Ohio, United States</t>
         </is>
@@ -2943,12 +2949,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H38" s="20" t="inlineStr">
+      <c r="H38" s="22" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="I38" s="20" t="inlineStr">
+      <c r="I38" s="22" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2963,20 +2969,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L38" s="20" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M38" s="20" t="inlineStr"/>
+      <c r="L38" s="22" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M38" s="22" t="inlineStr"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="21" t="inlineStr">
+      <c r="A39" s="23" t="inlineStr">
         <is>
           <t>3986118096</t>
         </is>
       </c>
-      <c r="B39" s="21" t="inlineStr">
+      <c r="B39" s="23" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
@@ -2986,12 +2992,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D39" s="21" t="inlineStr">
+      <c r="D39" s="23" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E39" s="21" t="inlineStr">
+      <c r="E39" s="23" t="inlineStr">
         <is>
           <t>Irving, TX</t>
         </is>
@@ -3006,12 +3012,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H39" s="21" t="inlineStr">
+      <c r="H39" s="23" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I39" s="21" t="inlineStr">
+      <c r="I39" s="23" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3026,12 +3032,12 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L39" s="21" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M39" s="21" t="inlineStr"/>
+      <c r="L39" s="23" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M39" s="23" t="inlineStr"/>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="22" t="inlineStr">
@@ -3663,8 +3669,701 @@
       </c>
       <c r="M49" s="23" t="inlineStr"/>
     </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="24" t="inlineStr">
+        <is>
+          <t>4417553585</t>
+        </is>
+      </c>
+      <c r="B50" s="24" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Entry-Level Software Engineer | Remote</t>
+        </is>
+      </c>
+      <c r="D50" s="24" t="inlineStr">
+        <is>
+          <t>Crossing Hurdles</t>
+        </is>
+      </c>
+      <c r="E50" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H50" s="24" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I50" s="24" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>Skills: javascript, react, node, api, sql, backend, Title match: Entry-Level Software Engineer | Remote</t>
+        </is>
+      </c>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L50" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M50" s="24" t="inlineStr"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="25" t="inlineStr">
+        <is>
+          <t>4309699451</t>
+        </is>
+      </c>
+      <c r="B51" s="25" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D51" s="25" t="inlineStr">
+        <is>
+          <t>DataAnnotation</t>
+        </is>
+      </c>
+      <c r="E51" s="25" t="inlineStr">
+        <is>
+          <t>Washington, United States</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="G51" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H51" s="25" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="I51" s="25" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J51" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, html, sql, full stack, c++, Location: Washington, United States, Title match: Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="K51" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L51" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M51" s="25" t="inlineStr"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="24" t="inlineStr">
+        <is>
+          <t>4406945262</t>
+        </is>
+      </c>
+      <c r="B52" s="24" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>DevSecOps Intern</t>
+        </is>
+      </c>
+      <c r="D52" s="24" t="inlineStr">
+        <is>
+          <t>Modern Technology Solutions, Inc. (MTSI)</t>
+        </is>
+      </c>
+      <c r="E52" s="24" t="inlineStr">
+        <is>
+          <t>Niceville, FL</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H52" s="24" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="I52" s="24" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, rest, docker, git, c++, Title match: DevSecOps Intern</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L52" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M52" s="24" t="inlineStr"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="25" t="inlineStr">
+        <is>
+          <t>4407937810</t>
+        </is>
+      </c>
+      <c r="B53" s="25" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>Temporary Intern - Agentic AI &amp; Neural-Symbolic Systems (Healthcare)</t>
+        </is>
+      </c>
+      <c r="D53" s="25" t="inlineStr">
+        <is>
+          <t>Cotiviti</t>
+        </is>
+      </c>
+      <c r="E53" s="25" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F53" s="18" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="G53" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H53" s="25" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I53" s="25" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J53" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, api, c, llm, Title match: Temporary Intern - Agentic AI &amp; Neural-Symbolic Systems (Healthcare)</t>
+        </is>
+      </c>
+      <c r="K53" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L53" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M53" s="25" t="inlineStr"/>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="24" t="inlineStr">
+        <is>
+          <t>4414089997</t>
+        </is>
+      </c>
+      <c r="B54" s="24" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Visualization Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D54" s="24" t="inlineStr">
+        <is>
+          <t>Leidos</t>
+        </is>
+      </c>
+      <c r="E54" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H54" s="24" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I54" s="24" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, aws, rest, api, git, c++, Title match: Visualization Engineer Intern</t>
+        </is>
+      </c>
+      <c r="K54" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L54" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M54" s="24" t="inlineStr"/>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="25" t="inlineStr">
+        <is>
+          <t>4387443129</t>
+        </is>
+      </c>
+      <c r="B55" s="25" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>2026 Interns</t>
+        </is>
+      </c>
+      <c r="D55" s="25" t="inlineStr">
+        <is>
+          <t>Givelify</t>
+        </is>
+      </c>
+      <c r="E55" s="25" t="inlineStr">
+        <is>
+          <t>Dallas, TX</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H55" s="25" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I55" s="25" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="J55" s="8" t="inlineStr">
+        <is>
+          <t>Skills: c, agile, Location: Dallas, TX, Title match: 2026 Interns</t>
+        </is>
+      </c>
+      <c r="K55" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L55" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M55" s="25" t="inlineStr"/>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="24" t="inlineStr">
+        <is>
+          <t>4337980765</t>
+        </is>
+      </c>
+      <c r="B56" s="24" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Submitting for a General Internship Application</t>
+        </is>
+      </c>
+      <c r="D56" s="24" t="inlineStr">
+        <is>
+          <t>Chainguard</t>
+        </is>
+      </c>
+      <c r="E56" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F56" s="18" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="G56" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H56" s="24" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I56" s="24" t="inlineStr">
+        <is>
+          <t>Volunteer</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>Skills: api, c, express, Title match: Submitting for a General Internship Application</t>
+        </is>
+      </c>
+      <c r="K56" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L56" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M56" s="24" t="inlineStr"/>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="25" t="inlineStr">
+        <is>
+          <t>4417030460</t>
+        </is>
+      </c>
+      <c r="B57" s="25" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>AI Researcher Intern</t>
+        </is>
+      </c>
+      <c r="D57" s="25" t="inlineStr">
+        <is>
+          <t>BioSpace</t>
+        </is>
+      </c>
+      <c r="E57" s="25" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H57" s="25" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="I57" s="25" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J57" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, api, docker, c, express, llm, Title match: AI Researcher Intern</t>
+        </is>
+      </c>
+      <c r="K57" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L57" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M57" s="25" t="inlineStr"/>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="24" t="inlineStr">
+        <is>
+          <t>4406930916</t>
+        </is>
+      </c>
+      <c r="B58" s="24" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>DevSecOps Intern</t>
+        </is>
+      </c>
+      <c r="D58" s="24" t="inlineStr">
+        <is>
+          <t>Modern Technology Solutions, Inc. (MTSI)</t>
+        </is>
+      </c>
+      <c r="E58" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H58" s="24" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I58" s="24" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, rest, docker, git, c++, Title match: DevSecOps Intern</t>
+        </is>
+      </c>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L58" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M58" s="24" t="inlineStr"/>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="25" t="inlineStr">
+        <is>
+          <t>4385798937</t>
+        </is>
+      </c>
+      <c r="B59" s="25" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>Research Intern on Generative and Protective AI for Content Creation</t>
+        </is>
+      </c>
+      <c r="D59" s="25" t="inlineStr">
+        <is>
+          <t>SonyAI</t>
+        </is>
+      </c>
+      <c r="E59" s="25" t="inlineStr">
+        <is>
+          <t>New York, United States</t>
+        </is>
+      </c>
+      <c r="F59" s="18" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="G59" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H59" s="25" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I59" s="25" t="inlineStr">
+        <is>
+          <t>Part-time</t>
+        </is>
+      </c>
+      <c r="J59" s="8" t="inlineStr">
+        <is>
+          <t>Skills: aws, pytorch, machine learning, c, algorithms, Title match: Research Intern on Generative and Protective AI for Content Creation</t>
+        </is>
+      </c>
+      <c r="K59" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L59" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M59" s="25" t="inlineStr"/>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="24" t="inlineStr">
+        <is>
+          <t>4414396950</t>
+        </is>
+      </c>
+      <c r="B60" s="24" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Power Platform Intern</t>
+        </is>
+      </c>
+      <c r="D60" s="24" t="inlineStr">
+        <is>
+          <t>Leidos</t>
+        </is>
+      </c>
+      <c r="E60" s="24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H60" s="24" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="I60" s="24" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>Skills: aws, rest, html, css, git, sql, Title match: Power Platform Intern</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L60" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M60" s="24" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M49"/>
+  <autoFilter ref="A1:M60"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -3714,6 +4413,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Job Matches" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Matches'!$A$1:$M$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Matches'!$A$1:$M$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -193,6 +193,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -560,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,12 +652,12 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>4406952064</t>
         </is>
       </c>
-      <c r="B2" s="22" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -661,12 +667,12 @@
           <t>DevSecOps Intern</t>
         </is>
       </c>
-      <c r="D2" s="22" t="inlineStr">
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>Modern Technology Solutions, Inc. (MTSI)</t>
         </is>
       </c>
-      <c r="E2" s="22" t="inlineStr">
+      <c r="E2" s="24" t="inlineStr">
         <is>
           <t>Huntsville, AL</t>
         </is>
@@ -681,12 +687,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H2" s="22" t="inlineStr">
+      <c r="H2" s="24" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="I2" s="22" t="inlineStr">
+      <c r="I2" s="24" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -701,20 +707,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L2" s="22" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M2" s="22" t="inlineStr"/>
+      <c r="L2" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M2" s="24" t="inlineStr"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>4405630173</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -724,12 +730,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="D3" s="25" t="inlineStr">
         <is>
           <t>DLRdmv®</t>
         </is>
       </c>
-      <c r="E3" s="23" t="inlineStr">
+      <c r="E3" s="25" t="inlineStr">
         <is>
           <t>Dallas, TX</t>
         </is>
@@ -744,12 +750,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H3" s="23" t="inlineStr">
+      <c r="H3" s="25" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I3" s="23" t="inlineStr">
+      <c r="I3" s="25" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -764,20 +770,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L3" s="23" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M3" s="23" t="inlineStr"/>
+      <c r="L3" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M3" s="25" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>4287414862</t>
         </is>
       </c>
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -787,12 +793,12 @@
           <t>[Online Assessment]Software Development Engineer Intern (Network Automation)- 2026 Summer (BS/ MS)</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>ByteDance</t>
         </is>
       </c>
-      <c r="E4" s="22" t="inlineStr">
+      <c r="E4" s="24" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -807,12 +813,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H4" s="22" t="inlineStr">
+      <c r="H4" s="24" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I4" s="22" t="inlineStr">
+      <c r="I4" s="24" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -827,20 +833,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L4" s="22" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M4" s="22" t="inlineStr"/>
+      <c r="L4" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M4" s="24" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>4309805269</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -850,12 +856,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>Delaware, United States</t>
         </is>
@@ -870,12 +876,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H5" s="23" t="inlineStr">
+      <c r="H5" s="25" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="I5" s="23" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -890,20 +896,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L5" s="23" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M5" s="23" t="inlineStr"/>
+      <c r="L5" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M5" s="25" t="inlineStr"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>4371812987</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -913,12 +919,12 @@
           <t>Software Development Engineer Fall Intern - Military Veteran</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -933,12 +939,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="H6" s="24" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="24" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -953,20 +959,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L6" s="22" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M6" s="22" t="inlineStr"/>
+      <c r="L6" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M6" s="24" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>4274682122</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -976,12 +982,12 @@
           <t>Software Engineer Intern (Data Ecosystem) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -996,12 +1002,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H7" s="23" t="inlineStr">
+      <c r="H7" s="25" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I7" s="23" t="inlineStr">
+      <c r="I7" s="25" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1016,20 +1022,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L7" s="23" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M7" s="23" t="inlineStr"/>
+      <c r="L7" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M7" s="25" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>4283848614</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1039,12 +1045,12 @@
           <t>[Online Assessment] Software Engineer Intern (Recommendation Infrastructure) - 2026 Fall (BS/ MS)</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="24" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1059,12 +1065,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H8" s="22" t="inlineStr">
+      <c r="H8" s="24" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="I8" s="24" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1079,20 +1085,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L8" s="22" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M8" s="22" t="inlineStr"/>
+      <c r="L8" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M8" s="24" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>4411790844</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1102,12 +1108,12 @@
           <t>Software Engineer Intern (Infrastructure Automation) - Fall 2026</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -1122,12 +1128,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H9" s="23" t="inlineStr">
+      <c r="H9" s="25" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I9" s="23" t="inlineStr">
+      <c r="I9" s="25" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1142,20 +1148,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L9" s="23" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M9" s="23" t="inlineStr"/>
+      <c r="L9" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M9" s="25" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>4332425058</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1165,12 +1171,12 @@
           <t>Software Development Engineer Internship - Fall 2026 (US)</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="24" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1185,12 +1191,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H10" s="22" t="inlineStr">
+      <c r="H10" s="24" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr">
+      <c r="I10" s="24" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1205,20 +1211,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L10" s="22" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M10" s="22" t="inlineStr"/>
+      <c r="L10" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M10" s="24" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>4323643644</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1228,12 +1234,12 @@
           <t>[Online Assessment] Software Engineer Intern (Recommendation Infrastructure) - 2026 Summer (BS/ MS)</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1248,12 +1254,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H11" s="23" t="inlineStr">
+      <c r="H11" s="25" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I11" s="23" t="inlineStr">
+      <c r="I11" s="25" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1268,20 +1274,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L11" s="23" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M11" s="23" t="inlineStr"/>
+      <c r="L11" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M11" s="25" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>4320849104</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1291,12 +1297,12 @@
           <t>Software Engineer Intern (Commerce Ads) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="24" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="24" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1311,12 +1317,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H12" s="24" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="24" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1331,20 +1337,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L12" s="22" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M12" s="22" t="inlineStr"/>
+      <c r="L12" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M12" s="24" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t>4401686051</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1354,12 +1360,12 @@
           <t>Front End Software Engineer</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="25" t="inlineStr">
         <is>
           <t>Saronic Technologies</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -1374,12 +1380,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H13" s="23" t="inlineStr">
+      <c r="H13" s="25" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I13" s="23" t="inlineStr">
+      <c r="I13" s="25" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1394,20 +1400,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L13" s="23" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M13" s="23" t="inlineStr"/>
+      <c r="L13" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M13" s="25" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>4309696652</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1417,12 +1423,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t>Rhode Island, United States</t>
         </is>
@@ -1437,12 +1443,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H14" s="24" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="I14" s="24" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1457,20 +1463,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L14" s="22" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M14" s="22" t="inlineStr"/>
+      <c r="L14" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M14" s="24" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>4309804319</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1480,12 +1486,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="25" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="25" t="inlineStr">
         <is>
           <t>Colorado, United States</t>
         </is>
@@ -1500,12 +1506,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H15" s="23" t="inlineStr">
+      <c r="H15" s="25" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="I15" s="23" t="inlineStr">
+      <c r="I15" s="25" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1520,20 +1526,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L15" s="23" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M15" s="23" t="inlineStr"/>
+      <c r="L15" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M15" s="25" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>4410271532</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1543,12 +1549,12 @@
           <t>Associate Developer</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>HealthStream</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="24" t="inlineStr">
         <is>
           <t>Nashville, TN</t>
         </is>
@@ -1563,12 +1569,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H16" s="22" t="inlineStr">
+      <c r="H16" s="24" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr">
+      <c r="I16" s="24" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1583,20 +1589,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L16" s="22" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M16" s="22" t="inlineStr"/>
+      <c r="L16" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M16" s="24" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>4304445726</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1606,12 +1612,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="25" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t>Oregon, United States</t>
         </is>
@@ -1626,12 +1632,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H17" s="23" t="inlineStr">
+      <c r="H17" s="25" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="I17" s="23" t="inlineStr">
+      <c r="I17" s="25" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1646,20 +1652,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L17" s="23" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M17" s="23" t="inlineStr"/>
+      <c r="L17" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M17" s="25" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>4342036151</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1669,12 +1675,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>Modern Treasury</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="24" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
@@ -1689,12 +1695,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="H18" s="24" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I18" s="22" t="inlineStr">
+      <c r="I18" s="24" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1709,20 +1715,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L18" s="22" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M18" s="22" t="inlineStr"/>
+      <c r="L18" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M18" s="24" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t>4304441843</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1732,12 +1738,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="25" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E19" s="25" t="inlineStr">
         <is>
           <t>Idaho, United States</t>
         </is>
@@ -1752,12 +1758,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H19" s="23" t="inlineStr">
+      <c r="H19" s="25" t="inlineStr">
         <is>
           <t>157</t>
         </is>
       </c>
-      <c r="I19" s="23" t="inlineStr">
+      <c r="I19" s="25" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1772,20 +1778,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L19" s="23" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M19" s="23" t="inlineStr"/>
+      <c r="L19" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M19" s="25" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="22" t="inlineStr">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t>4408047047</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1795,12 +1801,12 @@
           <t>Computer Sciences - Graduates - AI Training - Las Vegas, US</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="24" t="inlineStr">
         <is>
           <t>Prolific</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>Las Vegas, NV</t>
         </is>
@@ -1815,12 +1821,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H20" s="22" t="inlineStr">
+      <c r="H20" s="24" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I20" s="22" t="inlineStr">
+      <c r="I20" s="24" t="inlineStr">
         <is>
           <t>Temporary</t>
         </is>
@@ -1835,20 +1841,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L20" s="22" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M20" s="22" t="inlineStr"/>
+      <c r="L20" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M20" s="24" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>4304444837</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="25" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1858,12 +1864,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D21" s="25" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E21" s="25" t="inlineStr">
         <is>
           <t>New Jersey, United States</t>
         </is>
@@ -1878,12 +1884,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H21" s="23" t="inlineStr">
+      <c r="H21" s="25" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I21" s="23" t="inlineStr">
+      <c r="I21" s="25" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1898,20 +1904,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L21" s="23" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M21" s="23" t="inlineStr"/>
+      <c r="L21" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M21" s="25" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>4405641326</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1921,12 +1927,12 @@
           <t>Full-stack Engineer</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="24" t="inlineStr">
         <is>
           <t>PartnerTap</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1941,12 +1947,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H22" s="22" t="inlineStr">
+      <c r="H22" s="24" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I22" s="22" t="inlineStr">
+      <c r="I22" s="24" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1961,20 +1967,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L22" s="22" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M22" s="22" t="inlineStr"/>
+      <c r="L22" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M22" s="24" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="23" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>4341020900</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1984,12 +1990,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="25" t="inlineStr">
         <is>
           <t>PlanIT Group, LLC</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E23" s="25" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -2004,12 +2010,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H23" s="23" t="inlineStr">
+      <c r="H23" s="25" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I23" s="23" t="inlineStr">
+      <c r="I23" s="25" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
@@ -2024,20 +2030,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L23" s="23" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M23" s="23" t="inlineStr"/>
+      <c r="L23" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M23" s="25" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="22" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
         <is>
           <t>4304450637</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2047,12 +2053,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="24" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -2067,12 +2073,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H24" s="22" t="inlineStr">
+      <c r="H24" s="24" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I24" s="22" t="inlineStr">
+      <c r="I24" s="24" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2087,20 +2093,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L24" s="22" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M24" s="22" t="inlineStr"/>
+      <c r="L24" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M24" s="24" t="inlineStr"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="23" t="inlineStr">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>4304451654</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="25" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2110,12 +2116,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D25" s="23" t="inlineStr">
+      <c r="D25" s="25" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E25" s="25" t="inlineStr">
         <is>
           <t>Utah, United States</t>
         </is>
@@ -2130,12 +2136,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H25" s="23" t="inlineStr">
+      <c r="H25" s="25" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I25" s="23" t="inlineStr">
+      <c r="I25" s="25" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2150,20 +2156,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L25" s="23" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M25" s="23" t="inlineStr"/>
+      <c r="L25" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M25" s="25" t="inlineStr"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="22" t="inlineStr">
+      <c r="A26" s="24" t="inlineStr">
         <is>
           <t>4413745880</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="24" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2173,12 +2179,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="24" t="inlineStr">
         <is>
           <t>Crate &amp; Barrel</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="24" t="inlineStr">
         <is>
           <t>Northbrook, IL</t>
         </is>
@@ -2193,12 +2199,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H26" s="22" t="inlineStr">
+      <c r="H26" s="24" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I26" s="22" t="inlineStr">
+      <c r="I26" s="24" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2213,20 +2219,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L26" s="22" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M26" s="22" t="inlineStr"/>
+      <c r="L26" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M26" s="24" t="inlineStr"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="23" t="inlineStr">
+      <c r="A27" s="25" t="inlineStr">
         <is>
           <t>4304438841</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="25" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2236,12 +2242,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D27" s="23" t="inlineStr">
+      <c r="D27" s="25" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E27" s="25" t="inlineStr">
         <is>
           <t>Connecticut, United States</t>
         </is>
@@ -2256,12 +2262,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H27" s="23" t="inlineStr">
+      <c r="H27" s="25" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I27" s="23" t="inlineStr">
+      <c r="I27" s="25" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2276,20 +2282,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L27" s="23" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M27" s="23" t="inlineStr"/>
+      <c r="L27" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M27" s="25" t="inlineStr"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="22" t="inlineStr">
+      <c r="A28" s="24" t="inlineStr">
         <is>
           <t>4393215930</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2299,12 +2305,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="24" t="inlineStr">
         <is>
           <t>Transcend</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="24" t="inlineStr">
         <is>
           <t>California, United States</t>
         </is>
@@ -2319,12 +2325,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H28" s="22" t="inlineStr">
+      <c r="H28" s="24" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I28" s="22" t="inlineStr">
+      <c r="I28" s="24" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2339,20 +2345,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L28" s="22" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M28" s="22" t="inlineStr"/>
+      <c r="L28" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M28" s="24" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t>4304445723</t>
         </is>
       </c>
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B29" s="25" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2362,12 +2368,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D29" s="23" t="inlineStr">
+      <c r="D29" s="25" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="E29" s="25" t="inlineStr">
         <is>
           <t>Illinois, United States</t>
         </is>
@@ -2382,12 +2388,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H29" s="23" t="inlineStr">
+      <c r="H29" s="25" t="inlineStr">
         <is>
           <t>198</t>
         </is>
       </c>
-      <c r="I29" s="23" t="inlineStr">
+      <c r="I29" s="25" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2402,20 +2408,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L29" s="23" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M29" s="23" t="inlineStr"/>
+      <c r="L29" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M29" s="25" t="inlineStr"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="22" t="inlineStr">
+      <c r="A30" s="24" t="inlineStr">
         <is>
           <t>4396380649</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2425,12 +2431,12 @@
           <t>Full-Stack Developer Intern, Music &amp; Audio</t>
         </is>
       </c>
-      <c r="D30" s="22" t="inlineStr">
+      <c r="D30" s="24" t="inlineStr">
         <is>
           <t>Melotech</t>
         </is>
       </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
@@ -2445,12 +2451,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H30" s="22" t="inlineStr">
+      <c r="H30" s="24" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I30" s="22" t="inlineStr">
+      <c r="I30" s="24" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -2465,20 +2471,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L30" s="22" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M30" s="22" t="inlineStr"/>
+      <c r="L30" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M30" s="24" t="inlineStr"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="23" t="inlineStr">
+      <c r="A31" s="25" t="inlineStr">
         <is>
           <t>4304454025</t>
         </is>
       </c>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="25" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2488,12 +2494,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D31" s="23" t="inlineStr">
+      <c r="D31" s="25" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E31" s="25" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -2508,12 +2514,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H31" s="23" t="inlineStr">
+      <c r="H31" s="25" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I31" s="23" t="inlineStr">
+      <c r="I31" s="25" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2528,20 +2534,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L31" s="23" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M31" s="23" t="inlineStr"/>
+      <c r="L31" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M31" s="25" t="inlineStr"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="22" t="inlineStr">
+      <c r="A32" s="24" t="inlineStr">
         <is>
           <t>4309802287</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="24" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2551,12 +2557,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D32" s="22" t="inlineStr">
+      <c r="D32" s="24" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E32" s="22" t="inlineStr">
+      <c r="E32" s="24" t="inlineStr">
         <is>
           <t>New Jersey, United States</t>
         </is>
@@ -2571,12 +2577,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H32" s="22" t="inlineStr">
+      <c r="H32" s="24" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I32" s="22" t="inlineStr">
+      <c r="I32" s="24" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2591,20 +2597,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L32" s="22" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M32" s="22" t="inlineStr"/>
+      <c r="L32" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M32" s="24" t="inlineStr"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="23" t="inlineStr">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t>4309694880</t>
         </is>
       </c>
-      <c r="B33" s="23" t="inlineStr">
+      <c r="B33" s="25" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2614,12 +2620,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D33" s="23" t="inlineStr">
+      <c r="D33" s="25" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="E33" s="25" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -2634,12 +2640,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H33" s="23" t="inlineStr">
+      <c r="H33" s="25" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I33" s="23" t="inlineStr">
+      <c r="I33" s="25" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2654,20 +2660,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L33" s="23" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M33" s="23" t="inlineStr"/>
+      <c r="L33" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M33" s="25" t="inlineStr"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="22" t="inlineStr">
+      <c r="A34" s="24" t="inlineStr">
         <is>
           <t>4411274012</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B34" s="24" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2677,12 +2683,12 @@
           <t>Junior UI Developer</t>
         </is>
       </c>
-      <c r="D34" s="22" t="inlineStr">
+      <c r="D34" s="24" t="inlineStr">
         <is>
           <t>General Dynamics Information Technology</t>
         </is>
       </c>
-      <c r="E34" s="22" t="inlineStr">
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -2697,12 +2703,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H34" s="22" t="inlineStr">
+      <c r="H34" s="24" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I34" s="22" t="inlineStr">
+      <c r="I34" s="24" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2717,20 +2723,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L34" s="22" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M34" s="22" t="inlineStr"/>
+      <c r="L34" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M34" s="24" t="inlineStr"/>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="23" t="inlineStr">
+      <c r="A35" s="25" t="inlineStr">
         <is>
           <t>4264562292</t>
         </is>
       </c>
-      <c r="B35" s="23" t="inlineStr">
+      <c r="B35" s="25" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2740,12 +2746,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D35" s="23" t="inlineStr">
+      <c r="D35" s="25" t="inlineStr">
         <is>
           <t>Cymertek Corporation</t>
         </is>
       </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="E35" s="25" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
@@ -2760,12 +2766,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H35" s="23" t="inlineStr">
+      <c r="H35" s="25" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="I35" s="23" t="inlineStr">
+      <c r="I35" s="25" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2780,20 +2786,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L35" s="23" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M35" s="23" t="inlineStr"/>
+      <c r="L35" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M35" s="25" t="inlineStr"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="22" t="inlineStr">
+      <c r="A36" s="24" t="inlineStr">
         <is>
           <t>4417482675</t>
         </is>
       </c>
-      <c r="B36" s="22" t="inlineStr">
+      <c r="B36" s="24" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2803,12 +2809,12 @@
           <t>Software Developer I</t>
         </is>
       </c>
-      <c r="D36" s="22" t="inlineStr">
+      <c r="D36" s="24" t="inlineStr">
         <is>
           <t>El Paso Water</t>
         </is>
       </c>
-      <c r="E36" s="22" t="inlineStr">
+      <c r="E36" s="24" t="inlineStr">
         <is>
           <t>El Paso, TX</t>
         </is>
@@ -2823,12 +2829,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H36" s="22" t="inlineStr">
+      <c r="H36" s="24" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="I36" s="22" t="inlineStr">
+      <c r="I36" s="24" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2843,20 +2849,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L36" s="22" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M36" s="22" t="inlineStr"/>
+      <c r="L36" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M36" s="24" t="inlineStr"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="23" t="inlineStr">
+      <c r="A37" s="25" t="inlineStr">
         <is>
           <t>4416508200</t>
         </is>
       </c>
-      <c r="B37" s="23" t="inlineStr">
+      <c r="B37" s="25" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2866,12 +2872,12 @@
           <t>Software Development Engineer in Test Intern (Global E-Commerce) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D37" s="23" t="inlineStr">
+      <c r="D37" s="25" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="E37" s="25" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -2886,12 +2892,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H37" s="23" t="inlineStr">
+      <c r="H37" s="25" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I37" s="23" t="inlineStr">
+      <c r="I37" s="25" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -2906,20 +2912,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L37" s="23" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M37" s="23" t="inlineStr"/>
+      <c r="L37" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M37" s="25" t="inlineStr"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="22" t="inlineStr">
+      <c r="A38" s="24" t="inlineStr">
         <is>
           <t>4309809191</t>
         </is>
       </c>
-      <c r="B38" s="22" t="inlineStr">
+      <c r="B38" s="24" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
@@ -2929,12 +2935,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D38" s="22" t="inlineStr">
+      <c r="D38" s="24" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E38" s="22" t="inlineStr">
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t>Ohio, United States</t>
         </is>
@@ -2949,12 +2955,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H38" s="22" t="inlineStr">
+      <c r="H38" s="24" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="I38" s="22" t="inlineStr">
+      <c r="I38" s="24" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2969,20 +2975,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L38" s="22" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M38" s="22" t="inlineStr"/>
+      <c r="L38" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M38" s="24" t="inlineStr"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="23" t="inlineStr">
+      <c r="A39" s="25" t="inlineStr">
         <is>
           <t>3986118096</t>
         </is>
       </c>
-      <c r="B39" s="23" t="inlineStr">
+      <c r="B39" s="25" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
@@ -2992,12 +2998,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D39" s="23" t="inlineStr">
+      <c r="D39" s="25" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E39" s="23" t="inlineStr">
+      <c r="E39" s="25" t="inlineStr">
         <is>
           <t>Irving, TX</t>
         </is>
@@ -3012,12 +3018,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H39" s="23" t="inlineStr">
+      <c r="H39" s="25" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I39" s="23" t="inlineStr">
+      <c r="I39" s="25" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3032,20 +3038,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L39" s="23" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M39" s="23" t="inlineStr"/>
+      <c r="L39" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M39" s="25" t="inlineStr"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="22" t="inlineStr">
+      <c r="A40" s="24" t="inlineStr">
         <is>
           <t>4309808244</t>
         </is>
       </c>
-      <c r="B40" s="22" t="inlineStr">
+      <c r="B40" s="24" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3055,12 +3061,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D40" s="22" t="inlineStr">
+      <c r="D40" s="24" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E40" s="22" t="inlineStr">
+      <c r="E40" s="24" t="inlineStr">
         <is>
           <t>Massachusetts, United States</t>
         </is>
@@ -3075,12 +3081,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H40" s="22" t="inlineStr">
+      <c r="H40" s="24" t="inlineStr">
         <is>
           <t>166</t>
         </is>
       </c>
-      <c r="I40" s="22" t="inlineStr">
+      <c r="I40" s="24" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3095,20 +3101,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L40" s="22" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M40" s="22" t="inlineStr"/>
+      <c r="L40" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M40" s="24" t="inlineStr"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="23" t="inlineStr">
+      <c r="A41" s="25" t="inlineStr">
         <is>
           <t>4362173625</t>
         </is>
       </c>
-      <c r="B41" s="23" t="inlineStr">
+      <c r="B41" s="25" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3118,12 +3124,12 @@
           <t>Full Stack Engineer</t>
         </is>
       </c>
-      <c r="D41" s="23" t="inlineStr">
+      <c r="D41" s="25" t="inlineStr">
         <is>
           <t>Empower Sleep</t>
         </is>
       </c>
-      <c r="E41" s="23" t="inlineStr">
+      <c r="E41" s="25" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3138,12 +3144,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H41" s="23" t="inlineStr">
+      <c r="H41" s="25" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I41" s="23" t="inlineStr">
+      <c r="I41" s="25" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3158,20 +3164,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L41" s="23" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M41" s="23" t="inlineStr"/>
+      <c r="L41" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M41" s="25" t="inlineStr"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="22" t="inlineStr">
+      <c r="A42" s="24" t="inlineStr">
         <is>
           <t>4309812093</t>
         </is>
       </c>
-      <c r="B42" s="22" t="inlineStr">
+      <c r="B42" s="24" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3181,12 +3187,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D42" s="22" t="inlineStr">
+      <c r="D42" s="24" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E42" s="22" t="inlineStr">
+      <c r="E42" s="24" t="inlineStr">
         <is>
           <t>Florida, United States</t>
         </is>
@@ -3201,12 +3207,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H42" s="22" t="inlineStr">
+      <c r="H42" s="24" t="inlineStr">
         <is>
           <t>158</t>
         </is>
       </c>
-      <c r="I42" s="22" t="inlineStr">
+      <c r="I42" s="24" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3221,20 +3227,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L42" s="22" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M42" s="22" t="inlineStr"/>
+      <c r="L42" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M42" s="24" t="inlineStr"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="23" t="inlineStr">
+      <c r="A43" s="25" t="inlineStr">
         <is>
           <t>4391759914</t>
         </is>
       </c>
-      <c r="B43" s="23" t="inlineStr">
+      <c r="B43" s="25" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3244,12 +3250,12 @@
           <t>QA Engineering Internship</t>
         </is>
       </c>
-      <c r="D43" s="23" t="inlineStr">
+      <c r="D43" s="25" t="inlineStr">
         <is>
           <t>Chartbeat</t>
         </is>
       </c>
-      <c r="E43" s="23" t="inlineStr">
+      <c r="E43" s="25" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -3264,12 +3270,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H43" s="23" t="inlineStr">
+      <c r="H43" s="25" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="I43" s="23" t="inlineStr">
+      <c r="I43" s="25" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3284,20 +3290,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L43" s="23" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M43" s="23" t="inlineStr"/>
+      <c r="L43" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M43" s="25" t="inlineStr"/>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="22" t="inlineStr">
+      <c r="A44" s="24" t="inlineStr">
         <is>
           <t>4412855678</t>
         </is>
       </c>
-      <c r="B44" s="22" t="inlineStr">
+      <c r="B44" s="24" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3307,12 +3313,12 @@
           <t>AI Integration Engineer</t>
         </is>
       </c>
-      <c r="D44" s="22" t="inlineStr">
+      <c r="D44" s="24" t="inlineStr">
         <is>
           <t>UST</t>
         </is>
       </c>
-      <c r="E44" s="22" t="inlineStr">
+      <c r="E44" s="24" t="inlineStr">
         <is>
           <t>Santa Clara, CA</t>
         </is>
@@ -3327,12 +3333,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H44" s="22" t="inlineStr">
+      <c r="H44" s="24" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I44" s="22" t="inlineStr">
+      <c r="I44" s="24" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3347,20 +3353,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L44" s="22" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M44" s="22" t="inlineStr"/>
+      <c r="L44" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M44" s="24" t="inlineStr"/>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="23" t="inlineStr">
+      <c r="A45" s="25" t="inlineStr">
         <is>
           <t>4309805219</t>
         </is>
       </c>
-      <c r="B45" s="23" t="inlineStr">
+      <c r="B45" s="25" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3370,12 +3376,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D45" s="23" t="inlineStr">
+      <c r="D45" s="25" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E45" s="23" t="inlineStr">
+      <c r="E45" s="25" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -3390,12 +3396,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H45" s="23" t="inlineStr">
+      <c r="H45" s="25" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I45" s="23" t="inlineStr">
+      <c r="I45" s="25" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3410,20 +3416,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L45" s="23" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M45" s="23" t="inlineStr"/>
+      <c r="L45" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M45" s="25" t="inlineStr"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="22" t="inlineStr">
+      <c r="A46" s="24" t="inlineStr">
         <is>
           <t>4409726429</t>
         </is>
       </c>
-      <c r="B46" s="22" t="inlineStr">
+      <c r="B46" s="24" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3433,12 +3439,12 @@
           <t>Data Science Intern</t>
         </is>
       </c>
-      <c r="D46" s="22" t="inlineStr">
+      <c r="D46" s="24" t="inlineStr">
         <is>
           <t>Rundoo</t>
         </is>
       </c>
-      <c r="E46" s="22" t="inlineStr">
+      <c r="E46" s="24" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3453,12 +3459,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H46" s="22" t="inlineStr">
+      <c r="H46" s="24" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I46" s="22" t="inlineStr">
+      <c r="I46" s="24" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3473,20 +3479,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L46" s="22" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M46" s="22" t="inlineStr"/>
+      <c r="L46" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M46" s="24" t="inlineStr"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="23" t="inlineStr">
+      <c r="A47" s="25" t="inlineStr">
         <is>
           <t>4305671729</t>
         </is>
       </c>
-      <c r="B47" s="23" t="inlineStr">
+      <c r="B47" s="25" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3496,12 +3502,12 @@
           <t>DoD SkillBridge Internship/Fellowship Opportunity Application (U.S. Military Only)</t>
         </is>
       </c>
-      <c r="D47" s="23" t="inlineStr">
+      <c r="D47" s="25" t="inlineStr">
         <is>
           <t>Onsights</t>
         </is>
       </c>
-      <c r="E47" s="23" t="inlineStr">
+      <c r="E47" s="25" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -3516,12 +3522,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H47" s="23" t="inlineStr">
+      <c r="H47" s="25" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I47" s="23" t="inlineStr">
+      <c r="I47" s="25" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3536,20 +3542,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L47" s="23" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M47" s="23" t="inlineStr"/>
+      <c r="L47" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M47" s="25" t="inlineStr"/>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="22" t="inlineStr">
+      <c r="A48" s="24" t="inlineStr">
         <is>
           <t>4414096220</t>
         </is>
       </c>
-      <c r="B48" s="22" t="inlineStr">
+      <c r="B48" s="24" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3559,12 +3565,12 @@
           <t>Visualization Engineer Intern</t>
         </is>
       </c>
-      <c r="D48" s="22" t="inlineStr">
+      <c r="D48" s="24" t="inlineStr">
         <is>
           <t>Leidos</t>
         </is>
       </c>
-      <c r="E48" s="22" t="inlineStr">
+      <c r="E48" s="24" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3579,12 +3585,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H48" s="22" t="inlineStr">
+      <c r="H48" s="24" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="I48" s="22" t="inlineStr">
+      <c r="I48" s="24" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3599,20 +3605,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L48" s="22" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M48" s="22" t="inlineStr"/>
+      <c r="L48" s="24" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M48" s="24" t="inlineStr"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="23" t="inlineStr">
+      <c r="A49" s="25" t="inlineStr">
         <is>
           <t>4361076044</t>
         </is>
       </c>
-      <c r="B49" s="23" t="inlineStr">
+      <c r="B49" s="25" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3622,12 +3628,12 @@
           <t>GenAI Engineering Intern  - SkillBridge (Remote)</t>
         </is>
       </c>
-      <c r="D49" s="23" t="inlineStr">
+      <c r="D49" s="25" t="inlineStr">
         <is>
           <t>CrowdStrike</t>
         </is>
       </c>
-      <c r="E49" s="23" t="inlineStr">
+      <c r="E49" s="25" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3642,12 +3648,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H49" s="23" t="inlineStr">
+      <c r="H49" s="25" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I49" s="23" t="inlineStr">
+      <c r="I49" s="25" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3662,12 +3668,12 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L49" s="23" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M49" s="23" t="inlineStr"/>
+      <c r="L49" s="25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M49" s="25" t="inlineStr"/>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="24" t="inlineStr">
@@ -4362,8 +4368,1331 @@
       </c>
       <c r="M60" s="24" t="inlineStr"/>
     </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="26" t="inlineStr">
+        <is>
+          <t>4413699205</t>
+        </is>
+      </c>
+      <c r="B61" s="26" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer - Automation &amp; Integration</t>
+        </is>
+      </c>
+      <c r="D61" s="26" t="inlineStr">
+        <is>
+          <t>Fletcher Development LLC</t>
+        </is>
+      </c>
+      <c r="E61" s="26" t="inlineStr">
+        <is>
+          <t>Redding, CT</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H61" s="26" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="I61" s="26" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J61" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, rest, api, git, sql, backend, Title match: Junior Software Engineer - Automation &amp; Integration</t>
+        </is>
+      </c>
+      <c r="K61" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L61" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M61" s="26" t="inlineStr"/>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="27" t="inlineStr">
+        <is>
+          <t>4416171988</t>
+        </is>
+      </c>
+      <c r="B62" s="27" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="D62" s="27" t="inlineStr">
+        <is>
+          <t>Altec</t>
+        </is>
+      </c>
+      <c r="E62" s="27" t="inlineStr">
+        <is>
+          <t>Birmingham, AL</t>
+        </is>
+      </c>
+      <c r="F62" s="18" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="G62" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H62" s="27" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I62" s="27" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>Skills: api, sql, c, agile, Title match: Software Developer</t>
+        </is>
+      </c>
+      <c r="K62" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L62" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M62" s="27" t="inlineStr"/>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="26" t="inlineStr">
+        <is>
+          <t>4403444963</t>
+        </is>
+      </c>
+      <c r="B63" s="26" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>Junior Applications Developer (NY HELPS) #2026-252</t>
+        </is>
+      </c>
+      <c r="D63" s="26" t="inlineStr">
+        <is>
+          <t>Capital Region BOCES</t>
+        </is>
+      </c>
+      <c r="E63" s="26" t="inlineStr">
+        <is>
+          <t>Albany, NY</t>
+        </is>
+      </c>
+      <c r="F63" s="14" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="G63" s="15" t="inlineStr">
+        <is>
+          <t>Very Low</t>
+        </is>
+      </c>
+      <c r="H63" s="26" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I63" s="26" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J63" s="8" t="inlineStr">
+        <is>
+          <t>Skills: c</t>
+        </is>
+      </c>
+      <c r="K63" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L63" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M63" s="26" t="inlineStr"/>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="27" t="inlineStr">
+        <is>
+          <t>4418506121</t>
+        </is>
+      </c>
+      <c r="B64" s="27" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Core System Junior Developer</t>
+        </is>
+      </c>
+      <c r="D64" s="27" t="inlineStr">
+        <is>
+          <t>Cyprus Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="E64" s="27" t="inlineStr">
+        <is>
+          <t>West Jordan, UT</t>
+        </is>
+      </c>
+      <c r="F64" s="18" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="G64" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H64" s="27" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="I64" s="27" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, api, sql, c, Title match: Core System Junior Developer</t>
+        </is>
+      </c>
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L64" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M64" s="27" t="inlineStr"/>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="26" t="inlineStr">
+        <is>
+          <t>4413905706</t>
+        </is>
+      </c>
+      <c r="B65" s="26" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="D65" s="26" t="inlineStr">
+        <is>
+          <t>Arnex Solutions LLC</t>
+        </is>
+      </c>
+      <c r="E65" s="26" t="inlineStr">
+        <is>
+          <t>Princeton, NJ</t>
+        </is>
+      </c>
+      <c r="F65" s="18" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="G65" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H65" s="26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I65" s="26" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J65" s="8" t="inlineStr">
+        <is>
+          <t>Skills: javascript, html, css, sql, c, agile, Title match: Software Developer</t>
+        </is>
+      </c>
+      <c r="K65" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L65" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M65" s="26" t="inlineStr"/>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="27" t="inlineStr">
+        <is>
+          <t>4418963446</t>
+        </is>
+      </c>
+      <c r="B66" s="27" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer - Automation &amp; Integration</t>
+        </is>
+      </c>
+      <c r="D66" s="27" t="inlineStr">
+        <is>
+          <t>Vibrant Building Technologies</t>
+        </is>
+      </c>
+      <c r="E66" s="27" t="inlineStr">
+        <is>
+          <t>Ridgefield, CT</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H66" s="27" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="I66" s="27" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, rest, api, git, sql, backend, Title match: Junior Software Engineer - Automation &amp; Integration</t>
+        </is>
+      </c>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L66" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M66" s="27" t="inlineStr"/>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="26" t="inlineStr">
+        <is>
+          <t>4413759052</t>
+        </is>
+      </c>
+      <c r="B67" s="26" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>Junior Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D67" s="26" t="inlineStr">
+        <is>
+          <t>Allied World Reinsurance Company</t>
+        </is>
+      </c>
+      <c r="E67" s="26" t="inlineStr">
+        <is>
+          <t>Iselin, NJ</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H67" s="26" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I67" s="26" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J67" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, react, node, aws, api, Title match: Junior Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="K67" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L67" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M67" s="26" t="inlineStr"/>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="27" t="inlineStr">
+        <is>
+          <t>4417542502</t>
+        </is>
+      </c>
+      <c r="B68" s="27" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Junior Developer</t>
+        </is>
+      </c>
+      <c r="D68" s="27" t="inlineStr">
+        <is>
+          <t>CloudMasonry</t>
+        </is>
+      </c>
+      <c r="E68" s="27" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H68" s="27" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="I68" s="27" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, node, rest, api, html, Title match: Junior Developer</t>
+        </is>
+      </c>
+      <c r="K68" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L68" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M68" s="27" t="inlineStr"/>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="26" t="inlineStr">
+        <is>
+          <t>4374856035</t>
+        </is>
+      </c>
+      <c r="B69" s="26" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>Programmer II</t>
+        </is>
+      </c>
+      <c r="D69" s="26" t="inlineStr">
+        <is>
+          <t>Willis Knighton Health</t>
+        </is>
+      </c>
+      <c r="E69" s="26" t="inlineStr">
+        <is>
+          <t>Louisiana, United States</t>
+        </is>
+      </c>
+      <c r="F69" s="14" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="G69" s="15" t="inlineStr">
+        <is>
+          <t>Very Low</t>
+        </is>
+      </c>
+      <c r="H69" s="26" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I69" s="26" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J69" s="8" t="inlineStr">
+        <is>
+          <t>Skills: c</t>
+        </is>
+      </c>
+      <c r="K69" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L69" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M69" s="26" t="inlineStr"/>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="27" t="inlineStr">
+        <is>
+          <t>4416302564</t>
+        </is>
+      </c>
+      <c r="B70" s="27" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer I</t>
+        </is>
+      </c>
+      <c r="D70" s="27" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="E70" s="27" t="inlineStr">
+        <is>
+          <t>Sunrise, FL</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H70" s="27" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I70" s="27" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, react, aws, rest, api, docker, Title match: Software Engineer I</t>
+        </is>
+      </c>
+      <c r="K70" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L70" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M70" s="27" t="inlineStr"/>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="26" t="inlineStr">
+        <is>
+          <t>4417014137</t>
+        </is>
+      </c>
+      <c r="B71" s="26" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>Junior Software Developer, Applications</t>
+        </is>
+      </c>
+      <c r="D71" s="26" t="inlineStr">
+        <is>
+          <t>ECS</t>
+        </is>
+      </c>
+      <c r="E71" s="26" t="inlineStr">
+        <is>
+          <t>O'Fallon, IL</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H71" s="26" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="I71" s="26" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J71" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, html, docker, git, sql, Title match: Junior Software Developer, Applications</t>
+        </is>
+      </c>
+      <c r="K71" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L71" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M71" s="26" t="inlineStr"/>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="27" t="inlineStr">
+        <is>
+          <t>4381211472</t>
+        </is>
+      </c>
+      <c r="B72" s="27" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Programmer</t>
+        </is>
+      </c>
+      <c r="D72" s="27" t="inlineStr">
+        <is>
+          <t>City of New York</t>
+        </is>
+      </c>
+      <c r="E72" s="27" t="inlineStr">
+        <is>
+          <t>Bronx, NY</t>
+        </is>
+      </c>
+      <c r="F72" s="14" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="G72" s="15" t="inlineStr">
+        <is>
+          <t>Very Low</t>
+        </is>
+      </c>
+      <c r="H72" s="27" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="I72" s="27" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>Skills: javascript, react, html, sql, c, agile</t>
+        </is>
+      </c>
+      <c r="K72" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L72" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M72" s="27" t="inlineStr"/>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="26" t="inlineStr">
+        <is>
+          <t>4168416236</t>
+        </is>
+      </c>
+      <c r="B73" s="26" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D73" s="26" t="inlineStr">
+        <is>
+          <t>Interclypse</t>
+        </is>
+      </c>
+      <c r="E73" s="26" t="inlineStr">
+        <is>
+          <t>San Antonio, TX</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H73" s="26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I73" s="26" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J73" s="8" t="inlineStr">
+        <is>
+          <t>Skills: javascript, react, mongodb, sql, full stack, backend, Title match: Software Engineer</t>
+        </is>
+      </c>
+      <c r="K73" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L73" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M73" s="26" t="inlineStr"/>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="27" t="inlineStr">
+        <is>
+          <t>4403507357</t>
+        </is>
+      </c>
+      <c r="B74" s="27" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Software Developer:</t>
+        </is>
+      </c>
+      <c r="D74" s="27" t="inlineStr">
+        <is>
+          <t>IQuest Solutions Corporation</t>
+        </is>
+      </c>
+      <c r="E74" s="27" t="inlineStr">
+        <is>
+          <t>Plano, TX</t>
+        </is>
+      </c>
+      <c r="F74" s="18" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="G74" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H74" s="27" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I74" s="27" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>Skills: aws, rest, api, c, Title match: Software Developer:</t>
+        </is>
+      </c>
+      <c r="K74" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L74" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M74" s="27" t="inlineStr"/>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="26" t="inlineStr">
+        <is>
+          <t>4309800238</t>
+        </is>
+      </c>
+      <c r="B75" s="26" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>Backend Software Engineer</t>
+        </is>
+      </c>
+      <c r="D75" s="26" t="inlineStr">
+        <is>
+          <t>DataAnnotation</t>
+        </is>
+      </c>
+      <c r="E75" s="26" t="inlineStr">
+        <is>
+          <t>Texas, United States</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H75" s="26" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I75" s="26" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J75" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, html, sql, backend, c++, Location: Texas, United States, Title match: Backend Software Engineer</t>
+        </is>
+      </c>
+      <c r="K75" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L75" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M75" s="26" t="inlineStr"/>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="27" t="inlineStr">
+        <is>
+          <t>4404109089</t>
+        </is>
+      </c>
+      <c r="B76" s="27" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Software Development Engineer I</t>
+        </is>
+      </c>
+      <c r="D76" s="27" t="inlineStr">
+        <is>
+          <t>GM Financial</t>
+        </is>
+      </c>
+      <c r="E76" s="27" t="inlineStr">
+        <is>
+          <t>Arlington, TX</t>
+        </is>
+      </c>
+      <c r="F76" s="18" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="G76" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H76" s="27" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I76" s="27" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>Skills: javascript, node, api, css, docker, git</t>
+        </is>
+      </c>
+      <c r="K76" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L76" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M76" s="27" t="inlineStr"/>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="26" t="inlineStr">
+        <is>
+          <t>3986116411</t>
+        </is>
+      </c>
+      <c r="B77" s="26" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D77" s="26" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="E77" s="26" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H77" s="26" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I77" s="26" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J77" s="8" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, machine learning, c, Location: Austin, TX, Title match: Software Engineer</t>
+        </is>
+      </c>
+      <c r="K77" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L77" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M77" s="26" t="inlineStr"/>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="27" t="inlineStr">
+        <is>
+          <t>4418051524</t>
+        </is>
+      </c>
+      <c r="B78" s="27" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D78" s="27" t="inlineStr">
+        <is>
+          <t>Relativity</t>
+        </is>
+      </c>
+      <c r="E78" s="27" t="inlineStr">
+        <is>
+          <t>Texas, United States</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H78" s="27" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I78" s="27" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, api, git, backend, c, llm, Location: Texas, United States, Title match: Software Engineer</t>
+        </is>
+      </c>
+      <c r="K78" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L78" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M78" s="27" t="inlineStr"/>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="26" t="inlineStr">
+        <is>
+          <t>4409856693</t>
+        </is>
+      </c>
+      <c r="B79" s="26" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer - Payments</t>
+        </is>
+      </c>
+      <c r="D79" s="26" t="inlineStr">
+        <is>
+          <t>Cloudbeds</t>
+        </is>
+      </c>
+      <c r="E79" s="26" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="G79" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H79" s="26" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="I79" s="26" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J79" s="8" t="inlineStr">
+        <is>
+          <t>Skills: aws, api, docker, git, sql, machine learning, Location: Austin, TX, Title match: Software Engineer - Payments</t>
+        </is>
+      </c>
+      <c r="K79" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L79" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M79" s="26" t="inlineStr"/>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="27" t="inlineStr">
+        <is>
+          <t>3986111771</t>
+        </is>
+      </c>
+      <c r="B80" s="27" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D80" s="27" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="E80" s="27" t="inlineStr">
+        <is>
+          <t>Carrollton, TX</t>
+        </is>
+      </c>
+      <c r="F80" s="18" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="G80" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H80" s="27" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I80" s="27" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, machine learning, c, Title match: Software Engineer</t>
+        </is>
+      </c>
+      <c r="K80" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L80" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M80" s="27" t="inlineStr"/>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="26" t="inlineStr">
+        <is>
+          <t>4417160720</t>
+        </is>
+      </c>
+      <c r="B81" s="26" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>Full-Stack AI Developer</t>
+        </is>
+      </c>
+      <c r="D81" s="26" t="inlineStr">
+        <is>
+          <t>AnswerMyQ</t>
+        </is>
+      </c>
+      <c r="E81" s="26" t="inlineStr">
+        <is>
+          <t>Austin, Texas Metropolitan Area</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H81" s="26" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I81" s="26" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J81" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, react, aws, git, full-stack, backend, Location: Austin, Texas Metropolitan Area</t>
+        </is>
+      </c>
+      <c r="K81" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L81" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M81" s="26" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M60"/>
+  <autoFilter ref="A1:M81"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -4424,6 +5753,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId80"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Job Matches" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Matches'!$A$1:$M$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Matches'!$A$1:$M$87</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -199,6 +199,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -566,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -652,12 +658,12 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>4406952064</t>
         </is>
       </c>
-      <c r="B2" s="24" t="inlineStr">
+      <c r="B2" s="27" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -667,12 +673,12 @@
           <t>DevSecOps Intern</t>
         </is>
       </c>
-      <c r="D2" s="24" t="inlineStr">
+      <c r="D2" s="27" t="inlineStr">
         <is>
           <t>Modern Technology Solutions, Inc. (MTSI)</t>
         </is>
       </c>
-      <c r="E2" s="24" t="inlineStr">
+      <c r="E2" s="27" t="inlineStr">
         <is>
           <t>Huntsville, AL</t>
         </is>
@@ -687,12 +693,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H2" s="24" t="inlineStr">
+      <c r="H2" s="27" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="I2" s="24" t="inlineStr">
+      <c r="I2" s="27" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -707,20 +713,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L2" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M2" s="24" t="inlineStr"/>
+      <c r="L2" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M2" s="27" t="inlineStr"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>4405630173</t>
         </is>
       </c>
-      <c r="B3" s="25" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -730,12 +736,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D3" s="25" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>DLRdmv®</t>
         </is>
       </c>
-      <c r="E3" s="25" t="inlineStr">
+      <c r="E3" s="26" t="inlineStr">
         <is>
           <t>Dallas, TX</t>
         </is>
@@ -750,12 +756,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H3" s="25" t="inlineStr">
+      <c r="H3" s="26" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I3" s="25" t="inlineStr">
+      <c r="I3" s="26" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -770,20 +776,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L3" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M3" s="25" t="inlineStr"/>
+      <c r="L3" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M3" s="26" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>4287414862</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="27" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -793,12 +799,12 @@
           <t>[Online Assessment]Software Development Engineer Intern (Network Automation)- 2026 Summer (BS/ MS)</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="27" t="inlineStr">
         <is>
           <t>ByteDance</t>
         </is>
       </c>
-      <c r="E4" s="24" t="inlineStr">
+      <c r="E4" s="27" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -813,12 +819,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H4" s="24" t="inlineStr">
+      <c r="H4" s="27" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I4" s="24" t="inlineStr">
+      <c r="I4" s="27" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -833,20 +839,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L4" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M4" s="24" t="inlineStr"/>
+      <c r="L4" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M4" s="27" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>4309805269</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -856,12 +862,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>Delaware, United States</t>
         </is>
@@ -876,12 +882,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H5" s="26" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -896,20 +902,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L5" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M5" s="25" t="inlineStr"/>
+      <c r="L5" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M5" s="26" t="inlineStr"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>4371812987</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -919,12 +925,12 @@
           <t>Software Development Engineer Fall Intern - Military Veteran</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -939,12 +945,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H6" s="24" t="inlineStr">
+      <c r="H6" s="27" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="I6" s="24" t="inlineStr">
+      <c r="I6" s="27" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -959,20 +965,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L6" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M6" s="24" t="inlineStr"/>
+      <c r="L6" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M6" s="27" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>4274682122</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -982,12 +988,12 @@
           <t>Software Engineer Intern (Data Ecosystem) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1002,12 +1008,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H7" s="25" t="inlineStr">
+      <c r="H7" s="26" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I7" s="25" t="inlineStr">
+      <c r="I7" s="26" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1022,20 +1028,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L7" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M7" s="25" t="inlineStr"/>
+      <c r="L7" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M7" s="26" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>4283848614</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1045,12 +1051,12 @@
           <t>[Online Assessment] Software Engineer Intern (Recommendation Infrastructure) - 2026 Fall (BS/ MS)</t>
         </is>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E8" s="24" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1065,12 +1071,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H8" s="24" t="inlineStr">
+      <c r="H8" s="27" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I8" s="24" t="inlineStr">
+      <c r="I8" s="27" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1085,20 +1091,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L8" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M8" s="24" t="inlineStr"/>
+      <c r="L8" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M8" s="27" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>4411790844</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1108,12 +1114,12 @@
           <t>Software Engineer Intern (Infrastructure Automation) - Fall 2026</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="26" t="inlineStr">
         <is>
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="26" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -1128,12 +1134,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H9" s="25" t="inlineStr">
+      <c r="H9" s="26" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I9" s="25" t="inlineStr">
+      <c r="I9" s="26" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1148,20 +1154,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L9" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M9" s="25" t="inlineStr"/>
+      <c r="L9" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M9" s="26" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>4332425058</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1171,12 +1177,12 @@
           <t>Software Development Engineer Internship - Fall 2026 (US)</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E10" s="24" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1191,12 +1197,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H10" s="24" t="inlineStr">
+      <c r="H10" s="27" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I10" s="24" t="inlineStr">
+      <c r="I10" s="27" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1211,20 +1217,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L10" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M10" s="24" t="inlineStr"/>
+      <c r="L10" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M10" s="27" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="26" t="inlineStr">
         <is>
           <t>4323643644</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1234,12 +1240,12 @@
           <t>[Online Assessment] Software Engineer Intern (Recommendation Infrastructure) - 2026 Summer (BS/ MS)</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="26" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="26" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1254,12 +1260,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H11" s="25" t="inlineStr">
+      <c r="H11" s="26" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I11" s="25" t="inlineStr">
+      <c r="I11" s="26" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1274,20 +1280,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L11" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M11" s="25" t="inlineStr"/>
+      <c r="L11" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M11" s="26" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>4320849104</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1297,12 +1303,12 @@
           <t>Software Engineer Intern (Commerce Ads) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D12" s="24" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E12" s="24" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1317,12 +1323,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H12" s="24" t="inlineStr">
+      <c r="H12" s="27" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I12" s="24" t="inlineStr">
+      <c r="I12" s="27" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1337,20 +1343,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L12" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M12" s="24" t="inlineStr"/>
+      <c r="L12" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M12" s="27" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>4401686051</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1360,12 +1366,12 @@
           <t>Front End Software Engineer</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="D13" s="26" t="inlineStr">
         <is>
           <t>Saronic Technologies</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="26" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -1380,12 +1386,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H13" s="25" t="inlineStr">
+      <c r="H13" s="26" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I13" s="25" t="inlineStr">
+      <c r="I13" s="26" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1400,20 +1406,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L13" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M13" s="25" t="inlineStr"/>
+      <c r="L13" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M13" s="26" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>4309696652</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="27" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1423,12 +1429,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>Rhode Island, United States</t>
         </is>
@@ -1443,12 +1449,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H14" s="24" t="inlineStr">
+      <c r="H14" s="27" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="I14" s="24" t="inlineStr">
+      <c r="I14" s="27" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1463,20 +1469,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L14" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M14" s="24" t="inlineStr"/>
+      <c r="L14" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M14" s="27" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="26" t="inlineStr">
         <is>
           <t>4309804319</t>
         </is>
       </c>
-      <c r="B15" s="25" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1486,12 +1492,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr">
+      <c r="D15" s="26" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E15" s="25" t="inlineStr">
+      <c r="E15" s="26" t="inlineStr">
         <is>
           <t>Colorado, United States</t>
         </is>
@@ -1506,12 +1512,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H15" s="25" t="inlineStr">
+      <c r="H15" s="26" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="I15" s="25" t="inlineStr">
+      <c r="I15" s="26" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1526,20 +1532,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L15" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M15" s="25" t="inlineStr"/>
+      <c r="L15" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M15" s="26" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>4410271532</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="27" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1549,12 +1555,12 @@
           <t>Associate Developer</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>HealthStream</t>
         </is>
       </c>
-      <c r="E16" s="24" t="inlineStr">
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>Nashville, TN</t>
         </is>
@@ -1569,12 +1575,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H16" s="24" t="inlineStr">
+      <c r="H16" s="27" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I16" s="24" t="inlineStr">
+      <c r="I16" s="27" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1589,20 +1595,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L16" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M16" s="24" t="inlineStr"/>
+      <c r="L16" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M16" s="27" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="26" t="inlineStr">
         <is>
           <t>4304445726</t>
         </is>
       </c>
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1612,12 +1618,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
+      <c r="D17" s="26" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E17" s="25" t="inlineStr">
+      <c r="E17" s="26" t="inlineStr">
         <is>
           <t>Oregon, United States</t>
         </is>
@@ -1632,12 +1638,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H17" s="25" t="inlineStr">
+      <c r="H17" s="26" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="I17" s="25" t="inlineStr">
+      <c r="I17" s="26" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1652,20 +1658,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L17" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M17" s="25" t="inlineStr"/>
+      <c r="L17" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M17" s="26" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>4342036151</t>
         </is>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="27" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1675,12 +1681,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>Modern Treasury</t>
         </is>
       </c>
-      <c r="E18" s="24" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
@@ -1695,12 +1701,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H18" s="24" t="inlineStr">
+      <c r="H18" s="27" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I18" s="24" t="inlineStr">
+      <c r="I18" s="27" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1715,20 +1721,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L18" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M18" s="24" t="inlineStr"/>
+      <c r="L18" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M18" s="27" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="25" t="inlineStr">
+      <c r="A19" s="26" t="inlineStr">
         <is>
           <t>4304441843</t>
         </is>
       </c>
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1738,12 +1744,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D19" s="25" t="inlineStr">
+      <c r="D19" s="26" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E19" s="25" t="inlineStr">
+      <c r="E19" s="26" t="inlineStr">
         <is>
           <t>Idaho, United States</t>
         </is>
@@ -1758,12 +1764,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H19" s="25" t="inlineStr">
+      <c r="H19" s="26" t="inlineStr">
         <is>
           <t>157</t>
         </is>
       </c>
-      <c r="I19" s="25" t="inlineStr">
+      <c r="I19" s="26" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1778,20 +1784,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L19" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M19" s="25" t="inlineStr"/>
+      <c r="L19" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M19" s="26" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>4408047047</t>
         </is>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="27" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1801,12 +1807,12 @@
           <t>Computer Sciences - Graduates - AI Training - Las Vegas, US</t>
         </is>
       </c>
-      <c r="D20" s="24" t="inlineStr">
+      <c r="D20" s="27" t="inlineStr">
         <is>
           <t>Prolific</t>
         </is>
       </c>
-      <c r="E20" s="24" t="inlineStr">
+      <c r="E20" s="27" t="inlineStr">
         <is>
           <t>Las Vegas, NV</t>
         </is>
@@ -1821,12 +1827,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H20" s="24" t="inlineStr">
+      <c r="H20" s="27" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I20" s="24" t="inlineStr">
+      <c r="I20" s="27" t="inlineStr">
         <is>
           <t>Temporary</t>
         </is>
@@ -1841,20 +1847,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L20" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M20" s="24" t="inlineStr"/>
+      <c r="L20" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M20" s="27" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>4304444837</t>
         </is>
       </c>
-      <c r="B21" s="25" t="inlineStr">
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1864,12 +1870,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D21" s="25" t="inlineStr">
+      <c r="D21" s="26" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E21" s="25" t="inlineStr">
+      <c r="E21" s="26" t="inlineStr">
         <is>
           <t>New Jersey, United States</t>
         </is>
@@ -1884,12 +1890,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H21" s="25" t="inlineStr">
+      <c r="H21" s="26" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I21" s="25" t="inlineStr">
+      <c r="I21" s="26" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1904,20 +1910,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L21" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M21" s="25" t="inlineStr"/>
+      <c r="L21" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M21" s="26" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>4405641326</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="27" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1927,12 +1933,12 @@
           <t>Full-stack Engineer</t>
         </is>
       </c>
-      <c r="D22" s="24" t="inlineStr">
+      <c r="D22" s="27" t="inlineStr">
         <is>
           <t>PartnerTap</t>
         </is>
       </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="E22" s="27" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1947,12 +1953,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H22" s="24" t="inlineStr">
+      <c r="H22" s="27" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I22" s="24" t="inlineStr">
+      <c r="I22" s="27" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1967,20 +1973,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L22" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M22" s="24" t="inlineStr"/>
+      <c r="L22" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M22" s="27" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t>4341020900</t>
         </is>
       </c>
-      <c r="B23" s="25" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1990,12 +1996,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D23" s="25" t="inlineStr">
+      <c r="D23" s="26" t="inlineStr">
         <is>
           <t>PlanIT Group, LLC</t>
         </is>
       </c>
-      <c r="E23" s="25" t="inlineStr">
+      <c r="E23" s="26" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -2010,12 +2016,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H23" s="25" t="inlineStr">
+      <c r="H23" s="26" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I23" s="25" t="inlineStr">
+      <c r="I23" s="26" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
@@ -2030,20 +2036,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L23" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M23" s="25" t="inlineStr"/>
+      <c r="L23" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M23" s="26" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t>4304450637</t>
         </is>
       </c>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B24" s="27" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2053,12 +2059,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D24" s="24" t="inlineStr">
+      <c r="D24" s="27" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E24" s="24" t="inlineStr">
+      <c r="E24" s="27" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -2073,12 +2079,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H24" s="24" t="inlineStr">
+      <c r="H24" s="27" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I24" s="24" t="inlineStr">
+      <c r="I24" s="27" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2093,20 +2099,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L24" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M24" s="24" t="inlineStr"/>
+      <c r="L24" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M24" s="27" t="inlineStr"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="26" t="inlineStr">
         <is>
           <t>4304451654</t>
         </is>
       </c>
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2116,12 +2122,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D25" s="25" t="inlineStr">
+      <c r="D25" s="26" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E25" s="25" t="inlineStr">
+      <c r="E25" s="26" t="inlineStr">
         <is>
           <t>Utah, United States</t>
         </is>
@@ -2136,12 +2142,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H25" s="25" t="inlineStr">
+      <c r="H25" s="26" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I25" s="25" t="inlineStr">
+      <c r="I25" s="26" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2156,20 +2162,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L25" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M25" s="25" t="inlineStr"/>
+      <c r="L25" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M25" s="26" t="inlineStr"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="24" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>4413745880</t>
         </is>
       </c>
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B26" s="27" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2179,12 +2185,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D26" s="24" t="inlineStr">
+      <c r="D26" s="27" t="inlineStr">
         <is>
           <t>Crate &amp; Barrel</t>
         </is>
       </c>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="E26" s="27" t="inlineStr">
         <is>
           <t>Northbrook, IL</t>
         </is>
@@ -2199,12 +2205,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H26" s="24" t="inlineStr">
+      <c r="H26" s="27" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I26" s="24" t="inlineStr">
+      <c r="I26" s="27" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2219,20 +2225,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L26" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M26" s="24" t="inlineStr"/>
+      <c r="L26" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M26" s="27" t="inlineStr"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="25" t="inlineStr">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t>4304438841</t>
         </is>
       </c>
-      <c r="B27" s="25" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2242,12 +2248,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D27" s="25" t="inlineStr">
+      <c r="D27" s="26" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E27" s="25" t="inlineStr">
+      <c r="E27" s="26" t="inlineStr">
         <is>
           <t>Connecticut, United States</t>
         </is>
@@ -2262,12 +2268,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H27" s="25" t="inlineStr">
+      <c r="H27" s="26" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I27" s="25" t="inlineStr">
+      <c r="I27" s="26" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2282,20 +2288,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L27" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M27" s="25" t="inlineStr"/>
+      <c r="L27" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M27" s="26" t="inlineStr"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>4393215930</t>
         </is>
       </c>
-      <c r="B28" s="24" t="inlineStr">
+      <c r="B28" s="27" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2305,12 +2311,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D28" s="24" t="inlineStr">
+      <c r="D28" s="27" t="inlineStr">
         <is>
           <t>Transcend</t>
         </is>
       </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="E28" s="27" t="inlineStr">
         <is>
           <t>California, United States</t>
         </is>
@@ -2325,12 +2331,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H28" s="24" t="inlineStr">
+      <c r="H28" s="27" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I28" s="24" t="inlineStr">
+      <c r="I28" s="27" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2345,20 +2351,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L28" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M28" s="24" t="inlineStr"/>
+      <c r="L28" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M28" s="27" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t>4304445723</t>
         </is>
       </c>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B29" s="26" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2368,12 +2374,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D29" s="25" t="inlineStr">
+      <c r="D29" s="26" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E29" s="25" t="inlineStr">
+      <c r="E29" s="26" t="inlineStr">
         <is>
           <t>Illinois, United States</t>
         </is>
@@ -2388,12 +2394,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H29" s="25" t="inlineStr">
+      <c r="H29" s="26" t="inlineStr">
         <is>
           <t>198</t>
         </is>
       </c>
-      <c r="I29" s="25" t="inlineStr">
+      <c r="I29" s="26" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2408,20 +2414,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L29" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M29" s="25" t="inlineStr"/>
+      <c r="L29" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M29" s="26" t="inlineStr"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="A30" s="27" t="inlineStr">
         <is>
           <t>4396380649</t>
         </is>
       </c>
-      <c r="B30" s="24" t="inlineStr">
+      <c r="B30" s="27" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2431,12 +2437,12 @@
           <t>Full-Stack Developer Intern, Music &amp; Audio</t>
         </is>
       </c>
-      <c r="D30" s="24" t="inlineStr">
+      <c r="D30" s="27" t="inlineStr">
         <is>
           <t>Melotech</t>
         </is>
       </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="E30" s="27" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
@@ -2451,12 +2457,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H30" s="24" t="inlineStr">
+      <c r="H30" s="27" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I30" s="24" t="inlineStr">
+      <c r="I30" s="27" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -2471,20 +2477,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L30" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M30" s="24" t="inlineStr"/>
+      <c r="L30" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M30" s="27" t="inlineStr"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t>4304454025</t>
         </is>
       </c>
-      <c r="B31" s="25" t="inlineStr">
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2494,12 +2500,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D31" s="25" t="inlineStr">
+      <c r="D31" s="26" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E31" s="25" t="inlineStr">
+      <c r="E31" s="26" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -2514,12 +2520,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H31" s="25" t="inlineStr">
+      <c r="H31" s="26" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I31" s="25" t="inlineStr">
+      <c r="I31" s="26" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2534,20 +2540,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L31" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M31" s="25" t="inlineStr"/>
+      <c r="L31" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M31" s="26" t="inlineStr"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t>4309802287</t>
         </is>
       </c>
-      <c r="B32" s="24" t="inlineStr">
+      <c r="B32" s="27" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2557,12 +2563,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D32" s="24" t="inlineStr">
+      <c r="D32" s="27" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="E32" s="27" t="inlineStr">
         <is>
           <t>New Jersey, United States</t>
         </is>
@@ -2577,12 +2583,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H32" s="24" t="inlineStr">
+      <c r="H32" s="27" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I32" s="24" t="inlineStr">
+      <c r="I32" s="27" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2597,20 +2603,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L32" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M32" s="24" t="inlineStr"/>
+      <c r="L32" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M32" s="27" t="inlineStr"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="25" t="inlineStr">
+      <c r="A33" s="26" t="inlineStr">
         <is>
           <t>4309694880</t>
         </is>
       </c>
-      <c r="B33" s="25" t="inlineStr">
+      <c r="B33" s="26" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2620,12 +2626,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D33" s="25" t="inlineStr">
+      <c r="D33" s="26" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E33" s="25" t="inlineStr">
+      <c r="E33" s="26" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -2640,12 +2646,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H33" s="25" t="inlineStr">
+      <c r="H33" s="26" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I33" s="25" t="inlineStr">
+      <c r="I33" s="26" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2660,20 +2666,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L33" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M33" s="25" t="inlineStr"/>
+      <c r="L33" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M33" s="26" t="inlineStr"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="A34" s="27" t="inlineStr">
         <is>
           <t>4411274012</t>
         </is>
       </c>
-      <c r="B34" s="24" t="inlineStr">
+      <c r="B34" s="27" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2683,12 +2689,12 @@
           <t>Junior UI Developer</t>
         </is>
       </c>
-      <c r="D34" s="24" t="inlineStr">
+      <c r="D34" s="27" t="inlineStr">
         <is>
           <t>General Dynamics Information Technology</t>
         </is>
       </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="E34" s="27" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -2703,12 +2709,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H34" s="24" t="inlineStr">
+      <c r="H34" s="27" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I34" s="24" t="inlineStr">
+      <c r="I34" s="27" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2723,20 +2729,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L34" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M34" s="24" t="inlineStr"/>
+      <c r="L34" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M34" s="27" t="inlineStr"/>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="25" t="inlineStr">
+      <c r="A35" s="26" t="inlineStr">
         <is>
           <t>4264562292</t>
         </is>
       </c>
-      <c r="B35" s="25" t="inlineStr">
+      <c r="B35" s="26" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2746,12 +2752,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D35" s="25" t="inlineStr">
+      <c r="D35" s="26" t="inlineStr">
         <is>
           <t>Cymertek Corporation</t>
         </is>
       </c>
-      <c r="E35" s="25" t="inlineStr">
+      <c r="E35" s="26" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
@@ -2766,12 +2772,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H35" s="25" t="inlineStr">
+      <c r="H35" s="26" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="I35" s="25" t="inlineStr">
+      <c r="I35" s="26" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2786,20 +2792,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L35" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M35" s="25" t="inlineStr"/>
+      <c r="L35" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M35" s="26" t="inlineStr"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="24" t="inlineStr">
+      <c r="A36" s="27" t="inlineStr">
         <is>
           <t>4417482675</t>
         </is>
       </c>
-      <c r="B36" s="24" t="inlineStr">
+      <c r="B36" s="27" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2809,12 +2815,12 @@
           <t>Software Developer I</t>
         </is>
       </c>
-      <c r="D36" s="24" t="inlineStr">
+      <c r="D36" s="27" t="inlineStr">
         <is>
           <t>El Paso Water</t>
         </is>
       </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="E36" s="27" t="inlineStr">
         <is>
           <t>El Paso, TX</t>
         </is>
@@ -2829,12 +2835,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H36" s="24" t="inlineStr">
+      <c r="H36" s="27" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="I36" s="24" t="inlineStr">
+      <c r="I36" s="27" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2849,20 +2855,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L36" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M36" s="24" t="inlineStr"/>
+      <c r="L36" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M36" s="27" t="inlineStr"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="25" t="inlineStr">
+      <c r="A37" s="26" t="inlineStr">
         <is>
           <t>4416508200</t>
         </is>
       </c>
-      <c r="B37" s="25" t="inlineStr">
+      <c r="B37" s="26" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2872,12 +2878,12 @@
           <t>Software Development Engineer in Test Intern (Global E-Commerce) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D37" s="25" t="inlineStr">
+      <c r="D37" s="26" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E37" s="25" t="inlineStr">
+      <c r="E37" s="26" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -2892,12 +2898,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H37" s="25" t="inlineStr">
+      <c r="H37" s="26" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I37" s="25" t="inlineStr">
+      <c r="I37" s="26" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -2912,20 +2918,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L37" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M37" s="25" t="inlineStr"/>
+      <c r="L37" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M37" s="26" t="inlineStr"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="24" t="inlineStr">
+      <c r="A38" s="27" t="inlineStr">
         <is>
           <t>4309809191</t>
         </is>
       </c>
-      <c r="B38" s="24" t="inlineStr">
+      <c r="B38" s="27" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
@@ -2935,12 +2941,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D38" s="24" t="inlineStr">
+      <c r="D38" s="27" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E38" s="24" t="inlineStr">
+      <c r="E38" s="27" t="inlineStr">
         <is>
           <t>Ohio, United States</t>
         </is>
@@ -2955,12 +2961,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H38" s="24" t="inlineStr">
+      <c r="H38" s="27" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="I38" s="24" t="inlineStr">
+      <c r="I38" s="27" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2975,20 +2981,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L38" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M38" s="24" t="inlineStr"/>
+      <c r="L38" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M38" s="27" t="inlineStr"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="25" t="inlineStr">
+      <c r="A39" s="26" t="inlineStr">
         <is>
           <t>3986118096</t>
         </is>
       </c>
-      <c r="B39" s="25" t="inlineStr">
+      <c r="B39" s="26" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
@@ -2998,12 +3004,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D39" s="25" t="inlineStr">
+      <c r="D39" s="26" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E39" s="25" t="inlineStr">
+      <c r="E39" s="26" t="inlineStr">
         <is>
           <t>Irving, TX</t>
         </is>
@@ -3018,12 +3024,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H39" s="25" t="inlineStr">
+      <c r="H39" s="26" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I39" s="25" t="inlineStr">
+      <c r="I39" s="26" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3038,20 +3044,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L39" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M39" s="25" t="inlineStr"/>
+      <c r="L39" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M39" s="26" t="inlineStr"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="24" t="inlineStr">
+      <c r="A40" s="27" t="inlineStr">
         <is>
           <t>4309808244</t>
         </is>
       </c>
-      <c r="B40" s="24" t="inlineStr">
+      <c r="B40" s="27" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3061,12 +3067,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D40" s="24" t="inlineStr">
+      <c r="D40" s="27" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E40" s="24" t="inlineStr">
+      <c r="E40" s="27" t="inlineStr">
         <is>
           <t>Massachusetts, United States</t>
         </is>
@@ -3081,12 +3087,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H40" s="24" t="inlineStr">
+      <c r="H40" s="27" t="inlineStr">
         <is>
           <t>166</t>
         </is>
       </c>
-      <c r="I40" s="24" t="inlineStr">
+      <c r="I40" s="27" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3101,20 +3107,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L40" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M40" s="24" t="inlineStr"/>
+      <c r="L40" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M40" s="27" t="inlineStr"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="25" t="inlineStr">
+      <c r="A41" s="26" t="inlineStr">
         <is>
           <t>4362173625</t>
         </is>
       </c>
-      <c r="B41" s="25" t="inlineStr">
+      <c r="B41" s="26" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3124,12 +3130,12 @@
           <t>Full Stack Engineer</t>
         </is>
       </c>
-      <c r="D41" s="25" t="inlineStr">
+      <c r="D41" s="26" t="inlineStr">
         <is>
           <t>Empower Sleep</t>
         </is>
       </c>
-      <c r="E41" s="25" t="inlineStr">
+      <c r="E41" s="26" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3144,12 +3150,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H41" s="25" t="inlineStr">
+      <c r="H41" s="26" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I41" s="25" t="inlineStr">
+      <c r="I41" s="26" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3164,20 +3170,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L41" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M41" s="25" t="inlineStr"/>
+      <c r="L41" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M41" s="26" t="inlineStr"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="24" t="inlineStr">
+      <c r="A42" s="27" t="inlineStr">
         <is>
           <t>4309812093</t>
         </is>
       </c>
-      <c r="B42" s="24" t="inlineStr">
+      <c r="B42" s="27" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3187,12 +3193,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D42" s="24" t="inlineStr">
+      <c r="D42" s="27" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E42" s="24" t="inlineStr">
+      <c r="E42" s="27" t="inlineStr">
         <is>
           <t>Florida, United States</t>
         </is>
@@ -3207,12 +3213,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H42" s="24" t="inlineStr">
+      <c r="H42" s="27" t="inlineStr">
         <is>
           <t>158</t>
         </is>
       </c>
-      <c r="I42" s="24" t="inlineStr">
+      <c r="I42" s="27" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3227,20 +3233,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L42" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M42" s="24" t="inlineStr"/>
+      <c r="L42" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M42" s="27" t="inlineStr"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="25" t="inlineStr">
+      <c r="A43" s="26" t="inlineStr">
         <is>
           <t>4391759914</t>
         </is>
       </c>
-      <c r="B43" s="25" t="inlineStr">
+      <c r="B43" s="26" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3250,12 +3256,12 @@
           <t>QA Engineering Internship</t>
         </is>
       </c>
-      <c r="D43" s="25" t="inlineStr">
+      <c r="D43" s="26" t="inlineStr">
         <is>
           <t>Chartbeat</t>
         </is>
       </c>
-      <c r="E43" s="25" t="inlineStr">
+      <c r="E43" s="26" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -3270,12 +3276,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H43" s="25" t="inlineStr">
+      <c r="H43" s="26" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="I43" s="25" t="inlineStr">
+      <c r="I43" s="26" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3290,20 +3296,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L43" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M43" s="25" t="inlineStr"/>
+      <c r="L43" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M43" s="26" t="inlineStr"/>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="24" t="inlineStr">
+      <c r="A44" s="27" t="inlineStr">
         <is>
           <t>4412855678</t>
         </is>
       </c>
-      <c r="B44" s="24" t="inlineStr">
+      <c r="B44" s="27" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3313,12 +3319,12 @@
           <t>AI Integration Engineer</t>
         </is>
       </c>
-      <c r="D44" s="24" t="inlineStr">
+      <c r="D44" s="27" t="inlineStr">
         <is>
           <t>UST</t>
         </is>
       </c>
-      <c r="E44" s="24" t="inlineStr">
+      <c r="E44" s="27" t="inlineStr">
         <is>
           <t>Santa Clara, CA</t>
         </is>
@@ -3333,12 +3339,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H44" s="24" t="inlineStr">
+      <c r="H44" s="27" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I44" s="24" t="inlineStr">
+      <c r="I44" s="27" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3353,20 +3359,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L44" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M44" s="24" t="inlineStr"/>
+      <c r="L44" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M44" s="27" t="inlineStr"/>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="25" t="inlineStr">
+      <c r="A45" s="26" t="inlineStr">
         <is>
           <t>4309805219</t>
         </is>
       </c>
-      <c r="B45" s="25" t="inlineStr">
+      <c r="B45" s="26" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3376,12 +3382,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D45" s="25" t="inlineStr">
+      <c r="D45" s="26" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E45" s="25" t="inlineStr">
+      <c r="E45" s="26" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -3396,12 +3402,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H45" s="25" t="inlineStr">
+      <c r="H45" s="26" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I45" s="25" t="inlineStr">
+      <c r="I45" s="26" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3416,20 +3422,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L45" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M45" s="25" t="inlineStr"/>
+      <c r="L45" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M45" s="26" t="inlineStr"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="24" t="inlineStr">
+      <c r="A46" s="27" t="inlineStr">
         <is>
           <t>4409726429</t>
         </is>
       </c>
-      <c r="B46" s="24" t="inlineStr">
+      <c r="B46" s="27" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3439,12 +3445,12 @@
           <t>Data Science Intern</t>
         </is>
       </c>
-      <c r="D46" s="24" t="inlineStr">
+      <c r="D46" s="27" t="inlineStr">
         <is>
           <t>Rundoo</t>
         </is>
       </c>
-      <c r="E46" s="24" t="inlineStr">
+      <c r="E46" s="27" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3459,12 +3465,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H46" s="24" t="inlineStr">
+      <c r="H46" s="27" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I46" s="24" t="inlineStr">
+      <c r="I46" s="27" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3479,20 +3485,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L46" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M46" s="24" t="inlineStr"/>
+      <c r="L46" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M46" s="27" t="inlineStr"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="25" t="inlineStr">
+      <c r="A47" s="26" t="inlineStr">
         <is>
           <t>4305671729</t>
         </is>
       </c>
-      <c r="B47" s="25" t="inlineStr">
+      <c r="B47" s="26" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3502,12 +3508,12 @@
           <t>DoD SkillBridge Internship/Fellowship Opportunity Application (U.S. Military Only)</t>
         </is>
       </c>
-      <c r="D47" s="25" t="inlineStr">
+      <c r="D47" s="26" t="inlineStr">
         <is>
           <t>Onsights</t>
         </is>
       </c>
-      <c r="E47" s="25" t="inlineStr">
+      <c r="E47" s="26" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -3522,12 +3528,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H47" s="25" t="inlineStr">
+      <c r="H47" s="26" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I47" s="25" t="inlineStr">
+      <c r="I47" s="26" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3542,20 +3548,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L47" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M47" s="25" t="inlineStr"/>
+      <c r="L47" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M47" s="26" t="inlineStr"/>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="24" t="inlineStr">
+      <c r="A48" s="27" t="inlineStr">
         <is>
           <t>4414096220</t>
         </is>
       </c>
-      <c r="B48" s="24" t="inlineStr">
+      <c r="B48" s="27" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3565,12 +3571,12 @@
           <t>Visualization Engineer Intern</t>
         </is>
       </c>
-      <c r="D48" s="24" t="inlineStr">
+      <c r="D48" s="27" t="inlineStr">
         <is>
           <t>Leidos</t>
         </is>
       </c>
-      <c r="E48" s="24" t="inlineStr">
+      <c r="E48" s="27" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3585,12 +3591,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H48" s="24" t="inlineStr">
+      <c r="H48" s="27" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="I48" s="24" t="inlineStr">
+      <c r="I48" s="27" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3605,20 +3611,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L48" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M48" s="24" t="inlineStr"/>
+      <c r="L48" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M48" s="27" t="inlineStr"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="25" t="inlineStr">
+      <c r="A49" s="26" t="inlineStr">
         <is>
           <t>4361076044</t>
         </is>
       </c>
-      <c r="B49" s="25" t="inlineStr">
+      <c r="B49" s="26" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3628,12 +3634,12 @@
           <t>GenAI Engineering Intern  - SkillBridge (Remote)</t>
         </is>
       </c>
-      <c r="D49" s="25" t="inlineStr">
+      <c r="D49" s="26" t="inlineStr">
         <is>
           <t>CrowdStrike</t>
         </is>
       </c>
-      <c r="E49" s="25" t="inlineStr">
+      <c r="E49" s="26" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3648,12 +3654,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H49" s="25" t="inlineStr">
+      <c r="H49" s="26" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I49" s="25" t="inlineStr">
+      <c r="I49" s="26" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3668,20 +3674,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L49" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M49" s="25" t="inlineStr"/>
+      <c r="L49" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M49" s="26" t="inlineStr"/>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="24" t="inlineStr">
+      <c r="A50" s="27" t="inlineStr">
         <is>
           <t>4417553585</t>
         </is>
       </c>
-      <c r="B50" s="24" t="inlineStr">
+      <c r="B50" s="27" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3691,12 +3697,12 @@
           <t>Entry-Level Software Engineer | Remote</t>
         </is>
       </c>
-      <c r="D50" s="24" t="inlineStr">
+      <c r="D50" s="27" t="inlineStr">
         <is>
           <t>Crossing Hurdles</t>
         </is>
       </c>
-      <c r="E50" s="24" t="inlineStr">
+      <c r="E50" s="27" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3711,12 +3717,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H50" s="24" t="inlineStr">
+      <c r="H50" s="27" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I50" s="24" t="inlineStr">
+      <c r="I50" s="27" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3731,20 +3737,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L50" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M50" s="24" t="inlineStr"/>
+      <c r="L50" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M50" s="27" t="inlineStr"/>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="25" t="inlineStr">
+      <c r="A51" s="26" t="inlineStr">
         <is>
           <t>4309699451</t>
         </is>
       </c>
-      <c r="B51" s="25" t="inlineStr">
+      <c r="B51" s="26" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3754,12 +3760,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D51" s="25" t="inlineStr">
+      <c r="D51" s="26" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E51" s="25" t="inlineStr">
+      <c r="E51" s="26" t="inlineStr">
         <is>
           <t>Washington, United States</t>
         </is>
@@ -3774,12 +3780,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H51" s="25" t="inlineStr">
+      <c r="H51" s="26" t="inlineStr">
         <is>
           <t>109</t>
         </is>
       </c>
-      <c r="I51" s="25" t="inlineStr">
+      <c r="I51" s="26" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3794,20 +3800,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L51" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M51" s="25" t="inlineStr"/>
+      <c r="L51" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M51" s="26" t="inlineStr"/>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="24" t="inlineStr">
+      <c r="A52" s="27" t="inlineStr">
         <is>
           <t>4406945262</t>
         </is>
       </c>
-      <c r="B52" s="24" t="inlineStr">
+      <c r="B52" s="27" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3817,12 +3823,12 @@
           <t>DevSecOps Intern</t>
         </is>
       </c>
-      <c r="D52" s="24" t="inlineStr">
+      <c r="D52" s="27" t="inlineStr">
         <is>
           <t>Modern Technology Solutions, Inc. (MTSI)</t>
         </is>
       </c>
-      <c r="E52" s="24" t="inlineStr">
+      <c r="E52" s="27" t="inlineStr">
         <is>
           <t>Niceville, FL</t>
         </is>
@@ -3837,12 +3843,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H52" s="24" t="inlineStr">
+      <c r="H52" s="27" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="I52" s="24" t="inlineStr">
+      <c r="I52" s="27" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3857,20 +3863,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L52" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M52" s="24" t="inlineStr"/>
+      <c r="L52" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M52" s="27" t="inlineStr"/>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="25" t="inlineStr">
+      <c r="A53" s="26" t="inlineStr">
         <is>
           <t>4407937810</t>
         </is>
       </c>
-      <c r="B53" s="25" t="inlineStr">
+      <c r="B53" s="26" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3880,12 +3886,12 @@
           <t>Temporary Intern - Agentic AI &amp; Neural-Symbolic Systems (Healthcare)</t>
         </is>
       </c>
-      <c r="D53" s="25" t="inlineStr">
+      <c r="D53" s="26" t="inlineStr">
         <is>
           <t>Cotiviti</t>
         </is>
       </c>
-      <c r="E53" s="25" t="inlineStr">
+      <c r="E53" s="26" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3900,12 +3906,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H53" s="25" t="inlineStr">
+      <c r="H53" s="26" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I53" s="25" t="inlineStr">
+      <c r="I53" s="26" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3920,20 +3926,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L53" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M53" s="25" t="inlineStr"/>
+      <c r="L53" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M53" s="26" t="inlineStr"/>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="24" t="inlineStr">
+      <c r="A54" s="27" t="inlineStr">
         <is>
           <t>4414089997</t>
         </is>
       </c>
-      <c r="B54" s="24" t="inlineStr">
+      <c r="B54" s="27" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3943,12 +3949,12 @@
           <t>Visualization Engineer Intern</t>
         </is>
       </c>
-      <c r="D54" s="24" t="inlineStr">
+      <c r="D54" s="27" t="inlineStr">
         <is>
           <t>Leidos</t>
         </is>
       </c>
-      <c r="E54" s="24" t="inlineStr">
+      <c r="E54" s="27" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3963,12 +3969,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H54" s="24" t="inlineStr">
+      <c r="H54" s="27" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="I54" s="24" t="inlineStr">
+      <c r="I54" s="27" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3983,20 +3989,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L54" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M54" s="24" t="inlineStr"/>
+      <c r="L54" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M54" s="27" t="inlineStr"/>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="25" t="inlineStr">
+      <c r="A55" s="26" t="inlineStr">
         <is>
           <t>4387443129</t>
         </is>
       </c>
-      <c r="B55" s="25" t="inlineStr">
+      <c r="B55" s="26" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4006,12 +4012,12 @@
           <t>2026 Interns</t>
         </is>
       </c>
-      <c r="D55" s="25" t="inlineStr">
+      <c r="D55" s="26" t="inlineStr">
         <is>
           <t>Givelify</t>
         </is>
       </c>
-      <c r="E55" s="25" t="inlineStr">
+      <c r="E55" s="26" t="inlineStr">
         <is>
           <t>Dallas, TX</t>
         </is>
@@ -4026,12 +4032,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H55" s="25" t="inlineStr">
+      <c r="H55" s="26" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I55" s="25" t="inlineStr">
+      <c r="I55" s="26" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -4046,20 +4052,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L55" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M55" s="25" t="inlineStr"/>
+      <c r="L55" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M55" s="26" t="inlineStr"/>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="24" t="inlineStr">
+      <c r="A56" s="27" t="inlineStr">
         <is>
           <t>4337980765</t>
         </is>
       </c>
-      <c r="B56" s="24" t="inlineStr">
+      <c r="B56" s="27" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4069,12 +4075,12 @@
           <t>Submitting for a General Internship Application</t>
         </is>
       </c>
-      <c r="D56" s="24" t="inlineStr">
+      <c r="D56" s="27" t="inlineStr">
         <is>
           <t>Chainguard</t>
         </is>
       </c>
-      <c r="E56" s="24" t="inlineStr">
+      <c r="E56" s="27" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4089,12 +4095,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H56" s="24" t="inlineStr">
+      <c r="H56" s="27" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I56" s="24" t="inlineStr">
+      <c r="I56" s="27" t="inlineStr">
         <is>
           <t>Volunteer</t>
         </is>
@@ -4109,20 +4115,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L56" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M56" s="24" t="inlineStr"/>
+      <c r="L56" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M56" s="27" t="inlineStr"/>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="25" t="inlineStr">
+      <c r="A57" s="26" t="inlineStr">
         <is>
           <t>4417030460</t>
         </is>
       </c>
-      <c r="B57" s="25" t="inlineStr">
+      <c r="B57" s="26" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4132,12 +4138,12 @@
           <t>AI Researcher Intern</t>
         </is>
       </c>
-      <c r="D57" s="25" t="inlineStr">
+      <c r="D57" s="26" t="inlineStr">
         <is>
           <t>BioSpace</t>
         </is>
       </c>
-      <c r="E57" s="25" t="inlineStr">
+      <c r="E57" s="26" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4152,12 +4158,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H57" s="25" t="inlineStr">
+      <c r="H57" s="26" t="inlineStr">
         <is>
           <t>151</t>
         </is>
       </c>
-      <c r="I57" s="25" t="inlineStr">
+      <c r="I57" s="26" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4172,20 +4178,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L57" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M57" s="25" t="inlineStr"/>
+      <c r="L57" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M57" s="26" t="inlineStr"/>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="24" t="inlineStr">
+      <c r="A58" s="27" t="inlineStr">
         <is>
           <t>4406930916</t>
         </is>
       </c>
-      <c r="B58" s="24" t="inlineStr">
+      <c r="B58" s="27" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4195,12 +4201,12 @@
           <t>DevSecOps Intern</t>
         </is>
       </c>
-      <c r="D58" s="24" t="inlineStr">
+      <c r="D58" s="27" t="inlineStr">
         <is>
           <t>Modern Technology Solutions, Inc. (MTSI)</t>
         </is>
       </c>
-      <c r="E58" s="24" t="inlineStr">
+      <c r="E58" s="27" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4215,12 +4221,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H58" s="24" t="inlineStr">
+      <c r="H58" s="27" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I58" s="24" t="inlineStr">
+      <c r="I58" s="27" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -4235,20 +4241,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L58" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M58" s="24" t="inlineStr"/>
+      <c r="L58" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M58" s="27" t="inlineStr"/>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="25" t="inlineStr">
+      <c r="A59" s="26" t="inlineStr">
         <is>
           <t>4385798937</t>
         </is>
       </c>
-      <c r="B59" s="25" t="inlineStr">
+      <c r="B59" s="26" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4258,12 +4264,12 @@
           <t>Research Intern on Generative and Protective AI for Content Creation</t>
         </is>
       </c>
-      <c r="D59" s="25" t="inlineStr">
+      <c r="D59" s="26" t="inlineStr">
         <is>
           <t>SonyAI</t>
         </is>
       </c>
-      <c r="E59" s="25" t="inlineStr">
+      <c r="E59" s="26" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -4278,12 +4284,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H59" s="25" t="inlineStr">
+      <c r="H59" s="26" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I59" s="25" t="inlineStr">
+      <c r="I59" s="26" t="inlineStr">
         <is>
           <t>Part-time</t>
         </is>
@@ -4298,20 +4304,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L59" s="25" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M59" s="25" t="inlineStr"/>
+      <c r="L59" s="26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M59" s="26" t="inlineStr"/>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="24" t="inlineStr">
+      <c r="A60" s="27" t="inlineStr">
         <is>
           <t>4414396950</t>
         </is>
       </c>
-      <c r="B60" s="24" t="inlineStr">
+      <c r="B60" s="27" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4321,12 +4327,12 @@
           <t>Power Platform Intern</t>
         </is>
       </c>
-      <c r="D60" s="24" t="inlineStr">
+      <c r="D60" s="27" t="inlineStr">
         <is>
           <t>Leidos</t>
         </is>
       </c>
-      <c r="E60" s="24" t="inlineStr">
+      <c r="E60" s="27" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4341,12 +4347,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H60" s="24" t="inlineStr">
+      <c r="H60" s="27" t="inlineStr">
         <is>
           <t>135</t>
         </is>
       </c>
-      <c r="I60" s="24" t="inlineStr">
+      <c r="I60" s="27" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4361,12 +4367,12 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L60" s="24" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M60" s="24" t="inlineStr"/>
+      <c r="L60" s="27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M60" s="27" t="inlineStr"/>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="26" t="inlineStr">
@@ -5691,8 +5697,386 @@
       </c>
       <c r="M81" s="26" t="inlineStr"/>
     </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="28" t="inlineStr">
+        <is>
+          <t>4418507307</t>
+        </is>
+      </c>
+      <c r="B82" s="28" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Entry Level Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D82" s="28" t="inlineStr">
+        <is>
+          <t>CORMAC</t>
+        </is>
+      </c>
+      <c r="E82" s="28" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F82" s="18" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="G82" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H82" s="28" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="I82" s="28" t="inlineStr">
+        <is>
+          <t>Volunteer</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>Skills: javascript, git, c, express, agile, Title match: Entry Level Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="K82" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L82" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M82" s="28" t="inlineStr"/>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="29" t="inlineStr">
+        <is>
+          <t>4413360938</t>
+        </is>
+      </c>
+      <c r="B83" s="29" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer Internship (Remote)</t>
+        </is>
+      </c>
+      <c r="D83" s="29" t="inlineStr">
+        <is>
+          <t>Orange Trail</t>
+        </is>
+      </c>
+      <c r="E83" s="29" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H83" s="29" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I83" s="29" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="J83" s="8" t="inlineStr">
+        <is>
+          <t>Skills: javascript, html, css, backend, c, llm, Title match: Software Engineer Internship (Remote)</t>
+        </is>
+      </c>
+      <c r="K83" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L83" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M83" s="29" t="inlineStr"/>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="28" t="inlineStr">
+        <is>
+          <t>4348111641</t>
+        </is>
+      </c>
+      <c r="B84" s="28" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D84" s="28" t="inlineStr">
+        <is>
+          <t>Simular</t>
+        </is>
+      </c>
+      <c r="E84" s="28" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H84" s="28" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I84" s="28" t="inlineStr">
+        <is>
+          <t>Volunteer</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, rest, backend, frontend, c, Title match: Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="K84" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L84" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M84" s="28" t="inlineStr"/>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="29" t="inlineStr">
+        <is>
+          <t>4411853543</t>
+        </is>
+      </c>
+      <c r="B85" s="29" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>Intern, Software Engineer</t>
+        </is>
+      </c>
+      <c r="D85" s="29" t="inlineStr">
+        <is>
+          <t>Accelerate Learning</t>
+        </is>
+      </c>
+      <c r="E85" s="29" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H85" s="29" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I85" s="29" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J85" s="8" t="inlineStr">
+        <is>
+          <t>Skills: react, node, aws, rest, api, git, Title match: Intern, Software Engineer</t>
+        </is>
+      </c>
+      <c r="K85" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L85" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M85" s="29" t="inlineStr"/>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="28" t="inlineStr">
+        <is>
+          <t>4408586245</t>
+        </is>
+      </c>
+      <c r="B86" s="28" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D86" s="28" t="inlineStr">
+        <is>
+          <t>Cantaloupe Inc</t>
+        </is>
+      </c>
+      <c r="E86" s="28" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H86" s="28" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I86" s="28" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>Skills: javascript, aws, rest, html, css, git, Title match: Junior Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="K86" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L86" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M86" s="28" t="inlineStr"/>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="29" t="inlineStr">
+        <is>
+          <t>4364536992</t>
+        </is>
+      </c>
+      <c r="B87" s="29" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>Summer Internship - Measurement, Research and Development - Academic Measurement</t>
+        </is>
+      </c>
+      <c r="D87" s="29" t="inlineStr">
+        <is>
+          <t>ChatGPT Jobs</t>
+        </is>
+      </c>
+      <c r="E87" s="29" t="inlineStr">
+        <is>
+          <t>Iowa City, IA</t>
+        </is>
+      </c>
+      <c r="F87" s="18" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="G87" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H87" s="29" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I87" s="29" t="inlineStr">
+        <is>
+          <t>Volunteer</t>
+        </is>
+      </c>
+      <c r="J87" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, rest, git, pytorch, machine learning, c, Title match: Summer Internship - Measurement, Research and Development - Academic Measurement</t>
+        </is>
+      </c>
+      <c r="K87" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L87" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M87" s="29" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M81"/>
+  <autoFilter ref="A1:M87"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -5774,6 +6158,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K87" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Job Matches" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Matches'!$A$1:$M$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Matches'!$A$1:$M$108</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -199,6 +199,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -572,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -658,12 +664,12 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>4406952064</t>
         </is>
       </c>
-      <c r="B2" s="27" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -673,12 +679,12 @@
           <t>DevSecOps Intern</t>
         </is>
       </c>
-      <c r="D2" s="27" t="inlineStr">
+      <c r="D2" s="28" t="inlineStr">
         <is>
           <t>Modern Technology Solutions, Inc. (MTSI)</t>
         </is>
       </c>
-      <c r="E2" s="27" t="inlineStr">
+      <c r="E2" s="28" t="inlineStr">
         <is>
           <t>Huntsville, AL</t>
         </is>
@@ -693,12 +699,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H2" s="27" t="inlineStr">
+      <c r="H2" s="28" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="I2" s="27" t="inlineStr">
+      <c r="I2" s="28" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -713,20 +719,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L2" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M2" s="27" t="inlineStr"/>
+      <c r="L2" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M2" s="28" t="inlineStr"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>4405630173</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -736,12 +742,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D3" s="29" t="inlineStr">
         <is>
           <t>DLRdmv®</t>
         </is>
       </c>
-      <c r="E3" s="26" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t>Dallas, TX</t>
         </is>
@@ -756,12 +762,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H3" s="26" t="inlineStr">
+      <c r="H3" s="29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I3" s="26" t="inlineStr">
+      <c r="I3" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -776,20 +782,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L3" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M3" s="26" t="inlineStr"/>
+      <c r="L3" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M3" s="29" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="27" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>4287414862</t>
         </is>
       </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -799,12 +805,12 @@
           <t>[Online Assessment]Software Development Engineer Intern (Network Automation)- 2026 Summer (BS/ MS)</t>
         </is>
       </c>
-      <c r="D4" s="27" t="inlineStr">
+      <c r="D4" s="28" t="inlineStr">
         <is>
           <t>ByteDance</t>
         </is>
       </c>
-      <c r="E4" s="27" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -819,12 +825,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H4" s="27" t="inlineStr">
+      <c r="H4" s="28" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I4" s="27" t="inlineStr">
+      <c r="I4" s="28" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -839,20 +845,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L4" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M4" s="27" t="inlineStr"/>
+      <c r="L4" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M4" s="28" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>4309805269</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -862,12 +868,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="29" t="inlineStr">
         <is>
           <t>Delaware, United States</t>
         </is>
@@ -882,12 +888,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H5" s="26" t="inlineStr">
+      <c r="H5" s="29" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="I5" s="26" t="inlineStr">
+      <c r="I5" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -902,20 +908,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L5" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M5" s="26" t="inlineStr"/>
+      <c r="L5" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M5" s="29" t="inlineStr"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>4371812987</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -925,12 +931,12 @@
           <t>Software Development Engineer Fall Intern - Military Veteran</t>
         </is>
       </c>
-      <c r="D6" s="27" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E6" s="27" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -945,12 +951,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H6" s="27" t="inlineStr">
+      <c r="H6" s="28" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="I6" s="27" t="inlineStr">
+      <c r="I6" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -965,20 +971,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L6" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M6" s="27" t="inlineStr"/>
+      <c r="L6" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M6" s="28" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>4274682122</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -988,12 +994,12 @@
           <t>Software Engineer Intern (Data Ecosystem) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1008,12 +1014,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H7" s="26" t="inlineStr">
+      <c r="H7" s="29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I7" s="26" t="inlineStr">
+      <c r="I7" s="29" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1028,20 +1034,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L7" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M7" s="26" t="inlineStr"/>
+      <c r="L7" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M7" s="29" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>4283848614</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1051,12 +1057,12 @@
           <t>[Online Assessment] Software Engineer Intern (Recommendation Infrastructure) - 2026 Fall (BS/ MS)</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E8" s="27" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1071,12 +1077,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H8" s="27" t="inlineStr">
+      <c r="H8" s="28" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I8" s="27" t="inlineStr">
+      <c r="I8" s="28" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1091,20 +1097,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L8" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M8" s="27" t="inlineStr"/>
+      <c r="L8" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M8" s="28" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>4411790844</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1114,12 +1120,12 @@
           <t>Software Engineer Intern (Infrastructure Automation) - Fall 2026</t>
         </is>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="E9" s="26" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -1134,12 +1140,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H9" s="26" t="inlineStr">
+      <c r="H9" s="29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I9" s="26" t="inlineStr">
+      <c r="I9" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1154,20 +1160,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L9" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M9" s="26" t="inlineStr"/>
+      <c r="L9" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M9" s="29" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>4332425058</t>
         </is>
       </c>
-      <c r="B10" s="27" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1177,12 +1183,12 @@
           <t>Software Development Engineer Internship - Fall 2026 (US)</t>
         </is>
       </c>
-      <c r="D10" s="27" t="inlineStr">
+      <c r="D10" s="28" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E10" s="27" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1197,12 +1203,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H10" s="27" t="inlineStr">
+      <c r="H10" s="28" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I10" s="27" t="inlineStr">
+      <c r="I10" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1217,20 +1223,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L10" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M10" s="27" t="inlineStr"/>
+      <c r="L10" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M10" s="28" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>4323643644</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1240,12 +1246,12 @@
           <t>[Online Assessment] Software Engineer Intern (Recommendation Infrastructure) - 2026 Summer (BS/ MS)</t>
         </is>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E11" s="26" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1260,12 +1266,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H11" s="26" t="inlineStr">
+      <c r="H11" s="29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I11" s="26" t="inlineStr">
+      <c r="I11" s="29" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1280,20 +1286,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L11" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M11" s="26" t="inlineStr"/>
+      <c r="L11" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M11" s="29" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>4320849104</t>
         </is>
       </c>
-      <c r="B12" s="27" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1303,12 +1309,12 @@
           <t>Software Engineer Intern (Commerce Ads) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D12" s="27" t="inlineStr">
+      <c r="D12" s="28" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E12" s="27" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1323,12 +1329,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H12" s="27" t="inlineStr">
+      <c r="H12" s="28" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I12" s="27" t="inlineStr">
+      <c r="I12" s="28" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1343,20 +1349,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L12" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M12" s="27" t="inlineStr"/>
+      <c r="L12" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M12" s="28" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>4401686051</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1366,12 +1372,12 @@
           <t>Front End Software Engineer</t>
         </is>
       </c>
-      <c r="D13" s="26" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>Saronic Technologies</t>
         </is>
       </c>
-      <c r="E13" s="26" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -1386,12 +1392,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H13" s="26" t="inlineStr">
+      <c r="H13" s="29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I13" s="26" t="inlineStr">
+      <c r="I13" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1406,20 +1412,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L13" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M13" s="26" t="inlineStr"/>
+      <c r="L13" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M13" s="29" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>4309696652</t>
         </is>
       </c>
-      <c r="B14" s="27" t="inlineStr">
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1429,12 +1435,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D14" s="27" t="inlineStr">
+      <c r="D14" s="28" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E14" s="27" t="inlineStr">
+      <c r="E14" s="28" t="inlineStr">
         <is>
           <t>Rhode Island, United States</t>
         </is>
@@ -1449,12 +1455,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H14" s="27" t="inlineStr">
+      <c r="H14" s="28" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="I14" s="27" t="inlineStr">
+      <c r="I14" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1469,20 +1475,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L14" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M14" s="27" t="inlineStr"/>
+      <c r="L14" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M14" s="28" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>4309804319</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1492,12 +1498,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E15" s="26" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>Colorado, United States</t>
         </is>
@@ -1512,12 +1518,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H15" s="26" t="inlineStr">
+      <c r="H15" s="29" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="I15" s="26" t="inlineStr">
+      <c r="I15" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1532,20 +1538,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L15" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M15" s="26" t="inlineStr"/>
+      <c r="L15" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M15" s="29" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="27" t="inlineStr">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>4410271532</t>
         </is>
       </c>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1555,12 +1561,12 @@
           <t>Associate Developer</t>
         </is>
       </c>
-      <c r="D16" s="27" t="inlineStr">
+      <c r="D16" s="28" t="inlineStr">
         <is>
           <t>HealthStream</t>
         </is>
       </c>
-      <c r="E16" s="27" t="inlineStr">
+      <c r="E16" s="28" t="inlineStr">
         <is>
           <t>Nashville, TN</t>
         </is>
@@ -1575,12 +1581,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H16" s="27" t="inlineStr">
+      <c r="H16" s="28" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I16" s="27" t="inlineStr">
+      <c r="I16" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1595,20 +1601,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L16" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M16" s="27" t="inlineStr"/>
+      <c r="L16" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M16" s="28" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>4304445726</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="29" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1618,12 +1624,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D17" s="26" t="inlineStr">
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E17" s="26" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>Oregon, United States</t>
         </is>
@@ -1638,12 +1644,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H17" s="26" t="inlineStr">
+      <c r="H17" s="29" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="I17" s="26" t="inlineStr">
+      <c r="I17" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1658,20 +1664,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L17" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M17" s="26" t="inlineStr"/>
+      <c r="L17" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M17" s="29" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="27" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>4342036151</t>
         </is>
       </c>
-      <c r="B18" s="27" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1681,12 +1687,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D18" s="27" t="inlineStr">
+      <c r="D18" s="28" t="inlineStr">
         <is>
           <t>Modern Treasury</t>
         </is>
       </c>
-      <c r="E18" s="27" t="inlineStr">
+      <c r="E18" s="28" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
@@ -1701,12 +1707,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H18" s="27" t="inlineStr">
+      <c r="H18" s="28" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I18" s="27" t="inlineStr">
+      <c r="I18" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1721,20 +1727,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L18" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M18" s="27" t="inlineStr"/>
+      <c r="L18" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M18" s="28" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="26" t="inlineStr">
+      <c r="A19" s="29" t="inlineStr">
         <is>
           <t>4304441843</t>
         </is>
       </c>
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1744,12 +1750,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D19" s="26" t="inlineStr">
+      <c r="D19" s="29" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E19" s="26" t="inlineStr">
+      <c r="E19" s="29" t="inlineStr">
         <is>
           <t>Idaho, United States</t>
         </is>
@@ -1764,12 +1770,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H19" s="26" t="inlineStr">
+      <c r="H19" s="29" t="inlineStr">
         <is>
           <t>157</t>
         </is>
       </c>
-      <c r="I19" s="26" t="inlineStr">
+      <c r="I19" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1784,20 +1790,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L19" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M19" s="26" t="inlineStr"/>
+      <c r="L19" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M19" s="29" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="27" t="inlineStr">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>4408047047</t>
         </is>
       </c>
-      <c r="B20" s="27" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1807,12 +1813,12 @@
           <t>Computer Sciences - Graduates - AI Training - Las Vegas, US</t>
         </is>
       </c>
-      <c r="D20" s="27" t="inlineStr">
+      <c r="D20" s="28" t="inlineStr">
         <is>
           <t>Prolific</t>
         </is>
       </c>
-      <c r="E20" s="27" t="inlineStr">
+      <c r="E20" s="28" t="inlineStr">
         <is>
           <t>Las Vegas, NV</t>
         </is>
@@ -1827,12 +1833,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H20" s="27" t="inlineStr">
+      <c r="H20" s="28" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I20" s="27" t="inlineStr">
+      <c r="I20" s="28" t="inlineStr">
         <is>
           <t>Temporary</t>
         </is>
@@ -1847,20 +1853,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L20" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M20" s="27" t="inlineStr"/>
+      <c r="L20" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M20" s="28" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>4304444837</t>
         </is>
       </c>
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1870,12 +1876,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D21" s="26" t="inlineStr">
+      <c r="D21" s="29" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E21" s="26" t="inlineStr">
+      <c r="E21" s="29" t="inlineStr">
         <is>
           <t>New Jersey, United States</t>
         </is>
@@ -1890,12 +1896,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H21" s="26" t="inlineStr">
+      <c r="H21" s="29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I21" s="26" t="inlineStr">
+      <c r="I21" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1910,20 +1916,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L21" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M21" s="26" t="inlineStr"/>
+      <c r="L21" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M21" s="29" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="27" t="inlineStr">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t>4405641326</t>
         </is>
       </c>
-      <c r="B22" s="27" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1933,12 +1939,12 @@
           <t>Full-stack Engineer</t>
         </is>
       </c>
-      <c r="D22" s="27" t="inlineStr">
+      <c r="D22" s="28" t="inlineStr">
         <is>
           <t>PartnerTap</t>
         </is>
       </c>
-      <c r="E22" s="27" t="inlineStr">
+      <c r="E22" s="28" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1953,12 +1959,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H22" s="27" t="inlineStr">
+      <c r="H22" s="28" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I22" s="27" t="inlineStr">
+      <c r="I22" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1973,20 +1979,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L22" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M22" s="27" t="inlineStr"/>
+      <c r="L22" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M22" s="28" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="26" t="inlineStr">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t>4341020900</t>
         </is>
       </c>
-      <c r="B23" s="26" t="inlineStr">
+      <c r="B23" s="29" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1996,12 +2002,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D23" s="26" t="inlineStr">
+      <c r="D23" s="29" t="inlineStr">
         <is>
           <t>PlanIT Group, LLC</t>
         </is>
       </c>
-      <c r="E23" s="26" t="inlineStr">
+      <c r="E23" s="29" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -2016,12 +2022,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H23" s="26" t="inlineStr">
+      <c r="H23" s="29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I23" s="26" t="inlineStr">
+      <c r="I23" s="29" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
@@ -2036,20 +2042,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L23" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M23" s="26" t="inlineStr"/>
+      <c r="L23" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M23" s="29" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="27" t="inlineStr">
+      <c r="A24" s="28" t="inlineStr">
         <is>
           <t>4304450637</t>
         </is>
       </c>
-      <c r="B24" s="27" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2059,12 +2065,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D24" s="27" t="inlineStr">
+      <c r="D24" s="28" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E24" s="27" t="inlineStr">
+      <c r="E24" s="28" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -2079,12 +2085,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H24" s="27" t="inlineStr">
+      <c r="H24" s="28" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I24" s="27" t="inlineStr">
+      <c r="I24" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2099,20 +2105,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L24" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M24" s="27" t="inlineStr"/>
+      <c r="L24" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M24" s="28" t="inlineStr"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="A25" s="29" t="inlineStr">
         <is>
           <t>4304451654</t>
         </is>
       </c>
-      <c r="B25" s="26" t="inlineStr">
+      <c r="B25" s="29" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2122,12 +2128,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D25" s="26" t="inlineStr">
+      <c r="D25" s="29" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E25" s="26" t="inlineStr">
+      <c r="E25" s="29" t="inlineStr">
         <is>
           <t>Utah, United States</t>
         </is>
@@ -2142,12 +2148,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H25" s="26" t="inlineStr">
+      <c r="H25" s="29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I25" s="26" t="inlineStr">
+      <c r="I25" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2162,20 +2168,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L25" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M25" s="26" t="inlineStr"/>
+      <c r="L25" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M25" s="29" t="inlineStr"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="27" t="inlineStr">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t>4413745880</t>
         </is>
       </c>
-      <c r="B26" s="27" t="inlineStr">
+      <c r="B26" s="28" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2185,12 +2191,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D26" s="27" t="inlineStr">
+      <c r="D26" s="28" t="inlineStr">
         <is>
           <t>Crate &amp; Barrel</t>
         </is>
       </c>
-      <c r="E26" s="27" t="inlineStr">
+      <c r="E26" s="28" t="inlineStr">
         <is>
           <t>Northbrook, IL</t>
         </is>
@@ -2205,12 +2211,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H26" s="27" t="inlineStr">
+      <c r="H26" s="28" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I26" s="27" t="inlineStr">
+      <c r="I26" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2225,20 +2231,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L26" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M26" s="27" t="inlineStr"/>
+      <c r="L26" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M26" s="28" t="inlineStr"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="26" t="inlineStr">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t>4304438841</t>
         </is>
       </c>
-      <c r="B27" s="26" t="inlineStr">
+      <c r="B27" s="29" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2248,12 +2254,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D27" s="26" t="inlineStr">
+      <c r="D27" s="29" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E27" s="26" t="inlineStr">
+      <c r="E27" s="29" t="inlineStr">
         <is>
           <t>Connecticut, United States</t>
         </is>
@@ -2268,12 +2274,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H27" s="26" t="inlineStr">
+      <c r="H27" s="29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I27" s="26" t="inlineStr">
+      <c r="I27" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2288,20 +2294,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L27" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M27" s="26" t="inlineStr"/>
+      <c r="L27" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M27" s="29" t="inlineStr"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="27" t="inlineStr">
+      <c r="A28" s="28" t="inlineStr">
         <is>
           <t>4393215930</t>
         </is>
       </c>
-      <c r="B28" s="27" t="inlineStr">
+      <c r="B28" s="28" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2311,12 +2317,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D28" s="27" t="inlineStr">
+      <c r="D28" s="28" t="inlineStr">
         <is>
           <t>Transcend</t>
         </is>
       </c>
-      <c r="E28" s="27" t="inlineStr">
+      <c r="E28" s="28" t="inlineStr">
         <is>
           <t>California, United States</t>
         </is>
@@ -2331,12 +2337,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H28" s="27" t="inlineStr">
+      <c r="H28" s="28" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I28" s="27" t="inlineStr">
+      <c r="I28" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2351,20 +2357,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L28" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M28" s="27" t="inlineStr"/>
+      <c r="L28" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M28" s="28" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="26" t="inlineStr">
+      <c r="A29" s="29" t="inlineStr">
         <is>
           <t>4304445723</t>
         </is>
       </c>
-      <c r="B29" s="26" t="inlineStr">
+      <c r="B29" s="29" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2374,12 +2380,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D29" s="26" t="inlineStr">
+      <c r="D29" s="29" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E29" s="26" t="inlineStr">
+      <c r="E29" s="29" t="inlineStr">
         <is>
           <t>Illinois, United States</t>
         </is>
@@ -2394,12 +2400,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H29" s="26" t="inlineStr">
+      <c r="H29" s="29" t="inlineStr">
         <is>
           <t>198</t>
         </is>
       </c>
-      <c r="I29" s="26" t="inlineStr">
+      <c r="I29" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2414,20 +2420,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L29" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M29" s="26" t="inlineStr"/>
+      <c r="L29" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M29" s="29" t="inlineStr"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="27" t="inlineStr">
+      <c r="A30" s="28" t="inlineStr">
         <is>
           <t>4396380649</t>
         </is>
       </c>
-      <c r="B30" s="27" t="inlineStr">
+      <c r="B30" s="28" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2437,12 +2443,12 @@
           <t>Full-Stack Developer Intern, Music &amp; Audio</t>
         </is>
       </c>
-      <c r="D30" s="27" t="inlineStr">
+      <c r="D30" s="28" t="inlineStr">
         <is>
           <t>Melotech</t>
         </is>
       </c>
-      <c r="E30" s="27" t="inlineStr">
+      <c r="E30" s="28" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
@@ -2457,12 +2463,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H30" s="27" t="inlineStr">
+      <c r="H30" s="28" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I30" s="27" t="inlineStr">
+      <c r="I30" s="28" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -2477,20 +2483,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L30" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M30" s="27" t="inlineStr"/>
+      <c r="L30" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M30" s="28" t="inlineStr"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="A31" s="29" t="inlineStr">
         <is>
           <t>4304454025</t>
         </is>
       </c>
-      <c r="B31" s="26" t="inlineStr">
+      <c r="B31" s="29" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2500,12 +2506,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D31" s="26" t="inlineStr">
+      <c r="D31" s="29" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E31" s="26" t="inlineStr">
+      <c r="E31" s="29" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -2520,12 +2526,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H31" s="26" t="inlineStr">
+      <c r="H31" s="29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I31" s="26" t="inlineStr">
+      <c r="I31" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2540,20 +2546,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L31" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M31" s="26" t="inlineStr"/>
+      <c r="L31" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M31" s="29" t="inlineStr"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="27" t="inlineStr">
+      <c r="A32" s="28" t="inlineStr">
         <is>
           <t>4309802287</t>
         </is>
       </c>
-      <c r="B32" s="27" t="inlineStr">
+      <c r="B32" s="28" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2563,12 +2569,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D32" s="27" t="inlineStr">
+      <c r="D32" s="28" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E32" s="27" t="inlineStr">
+      <c r="E32" s="28" t="inlineStr">
         <is>
           <t>New Jersey, United States</t>
         </is>
@@ -2583,12 +2589,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H32" s="27" t="inlineStr">
+      <c r="H32" s="28" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I32" s="27" t="inlineStr">
+      <c r="I32" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2603,20 +2609,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L32" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M32" s="27" t="inlineStr"/>
+      <c r="L32" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M32" s="28" t="inlineStr"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="26" t="inlineStr">
+      <c r="A33" s="29" t="inlineStr">
         <is>
           <t>4309694880</t>
         </is>
       </c>
-      <c r="B33" s="26" t="inlineStr">
+      <c r="B33" s="29" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2626,12 +2632,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D33" s="26" t="inlineStr">
+      <c r="D33" s="29" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E33" s="26" t="inlineStr">
+      <c r="E33" s="29" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -2646,12 +2652,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H33" s="26" t="inlineStr">
+      <c r="H33" s="29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I33" s="26" t="inlineStr">
+      <c r="I33" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2666,20 +2672,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L33" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M33" s="26" t="inlineStr"/>
+      <c r="L33" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M33" s="29" t="inlineStr"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="27" t="inlineStr">
+      <c r="A34" s="28" t="inlineStr">
         <is>
           <t>4411274012</t>
         </is>
       </c>
-      <c r="B34" s="27" t="inlineStr">
+      <c r="B34" s="28" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2689,12 +2695,12 @@
           <t>Junior UI Developer</t>
         </is>
       </c>
-      <c r="D34" s="27" t="inlineStr">
+      <c r="D34" s="28" t="inlineStr">
         <is>
           <t>General Dynamics Information Technology</t>
         </is>
       </c>
-      <c r="E34" s="27" t="inlineStr">
+      <c r="E34" s="28" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -2709,12 +2715,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H34" s="27" t="inlineStr">
+      <c r="H34" s="28" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I34" s="27" t="inlineStr">
+      <c r="I34" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2729,20 +2735,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L34" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M34" s="27" t="inlineStr"/>
+      <c r="L34" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M34" s="28" t="inlineStr"/>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="26" t="inlineStr">
+      <c r="A35" s="29" t="inlineStr">
         <is>
           <t>4264562292</t>
         </is>
       </c>
-      <c r="B35" s="26" t="inlineStr">
+      <c r="B35" s="29" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2752,12 +2758,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D35" s="26" t="inlineStr">
+      <c r="D35" s="29" t="inlineStr">
         <is>
           <t>Cymertek Corporation</t>
         </is>
       </c>
-      <c r="E35" s="26" t="inlineStr">
+      <c r="E35" s="29" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
@@ -2772,12 +2778,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H35" s="26" t="inlineStr">
+      <c r="H35" s="29" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="I35" s="26" t="inlineStr">
+      <c r="I35" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2792,20 +2798,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L35" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M35" s="26" t="inlineStr"/>
+      <c r="L35" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M35" s="29" t="inlineStr"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="27" t="inlineStr">
+      <c r="A36" s="28" t="inlineStr">
         <is>
           <t>4417482675</t>
         </is>
       </c>
-      <c r="B36" s="27" t="inlineStr">
+      <c r="B36" s="28" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2815,12 +2821,12 @@
           <t>Software Developer I</t>
         </is>
       </c>
-      <c r="D36" s="27" t="inlineStr">
+      <c r="D36" s="28" t="inlineStr">
         <is>
           <t>El Paso Water</t>
         </is>
       </c>
-      <c r="E36" s="27" t="inlineStr">
+      <c r="E36" s="28" t="inlineStr">
         <is>
           <t>El Paso, TX</t>
         </is>
@@ -2835,12 +2841,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H36" s="27" t="inlineStr">
+      <c r="H36" s="28" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="I36" s="27" t="inlineStr">
+      <c r="I36" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2855,20 +2861,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L36" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M36" s="27" t="inlineStr"/>
+      <c r="L36" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M36" s="28" t="inlineStr"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="26" t="inlineStr">
+      <c r="A37" s="29" t="inlineStr">
         <is>
           <t>4416508200</t>
         </is>
       </c>
-      <c r="B37" s="26" t="inlineStr">
+      <c r="B37" s="29" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2878,12 +2884,12 @@
           <t>Software Development Engineer in Test Intern (Global E-Commerce) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D37" s="26" t="inlineStr">
+      <c r="D37" s="29" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E37" s="26" t="inlineStr">
+      <c r="E37" s="29" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -2898,12 +2904,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H37" s="26" t="inlineStr">
+      <c r="H37" s="29" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I37" s="26" t="inlineStr">
+      <c r="I37" s="29" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -2918,20 +2924,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L37" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M37" s="26" t="inlineStr"/>
+      <c r="L37" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M37" s="29" t="inlineStr"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="27" t="inlineStr">
+      <c r="A38" s="28" t="inlineStr">
         <is>
           <t>4309809191</t>
         </is>
       </c>
-      <c r="B38" s="27" t="inlineStr">
+      <c r="B38" s="28" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
@@ -2941,12 +2947,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D38" s="27" t="inlineStr">
+      <c r="D38" s="28" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E38" s="27" t="inlineStr">
+      <c r="E38" s="28" t="inlineStr">
         <is>
           <t>Ohio, United States</t>
         </is>
@@ -2961,12 +2967,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H38" s="27" t="inlineStr">
+      <c r="H38" s="28" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="I38" s="27" t="inlineStr">
+      <c r="I38" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2981,20 +2987,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L38" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M38" s="27" t="inlineStr"/>
+      <c r="L38" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M38" s="28" t="inlineStr"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="26" t="inlineStr">
+      <c r="A39" s="29" t="inlineStr">
         <is>
           <t>3986118096</t>
         </is>
       </c>
-      <c r="B39" s="26" t="inlineStr">
+      <c r="B39" s="29" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
@@ -3004,12 +3010,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D39" s="26" t="inlineStr">
+      <c r="D39" s="29" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E39" s="26" t="inlineStr">
+      <c r="E39" s="29" t="inlineStr">
         <is>
           <t>Irving, TX</t>
         </is>
@@ -3024,12 +3030,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H39" s="26" t="inlineStr">
+      <c r="H39" s="29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I39" s="26" t="inlineStr">
+      <c r="I39" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3044,20 +3050,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L39" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M39" s="26" t="inlineStr"/>
+      <c r="L39" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M39" s="29" t="inlineStr"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="27" t="inlineStr">
+      <c r="A40" s="28" t="inlineStr">
         <is>
           <t>4309808244</t>
         </is>
       </c>
-      <c r="B40" s="27" t="inlineStr">
+      <c r="B40" s="28" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3067,12 +3073,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D40" s="27" t="inlineStr">
+      <c r="D40" s="28" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E40" s="27" t="inlineStr">
+      <c r="E40" s="28" t="inlineStr">
         <is>
           <t>Massachusetts, United States</t>
         </is>
@@ -3087,12 +3093,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H40" s="27" t="inlineStr">
+      <c r="H40" s="28" t="inlineStr">
         <is>
           <t>166</t>
         </is>
       </c>
-      <c r="I40" s="27" t="inlineStr">
+      <c r="I40" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3107,20 +3113,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L40" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M40" s="27" t="inlineStr"/>
+      <c r="L40" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M40" s="28" t="inlineStr"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="26" t="inlineStr">
+      <c r="A41" s="29" t="inlineStr">
         <is>
           <t>4362173625</t>
         </is>
       </c>
-      <c r="B41" s="26" t="inlineStr">
+      <c r="B41" s="29" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3130,12 +3136,12 @@
           <t>Full Stack Engineer</t>
         </is>
       </c>
-      <c r="D41" s="26" t="inlineStr">
+      <c r="D41" s="29" t="inlineStr">
         <is>
           <t>Empower Sleep</t>
         </is>
       </c>
-      <c r="E41" s="26" t="inlineStr">
+      <c r="E41" s="29" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3150,12 +3156,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H41" s="26" t="inlineStr">
+      <c r="H41" s="29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I41" s="26" t="inlineStr">
+      <c r="I41" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3170,20 +3176,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L41" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M41" s="26" t="inlineStr"/>
+      <c r="L41" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M41" s="29" t="inlineStr"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="27" t="inlineStr">
+      <c r="A42" s="28" t="inlineStr">
         <is>
           <t>4309812093</t>
         </is>
       </c>
-      <c r="B42" s="27" t="inlineStr">
+      <c r="B42" s="28" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3193,12 +3199,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D42" s="27" t="inlineStr">
+      <c r="D42" s="28" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E42" s="27" t="inlineStr">
+      <c r="E42" s="28" t="inlineStr">
         <is>
           <t>Florida, United States</t>
         </is>
@@ -3213,12 +3219,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H42" s="27" t="inlineStr">
+      <c r="H42" s="28" t="inlineStr">
         <is>
           <t>158</t>
         </is>
       </c>
-      <c r="I42" s="27" t="inlineStr">
+      <c r="I42" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3233,20 +3239,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L42" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M42" s="27" t="inlineStr"/>
+      <c r="L42" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M42" s="28" t="inlineStr"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="26" t="inlineStr">
+      <c r="A43" s="29" t="inlineStr">
         <is>
           <t>4391759914</t>
         </is>
       </c>
-      <c r="B43" s="26" t="inlineStr">
+      <c r="B43" s="29" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3256,12 +3262,12 @@
           <t>QA Engineering Internship</t>
         </is>
       </c>
-      <c r="D43" s="26" t="inlineStr">
+      <c r="D43" s="29" t="inlineStr">
         <is>
           <t>Chartbeat</t>
         </is>
       </c>
-      <c r="E43" s="26" t="inlineStr">
+      <c r="E43" s="29" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -3276,12 +3282,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H43" s="26" t="inlineStr">
+      <c r="H43" s="29" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="I43" s="26" t="inlineStr">
+      <c r="I43" s="29" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3296,20 +3302,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L43" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M43" s="26" t="inlineStr"/>
+      <c r="L43" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M43" s="29" t="inlineStr"/>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="27" t="inlineStr">
+      <c r="A44" s="28" t="inlineStr">
         <is>
           <t>4412855678</t>
         </is>
       </c>
-      <c r="B44" s="27" t="inlineStr">
+      <c r="B44" s="28" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3319,12 +3325,12 @@
           <t>AI Integration Engineer</t>
         </is>
       </c>
-      <c r="D44" s="27" t="inlineStr">
+      <c r="D44" s="28" t="inlineStr">
         <is>
           <t>UST</t>
         </is>
       </c>
-      <c r="E44" s="27" t="inlineStr">
+      <c r="E44" s="28" t="inlineStr">
         <is>
           <t>Santa Clara, CA</t>
         </is>
@@ -3339,12 +3345,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H44" s="27" t="inlineStr">
+      <c r="H44" s="28" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I44" s="27" t="inlineStr">
+      <c r="I44" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3359,20 +3365,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L44" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M44" s="27" t="inlineStr"/>
+      <c r="L44" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M44" s="28" t="inlineStr"/>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="26" t="inlineStr">
+      <c r="A45" s="29" t="inlineStr">
         <is>
           <t>4309805219</t>
         </is>
       </c>
-      <c r="B45" s="26" t="inlineStr">
+      <c r="B45" s="29" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3382,12 +3388,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D45" s="26" t="inlineStr">
+      <c r="D45" s="29" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E45" s="26" t="inlineStr">
+      <c r="E45" s="29" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -3402,12 +3408,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H45" s="26" t="inlineStr">
+      <c r="H45" s="29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I45" s="26" t="inlineStr">
+      <c r="I45" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3422,20 +3428,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L45" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M45" s="26" t="inlineStr"/>
+      <c r="L45" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M45" s="29" t="inlineStr"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="27" t="inlineStr">
+      <c r="A46" s="28" t="inlineStr">
         <is>
           <t>4409726429</t>
         </is>
       </c>
-      <c r="B46" s="27" t="inlineStr">
+      <c r="B46" s="28" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3445,12 +3451,12 @@
           <t>Data Science Intern</t>
         </is>
       </c>
-      <c r="D46" s="27" t="inlineStr">
+      <c r="D46" s="28" t="inlineStr">
         <is>
           <t>Rundoo</t>
         </is>
       </c>
-      <c r="E46" s="27" t="inlineStr">
+      <c r="E46" s="28" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3465,12 +3471,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H46" s="27" t="inlineStr">
+      <c r="H46" s="28" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I46" s="27" t="inlineStr">
+      <c r="I46" s="28" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3485,20 +3491,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L46" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M46" s="27" t="inlineStr"/>
+      <c r="L46" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M46" s="28" t="inlineStr"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="26" t="inlineStr">
+      <c r="A47" s="29" t="inlineStr">
         <is>
           <t>4305671729</t>
         </is>
       </c>
-      <c r="B47" s="26" t="inlineStr">
+      <c r="B47" s="29" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3508,12 +3514,12 @@
           <t>DoD SkillBridge Internship/Fellowship Opportunity Application (U.S. Military Only)</t>
         </is>
       </c>
-      <c r="D47" s="26" t="inlineStr">
+      <c r="D47" s="29" t="inlineStr">
         <is>
           <t>Onsights</t>
         </is>
       </c>
-      <c r="E47" s="26" t="inlineStr">
+      <c r="E47" s="29" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -3528,12 +3534,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H47" s="26" t="inlineStr">
+      <c r="H47" s="29" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I47" s="26" t="inlineStr">
+      <c r="I47" s="29" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3548,20 +3554,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L47" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M47" s="26" t="inlineStr"/>
+      <c r="L47" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M47" s="29" t="inlineStr"/>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="27" t="inlineStr">
+      <c r="A48" s="28" t="inlineStr">
         <is>
           <t>4414096220</t>
         </is>
       </c>
-      <c r="B48" s="27" t="inlineStr">
+      <c r="B48" s="28" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3571,12 +3577,12 @@
           <t>Visualization Engineer Intern</t>
         </is>
       </c>
-      <c r="D48" s="27" t="inlineStr">
+      <c r="D48" s="28" t="inlineStr">
         <is>
           <t>Leidos</t>
         </is>
       </c>
-      <c r="E48" s="27" t="inlineStr">
+      <c r="E48" s="28" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3591,12 +3597,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H48" s="27" t="inlineStr">
+      <c r="H48" s="28" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="I48" s="27" t="inlineStr">
+      <c r="I48" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3611,20 +3617,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L48" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M48" s="27" t="inlineStr"/>
+      <c r="L48" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M48" s="28" t="inlineStr"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="26" t="inlineStr">
+      <c r="A49" s="29" t="inlineStr">
         <is>
           <t>4361076044</t>
         </is>
       </c>
-      <c r="B49" s="26" t="inlineStr">
+      <c r="B49" s="29" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3634,12 +3640,12 @@
           <t>GenAI Engineering Intern  - SkillBridge (Remote)</t>
         </is>
       </c>
-      <c r="D49" s="26" t="inlineStr">
+      <c r="D49" s="29" t="inlineStr">
         <is>
           <t>CrowdStrike</t>
         </is>
       </c>
-      <c r="E49" s="26" t="inlineStr">
+      <c r="E49" s="29" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3654,12 +3660,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H49" s="26" t="inlineStr">
+      <c r="H49" s="29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I49" s="26" t="inlineStr">
+      <c r="I49" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3674,20 +3680,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L49" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M49" s="26" t="inlineStr"/>
+      <c r="L49" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M49" s="29" t="inlineStr"/>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="27" t="inlineStr">
+      <c r="A50" s="28" t="inlineStr">
         <is>
           <t>4417553585</t>
         </is>
       </c>
-      <c r="B50" s="27" t="inlineStr">
+      <c r="B50" s="28" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3697,12 +3703,12 @@
           <t>Entry-Level Software Engineer | Remote</t>
         </is>
       </c>
-      <c r="D50" s="27" t="inlineStr">
+      <c r="D50" s="28" t="inlineStr">
         <is>
           <t>Crossing Hurdles</t>
         </is>
       </c>
-      <c r="E50" s="27" t="inlineStr">
+      <c r="E50" s="28" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3717,12 +3723,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H50" s="27" t="inlineStr">
+      <c r="H50" s="28" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I50" s="27" t="inlineStr">
+      <c r="I50" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3737,20 +3743,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L50" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M50" s="27" t="inlineStr"/>
+      <c r="L50" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M50" s="28" t="inlineStr"/>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="26" t="inlineStr">
+      <c r="A51" s="29" t="inlineStr">
         <is>
           <t>4309699451</t>
         </is>
       </c>
-      <c r="B51" s="26" t="inlineStr">
+      <c r="B51" s="29" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3760,12 +3766,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D51" s="26" t="inlineStr">
+      <c r="D51" s="29" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E51" s="26" t="inlineStr">
+      <c r="E51" s="29" t="inlineStr">
         <is>
           <t>Washington, United States</t>
         </is>
@@ -3780,12 +3786,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H51" s="26" t="inlineStr">
+      <c r="H51" s="29" t="inlineStr">
         <is>
           <t>109</t>
         </is>
       </c>
-      <c r="I51" s="26" t="inlineStr">
+      <c r="I51" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3800,20 +3806,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L51" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M51" s="26" t="inlineStr"/>
+      <c r="L51" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M51" s="29" t="inlineStr"/>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="27" t="inlineStr">
+      <c r="A52" s="28" t="inlineStr">
         <is>
           <t>4406945262</t>
         </is>
       </c>
-      <c r="B52" s="27" t="inlineStr">
+      <c r="B52" s="28" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3823,12 +3829,12 @@
           <t>DevSecOps Intern</t>
         </is>
       </c>
-      <c r="D52" s="27" t="inlineStr">
+      <c r="D52" s="28" t="inlineStr">
         <is>
           <t>Modern Technology Solutions, Inc. (MTSI)</t>
         </is>
       </c>
-      <c r="E52" s="27" t="inlineStr">
+      <c r="E52" s="28" t="inlineStr">
         <is>
           <t>Niceville, FL</t>
         </is>
@@ -3843,12 +3849,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H52" s="27" t="inlineStr">
+      <c r="H52" s="28" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="I52" s="27" t="inlineStr">
+      <c r="I52" s="28" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3863,20 +3869,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L52" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M52" s="27" t="inlineStr"/>
+      <c r="L52" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M52" s="28" t="inlineStr"/>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="26" t="inlineStr">
+      <c r="A53" s="29" t="inlineStr">
         <is>
           <t>4407937810</t>
         </is>
       </c>
-      <c r="B53" s="26" t="inlineStr">
+      <c r="B53" s="29" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3886,12 +3892,12 @@
           <t>Temporary Intern - Agentic AI &amp; Neural-Symbolic Systems (Healthcare)</t>
         </is>
       </c>
-      <c r="D53" s="26" t="inlineStr">
+      <c r="D53" s="29" t="inlineStr">
         <is>
           <t>Cotiviti</t>
         </is>
       </c>
-      <c r="E53" s="26" t="inlineStr">
+      <c r="E53" s="29" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3906,12 +3912,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H53" s="26" t="inlineStr">
+      <c r="H53" s="29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I53" s="26" t="inlineStr">
+      <c r="I53" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3926,20 +3932,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L53" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M53" s="26" t="inlineStr"/>
+      <c r="L53" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M53" s="29" t="inlineStr"/>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="27" t="inlineStr">
+      <c r="A54" s="28" t="inlineStr">
         <is>
           <t>4414089997</t>
         </is>
       </c>
-      <c r="B54" s="27" t="inlineStr">
+      <c r="B54" s="28" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3949,12 +3955,12 @@
           <t>Visualization Engineer Intern</t>
         </is>
       </c>
-      <c r="D54" s="27" t="inlineStr">
+      <c r="D54" s="28" t="inlineStr">
         <is>
           <t>Leidos</t>
         </is>
       </c>
-      <c r="E54" s="27" t="inlineStr">
+      <c r="E54" s="28" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3969,12 +3975,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H54" s="27" t="inlineStr">
+      <c r="H54" s="28" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="I54" s="27" t="inlineStr">
+      <c r="I54" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3989,20 +3995,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L54" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M54" s="27" t="inlineStr"/>
+      <c r="L54" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M54" s="28" t="inlineStr"/>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="26" t="inlineStr">
+      <c r="A55" s="29" t="inlineStr">
         <is>
           <t>4387443129</t>
         </is>
       </c>
-      <c r="B55" s="26" t="inlineStr">
+      <c r="B55" s="29" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4012,12 +4018,12 @@
           <t>2026 Interns</t>
         </is>
       </c>
-      <c r="D55" s="26" t="inlineStr">
+      <c r="D55" s="29" t="inlineStr">
         <is>
           <t>Givelify</t>
         </is>
       </c>
-      <c r="E55" s="26" t="inlineStr">
+      <c r="E55" s="29" t="inlineStr">
         <is>
           <t>Dallas, TX</t>
         </is>
@@ -4032,12 +4038,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H55" s="26" t="inlineStr">
+      <c r="H55" s="29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I55" s="26" t="inlineStr">
+      <c r="I55" s="29" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -4052,20 +4058,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L55" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M55" s="26" t="inlineStr"/>
+      <c r="L55" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M55" s="29" t="inlineStr"/>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="27" t="inlineStr">
+      <c r="A56" s="28" t="inlineStr">
         <is>
           <t>4337980765</t>
         </is>
       </c>
-      <c r="B56" s="27" t="inlineStr">
+      <c r="B56" s="28" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4075,12 +4081,12 @@
           <t>Submitting for a General Internship Application</t>
         </is>
       </c>
-      <c r="D56" s="27" t="inlineStr">
+      <c r="D56" s="28" t="inlineStr">
         <is>
           <t>Chainguard</t>
         </is>
       </c>
-      <c r="E56" s="27" t="inlineStr">
+      <c r="E56" s="28" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4095,12 +4101,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H56" s="27" t="inlineStr">
+      <c r="H56" s="28" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I56" s="27" t="inlineStr">
+      <c r="I56" s="28" t="inlineStr">
         <is>
           <t>Volunteer</t>
         </is>
@@ -4115,20 +4121,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L56" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M56" s="27" t="inlineStr"/>
+      <c r="L56" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M56" s="28" t="inlineStr"/>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="26" t="inlineStr">
+      <c r="A57" s="29" t="inlineStr">
         <is>
           <t>4417030460</t>
         </is>
       </c>
-      <c r="B57" s="26" t="inlineStr">
+      <c r="B57" s="29" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4138,12 +4144,12 @@
           <t>AI Researcher Intern</t>
         </is>
       </c>
-      <c r="D57" s="26" t="inlineStr">
+      <c r="D57" s="29" t="inlineStr">
         <is>
           <t>BioSpace</t>
         </is>
       </c>
-      <c r="E57" s="26" t="inlineStr">
+      <c r="E57" s="29" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4158,12 +4164,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H57" s="26" t="inlineStr">
+      <c r="H57" s="29" t="inlineStr">
         <is>
           <t>151</t>
         </is>
       </c>
-      <c r="I57" s="26" t="inlineStr">
+      <c r="I57" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4178,20 +4184,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L57" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M57" s="26" t="inlineStr"/>
+      <c r="L57" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M57" s="29" t="inlineStr"/>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="27" t="inlineStr">
+      <c r="A58" s="28" t="inlineStr">
         <is>
           <t>4406930916</t>
         </is>
       </c>
-      <c r="B58" s="27" t="inlineStr">
+      <c r="B58" s="28" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4201,12 +4207,12 @@
           <t>DevSecOps Intern</t>
         </is>
       </c>
-      <c r="D58" s="27" t="inlineStr">
+      <c r="D58" s="28" t="inlineStr">
         <is>
           <t>Modern Technology Solutions, Inc. (MTSI)</t>
         </is>
       </c>
-      <c r="E58" s="27" t="inlineStr">
+      <c r="E58" s="28" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4221,12 +4227,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H58" s="27" t="inlineStr">
+      <c r="H58" s="28" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I58" s="27" t="inlineStr">
+      <c r="I58" s="28" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -4241,20 +4247,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L58" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M58" s="27" t="inlineStr"/>
+      <c r="L58" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M58" s="28" t="inlineStr"/>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="26" t="inlineStr">
+      <c r="A59" s="29" t="inlineStr">
         <is>
           <t>4385798937</t>
         </is>
       </c>
-      <c r="B59" s="26" t="inlineStr">
+      <c r="B59" s="29" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4264,12 +4270,12 @@
           <t>Research Intern on Generative and Protective AI for Content Creation</t>
         </is>
       </c>
-      <c r="D59" s="26" t="inlineStr">
+      <c r="D59" s="29" t="inlineStr">
         <is>
           <t>SonyAI</t>
         </is>
       </c>
-      <c r="E59" s="26" t="inlineStr">
+      <c r="E59" s="29" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -4284,12 +4290,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H59" s="26" t="inlineStr">
+      <c r="H59" s="29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I59" s="26" t="inlineStr">
+      <c r="I59" s="29" t="inlineStr">
         <is>
           <t>Part-time</t>
         </is>
@@ -4304,20 +4310,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L59" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M59" s="26" t="inlineStr"/>
+      <c r="L59" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M59" s="29" t="inlineStr"/>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="27" t="inlineStr">
+      <c r="A60" s="28" t="inlineStr">
         <is>
           <t>4414396950</t>
         </is>
       </c>
-      <c r="B60" s="27" t="inlineStr">
+      <c r="B60" s="28" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4327,12 +4333,12 @@
           <t>Power Platform Intern</t>
         </is>
       </c>
-      <c r="D60" s="27" t="inlineStr">
+      <c r="D60" s="28" t="inlineStr">
         <is>
           <t>Leidos</t>
         </is>
       </c>
-      <c r="E60" s="27" t="inlineStr">
+      <c r="E60" s="28" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4347,12 +4353,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H60" s="27" t="inlineStr">
+      <c r="H60" s="28" t="inlineStr">
         <is>
           <t>135</t>
         </is>
       </c>
-      <c r="I60" s="27" t="inlineStr">
+      <c r="I60" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4367,20 +4373,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L60" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M60" s="27" t="inlineStr"/>
+      <c r="L60" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M60" s="28" t="inlineStr"/>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="26" t="inlineStr">
+      <c r="A61" s="29" t="inlineStr">
         <is>
           <t>4413699205</t>
         </is>
       </c>
-      <c r="B61" s="26" t="inlineStr">
+      <c r="B61" s="29" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4390,12 +4396,12 @@
           <t>Junior Software Engineer - Automation &amp; Integration</t>
         </is>
       </c>
-      <c r="D61" s="26" t="inlineStr">
+      <c r="D61" s="29" t="inlineStr">
         <is>
           <t>Fletcher Development LLC</t>
         </is>
       </c>
-      <c r="E61" s="26" t="inlineStr">
+      <c r="E61" s="29" t="inlineStr">
         <is>
           <t>Redding, CT</t>
         </is>
@@ -4410,12 +4416,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H61" s="26" t="inlineStr">
+      <c r="H61" s="29" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="I61" s="26" t="inlineStr">
+      <c r="I61" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4430,20 +4436,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L61" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M61" s="26" t="inlineStr"/>
+      <c r="L61" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M61" s="29" t="inlineStr"/>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="27" t="inlineStr">
+      <c r="A62" s="28" t="inlineStr">
         <is>
           <t>4416171988</t>
         </is>
       </c>
-      <c r="B62" s="27" t="inlineStr">
+      <c r="B62" s="28" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4453,12 +4459,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D62" s="27" t="inlineStr">
+      <c r="D62" s="28" t="inlineStr">
         <is>
           <t>Altec</t>
         </is>
       </c>
-      <c r="E62" s="27" t="inlineStr">
+      <c r="E62" s="28" t="inlineStr">
         <is>
           <t>Birmingham, AL</t>
         </is>
@@ -4473,12 +4479,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H62" s="27" t="inlineStr">
+      <c r="H62" s="28" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I62" s="27" t="inlineStr">
+      <c r="I62" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4493,20 +4499,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L62" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M62" s="27" t="inlineStr"/>
+      <c r="L62" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M62" s="28" t="inlineStr"/>
     </row>
     <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="26" t="inlineStr">
+      <c r="A63" s="29" t="inlineStr">
         <is>
           <t>4403444963</t>
         </is>
       </c>
-      <c r="B63" s="26" t="inlineStr">
+      <c r="B63" s="29" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4516,12 +4522,12 @@
           <t>Junior Applications Developer (NY HELPS) #2026-252</t>
         </is>
       </c>
-      <c r="D63" s="26" t="inlineStr">
+      <c r="D63" s="29" t="inlineStr">
         <is>
           <t>Capital Region BOCES</t>
         </is>
       </c>
-      <c r="E63" s="26" t="inlineStr">
+      <c r="E63" s="29" t="inlineStr">
         <is>
           <t>Albany, NY</t>
         </is>
@@ -4536,12 +4542,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H63" s="26" t="inlineStr">
+      <c r="H63" s="29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I63" s="26" t="inlineStr">
+      <c r="I63" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4556,20 +4562,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L63" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M63" s="26" t="inlineStr"/>
+      <c r="L63" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M63" s="29" t="inlineStr"/>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="27" t="inlineStr">
+      <c r="A64" s="28" t="inlineStr">
         <is>
           <t>4418506121</t>
         </is>
       </c>
-      <c r="B64" s="27" t="inlineStr">
+      <c r="B64" s="28" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4579,12 +4585,12 @@
           <t>Core System Junior Developer</t>
         </is>
       </c>
-      <c r="D64" s="27" t="inlineStr">
+      <c r="D64" s="28" t="inlineStr">
         <is>
           <t>Cyprus Federal Credit Union</t>
         </is>
       </c>
-      <c r="E64" s="27" t="inlineStr">
+      <c r="E64" s="28" t="inlineStr">
         <is>
           <t>West Jordan, UT</t>
         </is>
@@ -4599,12 +4605,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H64" s="27" t="inlineStr">
+      <c r="H64" s="28" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="I64" s="27" t="inlineStr">
+      <c r="I64" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4619,20 +4625,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L64" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M64" s="27" t="inlineStr"/>
+      <c r="L64" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M64" s="28" t="inlineStr"/>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="26" t="inlineStr">
+      <c r="A65" s="29" t="inlineStr">
         <is>
           <t>4413905706</t>
         </is>
       </c>
-      <c r="B65" s="26" t="inlineStr">
+      <c r="B65" s="29" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4642,12 +4648,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D65" s="26" t="inlineStr">
+      <c r="D65" s="29" t="inlineStr">
         <is>
           <t>Arnex Solutions LLC</t>
         </is>
       </c>
-      <c r="E65" s="26" t="inlineStr">
+      <c r="E65" s="29" t="inlineStr">
         <is>
           <t>Princeton, NJ</t>
         </is>
@@ -4662,12 +4668,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H65" s="26" t="inlineStr">
+      <c r="H65" s="29" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I65" s="26" t="inlineStr">
+      <c r="I65" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4682,20 +4688,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L65" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M65" s="26" t="inlineStr"/>
+      <c r="L65" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M65" s="29" t="inlineStr"/>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="27" t="inlineStr">
+      <c r="A66" s="28" t="inlineStr">
         <is>
           <t>4418963446</t>
         </is>
       </c>
-      <c r="B66" s="27" t="inlineStr">
+      <c r="B66" s="28" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4705,12 +4711,12 @@
           <t>Junior Software Engineer - Automation &amp; Integration</t>
         </is>
       </c>
-      <c r="D66" s="27" t="inlineStr">
+      <c r="D66" s="28" t="inlineStr">
         <is>
           <t>Vibrant Building Technologies</t>
         </is>
       </c>
-      <c r="E66" s="27" t="inlineStr">
+      <c r="E66" s="28" t="inlineStr">
         <is>
           <t>Ridgefield, CT</t>
         </is>
@@ -4725,12 +4731,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H66" s="27" t="inlineStr">
+      <c r="H66" s="28" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="I66" s="27" t="inlineStr">
+      <c r="I66" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4745,20 +4751,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L66" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M66" s="27" t="inlineStr"/>
+      <c r="L66" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M66" s="28" t="inlineStr"/>
     </row>
     <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="26" t="inlineStr">
+      <c r="A67" s="29" t="inlineStr">
         <is>
           <t>4413759052</t>
         </is>
       </c>
-      <c r="B67" s="26" t="inlineStr">
+      <c r="B67" s="29" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4768,12 +4774,12 @@
           <t>Junior Full Stack Developer</t>
         </is>
       </c>
-      <c r="D67" s="26" t="inlineStr">
+      <c r="D67" s="29" t="inlineStr">
         <is>
           <t>Allied World Reinsurance Company</t>
         </is>
       </c>
-      <c r="E67" s="26" t="inlineStr">
+      <c r="E67" s="29" t="inlineStr">
         <is>
           <t>Iselin, NJ</t>
         </is>
@@ -4788,12 +4794,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H67" s="26" t="inlineStr">
+      <c r="H67" s="29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I67" s="26" t="inlineStr">
+      <c r="I67" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4808,20 +4814,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L67" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M67" s="26" t="inlineStr"/>
+      <c r="L67" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M67" s="29" t="inlineStr"/>
     </row>
     <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="27" t="inlineStr">
+      <c r="A68" s="28" t="inlineStr">
         <is>
           <t>4417542502</t>
         </is>
       </c>
-      <c r="B68" s="27" t="inlineStr">
+      <c r="B68" s="28" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4831,12 +4837,12 @@
           <t>Junior Developer</t>
         </is>
       </c>
-      <c r="D68" s="27" t="inlineStr">
+      <c r="D68" s="28" t="inlineStr">
         <is>
           <t>CloudMasonry</t>
         </is>
       </c>
-      <c r="E68" s="27" t="inlineStr">
+      <c r="E68" s="28" t="inlineStr">
         <is>
           <t>Indianapolis, IN</t>
         </is>
@@ -4851,12 +4857,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H68" s="27" t="inlineStr">
+      <c r="H68" s="28" t="inlineStr">
         <is>
           <t>154</t>
         </is>
       </c>
-      <c r="I68" s="27" t="inlineStr">
+      <c r="I68" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4871,20 +4877,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L68" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M68" s="27" t="inlineStr"/>
+      <c r="L68" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M68" s="28" t="inlineStr"/>
     </row>
     <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="26" t="inlineStr">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>4374856035</t>
         </is>
       </c>
-      <c r="B69" s="26" t="inlineStr">
+      <c r="B69" s="29" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4894,12 +4900,12 @@
           <t>Programmer II</t>
         </is>
       </c>
-      <c r="D69" s="26" t="inlineStr">
+      <c r="D69" s="29" t="inlineStr">
         <is>
           <t>Willis Knighton Health</t>
         </is>
       </c>
-      <c r="E69" s="26" t="inlineStr">
+      <c r="E69" s="29" t="inlineStr">
         <is>
           <t>Louisiana, United States</t>
         </is>
@@ -4914,12 +4920,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H69" s="26" t="inlineStr">
+      <c r="H69" s="29" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="I69" s="26" t="inlineStr">
+      <c r="I69" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4934,20 +4940,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L69" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M69" s="26" t="inlineStr"/>
+      <c r="L69" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M69" s="29" t="inlineStr"/>
     </row>
     <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="27" t="inlineStr">
+      <c r="A70" s="28" t="inlineStr">
         <is>
           <t>4416302564</t>
         </is>
       </c>
-      <c r="B70" s="27" t="inlineStr">
+      <c r="B70" s="28" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4957,12 +4963,12 @@
           <t>Software Engineer I</t>
         </is>
       </c>
-      <c r="D70" s="27" t="inlineStr">
+      <c r="D70" s="28" t="inlineStr">
         <is>
           <t>American Express</t>
         </is>
       </c>
-      <c r="E70" s="27" t="inlineStr">
+      <c r="E70" s="28" t="inlineStr">
         <is>
           <t>Sunrise, FL</t>
         </is>
@@ -4977,12 +4983,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H70" s="27" t="inlineStr">
+      <c r="H70" s="28" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I70" s="27" t="inlineStr">
+      <c r="I70" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4997,20 +5003,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L70" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M70" s="27" t="inlineStr"/>
+      <c r="L70" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M70" s="28" t="inlineStr"/>
     </row>
     <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="26" t="inlineStr">
+      <c r="A71" s="29" t="inlineStr">
         <is>
           <t>4417014137</t>
         </is>
       </c>
-      <c r="B71" s="26" t="inlineStr">
+      <c r="B71" s="29" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5020,12 +5026,12 @@
           <t>Junior Software Developer, Applications</t>
         </is>
       </c>
-      <c r="D71" s="26" t="inlineStr">
+      <c r="D71" s="29" t="inlineStr">
         <is>
           <t>ECS</t>
         </is>
       </c>
-      <c r="E71" s="26" t="inlineStr">
+      <c r="E71" s="29" t="inlineStr">
         <is>
           <t>O'Fallon, IL</t>
         </is>
@@ -5040,12 +5046,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H71" s="26" t="inlineStr">
+      <c r="H71" s="29" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="I71" s="26" t="inlineStr">
+      <c r="I71" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5060,20 +5066,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L71" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M71" s="26" t="inlineStr"/>
+      <c r="L71" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M71" s="29" t="inlineStr"/>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="27" t="inlineStr">
+      <c r="A72" s="28" t="inlineStr">
         <is>
           <t>4381211472</t>
         </is>
       </c>
-      <c r="B72" s="27" t="inlineStr">
+      <c r="B72" s="28" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5083,12 +5089,12 @@
           <t>Programmer</t>
         </is>
       </c>
-      <c r="D72" s="27" t="inlineStr">
+      <c r="D72" s="28" t="inlineStr">
         <is>
           <t>City of New York</t>
         </is>
       </c>
-      <c r="E72" s="27" t="inlineStr">
+      <c r="E72" s="28" t="inlineStr">
         <is>
           <t>Bronx, NY</t>
         </is>
@@ -5103,12 +5109,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H72" s="27" t="inlineStr">
+      <c r="H72" s="28" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="I72" s="27" t="inlineStr">
+      <c r="I72" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5123,20 +5129,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L72" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M72" s="27" t="inlineStr"/>
+      <c r="L72" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M72" s="28" t="inlineStr"/>
     </row>
     <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="26" t="inlineStr">
+      <c r="A73" s="29" t="inlineStr">
         <is>
           <t>4168416236</t>
         </is>
       </c>
-      <c r="B73" s="26" t="inlineStr">
+      <c r="B73" s="29" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5146,12 +5152,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D73" s="26" t="inlineStr">
+      <c r="D73" s="29" t="inlineStr">
         <is>
           <t>Interclypse</t>
         </is>
       </c>
-      <c r="E73" s="26" t="inlineStr">
+      <c r="E73" s="29" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
@@ -5166,12 +5172,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H73" s="26" t="inlineStr">
+      <c r="H73" s="29" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I73" s="26" t="inlineStr">
+      <c r="I73" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5186,20 +5192,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L73" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M73" s="26" t="inlineStr"/>
+      <c r="L73" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M73" s="29" t="inlineStr"/>
     </row>
     <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="27" t="inlineStr">
+      <c r="A74" s="28" t="inlineStr">
         <is>
           <t>4403507357</t>
         </is>
       </c>
-      <c r="B74" s="27" t="inlineStr">
+      <c r="B74" s="28" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5209,12 +5215,12 @@
           <t>Software Developer:</t>
         </is>
       </c>
-      <c r="D74" s="27" t="inlineStr">
+      <c r="D74" s="28" t="inlineStr">
         <is>
           <t>IQuest Solutions Corporation</t>
         </is>
       </c>
-      <c r="E74" s="27" t="inlineStr">
+      <c r="E74" s="28" t="inlineStr">
         <is>
           <t>Plano, TX</t>
         </is>
@@ -5229,12 +5235,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H74" s="27" t="inlineStr">
+      <c r="H74" s="28" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I74" s="27" t="inlineStr">
+      <c r="I74" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5249,20 +5255,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L74" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M74" s="27" t="inlineStr"/>
+      <c r="L74" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M74" s="28" t="inlineStr"/>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="26" t="inlineStr">
+      <c r="A75" s="29" t="inlineStr">
         <is>
           <t>4309800238</t>
         </is>
       </c>
-      <c r="B75" s="26" t="inlineStr">
+      <c r="B75" s="29" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5272,12 +5278,12 @@
           <t>Backend Software Engineer</t>
         </is>
       </c>
-      <c r="D75" s="26" t="inlineStr">
+      <c r="D75" s="29" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E75" s="26" t="inlineStr">
+      <c r="E75" s="29" t="inlineStr">
         <is>
           <t>Texas, United States</t>
         </is>
@@ -5292,12 +5298,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H75" s="26" t="inlineStr">
+      <c r="H75" s="29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I75" s="26" t="inlineStr">
+      <c r="I75" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5312,20 +5318,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L75" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M75" s="26" t="inlineStr"/>
+      <c r="L75" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M75" s="29" t="inlineStr"/>
     </row>
     <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="27" t="inlineStr">
+      <c r="A76" s="28" t="inlineStr">
         <is>
           <t>4404109089</t>
         </is>
       </c>
-      <c r="B76" s="27" t="inlineStr">
+      <c r="B76" s="28" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5335,12 +5341,12 @@
           <t>Software Development Engineer I</t>
         </is>
       </c>
-      <c r="D76" s="27" t="inlineStr">
+      <c r="D76" s="28" t="inlineStr">
         <is>
           <t>GM Financial</t>
         </is>
       </c>
-      <c r="E76" s="27" t="inlineStr">
+      <c r="E76" s="28" t="inlineStr">
         <is>
           <t>Arlington, TX</t>
         </is>
@@ -5355,12 +5361,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H76" s="27" t="inlineStr">
+      <c r="H76" s="28" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I76" s="27" t="inlineStr">
+      <c r="I76" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5375,20 +5381,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L76" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M76" s="27" t="inlineStr"/>
+      <c r="L76" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M76" s="28" t="inlineStr"/>
     </row>
     <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="26" t="inlineStr">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>3986116411</t>
         </is>
       </c>
-      <c r="B77" s="26" t="inlineStr">
+      <c r="B77" s="29" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5398,12 +5404,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D77" s="26" t="inlineStr">
+      <c r="D77" s="29" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E77" s="26" t="inlineStr">
+      <c r="E77" s="29" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -5418,12 +5424,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H77" s="26" t="inlineStr">
+      <c r="H77" s="29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I77" s="26" t="inlineStr">
+      <c r="I77" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5438,20 +5444,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L77" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M77" s="26" t="inlineStr"/>
+      <c r="L77" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M77" s="29" t="inlineStr"/>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="27" t="inlineStr">
+      <c r="A78" s="28" t="inlineStr">
         <is>
           <t>4418051524</t>
         </is>
       </c>
-      <c r="B78" s="27" t="inlineStr">
+      <c r="B78" s="28" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5461,12 +5467,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D78" s="27" t="inlineStr">
+      <c r="D78" s="28" t="inlineStr">
         <is>
           <t>Relativity</t>
         </is>
       </c>
-      <c r="E78" s="27" t="inlineStr">
+      <c r="E78" s="28" t="inlineStr">
         <is>
           <t>Texas, United States</t>
         </is>
@@ -5481,12 +5487,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H78" s="27" t="inlineStr">
+      <c r="H78" s="28" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I78" s="27" t="inlineStr">
+      <c r="I78" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5501,20 +5507,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L78" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M78" s="27" t="inlineStr"/>
+      <c r="L78" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M78" s="28" t="inlineStr"/>
     </row>
     <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="26" t="inlineStr">
+      <c r="A79" s="29" t="inlineStr">
         <is>
           <t>4409856693</t>
         </is>
       </c>
-      <c r="B79" s="26" t="inlineStr">
+      <c r="B79" s="29" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5524,12 +5530,12 @@
           <t>Software Engineer - Payments</t>
         </is>
       </c>
-      <c r="D79" s="26" t="inlineStr">
+      <c r="D79" s="29" t="inlineStr">
         <is>
           <t>Cloudbeds</t>
         </is>
       </c>
-      <c r="E79" s="26" t="inlineStr">
+      <c r="E79" s="29" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -5544,12 +5550,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H79" s="26" t="inlineStr">
+      <c r="H79" s="29" t="inlineStr">
         <is>
           <t>177</t>
         </is>
       </c>
-      <c r="I79" s="26" t="inlineStr">
+      <c r="I79" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5564,20 +5570,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L79" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M79" s="26" t="inlineStr"/>
+      <c r="L79" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M79" s="29" t="inlineStr"/>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="27" t="inlineStr">
+      <c r="A80" s="28" t="inlineStr">
         <is>
           <t>3986111771</t>
         </is>
       </c>
-      <c r="B80" s="27" t="inlineStr">
+      <c r="B80" s="28" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5587,12 +5593,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D80" s="27" t="inlineStr">
+      <c r="D80" s="28" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E80" s="27" t="inlineStr">
+      <c r="E80" s="28" t="inlineStr">
         <is>
           <t>Carrollton, TX</t>
         </is>
@@ -5607,12 +5613,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H80" s="27" t="inlineStr">
+      <c r="H80" s="28" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I80" s="27" t="inlineStr">
+      <c r="I80" s="28" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5627,20 +5633,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L80" s="27" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M80" s="27" t="inlineStr"/>
+      <c r="L80" s="28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M80" s="28" t="inlineStr"/>
     </row>
     <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="26" t="inlineStr">
+      <c r="A81" s="29" t="inlineStr">
         <is>
           <t>4417160720</t>
         </is>
       </c>
-      <c r="B81" s="26" t="inlineStr">
+      <c r="B81" s="29" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5650,12 +5656,12 @@
           <t>Full-Stack AI Developer</t>
         </is>
       </c>
-      <c r="D81" s="26" t="inlineStr">
+      <c r="D81" s="29" t="inlineStr">
         <is>
           <t>AnswerMyQ</t>
         </is>
       </c>
-      <c r="E81" s="26" t="inlineStr">
+      <c r="E81" s="29" t="inlineStr">
         <is>
           <t>Austin, Texas Metropolitan Area</t>
         </is>
@@ -5670,12 +5676,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H81" s="26" t="inlineStr">
+      <c r="H81" s="29" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I81" s="26" t="inlineStr">
+      <c r="I81" s="29" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5690,12 +5696,12 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L81" s="26" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M81" s="26" t="inlineStr"/>
+      <c r="L81" s="29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M81" s="29" t="inlineStr"/>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="A82" s="28" t="inlineStr">
@@ -6075,8 +6081,1331 @@
       </c>
       <c r="M87" s="29" t="inlineStr"/>
     </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="30" t="inlineStr">
+        <is>
+          <t>4413206045</t>
+        </is>
+      </c>
+      <c r="B88" s="30" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Software Development Engineer, EC2 Nitro Specialized Instances</t>
+        </is>
+      </c>
+      <c r="D88" s="30" t="inlineStr">
+        <is>
+          <t>Amazon Web Services (AWS)</t>
+        </is>
+      </c>
+      <c r="E88" s="30" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="F88" s="18" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="G88" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H88" s="30" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I88" s="30" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, aws, rest, c++, c, Location: Seattle, WA</t>
+        </is>
+      </c>
+      <c r="K88" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L88" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M88" s="30" t="inlineStr"/>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="31" t="inlineStr">
+        <is>
+          <t>4383211797</t>
+        </is>
+      </c>
+      <c r="B89" s="31" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>software development engineer</t>
+        </is>
+      </c>
+      <c r="D89" s="31" t="inlineStr">
+        <is>
+          <t>Abacus Business Computer</t>
+        </is>
+      </c>
+      <c r="E89" s="31" t="inlineStr">
+        <is>
+          <t>Queens, NY</t>
+        </is>
+      </c>
+      <c r="F89" s="14" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="G89" s="15" t="inlineStr">
+        <is>
+          <t>Very Low</t>
+        </is>
+      </c>
+      <c r="H89" s="31" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I89" s="31" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J89" s="8" t="inlineStr">
+        <is>
+          <t>Skills: rest, c</t>
+        </is>
+      </c>
+      <c r="K89" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L89" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M89" s="31" t="inlineStr"/>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="A90" s="30" t="inlineStr">
+        <is>
+          <t>4418169749</t>
+        </is>
+      </c>
+      <c r="B90" s="30" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>AI/ML Engineering Intern</t>
+        </is>
+      </c>
+      <c r="D90" s="30" t="inlineStr">
+        <is>
+          <t>Daice Labs</t>
+        </is>
+      </c>
+      <c r="E90" s="30" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H90" s="30" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I90" s="30" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, aws, api, git, tensorflow, pytorch, Title match: AI/ML Engineering Intern</t>
+        </is>
+      </c>
+      <c r="K90" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L90" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M90" s="30" t="inlineStr"/>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="A91" s="31" t="inlineStr">
+        <is>
+          <t>4281120416</t>
+        </is>
+      </c>
+      <c r="B91" s="31" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer Intern (Compute Platform) - 2026 Summer (BS/MS)</t>
+        </is>
+      </c>
+      <c r="D91" s="31" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E91" s="31" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="G91" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H91" s="31" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I91" s="31" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="J91" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, aws, rest, api, c, express, Location: Seattle, WA, Title match: Site Reliability Engineer Intern (Compute Platform) - 2026 Summer (BS/MS)</t>
+        </is>
+      </c>
+      <c r="K91" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L91" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M91" s="31" t="inlineStr"/>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="30" t="inlineStr">
+        <is>
+          <t>4377549744</t>
+        </is>
+      </c>
+      <c r="B92" s="30" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Software Development Engineer Apprentice - Military Veterans</t>
+        </is>
+      </c>
+      <c r="D92" s="30" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E92" s="30" t="inlineStr">
+        <is>
+          <t>Bellevue, WA</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H92" s="30" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="I92" s="30" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, aws, rest, c++, c, oop, Location: Bellevue, WA</t>
+        </is>
+      </c>
+      <c r="K92" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L92" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M92" s="30" t="inlineStr"/>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="31" t="inlineStr">
+        <is>
+          <t>4377564429</t>
+        </is>
+      </c>
+      <c r="B93" s="31" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>Software Development Engineer Apprentice - Military Veterans</t>
+        </is>
+      </c>
+      <c r="D93" s="31" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E93" s="31" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H93" s="31" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I93" s="31" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J93" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, aws, rest, c++, c, oop, Location: Seattle, WA</t>
+        </is>
+      </c>
+      <c r="K93" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L93" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M93" s="31" t="inlineStr"/>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="30" t="inlineStr">
+        <is>
+          <t>4413206046</t>
+        </is>
+      </c>
+      <c r="B94" s="30" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Software Development Engineer, Vendor Funding</t>
+        </is>
+      </c>
+      <c r="D94" s="30" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E94" s="30" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="F94" s="18" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="G94" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H94" s="30" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I94" s="30" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, machine learning, c, Location: Seattle, WA</t>
+        </is>
+      </c>
+      <c r="K94" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L94" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M94" s="30" t="inlineStr"/>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="31" t="inlineStr">
+        <is>
+          <t>4408778227</t>
+        </is>
+      </c>
+      <c r="B95" s="31" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>Front-End Engineer Fall Internship – 2026 (US)</t>
+        </is>
+      </c>
+      <c r="D95" s="31" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E95" s="31" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="G95" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H95" s="31" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I95" s="31" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J95" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, react, html, css, c, Location: Seattle, WA, Title match: Front-End Engineer Fall Internship – 2026 (US)</t>
+        </is>
+      </c>
+      <c r="K95" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L95" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M95" s="31" t="inlineStr"/>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="30" t="inlineStr">
+        <is>
+          <t>4281117648</t>
+        </is>
+      </c>
+      <c r="B96" s="30" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>Data Engineer Intern (E-commerce) - 2026 Summer (BS/MS)</t>
+        </is>
+      </c>
+      <c r="D96" s="30" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E96" s="30" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="G96" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H96" s="30" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I96" s="30" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>Skills: aws, rest, api, sql, c, express, Location: Seattle, WA, Title match: Data Engineer Intern (E-commerce) - 2026 Summer (BS/MS)</t>
+        </is>
+      </c>
+      <c r="K96" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L96" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M96" s="30" t="inlineStr"/>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="31" t="inlineStr">
+        <is>
+          <t>4407126060</t>
+        </is>
+      </c>
+      <c r="B97" s="31" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer Intern (Data Infrastructure) - 2026 Summer (BS/MS)</t>
+        </is>
+      </c>
+      <c r="D97" s="31" t="inlineStr">
+        <is>
+          <t>ByteDance</t>
+        </is>
+      </c>
+      <c r="E97" s="31" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="G97" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H97" s="31" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="I97" s="31" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="J97" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, aws, rest, api, docker, sql, Location: Seattle, WA, Title match: Site Reliability Engineer Intern (Data Infrastructure) - 2026 Summer (BS/MS)</t>
+        </is>
+      </c>
+      <c r="K97" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L97" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M97" s="31" t="inlineStr"/>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="A98" s="30" t="inlineStr">
+        <is>
+          <t>4392432360</t>
+        </is>
+      </c>
+      <c r="B98" s="30" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (AI Model Optimization) - 2026 Summer (BS/MS)</t>
+        </is>
+      </c>
+      <c r="D98" s="30" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E98" s="30" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="G98" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H98" s="30" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I98" s="30" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, aws, rest, api, tensorflow, pytorch, Location: Seattle, WA, Title match: Software Engineer Intern (AI Model Optimization) - 2026 Summer (BS/MS)</t>
+        </is>
+      </c>
+      <c r="K98" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L98" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M98" s="30" t="inlineStr"/>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="A99" s="31" t="inlineStr">
+        <is>
+          <t>4341279371</t>
+        </is>
+      </c>
+      <c r="B99" s="31" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>Robotics - Software Development Engineer Intern/Co-op - 2026</t>
+        </is>
+      </c>
+      <c r="D99" s="31" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E99" s="31" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="G99" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H99" s="31" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I99" s="31" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J99" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, aws, rest, sql, machine learning, c++, Location: Seattle, WA, Title match: Robotics - Software Development Engineer Intern/Co-op - 2026</t>
+        </is>
+      </c>
+      <c r="K99" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L99" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M99" s="31" t="inlineStr"/>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="30" t="inlineStr">
+        <is>
+          <t>4417646890</t>
+        </is>
+      </c>
+      <c r="B100" s="30" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="D100" s="30" t="inlineStr">
+        <is>
+          <t>Compass</t>
+        </is>
+      </c>
+      <c r="E100" s="30" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H100" s="30" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I100" s="30" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, aws, rest, c, Location: Seattle, WA, Title match: Software Engineer II</t>
+        </is>
+      </c>
+      <c r="K100" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L100" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M100" s="30" t="inlineStr"/>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="A101" s="31" t="inlineStr">
+        <is>
+          <t>4417565729</t>
+        </is>
+      </c>
+      <c r="B101" s="31" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>software engineer- ST, Seattle, WA</t>
+        </is>
+      </c>
+      <c r="D101" s="31" t="inlineStr">
+        <is>
+          <t>Starbucks</t>
+        </is>
+      </c>
+      <c r="E101" s="31" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H101" s="31" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I101" s="31" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J101" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, aws, sql, c++, c, ci/cd, Location: Seattle, WA, Title match: software engineer- ST, Seattle, WA</t>
+        </is>
+      </c>
+      <c r="K101" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L101" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M101" s="31" t="inlineStr"/>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="A102" s="30" t="inlineStr">
+        <is>
+          <t>4420492781</t>
+        </is>
+      </c>
+      <c r="B102" s="30" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer (Starlink Mobile)</t>
+        </is>
+      </c>
+      <c r="D102" s="30" t="inlineStr">
+        <is>
+          <t>SpaceX</t>
+        </is>
+      </c>
+      <c r="E102" s="30" t="inlineStr">
+        <is>
+          <t>Redmond, WA</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H102" s="30" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="I102" s="30" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, api, c++, c, oop, Location: Redmond, WA, Title match: Software Engineer (Starlink Mobile)</t>
+        </is>
+      </c>
+      <c r="K102" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L102" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M102" s="30" t="inlineStr"/>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="31" t="inlineStr">
+        <is>
+          <t>4418203886</t>
+        </is>
+      </c>
+      <c r="B103" s="31" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t>System Software Engineer - Performance</t>
+        </is>
+      </c>
+      <c r="D103" s="31" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="E103" s="31" t="inlineStr">
+        <is>
+          <t>Redmond, WA</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H103" s="31" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="I103" s="31" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J103" s="8" t="inlineStr">
+        <is>
+          <t>Skills: c, express, Location: Redmond, WA, Title match: System Software Engineer - Performance</t>
+        </is>
+      </c>
+      <c r="K103" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L103" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M103" s="31" t="inlineStr"/>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="A104" s="30" t="inlineStr">
+        <is>
+          <t>4332886298</t>
+        </is>
+      </c>
+      <c r="B104" s="30" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer - AI Travel Agent</t>
+        </is>
+      </c>
+      <c r="D104" s="30" t="inlineStr">
+        <is>
+          <t>Axel</t>
+        </is>
+      </c>
+      <c r="E104" s="30" t="inlineStr">
+        <is>
+          <t>Bellevue, WA</t>
+        </is>
+      </c>
+      <c r="F104" s="18" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="G104" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H104" s="30" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="I104" s="30" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>Skills: c, Location: Bellevue, WA, Title match: Software Engineer - AI Travel Agent</t>
+        </is>
+      </c>
+      <c r="K104" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L104" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M104" s="30" t="inlineStr"/>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="31" t="inlineStr">
+        <is>
+          <t>4388596468</t>
+        </is>
+      </c>
+      <c r="B105" s="31" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D105" s="31" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="E105" s="31" t="inlineStr">
+        <is>
+          <t>Bellevue, WA</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H105" s="31" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="I105" s="31" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J105" s="8" t="inlineStr">
+        <is>
+          <t>Skills: aws, git, c, express, Location: Bellevue, WA, Title match: Software Engineer</t>
+        </is>
+      </c>
+      <c r="K105" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L105" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M105" s="31" t="inlineStr"/>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="A106" s="30" t="inlineStr">
+        <is>
+          <t>4419517103</t>
+        </is>
+      </c>
+      <c r="B106" s="30" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="D106" s="30" t="inlineStr">
+        <is>
+          <t>Chewy</t>
+        </is>
+      </c>
+      <c r="E106" s="30" t="inlineStr">
+        <is>
+          <t>Bellevue, WA</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="G106" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H106" s="30" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I106" s="30" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, aws, api, docker, sql, c, Location: Bellevue, WA, Title match: Software Engineer II</t>
+        </is>
+      </c>
+      <c r="K106" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L106" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M106" s="30" t="inlineStr"/>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="31" t="inlineStr">
+        <is>
+          <t>4395225418</t>
+        </is>
+      </c>
+      <c r="B107" s="31" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer - Backend</t>
+        </is>
+      </c>
+      <c r="D107" s="31" t="inlineStr">
+        <is>
+          <t>MotherDuck</t>
+        </is>
+      </c>
+      <c r="E107" s="31" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="F107" s="9" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="G107" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H107" s="31" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I107" s="31" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J107" s="8" t="inlineStr">
+        <is>
+          <t>Skills: node, rest, api, backend, frontend, c++, Location: Seattle, WA, Title match: Software Engineer - Backend</t>
+        </is>
+      </c>
+      <c r="K107" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L107" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M107" s="31" t="inlineStr"/>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="30" t="inlineStr">
+        <is>
+          <t>4417163235</t>
+        </is>
+      </c>
+      <c r="B108" s="30" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer, Cloud SDK</t>
+        </is>
+      </c>
+      <c r="D108" s="30" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E108" s="30" t="inlineStr">
+        <is>
+          <t>Kirkland, WA</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H108" s="30" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="I108" s="30" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>Skills: api, git, full-stack, c++, c, data structures, Title match: Software Engineer, Cloud SDK</t>
+        </is>
+      </c>
+      <c r="K108" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L108" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M108" s="30" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M87"/>
+  <autoFilter ref="A1:M108"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -6164,6 +7493,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K85" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K86" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId107"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Job Matches" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Matches'!$A$1:$M$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Matches'!$A$1:$M$125</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -211,6 +211,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -578,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M108"/>
+  <dimension ref="A1:M125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -664,12 +670,12 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="28" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>4406952064</t>
         </is>
       </c>
-      <c r="B2" s="28" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -679,12 +685,12 @@
           <t>DevSecOps Intern</t>
         </is>
       </c>
-      <c r="D2" s="28" t="inlineStr">
+      <c r="D2" s="30" t="inlineStr">
         <is>
           <t>Modern Technology Solutions, Inc. (MTSI)</t>
         </is>
       </c>
-      <c r="E2" s="28" t="inlineStr">
+      <c r="E2" s="30" t="inlineStr">
         <is>
           <t>Huntsville, AL</t>
         </is>
@@ -699,12 +705,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H2" s="28" t="inlineStr">
+      <c r="H2" s="30" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="I2" s="28" t="inlineStr">
+      <c r="I2" s="30" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -719,20 +725,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L2" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M2" s="28" t="inlineStr"/>
+      <c r="L2" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M2" s="30" t="inlineStr"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="31" t="inlineStr">
         <is>
           <t>4405630173</t>
         </is>
       </c>
-      <c r="B3" s="29" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -742,12 +748,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D3" s="29" t="inlineStr">
+      <c r="D3" s="31" t="inlineStr">
         <is>
           <t>DLRdmv®</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" s="31" t="inlineStr">
         <is>
           <t>Dallas, TX</t>
         </is>
@@ -762,12 +768,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H3" s="29" t="inlineStr">
+      <c r="H3" s="31" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I3" s="29" t="inlineStr">
+      <c r="I3" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -782,20 +788,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L3" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M3" s="29" t="inlineStr"/>
+      <c r="L3" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M3" s="31" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>4287414862</t>
         </is>
       </c>
-      <c r="B4" s="28" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -805,12 +811,12 @@
           <t>[Online Assessment]Software Development Engineer Intern (Network Automation)- 2026 Summer (BS/ MS)</t>
         </is>
       </c>
-      <c r="D4" s="28" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>ByteDance</t>
         </is>
       </c>
-      <c r="E4" s="28" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -825,12 +831,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H4" s="28" t="inlineStr">
+      <c r="H4" s="30" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I4" s="28" t="inlineStr">
+      <c r="I4" s="30" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -845,20 +851,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L4" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M4" s="28" t="inlineStr"/>
+      <c r="L4" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M4" s="30" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>4309805269</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -868,12 +874,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D5" s="29" t="inlineStr">
+      <c r="D5" s="31" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E5" s="29" t="inlineStr">
+      <c r="E5" s="31" t="inlineStr">
         <is>
           <t>Delaware, United States</t>
         </is>
@@ -888,12 +894,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H5" s="29" t="inlineStr">
+      <c r="H5" s="31" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="I5" s="29" t="inlineStr">
+      <c r="I5" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -908,20 +914,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L5" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M5" s="29" t="inlineStr"/>
+      <c r="L5" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M5" s="31" t="inlineStr"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>4371812987</t>
         </is>
       </c>
-      <c r="B6" s="28" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -931,12 +937,12 @@
           <t>Software Development Engineer Fall Intern - Military Veteran</t>
         </is>
       </c>
-      <c r="D6" s="28" t="inlineStr">
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E6" s="28" t="inlineStr">
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -951,12 +957,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H6" s="28" t="inlineStr">
+      <c r="H6" s="30" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="I6" s="28" t="inlineStr">
+      <c r="I6" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -971,20 +977,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L6" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M6" s="28" t="inlineStr"/>
+      <c r="L6" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M6" s="30" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>4274682122</t>
         </is>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -994,12 +1000,12 @@
           <t>Software Engineer Intern (Data Ecosystem) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D7" s="29" t="inlineStr">
+      <c r="D7" s="31" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E7" s="29" t="inlineStr">
+      <c r="E7" s="31" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1014,12 +1020,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H7" s="29" t="inlineStr">
+      <c r="H7" s="31" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I7" s="29" t="inlineStr">
+      <c r="I7" s="31" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1034,20 +1040,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L7" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M7" s="29" t="inlineStr"/>
+      <c r="L7" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M7" s="31" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>4283848614</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1057,12 +1063,12 @@
           <t>[Online Assessment] Software Engineer Intern (Recommendation Infrastructure) - 2026 Fall (BS/ MS)</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1077,12 +1083,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H8" s="28" t="inlineStr">
+      <c r="H8" s="30" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I8" s="28" t="inlineStr">
+      <c r="I8" s="30" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1097,20 +1103,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L8" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M8" s="28" t="inlineStr"/>
+      <c r="L8" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M8" s="30" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>4411790844</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="31" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1120,12 +1126,12 @@
           <t>Software Engineer Intern (Infrastructure Automation) - Fall 2026</t>
         </is>
       </c>
-      <c r="D9" s="29" t="inlineStr">
+      <c r="D9" s="31" t="inlineStr">
         <is>
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="E9" s="29" t="inlineStr">
+      <c r="E9" s="31" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -1140,12 +1146,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H9" s="29" t="inlineStr">
+      <c r="H9" s="31" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I9" s="29" t="inlineStr">
+      <c r="I9" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1160,20 +1166,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L9" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M9" s="29" t="inlineStr"/>
+      <c r="L9" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M9" s="31" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="28" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>4332425058</t>
         </is>
       </c>
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1183,12 +1189,12 @@
           <t>Software Development Engineer Internship - Fall 2026 (US)</t>
         </is>
       </c>
-      <c r="D10" s="28" t="inlineStr">
+      <c r="D10" s="30" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E10" s="28" t="inlineStr">
+      <c r="E10" s="30" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1203,12 +1209,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H10" s="28" t="inlineStr">
+      <c r="H10" s="30" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I10" s="28" t="inlineStr">
+      <c r="I10" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1223,20 +1229,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L10" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M10" s="28" t="inlineStr"/>
+      <c r="L10" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M10" s="30" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>4323643644</t>
         </is>
       </c>
-      <c r="B11" s="29" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1246,12 +1252,12 @@
           <t>[Online Assessment] Software Engineer Intern (Recommendation Infrastructure) - 2026 Summer (BS/ MS)</t>
         </is>
       </c>
-      <c r="D11" s="29" t="inlineStr">
+      <c r="D11" s="31" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E11" s="29" t="inlineStr">
+      <c r="E11" s="31" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1266,12 +1272,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H11" s="29" t="inlineStr">
+      <c r="H11" s="31" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I11" s="29" t="inlineStr">
+      <c r="I11" s="31" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1286,20 +1292,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L11" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M11" s="29" t="inlineStr"/>
+      <c r="L11" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M11" s="31" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>4320849104</t>
         </is>
       </c>
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1309,12 +1315,12 @@
           <t>Software Engineer Intern (Commerce Ads) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D12" s="28" t="inlineStr">
+      <c r="D12" s="30" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E12" s="28" t="inlineStr">
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1329,12 +1335,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H12" s="28" t="inlineStr">
+      <c r="H12" s="30" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I12" s="28" t="inlineStr">
+      <c r="I12" s="30" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1349,20 +1355,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L12" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M12" s="28" t="inlineStr"/>
+      <c r="L12" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M12" s="30" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>4401686051</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1372,12 +1378,12 @@
           <t>Front End Software Engineer</t>
         </is>
       </c>
-      <c r="D13" s="29" t="inlineStr">
+      <c r="D13" s="31" t="inlineStr">
         <is>
           <t>Saronic Technologies</t>
         </is>
       </c>
-      <c r="E13" s="29" t="inlineStr">
+      <c r="E13" s="31" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -1392,12 +1398,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H13" s="29" t="inlineStr">
+      <c r="H13" s="31" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I13" s="29" t="inlineStr">
+      <c r="I13" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1412,20 +1418,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L13" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M13" s="29" t="inlineStr"/>
+      <c r="L13" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M13" s="31" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="28" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>4309696652</t>
         </is>
       </c>
-      <c r="B14" s="28" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1435,12 +1441,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D14" s="28" t="inlineStr">
+      <c r="D14" s="30" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E14" s="28" t="inlineStr">
+      <c r="E14" s="30" t="inlineStr">
         <is>
           <t>Rhode Island, United States</t>
         </is>
@@ -1455,12 +1461,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H14" s="28" t="inlineStr">
+      <c r="H14" s="30" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="I14" s="28" t="inlineStr">
+      <c r="I14" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1475,20 +1481,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L14" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M14" s="28" t="inlineStr"/>
+      <c r="L14" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M14" s="30" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="29" t="inlineStr">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>4309804319</t>
         </is>
       </c>
-      <c r="B15" s="29" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1498,12 +1504,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D15" s="29" t="inlineStr">
+      <c r="D15" s="31" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E15" s="29" t="inlineStr">
+      <c r="E15" s="31" t="inlineStr">
         <is>
           <t>Colorado, United States</t>
         </is>
@@ -1518,12 +1524,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H15" s="29" t="inlineStr">
+      <c r="H15" s="31" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="I15" s="29" t="inlineStr">
+      <c r="I15" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1538,20 +1544,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L15" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M15" s="29" t="inlineStr"/>
+      <c r="L15" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M15" s="31" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="28" t="inlineStr">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>4410271532</t>
         </is>
       </c>
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1561,12 +1567,12 @@
           <t>Associate Developer</t>
         </is>
       </c>
-      <c r="D16" s="28" t="inlineStr">
+      <c r="D16" s="30" t="inlineStr">
         <is>
           <t>HealthStream</t>
         </is>
       </c>
-      <c r="E16" s="28" t="inlineStr">
+      <c r="E16" s="30" t="inlineStr">
         <is>
           <t>Nashville, TN</t>
         </is>
@@ -1581,12 +1587,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H16" s="28" t="inlineStr">
+      <c r="H16" s="30" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I16" s="28" t="inlineStr">
+      <c r="I16" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1601,20 +1607,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L16" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M16" s="28" t="inlineStr"/>
+      <c r="L16" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M16" s="30" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="29" t="inlineStr">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>4304445726</t>
         </is>
       </c>
-      <c r="B17" s="29" t="inlineStr">
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1624,12 +1630,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D17" s="29" t="inlineStr">
+      <c r="D17" s="31" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E17" s="29" t="inlineStr">
+      <c r="E17" s="31" t="inlineStr">
         <is>
           <t>Oregon, United States</t>
         </is>
@@ -1644,12 +1650,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H17" s="29" t="inlineStr">
+      <c r="H17" s="31" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="I17" s="29" t="inlineStr">
+      <c r="I17" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1664,20 +1670,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L17" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M17" s="29" t="inlineStr"/>
+      <c r="L17" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M17" s="31" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="28" t="inlineStr">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t>4342036151</t>
         </is>
       </c>
-      <c r="B18" s="28" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1687,12 +1693,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D18" s="28" t="inlineStr">
+      <c r="D18" s="30" t="inlineStr">
         <is>
           <t>Modern Treasury</t>
         </is>
       </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="E18" s="30" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
@@ -1707,12 +1713,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H18" s="28" t="inlineStr">
+      <c r="H18" s="30" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I18" s="28" t="inlineStr">
+      <c r="I18" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1727,20 +1733,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L18" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M18" s="28" t="inlineStr"/>
+      <c r="L18" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M18" s="30" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>4304441843</t>
         </is>
       </c>
-      <c r="B19" s="29" t="inlineStr">
+      <c r="B19" s="31" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1750,12 +1756,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D19" s="29" t="inlineStr">
+      <c r="D19" s="31" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E19" s="29" t="inlineStr">
+      <c r="E19" s="31" t="inlineStr">
         <is>
           <t>Idaho, United States</t>
         </is>
@@ -1770,12 +1776,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H19" s="29" t="inlineStr">
+      <c r="H19" s="31" t="inlineStr">
         <is>
           <t>157</t>
         </is>
       </c>
-      <c r="I19" s="29" t="inlineStr">
+      <c r="I19" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1790,20 +1796,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L19" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M19" s="29" t="inlineStr"/>
+      <c r="L19" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M19" s="31" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="28" t="inlineStr">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t>4408047047</t>
         </is>
       </c>
-      <c r="B20" s="28" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1813,12 +1819,12 @@
           <t>Computer Sciences - Graduates - AI Training - Las Vegas, US</t>
         </is>
       </c>
-      <c r="D20" s="28" t="inlineStr">
+      <c r="D20" s="30" t="inlineStr">
         <is>
           <t>Prolific</t>
         </is>
       </c>
-      <c r="E20" s="28" t="inlineStr">
+      <c r="E20" s="30" t="inlineStr">
         <is>
           <t>Las Vegas, NV</t>
         </is>
@@ -1833,12 +1839,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H20" s="28" t="inlineStr">
+      <c r="H20" s="30" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I20" s="28" t="inlineStr">
+      <c r="I20" s="30" t="inlineStr">
         <is>
           <t>Temporary</t>
         </is>
@@ -1853,20 +1859,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L20" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M20" s="28" t="inlineStr"/>
+      <c r="L20" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M20" s="30" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>4304444837</t>
         </is>
       </c>
-      <c r="B21" s="29" t="inlineStr">
+      <c r="B21" s="31" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1876,12 +1882,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D21" s="29" t="inlineStr">
+      <c r="D21" s="31" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E21" s="29" t="inlineStr">
+      <c r="E21" s="31" t="inlineStr">
         <is>
           <t>New Jersey, United States</t>
         </is>
@@ -1896,12 +1902,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H21" s="29" t="inlineStr">
+      <c r="H21" s="31" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I21" s="29" t="inlineStr">
+      <c r="I21" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1916,20 +1922,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L21" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M21" s="29" t="inlineStr"/>
+      <c r="L21" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M21" s="31" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="28" t="inlineStr">
+      <c r="A22" s="30" t="inlineStr">
         <is>
           <t>4405641326</t>
         </is>
       </c>
-      <c r="B22" s="28" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1939,12 +1945,12 @@
           <t>Full-stack Engineer</t>
         </is>
       </c>
-      <c r="D22" s="28" t="inlineStr">
+      <c r="D22" s="30" t="inlineStr">
         <is>
           <t>PartnerTap</t>
         </is>
       </c>
-      <c r="E22" s="28" t="inlineStr">
+      <c r="E22" s="30" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1959,12 +1965,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H22" s="28" t="inlineStr">
+      <c r="H22" s="30" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I22" s="28" t="inlineStr">
+      <c r="I22" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1979,20 +1985,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L22" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M22" s="28" t="inlineStr"/>
+      <c r="L22" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M22" s="30" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="29" t="inlineStr">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t>4341020900</t>
         </is>
       </c>
-      <c r="B23" s="29" t="inlineStr">
+      <c r="B23" s="31" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2002,12 +2008,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D23" s="29" t="inlineStr">
+      <c r="D23" s="31" t="inlineStr">
         <is>
           <t>PlanIT Group, LLC</t>
         </is>
       </c>
-      <c r="E23" s="29" t="inlineStr">
+      <c r="E23" s="31" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -2022,12 +2028,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H23" s="29" t="inlineStr">
+      <c r="H23" s="31" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I23" s="29" t="inlineStr">
+      <c r="I23" s="31" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
@@ -2042,20 +2048,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L23" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M23" s="29" t="inlineStr"/>
+      <c r="L23" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M23" s="31" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="28" t="inlineStr">
+      <c r="A24" s="30" t="inlineStr">
         <is>
           <t>4304450637</t>
         </is>
       </c>
-      <c r="B24" s="28" t="inlineStr">
+      <c r="B24" s="30" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2065,12 +2071,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D24" s="28" t="inlineStr">
+      <c r="D24" s="30" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E24" s="28" t="inlineStr">
+      <c r="E24" s="30" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -2085,12 +2091,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H24" s="28" t="inlineStr">
+      <c r="H24" s="30" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I24" s="28" t="inlineStr">
+      <c r="I24" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2105,20 +2111,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L24" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M24" s="28" t="inlineStr"/>
+      <c r="L24" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M24" s="30" t="inlineStr"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="29" t="inlineStr">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>4304451654</t>
         </is>
       </c>
-      <c r="B25" s="29" t="inlineStr">
+      <c r="B25" s="31" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2128,12 +2134,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D25" s="29" t="inlineStr">
+      <c r="D25" s="31" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E25" s="29" t="inlineStr">
+      <c r="E25" s="31" t="inlineStr">
         <is>
           <t>Utah, United States</t>
         </is>
@@ -2148,12 +2154,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H25" s="29" t="inlineStr">
+      <c r="H25" s="31" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I25" s="29" t="inlineStr">
+      <c r="I25" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2168,20 +2174,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L25" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M25" s="29" t="inlineStr"/>
+      <c r="L25" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M25" s="31" t="inlineStr"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="28" t="inlineStr">
+      <c r="A26" s="30" t="inlineStr">
         <is>
           <t>4413745880</t>
         </is>
       </c>
-      <c r="B26" s="28" t="inlineStr">
+      <c r="B26" s="30" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2191,12 +2197,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D26" s="28" t="inlineStr">
+      <c r="D26" s="30" t="inlineStr">
         <is>
           <t>Crate &amp; Barrel</t>
         </is>
       </c>
-      <c r="E26" s="28" t="inlineStr">
+      <c r="E26" s="30" t="inlineStr">
         <is>
           <t>Northbrook, IL</t>
         </is>
@@ -2211,12 +2217,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H26" s="28" t="inlineStr">
+      <c r="H26" s="30" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I26" s="28" t="inlineStr">
+      <c r="I26" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2231,20 +2237,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L26" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M26" s="28" t="inlineStr"/>
+      <c r="L26" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M26" s="30" t="inlineStr"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="29" t="inlineStr">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>4304438841</t>
         </is>
       </c>
-      <c r="B27" s="29" t="inlineStr">
+      <c r="B27" s="31" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2254,12 +2260,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D27" s="29" t="inlineStr">
+      <c r="D27" s="31" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E27" s="29" t="inlineStr">
+      <c r="E27" s="31" t="inlineStr">
         <is>
           <t>Connecticut, United States</t>
         </is>
@@ -2274,12 +2280,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H27" s="29" t="inlineStr">
+      <c r="H27" s="31" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I27" s="29" t="inlineStr">
+      <c r="I27" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2294,20 +2300,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L27" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M27" s="29" t="inlineStr"/>
+      <c r="L27" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M27" s="31" t="inlineStr"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="28" t="inlineStr">
+      <c r="A28" s="30" t="inlineStr">
         <is>
           <t>4393215930</t>
         </is>
       </c>
-      <c r="B28" s="28" t="inlineStr">
+      <c r="B28" s="30" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2317,12 +2323,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D28" s="28" t="inlineStr">
+      <c r="D28" s="30" t="inlineStr">
         <is>
           <t>Transcend</t>
         </is>
       </c>
-      <c r="E28" s="28" t="inlineStr">
+      <c r="E28" s="30" t="inlineStr">
         <is>
           <t>California, United States</t>
         </is>
@@ -2337,12 +2343,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H28" s="28" t="inlineStr">
+      <c r="H28" s="30" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I28" s="28" t="inlineStr">
+      <c r="I28" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2357,20 +2363,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L28" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M28" s="28" t="inlineStr"/>
+      <c r="L28" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M28" s="30" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="29" t="inlineStr">
+      <c r="A29" s="31" t="inlineStr">
         <is>
           <t>4304445723</t>
         </is>
       </c>
-      <c r="B29" s="29" t="inlineStr">
+      <c r="B29" s="31" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2380,12 +2386,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D29" s="29" t="inlineStr">
+      <c r="D29" s="31" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E29" s="29" t="inlineStr">
+      <c r="E29" s="31" t="inlineStr">
         <is>
           <t>Illinois, United States</t>
         </is>
@@ -2400,12 +2406,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H29" s="29" t="inlineStr">
+      <c r="H29" s="31" t="inlineStr">
         <is>
           <t>198</t>
         </is>
       </c>
-      <c r="I29" s="29" t="inlineStr">
+      <c r="I29" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2420,20 +2426,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L29" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M29" s="29" t="inlineStr"/>
+      <c r="L29" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M29" s="31" t="inlineStr"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="28" t="inlineStr">
+      <c r="A30" s="30" t="inlineStr">
         <is>
           <t>4396380649</t>
         </is>
       </c>
-      <c r="B30" s="28" t="inlineStr">
+      <c r="B30" s="30" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2443,12 +2449,12 @@
           <t>Full-Stack Developer Intern, Music &amp; Audio</t>
         </is>
       </c>
-      <c r="D30" s="28" t="inlineStr">
+      <c r="D30" s="30" t="inlineStr">
         <is>
           <t>Melotech</t>
         </is>
       </c>
-      <c r="E30" s="28" t="inlineStr">
+      <c r="E30" s="30" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
@@ -2463,12 +2469,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H30" s="28" t="inlineStr">
+      <c r="H30" s="30" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I30" s="28" t="inlineStr">
+      <c r="I30" s="30" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -2483,20 +2489,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L30" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M30" s="28" t="inlineStr"/>
+      <c r="L30" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M30" s="30" t="inlineStr"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="29" t="inlineStr">
+      <c r="A31" s="31" t="inlineStr">
         <is>
           <t>4304454025</t>
         </is>
       </c>
-      <c r="B31" s="29" t="inlineStr">
+      <c r="B31" s="31" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2506,12 +2512,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D31" s="29" t="inlineStr">
+      <c r="D31" s="31" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E31" s="29" t="inlineStr">
+      <c r="E31" s="31" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -2526,12 +2532,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H31" s="29" t="inlineStr">
+      <c r="H31" s="31" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I31" s="29" t="inlineStr">
+      <c r="I31" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2546,20 +2552,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L31" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M31" s="29" t="inlineStr"/>
+      <c r="L31" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M31" s="31" t="inlineStr"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="28" t="inlineStr">
+      <c r="A32" s="30" t="inlineStr">
         <is>
           <t>4309802287</t>
         </is>
       </c>
-      <c r="B32" s="28" t="inlineStr">
+      <c r="B32" s="30" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2569,12 +2575,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D32" s="28" t="inlineStr">
+      <c r="D32" s="30" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E32" s="28" t="inlineStr">
+      <c r="E32" s="30" t="inlineStr">
         <is>
           <t>New Jersey, United States</t>
         </is>
@@ -2589,12 +2595,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H32" s="28" t="inlineStr">
+      <c r="H32" s="30" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I32" s="28" t="inlineStr">
+      <c r="I32" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2609,20 +2615,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L32" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M32" s="28" t="inlineStr"/>
+      <c r="L32" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M32" s="30" t="inlineStr"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="29" t="inlineStr">
+      <c r="A33" s="31" t="inlineStr">
         <is>
           <t>4309694880</t>
         </is>
       </c>
-      <c r="B33" s="29" t="inlineStr">
+      <c r="B33" s="31" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2632,12 +2638,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D33" s="29" t="inlineStr">
+      <c r="D33" s="31" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E33" s="29" t="inlineStr">
+      <c r="E33" s="31" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -2652,12 +2658,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H33" s="29" t="inlineStr">
+      <c r="H33" s="31" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I33" s="29" t="inlineStr">
+      <c r="I33" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2672,20 +2678,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L33" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M33" s="29" t="inlineStr"/>
+      <c r="L33" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M33" s="31" t="inlineStr"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="28" t="inlineStr">
+      <c r="A34" s="30" t="inlineStr">
         <is>
           <t>4411274012</t>
         </is>
       </c>
-      <c r="B34" s="28" t="inlineStr">
+      <c r="B34" s="30" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2695,12 +2701,12 @@
           <t>Junior UI Developer</t>
         </is>
       </c>
-      <c r="D34" s="28" t="inlineStr">
+      <c r="D34" s="30" t="inlineStr">
         <is>
           <t>General Dynamics Information Technology</t>
         </is>
       </c>
-      <c r="E34" s="28" t="inlineStr">
+      <c r="E34" s="30" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -2715,12 +2721,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H34" s="28" t="inlineStr">
+      <c r="H34" s="30" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I34" s="28" t="inlineStr">
+      <c r="I34" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2735,20 +2741,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L34" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M34" s="28" t="inlineStr"/>
+      <c r="L34" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M34" s="30" t="inlineStr"/>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="29" t="inlineStr">
+      <c r="A35" s="31" t="inlineStr">
         <is>
           <t>4264562292</t>
         </is>
       </c>
-      <c r="B35" s="29" t="inlineStr">
+      <c r="B35" s="31" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2758,12 +2764,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D35" s="29" t="inlineStr">
+      <c r="D35" s="31" t="inlineStr">
         <is>
           <t>Cymertek Corporation</t>
         </is>
       </c>
-      <c r="E35" s="29" t="inlineStr">
+      <c r="E35" s="31" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
@@ -2778,12 +2784,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H35" s="29" t="inlineStr">
+      <c r="H35" s="31" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="I35" s="29" t="inlineStr">
+      <c r="I35" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2798,20 +2804,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L35" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M35" s="29" t="inlineStr"/>
+      <c r="L35" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M35" s="31" t="inlineStr"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="28" t="inlineStr">
+      <c r="A36" s="30" t="inlineStr">
         <is>
           <t>4417482675</t>
         </is>
       </c>
-      <c r="B36" s="28" t="inlineStr">
+      <c r="B36" s="30" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2821,12 +2827,12 @@
           <t>Software Developer I</t>
         </is>
       </c>
-      <c r="D36" s="28" t="inlineStr">
+      <c r="D36" s="30" t="inlineStr">
         <is>
           <t>El Paso Water</t>
         </is>
       </c>
-      <c r="E36" s="28" t="inlineStr">
+      <c r="E36" s="30" t="inlineStr">
         <is>
           <t>El Paso, TX</t>
         </is>
@@ -2841,12 +2847,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H36" s="28" t="inlineStr">
+      <c r="H36" s="30" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="I36" s="28" t="inlineStr">
+      <c r="I36" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2861,20 +2867,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L36" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M36" s="28" t="inlineStr"/>
+      <c r="L36" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M36" s="30" t="inlineStr"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="29" t="inlineStr">
+      <c r="A37" s="31" t="inlineStr">
         <is>
           <t>4416508200</t>
         </is>
       </c>
-      <c r="B37" s="29" t="inlineStr">
+      <c r="B37" s="31" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2884,12 +2890,12 @@
           <t>Software Development Engineer in Test Intern (Global E-Commerce) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D37" s="29" t="inlineStr">
+      <c r="D37" s="31" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E37" s="29" t="inlineStr">
+      <c r="E37" s="31" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -2904,12 +2910,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H37" s="29" t="inlineStr">
+      <c r="H37" s="31" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I37" s="29" t="inlineStr">
+      <c r="I37" s="31" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -2924,20 +2930,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L37" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M37" s="29" t="inlineStr"/>
+      <c r="L37" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M37" s="31" t="inlineStr"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="28" t="inlineStr">
+      <c r="A38" s="30" t="inlineStr">
         <is>
           <t>4309809191</t>
         </is>
       </c>
-      <c r="B38" s="28" t="inlineStr">
+      <c r="B38" s="30" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
@@ -2947,12 +2953,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D38" s="28" t="inlineStr">
+      <c r="D38" s="30" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E38" s="28" t="inlineStr">
+      <c r="E38" s="30" t="inlineStr">
         <is>
           <t>Ohio, United States</t>
         </is>
@@ -2967,12 +2973,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H38" s="28" t="inlineStr">
+      <c r="H38" s="30" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="I38" s="28" t="inlineStr">
+      <c r="I38" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2987,20 +2993,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L38" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M38" s="28" t="inlineStr"/>
+      <c r="L38" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M38" s="30" t="inlineStr"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="29" t="inlineStr">
+      <c r="A39" s="31" t="inlineStr">
         <is>
           <t>3986118096</t>
         </is>
       </c>
-      <c r="B39" s="29" t="inlineStr">
+      <c r="B39" s="31" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
@@ -3010,12 +3016,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D39" s="29" t="inlineStr">
+      <c r="D39" s="31" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E39" s="29" t="inlineStr">
+      <c r="E39" s="31" t="inlineStr">
         <is>
           <t>Irving, TX</t>
         </is>
@@ -3030,12 +3036,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H39" s="29" t="inlineStr">
+      <c r="H39" s="31" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I39" s="29" t="inlineStr">
+      <c r="I39" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3050,20 +3056,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L39" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M39" s="29" t="inlineStr"/>
+      <c r="L39" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M39" s="31" t="inlineStr"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="28" t="inlineStr">
+      <c r="A40" s="30" t="inlineStr">
         <is>
           <t>4309808244</t>
         </is>
       </c>
-      <c r="B40" s="28" t="inlineStr">
+      <c r="B40" s="30" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3073,12 +3079,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D40" s="28" t="inlineStr">
+      <c r="D40" s="30" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E40" s="28" t="inlineStr">
+      <c r="E40" s="30" t="inlineStr">
         <is>
           <t>Massachusetts, United States</t>
         </is>
@@ -3093,12 +3099,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H40" s="28" t="inlineStr">
+      <c r="H40" s="30" t="inlineStr">
         <is>
           <t>166</t>
         </is>
       </c>
-      <c r="I40" s="28" t="inlineStr">
+      <c r="I40" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3113,20 +3119,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L40" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M40" s="28" t="inlineStr"/>
+      <c r="L40" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M40" s="30" t="inlineStr"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="29" t="inlineStr">
+      <c r="A41" s="31" t="inlineStr">
         <is>
           <t>4362173625</t>
         </is>
       </c>
-      <c r="B41" s="29" t="inlineStr">
+      <c r="B41" s="31" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3136,12 +3142,12 @@
           <t>Full Stack Engineer</t>
         </is>
       </c>
-      <c r="D41" s="29" t="inlineStr">
+      <c r="D41" s="31" t="inlineStr">
         <is>
           <t>Empower Sleep</t>
         </is>
       </c>
-      <c r="E41" s="29" t="inlineStr">
+      <c r="E41" s="31" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3156,12 +3162,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H41" s="29" t="inlineStr">
+      <c r="H41" s="31" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I41" s="29" t="inlineStr">
+      <c r="I41" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3176,20 +3182,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L41" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M41" s="29" t="inlineStr"/>
+      <c r="L41" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M41" s="31" t="inlineStr"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="28" t="inlineStr">
+      <c r="A42" s="30" t="inlineStr">
         <is>
           <t>4309812093</t>
         </is>
       </c>
-      <c r="B42" s="28" t="inlineStr">
+      <c r="B42" s="30" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3199,12 +3205,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D42" s="28" t="inlineStr">
+      <c r="D42" s="30" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E42" s="28" t="inlineStr">
+      <c r="E42" s="30" t="inlineStr">
         <is>
           <t>Florida, United States</t>
         </is>
@@ -3219,12 +3225,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H42" s="28" t="inlineStr">
+      <c r="H42" s="30" t="inlineStr">
         <is>
           <t>158</t>
         </is>
       </c>
-      <c r="I42" s="28" t="inlineStr">
+      <c r="I42" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3239,20 +3245,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L42" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M42" s="28" t="inlineStr"/>
+      <c r="L42" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M42" s="30" t="inlineStr"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="29" t="inlineStr">
+      <c r="A43" s="31" t="inlineStr">
         <is>
           <t>4391759914</t>
         </is>
       </c>
-      <c r="B43" s="29" t="inlineStr">
+      <c r="B43" s="31" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3262,12 +3268,12 @@
           <t>QA Engineering Internship</t>
         </is>
       </c>
-      <c r="D43" s="29" t="inlineStr">
+      <c r="D43" s="31" t="inlineStr">
         <is>
           <t>Chartbeat</t>
         </is>
       </c>
-      <c r="E43" s="29" t="inlineStr">
+      <c r="E43" s="31" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -3282,12 +3288,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H43" s="29" t="inlineStr">
+      <c r="H43" s="31" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="I43" s="29" t="inlineStr">
+      <c r="I43" s="31" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3302,20 +3308,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L43" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M43" s="29" t="inlineStr"/>
+      <c r="L43" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M43" s="31" t="inlineStr"/>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="28" t="inlineStr">
+      <c r="A44" s="30" t="inlineStr">
         <is>
           <t>4412855678</t>
         </is>
       </c>
-      <c r="B44" s="28" t="inlineStr">
+      <c r="B44" s="30" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3325,12 +3331,12 @@
           <t>AI Integration Engineer</t>
         </is>
       </c>
-      <c r="D44" s="28" t="inlineStr">
+      <c r="D44" s="30" t="inlineStr">
         <is>
           <t>UST</t>
         </is>
       </c>
-      <c r="E44" s="28" t="inlineStr">
+      <c r="E44" s="30" t="inlineStr">
         <is>
           <t>Santa Clara, CA</t>
         </is>
@@ -3345,12 +3351,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H44" s="28" t="inlineStr">
+      <c r="H44" s="30" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I44" s="28" t="inlineStr">
+      <c r="I44" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3365,20 +3371,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L44" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M44" s="28" t="inlineStr"/>
+      <c r="L44" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M44" s="30" t="inlineStr"/>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="29" t="inlineStr">
+      <c r="A45" s="31" t="inlineStr">
         <is>
           <t>4309805219</t>
         </is>
       </c>
-      <c r="B45" s="29" t="inlineStr">
+      <c r="B45" s="31" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3388,12 +3394,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D45" s="29" t="inlineStr">
+      <c r="D45" s="31" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E45" s="29" t="inlineStr">
+      <c r="E45" s="31" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -3408,12 +3414,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H45" s="29" t="inlineStr">
+      <c r="H45" s="31" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I45" s="29" t="inlineStr">
+      <c r="I45" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3428,20 +3434,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L45" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M45" s="29" t="inlineStr"/>
+      <c r="L45" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M45" s="31" t="inlineStr"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="28" t="inlineStr">
+      <c r="A46" s="30" t="inlineStr">
         <is>
           <t>4409726429</t>
         </is>
       </c>
-      <c r="B46" s="28" t="inlineStr">
+      <c r="B46" s="30" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3451,12 +3457,12 @@
           <t>Data Science Intern</t>
         </is>
       </c>
-      <c r="D46" s="28" t="inlineStr">
+      <c r="D46" s="30" t="inlineStr">
         <is>
           <t>Rundoo</t>
         </is>
       </c>
-      <c r="E46" s="28" t="inlineStr">
+      <c r="E46" s="30" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3471,12 +3477,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H46" s="28" t="inlineStr">
+      <c r="H46" s="30" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I46" s="28" t="inlineStr">
+      <c r="I46" s="30" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3491,20 +3497,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L46" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M46" s="28" t="inlineStr"/>
+      <c r="L46" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M46" s="30" t="inlineStr"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="29" t="inlineStr">
+      <c r="A47" s="31" t="inlineStr">
         <is>
           <t>4305671729</t>
         </is>
       </c>
-      <c r="B47" s="29" t="inlineStr">
+      <c r="B47" s="31" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3514,12 +3520,12 @@
           <t>DoD SkillBridge Internship/Fellowship Opportunity Application (U.S. Military Only)</t>
         </is>
       </c>
-      <c r="D47" s="29" t="inlineStr">
+      <c r="D47" s="31" t="inlineStr">
         <is>
           <t>Onsights</t>
         </is>
       </c>
-      <c r="E47" s="29" t="inlineStr">
+      <c r="E47" s="31" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -3534,12 +3540,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H47" s="29" t="inlineStr">
+      <c r="H47" s="31" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I47" s="29" t="inlineStr">
+      <c r="I47" s="31" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3554,20 +3560,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L47" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M47" s="29" t="inlineStr"/>
+      <c r="L47" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M47" s="31" t="inlineStr"/>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="28" t="inlineStr">
+      <c r="A48" s="30" t="inlineStr">
         <is>
           <t>4414096220</t>
         </is>
       </c>
-      <c r="B48" s="28" t="inlineStr">
+      <c r="B48" s="30" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3577,12 +3583,12 @@
           <t>Visualization Engineer Intern</t>
         </is>
       </c>
-      <c r="D48" s="28" t="inlineStr">
+      <c r="D48" s="30" t="inlineStr">
         <is>
           <t>Leidos</t>
         </is>
       </c>
-      <c r="E48" s="28" t="inlineStr">
+      <c r="E48" s="30" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3597,12 +3603,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H48" s="28" t="inlineStr">
+      <c r="H48" s="30" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="I48" s="28" t="inlineStr">
+      <c r="I48" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3617,20 +3623,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L48" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M48" s="28" t="inlineStr"/>
+      <c r="L48" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M48" s="30" t="inlineStr"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="29" t="inlineStr">
+      <c r="A49" s="31" t="inlineStr">
         <is>
           <t>4361076044</t>
         </is>
       </c>
-      <c r="B49" s="29" t="inlineStr">
+      <c r="B49" s="31" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3640,12 +3646,12 @@
           <t>GenAI Engineering Intern  - SkillBridge (Remote)</t>
         </is>
       </c>
-      <c r="D49" s="29" t="inlineStr">
+      <c r="D49" s="31" t="inlineStr">
         <is>
           <t>CrowdStrike</t>
         </is>
       </c>
-      <c r="E49" s="29" t="inlineStr">
+      <c r="E49" s="31" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3660,12 +3666,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H49" s="29" t="inlineStr">
+      <c r="H49" s="31" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I49" s="29" t="inlineStr">
+      <c r="I49" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3680,20 +3686,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L49" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M49" s="29" t="inlineStr"/>
+      <c r="L49" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M49" s="31" t="inlineStr"/>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="28" t="inlineStr">
+      <c r="A50" s="30" t="inlineStr">
         <is>
           <t>4417553585</t>
         </is>
       </c>
-      <c r="B50" s="28" t="inlineStr">
+      <c r="B50" s="30" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3703,12 +3709,12 @@
           <t>Entry-Level Software Engineer | Remote</t>
         </is>
       </c>
-      <c r="D50" s="28" t="inlineStr">
+      <c r="D50" s="30" t="inlineStr">
         <is>
           <t>Crossing Hurdles</t>
         </is>
       </c>
-      <c r="E50" s="28" t="inlineStr">
+      <c r="E50" s="30" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3723,12 +3729,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H50" s="28" t="inlineStr">
+      <c r="H50" s="30" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I50" s="28" t="inlineStr">
+      <c r="I50" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3743,20 +3749,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L50" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M50" s="28" t="inlineStr"/>
+      <c r="L50" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M50" s="30" t="inlineStr"/>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="29" t="inlineStr">
+      <c r="A51" s="31" t="inlineStr">
         <is>
           <t>4309699451</t>
         </is>
       </c>
-      <c r="B51" s="29" t="inlineStr">
+      <c r="B51" s="31" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3766,12 +3772,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D51" s="29" t="inlineStr">
+      <c r="D51" s="31" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E51" s="29" t="inlineStr">
+      <c r="E51" s="31" t="inlineStr">
         <is>
           <t>Washington, United States</t>
         </is>
@@ -3786,12 +3792,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H51" s="29" t="inlineStr">
+      <c r="H51" s="31" t="inlineStr">
         <is>
           <t>109</t>
         </is>
       </c>
-      <c r="I51" s="29" t="inlineStr">
+      <c r="I51" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3806,20 +3812,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L51" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M51" s="29" t="inlineStr"/>
+      <c r="L51" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M51" s="31" t="inlineStr"/>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="28" t="inlineStr">
+      <c r="A52" s="30" t="inlineStr">
         <is>
           <t>4406945262</t>
         </is>
       </c>
-      <c r="B52" s="28" t="inlineStr">
+      <c r="B52" s="30" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3829,12 +3835,12 @@
           <t>DevSecOps Intern</t>
         </is>
       </c>
-      <c r="D52" s="28" t="inlineStr">
+      <c r="D52" s="30" t="inlineStr">
         <is>
           <t>Modern Technology Solutions, Inc. (MTSI)</t>
         </is>
       </c>
-      <c r="E52" s="28" t="inlineStr">
+      <c r="E52" s="30" t="inlineStr">
         <is>
           <t>Niceville, FL</t>
         </is>
@@ -3849,12 +3855,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H52" s="28" t="inlineStr">
+      <c r="H52" s="30" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="I52" s="28" t="inlineStr">
+      <c r="I52" s="30" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3869,20 +3875,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L52" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M52" s="28" t="inlineStr"/>
+      <c r="L52" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M52" s="30" t="inlineStr"/>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="29" t="inlineStr">
+      <c r="A53" s="31" t="inlineStr">
         <is>
           <t>4407937810</t>
         </is>
       </c>
-      <c r="B53" s="29" t="inlineStr">
+      <c r="B53" s="31" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3892,12 +3898,12 @@
           <t>Temporary Intern - Agentic AI &amp; Neural-Symbolic Systems (Healthcare)</t>
         </is>
       </c>
-      <c r="D53" s="29" t="inlineStr">
+      <c r="D53" s="31" t="inlineStr">
         <is>
           <t>Cotiviti</t>
         </is>
       </c>
-      <c r="E53" s="29" t="inlineStr">
+      <c r="E53" s="31" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3912,12 +3918,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H53" s="29" t="inlineStr">
+      <c r="H53" s="31" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I53" s="29" t="inlineStr">
+      <c r="I53" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3932,20 +3938,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L53" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M53" s="29" t="inlineStr"/>
+      <c r="L53" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M53" s="31" t="inlineStr"/>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="28" t="inlineStr">
+      <c r="A54" s="30" t="inlineStr">
         <is>
           <t>4414089997</t>
         </is>
       </c>
-      <c r="B54" s="28" t="inlineStr">
+      <c r="B54" s="30" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3955,12 +3961,12 @@
           <t>Visualization Engineer Intern</t>
         </is>
       </c>
-      <c r="D54" s="28" t="inlineStr">
+      <c r="D54" s="30" t="inlineStr">
         <is>
           <t>Leidos</t>
         </is>
       </c>
-      <c r="E54" s="28" t="inlineStr">
+      <c r="E54" s="30" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3975,12 +3981,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H54" s="28" t="inlineStr">
+      <c r="H54" s="30" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="I54" s="28" t="inlineStr">
+      <c r="I54" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3995,20 +4001,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L54" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M54" s="28" t="inlineStr"/>
+      <c r="L54" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M54" s="30" t="inlineStr"/>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="29" t="inlineStr">
+      <c r="A55" s="31" t="inlineStr">
         <is>
           <t>4387443129</t>
         </is>
       </c>
-      <c r="B55" s="29" t="inlineStr">
+      <c r="B55" s="31" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4018,12 +4024,12 @@
           <t>2026 Interns</t>
         </is>
       </c>
-      <c r="D55" s="29" t="inlineStr">
+      <c r="D55" s="31" t="inlineStr">
         <is>
           <t>Givelify</t>
         </is>
       </c>
-      <c r="E55" s="29" t="inlineStr">
+      <c r="E55" s="31" t="inlineStr">
         <is>
           <t>Dallas, TX</t>
         </is>
@@ -4038,12 +4044,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H55" s="29" t="inlineStr">
+      <c r="H55" s="31" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I55" s="29" t="inlineStr">
+      <c r="I55" s="31" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -4058,20 +4064,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L55" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M55" s="29" t="inlineStr"/>
+      <c r="L55" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M55" s="31" t="inlineStr"/>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="28" t="inlineStr">
+      <c r="A56" s="30" t="inlineStr">
         <is>
           <t>4337980765</t>
         </is>
       </c>
-      <c r="B56" s="28" t="inlineStr">
+      <c r="B56" s="30" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4081,12 +4087,12 @@
           <t>Submitting for a General Internship Application</t>
         </is>
       </c>
-      <c r="D56" s="28" t="inlineStr">
+      <c r="D56" s="30" t="inlineStr">
         <is>
           <t>Chainguard</t>
         </is>
       </c>
-      <c r="E56" s="28" t="inlineStr">
+      <c r="E56" s="30" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4101,12 +4107,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H56" s="28" t="inlineStr">
+      <c r="H56" s="30" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I56" s="28" t="inlineStr">
+      <c r="I56" s="30" t="inlineStr">
         <is>
           <t>Volunteer</t>
         </is>
@@ -4121,20 +4127,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L56" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M56" s="28" t="inlineStr"/>
+      <c r="L56" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M56" s="30" t="inlineStr"/>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="29" t="inlineStr">
+      <c r="A57" s="31" t="inlineStr">
         <is>
           <t>4417030460</t>
         </is>
       </c>
-      <c r="B57" s="29" t="inlineStr">
+      <c r="B57" s="31" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4144,12 +4150,12 @@
           <t>AI Researcher Intern</t>
         </is>
       </c>
-      <c r="D57" s="29" t="inlineStr">
+      <c r="D57" s="31" t="inlineStr">
         <is>
           <t>BioSpace</t>
         </is>
       </c>
-      <c r="E57" s="29" t="inlineStr">
+      <c r="E57" s="31" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4164,12 +4170,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H57" s="29" t="inlineStr">
+      <c r="H57" s="31" t="inlineStr">
         <is>
           <t>151</t>
         </is>
       </c>
-      <c r="I57" s="29" t="inlineStr">
+      <c r="I57" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4184,20 +4190,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L57" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M57" s="29" t="inlineStr"/>
+      <c r="L57" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M57" s="31" t="inlineStr"/>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="28" t="inlineStr">
+      <c r="A58" s="30" t="inlineStr">
         <is>
           <t>4406930916</t>
         </is>
       </c>
-      <c r="B58" s="28" t="inlineStr">
+      <c r="B58" s="30" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4207,12 +4213,12 @@
           <t>DevSecOps Intern</t>
         </is>
       </c>
-      <c r="D58" s="28" t="inlineStr">
+      <c r="D58" s="30" t="inlineStr">
         <is>
           <t>Modern Technology Solutions, Inc. (MTSI)</t>
         </is>
       </c>
-      <c r="E58" s="28" t="inlineStr">
+      <c r="E58" s="30" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4227,12 +4233,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H58" s="28" t="inlineStr">
+      <c r="H58" s="30" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I58" s="28" t="inlineStr">
+      <c r="I58" s="30" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -4247,20 +4253,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L58" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M58" s="28" t="inlineStr"/>
+      <c r="L58" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M58" s="30" t="inlineStr"/>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="29" t="inlineStr">
+      <c r="A59" s="31" t="inlineStr">
         <is>
           <t>4385798937</t>
         </is>
       </c>
-      <c r="B59" s="29" t="inlineStr">
+      <c r="B59" s="31" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4270,12 +4276,12 @@
           <t>Research Intern on Generative and Protective AI for Content Creation</t>
         </is>
       </c>
-      <c r="D59" s="29" t="inlineStr">
+      <c r="D59" s="31" t="inlineStr">
         <is>
           <t>SonyAI</t>
         </is>
       </c>
-      <c r="E59" s="29" t="inlineStr">
+      <c r="E59" s="31" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -4290,12 +4296,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H59" s="29" t="inlineStr">
+      <c r="H59" s="31" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I59" s="29" t="inlineStr">
+      <c r="I59" s="31" t="inlineStr">
         <is>
           <t>Part-time</t>
         </is>
@@ -4310,20 +4316,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L59" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M59" s="29" t="inlineStr"/>
+      <c r="L59" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M59" s="31" t="inlineStr"/>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="28" t="inlineStr">
+      <c r="A60" s="30" t="inlineStr">
         <is>
           <t>4414396950</t>
         </is>
       </c>
-      <c r="B60" s="28" t="inlineStr">
+      <c r="B60" s="30" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4333,12 +4339,12 @@
           <t>Power Platform Intern</t>
         </is>
       </c>
-      <c r="D60" s="28" t="inlineStr">
+      <c r="D60" s="30" t="inlineStr">
         <is>
           <t>Leidos</t>
         </is>
       </c>
-      <c r="E60" s="28" t="inlineStr">
+      <c r="E60" s="30" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4353,12 +4359,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H60" s="28" t="inlineStr">
+      <c r="H60" s="30" t="inlineStr">
         <is>
           <t>135</t>
         </is>
       </c>
-      <c r="I60" s="28" t="inlineStr">
+      <c r="I60" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4373,20 +4379,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L60" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M60" s="28" t="inlineStr"/>
+      <c r="L60" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M60" s="30" t="inlineStr"/>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="29" t="inlineStr">
+      <c r="A61" s="31" t="inlineStr">
         <is>
           <t>4413699205</t>
         </is>
       </c>
-      <c r="B61" s="29" t="inlineStr">
+      <c r="B61" s="31" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4396,12 +4402,12 @@
           <t>Junior Software Engineer - Automation &amp; Integration</t>
         </is>
       </c>
-      <c r="D61" s="29" t="inlineStr">
+      <c r="D61" s="31" t="inlineStr">
         <is>
           <t>Fletcher Development LLC</t>
         </is>
       </c>
-      <c r="E61" s="29" t="inlineStr">
+      <c r="E61" s="31" t="inlineStr">
         <is>
           <t>Redding, CT</t>
         </is>
@@ -4416,12 +4422,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H61" s="29" t="inlineStr">
+      <c r="H61" s="31" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="I61" s="29" t="inlineStr">
+      <c r="I61" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4436,20 +4442,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L61" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M61" s="29" t="inlineStr"/>
+      <c r="L61" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M61" s="31" t="inlineStr"/>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="28" t="inlineStr">
+      <c r="A62" s="30" t="inlineStr">
         <is>
           <t>4416171988</t>
         </is>
       </c>
-      <c r="B62" s="28" t="inlineStr">
+      <c r="B62" s="30" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4459,12 +4465,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D62" s="28" t="inlineStr">
+      <c r="D62" s="30" t="inlineStr">
         <is>
           <t>Altec</t>
         </is>
       </c>
-      <c r="E62" s="28" t="inlineStr">
+      <c r="E62" s="30" t="inlineStr">
         <is>
           <t>Birmingham, AL</t>
         </is>
@@ -4479,12 +4485,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H62" s="28" t="inlineStr">
+      <c r="H62" s="30" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I62" s="28" t="inlineStr">
+      <c r="I62" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4499,20 +4505,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L62" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M62" s="28" t="inlineStr"/>
+      <c r="L62" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M62" s="30" t="inlineStr"/>
     </row>
     <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="29" t="inlineStr">
+      <c r="A63" s="31" t="inlineStr">
         <is>
           <t>4403444963</t>
         </is>
       </c>
-      <c r="B63" s="29" t="inlineStr">
+      <c r="B63" s="31" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4522,12 +4528,12 @@
           <t>Junior Applications Developer (NY HELPS) #2026-252</t>
         </is>
       </c>
-      <c r="D63" s="29" t="inlineStr">
+      <c r="D63" s="31" t="inlineStr">
         <is>
           <t>Capital Region BOCES</t>
         </is>
       </c>
-      <c r="E63" s="29" t="inlineStr">
+      <c r="E63" s="31" t="inlineStr">
         <is>
           <t>Albany, NY</t>
         </is>
@@ -4542,12 +4548,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H63" s="29" t="inlineStr">
+      <c r="H63" s="31" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I63" s="29" t="inlineStr">
+      <c r="I63" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4562,20 +4568,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L63" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M63" s="29" t="inlineStr"/>
+      <c r="L63" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M63" s="31" t="inlineStr"/>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="28" t="inlineStr">
+      <c r="A64" s="30" t="inlineStr">
         <is>
           <t>4418506121</t>
         </is>
       </c>
-      <c r="B64" s="28" t="inlineStr">
+      <c r="B64" s="30" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4585,12 +4591,12 @@
           <t>Core System Junior Developer</t>
         </is>
       </c>
-      <c r="D64" s="28" t="inlineStr">
+      <c r="D64" s="30" t="inlineStr">
         <is>
           <t>Cyprus Federal Credit Union</t>
         </is>
       </c>
-      <c r="E64" s="28" t="inlineStr">
+      <c r="E64" s="30" t="inlineStr">
         <is>
           <t>West Jordan, UT</t>
         </is>
@@ -4605,12 +4611,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H64" s="28" t="inlineStr">
+      <c r="H64" s="30" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="I64" s="28" t="inlineStr">
+      <c r="I64" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4625,20 +4631,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L64" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M64" s="28" t="inlineStr"/>
+      <c r="L64" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M64" s="30" t="inlineStr"/>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="29" t="inlineStr">
+      <c r="A65" s="31" t="inlineStr">
         <is>
           <t>4413905706</t>
         </is>
       </c>
-      <c r="B65" s="29" t="inlineStr">
+      <c r="B65" s="31" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4648,12 +4654,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D65" s="29" t="inlineStr">
+      <c r="D65" s="31" t="inlineStr">
         <is>
           <t>Arnex Solutions LLC</t>
         </is>
       </c>
-      <c r="E65" s="29" t="inlineStr">
+      <c r="E65" s="31" t="inlineStr">
         <is>
           <t>Princeton, NJ</t>
         </is>
@@ -4668,12 +4674,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H65" s="29" t="inlineStr">
+      <c r="H65" s="31" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I65" s="29" t="inlineStr">
+      <c r="I65" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4688,20 +4694,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L65" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M65" s="29" t="inlineStr"/>
+      <c r="L65" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M65" s="31" t="inlineStr"/>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="28" t="inlineStr">
+      <c r="A66" s="30" t="inlineStr">
         <is>
           <t>4418963446</t>
         </is>
       </c>
-      <c r="B66" s="28" t="inlineStr">
+      <c r="B66" s="30" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4711,12 +4717,12 @@
           <t>Junior Software Engineer - Automation &amp; Integration</t>
         </is>
       </c>
-      <c r="D66" s="28" t="inlineStr">
+      <c r="D66" s="30" t="inlineStr">
         <is>
           <t>Vibrant Building Technologies</t>
         </is>
       </c>
-      <c r="E66" s="28" t="inlineStr">
+      <c r="E66" s="30" t="inlineStr">
         <is>
           <t>Ridgefield, CT</t>
         </is>
@@ -4731,12 +4737,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H66" s="28" t="inlineStr">
+      <c r="H66" s="30" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="I66" s="28" t="inlineStr">
+      <c r="I66" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4751,20 +4757,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L66" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M66" s="28" t="inlineStr"/>
+      <c r="L66" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M66" s="30" t="inlineStr"/>
     </row>
     <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="29" t="inlineStr">
+      <c r="A67" s="31" t="inlineStr">
         <is>
           <t>4413759052</t>
         </is>
       </c>
-      <c r="B67" s="29" t="inlineStr">
+      <c r="B67" s="31" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4774,12 +4780,12 @@
           <t>Junior Full Stack Developer</t>
         </is>
       </c>
-      <c r="D67" s="29" t="inlineStr">
+      <c r="D67" s="31" t="inlineStr">
         <is>
           <t>Allied World Reinsurance Company</t>
         </is>
       </c>
-      <c r="E67" s="29" t="inlineStr">
+      <c r="E67" s="31" t="inlineStr">
         <is>
           <t>Iselin, NJ</t>
         </is>
@@ -4794,12 +4800,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H67" s="29" t="inlineStr">
+      <c r="H67" s="31" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I67" s="29" t="inlineStr">
+      <c r="I67" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4814,20 +4820,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L67" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M67" s="29" t="inlineStr"/>
+      <c r="L67" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M67" s="31" t="inlineStr"/>
     </row>
     <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="28" t="inlineStr">
+      <c r="A68" s="30" t="inlineStr">
         <is>
           <t>4417542502</t>
         </is>
       </c>
-      <c r="B68" s="28" t="inlineStr">
+      <c r="B68" s="30" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4837,12 +4843,12 @@
           <t>Junior Developer</t>
         </is>
       </c>
-      <c r="D68" s="28" t="inlineStr">
+      <c r="D68" s="30" t="inlineStr">
         <is>
           <t>CloudMasonry</t>
         </is>
       </c>
-      <c r="E68" s="28" t="inlineStr">
+      <c r="E68" s="30" t="inlineStr">
         <is>
           <t>Indianapolis, IN</t>
         </is>
@@ -4857,12 +4863,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H68" s="28" t="inlineStr">
+      <c r="H68" s="30" t="inlineStr">
         <is>
           <t>154</t>
         </is>
       </c>
-      <c r="I68" s="28" t="inlineStr">
+      <c r="I68" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4877,20 +4883,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L68" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M68" s="28" t="inlineStr"/>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr"/>
     </row>
     <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="29" t="inlineStr">
+      <c r="A69" s="31" t="inlineStr">
         <is>
           <t>4374856035</t>
         </is>
       </c>
-      <c r="B69" s="29" t="inlineStr">
+      <c r="B69" s="31" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4900,12 +4906,12 @@
           <t>Programmer II</t>
         </is>
       </c>
-      <c r="D69" s="29" t="inlineStr">
+      <c r="D69" s="31" t="inlineStr">
         <is>
           <t>Willis Knighton Health</t>
         </is>
       </c>
-      <c r="E69" s="29" t="inlineStr">
+      <c r="E69" s="31" t="inlineStr">
         <is>
           <t>Louisiana, United States</t>
         </is>
@@ -4920,12 +4926,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H69" s="29" t="inlineStr">
+      <c r="H69" s="31" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="I69" s="29" t="inlineStr">
+      <c r="I69" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4940,20 +4946,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L69" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M69" s="29" t="inlineStr"/>
+      <c r="L69" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M69" s="31" t="inlineStr"/>
     </row>
     <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="28" t="inlineStr">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>4416302564</t>
         </is>
       </c>
-      <c r="B70" s="28" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4963,12 +4969,12 @@
           <t>Software Engineer I</t>
         </is>
       </c>
-      <c r="D70" s="28" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>American Express</t>
         </is>
       </c>
-      <c r="E70" s="28" t="inlineStr">
+      <c r="E70" s="30" t="inlineStr">
         <is>
           <t>Sunrise, FL</t>
         </is>
@@ -4983,12 +4989,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H70" s="28" t="inlineStr">
+      <c r="H70" s="30" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I70" s="28" t="inlineStr">
+      <c r="I70" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5003,20 +5009,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L70" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M70" s="28" t="inlineStr"/>
+      <c r="L70" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M70" s="30" t="inlineStr"/>
     </row>
     <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="29" t="inlineStr">
+      <c r="A71" s="31" t="inlineStr">
         <is>
           <t>4417014137</t>
         </is>
       </c>
-      <c r="B71" s="29" t="inlineStr">
+      <c r="B71" s="31" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5026,12 +5032,12 @@
           <t>Junior Software Developer, Applications</t>
         </is>
       </c>
-      <c r="D71" s="29" t="inlineStr">
+      <c r="D71" s="31" t="inlineStr">
         <is>
           <t>ECS</t>
         </is>
       </c>
-      <c r="E71" s="29" t="inlineStr">
+      <c r="E71" s="31" t="inlineStr">
         <is>
           <t>O'Fallon, IL</t>
         </is>
@@ -5046,12 +5052,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H71" s="29" t="inlineStr">
+      <c r="H71" s="31" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="I71" s="29" t="inlineStr">
+      <c r="I71" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5066,20 +5072,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L71" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M71" s="29" t="inlineStr"/>
+      <c r="L71" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M71" s="31" t="inlineStr"/>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="28" t="inlineStr">
+      <c r="A72" s="30" t="inlineStr">
         <is>
           <t>4381211472</t>
         </is>
       </c>
-      <c r="B72" s="28" t="inlineStr">
+      <c r="B72" s="30" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5089,12 +5095,12 @@
           <t>Programmer</t>
         </is>
       </c>
-      <c r="D72" s="28" t="inlineStr">
+      <c r="D72" s="30" t="inlineStr">
         <is>
           <t>City of New York</t>
         </is>
       </c>
-      <c r="E72" s="28" t="inlineStr">
+      <c r="E72" s="30" t="inlineStr">
         <is>
           <t>Bronx, NY</t>
         </is>
@@ -5109,12 +5115,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H72" s="28" t="inlineStr">
+      <c r="H72" s="30" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="I72" s="28" t="inlineStr">
+      <c r="I72" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5129,20 +5135,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L72" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M72" s="28" t="inlineStr"/>
+      <c r="L72" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M72" s="30" t="inlineStr"/>
     </row>
     <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="29" t="inlineStr">
+      <c r="A73" s="31" t="inlineStr">
         <is>
           <t>4168416236</t>
         </is>
       </c>
-      <c r="B73" s="29" t="inlineStr">
+      <c r="B73" s="31" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5152,12 +5158,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D73" s="29" t="inlineStr">
+      <c r="D73" s="31" t="inlineStr">
         <is>
           <t>Interclypse</t>
         </is>
       </c>
-      <c r="E73" s="29" t="inlineStr">
+      <c r="E73" s="31" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
@@ -5172,12 +5178,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H73" s="29" t="inlineStr">
+      <c r="H73" s="31" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I73" s="29" t="inlineStr">
+      <c r="I73" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5192,20 +5198,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L73" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M73" s="29" t="inlineStr"/>
+      <c r="L73" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M73" s="31" t="inlineStr"/>
     </row>
     <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="28" t="inlineStr">
+      <c r="A74" s="30" t="inlineStr">
         <is>
           <t>4403507357</t>
         </is>
       </c>
-      <c r="B74" s="28" t="inlineStr">
+      <c r="B74" s="30" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5215,12 +5221,12 @@
           <t>Software Developer:</t>
         </is>
       </c>
-      <c r="D74" s="28" t="inlineStr">
+      <c r="D74" s="30" t="inlineStr">
         <is>
           <t>IQuest Solutions Corporation</t>
         </is>
       </c>
-      <c r="E74" s="28" t="inlineStr">
+      <c r="E74" s="30" t="inlineStr">
         <is>
           <t>Plano, TX</t>
         </is>
@@ -5235,12 +5241,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H74" s="28" t="inlineStr">
+      <c r="H74" s="30" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I74" s="28" t="inlineStr">
+      <c r="I74" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5255,20 +5261,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L74" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M74" s="28" t="inlineStr"/>
+      <c r="L74" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M74" s="30" t="inlineStr"/>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="29" t="inlineStr">
+      <c r="A75" s="31" t="inlineStr">
         <is>
           <t>4309800238</t>
         </is>
       </c>
-      <c r="B75" s="29" t="inlineStr">
+      <c r="B75" s="31" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5278,12 +5284,12 @@
           <t>Backend Software Engineer</t>
         </is>
       </c>
-      <c r="D75" s="29" t="inlineStr">
+      <c r="D75" s="31" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E75" s="29" t="inlineStr">
+      <c r="E75" s="31" t="inlineStr">
         <is>
           <t>Texas, United States</t>
         </is>
@@ -5298,12 +5304,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H75" s="29" t="inlineStr">
+      <c r="H75" s="31" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I75" s="29" t="inlineStr">
+      <c r="I75" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5318,20 +5324,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L75" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M75" s="29" t="inlineStr"/>
+      <c r="L75" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M75" s="31" t="inlineStr"/>
     </row>
     <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="28" t="inlineStr">
+      <c r="A76" s="30" t="inlineStr">
         <is>
           <t>4404109089</t>
         </is>
       </c>
-      <c r="B76" s="28" t="inlineStr">
+      <c r="B76" s="30" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5341,12 +5347,12 @@
           <t>Software Development Engineer I</t>
         </is>
       </c>
-      <c r="D76" s="28" t="inlineStr">
+      <c r="D76" s="30" t="inlineStr">
         <is>
           <t>GM Financial</t>
         </is>
       </c>
-      <c r="E76" s="28" t="inlineStr">
+      <c r="E76" s="30" t="inlineStr">
         <is>
           <t>Arlington, TX</t>
         </is>
@@ -5361,12 +5367,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H76" s="28" t="inlineStr">
+      <c r="H76" s="30" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I76" s="28" t="inlineStr">
+      <c r="I76" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5381,20 +5387,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L76" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M76" s="28" t="inlineStr"/>
+      <c r="L76" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M76" s="30" t="inlineStr"/>
     </row>
     <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="29" t="inlineStr">
+      <c r="A77" s="31" t="inlineStr">
         <is>
           <t>3986116411</t>
         </is>
       </c>
-      <c r="B77" s="29" t="inlineStr">
+      <c r="B77" s="31" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5404,12 +5410,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D77" s="29" t="inlineStr">
+      <c r="D77" s="31" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E77" s="29" t="inlineStr">
+      <c r="E77" s="31" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -5424,12 +5430,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H77" s="29" t="inlineStr">
+      <c r="H77" s="31" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I77" s="29" t="inlineStr">
+      <c r="I77" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5444,20 +5450,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L77" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M77" s="29" t="inlineStr"/>
+      <c r="L77" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M77" s="31" t="inlineStr"/>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="28" t="inlineStr">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>4418051524</t>
         </is>
       </c>
-      <c r="B78" s="28" t="inlineStr">
+      <c r="B78" s="30" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5467,12 +5473,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D78" s="28" t="inlineStr">
+      <c r="D78" s="30" t="inlineStr">
         <is>
           <t>Relativity</t>
         </is>
       </c>
-      <c r="E78" s="28" t="inlineStr">
+      <c r="E78" s="30" t="inlineStr">
         <is>
           <t>Texas, United States</t>
         </is>
@@ -5487,12 +5493,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H78" s="28" t="inlineStr">
+      <c r="H78" s="30" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I78" s="28" t="inlineStr">
+      <c r="I78" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5507,20 +5513,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L78" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M78" s="28" t="inlineStr"/>
+      <c r="L78" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M78" s="30" t="inlineStr"/>
     </row>
     <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="29" t="inlineStr">
+      <c r="A79" s="31" t="inlineStr">
         <is>
           <t>4409856693</t>
         </is>
       </c>
-      <c r="B79" s="29" t="inlineStr">
+      <c r="B79" s="31" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5530,12 +5536,12 @@
           <t>Software Engineer - Payments</t>
         </is>
       </c>
-      <c r="D79" s="29" t="inlineStr">
+      <c r="D79" s="31" t="inlineStr">
         <is>
           <t>Cloudbeds</t>
         </is>
       </c>
-      <c r="E79" s="29" t="inlineStr">
+      <c r="E79" s="31" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -5550,12 +5556,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H79" s="29" t="inlineStr">
+      <c r="H79" s="31" t="inlineStr">
         <is>
           <t>177</t>
         </is>
       </c>
-      <c r="I79" s="29" t="inlineStr">
+      <c r="I79" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5570,20 +5576,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L79" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M79" s="29" t="inlineStr"/>
+      <c r="L79" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M79" s="31" t="inlineStr"/>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="28" t="inlineStr">
+      <c r="A80" s="30" t="inlineStr">
         <is>
           <t>3986111771</t>
         </is>
       </c>
-      <c r="B80" s="28" t="inlineStr">
+      <c r="B80" s="30" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5593,12 +5599,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D80" s="28" t="inlineStr">
+      <c r="D80" s="30" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E80" s="28" t="inlineStr">
+      <c r="E80" s="30" t="inlineStr">
         <is>
           <t>Carrollton, TX</t>
         </is>
@@ -5613,12 +5619,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H80" s="28" t="inlineStr">
+      <c r="H80" s="30" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I80" s="28" t="inlineStr">
+      <c r="I80" s="30" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5633,20 +5639,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L80" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M80" s="28" t="inlineStr"/>
+      <c r="L80" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M80" s="30" t="inlineStr"/>
     </row>
     <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="29" t="inlineStr">
+      <c r="A81" s="31" t="inlineStr">
         <is>
           <t>4417160720</t>
         </is>
       </c>
-      <c r="B81" s="29" t="inlineStr">
+      <c r="B81" s="31" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5656,12 +5662,12 @@
           <t>Full-Stack AI Developer</t>
         </is>
       </c>
-      <c r="D81" s="29" t="inlineStr">
+      <c r="D81" s="31" t="inlineStr">
         <is>
           <t>AnswerMyQ</t>
         </is>
       </c>
-      <c r="E81" s="29" t="inlineStr">
+      <c r="E81" s="31" t="inlineStr">
         <is>
           <t>Austin, Texas Metropolitan Area</t>
         </is>
@@ -5676,12 +5682,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H81" s="29" t="inlineStr">
+      <c r="H81" s="31" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I81" s="29" t="inlineStr">
+      <c r="I81" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5696,20 +5702,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L81" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M81" s="29" t="inlineStr"/>
+      <c r="L81" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M81" s="31" t="inlineStr"/>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="28" t="inlineStr">
+      <c r="A82" s="30" t="inlineStr">
         <is>
           <t>4418507307</t>
         </is>
       </c>
-      <c r="B82" s="28" t="inlineStr">
+      <c r="B82" s="30" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -5719,12 +5725,12 @@
           <t>Entry Level Software Engineer Intern</t>
         </is>
       </c>
-      <c r="D82" s="28" t="inlineStr">
+      <c r="D82" s="30" t="inlineStr">
         <is>
           <t>CORMAC</t>
         </is>
       </c>
-      <c r="E82" s="28" t="inlineStr">
+      <c r="E82" s="30" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -5739,12 +5745,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H82" s="28" t="inlineStr">
+      <c r="H82" s="30" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="I82" s="28" t="inlineStr">
+      <c r="I82" s="30" t="inlineStr">
         <is>
           <t>Volunteer</t>
         </is>
@@ -5759,20 +5765,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L82" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M82" s="28" t="inlineStr"/>
+      <c r="L82" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M82" s="30" t="inlineStr"/>
     </row>
     <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="29" t="inlineStr">
+      <c r="A83" s="31" t="inlineStr">
         <is>
           <t>4413360938</t>
         </is>
       </c>
-      <c r="B83" s="29" t="inlineStr">
+      <c r="B83" s="31" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -5782,12 +5788,12 @@
           <t>Software Engineer Internship (Remote)</t>
         </is>
       </c>
-      <c r="D83" s="29" t="inlineStr">
+      <c r="D83" s="31" t="inlineStr">
         <is>
           <t>Orange Trail</t>
         </is>
       </c>
-      <c r="E83" s="29" t="inlineStr">
+      <c r="E83" s="31" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -5802,12 +5808,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H83" s="29" t="inlineStr">
+      <c r="H83" s="31" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I83" s="29" t="inlineStr">
+      <c r="I83" s="31" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -5822,20 +5828,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L83" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M83" s="29" t="inlineStr"/>
+      <c r="L83" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M83" s="31" t="inlineStr"/>
     </row>
     <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="28" t="inlineStr">
+      <c r="A84" s="30" t="inlineStr">
         <is>
           <t>4348111641</t>
         </is>
       </c>
-      <c r="B84" s="28" t="inlineStr">
+      <c r="B84" s="30" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -5845,12 +5851,12 @@
           <t>Software Engineer Intern</t>
         </is>
       </c>
-      <c r="D84" s="28" t="inlineStr">
+      <c r="D84" s="30" t="inlineStr">
         <is>
           <t>Simular</t>
         </is>
       </c>
-      <c r="E84" s="28" t="inlineStr">
+      <c r="E84" s="30" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -5865,12 +5871,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H84" s="28" t="inlineStr">
+      <c r="H84" s="30" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I84" s="28" t="inlineStr">
+      <c r="I84" s="30" t="inlineStr">
         <is>
           <t>Volunteer</t>
         </is>
@@ -5885,20 +5891,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L84" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M84" s="28" t="inlineStr"/>
+      <c r="L84" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M84" s="30" t="inlineStr"/>
     </row>
     <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="29" t="inlineStr">
+      <c r="A85" s="31" t="inlineStr">
         <is>
           <t>4411853543</t>
         </is>
       </c>
-      <c r="B85" s="29" t="inlineStr">
+      <c r="B85" s="31" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -5908,12 +5914,12 @@
           <t>Intern, Software Engineer</t>
         </is>
       </c>
-      <c r="D85" s="29" t="inlineStr">
+      <c r="D85" s="31" t="inlineStr">
         <is>
           <t>Accelerate Learning</t>
         </is>
       </c>
-      <c r="E85" s="29" t="inlineStr">
+      <c r="E85" s="31" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -5928,12 +5934,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H85" s="29" t="inlineStr">
+      <c r="H85" s="31" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I85" s="29" t="inlineStr">
+      <c r="I85" s="31" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5948,20 +5954,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L85" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M85" s="29" t="inlineStr"/>
+      <c r="L85" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M85" s="31" t="inlineStr"/>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="28" t="inlineStr">
+      <c r="A86" s="30" t="inlineStr">
         <is>
           <t>4408586245</t>
         </is>
       </c>
-      <c r="B86" s="28" t="inlineStr">
+      <c r="B86" s="30" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -5971,12 +5977,12 @@
           <t>Junior Software Engineer Intern</t>
         </is>
       </c>
-      <c r="D86" s="28" t="inlineStr">
+      <c r="D86" s="30" t="inlineStr">
         <is>
           <t>Cantaloupe Inc</t>
         </is>
       </c>
-      <c r="E86" s="28" t="inlineStr">
+      <c r="E86" s="30" t="inlineStr">
         <is>
           <t>Atlanta, GA</t>
         </is>
@@ -5991,12 +5997,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H86" s="28" t="inlineStr">
+      <c r="H86" s="30" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I86" s="28" t="inlineStr">
+      <c r="I86" s="30" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -6011,20 +6017,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L86" s="28" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M86" s="28" t="inlineStr"/>
+      <c r="L86" s="30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M86" s="30" t="inlineStr"/>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="29" t="inlineStr">
+      <c r="A87" s="31" t="inlineStr">
         <is>
           <t>4364536992</t>
         </is>
       </c>
-      <c r="B87" s="29" t="inlineStr">
+      <c r="B87" s="31" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -6034,12 +6040,12 @@
           <t>Summer Internship - Measurement, Research and Development - Academic Measurement</t>
         </is>
       </c>
-      <c r="D87" s="29" t="inlineStr">
+      <c r="D87" s="31" t="inlineStr">
         <is>
           <t>ChatGPT Jobs</t>
         </is>
       </c>
-      <c r="E87" s="29" t="inlineStr">
+      <c r="E87" s="31" t="inlineStr">
         <is>
           <t>Iowa City, IA</t>
         </is>
@@ -6054,12 +6060,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H87" s="29" t="inlineStr">
+      <c r="H87" s="31" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I87" s="29" t="inlineStr">
+      <c r="I87" s="31" t="inlineStr">
         <is>
           <t>Volunteer</t>
         </is>
@@ -6074,12 +6080,12 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L87" s="29" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M87" s="29" t="inlineStr"/>
+      <c r="L87" s="31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M87" s="31" t="inlineStr"/>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="A88" s="30" t="inlineStr">
@@ -7404,8 +7410,1079 @@
       </c>
       <c r="M108" s="30" t="inlineStr"/>
     </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="A109" s="32" t="inlineStr">
+        <is>
+          <t>4412210123</t>
+        </is>
+      </c>
+      <c r="B109" s="32" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>Summer Intern - Software Engineer</t>
+        </is>
+      </c>
+      <c r="D109" s="32" t="inlineStr">
+        <is>
+          <t>Allegion (Southeast Asia) Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="E109" s="32" t="inlineStr">
+        <is>
+          <t>Carmel, IN</t>
+        </is>
+      </c>
+      <c r="F109" s="18" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="G109" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H109" s="32" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I109" s="32" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J109" s="8" t="inlineStr">
+        <is>
+          <t>Skills: c, agile, Title match: Summer Intern - Software Engineer</t>
+        </is>
+      </c>
+      <c r="K109" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L109" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M109" s="32" t="inlineStr"/>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="A110" s="33" t="inlineStr">
+        <is>
+          <t>4414924766</t>
+        </is>
+      </c>
+      <c r="B110" s="33" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D110" s="33" t="inlineStr">
+        <is>
+          <t>Uneek Global</t>
+        </is>
+      </c>
+      <c r="E110" s="33" t="inlineStr">
+        <is>
+          <t>Texas, United States</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="G110" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H110" s="33" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I110" s="33" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, react, node, docker, full-stack, c, Location: Texas, United States, Title match: Software Engineer</t>
+        </is>
+      </c>
+      <c r="K110" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L110" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M110" s="33" t="inlineStr"/>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="32" t="inlineStr">
+        <is>
+          <t>4411278313</t>
+        </is>
+      </c>
+      <c r="B111" s="32" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C111" s="8" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer (.NET)</t>
+        </is>
+      </c>
+      <c r="D111" s="32" t="inlineStr">
+        <is>
+          <t>Quintrix, by Mindlance</t>
+        </is>
+      </c>
+      <c r="E111" s="32" t="inlineStr">
+        <is>
+          <t>Austin, Texas Metropolitan Area</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H111" s="32" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I111" s="32" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="J111" s="8" t="inlineStr">
+        <is>
+          <t>Skills: aws, rest, api, sql, c, agile, Location: Austin, Texas Metropolitan Area, Title match: Junior Software Engineer (.NET)</t>
+        </is>
+      </c>
+      <c r="K111" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L111" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M111" s="32" t="inlineStr"/>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="A112" s="33" t="inlineStr">
+        <is>
+          <t>4340327286</t>
+        </is>
+      </c>
+      <c r="B112" s="33" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>IT Services - SOFTWARE DEVELOPERS</t>
+        </is>
+      </c>
+      <c r="D112" s="33" t="inlineStr">
+        <is>
+          <t>Fuge Technologies Inc</t>
+        </is>
+      </c>
+      <c r="E112" s="33" t="inlineStr">
+        <is>
+          <t>Irving, TX</t>
+        </is>
+      </c>
+      <c r="F112" s="18" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="G112" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H112" s="33" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="I112" s="33" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>Skills: docker, git, sql, c, Title match: IT Services - SOFTWARE DEVELOPERS</t>
+        </is>
+      </c>
+      <c r="K112" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L112" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M112" s="33" t="inlineStr"/>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="A113" s="32" t="inlineStr">
+        <is>
+          <t>4243859384</t>
+        </is>
+      </c>
+      <c r="B113" s="32" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t>Test analyst</t>
+        </is>
+      </c>
+      <c r="D113" s="32" t="inlineStr">
+        <is>
+          <t>ADP WFN Test Company 3</t>
+        </is>
+      </c>
+      <c r="E113" s="32" t="inlineStr">
+        <is>
+          <t>San Antonio, TX</t>
+        </is>
+      </c>
+      <c r="F113" s="14" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="G113" s="15" t="inlineStr">
+        <is>
+          <t>Very Low</t>
+        </is>
+      </c>
+      <c r="H113" s="32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I113" s="32" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J113" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, html, c++, c, agile</t>
+        </is>
+      </c>
+      <c r="K113" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L113" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M113" s="32" t="inlineStr"/>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="A114" s="33" t="inlineStr">
+        <is>
+          <t>4407894427</t>
+        </is>
+      </c>
+      <c r="B114" s="33" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D114" s="33" t="inlineStr">
+        <is>
+          <t>Meriplex</t>
+        </is>
+      </c>
+      <c r="E114" s="33" t="inlineStr">
+        <is>
+          <t>Houston, TX</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="G114" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H114" s="33" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I114" s="33" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>Skills: javascript, react, aws, rest, api, git, Location: Houston, TX, Title match: Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="K114" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L114" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M114" s="33" t="inlineStr"/>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="A115" s="32" t="inlineStr">
+        <is>
+          <t>4414252424</t>
+        </is>
+      </c>
+      <c r="B115" s="32" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr">
+        <is>
+          <t>Junior Developer</t>
+        </is>
+      </c>
+      <c r="D115" s="32" t="inlineStr">
+        <is>
+          <t>Joyce Meyer Ministries</t>
+        </is>
+      </c>
+      <c r="E115" s="32" t="inlineStr">
+        <is>
+          <t>Fenton, MO</t>
+        </is>
+      </c>
+      <c r="F115" s="14" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="G115" s="15" t="inlineStr">
+        <is>
+          <t>Very Low</t>
+        </is>
+      </c>
+      <c r="H115" s="32" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="I115" s="32" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J115" s="8" t="inlineStr">
+        <is>
+          <t>Skills: c, Title match: Junior Developer</t>
+        </is>
+      </c>
+      <c r="K115" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L115" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M115" s="32" t="inlineStr"/>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="A116" s="33" t="inlineStr">
+        <is>
+          <t>4401782778</t>
+        </is>
+      </c>
+      <c r="B116" s="33" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>Junior Full-Stack Software Developer</t>
+        </is>
+      </c>
+      <c r="D116" s="33" t="inlineStr">
+        <is>
+          <t>Visionist, Inc.</t>
+        </is>
+      </c>
+      <c r="E116" s="33" t="inlineStr">
+        <is>
+          <t>Columbia, MD</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H116" s="33" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="I116" s="33" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, rest, api, git, full-stack, Title match: Junior Full-Stack Software Developer</t>
+        </is>
+      </c>
+      <c r="K116" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L116" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M116" s="33" t="inlineStr"/>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="A117" s="32" t="inlineStr">
+        <is>
+          <t>4411523361</t>
+        </is>
+      </c>
+      <c r="B117" s="32" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t>Junior Application Developer</t>
+        </is>
+      </c>
+      <c r="D117" s="32" t="inlineStr">
+        <is>
+          <t>HCL Global Systems Inc</t>
+        </is>
+      </c>
+      <c r="E117" s="32" t="inlineStr">
+        <is>
+          <t>Georgia, United States</t>
+        </is>
+      </c>
+      <c r="F117" s="14" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="G117" s="15" t="inlineStr">
+        <is>
+          <t>Very Low</t>
+        </is>
+      </c>
+      <c r="H117" s="32" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I117" s="32" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="J117" s="8" t="inlineStr">
+        <is>
+          <t>Skills: sql, c</t>
+        </is>
+      </c>
+      <c r="K117" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L117" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M117" s="32" t="inlineStr"/>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="A118" s="33" t="inlineStr">
+        <is>
+          <t>4261490006</t>
+        </is>
+      </c>
+      <c r="B118" s="33" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="D118" s="33" t="inlineStr">
+        <is>
+          <t>ADP WFN Test Company 3</t>
+        </is>
+      </c>
+      <c r="E118" s="33" t="inlineStr">
+        <is>
+          <t>San Antonio, TX</t>
+        </is>
+      </c>
+      <c r="F118" s="18" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="G118" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H118" s="33" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I118" s="33" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>Skills: javascript, aws, html, css, git, sql</t>
+        </is>
+      </c>
+      <c r="K118" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L118" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M118" s="33" t="inlineStr"/>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="A119" s="32" t="inlineStr">
+        <is>
+          <t>4422878758</t>
+        </is>
+      </c>
+      <c r="B119" s="32" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer</t>
+        </is>
+      </c>
+      <c r="D119" s="32" t="inlineStr">
+        <is>
+          <t>Brooksource</t>
+        </is>
+      </c>
+      <c r="E119" s="32" t="inlineStr">
+        <is>
+          <t>Lansing, MI</t>
+        </is>
+      </c>
+      <c r="F119" s="14" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="G119" s="15" t="inlineStr">
+        <is>
+          <t>Very Low</t>
+        </is>
+      </c>
+      <c r="H119" s="32" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I119" s="32" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J119" s="8" t="inlineStr">
+        <is>
+          <t>Skills: c, Title match: Junior Software Engineer</t>
+        </is>
+      </c>
+      <c r="K119" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L119" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M119" s="32" t="inlineStr"/>
+    </row>
+    <row r="120" ht="18" customHeight="1">
+      <c r="A120" s="33" t="inlineStr">
+        <is>
+          <t>4419071723</t>
+        </is>
+      </c>
+      <c r="B120" s="33" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>Junior Software Developer</t>
+        </is>
+      </c>
+      <c r="D120" s="33" t="inlineStr">
+        <is>
+          <t>IPTA</t>
+        </is>
+      </c>
+      <c r="E120" s="33" t="inlineStr">
+        <is>
+          <t>Layton, UT</t>
+        </is>
+      </c>
+      <c r="F120" s="18" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="G120" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H120" s="33" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="I120" s="33" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>Skills: aws, html, css, sql, c, Title match: Junior Software Developer</t>
+        </is>
+      </c>
+      <c r="K120" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L120" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M120" s="33" t="inlineStr"/>
+    </row>
+    <row r="121" ht="18" customHeight="1">
+      <c r="A121" s="32" t="inlineStr">
+        <is>
+          <t>4420988356</t>
+        </is>
+      </c>
+      <c r="B121" s="32" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C121" s="8" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer</t>
+        </is>
+      </c>
+      <c r="D121" s="32" t="inlineStr">
+        <is>
+          <t>Switchboard</t>
+        </is>
+      </c>
+      <c r="E121" s="32" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H121" s="32" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I121" s="32" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J121" s="8" t="inlineStr">
+        <is>
+          <t>Skills: aws, rest, git, full-stack, backend, frontend, Title match: Junior Software Engineer</t>
+        </is>
+      </c>
+      <c r="K121" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L121" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M121" s="32" t="inlineStr"/>
+    </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="A122" s="33" t="inlineStr">
+        <is>
+          <t>4419072850</t>
+        </is>
+      </c>
+      <c r="B122" s="33" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>junior software engineer analyst</t>
+        </is>
+      </c>
+      <c r="D122" s="33" t="inlineStr">
+        <is>
+          <t>Altamira Technologies Corporation</t>
+        </is>
+      </c>
+      <c r="E122" s="33" t="inlineStr">
+        <is>
+          <t>State College, PA</t>
+        </is>
+      </c>
+      <c r="F122" s="18" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="G122" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H122" s="33" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="I122" s="33" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, react, full-stack, c, Title match: junior software engineer analyst</t>
+        </is>
+      </c>
+      <c r="K122" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L122" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M122" s="33" t="inlineStr"/>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="A123" s="32" t="inlineStr">
+        <is>
+          <t>4406854247</t>
+        </is>
+      </c>
+      <c r="B123" s="32" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C123" s="8" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D123" s="32" t="inlineStr">
+        <is>
+          <t>The Anywhere Company</t>
+        </is>
+      </c>
+      <c r="E123" s="32" t="inlineStr">
+        <is>
+          <t>Hilton Head Island, SC</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H123" s="32" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I123" s="32" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J123" s="8" t="inlineStr">
+        <is>
+          <t>Skills: javascript, aws, api, html, css, sql, Title match: Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="K123" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L123" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M123" s="32" t="inlineStr"/>
+    </row>
+    <row r="124" ht="18" customHeight="1">
+      <c r="A124" s="33" t="inlineStr">
+        <is>
+          <t>4394719485</t>
+        </is>
+      </c>
+      <c r="B124" s="33" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>Software Developer I, II (Days 8am to 5pm) *On-Site Victor, NY*</t>
+        </is>
+      </c>
+      <c r="D124" s="33" t="inlineStr">
+        <is>
+          <t>LSI SOLUTIONS®</t>
+        </is>
+      </c>
+      <c r="E124" s="33" t="inlineStr">
+        <is>
+          <t>Victor, NY</t>
+        </is>
+      </c>
+      <c r="F124" s="18" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="G124" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H124" s="33" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I124" s="33" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>Skills: c, data structures, Title match: Software Developer I, II (Days 8am to 5pm) *On-Site Victor, NY*</t>
+        </is>
+      </c>
+      <c r="K124" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L124" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M124" s="33" t="inlineStr"/>
+    </row>
+    <row r="125" ht="18" customHeight="1">
+      <c r="A125" s="32" t="inlineStr">
+        <is>
+          <t>4367493426</t>
+        </is>
+      </c>
+      <c r="B125" s="32" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C125" s="8" t="inlineStr">
+        <is>
+          <t>Junior Software Developer</t>
+        </is>
+      </c>
+      <c r="D125" s="32" t="inlineStr">
+        <is>
+          <t>KIHOMAC</t>
+        </is>
+      </c>
+      <c r="E125" s="32" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H125" s="32" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="I125" s="32" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J125" s="8" t="inlineStr">
+        <is>
+          <t>Skills: javascript, react, node, rest, api, html, Title match: Junior Software Developer</t>
+        </is>
+      </c>
+      <c r="K125" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L125" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M125" s="32" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M108"/>
+  <autoFilter ref="A1:M125"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -7514,6 +8591,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId105"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K125" r:id="rId124"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Job Matches" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Matches'!$A$1:$M$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Matches'!$A$1:$M$129</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -217,6 +217,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -584,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M125"/>
+  <dimension ref="A1:M129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -670,12 +676,12 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="30" t="inlineStr">
+      <c r="A2" s="33" t="inlineStr">
         <is>
           <t>4406952064</t>
         </is>
       </c>
-      <c r="B2" s="30" t="inlineStr">
+      <c r="B2" s="33" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -685,12 +691,12 @@
           <t>DevSecOps Intern</t>
         </is>
       </c>
-      <c r="D2" s="30" t="inlineStr">
+      <c r="D2" s="33" t="inlineStr">
         <is>
           <t>Modern Technology Solutions, Inc. (MTSI)</t>
         </is>
       </c>
-      <c r="E2" s="30" t="inlineStr">
+      <c r="E2" s="33" t="inlineStr">
         <is>
           <t>Huntsville, AL</t>
         </is>
@@ -705,12 +711,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H2" s="30" t="inlineStr">
+      <c r="H2" s="33" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="I2" s="30" t="inlineStr">
+      <c r="I2" s="33" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -725,20 +731,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L2" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M2" s="30" t="inlineStr"/>
+      <c r="L2" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M2" s="33" t="inlineStr"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="31" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>4405630173</t>
         </is>
       </c>
-      <c r="B3" s="31" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -748,12 +754,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D3" s="31" t="inlineStr">
+      <c r="D3" s="32" t="inlineStr">
         <is>
           <t>DLRdmv®</t>
         </is>
       </c>
-      <c r="E3" s="31" t="inlineStr">
+      <c r="E3" s="32" t="inlineStr">
         <is>
           <t>Dallas, TX</t>
         </is>
@@ -768,12 +774,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H3" s="31" t="inlineStr">
+      <c r="H3" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I3" s="31" t="inlineStr">
+      <c r="I3" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -788,20 +794,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L3" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M3" s="31" t="inlineStr"/>
+      <c r="L3" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M3" s="32" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>4287414862</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -811,12 +817,12 @@
           <t>[Online Assessment]Software Development Engineer Intern (Network Automation)- 2026 Summer (BS/ MS)</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="33" t="inlineStr">
         <is>
           <t>ByteDance</t>
         </is>
       </c>
-      <c r="E4" s="30" t="inlineStr">
+      <c r="E4" s="33" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -831,12 +837,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H4" s="30" t="inlineStr">
+      <c r="H4" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I4" s="30" t="inlineStr">
+      <c r="I4" s="33" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -851,20 +857,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L4" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M4" s="30" t="inlineStr"/>
+      <c r="L4" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M4" s="33" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>4309805269</t>
         </is>
       </c>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -874,12 +880,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D5" s="31" t="inlineStr">
+      <c r="D5" s="32" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E5" s="31" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t>Delaware, United States</t>
         </is>
@@ -894,12 +900,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H5" s="31" t="inlineStr">
+      <c r="H5" s="32" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="I5" s="31" t="inlineStr">
+      <c r="I5" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -914,20 +920,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L5" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M5" s="31" t="inlineStr"/>
+      <c r="L5" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M5" s="32" t="inlineStr"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>4371812987</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -937,12 +943,12 @@
           <t>Software Development Engineer Fall Intern - Military Veteran</t>
         </is>
       </c>
-      <c r="D6" s="30" t="inlineStr">
+      <c r="D6" s="33" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E6" s="30" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -957,12 +963,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H6" s="30" t="inlineStr">
+      <c r="H6" s="33" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="I6" s="30" t="inlineStr">
+      <c r="I6" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -977,20 +983,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L6" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M6" s="30" t="inlineStr"/>
+      <c r="L6" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M6" s="33" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>4274682122</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1000,12 +1006,12 @@
           <t>Software Engineer Intern (Data Ecosystem) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D7" s="31" t="inlineStr">
+      <c r="D7" s="32" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E7" s="31" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1020,12 +1026,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H7" s="31" t="inlineStr">
+      <c r="H7" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I7" s="31" t="inlineStr">
+      <c r="I7" s="32" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1040,20 +1046,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L7" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M7" s="31" t="inlineStr"/>
+      <c r="L7" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M7" s="32" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>4283848614</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1063,12 +1069,12 @@
           <t>[Online Assessment] Software Engineer Intern (Recommendation Infrastructure) - 2026 Fall (BS/ MS)</t>
         </is>
       </c>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="D8" s="33" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E8" s="30" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1083,12 +1089,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H8" s="30" t="inlineStr">
+      <c r="H8" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I8" s="30" t="inlineStr">
+      <c r="I8" s="33" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1103,20 +1109,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L8" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M8" s="30" t="inlineStr"/>
+      <c r="L8" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M8" s="33" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>4411790844</t>
         </is>
       </c>
-      <c r="B9" s="31" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1126,12 +1132,12 @@
           <t>Software Engineer Intern (Infrastructure Automation) - Fall 2026</t>
         </is>
       </c>
-      <c r="D9" s="31" t="inlineStr">
+      <c r="D9" s="32" t="inlineStr">
         <is>
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="E9" s="31" t="inlineStr">
+      <c r="E9" s="32" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -1146,12 +1152,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H9" s="31" t="inlineStr">
+      <c r="H9" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I9" s="31" t="inlineStr">
+      <c r="I9" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1166,20 +1172,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L9" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M9" s="31" t="inlineStr"/>
+      <c r="L9" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M9" s="32" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>4332425058</t>
         </is>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1189,12 +1195,12 @@
           <t>Software Development Engineer Internship - Fall 2026 (US)</t>
         </is>
       </c>
-      <c r="D10" s="30" t="inlineStr">
+      <c r="D10" s="33" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E10" s="30" t="inlineStr">
+      <c r="E10" s="33" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1209,12 +1215,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H10" s="30" t="inlineStr">
+      <c r="H10" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I10" s="30" t="inlineStr">
+      <c r="I10" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1229,20 +1235,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L10" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M10" s="30" t="inlineStr"/>
+      <c r="L10" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M10" s="33" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>4323643644</t>
         </is>
       </c>
-      <c r="B11" s="31" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1252,12 +1258,12 @@
           <t>[Online Assessment] Software Engineer Intern (Recommendation Infrastructure) - 2026 Summer (BS/ MS)</t>
         </is>
       </c>
-      <c r="D11" s="31" t="inlineStr">
+      <c r="D11" s="32" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E11" s="31" t="inlineStr">
+      <c r="E11" s="32" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1272,12 +1278,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H11" s="31" t="inlineStr">
+      <c r="H11" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I11" s="31" t="inlineStr">
+      <c r="I11" s="32" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1292,20 +1298,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L11" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M11" s="31" t="inlineStr"/>
+      <c r="L11" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M11" s="32" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="A12" s="33" t="inlineStr">
         <is>
           <t>4320849104</t>
         </is>
       </c>
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1315,12 +1321,12 @@
           <t>Software Engineer Intern (Commerce Ads) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D12" s="30" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E12" s="30" t="inlineStr">
+      <c r="E12" s="33" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1335,12 +1341,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H12" s="30" t="inlineStr">
+      <c r="H12" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I12" s="30" t="inlineStr">
+      <c r="I12" s="33" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1355,20 +1361,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L12" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M12" s="30" t="inlineStr"/>
+      <c r="L12" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M12" s="33" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>4401686051</t>
         </is>
       </c>
-      <c r="B13" s="31" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1378,12 +1384,12 @@
           <t>Front End Software Engineer</t>
         </is>
       </c>
-      <c r="D13" s="31" t="inlineStr">
+      <c r="D13" s="32" t="inlineStr">
         <is>
           <t>Saronic Technologies</t>
         </is>
       </c>
-      <c r="E13" s="31" t="inlineStr">
+      <c r="E13" s="32" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -1398,12 +1404,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H13" s="31" t="inlineStr">
+      <c r="H13" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I13" s="31" t="inlineStr">
+      <c r="I13" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1418,20 +1424,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L13" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M13" s="31" t="inlineStr"/>
+      <c r="L13" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M13" s="32" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="30" t="inlineStr">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>4309696652</t>
         </is>
       </c>
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="33" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1441,12 +1447,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D14" s="30" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E14" s="30" t="inlineStr">
+      <c r="E14" s="33" t="inlineStr">
         <is>
           <t>Rhode Island, United States</t>
         </is>
@@ -1461,12 +1467,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H14" s="30" t="inlineStr">
+      <c r="H14" s="33" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="I14" s="30" t="inlineStr">
+      <c r="I14" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1481,20 +1487,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L14" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M14" s="30" t="inlineStr"/>
+      <c r="L14" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M14" s="33" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>4309804319</t>
         </is>
       </c>
-      <c r="B15" s="31" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1504,12 +1510,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D15" s="31" t="inlineStr">
+      <c r="D15" s="32" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E15" s="31" t="inlineStr">
+      <c r="E15" s="32" t="inlineStr">
         <is>
           <t>Colorado, United States</t>
         </is>
@@ -1524,12 +1530,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H15" s="31" t="inlineStr">
+      <c r="H15" s="32" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="I15" s="31" t="inlineStr">
+      <c r="I15" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1544,20 +1550,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L15" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M15" s="31" t="inlineStr"/>
+      <c r="L15" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M15" s="32" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="30" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>4410271532</t>
         </is>
       </c>
-      <c r="B16" s="30" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1567,12 +1573,12 @@
           <t>Associate Developer</t>
         </is>
       </c>
-      <c r="D16" s="30" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>HealthStream</t>
         </is>
       </c>
-      <c r="E16" s="30" t="inlineStr">
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t>Nashville, TN</t>
         </is>
@@ -1587,12 +1593,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H16" s="30" t="inlineStr">
+      <c r="H16" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I16" s="30" t="inlineStr">
+      <c r="I16" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1607,20 +1613,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L16" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M16" s="30" t="inlineStr"/>
+      <c r="L16" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M16" s="33" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="31" t="inlineStr">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>4304445726</t>
         </is>
       </c>
-      <c r="B17" s="31" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1630,12 +1636,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D17" s="31" t="inlineStr">
+      <c r="D17" s="32" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E17" s="31" t="inlineStr">
+      <c r="E17" s="32" t="inlineStr">
         <is>
           <t>Oregon, United States</t>
         </is>
@@ -1650,12 +1656,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H17" s="31" t="inlineStr">
+      <c r="H17" s="32" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="I17" s="31" t="inlineStr">
+      <c r="I17" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1670,20 +1676,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L17" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M17" s="31" t="inlineStr"/>
+      <c r="L17" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M17" s="32" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="30" t="inlineStr">
+      <c r="A18" s="33" t="inlineStr">
         <is>
           <t>4342036151</t>
         </is>
       </c>
-      <c r="B18" s="30" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1693,12 +1699,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D18" s="30" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>Modern Treasury</t>
         </is>
       </c>
-      <c r="E18" s="30" t="inlineStr">
+      <c r="E18" s="33" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
@@ -1713,12 +1719,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H18" s="30" t="inlineStr">
+      <c r="H18" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I18" s="30" t="inlineStr">
+      <c r="I18" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1733,20 +1739,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L18" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M18" s="30" t="inlineStr"/>
+      <c r="L18" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M18" s="33" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>4304441843</t>
         </is>
       </c>
-      <c r="B19" s="31" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1756,12 +1762,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D19" s="31" t="inlineStr">
+      <c r="D19" s="32" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E19" s="31" t="inlineStr">
+      <c r="E19" s="32" t="inlineStr">
         <is>
           <t>Idaho, United States</t>
         </is>
@@ -1776,12 +1782,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H19" s="31" t="inlineStr">
+      <c r="H19" s="32" t="inlineStr">
         <is>
           <t>157</t>
         </is>
       </c>
-      <c r="I19" s="31" t="inlineStr">
+      <c r="I19" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1796,20 +1802,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L19" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M19" s="31" t="inlineStr"/>
+      <c r="L19" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M19" s="32" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
+      <c r="A20" s="33" t="inlineStr">
         <is>
           <t>4408047047</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1819,12 +1825,12 @@
           <t>Computer Sciences - Graduates - AI Training - Las Vegas, US</t>
         </is>
       </c>
-      <c r="D20" s="30" t="inlineStr">
+      <c r="D20" s="33" t="inlineStr">
         <is>
           <t>Prolific</t>
         </is>
       </c>
-      <c r="E20" s="30" t="inlineStr">
+      <c r="E20" s="33" t="inlineStr">
         <is>
           <t>Las Vegas, NV</t>
         </is>
@@ -1839,12 +1845,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H20" s="30" t="inlineStr">
+      <c r="H20" s="33" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I20" s="30" t="inlineStr">
+      <c r="I20" s="33" t="inlineStr">
         <is>
           <t>Temporary</t>
         </is>
@@ -1859,20 +1865,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L20" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M20" s="30" t="inlineStr"/>
+      <c r="L20" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M20" s="33" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="31" t="inlineStr">
+      <c r="A21" s="32" t="inlineStr">
         <is>
           <t>4304444837</t>
         </is>
       </c>
-      <c r="B21" s="31" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1882,12 +1888,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D21" s="31" t="inlineStr">
+      <c r="D21" s="32" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E21" s="31" t="inlineStr">
+      <c r="E21" s="32" t="inlineStr">
         <is>
           <t>New Jersey, United States</t>
         </is>
@@ -1902,12 +1908,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H21" s="31" t="inlineStr">
+      <c r="H21" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I21" s="31" t="inlineStr">
+      <c r="I21" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1922,20 +1928,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L21" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M21" s="31" t="inlineStr"/>
+      <c r="L21" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M21" s="32" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="30" t="inlineStr">
+      <c r="A22" s="33" t="inlineStr">
         <is>
           <t>4405641326</t>
         </is>
       </c>
-      <c r="B22" s="30" t="inlineStr">
+      <c r="B22" s="33" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1945,12 +1951,12 @@
           <t>Full-stack Engineer</t>
         </is>
       </c>
-      <c r="D22" s="30" t="inlineStr">
+      <c r="D22" s="33" t="inlineStr">
         <is>
           <t>PartnerTap</t>
         </is>
       </c>
-      <c r="E22" s="30" t="inlineStr">
+      <c r="E22" s="33" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1965,12 +1971,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H22" s="30" t="inlineStr">
+      <c r="H22" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I22" s="30" t="inlineStr">
+      <c r="I22" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1985,20 +1991,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L22" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M22" s="30" t="inlineStr"/>
+      <c r="L22" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M22" s="33" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="31" t="inlineStr">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>4341020900</t>
         </is>
       </c>
-      <c r="B23" s="31" t="inlineStr">
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2008,12 +2014,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D23" s="31" t="inlineStr">
+      <c r="D23" s="32" t="inlineStr">
         <is>
           <t>PlanIT Group, LLC</t>
         </is>
       </c>
-      <c r="E23" s="31" t="inlineStr">
+      <c r="E23" s="32" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -2028,12 +2034,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H23" s="31" t="inlineStr">
+      <c r="H23" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I23" s="31" t="inlineStr">
+      <c r="I23" s="32" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
@@ -2048,20 +2054,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L23" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M23" s="31" t="inlineStr"/>
+      <c r="L23" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M23" s="32" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="30" t="inlineStr">
+      <c r="A24" s="33" t="inlineStr">
         <is>
           <t>4304450637</t>
         </is>
       </c>
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B24" s="33" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2071,12 +2077,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D24" s="30" t="inlineStr">
+      <c r="D24" s="33" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E24" s="30" t="inlineStr">
+      <c r="E24" s="33" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -2091,12 +2097,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H24" s="30" t="inlineStr">
+      <c r="H24" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I24" s="30" t="inlineStr">
+      <c r="I24" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2111,20 +2117,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L24" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M24" s="30" t="inlineStr"/>
+      <c r="L24" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M24" s="33" t="inlineStr"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="31" t="inlineStr">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t>4304451654</t>
         </is>
       </c>
-      <c r="B25" s="31" t="inlineStr">
+      <c r="B25" s="32" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2134,12 +2140,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D25" s="31" t="inlineStr">
+      <c r="D25" s="32" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E25" s="31" t="inlineStr">
+      <c r="E25" s="32" t="inlineStr">
         <is>
           <t>Utah, United States</t>
         </is>
@@ -2154,12 +2160,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H25" s="31" t="inlineStr">
+      <c r="H25" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I25" s="31" t="inlineStr">
+      <c r="I25" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2174,20 +2180,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L25" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M25" s="31" t="inlineStr"/>
+      <c r="L25" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M25" s="32" t="inlineStr"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="30" t="inlineStr">
+      <c r="A26" s="33" t="inlineStr">
         <is>
           <t>4413745880</t>
         </is>
       </c>
-      <c r="B26" s="30" t="inlineStr">
+      <c r="B26" s="33" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2197,12 +2203,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D26" s="30" t="inlineStr">
+      <c r="D26" s="33" t="inlineStr">
         <is>
           <t>Crate &amp; Barrel</t>
         </is>
       </c>
-      <c r="E26" s="30" t="inlineStr">
+      <c r="E26" s="33" t="inlineStr">
         <is>
           <t>Northbrook, IL</t>
         </is>
@@ -2217,12 +2223,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H26" s="30" t="inlineStr">
+      <c r="H26" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I26" s="30" t="inlineStr">
+      <c r="I26" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2237,20 +2243,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L26" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M26" s="30" t="inlineStr"/>
+      <c r="L26" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M26" s="33" t="inlineStr"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="31" t="inlineStr">
+      <c r="A27" s="32" t="inlineStr">
         <is>
           <t>4304438841</t>
         </is>
       </c>
-      <c r="B27" s="31" t="inlineStr">
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2260,12 +2266,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D27" s="31" t="inlineStr">
+      <c r="D27" s="32" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E27" s="31" t="inlineStr">
+      <c r="E27" s="32" t="inlineStr">
         <is>
           <t>Connecticut, United States</t>
         </is>
@@ -2280,12 +2286,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H27" s="31" t="inlineStr">
+      <c r="H27" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I27" s="31" t="inlineStr">
+      <c r="I27" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2300,20 +2306,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L27" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M27" s="31" t="inlineStr"/>
+      <c r="L27" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M27" s="32" t="inlineStr"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="30" t="inlineStr">
+      <c r="A28" s="33" t="inlineStr">
         <is>
           <t>4393215930</t>
         </is>
       </c>
-      <c r="B28" s="30" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2323,12 +2329,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D28" s="30" t="inlineStr">
+      <c r="D28" s="33" t="inlineStr">
         <is>
           <t>Transcend</t>
         </is>
       </c>
-      <c r="E28" s="30" t="inlineStr">
+      <c r="E28" s="33" t="inlineStr">
         <is>
           <t>California, United States</t>
         </is>
@@ -2343,12 +2349,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H28" s="30" t="inlineStr">
+      <c r="H28" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I28" s="30" t="inlineStr">
+      <c r="I28" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2363,20 +2369,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L28" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M28" s="30" t="inlineStr"/>
+      <c r="L28" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M28" s="33" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="31" t="inlineStr">
+      <c r="A29" s="32" t="inlineStr">
         <is>
           <t>4304445723</t>
         </is>
       </c>
-      <c r="B29" s="31" t="inlineStr">
+      <c r="B29" s="32" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2386,12 +2392,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D29" s="31" t="inlineStr">
+      <c r="D29" s="32" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E29" s="31" t="inlineStr">
+      <c r="E29" s="32" t="inlineStr">
         <is>
           <t>Illinois, United States</t>
         </is>
@@ -2406,12 +2412,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H29" s="31" t="inlineStr">
+      <c r="H29" s="32" t="inlineStr">
         <is>
           <t>198</t>
         </is>
       </c>
-      <c r="I29" s="31" t="inlineStr">
+      <c r="I29" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2426,20 +2432,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L29" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M29" s="31" t="inlineStr"/>
+      <c r="L29" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M29" s="32" t="inlineStr"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="30" t="inlineStr">
+      <c r="A30" s="33" t="inlineStr">
         <is>
           <t>4396380649</t>
         </is>
       </c>
-      <c r="B30" s="30" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2449,12 +2455,12 @@
           <t>Full-Stack Developer Intern, Music &amp; Audio</t>
         </is>
       </c>
-      <c r="D30" s="30" t="inlineStr">
+      <c r="D30" s="33" t="inlineStr">
         <is>
           <t>Melotech</t>
         </is>
       </c>
-      <c r="E30" s="30" t="inlineStr">
+      <c r="E30" s="33" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
@@ -2469,12 +2475,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H30" s="30" t="inlineStr">
+      <c r="H30" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I30" s="30" t="inlineStr">
+      <c r="I30" s="33" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -2489,20 +2495,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L30" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M30" s="30" t="inlineStr"/>
+      <c r="L30" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M30" s="33" t="inlineStr"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="31" t="inlineStr">
+      <c r="A31" s="32" t="inlineStr">
         <is>
           <t>4304454025</t>
         </is>
       </c>
-      <c r="B31" s="31" t="inlineStr">
+      <c r="B31" s="32" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2512,12 +2518,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D31" s="31" t="inlineStr">
+      <c r="D31" s="32" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E31" s="31" t="inlineStr">
+      <c r="E31" s="32" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -2532,12 +2538,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H31" s="31" t="inlineStr">
+      <c r="H31" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I31" s="31" t="inlineStr">
+      <c r="I31" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2552,20 +2558,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L31" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M31" s="31" t="inlineStr"/>
+      <c r="L31" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M31" s="32" t="inlineStr"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="30" t="inlineStr">
+      <c r="A32" s="33" t="inlineStr">
         <is>
           <t>4309802287</t>
         </is>
       </c>
-      <c r="B32" s="30" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2575,12 +2581,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D32" s="30" t="inlineStr">
+      <c r="D32" s="33" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E32" s="30" t="inlineStr">
+      <c r="E32" s="33" t="inlineStr">
         <is>
           <t>New Jersey, United States</t>
         </is>
@@ -2595,12 +2601,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H32" s="30" t="inlineStr">
+      <c r="H32" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I32" s="30" t="inlineStr">
+      <c r="I32" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2615,20 +2621,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L32" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M32" s="30" t="inlineStr"/>
+      <c r="L32" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M32" s="33" t="inlineStr"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="31" t="inlineStr">
+      <c r="A33" s="32" t="inlineStr">
         <is>
           <t>4309694880</t>
         </is>
       </c>
-      <c r="B33" s="31" t="inlineStr">
+      <c r="B33" s="32" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2638,12 +2644,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D33" s="31" t="inlineStr">
+      <c r="D33" s="32" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E33" s="31" t="inlineStr">
+      <c r="E33" s="32" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -2658,12 +2664,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H33" s="31" t="inlineStr">
+      <c r="H33" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I33" s="31" t="inlineStr">
+      <c r="I33" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2678,20 +2684,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L33" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M33" s="31" t="inlineStr"/>
+      <c r="L33" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M33" s="32" t="inlineStr"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="30" t="inlineStr">
+      <c r="A34" s="33" t="inlineStr">
         <is>
           <t>4411274012</t>
         </is>
       </c>
-      <c r="B34" s="30" t="inlineStr">
+      <c r="B34" s="33" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2701,12 +2707,12 @@
           <t>Junior UI Developer</t>
         </is>
       </c>
-      <c r="D34" s="30" t="inlineStr">
+      <c r="D34" s="33" t="inlineStr">
         <is>
           <t>General Dynamics Information Technology</t>
         </is>
       </c>
-      <c r="E34" s="30" t="inlineStr">
+      <c r="E34" s="33" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -2721,12 +2727,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H34" s="30" t="inlineStr">
+      <c r="H34" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I34" s="30" t="inlineStr">
+      <c r="I34" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2741,20 +2747,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L34" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M34" s="30" t="inlineStr"/>
+      <c r="L34" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M34" s="33" t="inlineStr"/>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="31" t="inlineStr">
+      <c r="A35" s="32" t="inlineStr">
         <is>
           <t>4264562292</t>
         </is>
       </c>
-      <c r="B35" s="31" t="inlineStr">
+      <c r="B35" s="32" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2764,12 +2770,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D35" s="31" t="inlineStr">
+      <c r="D35" s="32" t="inlineStr">
         <is>
           <t>Cymertek Corporation</t>
         </is>
       </c>
-      <c r="E35" s="31" t="inlineStr">
+      <c r="E35" s="32" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
@@ -2784,12 +2790,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H35" s="31" t="inlineStr">
+      <c r="H35" s="32" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="I35" s="31" t="inlineStr">
+      <c r="I35" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2804,20 +2810,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L35" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M35" s="31" t="inlineStr"/>
+      <c r="L35" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M35" s="32" t="inlineStr"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="30" t="inlineStr">
+      <c r="A36" s="33" t="inlineStr">
         <is>
           <t>4417482675</t>
         </is>
       </c>
-      <c r="B36" s="30" t="inlineStr">
+      <c r="B36" s="33" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2827,12 +2833,12 @@
           <t>Software Developer I</t>
         </is>
       </c>
-      <c r="D36" s="30" t="inlineStr">
+      <c r="D36" s="33" t="inlineStr">
         <is>
           <t>El Paso Water</t>
         </is>
       </c>
-      <c r="E36" s="30" t="inlineStr">
+      <c r="E36" s="33" t="inlineStr">
         <is>
           <t>El Paso, TX</t>
         </is>
@@ -2847,12 +2853,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H36" s="30" t="inlineStr">
+      <c r="H36" s="33" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="I36" s="30" t="inlineStr">
+      <c r="I36" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2867,20 +2873,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L36" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M36" s="30" t="inlineStr"/>
+      <c r="L36" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M36" s="33" t="inlineStr"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="31" t="inlineStr">
+      <c r="A37" s="32" t="inlineStr">
         <is>
           <t>4416508200</t>
         </is>
       </c>
-      <c r="B37" s="31" t="inlineStr">
+      <c r="B37" s="32" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2890,12 +2896,12 @@
           <t>Software Development Engineer in Test Intern (Global E-Commerce) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D37" s="31" t="inlineStr">
+      <c r="D37" s="32" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E37" s="31" t="inlineStr">
+      <c r="E37" s="32" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -2910,12 +2916,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H37" s="31" t="inlineStr">
+      <c r="H37" s="32" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I37" s="31" t="inlineStr">
+      <c r="I37" s="32" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -2930,20 +2936,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L37" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M37" s="31" t="inlineStr"/>
+      <c r="L37" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M37" s="32" t="inlineStr"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="30" t="inlineStr">
+      <c r="A38" s="33" t="inlineStr">
         <is>
           <t>4309809191</t>
         </is>
       </c>
-      <c r="B38" s="30" t="inlineStr">
+      <c r="B38" s="33" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
@@ -2953,12 +2959,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D38" s="30" t="inlineStr">
+      <c r="D38" s="33" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E38" s="30" t="inlineStr">
+      <c r="E38" s="33" t="inlineStr">
         <is>
           <t>Ohio, United States</t>
         </is>
@@ -2973,12 +2979,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H38" s="30" t="inlineStr">
+      <c r="H38" s="33" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="I38" s="30" t="inlineStr">
+      <c r="I38" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2993,20 +2999,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L38" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M38" s="30" t="inlineStr"/>
+      <c r="L38" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M38" s="33" t="inlineStr"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="31" t="inlineStr">
+      <c r="A39" s="32" t="inlineStr">
         <is>
           <t>3986118096</t>
         </is>
       </c>
-      <c r="B39" s="31" t="inlineStr">
+      <c r="B39" s="32" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
@@ -3016,12 +3022,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D39" s="31" t="inlineStr">
+      <c r="D39" s="32" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E39" s="31" t="inlineStr">
+      <c r="E39" s="32" t="inlineStr">
         <is>
           <t>Irving, TX</t>
         </is>
@@ -3036,12 +3042,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H39" s="31" t="inlineStr">
+      <c r="H39" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I39" s="31" t="inlineStr">
+      <c r="I39" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3056,20 +3062,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L39" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M39" s="31" t="inlineStr"/>
+      <c r="L39" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M39" s="32" t="inlineStr"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="30" t="inlineStr">
+      <c r="A40" s="33" t="inlineStr">
         <is>
           <t>4309808244</t>
         </is>
       </c>
-      <c r="B40" s="30" t="inlineStr">
+      <c r="B40" s="33" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3079,12 +3085,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D40" s="30" t="inlineStr">
+      <c r="D40" s="33" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E40" s="30" t="inlineStr">
+      <c r="E40" s="33" t="inlineStr">
         <is>
           <t>Massachusetts, United States</t>
         </is>
@@ -3099,12 +3105,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H40" s="30" t="inlineStr">
+      <c r="H40" s="33" t="inlineStr">
         <is>
           <t>166</t>
         </is>
       </c>
-      <c r="I40" s="30" t="inlineStr">
+      <c r="I40" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3119,20 +3125,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L40" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M40" s="30" t="inlineStr"/>
+      <c r="L40" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M40" s="33" t="inlineStr"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="31" t="inlineStr">
+      <c r="A41" s="32" t="inlineStr">
         <is>
           <t>4362173625</t>
         </is>
       </c>
-      <c r="B41" s="31" t="inlineStr">
+      <c r="B41" s="32" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3142,12 +3148,12 @@
           <t>Full Stack Engineer</t>
         </is>
       </c>
-      <c r="D41" s="31" t="inlineStr">
+      <c r="D41" s="32" t="inlineStr">
         <is>
           <t>Empower Sleep</t>
         </is>
       </c>
-      <c r="E41" s="31" t="inlineStr">
+      <c r="E41" s="32" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3162,12 +3168,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H41" s="31" t="inlineStr">
+      <c r="H41" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I41" s="31" t="inlineStr">
+      <c r="I41" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3182,20 +3188,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L41" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M41" s="31" t="inlineStr"/>
+      <c r="L41" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M41" s="32" t="inlineStr"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="30" t="inlineStr">
+      <c r="A42" s="33" t="inlineStr">
         <is>
           <t>4309812093</t>
         </is>
       </c>
-      <c r="B42" s="30" t="inlineStr">
+      <c r="B42" s="33" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3205,12 +3211,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D42" s="30" t="inlineStr">
+      <c r="D42" s="33" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E42" s="30" t="inlineStr">
+      <c r="E42" s="33" t="inlineStr">
         <is>
           <t>Florida, United States</t>
         </is>
@@ -3225,12 +3231,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H42" s="30" t="inlineStr">
+      <c r="H42" s="33" t="inlineStr">
         <is>
           <t>158</t>
         </is>
       </c>
-      <c r="I42" s="30" t="inlineStr">
+      <c r="I42" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3245,20 +3251,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L42" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M42" s="30" t="inlineStr"/>
+      <c r="L42" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M42" s="33" t="inlineStr"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="31" t="inlineStr">
+      <c r="A43" s="32" t="inlineStr">
         <is>
           <t>4391759914</t>
         </is>
       </c>
-      <c r="B43" s="31" t="inlineStr">
+      <c r="B43" s="32" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3268,12 +3274,12 @@
           <t>QA Engineering Internship</t>
         </is>
       </c>
-      <c r="D43" s="31" t="inlineStr">
+      <c r="D43" s="32" t="inlineStr">
         <is>
           <t>Chartbeat</t>
         </is>
       </c>
-      <c r="E43" s="31" t="inlineStr">
+      <c r="E43" s="32" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -3288,12 +3294,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H43" s="31" t="inlineStr">
+      <c r="H43" s="32" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="I43" s="31" t="inlineStr">
+      <c r="I43" s="32" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3308,20 +3314,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L43" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M43" s="31" t="inlineStr"/>
+      <c r="L43" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M43" s="32" t="inlineStr"/>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="30" t="inlineStr">
+      <c r="A44" s="33" t="inlineStr">
         <is>
           <t>4412855678</t>
         </is>
       </c>
-      <c r="B44" s="30" t="inlineStr">
+      <c r="B44" s="33" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3331,12 +3337,12 @@
           <t>AI Integration Engineer</t>
         </is>
       </c>
-      <c r="D44" s="30" t="inlineStr">
+      <c r="D44" s="33" t="inlineStr">
         <is>
           <t>UST</t>
         </is>
       </c>
-      <c r="E44" s="30" t="inlineStr">
+      <c r="E44" s="33" t="inlineStr">
         <is>
           <t>Santa Clara, CA</t>
         </is>
@@ -3351,12 +3357,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H44" s="30" t="inlineStr">
+      <c r="H44" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I44" s="30" t="inlineStr">
+      <c r="I44" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3371,20 +3377,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L44" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M44" s="30" t="inlineStr"/>
+      <c r="L44" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M44" s="33" t="inlineStr"/>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="31" t="inlineStr">
+      <c r="A45" s="32" t="inlineStr">
         <is>
           <t>4309805219</t>
         </is>
       </c>
-      <c r="B45" s="31" t="inlineStr">
+      <c r="B45" s="32" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3394,12 +3400,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D45" s="31" t="inlineStr">
+      <c r="D45" s="32" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E45" s="31" t="inlineStr">
+      <c r="E45" s="32" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -3414,12 +3420,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H45" s="31" t="inlineStr">
+      <c r="H45" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I45" s="31" t="inlineStr">
+      <c r="I45" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3434,20 +3440,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L45" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M45" s="31" t="inlineStr"/>
+      <c r="L45" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M45" s="32" t="inlineStr"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="30" t="inlineStr">
+      <c r="A46" s="33" t="inlineStr">
         <is>
           <t>4409726429</t>
         </is>
       </c>
-      <c r="B46" s="30" t="inlineStr">
+      <c r="B46" s="33" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3457,12 +3463,12 @@
           <t>Data Science Intern</t>
         </is>
       </c>
-      <c r="D46" s="30" t="inlineStr">
+      <c r="D46" s="33" t="inlineStr">
         <is>
           <t>Rundoo</t>
         </is>
       </c>
-      <c r="E46" s="30" t="inlineStr">
+      <c r="E46" s="33" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3477,12 +3483,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H46" s="30" t="inlineStr">
+      <c r="H46" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I46" s="30" t="inlineStr">
+      <c r="I46" s="33" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3497,20 +3503,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L46" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M46" s="30" t="inlineStr"/>
+      <c r="L46" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M46" s="33" t="inlineStr"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="31" t="inlineStr">
+      <c r="A47" s="32" t="inlineStr">
         <is>
           <t>4305671729</t>
         </is>
       </c>
-      <c r="B47" s="31" t="inlineStr">
+      <c r="B47" s="32" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3520,12 +3526,12 @@
           <t>DoD SkillBridge Internship/Fellowship Opportunity Application (U.S. Military Only)</t>
         </is>
       </c>
-      <c r="D47" s="31" t="inlineStr">
+      <c r="D47" s="32" t="inlineStr">
         <is>
           <t>Onsights</t>
         </is>
       </c>
-      <c r="E47" s="31" t="inlineStr">
+      <c r="E47" s="32" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -3540,12 +3546,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H47" s="31" t="inlineStr">
+      <c r="H47" s="32" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I47" s="31" t="inlineStr">
+      <c r="I47" s="32" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3560,20 +3566,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L47" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M47" s="31" t="inlineStr"/>
+      <c r="L47" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M47" s="32" t="inlineStr"/>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="30" t="inlineStr">
+      <c r="A48" s="33" t="inlineStr">
         <is>
           <t>4414096220</t>
         </is>
       </c>
-      <c r="B48" s="30" t="inlineStr">
+      <c r="B48" s="33" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3583,12 +3589,12 @@
           <t>Visualization Engineer Intern</t>
         </is>
       </c>
-      <c r="D48" s="30" t="inlineStr">
+      <c r="D48" s="33" t="inlineStr">
         <is>
           <t>Leidos</t>
         </is>
       </c>
-      <c r="E48" s="30" t="inlineStr">
+      <c r="E48" s="33" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3603,12 +3609,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H48" s="30" t="inlineStr">
+      <c r="H48" s="33" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="I48" s="30" t="inlineStr">
+      <c r="I48" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3623,20 +3629,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L48" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M48" s="30" t="inlineStr"/>
+      <c r="L48" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M48" s="33" t="inlineStr"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="31" t="inlineStr">
+      <c r="A49" s="32" t="inlineStr">
         <is>
           <t>4361076044</t>
         </is>
       </c>
-      <c r="B49" s="31" t="inlineStr">
+      <c r="B49" s="32" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3646,12 +3652,12 @@
           <t>GenAI Engineering Intern  - SkillBridge (Remote)</t>
         </is>
       </c>
-      <c r="D49" s="31" t="inlineStr">
+      <c r="D49" s="32" t="inlineStr">
         <is>
           <t>CrowdStrike</t>
         </is>
       </c>
-      <c r="E49" s="31" t="inlineStr">
+      <c r="E49" s="32" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3666,12 +3672,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H49" s="31" t="inlineStr">
+      <c r="H49" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I49" s="31" t="inlineStr">
+      <c r="I49" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3686,20 +3692,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L49" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M49" s="31" t="inlineStr"/>
+      <c r="L49" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M49" s="32" t="inlineStr"/>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="30" t="inlineStr">
+      <c r="A50" s="33" t="inlineStr">
         <is>
           <t>4417553585</t>
         </is>
       </c>
-      <c r="B50" s="30" t="inlineStr">
+      <c r="B50" s="33" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3709,12 +3715,12 @@
           <t>Entry-Level Software Engineer | Remote</t>
         </is>
       </c>
-      <c r="D50" s="30" t="inlineStr">
+      <c r="D50" s="33" t="inlineStr">
         <is>
           <t>Crossing Hurdles</t>
         </is>
       </c>
-      <c r="E50" s="30" t="inlineStr">
+      <c r="E50" s="33" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3729,12 +3735,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H50" s="30" t="inlineStr">
+      <c r="H50" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I50" s="30" t="inlineStr">
+      <c r="I50" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3749,20 +3755,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L50" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M50" s="30" t="inlineStr"/>
+      <c r="L50" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M50" s="33" t="inlineStr"/>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="31" t="inlineStr">
+      <c r="A51" s="32" t="inlineStr">
         <is>
           <t>4309699451</t>
         </is>
       </c>
-      <c r="B51" s="31" t="inlineStr">
+      <c r="B51" s="32" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3772,12 +3778,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D51" s="31" t="inlineStr">
+      <c r="D51" s="32" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E51" s="31" t="inlineStr">
+      <c r="E51" s="32" t="inlineStr">
         <is>
           <t>Washington, United States</t>
         </is>
@@ -3792,12 +3798,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H51" s="31" t="inlineStr">
+      <c r="H51" s="32" t="inlineStr">
         <is>
           <t>109</t>
         </is>
       </c>
-      <c r="I51" s="31" t="inlineStr">
+      <c r="I51" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3812,20 +3818,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L51" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M51" s="31" t="inlineStr"/>
+      <c r="L51" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M51" s="32" t="inlineStr"/>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="30" t="inlineStr">
+      <c r="A52" s="33" t="inlineStr">
         <is>
           <t>4406945262</t>
         </is>
       </c>
-      <c r="B52" s="30" t="inlineStr">
+      <c r="B52" s="33" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3835,12 +3841,12 @@
           <t>DevSecOps Intern</t>
         </is>
       </c>
-      <c r="D52" s="30" t="inlineStr">
+      <c r="D52" s="33" t="inlineStr">
         <is>
           <t>Modern Technology Solutions, Inc. (MTSI)</t>
         </is>
       </c>
-      <c r="E52" s="30" t="inlineStr">
+      <c r="E52" s="33" t="inlineStr">
         <is>
           <t>Niceville, FL</t>
         </is>
@@ -3855,12 +3861,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H52" s="30" t="inlineStr">
+      <c r="H52" s="33" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="I52" s="30" t="inlineStr">
+      <c r="I52" s="33" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3875,20 +3881,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L52" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M52" s="30" t="inlineStr"/>
+      <c r="L52" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M52" s="33" t="inlineStr"/>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="31" t="inlineStr">
+      <c r="A53" s="32" t="inlineStr">
         <is>
           <t>4407937810</t>
         </is>
       </c>
-      <c r="B53" s="31" t="inlineStr">
+      <c r="B53" s="32" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3898,12 +3904,12 @@
           <t>Temporary Intern - Agentic AI &amp; Neural-Symbolic Systems (Healthcare)</t>
         </is>
       </c>
-      <c r="D53" s="31" t="inlineStr">
+      <c r="D53" s="32" t="inlineStr">
         <is>
           <t>Cotiviti</t>
         </is>
       </c>
-      <c r="E53" s="31" t="inlineStr">
+      <c r="E53" s="32" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3918,12 +3924,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H53" s="31" t="inlineStr">
+      <c r="H53" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I53" s="31" t="inlineStr">
+      <c r="I53" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3938,20 +3944,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L53" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M53" s="31" t="inlineStr"/>
+      <c r="L53" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M53" s="32" t="inlineStr"/>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="30" t="inlineStr">
+      <c r="A54" s="33" t="inlineStr">
         <is>
           <t>4414089997</t>
         </is>
       </c>
-      <c r="B54" s="30" t="inlineStr">
+      <c r="B54" s="33" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3961,12 +3967,12 @@
           <t>Visualization Engineer Intern</t>
         </is>
       </c>
-      <c r="D54" s="30" t="inlineStr">
+      <c r="D54" s="33" t="inlineStr">
         <is>
           <t>Leidos</t>
         </is>
       </c>
-      <c r="E54" s="30" t="inlineStr">
+      <c r="E54" s="33" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3981,12 +3987,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H54" s="30" t="inlineStr">
+      <c r="H54" s="33" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="I54" s="30" t="inlineStr">
+      <c r="I54" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4001,20 +4007,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L54" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M54" s="30" t="inlineStr"/>
+      <c r="L54" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M54" s="33" t="inlineStr"/>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="31" t="inlineStr">
+      <c r="A55" s="32" t="inlineStr">
         <is>
           <t>4387443129</t>
         </is>
       </c>
-      <c r="B55" s="31" t="inlineStr">
+      <c r="B55" s="32" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4024,12 +4030,12 @@
           <t>2026 Interns</t>
         </is>
       </c>
-      <c r="D55" s="31" t="inlineStr">
+      <c r="D55" s="32" t="inlineStr">
         <is>
           <t>Givelify</t>
         </is>
       </c>
-      <c r="E55" s="31" t="inlineStr">
+      <c r="E55" s="32" t="inlineStr">
         <is>
           <t>Dallas, TX</t>
         </is>
@@ -4044,12 +4050,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H55" s="31" t="inlineStr">
+      <c r="H55" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I55" s="31" t="inlineStr">
+      <c r="I55" s="32" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -4064,20 +4070,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L55" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M55" s="31" t="inlineStr"/>
+      <c r="L55" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M55" s="32" t="inlineStr"/>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="30" t="inlineStr">
+      <c r="A56" s="33" t="inlineStr">
         <is>
           <t>4337980765</t>
         </is>
       </c>
-      <c r="B56" s="30" t="inlineStr">
+      <c r="B56" s="33" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4087,12 +4093,12 @@
           <t>Submitting for a General Internship Application</t>
         </is>
       </c>
-      <c r="D56" s="30" t="inlineStr">
+      <c r="D56" s="33" t="inlineStr">
         <is>
           <t>Chainguard</t>
         </is>
       </c>
-      <c r="E56" s="30" t="inlineStr">
+      <c r="E56" s="33" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4107,12 +4113,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H56" s="30" t="inlineStr">
+      <c r="H56" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I56" s="30" t="inlineStr">
+      <c r="I56" s="33" t="inlineStr">
         <is>
           <t>Volunteer</t>
         </is>
@@ -4127,20 +4133,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L56" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M56" s="30" t="inlineStr"/>
+      <c r="L56" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M56" s="33" t="inlineStr"/>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="31" t="inlineStr">
+      <c r="A57" s="32" t="inlineStr">
         <is>
           <t>4417030460</t>
         </is>
       </c>
-      <c r="B57" s="31" t="inlineStr">
+      <c r="B57" s="32" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4150,12 +4156,12 @@
           <t>AI Researcher Intern</t>
         </is>
       </c>
-      <c r="D57" s="31" t="inlineStr">
+      <c r="D57" s="32" t="inlineStr">
         <is>
           <t>BioSpace</t>
         </is>
       </c>
-      <c r="E57" s="31" t="inlineStr">
+      <c r="E57" s="32" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4170,12 +4176,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H57" s="31" t="inlineStr">
+      <c r="H57" s="32" t="inlineStr">
         <is>
           <t>151</t>
         </is>
       </c>
-      <c r="I57" s="31" t="inlineStr">
+      <c r="I57" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4190,20 +4196,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L57" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M57" s="31" t="inlineStr"/>
+      <c r="L57" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M57" s="32" t="inlineStr"/>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="30" t="inlineStr">
+      <c r="A58" s="33" t="inlineStr">
         <is>
           <t>4406930916</t>
         </is>
       </c>
-      <c r="B58" s="30" t="inlineStr">
+      <c r="B58" s="33" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4213,12 +4219,12 @@
           <t>DevSecOps Intern</t>
         </is>
       </c>
-      <c r="D58" s="30" t="inlineStr">
+      <c r="D58" s="33" t="inlineStr">
         <is>
           <t>Modern Technology Solutions, Inc. (MTSI)</t>
         </is>
       </c>
-      <c r="E58" s="30" t="inlineStr">
+      <c r="E58" s="33" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4233,12 +4239,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H58" s="30" t="inlineStr">
+      <c r="H58" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I58" s="30" t="inlineStr">
+      <c r="I58" s="33" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -4253,20 +4259,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L58" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M58" s="30" t="inlineStr"/>
+      <c r="L58" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M58" s="33" t="inlineStr"/>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="31" t="inlineStr">
+      <c r="A59" s="32" t="inlineStr">
         <is>
           <t>4385798937</t>
         </is>
       </c>
-      <c r="B59" s="31" t="inlineStr">
+      <c r="B59" s="32" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4276,12 +4282,12 @@
           <t>Research Intern on Generative and Protective AI for Content Creation</t>
         </is>
       </c>
-      <c r="D59" s="31" t="inlineStr">
+      <c r="D59" s="32" t="inlineStr">
         <is>
           <t>SonyAI</t>
         </is>
       </c>
-      <c r="E59" s="31" t="inlineStr">
+      <c r="E59" s="32" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -4296,12 +4302,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H59" s="31" t="inlineStr">
+      <c r="H59" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I59" s="31" t="inlineStr">
+      <c r="I59" s="32" t="inlineStr">
         <is>
           <t>Part-time</t>
         </is>
@@ -4316,20 +4322,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L59" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M59" s="31" t="inlineStr"/>
+      <c r="L59" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M59" s="32" t="inlineStr"/>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="30" t="inlineStr">
+      <c r="A60" s="33" t="inlineStr">
         <is>
           <t>4414396950</t>
         </is>
       </c>
-      <c r="B60" s="30" t="inlineStr">
+      <c r="B60" s="33" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4339,12 +4345,12 @@
           <t>Power Platform Intern</t>
         </is>
       </c>
-      <c r="D60" s="30" t="inlineStr">
+      <c r="D60" s="33" t="inlineStr">
         <is>
           <t>Leidos</t>
         </is>
       </c>
-      <c r="E60" s="30" t="inlineStr">
+      <c r="E60" s="33" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4359,12 +4365,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H60" s="30" t="inlineStr">
+      <c r="H60" s="33" t="inlineStr">
         <is>
           <t>135</t>
         </is>
       </c>
-      <c r="I60" s="30" t="inlineStr">
+      <c r="I60" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4379,20 +4385,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L60" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M60" s="30" t="inlineStr"/>
+      <c r="L60" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M60" s="33" t="inlineStr"/>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="31" t="inlineStr">
+      <c r="A61" s="32" t="inlineStr">
         <is>
           <t>4413699205</t>
         </is>
       </c>
-      <c r="B61" s="31" t="inlineStr">
+      <c r="B61" s="32" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4402,12 +4408,12 @@
           <t>Junior Software Engineer - Automation &amp; Integration</t>
         </is>
       </c>
-      <c r="D61" s="31" t="inlineStr">
+      <c r="D61" s="32" t="inlineStr">
         <is>
           <t>Fletcher Development LLC</t>
         </is>
       </c>
-      <c r="E61" s="31" t="inlineStr">
+      <c r="E61" s="32" t="inlineStr">
         <is>
           <t>Redding, CT</t>
         </is>
@@ -4422,12 +4428,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H61" s="31" t="inlineStr">
+      <c r="H61" s="32" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="I61" s="31" t="inlineStr">
+      <c r="I61" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4442,20 +4448,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L61" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M61" s="31" t="inlineStr"/>
+      <c r="L61" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M61" s="32" t="inlineStr"/>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="30" t="inlineStr">
+      <c r="A62" s="33" t="inlineStr">
         <is>
           <t>4416171988</t>
         </is>
       </c>
-      <c r="B62" s="30" t="inlineStr">
+      <c r="B62" s="33" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4465,12 +4471,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D62" s="30" t="inlineStr">
+      <c r="D62" s="33" t="inlineStr">
         <is>
           <t>Altec</t>
         </is>
       </c>
-      <c r="E62" s="30" t="inlineStr">
+      <c r="E62" s="33" t="inlineStr">
         <is>
           <t>Birmingham, AL</t>
         </is>
@@ -4485,12 +4491,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H62" s="30" t="inlineStr">
+      <c r="H62" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I62" s="30" t="inlineStr">
+      <c r="I62" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4505,20 +4511,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L62" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M62" s="30" t="inlineStr"/>
+      <c r="L62" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M62" s="33" t="inlineStr"/>
     </row>
     <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="31" t="inlineStr">
+      <c r="A63" s="32" t="inlineStr">
         <is>
           <t>4403444963</t>
         </is>
       </c>
-      <c r="B63" s="31" t="inlineStr">
+      <c r="B63" s="32" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4528,12 +4534,12 @@
           <t>Junior Applications Developer (NY HELPS) #2026-252</t>
         </is>
       </c>
-      <c r="D63" s="31" t="inlineStr">
+      <c r="D63" s="32" t="inlineStr">
         <is>
           <t>Capital Region BOCES</t>
         </is>
       </c>
-      <c r="E63" s="31" t="inlineStr">
+      <c r="E63" s="32" t="inlineStr">
         <is>
           <t>Albany, NY</t>
         </is>
@@ -4548,12 +4554,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H63" s="31" t="inlineStr">
+      <c r="H63" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I63" s="31" t="inlineStr">
+      <c r="I63" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4568,20 +4574,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L63" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M63" s="31" t="inlineStr"/>
+      <c r="L63" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M63" s="32" t="inlineStr"/>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="30" t="inlineStr">
+      <c r="A64" s="33" t="inlineStr">
         <is>
           <t>4418506121</t>
         </is>
       </c>
-      <c r="B64" s="30" t="inlineStr">
+      <c r="B64" s="33" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4591,12 +4597,12 @@
           <t>Core System Junior Developer</t>
         </is>
       </c>
-      <c r="D64" s="30" t="inlineStr">
+      <c r="D64" s="33" t="inlineStr">
         <is>
           <t>Cyprus Federal Credit Union</t>
         </is>
       </c>
-      <c r="E64" s="30" t="inlineStr">
+      <c r="E64" s="33" t="inlineStr">
         <is>
           <t>West Jordan, UT</t>
         </is>
@@ -4611,12 +4617,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H64" s="30" t="inlineStr">
+      <c r="H64" s="33" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="I64" s="30" t="inlineStr">
+      <c r="I64" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4631,20 +4637,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L64" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M64" s="30" t="inlineStr"/>
+      <c r="L64" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M64" s="33" t="inlineStr"/>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="31" t="inlineStr">
+      <c r="A65" s="32" t="inlineStr">
         <is>
           <t>4413905706</t>
         </is>
       </c>
-      <c r="B65" s="31" t="inlineStr">
+      <c r="B65" s="32" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4654,12 +4660,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D65" s="31" t="inlineStr">
+      <c r="D65" s="32" t="inlineStr">
         <is>
           <t>Arnex Solutions LLC</t>
         </is>
       </c>
-      <c r="E65" s="31" t="inlineStr">
+      <c r="E65" s="32" t="inlineStr">
         <is>
           <t>Princeton, NJ</t>
         </is>
@@ -4674,12 +4680,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H65" s="31" t="inlineStr">
+      <c r="H65" s="32" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I65" s="31" t="inlineStr">
+      <c r="I65" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4694,20 +4700,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L65" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M65" s="31" t="inlineStr"/>
+      <c r="L65" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M65" s="32" t="inlineStr"/>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="30" t="inlineStr">
+      <c r="A66" s="33" t="inlineStr">
         <is>
           <t>4418963446</t>
         </is>
       </c>
-      <c r="B66" s="30" t="inlineStr">
+      <c r="B66" s="33" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4717,12 +4723,12 @@
           <t>Junior Software Engineer - Automation &amp; Integration</t>
         </is>
       </c>
-      <c r="D66" s="30" t="inlineStr">
+      <c r="D66" s="33" t="inlineStr">
         <is>
           <t>Vibrant Building Technologies</t>
         </is>
       </c>
-      <c r="E66" s="30" t="inlineStr">
+      <c r="E66" s="33" t="inlineStr">
         <is>
           <t>Ridgefield, CT</t>
         </is>
@@ -4737,12 +4743,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H66" s="30" t="inlineStr">
+      <c r="H66" s="33" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="I66" s="30" t="inlineStr">
+      <c r="I66" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4757,20 +4763,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L66" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M66" s="30" t="inlineStr"/>
+      <c r="L66" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M66" s="33" t="inlineStr"/>
     </row>
     <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="31" t="inlineStr">
+      <c r="A67" s="32" t="inlineStr">
         <is>
           <t>4413759052</t>
         </is>
       </c>
-      <c r="B67" s="31" t="inlineStr">
+      <c r="B67" s="32" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4780,12 +4786,12 @@
           <t>Junior Full Stack Developer</t>
         </is>
       </c>
-      <c r="D67" s="31" t="inlineStr">
+      <c r="D67" s="32" t="inlineStr">
         <is>
           <t>Allied World Reinsurance Company</t>
         </is>
       </c>
-      <c r="E67" s="31" t="inlineStr">
+      <c r="E67" s="32" t="inlineStr">
         <is>
           <t>Iselin, NJ</t>
         </is>
@@ -4800,12 +4806,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H67" s="31" t="inlineStr">
+      <c r="H67" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I67" s="31" t="inlineStr">
+      <c r="I67" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4820,20 +4826,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L67" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M67" s="31" t="inlineStr"/>
+      <c r="L67" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M67" s="32" t="inlineStr"/>
     </row>
     <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="30" t="inlineStr">
+      <c r="A68" s="33" t="inlineStr">
         <is>
           <t>4417542502</t>
         </is>
       </c>
-      <c r="B68" s="30" t="inlineStr">
+      <c r="B68" s="33" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4843,12 +4849,12 @@
           <t>Junior Developer</t>
         </is>
       </c>
-      <c r="D68" s="30" t="inlineStr">
+      <c r="D68" s="33" t="inlineStr">
         <is>
           <t>CloudMasonry</t>
         </is>
       </c>
-      <c r="E68" s="30" t="inlineStr">
+      <c r="E68" s="33" t="inlineStr">
         <is>
           <t>Indianapolis, IN</t>
         </is>
@@ -4863,12 +4869,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H68" s="30" t="inlineStr">
+      <c r="H68" s="33" t="inlineStr">
         <is>
           <t>154</t>
         </is>
       </c>
-      <c r="I68" s="30" t="inlineStr">
+      <c r="I68" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4883,20 +4889,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L68" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M68" s="30" t="inlineStr"/>
+      <c r="L68" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M68" s="33" t="inlineStr"/>
     </row>
     <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="31" t="inlineStr">
+      <c r="A69" s="32" t="inlineStr">
         <is>
           <t>4374856035</t>
         </is>
       </c>
-      <c r="B69" s="31" t="inlineStr">
+      <c r="B69" s="32" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4906,12 +4912,12 @@
           <t>Programmer II</t>
         </is>
       </c>
-      <c r="D69" s="31" t="inlineStr">
+      <c r="D69" s="32" t="inlineStr">
         <is>
           <t>Willis Knighton Health</t>
         </is>
       </c>
-      <c r="E69" s="31" t="inlineStr">
+      <c r="E69" s="32" t="inlineStr">
         <is>
           <t>Louisiana, United States</t>
         </is>
@@ -4926,12 +4932,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H69" s="31" t="inlineStr">
+      <c r="H69" s="32" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="I69" s="31" t="inlineStr">
+      <c r="I69" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4946,20 +4952,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L69" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M69" s="31" t="inlineStr"/>
+      <c r="L69" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M69" s="32" t="inlineStr"/>
     </row>
     <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="30" t="inlineStr">
+      <c r="A70" s="33" t="inlineStr">
         <is>
           <t>4416302564</t>
         </is>
       </c>
-      <c r="B70" s="30" t="inlineStr">
+      <c r="B70" s="33" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4969,12 +4975,12 @@
           <t>Software Engineer I</t>
         </is>
       </c>
-      <c r="D70" s="30" t="inlineStr">
+      <c r="D70" s="33" t="inlineStr">
         <is>
           <t>American Express</t>
         </is>
       </c>
-      <c r="E70" s="30" t="inlineStr">
+      <c r="E70" s="33" t="inlineStr">
         <is>
           <t>Sunrise, FL</t>
         </is>
@@ -4989,12 +4995,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H70" s="30" t="inlineStr">
+      <c r="H70" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I70" s="30" t="inlineStr">
+      <c r="I70" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5009,20 +5015,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr"/>
+      <c r="L70" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M70" s="33" t="inlineStr"/>
     </row>
     <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="31" t="inlineStr">
+      <c r="A71" s="32" t="inlineStr">
         <is>
           <t>4417014137</t>
         </is>
       </c>
-      <c r="B71" s="31" t="inlineStr">
+      <c r="B71" s="32" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5032,12 +5038,12 @@
           <t>Junior Software Developer, Applications</t>
         </is>
       </c>
-      <c r="D71" s="31" t="inlineStr">
+      <c r="D71" s="32" t="inlineStr">
         <is>
           <t>ECS</t>
         </is>
       </c>
-      <c r="E71" s="31" t="inlineStr">
+      <c r="E71" s="32" t="inlineStr">
         <is>
           <t>O'Fallon, IL</t>
         </is>
@@ -5052,12 +5058,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H71" s="31" t="inlineStr">
+      <c r="H71" s="32" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="I71" s="31" t="inlineStr">
+      <c r="I71" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5072,20 +5078,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L71" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M71" s="31" t="inlineStr"/>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr"/>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="30" t="inlineStr">
+      <c r="A72" s="33" t="inlineStr">
         <is>
           <t>4381211472</t>
         </is>
       </c>
-      <c r="B72" s="30" t="inlineStr">
+      <c r="B72" s="33" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5095,12 +5101,12 @@
           <t>Programmer</t>
         </is>
       </c>
-      <c r="D72" s="30" t="inlineStr">
+      <c r="D72" s="33" t="inlineStr">
         <is>
           <t>City of New York</t>
         </is>
       </c>
-      <c r="E72" s="30" t="inlineStr">
+      <c r="E72" s="33" t="inlineStr">
         <is>
           <t>Bronx, NY</t>
         </is>
@@ -5115,12 +5121,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H72" s="30" t="inlineStr">
+      <c r="H72" s="33" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="I72" s="30" t="inlineStr">
+      <c r="I72" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5135,20 +5141,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L72" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M72" s="30" t="inlineStr"/>
+      <c r="L72" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M72" s="33" t="inlineStr"/>
     </row>
     <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="31" t="inlineStr">
+      <c r="A73" s="32" t="inlineStr">
         <is>
           <t>4168416236</t>
         </is>
       </c>
-      <c r="B73" s="31" t="inlineStr">
+      <c r="B73" s="32" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5158,12 +5164,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D73" s="31" t="inlineStr">
+      <c r="D73" s="32" t="inlineStr">
         <is>
           <t>Interclypse</t>
         </is>
       </c>
-      <c r="E73" s="31" t="inlineStr">
+      <c r="E73" s="32" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
@@ -5178,12 +5184,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H73" s="31" t="inlineStr">
+      <c r="H73" s="32" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I73" s="31" t="inlineStr">
+      <c r="I73" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5198,20 +5204,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L73" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M73" s="31" t="inlineStr"/>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr"/>
     </row>
     <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="30" t="inlineStr">
+      <c r="A74" s="33" t="inlineStr">
         <is>
           <t>4403507357</t>
         </is>
       </c>
-      <c r="B74" s="30" t="inlineStr">
+      <c r="B74" s="33" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5221,12 +5227,12 @@
           <t>Software Developer:</t>
         </is>
       </c>
-      <c r="D74" s="30" t="inlineStr">
+      <c r="D74" s="33" t="inlineStr">
         <is>
           <t>IQuest Solutions Corporation</t>
         </is>
       </c>
-      <c r="E74" s="30" t="inlineStr">
+      <c r="E74" s="33" t="inlineStr">
         <is>
           <t>Plano, TX</t>
         </is>
@@ -5241,12 +5247,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H74" s="30" t="inlineStr">
+      <c r="H74" s="33" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I74" s="30" t="inlineStr">
+      <c r="I74" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5261,20 +5267,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L74" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M74" s="30" t="inlineStr"/>
+      <c r="L74" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M74" s="33" t="inlineStr"/>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="31" t="inlineStr">
+      <c r="A75" s="32" t="inlineStr">
         <is>
           <t>4309800238</t>
         </is>
       </c>
-      <c r="B75" s="31" t="inlineStr">
+      <c r="B75" s="32" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5284,12 +5290,12 @@
           <t>Backend Software Engineer</t>
         </is>
       </c>
-      <c r="D75" s="31" t="inlineStr">
+      <c r="D75" s="32" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E75" s="31" t="inlineStr">
+      <c r="E75" s="32" t="inlineStr">
         <is>
           <t>Texas, United States</t>
         </is>
@@ -5304,12 +5310,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H75" s="31" t="inlineStr">
+      <c r="H75" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I75" s="31" t="inlineStr">
+      <c r="I75" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5324,20 +5330,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L75" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M75" s="31" t="inlineStr"/>
+      <c r="L75" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M75" s="32" t="inlineStr"/>
     </row>
     <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="30" t="inlineStr">
+      <c r="A76" s="33" t="inlineStr">
         <is>
           <t>4404109089</t>
         </is>
       </c>
-      <c r="B76" s="30" t="inlineStr">
+      <c r="B76" s="33" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5347,12 +5353,12 @@
           <t>Software Development Engineer I</t>
         </is>
       </c>
-      <c r="D76" s="30" t="inlineStr">
+      <c r="D76" s="33" t="inlineStr">
         <is>
           <t>GM Financial</t>
         </is>
       </c>
-      <c r="E76" s="30" t="inlineStr">
+      <c r="E76" s="33" t="inlineStr">
         <is>
           <t>Arlington, TX</t>
         </is>
@@ -5367,12 +5373,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H76" s="30" t="inlineStr">
+      <c r="H76" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I76" s="30" t="inlineStr">
+      <c r="I76" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5387,20 +5393,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L76" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M76" s="30" t="inlineStr"/>
+      <c r="L76" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M76" s="33" t="inlineStr"/>
     </row>
     <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="31" t="inlineStr">
+      <c r="A77" s="32" t="inlineStr">
         <is>
           <t>3986116411</t>
         </is>
       </c>
-      <c r="B77" s="31" t="inlineStr">
+      <c r="B77" s="32" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5410,12 +5416,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D77" s="31" t="inlineStr">
+      <c r="D77" s="32" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E77" s="31" t="inlineStr">
+      <c r="E77" s="32" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -5430,12 +5436,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H77" s="31" t="inlineStr">
+      <c r="H77" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I77" s="31" t="inlineStr">
+      <c r="I77" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5450,20 +5456,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L77" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M77" s="31" t="inlineStr"/>
+      <c r="L77" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M77" s="32" t="inlineStr"/>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="30" t="inlineStr">
+      <c r="A78" s="33" t="inlineStr">
         <is>
           <t>4418051524</t>
         </is>
       </c>
-      <c r="B78" s="30" t="inlineStr">
+      <c r="B78" s="33" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5473,12 +5479,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D78" s="30" t="inlineStr">
+      <c r="D78" s="33" t="inlineStr">
         <is>
           <t>Relativity</t>
         </is>
       </c>
-      <c r="E78" s="30" t="inlineStr">
+      <c r="E78" s="33" t="inlineStr">
         <is>
           <t>Texas, United States</t>
         </is>
@@ -5493,12 +5499,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H78" s="30" t="inlineStr">
+      <c r="H78" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I78" s="30" t="inlineStr">
+      <c r="I78" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5513,20 +5519,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L78" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M78" s="30" t="inlineStr"/>
+      <c r="L78" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M78" s="33" t="inlineStr"/>
     </row>
     <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="31" t="inlineStr">
+      <c r="A79" s="32" t="inlineStr">
         <is>
           <t>4409856693</t>
         </is>
       </c>
-      <c r="B79" s="31" t="inlineStr">
+      <c r="B79" s="32" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5536,12 +5542,12 @@
           <t>Software Engineer - Payments</t>
         </is>
       </c>
-      <c r="D79" s="31" t="inlineStr">
+      <c r="D79" s="32" t="inlineStr">
         <is>
           <t>Cloudbeds</t>
         </is>
       </c>
-      <c r="E79" s="31" t="inlineStr">
+      <c r="E79" s="32" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -5556,12 +5562,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H79" s="31" t="inlineStr">
+      <c r="H79" s="32" t="inlineStr">
         <is>
           <t>177</t>
         </is>
       </c>
-      <c r="I79" s="31" t="inlineStr">
+      <c r="I79" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5576,20 +5582,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L79" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M79" s="31" t="inlineStr"/>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr"/>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="30" t="inlineStr">
+      <c r="A80" s="33" t="inlineStr">
         <is>
           <t>3986111771</t>
         </is>
       </c>
-      <c r="B80" s="30" t="inlineStr">
+      <c r="B80" s="33" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5599,12 +5605,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D80" s="30" t="inlineStr">
+      <c r="D80" s="33" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E80" s="30" t="inlineStr">
+      <c r="E80" s="33" t="inlineStr">
         <is>
           <t>Carrollton, TX</t>
         </is>
@@ -5619,12 +5625,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H80" s="30" t="inlineStr">
+      <c r="H80" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I80" s="30" t="inlineStr">
+      <c r="I80" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5639,20 +5645,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L80" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M80" s="30" t="inlineStr"/>
+      <c r="L80" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M80" s="33" t="inlineStr"/>
     </row>
     <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="31" t="inlineStr">
+      <c r="A81" s="32" t="inlineStr">
         <is>
           <t>4417160720</t>
         </is>
       </c>
-      <c r="B81" s="31" t="inlineStr">
+      <c r="B81" s="32" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5662,12 +5668,12 @@
           <t>Full-Stack AI Developer</t>
         </is>
       </c>
-      <c r="D81" s="31" t="inlineStr">
+      <c r="D81" s="32" t="inlineStr">
         <is>
           <t>AnswerMyQ</t>
         </is>
       </c>
-      <c r="E81" s="31" t="inlineStr">
+      <c r="E81" s="32" t="inlineStr">
         <is>
           <t>Austin, Texas Metropolitan Area</t>
         </is>
@@ -5682,12 +5688,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H81" s="31" t="inlineStr">
+      <c r="H81" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I81" s="31" t="inlineStr">
+      <c r="I81" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5702,20 +5708,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L81" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M81" s="31" t="inlineStr"/>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr"/>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="30" t="inlineStr">
+      <c r="A82" s="33" t="inlineStr">
         <is>
           <t>4418507307</t>
         </is>
       </c>
-      <c r="B82" s="30" t="inlineStr">
+      <c r="B82" s="33" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -5725,12 +5731,12 @@
           <t>Entry Level Software Engineer Intern</t>
         </is>
       </c>
-      <c r="D82" s="30" t="inlineStr">
+      <c r="D82" s="33" t="inlineStr">
         <is>
           <t>CORMAC</t>
         </is>
       </c>
-      <c r="E82" s="30" t="inlineStr">
+      <c r="E82" s="33" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -5745,12 +5751,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H82" s="30" t="inlineStr">
+      <c r="H82" s="33" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="I82" s="30" t="inlineStr">
+      <c r="I82" s="33" t="inlineStr">
         <is>
           <t>Volunteer</t>
         </is>
@@ -5765,20 +5771,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L82" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M82" s="30" t="inlineStr"/>
+      <c r="L82" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M82" s="33" t="inlineStr"/>
     </row>
     <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="31" t="inlineStr">
+      <c r="A83" s="32" t="inlineStr">
         <is>
           <t>4413360938</t>
         </is>
       </c>
-      <c r="B83" s="31" t="inlineStr">
+      <c r="B83" s="32" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -5788,12 +5794,12 @@
           <t>Software Engineer Internship (Remote)</t>
         </is>
       </c>
-      <c r="D83" s="31" t="inlineStr">
+      <c r="D83" s="32" t="inlineStr">
         <is>
           <t>Orange Trail</t>
         </is>
       </c>
-      <c r="E83" s="31" t="inlineStr">
+      <c r="E83" s="32" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -5808,12 +5814,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H83" s="31" t="inlineStr">
+      <c r="H83" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I83" s="31" t="inlineStr">
+      <c r="I83" s="32" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -5828,20 +5834,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L83" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M83" s="31" t="inlineStr"/>
+      <c r="L83" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M83" s="32" t="inlineStr"/>
     </row>
     <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="30" t="inlineStr">
+      <c r="A84" s="33" t="inlineStr">
         <is>
           <t>4348111641</t>
         </is>
       </c>
-      <c r="B84" s="30" t="inlineStr">
+      <c r="B84" s="33" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -5851,12 +5857,12 @@
           <t>Software Engineer Intern</t>
         </is>
       </c>
-      <c r="D84" s="30" t="inlineStr">
+      <c r="D84" s="33" t="inlineStr">
         <is>
           <t>Simular</t>
         </is>
       </c>
-      <c r="E84" s="30" t="inlineStr">
+      <c r="E84" s="33" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -5871,12 +5877,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H84" s="30" t="inlineStr">
+      <c r="H84" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I84" s="30" t="inlineStr">
+      <c r="I84" s="33" t="inlineStr">
         <is>
           <t>Volunteer</t>
         </is>
@@ -5891,20 +5897,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L84" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M84" s="30" t="inlineStr"/>
+      <c r="L84" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M84" s="33" t="inlineStr"/>
     </row>
     <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="31" t="inlineStr">
+      <c r="A85" s="32" t="inlineStr">
         <is>
           <t>4411853543</t>
         </is>
       </c>
-      <c r="B85" s="31" t="inlineStr">
+      <c r="B85" s="32" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -5914,12 +5920,12 @@
           <t>Intern, Software Engineer</t>
         </is>
       </c>
-      <c r="D85" s="31" t="inlineStr">
+      <c r="D85" s="32" t="inlineStr">
         <is>
           <t>Accelerate Learning</t>
         </is>
       </c>
-      <c r="E85" s="31" t="inlineStr">
+      <c r="E85" s="32" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -5934,12 +5940,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H85" s="31" t="inlineStr">
+      <c r="H85" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I85" s="31" t="inlineStr">
+      <c r="I85" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5954,20 +5960,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L85" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M85" s="31" t="inlineStr"/>
+      <c r="L85" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M85" s="32" t="inlineStr"/>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="30" t="inlineStr">
+      <c r="A86" s="33" t="inlineStr">
         <is>
           <t>4408586245</t>
         </is>
       </c>
-      <c r="B86" s="30" t="inlineStr">
+      <c r="B86" s="33" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -5977,12 +5983,12 @@
           <t>Junior Software Engineer Intern</t>
         </is>
       </c>
-      <c r="D86" s="30" t="inlineStr">
+      <c r="D86" s="33" t="inlineStr">
         <is>
           <t>Cantaloupe Inc</t>
         </is>
       </c>
-      <c r="E86" s="30" t="inlineStr">
+      <c r="E86" s="33" t="inlineStr">
         <is>
           <t>Atlanta, GA</t>
         </is>
@@ -5997,12 +6003,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H86" s="30" t="inlineStr">
+      <c r="H86" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I86" s="30" t="inlineStr">
+      <c r="I86" s="33" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -6017,20 +6023,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L86" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M86" s="30" t="inlineStr"/>
+      <c r="L86" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M86" s="33" t="inlineStr"/>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="31" t="inlineStr">
+      <c r="A87" s="32" t="inlineStr">
         <is>
           <t>4364536992</t>
         </is>
       </c>
-      <c r="B87" s="31" t="inlineStr">
+      <c r="B87" s="32" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -6040,12 +6046,12 @@
           <t>Summer Internship - Measurement, Research and Development - Academic Measurement</t>
         </is>
       </c>
-      <c r="D87" s="31" t="inlineStr">
+      <c r="D87" s="32" t="inlineStr">
         <is>
           <t>ChatGPT Jobs</t>
         </is>
       </c>
-      <c r="E87" s="31" t="inlineStr">
+      <c r="E87" s="32" t="inlineStr">
         <is>
           <t>Iowa City, IA</t>
         </is>
@@ -6060,12 +6066,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H87" s="31" t="inlineStr">
+      <c r="H87" s="32" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I87" s="31" t="inlineStr">
+      <c r="I87" s="32" t="inlineStr">
         <is>
           <t>Volunteer</t>
         </is>
@@ -6080,20 +6086,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L87" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M87" s="31" t="inlineStr"/>
+      <c r="L87" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M87" s="32" t="inlineStr"/>
     </row>
     <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="30" t="inlineStr">
+      <c r="A88" s="33" t="inlineStr">
         <is>
           <t>4413206045</t>
         </is>
       </c>
-      <c r="B88" s="30" t="inlineStr">
+      <c r="B88" s="33" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6103,12 +6109,12 @@
           <t>Software Development Engineer, EC2 Nitro Specialized Instances</t>
         </is>
       </c>
-      <c r="D88" s="30" t="inlineStr">
+      <c r="D88" s="33" t="inlineStr">
         <is>
           <t>Amazon Web Services (AWS)</t>
         </is>
       </c>
-      <c r="E88" s="30" t="inlineStr">
+      <c r="E88" s="33" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6123,12 +6129,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H88" s="30" t="inlineStr">
+      <c r="H88" s="33" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I88" s="30" t="inlineStr">
+      <c r="I88" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6143,20 +6149,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L88" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M88" s="30" t="inlineStr"/>
+      <c r="L88" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M88" s="33" t="inlineStr"/>
     </row>
     <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="31" t="inlineStr">
+      <c r="A89" s="32" t="inlineStr">
         <is>
           <t>4383211797</t>
         </is>
       </c>
-      <c r="B89" s="31" t="inlineStr">
+      <c r="B89" s="32" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6166,12 +6172,12 @@
           <t>software development engineer</t>
         </is>
       </c>
-      <c r="D89" s="31" t="inlineStr">
+      <c r="D89" s="32" t="inlineStr">
         <is>
           <t>Abacus Business Computer</t>
         </is>
       </c>
-      <c r="E89" s="31" t="inlineStr">
+      <c r="E89" s="32" t="inlineStr">
         <is>
           <t>Queens, NY</t>
         </is>
@@ -6186,12 +6192,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H89" s="31" t="inlineStr">
+      <c r="H89" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I89" s="31" t="inlineStr">
+      <c r="I89" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6206,20 +6212,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L89" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M89" s="31" t="inlineStr"/>
+      <c r="L89" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M89" s="32" t="inlineStr"/>
     </row>
     <row r="90" ht="18" customHeight="1">
-      <c r="A90" s="30" t="inlineStr">
+      <c r="A90" s="33" t="inlineStr">
         <is>
           <t>4418169749</t>
         </is>
       </c>
-      <c r="B90" s="30" t="inlineStr">
+      <c r="B90" s="33" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6229,12 +6235,12 @@
           <t>AI/ML Engineering Intern</t>
         </is>
       </c>
-      <c r="D90" s="30" t="inlineStr">
+      <c r="D90" s="33" t="inlineStr">
         <is>
           <t>Daice Labs</t>
         </is>
       </c>
-      <c r="E90" s="30" t="inlineStr">
+      <c r="E90" s="33" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -6249,12 +6255,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H90" s="30" t="inlineStr">
+      <c r="H90" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I90" s="30" t="inlineStr">
+      <c r="I90" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6269,20 +6275,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L90" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M90" s="30" t="inlineStr"/>
+      <c r="L90" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M90" s="33" t="inlineStr"/>
     </row>
     <row r="91" ht="18" customHeight="1">
-      <c r="A91" s="31" t="inlineStr">
+      <c r="A91" s="32" t="inlineStr">
         <is>
           <t>4281120416</t>
         </is>
       </c>
-      <c r="B91" s="31" t="inlineStr">
+      <c r="B91" s="32" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6292,12 +6298,12 @@
           <t>Site Reliability Engineer Intern (Compute Platform) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D91" s="31" t="inlineStr">
+      <c r="D91" s="32" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E91" s="31" t="inlineStr">
+      <c r="E91" s="32" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6312,12 +6318,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H91" s="31" t="inlineStr">
+      <c r="H91" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I91" s="31" t="inlineStr">
+      <c r="I91" s="32" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -6332,20 +6338,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L91" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M91" s="31" t="inlineStr"/>
+      <c r="L91" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M91" s="32" t="inlineStr"/>
     </row>
     <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="30" t="inlineStr">
+      <c r="A92" s="33" t="inlineStr">
         <is>
           <t>4377549744</t>
         </is>
       </c>
-      <c r="B92" s="30" t="inlineStr">
+      <c r="B92" s="33" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6355,12 +6361,12 @@
           <t>Software Development Engineer Apprentice - Military Veterans</t>
         </is>
       </c>
-      <c r="D92" s="30" t="inlineStr">
+      <c r="D92" s="33" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E92" s="30" t="inlineStr">
+      <c r="E92" s="33" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -6375,12 +6381,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H92" s="30" t="inlineStr">
+      <c r="H92" s="33" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="I92" s="30" t="inlineStr">
+      <c r="I92" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6395,20 +6401,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L92" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M92" s="30" t="inlineStr"/>
+      <c r="L92" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M92" s="33" t="inlineStr"/>
     </row>
     <row r="93" ht="18" customHeight="1">
-      <c r="A93" s="31" t="inlineStr">
+      <c r="A93" s="32" t="inlineStr">
         <is>
           <t>4377564429</t>
         </is>
       </c>
-      <c r="B93" s="31" t="inlineStr">
+      <c r="B93" s="32" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6418,12 +6424,12 @@
           <t>Software Development Engineer Apprentice - Military Veterans</t>
         </is>
       </c>
-      <c r="D93" s="31" t="inlineStr">
+      <c r="D93" s="32" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E93" s="31" t="inlineStr">
+      <c r="E93" s="32" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6438,12 +6444,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H93" s="31" t="inlineStr">
+      <c r="H93" s="32" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="I93" s="31" t="inlineStr">
+      <c r="I93" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6458,20 +6464,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L93" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M93" s="31" t="inlineStr"/>
+      <c r="L93" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M93" s="32" t="inlineStr"/>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="A94" s="30" t="inlineStr">
+      <c r="A94" s="33" t="inlineStr">
         <is>
           <t>4413206046</t>
         </is>
       </c>
-      <c r="B94" s="30" t="inlineStr">
+      <c r="B94" s="33" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6481,12 +6487,12 @@
           <t>Software Development Engineer, Vendor Funding</t>
         </is>
       </c>
-      <c r="D94" s="30" t="inlineStr">
+      <c r="D94" s="33" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E94" s="30" t="inlineStr">
+      <c r="E94" s="33" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6501,12 +6507,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H94" s="30" t="inlineStr">
+      <c r="H94" s="33" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I94" s="30" t="inlineStr">
+      <c r="I94" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6521,20 +6527,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L94" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M94" s="30" t="inlineStr"/>
+      <c r="L94" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M94" s="33" t="inlineStr"/>
     </row>
     <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="31" t="inlineStr">
+      <c r="A95" s="32" t="inlineStr">
         <is>
           <t>4408778227</t>
         </is>
       </c>
-      <c r="B95" s="31" t="inlineStr">
+      <c r="B95" s="32" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6544,12 +6550,12 @@
           <t>Front-End Engineer Fall Internship – 2026 (US)</t>
         </is>
       </c>
-      <c r="D95" s="31" t="inlineStr">
+      <c r="D95" s="32" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E95" s="31" t="inlineStr">
+      <c r="E95" s="32" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6564,12 +6570,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H95" s="31" t="inlineStr">
+      <c r="H95" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I95" s="31" t="inlineStr">
+      <c r="I95" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6584,20 +6590,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L95" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M95" s="31" t="inlineStr"/>
+      <c r="L95" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M95" s="32" t="inlineStr"/>
     </row>
     <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="30" t="inlineStr">
+      <c r="A96" s="33" t="inlineStr">
         <is>
           <t>4281117648</t>
         </is>
       </c>
-      <c r="B96" s="30" t="inlineStr">
+      <c r="B96" s="33" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6607,12 +6613,12 @@
           <t>Data Engineer Intern (E-commerce) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D96" s="30" t="inlineStr">
+      <c r="D96" s="33" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E96" s="30" t="inlineStr">
+      <c r="E96" s="33" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6627,12 +6633,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H96" s="30" t="inlineStr">
+      <c r="H96" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I96" s="30" t="inlineStr">
+      <c r="I96" s="33" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -6647,20 +6653,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L96" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M96" s="30" t="inlineStr"/>
+      <c r="L96" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M96" s="33" t="inlineStr"/>
     </row>
     <row r="97" ht="18" customHeight="1">
-      <c r="A97" s="31" t="inlineStr">
+      <c r="A97" s="32" t="inlineStr">
         <is>
           <t>4407126060</t>
         </is>
       </c>
-      <c r="B97" s="31" t="inlineStr">
+      <c r="B97" s="32" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6670,12 +6676,12 @@
           <t>Site Reliability Engineer Intern (Data Infrastructure) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D97" s="31" t="inlineStr">
+      <c r="D97" s="32" t="inlineStr">
         <is>
           <t>ByteDance</t>
         </is>
       </c>
-      <c r="E97" s="31" t="inlineStr">
+      <c r="E97" s="32" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6690,12 +6696,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H97" s="31" t="inlineStr">
+      <c r="H97" s="32" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="I97" s="31" t="inlineStr">
+      <c r="I97" s="32" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -6710,20 +6716,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L97" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M97" s="31" t="inlineStr"/>
+      <c r="L97" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M97" s="32" t="inlineStr"/>
     </row>
     <row r="98" ht="18" customHeight="1">
-      <c r="A98" s="30" t="inlineStr">
+      <c r="A98" s="33" t="inlineStr">
         <is>
           <t>4392432360</t>
         </is>
       </c>
-      <c r="B98" s="30" t="inlineStr">
+      <c r="B98" s="33" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6733,12 +6739,12 @@
           <t>Software Engineer Intern (AI Model Optimization) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D98" s="30" t="inlineStr">
+      <c r="D98" s="33" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E98" s="30" t="inlineStr">
+      <c r="E98" s="33" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6753,12 +6759,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H98" s="30" t="inlineStr">
+      <c r="H98" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I98" s="30" t="inlineStr">
+      <c r="I98" s="33" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -6773,20 +6779,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L98" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M98" s="30" t="inlineStr"/>
+      <c r="L98" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M98" s="33" t="inlineStr"/>
     </row>
     <row r="99" ht="18" customHeight="1">
-      <c r="A99" s="31" t="inlineStr">
+      <c r="A99" s="32" t="inlineStr">
         <is>
           <t>4341279371</t>
         </is>
       </c>
-      <c r="B99" s="31" t="inlineStr">
+      <c r="B99" s="32" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6796,12 +6802,12 @@
           <t>Robotics - Software Development Engineer Intern/Co-op - 2026</t>
         </is>
       </c>
-      <c r="D99" s="31" t="inlineStr">
+      <c r="D99" s="32" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E99" s="31" t="inlineStr">
+      <c r="E99" s="32" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6816,12 +6822,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H99" s="31" t="inlineStr">
+      <c r="H99" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I99" s="31" t="inlineStr">
+      <c r="I99" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6836,20 +6842,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L99" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M99" s="31" t="inlineStr"/>
+      <c r="L99" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M99" s="32" t="inlineStr"/>
     </row>
     <row r="100" ht="18" customHeight="1">
-      <c r="A100" s="30" t="inlineStr">
+      <c r="A100" s="33" t="inlineStr">
         <is>
           <t>4417646890</t>
         </is>
       </c>
-      <c r="B100" s="30" t="inlineStr">
+      <c r="B100" s="33" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6859,12 +6865,12 @@
           <t>Software Engineer II</t>
         </is>
       </c>
-      <c r="D100" s="30" t="inlineStr">
+      <c r="D100" s="33" t="inlineStr">
         <is>
           <t>Compass</t>
         </is>
       </c>
-      <c r="E100" s="30" t="inlineStr">
+      <c r="E100" s="33" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6879,12 +6885,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H100" s="30" t="inlineStr">
+      <c r="H100" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I100" s="30" t="inlineStr">
+      <c r="I100" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6899,20 +6905,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L100" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M100" s="30" t="inlineStr"/>
+      <c r="L100" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M100" s="33" t="inlineStr"/>
     </row>
     <row r="101" ht="18" customHeight="1">
-      <c r="A101" s="31" t="inlineStr">
+      <c r="A101" s="32" t="inlineStr">
         <is>
           <t>4417565729</t>
         </is>
       </c>
-      <c r="B101" s="31" t="inlineStr">
+      <c r="B101" s="32" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6922,12 +6928,12 @@
           <t>software engineer- ST, Seattle, WA</t>
         </is>
       </c>
-      <c r="D101" s="31" t="inlineStr">
+      <c r="D101" s="32" t="inlineStr">
         <is>
           <t>Starbucks</t>
         </is>
       </c>
-      <c r="E101" s="31" t="inlineStr">
+      <c r="E101" s="32" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6942,12 +6948,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H101" s="31" t="inlineStr">
+      <c r="H101" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I101" s="31" t="inlineStr">
+      <c r="I101" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6962,20 +6968,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L101" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M101" s="31" t="inlineStr"/>
+      <c r="L101" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M101" s="32" t="inlineStr"/>
     </row>
     <row r="102" ht="18" customHeight="1">
-      <c r="A102" s="30" t="inlineStr">
+      <c r="A102" s="33" t="inlineStr">
         <is>
           <t>4420492781</t>
         </is>
       </c>
-      <c r="B102" s="30" t="inlineStr">
+      <c r="B102" s="33" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6985,12 +6991,12 @@
           <t>Software Engineer (Starlink Mobile)</t>
         </is>
       </c>
-      <c r="D102" s="30" t="inlineStr">
+      <c r="D102" s="33" t="inlineStr">
         <is>
           <t>SpaceX</t>
         </is>
       </c>
-      <c r="E102" s="30" t="inlineStr">
+      <c r="E102" s="33" t="inlineStr">
         <is>
           <t>Redmond, WA</t>
         </is>
@@ -7005,12 +7011,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H102" s="30" t="inlineStr">
+      <c r="H102" s="33" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="I102" s="30" t="inlineStr">
+      <c r="I102" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7025,20 +7031,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L102" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M102" s="30" t="inlineStr"/>
+      <c r="L102" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M102" s="33" t="inlineStr"/>
     </row>
     <row r="103" ht="18" customHeight="1">
-      <c r="A103" s="31" t="inlineStr">
+      <c r="A103" s="32" t="inlineStr">
         <is>
           <t>4418203886</t>
         </is>
       </c>
-      <c r="B103" s="31" t="inlineStr">
+      <c r="B103" s="32" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -7048,12 +7054,12 @@
           <t>System Software Engineer - Performance</t>
         </is>
       </c>
-      <c r="D103" s="31" t="inlineStr">
+      <c r="D103" s="32" t="inlineStr">
         <is>
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="E103" s="31" t="inlineStr">
+      <c r="E103" s="32" t="inlineStr">
         <is>
           <t>Redmond, WA</t>
         </is>
@@ -7068,12 +7074,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H103" s="31" t="inlineStr">
+      <c r="H103" s="32" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
-      <c r="I103" s="31" t="inlineStr">
+      <c r="I103" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7088,20 +7094,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L103" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M103" s="31" t="inlineStr"/>
+      <c r="L103" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M103" s="32" t="inlineStr"/>
     </row>
     <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="30" t="inlineStr">
+      <c r="A104" s="33" t="inlineStr">
         <is>
           <t>4332886298</t>
         </is>
       </c>
-      <c r="B104" s="30" t="inlineStr">
+      <c r="B104" s="33" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -7111,12 +7117,12 @@
           <t>Software Engineer - AI Travel Agent</t>
         </is>
       </c>
-      <c r="D104" s="30" t="inlineStr">
+      <c r="D104" s="33" t="inlineStr">
         <is>
           <t>Axel</t>
         </is>
       </c>
-      <c r="E104" s="30" t="inlineStr">
+      <c r="E104" s="33" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -7131,12 +7137,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H104" s="30" t="inlineStr">
+      <c r="H104" s="33" t="inlineStr">
         <is>
           <t>163</t>
         </is>
       </c>
-      <c r="I104" s="30" t="inlineStr">
+      <c r="I104" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7151,20 +7157,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L104" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M104" s="30" t="inlineStr"/>
+      <c r="L104" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M104" s="33" t="inlineStr"/>
     </row>
     <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="31" t="inlineStr">
+      <c r="A105" s="32" t="inlineStr">
         <is>
           <t>4388596468</t>
         </is>
       </c>
-      <c r="B105" s="31" t="inlineStr">
+      <c r="B105" s="32" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -7174,12 +7180,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D105" s="31" t="inlineStr">
+      <c r="D105" s="32" t="inlineStr">
         <is>
           <t>Capgemini</t>
         </is>
       </c>
-      <c r="E105" s="31" t="inlineStr">
+      <c r="E105" s="32" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -7194,12 +7200,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H105" s="31" t="inlineStr">
+      <c r="H105" s="32" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="I105" s="31" t="inlineStr">
+      <c r="I105" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7214,20 +7220,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L105" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M105" s="31" t="inlineStr"/>
+      <c r="L105" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M105" s="32" t="inlineStr"/>
     </row>
     <row r="106" ht="18" customHeight="1">
-      <c r="A106" s="30" t="inlineStr">
+      <c r="A106" s="33" t="inlineStr">
         <is>
           <t>4419517103</t>
         </is>
       </c>
-      <c r="B106" s="30" t="inlineStr">
+      <c r="B106" s="33" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -7237,12 +7243,12 @@
           <t>Software Engineer II</t>
         </is>
       </c>
-      <c r="D106" s="30" t="inlineStr">
+      <c r="D106" s="33" t="inlineStr">
         <is>
           <t>Chewy</t>
         </is>
       </c>
-      <c r="E106" s="30" t="inlineStr">
+      <c r="E106" s="33" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -7257,12 +7263,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H106" s="30" t="inlineStr">
+      <c r="H106" s="33" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I106" s="30" t="inlineStr">
+      <c r="I106" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7277,20 +7283,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L106" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M106" s="30" t="inlineStr"/>
+      <c r="L106" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M106" s="33" t="inlineStr"/>
     </row>
     <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="31" t="inlineStr">
+      <c r="A107" s="32" t="inlineStr">
         <is>
           <t>4395225418</t>
         </is>
       </c>
-      <c r="B107" s="31" t="inlineStr">
+      <c r="B107" s="32" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -7300,12 +7306,12 @@
           <t>Software Engineer - Backend</t>
         </is>
       </c>
-      <c r="D107" s="31" t="inlineStr">
+      <c r="D107" s="32" t="inlineStr">
         <is>
           <t>MotherDuck</t>
         </is>
       </c>
-      <c r="E107" s="31" t="inlineStr">
+      <c r="E107" s="32" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -7320,12 +7326,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H107" s="31" t="inlineStr">
+      <c r="H107" s="32" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I107" s="31" t="inlineStr">
+      <c r="I107" s="32" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7340,20 +7346,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L107" s="31" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M107" s="31" t="inlineStr"/>
+      <c r="L107" s="32" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M107" s="32" t="inlineStr"/>
     </row>
     <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="30" t="inlineStr">
+      <c r="A108" s="33" t="inlineStr">
         <is>
           <t>4417163235</t>
         </is>
       </c>
-      <c r="B108" s="30" t="inlineStr">
+      <c r="B108" s="33" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -7363,12 +7369,12 @@
           <t>Software Engineer, Cloud SDK</t>
         </is>
       </c>
-      <c r="D108" s="30" t="inlineStr">
+      <c r="D108" s="33" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="E108" s="30" t="inlineStr">
+      <c r="E108" s="33" t="inlineStr">
         <is>
           <t>Kirkland, WA</t>
         </is>
@@ -7383,12 +7389,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H108" s="30" t="inlineStr">
+      <c r="H108" s="33" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="I108" s="30" t="inlineStr">
+      <c r="I108" s="33" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7403,12 +7409,12 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L108" s="30" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M108" s="30" t="inlineStr"/>
+      <c r="L108" s="33" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M108" s="33" t="inlineStr"/>
     </row>
     <row r="109" ht="18" customHeight="1">
       <c r="A109" s="32" t="inlineStr">
@@ -8481,8 +8487,260 @@
       </c>
       <c r="M125" s="32" t="inlineStr"/>
     </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="A126" s="34" t="inlineStr">
+        <is>
+          <t>4304448690</t>
+        </is>
+      </c>
+      <c r="B126" s="34" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="D126" s="34" t="inlineStr">
+        <is>
+          <t>DataAnnotation</t>
+        </is>
+      </c>
+      <c r="E126" s="34" t="inlineStr">
+        <is>
+          <t>Pennsylvania, United States</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H126" s="34" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="I126" s="34" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, html, sql, c++, c, Title match: Software Developer</t>
+        </is>
+      </c>
+      <c r="K126" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L126" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M126" s="34" t="inlineStr"/>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="A127" s="35" t="inlineStr">
+        <is>
+          <t>4305126185</t>
+        </is>
+      </c>
+      <c r="B127" s="35" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C127" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (Payment Network) - Global Payment - 2026 Summer(BS/MS)</t>
+        </is>
+      </c>
+      <c r="D127" s="35" t="inlineStr">
+        <is>
+          <t>ByteDance</t>
+        </is>
+      </c>
+      <c r="E127" s="35" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="F127" s="9" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="G127" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H127" s="35" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I127" s="35" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="J127" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, aws, rest, api, backend, c++, Location: Seattle, WA, Title match: Software Engineer Intern (Payment Network) - Global Payment - 2026 Summer(BS/MS)</t>
+        </is>
+      </c>
+      <c r="K127" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L127" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M127" s="35" t="inlineStr"/>
+    </row>
+    <row r="128" ht="18" customHeight="1">
+      <c r="A128" s="34" t="inlineStr">
+        <is>
+          <t>4418276914</t>
+        </is>
+      </c>
+      <c r="B128" s="34" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D128" s="34" t="inlineStr">
+        <is>
+          <t>fieldd</t>
+        </is>
+      </c>
+      <c r="E128" s="34" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H128" s="34" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I128" s="34" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>Skills: node, c, oop, Location: Austin, TX, Title match: Software Engineer</t>
+        </is>
+      </c>
+      <c r="K128" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L128" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M128" s="34" t="inlineStr"/>
+    </row>
+    <row r="129" ht="18" customHeight="1">
+      <c r="A129" s="35" t="inlineStr">
+        <is>
+          <t>4420219582</t>
+        </is>
+      </c>
+      <c r="B129" s="35" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C129" s="8" t="inlineStr">
+        <is>
+          <t>Internship, Software Engineer, Information Security (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="D129" s="35" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="E129" s="35" t="inlineStr">
+        <is>
+          <t>Bellevue, WA</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H129" s="35" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="I129" s="35" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="J129" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, flask, rest, api, c, ci/cd, Location: Bellevue, WA, Title match: Internship, Software Engineer, Information Security (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="K129" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L129" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M129" s="35" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M125"/>
+  <autoFilter ref="A1:M129"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -8608,6 +8866,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K123" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K124" r:id="rId123"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K129" r:id="rId128"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Job Matches" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Matches'!$A$1:$M$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Matches'!$A$1:$M$150</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -217,6 +217,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -590,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M129"/>
+  <dimension ref="A1:M150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -676,12 +682,12 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="33" t="inlineStr">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>4406952064</t>
         </is>
       </c>
-      <c r="B2" s="33" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -691,12 +697,12 @@
           <t>DevSecOps Intern</t>
         </is>
       </c>
-      <c r="D2" s="33" t="inlineStr">
+      <c r="D2" s="34" t="inlineStr">
         <is>
           <t>Modern Technology Solutions, Inc. (MTSI)</t>
         </is>
       </c>
-      <c r="E2" s="33" t="inlineStr">
+      <c r="E2" s="34" t="inlineStr">
         <is>
           <t>Huntsville, AL</t>
         </is>
@@ -711,12 +717,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H2" s="33" t="inlineStr">
+      <c r="H2" s="34" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="I2" s="33" t="inlineStr">
+      <c r="I2" s="34" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -731,20 +737,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L2" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M2" s="33" t="inlineStr"/>
+      <c r="L2" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M2" s="34" t="inlineStr"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>4405630173</t>
         </is>
       </c>
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" s="35" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -754,12 +760,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D3" s="32" t="inlineStr">
+      <c r="D3" s="35" t="inlineStr">
         <is>
           <t>DLRdmv®</t>
         </is>
       </c>
-      <c r="E3" s="32" t="inlineStr">
+      <c r="E3" s="35" t="inlineStr">
         <is>
           <t>Dallas, TX</t>
         </is>
@@ -774,12 +780,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H3" s="32" t="inlineStr">
+      <c r="H3" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I3" s="32" t="inlineStr">
+      <c r="I3" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -794,20 +800,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L3" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M3" s="32" t="inlineStr"/>
+      <c r="L3" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M3" s="35" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>4287414862</t>
         </is>
       </c>
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -817,12 +823,12 @@
           <t>[Online Assessment]Software Development Engineer Intern (Network Automation)- 2026 Summer (BS/ MS)</t>
         </is>
       </c>
-      <c r="D4" s="33" t="inlineStr">
+      <c r="D4" s="34" t="inlineStr">
         <is>
           <t>ByteDance</t>
         </is>
       </c>
-      <c r="E4" s="33" t="inlineStr">
+      <c r="E4" s="34" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -837,12 +843,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H4" s="33" t="inlineStr">
+      <c r="H4" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I4" s="33" t="inlineStr">
+      <c r="I4" s="34" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -857,20 +863,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L4" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M4" s="33" t="inlineStr"/>
+      <c r="L4" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M4" s="34" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>4309805269</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -880,12 +886,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D5" s="32" t="inlineStr">
+      <c r="D5" s="35" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E5" s="32" t="inlineStr">
+      <c r="E5" s="35" t="inlineStr">
         <is>
           <t>Delaware, United States</t>
         </is>
@@ -900,12 +906,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H5" s="32" t="inlineStr">
+      <c r="H5" s="35" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="I5" s="32" t="inlineStr">
+      <c r="I5" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -920,20 +926,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L5" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M5" s="32" t="inlineStr"/>
+      <c r="L5" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M5" s="35" t="inlineStr"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>4371812987</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -943,12 +949,12 @@
           <t>Software Development Engineer Fall Intern - Military Veteran</t>
         </is>
       </c>
-      <c r="D6" s="33" t="inlineStr">
+      <c r="D6" s="34" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E6" s="33" t="inlineStr">
+      <c r="E6" s="34" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -963,12 +969,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H6" s="33" t="inlineStr">
+      <c r="H6" s="34" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="I6" s="33" t="inlineStr">
+      <c r="I6" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -983,20 +989,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L6" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M6" s="33" t="inlineStr"/>
+      <c r="L6" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M6" s="34" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="32" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>4274682122</t>
         </is>
       </c>
-      <c r="B7" s="32" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1006,12 +1012,12 @@
           <t>Software Engineer Intern (Data Ecosystem) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D7" s="32" t="inlineStr">
+      <c r="D7" s="35" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E7" s="32" t="inlineStr">
+      <c r="E7" s="35" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1026,12 +1032,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H7" s="32" t="inlineStr">
+      <c r="H7" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I7" s="32" t="inlineStr">
+      <c r="I7" s="35" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1046,20 +1052,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L7" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M7" s="32" t="inlineStr"/>
+      <c r="L7" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M7" s="35" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="33" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>4283848614</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1069,12 +1075,12 @@
           <t>[Online Assessment] Software Engineer Intern (Recommendation Infrastructure) - 2026 Fall (BS/ MS)</t>
         </is>
       </c>
-      <c r="D8" s="33" t="inlineStr">
+      <c r="D8" s="34" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E8" s="33" t="inlineStr">
+      <c r="E8" s="34" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1089,12 +1095,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H8" s="33" t="inlineStr">
+      <c r="H8" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I8" s="33" t="inlineStr">
+      <c r="I8" s="34" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1109,20 +1115,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L8" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M8" s="33" t="inlineStr"/>
+      <c r="L8" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M8" s="34" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>4411790844</t>
         </is>
       </c>
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1132,12 +1138,12 @@
           <t>Software Engineer Intern (Infrastructure Automation) - Fall 2026</t>
         </is>
       </c>
-      <c r="D9" s="32" t="inlineStr">
+      <c r="D9" s="35" t="inlineStr">
         <is>
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="E9" s="32" t="inlineStr">
+      <c r="E9" s="35" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -1152,12 +1158,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H9" s="32" t="inlineStr">
+      <c r="H9" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I9" s="32" t="inlineStr">
+      <c r="I9" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1172,20 +1178,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L9" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M9" s="32" t="inlineStr"/>
+      <c r="L9" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M9" s="35" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="33" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>4332425058</t>
         </is>
       </c>
-      <c r="B10" s="33" t="inlineStr">
+      <c r="B10" s="34" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1195,12 +1201,12 @@
           <t>Software Development Engineer Internship - Fall 2026 (US)</t>
         </is>
       </c>
-      <c r="D10" s="33" t="inlineStr">
+      <c r="D10" s="34" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E10" s="33" t="inlineStr">
+      <c r="E10" s="34" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1215,12 +1221,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H10" s="33" t="inlineStr">
+      <c r="H10" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I10" s="33" t="inlineStr">
+      <c r="I10" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1235,20 +1241,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L10" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M10" s="33" t="inlineStr"/>
+      <c r="L10" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M10" s="34" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="32" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>4323643644</t>
         </is>
       </c>
-      <c r="B11" s="32" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1258,12 +1264,12 @@
           <t>[Online Assessment] Software Engineer Intern (Recommendation Infrastructure) - 2026 Summer (BS/ MS)</t>
         </is>
       </c>
-      <c r="D11" s="32" t="inlineStr">
+      <c r="D11" s="35" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E11" s="32" t="inlineStr">
+      <c r="E11" s="35" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1278,12 +1284,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H11" s="32" t="inlineStr">
+      <c r="H11" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I11" s="32" t="inlineStr">
+      <c r="I11" s="35" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1298,20 +1304,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L11" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M11" s="32" t="inlineStr"/>
+      <c r="L11" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M11" s="35" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>4320849104</t>
         </is>
       </c>
-      <c r="B12" s="33" t="inlineStr">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1321,12 +1327,12 @@
           <t>Software Engineer Intern (Commerce Ads) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D12" s="33" t="inlineStr">
+      <c r="D12" s="34" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E12" s="33" t="inlineStr">
+      <c r="E12" s="34" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1341,12 +1347,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H12" s="33" t="inlineStr">
+      <c r="H12" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I12" s="33" t="inlineStr">
+      <c r="I12" s="34" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1361,20 +1367,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L12" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M12" s="33" t="inlineStr"/>
+      <c r="L12" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M12" s="34" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="32" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>4401686051</t>
         </is>
       </c>
-      <c r="B13" s="32" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1384,12 +1390,12 @@
           <t>Front End Software Engineer</t>
         </is>
       </c>
-      <c r="D13" s="32" t="inlineStr">
+      <c r="D13" s="35" t="inlineStr">
         <is>
           <t>Saronic Technologies</t>
         </is>
       </c>
-      <c r="E13" s="32" t="inlineStr">
+      <c r="E13" s="35" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -1404,12 +1410,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H13" s="32" t="inlineStr">
+      <c r="H13" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I13" s="32" t="inlineStr">
+      <c r="I13" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1424,20 +1430,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L13" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M13" s="32" t="inlineStr"/>
+      <c r="L13" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M13" s="35" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>4309696652</t>
         </is>
       </c>
-      <c r="B14" s="33" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1447,12 +1453,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D14" s="33" t="inlineStr">
+      <c r="D14" s="34" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E14" s="33" t="inlineStr">
+      <c r="E14" s="34" t="inlineStr">
         <is>
           <t>Rhode Island, United States</t>
         </is>
@@ -1467,12 +1473,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H14" s="33" t="inlineStr">
+      <c r="H14" s="34" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="I14" s="33" t="inlineStr">
+      <c r="I14" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1487,20 +1493,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L14" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M14" s="33" t="inlineStr"/>
+      <c r="L14" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M14" s="34" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>4309804319</t>
         </is>
       </c>
-      <c r="B15" s="32" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1510,12 +1516,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D15" s="32" t="inlineStr">
+      <c r="D15" s="35" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E15" s="32" t="inlineStr">
+      <c r="E15" s="35" t="inlineStr">
         <is>
           <t>Colorado, United States</t>
         </is>
@@ -1530,12 +1536,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H15" s="32" t="inlineStr">
+      <c r="H15" s="35" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="I15" s="32" t="inlineStr">
+      <c r="I15" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1550,20 +1556,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L15" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M15" s="32" t="inlineStr"/>
+      <c r="L15" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M15" s="35" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="33" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>4410271532</t>
         </is>
       </c>
-      <c r="B16" s="33" t="inlineStr">
+      <c r="B16" s="34" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1573,12 +1579,12 @@
           <t>Associate Developer</t>
         </is>
       </c>
-      <c r="D16" s="33" t="inlineStr">
+      <c r="D16" s="34" t="inlineStr">
         <is>
           <t>HealthStream</t>
         </is>
       </c>
-      <c r="E16" s="33" t="inlineStr">
+      <c r="E16" s="34" t="inlineStr">
         <is>
           <t>Nashville, TN</t>
         </is>
@@ -1593,12 +1599,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H16" s="33" t="inlineStr">
+      <c r="H16" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I16" s="33" t="inlineStr">
+      <c r="I16" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1613,20 +1619,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L16" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M16" s="33" t="inlineStr"/>
+      <c r="L16" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M16" s="34" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="32" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>4304445726</t>
         </is>
       </c>
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1636,12 +1642,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D17" s="32" t="inlineStr">
+      <c r="D17" s="35" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E17" s="32" t="inlineStr">
+      <c r="E17" s="35" t="inlineStr">
         <is>
           <t>Oregon, United States</t>
         </is>
@@ -1656,12 +1662,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H17" s="32" t="inlineStr">
+      <c r="H17" s="35" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="I17" s="32" t="inlineStr">
+      <c r="I17" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1676,20 +1682,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L17" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M17" s="32" t="inlineStr"/>
+      <c r="L17" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M17" s="35" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="33" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>4342036151</t>
         </is>
       </c>
-      <c r="B18" s="33" t="inlineStr">
+      <c r="B18" s="34" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1699,12 +1705,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D18" s="33" t="inlineStr">
+      <c r="D18" s="34" t="inlineStr">
         <is>
           <t>Modern Treasury</t>
         </is>
       </c>
-      <c r="E18" s="33" t="inlineStr">
+      <c r="E18" s="34" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
@@ -1719,12 +1725,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H18" s="33" t="inlineStr">
+      <c r="H18" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I18" s="33" t="inlineStr">
+      <c r="I18" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1739,20 +1745,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L18" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M18" s="33" t="inlineStr"/>
+      <c r="L18" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M18" s="34" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="32" t="inlineStr">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>4304441843</t>
         </is>
       </c>
-      <c r="B19" s="32" t="inlineStr">
+      <c r="B19" s="35" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1762,12 +1768,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D19" s="32" t="inlineStr">
+      <c r="D19" s="35" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E19" s="32" t="inlineStr">
+      <c r="E19" s="35" t="inlineStr">
         <is>
           <t>Idaho, United States</t>
         </is>
@@ -1782,12 +1788,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H19" s="32" t="inlineStr">
+      <c r="H19" s="35" t="inlineStr">
         <is>
           <t>157</t>
         </is>
       </c>
-      <c r="I19" s="32" t="inlineStr">
+      <c r="I19" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1802,20 +1808,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L19" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M19" s="32" t="inlineStr"/>
+      <c r="L19" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M19" s="35" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="33" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>4408047047</t>
         </is>
       </c>
-      <c r="B20" s="33" t="inlineStr">
+      <c r="B20" s="34" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1825,12 +1831,12 @@
           <t>Computer Sciences - Graduates - AI Training - Las Vegas, US</t>
         </is>
       </c>
-      <c r="D20" s="33" t="inlineStr">
+      <c r="D20" s="34" t="inlineStr">
         <is>
           <t>Prolific</t>
         </is>
       </c>
-      <c r="E20" s="33" t="inlineStr">
+      <c r="E20" s="34" t="inlineStr">
         <is>
           <t>Las Vegas, NV</t>
         </is>
@@ -1845,12 +1851,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H20" s="33" t="inlineStr">
+      <c r="H20" s="34" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I20" s="33" t="inlineStr">
+      <c r="I20" s="34" t="inlineStr">
         <is>
           <t>Temporary</t>
         </is>
@@ -1865,20 +1871,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L20" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M20" s="33" t="inlineStr"/>
+      <c r="L20" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M20" s="34" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="32" t="inlineStr">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>4304444837</t>
         </is>
       </c>
-      <c r="B21" s="32" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1888,12 +1894,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D21" s="32" t="inlineStr">
+      <c r="D21" s="35" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E21" s="32" t="inlineStr">
+      <c r="E21" s="35" t="inlineStr">
         <is>
           <t>New Jersey, United States</t>
         </is>
@@ -1908,12 +1914,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H21" s="32" t="inlineStr">
+      <c r="H21" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I21" s="32" t="inlineStr">
+      <c r="I21" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1928,20 +1934,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L21" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M21" s="32" t="inlineStr"/>
+      <c r="L21" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M21" s="35" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="33" t="inlineStr">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t>4405641326</t>
         </is>
       </c>
-      <c r="B22" s="33" t="inlineStr">
+      <c r="B22" s="34" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1951,12 +1957,12 @@
           <t>Full-stack Engineer</t>
         </is>
       </c>
-      <c r="D22" s="33" t="inlineStr">
+      <c r="D22" s="34" t="inlineStr">
         <is>
           <t>PartnerTap</t>
         </is>
       </c>
-      <c r="E22" s="33" t="inlineStr">
+      <c r="E22" s="34" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1971,12 +1977,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H22" s="33" t="inlineStr">
+      <c r="H22" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I22" s="33" t="inlineStr">
+      <c r="I22" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1991,20 +1997,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L22" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M22" s="33" t="inlineStr"/>
+      <c r="L22" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M22" s="34" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="32" t="inlineStr">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>4341020900</t>
         </is>
       </c>
-      <c r="B23" s="32" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2014,12 +2020,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D23" s="32" t="inlineStr">
+      <c r="D23" s="35" t="inlineStr">
         <is>
           <t>PlanIT Group, LLC</t>
         </is>
       </c>
-      <c r="E23" s="32" t="inlineStr">
+      <c r="E23" s="35" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -2034,12 +2040,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H23" s="32" t="inlineStr">
+      <c r="H23" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I23" s="32" t="inlineStr">
+      <c r="I23" s="35" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
@@ -2054,20 +2060,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L23" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M23" s="32" t="inlineStr"/>
+      <c r="L23" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M23" s="35" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="33" t="inlineStr">
+      <c r="A24" s="34" t="inlineStr">
         <is>
           <t>4304450637</t>
         </is>
       </c>
-      <c r="B24" s="33" t="inlineStr">
+      <c r="B24" s="34" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2077,12 +2083,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D24" s="33" t="inlineStr">
+      <c r="D24" s="34" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E24" s="33" t="inlineStr">
+      <c r="E24" s="34" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -2097,12 +2103,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H24" s="33" t="inlineStr">
+      <c r="H24" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I24" s="33" t="inlineStr">
+      <c r="I24" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2117,20 +2123,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L24" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M24" s="33" t="inlineStr"/>
+      <c r="L24" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M24" s="34" t="inlineStr"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="32" t="inlineStr">
+      <c r="A25" s="35" t="inlineStr">
         <is>
           <t>4304451654</t>
         </is>
       </c>
-      <c r="B25" s="32" t="inlineStr">
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2140,12 +2146,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D25" s="32" t="inlineStr">
+      <c r="D25" s="35" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E25" s="32" t="inlineStr">
+      <c r="E25" s="35" t="inlineStr">
         <is>
           <t>Utah, United States</t>
         </is>
@@ -2160,12 +2166,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H25" s="32" t="inlineStr">
+      <c r="H25" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I25" s="32" t="inlineStr">
+      <c r="I25" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2180,20 +2186,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L25" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M25" s="32" t="inlineStr"/>
+      <c r="L25" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M25" s="35" t="inlineStr"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="33" t="inlineStr">
+      <c r="A26" s="34" t="inlineStr">
         <is>
           <t>4413745880</t>
         </is>
       </c>
-      <c r="B26" s="33" t="inlineStr">
+      <c r="B26" s="34" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2203,12 +2209,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D26" s="33" t="inlineStr">
+      <c r="D26" s="34" t="inlineStr">
         <is>
           <t>Crate &amp; Barrel</t>
         </is>
       </c>
-      <c r="E26" s="33" t="inlineStr">
+      <c r="E26" s="34" t="inlineStr">
         <is>
           <t>Northbrook, IL</t>
         </is>
@@ -2223,12 +2229,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H26" s="33" t="inlineStr">
+      <c r="H26" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I26" s="33" t="inlineStr">
+      <c r="I26" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2243,20 +2249,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L26" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M26" s="33" t="inlineStr"/>
+      <c r="L26" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M26" s="34" t="inlineStr"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="32" t="inlineStr">
+      <c r="A27" s="35" t="inlineStr">
         <is>
           <t>4304438841</t>
         </is>
       </c>
-      <c r="B27" s="32" t="inlineStr">
+      <c r="B27" s="35" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2266,12 +2272,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D27" s="32" t="inlineStr">
+      <c r="D27" s="35" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E27" s="32" t="inlineStr">
+      <c r="E27" s="35" t="inlineStr">
         <is>
           <t>Connecticut, United States</t>
         </is>
@@ -2286,12 +2292,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H27" s="32" t="inlineStr">
+      <c r="H27" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I27" s="32" t="inlineStr">
+      <c r="I27" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2306,20 +2312,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L27" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M27" s="32" t="inlineStr"/>
+      <c r="L27" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M27" s="35" t="inlineStr"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="33" t="inlineStr">
+      <c r="A28" s="34" t="inlineStr">
         <is>
           <t>4393215930</t>
         </is>
       </c>
-      <c r="B28" s="33" t="inlineStr">
+      <c r="B28" s="34" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2329,12 +2335,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D28" s="33" t="inlineStr">
+      <c r="D28" s="34" t="inlineStr">
         <is>
           <t>Transcend</t>
         </is>
       </c>
-      <c r="E28" s="33" t="inlineStr">
+      <c r="E28" s="34" t="inlineStr">
         <is>
           <t>California, United States</t>
         </is>
@@ -2349,12 +2355,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H28" s="33" t="inlineStr">
+      <c r="H28" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I28" s="33" t="inlineStr">
+      <c r="I28" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2369,20 +2375,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L28" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M28" s="33" t="inlineStr"/>
+      <c r="L28" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M28" s="34" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="32" t="inlineStr">
+      <c r="A29" s="35" t="inlineStr">
         <is>
           <t>4304445723</t>
         </is>
       </c>
-      <c r="B29" s="32" t="inlineStr">
+      <c r="B29" s="35" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2392,12 +2398,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D29" s="32" t="inlineStr">
+      <c r="D29" s="35" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E29" s="32" t="inlineStr">
+      <c r="E29" s="35" t="inlineStr">
         <is>
           <t>Illinois, United States</t>
         </is>
@@ -2412,12 +2418,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H29" s="32" t="inlineStr">
+      <c r="H29" s="35" t="inlineStr">
         <is>
           <t>198</t>
         </is>
       </c>
-      <c r="I29" s="32" t="inlineStr">
+      <c r="I29" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2432,20 +2438,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L29" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M29" s="32" t="inlineStr"/>
+      <c r="L29" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M29" s="35" t="inlineStr"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="33" t="inlineStr">
+      <c r="A30" s="34" t="inlineStr">
         <is>
           <t>4396380649</t>
         </is>
       </c>
-      <c r="B30" s="33" t="inlineStr">
+      <c r="B30" s="34" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2455,12 +2461,12 @@
           <t>Full-Stack Developer Intern, Music &amp; Audio</t>
         </is>
       </c>
-      <c r="D30" s="33" t="inlineStr">
+      <c r="D30" s="34" t="inlineStr">
         <is>
           <t>Melotech</t>
         </is>
       </c>
-      <c r="E30" s="33" t="inlineStr">
+      <c r="E30" s="34" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
@@ -2475,12 +2481,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H30" s="33" t="inlineStr">
+      <c r="H30" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I30" s="33" t="inlineStr">
+      <c r="I30" s="34" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -2495,20 +2501,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L30" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M30" s="33" t="inlineStr"/>
+      <c r="L30" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M30" s="34" t="inlineStr"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="32" t="inlineStr">
+      <c r="A31" s="35" t="inlineStr">
         <is>
           <t>4304454025</t>
         </is>
       </c>
-      <c r="B31" s="32" t="inlineStr">
+      <c r="B31" s="35" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2518,12 +2524,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D31" s="32" t="inlineStr">
+      <c r="D31" s="35" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E31" s="32" t="inlineStr">
+      <c r="E31" s="35" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -2538,12 +2544,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H31" s="32" t="inlineStr">
+      <c r="H31" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I31" s="32" t="inlineStr">
+      <c r="I31" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2558,20 +2564,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L31" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M31" s="32" t="inlineStr"/>
+      <c r="L31" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M31" s="35" t="inlineStr"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="33" t="inlineStr">
+      <c r="A32" s="34" t="inlineStr">
         <is>
           <t>4309802287</t>
         </is>
       </c>
-      <c r="B32" s="33" t="inlineStr">
+      <c r="B32" s="34" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2581,12 +2587,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D32" s="33" t="inlineStr">
+      <c r="D32" s="34" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E32" s="33" t="inlineStr">
+      <c r="E32" s="34" t="inlineStr">
         <is>
           <t>New Jersey, United States</t>
         </is>
@@ -2601,12 +2607,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H32" s="33" t="inlineStr">
+      <c r="H32" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I32" s="33" t="inlineStr">
+      <c r="I32" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2621,20 +2627,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L32" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M32" s="33" t="inlineStr"/>
+      <c r="L32" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M32" s="34" t="inlineStr"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="32" t="inlineStr">
+      <c r="A33" s="35" t="inlineStr">
         <is>
           <t>4309694880</t>
         </is>
       </c>
-      <c r="B33" s="32" t="inlineStr">
+      <c r="B33" s="35" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2644,12 +2650,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D33" s="32" t="inlineStr">
+      <c r="D33" s="35" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E33" s="32" t="inlineStr">
+      <c r="E33" s="35" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -2664,12 +2670,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H33" s="32" t="inlineStr">
+      <c r="H33" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I33" s="32" t="inlineStr">
+      <c r="I33" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2684,20 +2690,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L33" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M33" s="32" t="inlineStr"/>
+      <c r="L33" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M33" s="35" t="inlineStr"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="33" t="inlineStr">
+      <c r="A34" s="34" t="inlineStr">
         <is>
           <t>4411274012</t>
         </is>
       </c>
-      <c r="B34" s="33" t="inlineStr">
+      <c r="B34" s="34" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2707,12 +2713,12 @@
           <t>Junior UI Developer</t>
         </is>
       </c>
-      <c r="D34" s="33" t="inlineStr">
+      <c r="D34" s="34" t="inlineStr">
         <is>
           <t>General Dynamics Information Technology</t>
         </is>
       </c>
-      <c r="E34" s="33" t="inlineStr">
+      <c r="E34" s="34" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -2727,12 +2733,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H34" s="33" t="inlineStr">
+      <c r="H34" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I34" s="33" t="inlineStr">
+      <c r="I34" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2747,20 +2753,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L34" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M34" s="33" t="inlineStr"/>
+      <c r="L34" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M34" s="34" t="inlineStr"/>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="32" t="inlineStr">
+      <c r="A35" s="35" t="inlineStr">
         <is>
           <t>4264562292</t>
         </is>
       </c>
-      <c r="B35" s="32" t="inlineStr">
+      <c r="B35" s="35" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2770,12 +2776,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D35" s="32" t="inlineStr">
+      <c r="D35" s="35" t="inlineStr">
         <is>
           <t>Cymertek Corporation</t>
         </is>
       </c>
-      <c r="E35" s="32" t="inlineStr">
+      <c r="E35" s="35" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
@@ -2790,12 +2796,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H35" s="32" t="inlineStr">
+      <c r="H35" s="35" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="I35" s="32" t="inlineStr">
+      <c r="I35" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2810,20 +2816,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L35" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M35" s="32" t="inlineStr"/>
+      <c r="L35" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M35" s="35" t="inlineStr"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="33" t="inlineStr">
+      <c r="A36" s="34" t="inlineStr">
         <is>
           <t>4417482675</t>
         </is>
       </c>
-      <c r="B36" s="33" t="inlineStr">
+      <c r="B36" s="34" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2833,12 +2839,12 @@
           <t>Software Developer I</t>
         </is>
       </c>
-      <c r="D36" s="33" t="inlineStr">
+      <c r="D36" s="34" t="inlineStr">
         <is>
           <t>El Paso Water</t>
         </is>
       </c>
-      <c r="E36" s="33" t="inlineStr">
+      <c r="E36" s="34" t="inlineStr">
         <is>
           <t>El Paso, TX</t>
         </is>
@@ -2853,12 +2859,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H36" s="33" t="inlineStr">
+      <c r="H36" s="34" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="I36" s="33" t="inlineStr">
+      <c r="I36" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2873,20 +2879,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L36" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M36" s="33" t="inlineStr"/>
+      <c r="L36" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M36" s="34" t="inlineStr"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="32" t="inlineStr">
+      <c r="A37" s="35" t="inlineStr">
         <is>
           <t>4416508200</t>
         </is>
       </c>
-      <c r="B37" s="32" t="inlineStr">
+      <c r="B37" s="35" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2896,12 +2902,12 @@
           <t>Software Development Engineer in Test Intern (Global E-Commerce) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D37" s="32" t="inlineStr">
+      <c r="D37" s="35" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E37" s="32" t="inlineStr">
+      <c r="E37" s="35" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -2916,12 +2922,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H37" s="32" t="inlineStr">
+      <c r="H37" s="35" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I37" s="32" t="inlineStr">
+      <c r="I37" s="35" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -2936,20 +2942,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L37" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M37" s="32" t="inlineStr"/>
+      <c r="L37" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M37" s="35" t="inlineStr"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="33" t="inlineStr">
+      <c r="A38" s="34" t="inlineStr">
         <is>
           <t>4309809191</t>
         </is>
       </c>
-      <c r="B38" s="33" t="inlineStr">
+      <c r="B38" s="34" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
@@ -2959,12 +2965,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D38" s="33" t="inlineStr">
+      <c r="D38" s="34" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E38" s="33" t="inlineStr">
+      <c r="E38" s="34" t="inlineStr">
         <is>
           <t>Ohio, United States</t>
         </is>
@@ -2979,12 +2985,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H38" s="33" t="inlineStr">
+      <c r="H38" s="34" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="I38" s="33" t="inlineStr">
+      <c r="I38" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2999,20 +3005,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L38" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M38" s="33" t="inlineStr"/>
+      <c r="L38" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M38" s="34" t="inlineStr"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="32" t="inlineStr">
+      <c r="A39" s="35" t="inlineStr">
         <is>
           <t>3986118096</t>
         </is>
       </c>
-      <c r="B39" s="32" t="inlineStr">
+      <c r="B39" s="35" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
@@ -3022,12 +3028,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D39" s="32" t="inlineStr">
+      <c r="D39" s="35" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E39" s="32" t="inlineStr">
+      <c r="E39" s="35" t="inlineStr">
         <is>
           <t>Irving, TX</t>
         </is>
@@ -3042,12 +3048,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H39" s="32" t="inlineStr">
+      <c r="H39" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I39" s="32" t="inlineStr">
+      <c r="I39" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3062,20 +3068,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L39" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M39" s="32" t="inlineStr"/>
+      <c r="L39" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M39" s="35" t="inlineStr"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="33" t="inlineStr">
+      <c r="A40" s="34" t="inlineStr">
         <is>
           <t>4309808244</t>
         </is>
       </c>
-      <c r="B40" s="33" t="inlineStr">
+      <c r="B40" s="34" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3085,12 +3091,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D40" s="33" t="inlineStr">
+      <c r="D40" s="34" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E40" s="33" t="inlineStr">
+      <c r="E40" s="34" t="inlineStr">
         <is>
           <t>Massachusetts, United States</t>
         </is>
@@ -3105,12 +3111,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H40" s="33" t="inlineStr">
+      <c r="H40" s="34" t="inlineStr">
         <is>
           <t>166</t>
         </is>
       </c>
-      <c r="I40" s="33" t="inlineStr">
+      <c r="I40" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3125,20 +3131,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L40" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M40" s="33" t="inlineStr"/>
+      <c r="L40" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M40" s="34" t="inlineStr"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="32" t="inlineStr">
+      <c r="A41" s="35" t="inlineStr">
         <is>
           <t>4362173625</t>
         </is>
       </c>
-      <c r="B41" s="32" t="inlineStr">
+      <c r="B41" s="35" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3148,12 +3154,12 @@
           <t>Full Stack Engineer</t>
         </is>
       </c>
-      <c r="D41" s="32" t="inlineStr">
+      <c r="D41" s="35" t="inlineStr">
         <is>
           <t>Empower Sleep</t>
         </is>
       </c>
-      <c r="E41" s="32" t="inlineStr">
+      <c r="E41" s="35" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3168,12 +3174,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H41" s="32" t="inlineStr">
+      <c r="H41" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I41" s="32" t="inlineStr">
+      <c r="I41" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3188,20 +3194,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L41" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M41" s="32" t="inlineStr"/>
+      <c r="L41" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M41" s="35" t="inlineStr"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="33" t="inlineStr">
+      <c r="A42" s="34" t="inlineStr">
         <is>
           <t>4309812093</t>
         </is>
       </c>
-      <c r="B42" s="33" t="inlineStr">
+      <c r="B42" s="34" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3211,12 +3217,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D42" s="33" t="inlineStr">
+      <c r="D42" s="34" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E42" s="33" t="inlineStr">
+      <c r="E42" s="34" t="inlineStr">
         <is>
           <t>Florida, United States</t>
         </is>
@@ -3231,12 +3237,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H42" s="33" t="inlineStr">
+      <c r="H42" s="34" t="inlineStr">
         <is>
           <t>158</t>
         </is>
       </c>
-      <c r="I42" s="33" t="inlineStr">
+      <c r="I42" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3251,20 +3257,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L42" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M42" s="33" t="inlineStr"/>
+      <c r="L42" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M42" s="34" t="inlineStr"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="32" t="inlineStr">
+      <c r="A43" s="35" t="inlineStr">
         <is>
           <t>4391759914</t>
         </is>
       </c>
-      <c r="B43" s="32" t="inlineStr">
+      <c r="B43" s="35" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3274,12 +3280,12 @@
           <t>QA Engineering Internship</t>
         </is>
       </c>
-      <c r="D43" s="32" t="inlineStr">
+      <c r="D43" s="35" t="inlineStr">
         <is>
           <t>Chartbeat</t>
         </is>
       </c>
-      <c r="E43" s="32" t="inlineStr">
+      <c r="E43" s="35" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -3294,12 +3300,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H43" s="32" t="inlineStr">
+      <c r="H43" s="35" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="I43" s="32" t="inlineStr">
+      <c r="I43" s="35" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3314,20 +3320,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L43" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M43" s="32" t="inlineStr"/>
+      <c r="L43" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M43" s="35" t="inlineStr"/>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="33" t="inlineStr">
+      <c r="A44" s="34" t="inlineStr">
         <is>
           <t>4412855678</t>
         </is>
       </c>
-      <c r="B44" s="33" t="inlineStr">
+      <c r="B44" s="34" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3337,12 +3343,12 @@
           <t>AI Integration Engineer</t>
         </is>
       </c>
-      <c r="D44" s="33" t="inlineStr">
+      <c r="D44" s="34" t="inlineStr">
         <is>
           <t>UST</t>
         </is>
       </c>
-      <c r="E44" s="33" t="inlineStr">
+      <c r="E44" s="34" t="inlineStr">
         <is>
           <t>Santa Clara, CA</t>
         </is>
@@ -3357,12 +3363,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H44" s="33" t="inlineStr">
+      <c r="H44" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I44" s="33" t="inlineStr">
+      <c r="I44" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3377,20 +3383,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L44" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M44" s="33" t="inlineStr"/>
+      <c r="L44" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M44" s="34" t="inlineStr"/>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="32" t="inlineStr">
+      <c r="A45" s="35" t="inlineStr">
         <is>
           <t>4309805219</t>
         </is>
       </c>
-      <c r="B45" s="32" t="inlineStr">
+      <c r="B45" s="35" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3400,12 +3406,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D45" s="32" t="inlineStr">
+      <c r="D45" s="35" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E45" s="32" t="inlineStr">
+      <c r="E45" s="35" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -3420,12 +3426,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H45" s="32" t="inlineStr">
+      <c r="H45" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I45" s="32" t="inlineStr">
+      <c r="I45" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3440,20 +3446,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L45" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M45" s="32" t="inlineStr"/>
+      <c r="L45" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M45" s="35" t="inlineStr"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="33" t="inlineStr">
+      <c r="A46" s="34" t="inlineStr">
         <is>
           <t>4409726429</t>
         </is>
       </c>
-      <c r="B46" s="33" t="inlineStr">
+      <c r="B46" s="34" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3463,12 +3469,12 @@
           <t>Data Science Intern</t>
         </is>
       </c>
-      <c r="D46" s="33" t="inlineStr">
+      <c r="D46" s="34" t="inlineStr">
         <is>
           <t>Rundoo</t>
         </is>
       </c>
-      <c r="E46" s="33" t="inlineStr">
+      <c r="E46" s="34" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3483,12 +3489,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H46" s="33" t="inlineStr">
+      <c r="H46" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I46" s="33" t="inlineStr">
+      <c r="I46" s="34" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3503,20 +3509,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L46" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M46" s="33" t="inlineStr"/>
+      <c r="L46" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M46" s="34" t="inlineStr"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="32" t="inlineStr">
+      <c r="A47" s="35" t="inlineStr">
         <is>
           <t>4305671729</t>
         </is>
       </c>
-      <c r="B47" s="32" t="inlineStr">
+      <c r="B47" s="35" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3526,12 +3532,12 @@
           <t>DoD SkillBridge Internship/Fellowship Opportunity Application (U.S. Military Only)</t>
         </is>
       </c>
-      <c r="D47" s="32" t="inlineStr">
+      <c r="D47" s="35" t="inlineStr">
         <is>
           <t>Onsights</t>
         </is>
       </c>
-      <c r="E47" s="32" t="inlineStr">
+      <c r="E47" s="35" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -3546,12 +3552,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H47" s="32" t="inlineStr">
+      <c r="H47" s="35" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I47" s="32" t="inlineStr">
+      <c r="I47" s="35" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3566,20 +3572,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L47" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M47" s="32" t="inlineStr"/>
+      <c r="L47" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M47" s="35" t="inlineStr"/>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="33" t="inlineStr">
+      <c r="A48" s="34" t="inlineStr">
         <is>
           <t>4414096220</t>
         </is>
       </c>
-      <c r="B48" s="33" t="inlineStr">
+      <c r="B48" s="34" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3589,12 +3595,12 @@
           <t>Visualization Engineer Intern</t>
         </is>
       </c>
-      <c r="D48" s="33" t="inlineStr">
+      <c r="D48" s="34" t="inlineStr">
         <is>
           <t>Leidos</t>
         </is>
       </c>
-      <c r="E48" s="33" t="inlineStr">
+      <c r="E48" s="34" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3609,12 +3615,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H48" s="33" t="inlineStr">
+      <c r="H48" s="34" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="I48" s="33" t="inlineStr">
+      <c r="I48" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3629,20 +3635,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L48" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M48" s="33" t="inlineStr"/>
+      <c r="L48" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M48" s="34" t="inlineStr"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="32" t="inlineStr">
+      <c r="A49" s="35" t="inlineStr">
         <is>
           <t>4361076044</t>
         </is>
       </c>
-      <c r="B49" s="32" t="inlineStr">
+      <c r="B49" s="35" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3652,12 +3658,12 @@
           <t>GenAI Engineering Intern  - SkillBridge (Remote)</t>
         </is>
       </c>
-      <c r="D49" s="32" t="inlineStr">
+      <c r="D49" s="35" t="inlineStr">
         <is>
           <t>CrowdStrike</t>
         </is>
       </c>
-      <c r="E49" s="32" t="inlineStr">
+      <c r="E49" s="35" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3672,12 +3678,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H49" s="32" t="inlineStr">
+      <c r="H49" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I49" s="32" t="inlineStr">
+      <c r="I49" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3692,20 +3698,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L49" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M49" s="32" t="inlineStr"/>
+      <c r="L49" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M49" s="35" t="inlineStr"/>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="33" t="inlineStr">
+      <c r="A50" s="34" t="inlineStr">
         <is>
           <t>4417553585</t>
         </is>
       </c>
-      <c r="B50" s="33" t="inlineStr">
+      <c r="B50" s="34" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3715,12 +3721,12 @@
           <t>Entry-Level Software Engineer | Remote</t>
         </is>
       </c>
-      <c r="D50" s="33" t="inlineStr">
+      <c r="D50" s="34" t="inlineStr">
         <is>
           <t>Crossing Hurdles</t>
         </is>
       </c>
-      <c r="E50" s="33" t="inlineStr">
+      <c r="E50" s="34" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3735,12 +3741,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H50" s="33" t="inlineStr">
+      <c r="H50" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I50" s="33" t="inlineStr">
+      <c r="I50" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3755,20 +3761,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L50" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M50" s="33" t="inlineStr"/>
+      <c r="L50" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M50" s="34" t="inlineStr"/>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="32" t="inlineStr">
+      <c r="A51" s="35" t="inlineStr">
         <is>
           <t>4309699451</t>
         </is>
       </c>
-      <c r="B51" s="32" t="inlineStr">
+      <c r="B51" s="35" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3778,12 +3784,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D51" s="32" t="inlineStr">
+      <c r="D51" s="35" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E51" s="32" t="inlineStr">
+      <c r="E51" s="35" t="inlineStr">
         <is>
           <t>Washington, United States</t>
         </is>
@@ -3798,12 +3804,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H51" s="32" t="inlineStr">
+      <c r="H51" s="35" t="inlineStr">
         <is>
           <t>109</t>
         </is>
       </c>
-      <c r="I51" s="32" t="inlineStr">
+      <c r="I51" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3818,20 +3824,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L51" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M51" s="32" t="inlineStr"/>
+      <c r="L51" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M51" s="35" t="inlineStr"/>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="33" t="inlineStr">
+      <c r="A52" s="34" t="inlineStr">
         <is>
           <t>4406945262</t>
         </is>
       </c>
-      <c r="B52" s="33" t="inlineStr">
+      <c r="B52" s="34" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3841,12 +3847,12 @@
           <t>DevSecOps Intern</t>
         </is>
       </c>
-      <c r="D52" s="33" t="inlineStr">
+      <c r="D52" s="34" t="inlineStr">
         <is>
           <t>Modern Technology Solutions, Inc. (MTSI)</t>
         </is>
       </c>
-      <c r="E52" s="33" t="inlineStr">
+      <c r="E52" s="34" t="inlineStr">
         <is>
           <t>Niceville, FL</t>
         </is>
@@ -3861,12 +3867,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H52" s="33" t="inlineStr">
+      <c r="H52" s="34" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="I52" s="33" t="inlineStr">
+      <c r="I52" s="34" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3881,20 +3887,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L52" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M52" s="33" t="inlineStr"/>
+      <c r="L52" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M52" s="34" t="inlineStr"/>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="32" t="inlineStr">
+      <c r="A53" s="35" t="inlineStr">
         <is>
           <t>4407937810</t>
         </is>
       </c>
-      <c r="B53" s="32" t="inlineStr">
+      <c r="B53" s="35" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3904,12 +3910,12 @@
           <t>Temporary Intern - Agentic AI &amp; Neural-Symbolic Systems (Healthcare)</t>
         </is>
       </c>
-      <c r="D53" s="32" t="inlineStr">
+      <c r="D53" s="35" t="inlineStr">
         <is>
           <t>Cotiviti</t>
         </is>
       </c>
-      <c r="E53" s="32" t="inlineStr">
+      <c r="E53" s="35" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3924,12 +3930,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H53" s="32" t="inlineStr">
+      <c r="H53" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I53" s="32" t="inlineStr">
+      <c r="I53" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3944,20 +3950,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L53" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M53" s="32" t="inlineStr"/>
+      <c r="L53" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M53" s="35" t="inlineStr"/>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="33" t="inlineStr">
+      <c r="A54" s="34" t="inlineStr">
         <is>
           <t>4414089997</t>
         </is>
       </c>
-      <c r="B54" s="33" t="inlineStr">
+      <c r="B54" s="34" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3967,12 +3973,12 @@
           <t>Visualization Engineer Intern</t>
         </is>
       </c>
-      <c r="D54" s="33" t="inlineStr">
+      <c r="D54" s="34" t="inlineStr">
         <is>
           <t>Leidos</t>
         </is>
       </c>
-      <c r="E54" s="33" t="inlineStr">
+      <c r="E54" s="34" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3987,12 +3993,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H54" s="33" t="inlineStr">
+      <c r="H54" s="34" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="I54" s="33" t="inlineStr">
+      <c r="I54" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4007,20 +4013,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L54" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M54" s="33" t="inlineStr"/>
+      <c r="L54" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M54" s="34" t="inlineStr"/>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="32" t="inlineStr">
+      <c r="A55" s="35" t="inlineStr">
         <is>
           <t>4387443129</t>
         </is>
       </c>
-      <c r="B55" s="32" t="inlineStr">
+      <c r="B55" s="35" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4030,12 +4036,12 @@
           <t>2026 Interns</t>
         </is>
       </c>
-      <c r="D55" s="32" t="inlineStr">
+      <c r="D55" s="35" t="inlineStr">
         <is>
           <t>Givelify</t>
         </is>
       </c>
-      <c r="E55" s="32" t="inlineStr">
+      <c r="E55" s="35" t="inlineStr">
         <is>
           <t>Dallas, TX</t>
         </is>
@@ -4050,12 +4056,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H55" s="32" t="inlineStr">
+      <c r="H55" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I55" s="32" t="inlineStr">
+      <c r="I55" s="35" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -4070,20 +4076,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L55" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M55" s="32" t="inlineStr"/>
+      <c r="L55" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M55" s="35" t="inlineStr"/>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="33" t="inlineStr">
+      <c r="A56" s="34" t="inlineStr">
         <is>
           <t>4337980765</t>
         </is>
       </c>
-      <c r="B56" s="33" t="inlineStr">
+      <c r="B56" s="34" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4093,12 +4099,12 @@
           <t>Submitting for a General Internship Application</t>
         </is>
       </c>
-      <c r="D56" s="33" t="inlineStr">
+      <c r="D56" s="34" t="inlineStr">
         <is>
           <t>Chainguard</t>
         </is>
       </c>
-      <c r="E56" s="33" t="inlineStr">
+      <c r="E56" s="34" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4113,12 +4119,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H56" s="33" t="inlineStr">
+      <c r="H56" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I56" s="33" t="inlineStr">
+      <c r="I56" s="34" t="inlineStr">
         <is>
           <t>Volunteer</t>
         </is>
@@ -4133,20 +4139,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L56" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M56" s="33" t="inlineStr"/>
+      <c r="L56" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M56" s="34" t="inlineStr"/>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="32" t="inlineStr">
+      <c r="A57" s="35" t="inlineStr">
         <is>
           <t>4417030460</t>
         </is>
       </c>
-      <c r="B57" s="32" t="inlineStr">
+      <c r="B57" s="35" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4156,12 +4162,12 @@
           <t>AI Researcher Intern</t>
         </is>
       </c>
-      <c r="D57" s="32" t="inlineStr">
+      <c r="D57" s="35" t="inlineStr">
         <is>
           <t>BioSpace</t>
         </is>
       </c>
-      <c r="E57" s="32" t="inlineStr">
+      <c r="E57" s="35" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4176,12 +4182,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H57" s="32" t="inlineStr">
+      <c r="H57" s="35" t="inlineStr">
         <is>
           <t>151</t>
         </is>
       </c>
-      <c r="I57" s="32" t="inlineStr">
+      <c r="I57" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4196,20 +4202,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L57" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M57" s="32" t="inlineStr"/>
+      <c r="L57" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M57" s="35" t="inlineStr"/>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="33" t="inlineStr">
+      <c r="A58" s="34" t="inlineStr">
         <is>
           <t>4406930916</t>
         </is>
       </c>
-      <c r="B58" s="33" t="inlineStr">
+      <c r="B58" s="34" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4219,12 +4225,12 @@
           <t>DevSecOps Intern</t>
         </is>
       </c>
-      <c r="D58" s="33" t="inlineStr">
+      <c r="D58" s="34" t="inlineStr">
         <is>
           <t>Modern Technology Solutions, Inc. (MTSI)</t>
         </is>
       </c>
-      <c r="E58" s="33" t="inlineStr">
+      <c r="E58" s="34" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4239,12 +4245,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H58" s="33" t="inlineStr">
+      <c r="H58" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I58" s="33" t="inlineStr">
+      <c r="I58" s="34" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -4259,20 +4265,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L58" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M58" s="33" t="inlineStr"/>
+      <c r="L58" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M58" s="34" t="inlineStr"/>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="32" t="inlineStr">
+      <c r="A59" s="35" t="inlineStr">
         <is>
           <t>4385798937</t>
         </is>
       </c>
-      <c r="B59" s="32" t="inlineStr">
+      <c r="B59" s="35" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4282,12 +4288,12 @@
           <t>Research Intern on Generative and Protective AI for Content Creation</t>
         </is>
       </c>
-      <c r="D59" s="32" t="inlineStr">
+      <c r="D59" s="35" t="inlineStr">
         <is>
           <t>SonyAI</t>
         </is>
       </c>
-      <c r="E59" s="32" t="inlineStr">
+      <c r="E59" s="35" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -4302,12 +4308,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H59" s="32" t="inlineStr">
+      <c r="H59" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I59" s="32" t="inlineStr">
+      <c r="I59" s="35" t="inlineStr">
         <is>
           <t>Part-time</t>
         </is>
@@ -4322,20 +4328,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L59" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M59" s="32" t="inlineStr"/>
+      <c r="L59" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M59" s="35" t="inlineStr"/>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="33" t="inlineStr">
+      <c r="A60" s="34" t="inlineStr">
         <is>
           <t>4414396950</t>
         </is>
       </c>
-      <c r="B60" s="33" t="inlineStr">
+      <c r="B60" s="34" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4345,12 +4351,12 @@
           <t>Power Platform Intern</t>
         </is>
       </c>
-      <c r="D60" s="33" t="inlineStr">
+      <c r="D60" s="34" t="inlineStr">
         <is>
           <t>Leidos</t>
         </is>
       </c>
-      <c r="E60" s="33" t="inlineStr">
+      <c r="E60" s="34" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4365,12 +4371,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H60" s="33" t="inlineStr">
+      <c r="H60" s="34" t="inlineStr">
         <is>
           <t>135</t>
         </is>
       </c>
-      <c r="I60" s="33" t="inlineStr">
+      <c r="I60" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4385,20 +4391,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L60" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M60" s="33" t="inlineStr"/>
+      <c r="L60" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M60" s="34" t="inlineStr"/>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="32" t="inlineStr">
+      <c r="A61" s="35" t="inlineStr">
         <is>
           <t>4413699205</t>
         </is>
       </c>
-      <c r="B61" s="32" t="inlineStr">
+      <c r="B61" s="35" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4408,12 +4414,12 @@
           <t>Junior Software Engineer - Automation &amp; Integration</t>
         </is>
       </c>
-      <c r="D61" s="32" t="inlineStr">
+      <c r="D61" s="35" t="inlineStr">
         <is>
           <t>Fletcher Development LLC</t>
         </is>
       </c>
-      <c r="E61" s="32" t="inlineStr">
+      <c r="E61" s="35" t="inlineStr">
         <is>
           <t>Redding, CT</t>
         </is>
@@ -4428,12 +4434,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H61" s="32" t="inlineStr">
+      <c r="H61" s="35" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="I61" s="32" t="inlineStr">
+      <c r="I61" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4448,20 +4454,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L61" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M61" s="32" t="inlineStr"/>
+      <c r="L61" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M61" s="35" t="inlineStr"/>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="33" t="inlineStr">
+      <c r="A62" s="34" t="inlineStr">
         <is>
           <t>4416171988</t>
         </is>
       </c>
-      <c r="B62" s="33" t="inlineStr">
+      <c r="B62" s="34" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4471,12 +4477,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D62" s="33" t="inlineStr">
+      <c r="D62" s="34" t="inlineStr">
         <is>
           <t>Altec</t>
         </is>
       </c>
-      <c r="E62" s="33" t="inlineStr">
+      <c r="E62" s="34" t="inlineStr">
         <is>
           <t>Birmingham, AL</t>
         </is>
@@ -4491,12 +4497,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H62" s="33" t="inlineStr">
+      <c r="H62" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I62" s="33" t="inlineStr">
+      <c r="I62" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4511,20 +4517,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L62" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M62" s="33" t="inlineStr"/>
+      <c r="L62" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M62" s="34" t="inlineStr"/>
     </row>
     <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="32" t="inlineStr">
+      <c r="A63" s="35" t="inlineStr">
         <is>
           <t>4403444963</t>
         </is>
       </c>
-      <c r="B63" s="32" t="inlineStr">
+      <c r="B63" s="35" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4534,12 +4540,12 @@
           <t>Junior Applications Developer (NY HELPS) #2026-252</t>
         </is>
       </c>
-      <c r="D63" s="32" t="inlineStr">
+      <c r="D63" s="35" t="inlineStr">
         <is>
           <t>Capital Region BOCES</t>
         </is>
       </c>
-      <c r="E63" s="32" t="inlineStr">
+      <c r="E63" s="35" t="inlineStr">
         <is>
           <t>Albany, NY</t>
         </is>
@@ -4554,12 +4560,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H63" s="32" t="inlineStr">
+      <c r="H63" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I63" s="32" t="inlineStr">
+      <c r="I63" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4574,20 +4580,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L63" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M63" s="32" t="inlineStr"/>
+      <c r="L63" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M63" s="35" t="inlineStr"/>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="33" t="inlineStr">
+      <c r="A64" s="34" t="inlineStr">
         <is>
           <t>4418506121</t>
         </is>
       </c>
-      <c r="B64" s="33" t="inlineStr">
+      <c r="B64" s="34" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4597,12 +4603,12 @@
           <t>Core System Junior Developer</t>
         </is>
       </c>
-      <c r="D64" s="33" t="inlineStr">
+      <c r="D64" s="34" t="inlineStr">
         <is>
           <t>Cyprus Federal Credit Union</t>
         </is>
       </c>
-      <c r="E64" s="33" t="inlineStr">
+      <c r="E64" s="34" t="inlineStr">
         <is>
           <t>West Jordan, UT</t>
         </is>
@@ -4617,12 +4623,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H64" s="33" t="inlineStr">
+      <c r="H64" s="34" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="I64" s="33" t="inlineStr">
+      <c r="I64" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4637,20 +4643,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L64" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M64" s="33" t="inlineStr"/>
+      <c r="L64" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M64" s="34" t="inlineStr"/>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="32" t="inlineStr">
+      <c r="A65" s="35" t="inlineStr">
         <is>
           <t>4413905706</t>
         </is>
       </c>
-      <c r="B65" s="32" t="inlineStr">
+      <c r="B65" s="35" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4660,12 +4666,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D65" s="32" t="inlineStr">
+      <c r="D65" s="35" t="inlineStr">
         <is>
           <t>Arnex Solutions LLC</t>
         </is>
       </c>
-      <c r="E65" s="32" t="inlineStr">
+      <c r="E65" s="35" t="inlineStr">
         <is>
           <t>Princeton, NJ</t>
         </is>
@@ -4680,12 +4686,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H65" s="32" t="inlineStr">
+      <c r="H65" s="35" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I65" s="32" t="inlineStr">
+      <c r="I65" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4700,20 +4706,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L65" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M65" s="32" t="inlineStr"/>
+      <c r="L65" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M65" s="35" t="inlineStr"/>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="33" t="inlineStr">
+      <c r="A66" s="34" t="inlineStr">
         <is>
           <t>4418963446</t>
         </is>
       </c>
-      <c r="B66" s="33" t="inlineStr">
+      <c r="B66" s="34" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4723,12 +4729,12 @@
           <t>Junior Software Engineer - Automation &amp; Integration</t>
         </is>
       </c>
-      <c r="D66" s="33" t="inlineStr">
+      <c r="D66" s="34" t="inlineStr">
         <is>
           <t>Vibrant Building Technologies</t>
         </is>
       </c>
-      <c r="E66" s="33" t="inlineStr">
+      <c r="E66" s="34" t="inlineStr">
         <is>
           <t>Ridgefield, CT</t>
         </is>
@@ -4743,12 +4749,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H66" s="33" t="inlineStr">
+      <c r="H66" s="34" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="I66" s="33" t="inlineStr">
+      <c r="I66" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4763,20 +4769,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L66" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M66" s="33" t="inlineStr"/>
+      <c r="L66" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M66" s="34" t="inlineStr"/>
     </row>
     <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="32" t="inlineStr">
+      <c r="A67" s="35" t="inlineStr">
         <is>
           <t>4413759052</t>
         </is>
       </c>
-      <c r="B67" s="32" t="inlineStr">
+      <c r="B67" s="35" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4786,12 +4792,12 @@
           <t>Junior Full Stack Developer</t>
         </is>
       </c>
-      <c r="D67" s="32" t="inlineStr">
+      <c r="D67" s="35" t="inlineStr">
         <is>
           <t>Allied World Reinsurance Company</t>
         </is>
       </c>
-      <c r="E67" s="32" t="inlineStr">
+      <c r="E67" s="35" t="inlineStr">
         <is>
           <t>Iselin, NJ</t>
         </is>
@@ -4806,12 +4812,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H67" s="32" t="inlineStr">
+      <c r="H67" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I67" s="32" t="inlineStr">
+      <c r="I67" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4826,20 +4832,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L67" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M67" s="32" t="inlineStr"/>
+      <c r="L67" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M67" s="35" t="inlineStr"/>
     </row>
     <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="33" t="inlineStr">
+      <c r="A68" s="34" t="inlineStr">
         <is>
           <t>4417542502</t>
         </is>
       </c>
-      <c r="B68" s="33" t="inlineStr">
+      <c r="B68" s="34" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4849,12 +4855,12 @@
           <t>Junior Developer</t>
         </is>
       </c>
-      <c r="D68" s="33" t="inlineStr">
+      <c r="D68" s="34" t="inlineStr">
         <is>
           <t>CloudMasonry</t>
         </is>
       </c>
-      <c r="E68" s="33" t="inlineStr">
+      <c r="E68" s="34" t="inlineStr">
         <is>
           <t>Indianapolis, IN</t>
         </is>
@@ -4869,12 +4875,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H68" s="33" t="inlineStr">
+      <c r="H68" s="34" t="inlineStr">
         <is>
           <t>154</t>
         </is>
       </c>
-      <c r="I68" s="33" t="inlineStr">
+      <c r="I68" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4889,20 +4895,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L68" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M68" s="33" t="inlineStr"/>
+      <c r="L68" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M68" s="34" t="inlineStr"/>
     </row>
     <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="32" t="inlineStr">
+      <c r="A69" s="35" t="inlineStr">
         <is>
           <t>4374856035</t>
         </is>
       </c>
-      <c r="B69" s="32" t="inlineStr">
+      <c r="B69" s="35" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4912,12 +4918,12 @@
           <t>Programmer II</t>
         </is>
       </c>
-      <c r="D69" s="32" t="inlineStr">
+      <c r="D69" s="35" t="inlineStr">
         <is>
           <t>Willis Knighton Health</t>
         </is>
       </c>
-      <c r="E69" s="32" t="inlineStr">
+      <c r="E69" s="35" t="inlineStr">
         <is>
           <t>Louisiana, United States</t>
         </is>
@@ -4932,12 +4938,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H69" s="32" t="inlineStr">
+      <c r="H69" s="35" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="I69" s="32" t="inlineStr">
+      <c r="I69" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4952,20 +4958,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L69" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M69" s="32" t="inlineStr"/>
+      <c r="L69" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M69" s="35" t="inlineStr"/>
     </row>
     <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="33" t="inlineStr">
+      <c r="A70" s="34" t="inlineStr">
         <is>
           <t>4416302564</t>
         </is>
       </c>
-      <c r="B70" s="33" t="inlineStr">
+      <c r="B70" s="34" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4975,12 +4981,12 @@
           <t>Software Engineer I</t>
         </is>
       </c>
-      <c r="D70" s="33" t="inlineStr">
+      <c r="D70" s="34" t="inlineStr">
         <is>
           <t>American Express</t>
         </is>
       </c>
-      <c r="E70" s="33" t="inlineStr">
+      <c r="E70" s="34" t="inlineStr">
         <is>
           <t>Sunrise, FL</t>
         </is>
@@ -4995,12 +5001,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H70" s="33" t="inlineStr">
+      <c r="H70" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I70" s="33" t="inlineStr">
+      <c r="I70" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5015,20 +5021,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L70" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M70" s="33" t="inlineStr"/>
+      <c r="L70" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M70" s="34" t="inlineStr"/>
     </row>
     <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="32" t="inlineStr">
+      <c r="A71" s="35" t="inlineStr">
         <is>
           <t>4417014137</t>
         </is>
       </c>
-      <c r="B71" s="32" t="inlineStr">
+      <c r="B71" s="35" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5038,12 +5044,12 @@
           <t>Junior Software Developer, Applications</t>
         </is>
       </c>
-      <c r="D71" s="32" t="inlineStr">
+      <c r="D71" s="35" t="inlineStr">
         <is>
           <t>ECS</t>
         </is>
       </c>
-      <c r="E71" s="32" t="inlineStr">
+      <c r="E71" s="35" t="inlineStr">
         <is>
           <t>O'Fallon, IL</t>
         </is>
@@ -5058,12 +5064,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H71" s="32" t="inlineStr">
+      <c r="H71" s="35" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="I71" s="32" t="inlineStr">
+      <c r="I71" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5078,20 +5084,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr"/>
+      <c r="L71" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M71" s="35" t="inlineStr"/>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="33" t="inlineStr">
+      <c r="A72" s="34" t="inlineStr">
         <is>
           <t>4381211472</t>
         </is>
       </c>
-      <c r="B72" s="33" t="inlineStr">
+      <c r="B72" s="34" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5101,12 +5107,12 @@
           <t>Programmer</t>
         </is>
       </c>
-      <c r="D72" s="33" t="inlineStr">
+      <c r="D72" s="34" t="inlineStr">
         <is>
           <t>City of New York</t>
         </is>
       </c>
-      <c r="E72" s="33" t="inlineStr">
+      <c r="E72" s="34" t="inlineStr">
         <is>
           <t>Bronx, NY</t>
         </is>
@@ -5121,12 +5127,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H72" s="33" t="inlineStr">
+      <c r="H72" s="34" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="I72" s="33" t="inlineStr">
+      <c r="I72" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5141,20 +5147,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L72" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M72" s="33" t="inlineStr"/>
+      <c r="L72" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M72" s="34" t="inlineStr"/>
     </row>
     <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="32" t="inlineStr">
+      <c r="A73" s="35" t="inlineStr">
         <is>
           <t>4168416236</t>
         </is>
       </c>
-      <c r="B73" s="32" t="inlineStr">
+      <c r="B73" s="35" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5164,12 +5170,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D73" s="32" t="inlineStr">
+      <c r="D73" s="35" t="inlineStr">
         <is>
           <t>Interclypse</t>
         </is>
       </c>
-      <c r="E73" s="32" t="inlineStr">
+      <c r="E73" s="35" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
@@ -5184,12 +5190,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H73" s="32" t="inlineStr">
+      <c r="H73" s="35" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I73" s="32" t="inlineStr">
+      <c r="I73" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5204,20 +5210,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr"/>
+      <c r="L73" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M73" s="35" t="inlineStr"/>
     </row>
     <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="33" t="inlineStr">
+      <c r="A74" s="34" t="inlineStr">
         <is>
           <t>4403507357</t>
         </is>
       </c>
-      <c r="B74" s="33" t="inlineStr">
+      <c r="B74" s="34" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5227,12 +5233,12 @@
           <t>Software Developer:</t>
         </is>
       </c>
-      <c r="D74" s="33" t="inlineStr">
+      <c r="D74" s="34" t="inlineStr">
         <is>
           <t>IQuest Solutions Corporation</t>
         </is>
       </c>
-      <c r="E74" s="33" t="inlineStr">
+      <c r="E74" s="34" t="inlineStr">
         <is>
           <t>Plano, TX</t>
         </is>
@@ -5247,12 +5253,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H74" s="33" t="inlineStr">
+      <c r="H74" s="34" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I74" s="33" t="inlineStr">
+      <c r="I74" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5267,20 +5273,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L74" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M74" s="33" t="inlineStr"/>
+      <c r="L74" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M74" s="34" t="inlineStr"/>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="32" t="inlineStr">
+      <c r="A75" s="35" t="inlineStr">
         <is>
           <t>4309800238</t>
         </is>
       </c>
-      <c r="B75" s="32" t="inlineStr">
+      <c r="B75" s="35" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5290,12 +5296,12 @@
           <t>Backend Software Engineer</t>
         </is>
       </c>
-      <c r="D75" s="32" t="inlineStr">
+      <c r="D75" s="35" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E75" s="32" t="inlineStr">
+      <c r="E75" s="35" t="inlineStr">
         <is>
           <t>Texas, United States</t>
         </is>
@@ -5310,12 +5316,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H75" s="32" t="inlineStr">
+      <c r="H75" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I75" s="32" t="inlineStr">
+      <c r="I75" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5330,20 +5336,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L75" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M75" s="32" t="inlineStr"/>
+      <c r="L75" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M75" s="35" t="inlineStr"/>
     </row>
     <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="33" t="inlineStr">
+      <c r="A76" s="34" t="inlineStr">
         <is>
           <t>4404109089</t>
         </is>
       </c>
-      <c r="B76" s="33" t="inlineStr">
+      <c r="B76" s="34" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5353,12 +5359,12 @@
           <t>Software Development Engineer I</t>
         </is>
       </c>
-      <c r="D76" s="33" t="inlineStr">
+      <c r="D76" s="34" t="inlineStr">
         <is>
           <t>GM Financial</t>
         </is>
       </c>
-      <c r="E76" s="33" t="inlineStr">
+      <c r="E76" s="34" t="inlineStr">
         <is>
           <t>Arlington, TX</t>
         </is>
@@ -5373,12 +5379,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H76" s="33" t="inlineStr">
+      <c r="H76" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I76" s="33" t="inlineStr">
+      <c r="I76" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5393,20 +5399,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L76" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M76" s="33" t="inlineStr"/>
+      <c r="L76" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M76" s="34" t="inlineStr"/>
     </row>
     <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="32" t="inlineStr">
+      <c r="A77" s="35" t="inlineStr">
         <is>
           <t>3986116411</t>
         </is>
       </c>
-      <c r="B77" s="32" t="inlineStr">
+      <c r="B77" s="35" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5416,12 +5422,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D77" s="32" t="inlineStr">
+      <c r="D77" s="35" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E77" s="32" t="inlineStr">
+      <c r="E77" s="35" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -5436,12 +5442,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H77" s="32" t="inlineStr">
+      <c r="H77" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I77" s="32" t="inlineStr">
+      <c r="I77" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5456,20 +5462,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L77" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M77" s="32" t="inlineStr"/>
+      <c r="L77" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M77" s="35" t="inlineStr"/>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="33" t="inlineStr">
+      <c r="A78" s="34" t="inlineStr">
         <is>
           <t>4418051524</t>
         </is>
       </c>
-      <c r="B78" s="33" t="inlineStr">
+      <c r="B78" s="34" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5479,12 +5485,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D78" s="33" t="inlineStr">
+      <c r="D78" s="34" t="inlineStr">
         <is>
           <t>Relativity</t>
         </is>
       </c>
-      <c r="E78" s="33" t="inlineStr">
+      <c r="E78" s="34" t="inlineStr">
         <is>
           <t>Texas, United States</t>
         </is>
@@ -5499,12 +5505,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H78" s="33" t="inlineStr">
+      <c r="H78" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I78" s="33" t="inlineStr">
+      <c r="I78" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5519,20 +5525,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L78" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M78" s="33" t="inlineStr"/>
+      <c r="L78" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M78" s="34" t="inlineStr"/>
     </row>
     <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="32" t="inlineStr">
+      <c r="A79" s="35" t="inlineStr">
         <is>
           <t>4409856693</t>
         </is>
       </c>
-      <c r="B79" s="32" t="inlineStr">
+      <c r="B79" s="35" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5542,12 +5548,12 @@
           <t>Software Engineer - Payments</t>
         </is>
       </c>
-      <c r="D79" s="32" t="inlineStr">
+      <c r="D79" s="35" t="inlineStr">
         <is>
           <t>Cloudbeds</t>
         </is>
       </c>
-      <c r="E79" s="32" t="inlineStr">
+      <c r="E79" s="35" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -5562,12 +5568,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H79" s="32" t="inlineStr">
+      <c r="H79" s="35" t="inlineStr">
         <is>
           <t>177</t>
         </is>
       </c>
-      <c r="I79" s="32" t="inlineStr">
+      <c r="I79" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5582,20 +5588,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr"/>
+      <c r="L79" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M79" s="35" t="inlineStr"/>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="33" t="inlineStr">
+      <c r="A80" s="34" t="inlineStr">
         <is>
           <t>3986111771</t>
         </is>
       </c>
-      <c r="B80" s="33" t="inlineStr">
+      <c r="B80" s="34" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5605,12 +5611,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D80" s="33" t="inlineStr">
+      <c r="D80" s="34" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E80" s="33" t="inlineStr">
+      <c r="E80" s="34" t="inlineStr">
         <is>
           <t>Carrollton, TX</t>
         </is>
@@ -5625,12 +5631,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H80" s="33" t="inlineStr">
+      <c r="H80" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I80" s="33" t="inlineStr">
+      <c r="I80" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5645,20 +5651,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L80" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M80" s="33" t="inlineStr"/>
+      <c r="L80" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M80" s="34" t="inlineStr"/>
     </row>
     <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="32" t="inlineStr">
+      <c r="A81" s="35" t="inlineStr">
         <is>
           <t>4417160720</t>
         </is>
       </c>
-      <c r="B81" s="32" t="inlineStr">
+      <c r="B81" s="35" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5668,12 +5674,12 @@
           <t>Full-Stack AI Developer</t>
         </is>
       </c>
-      <c r="D81" s="32" t="inlineStr">
+      <c r="D81" s="35" t="inlineStr">
         <is>
           <t>AnswerMyQ</t>
         </is>
       </c>
-      <c r="E81" s="32" t="inlineStr">
+      <c r="E81" s="35" t="inlineStr">
         <is>
           <t>Austin, Texas Metropolitan Area</t>
         </is>
@@ -5688,12 +5694,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H81" s="32" t="inlineStr">
+      <c r="H81" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I81" s="32" t="inlineStr">
+      <c r="I81" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5708,20 +5714,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr"/>
+      <c r="L81" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M81" s="35" t="inlineStr"/>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="33" t="inlineStr">
+      <c r="A82" s="34" t="inlineStr">
         <is>
           <t>4418507307</t>
         </is>
       </c>
-      <c r="B82" s="33" t="inlineStr">
+      <c r="B82" s="34" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -5731,12 +5737,12 @@
           <t>Entry Level Software Engineer Intern</t>
         </is>
       </c>
-      <c r="D82" s="33" t="inlineStr">
+      <c r="D82" s="34" t="inlineStr">
         <is>
           <t>CORMAC</t>
         </is>
       </c>
-      <c r="E82" s="33" t="inlineStr">
+      <c r="E82" s="34" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -5751,12 +5757,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H82" s="33" t="inlineStr">
+      <c r="H82" s="34" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="I82" s="33" t="inlineStr">
+      <c r="I82" s="34" t="inlineStr">
         <is>
           <t>Volunteer</t>
         </is>
@@ -5771,20 +5777,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L82" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M82" s="33" t="inlineStr"/>
+      <c r="L82" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M82" s="34" t="inlineStr"/>
     </row>
     <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="32" t="inlineStr">
+      <c r="A83" s="35" t="inlineStr">
         <is>
           <t>4413360938</t>
         </is>
       </c>
-      <c r="B83" s="32" t="inlineStr">
+      <c r="B83" s="35" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -5794,12 +5800,12 @@
           <t>Software Engineer Internship (Remote)</t>
         </is>
       </c>
-      <c r="D83" s="32" t="inlineStr">
+      <c r="D83" s="35" t="inlineStr">
         <is>
           <t>Orange Trail</t>
         </is>
       </c>
-      <c r="E83" s="32" t="inlineStr">
+      <c r="E83" s="35" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -5814,12 +5820,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H83" s="32" t="inlineStr">
+      <c r="H83" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I83" s="32" t="inlineStr">
+      <c r="I83" s="35" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -5834,20 +5840,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L83" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M83" s="32" t="inlineStr"/>
+      <c r="L83" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M83" s="35" t="inlineStr"/>
     </row>
     <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="33" t="inlineStr">
+      <c r="A84" s="34" t="inlineStr">
         <is>
           <t>4348111641</t>
         </is>
       </c>
-      <c r="B84" s="33" t="inlineStr">
+      <c r="B84" s="34" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -5857,12 +5863,12 @@
           <t>Software Engineer Intern</t>
         </is>
       </c>
-      <c r="D84" s="33" t="inlineStr">
+      <c r="D84" s="34" t="inlineStr">
         <is>
           <t>Simular</t>
         </is>
       </c>
-      <c r="E84" s="33" t="inlineStr">
+      <c r="E84" s="34" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -5877,12 +5883,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H84" s="33" t="inlineStr">
+      <c r="H84" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I84" s="33" t="inlineStr">
+      <c r="I84" s="34" t="inlineStr">
         <is>
           <t>Volunteer</t>
         </is>
@@ -5897,20 +5903,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L84" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M84" s="33" t="inlineStr"/>
+      <c r="L84" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M84" s="34" t="inlineStr"/>
     </row>
     <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="32" t="inlineStr">
+      <c r="A85" s="35" t="inlineStr">
         <is>
           <t>4411853543</t>
         </is>
       </c>
-      <c r="B85" s="32" t="inlineStr">
+      <c r="B85" s="35" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -5920,12 +5926,12 @@
           <t>Intern, Software Engineer</t>
         </is>
       </c>
-      <c r="D85" s="32" t="inlineStr">
+      <c r="D85" s="35" t="inlineStr">
         <is>
           <t>Accelerate Learning</t>
         </is>
       </c>
-      <c r="E85" s="32" t="inlineStr">
+      <c r="E85" s="35" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -5940,12 +5946,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H85" s="32" t="inlineStr">
+      <c r="H85" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I85" s="32" t="inlineStr">
+      <c r="I85" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5960,20 +5966,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L85" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M85" s="32" t="inlineStr"/>
+      <c r="L85" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M85" s="35" t="inlineStr"/>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="33" t="inlineStr">
+      <c r="A86" s="34" t="inlineStr">
         <is>
           <t>4408586245</t>
         </is>
       </c>
-      <c r="B86" s="33" t="inlineStr">
+      <c r="B86" s="34" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -5983,12 +5989,12 @@
           <t>Junior Software Engineer Intern</t>
         </is>
       </c>
-      <c r="D86" s="33" t="inlineStr">
+      <c r="D86" s="34" t="inlineStr">
         <is>
           <t>Cantaloupe Inc</t>
         </is>
       </c>
-      <c r="E86" s="33" t="inlineStr">
+      <c r="E86" s="34" t="inlineStr">
         <is>
           <t>Atlanta, GA</t>
         </is>
@@ -6003,12 +6009,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H86" s="33" t="inlineStr">
+      <c r="H86" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I86" s="33" t="inlineStr">
+      <c r="I86" s="34" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -6023,20 +6029,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L86" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M86" s="33" t="inlineStr"/>
+      <c r="L86" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M86" s="34" t="inlineStr"/>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="32" t="inlineStr">
+      <c r="A87" s="35" t="inlineStr">
         <is>
           <t>4364536992</t>
         </is>
       </c>
-      <c r="B87" s="32" t="inlineStr">
+      <c r="B87" s="35" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -6046,12 +6052,12 @@
           <t>Summer Internship - Measurement, Research and Development - Academic Measurement</t>
         </is>
       </c>
-      <c r="D87" s="32" t="inlineStr">
+      <c r="D87" s="35" t="inlineStr">
         <is>
           <t>ChatGPT Jobs</t>
         </is>
       </c>
-      <c r="E87" s="32" t="inlineStr">
+      <c r="E87" s="35" t="inlineStr">
         <is>
           <t>Iowa City, IA</t>
         </is>
@@ -6066,12 +6072,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H87" s="32" t="inlineStr">
+      <c r="H87" s="35" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I87" s="32" t="inlineStr">
+      <c r="I87" s="35" t="inlineStr">
         <is>
           <t>Volunteer</t>
         </is>
@@ -6086,20 +6092,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L87" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M87" s="32" t="inlineStr"/>
+      <c r="L87" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M87" s="35" t="inlineStr"/>
     </row>
     <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="33" t="inlineStr">
+      <c r="A88" s="34" t="inlineStr">
         <is>
           <t>4413206045</t>
         </is>
       </c>
-      <c r="B88" s="33" t="inlineStr">
+      <c r="B88" s="34" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6109,12 +6115,12 @@
           <t>Software Development Engineer, EC2 Nitro Specialized Instances</t>
         </is>
       </c>
-      <c r="D88" s="33" t="inlineStr">
+      <c r="D88" s="34" t="inlineStr">
         <is>
           <t>Amazon Web Services (AWS)</t>
         </is>
       </c>
-      <c r="E88" s="33" t="inlineStr">
+      <c r="E88" s="34" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6129,12 +6135,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H88" s="33" t="inlineStr">
+      <c r="H88" s="34" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I88" s="33" t="inlineStr">
+      <c r="I88" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6149,20 +6155,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L88" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M88" s="33" t="inlineStr"/>
+      <c r="L88" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M88" s="34" t="inlineStr"/>
     </row>
     <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="32" t="inlineStr">
+      <c r="A89" s="35" t="inlineStr">
         <is>
           <t>4383211797</t>
         </is>
       </c>
-      <c r="B89" s="32" t="inlineStr">
+      <c r="B89" s="35" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6172,12 +6178,12 @@
           <t>software development engineer</t>
         </is>
       </c>
-      <c r="D89" s="32" t="inlineStr">
+      <c r="D89" s="35" t="inlineStr">
         <is>
           <t>Abacus Business Computer</t>
         </is>
       </c>
-      <c r="E89" s="32" t="inlineStr">
+      <c r="E89" s="35" t="inlineStr">
         <is>
           <t>Queens, NY</t>
         </is>
@@ -6192,12 +6198,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H89" s="32" t="inlineStr">
+      <c r="H89" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I89" s="32" t="inlineStr">
+      <c r="I89" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6212,20 +6218,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L89" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M89" s="32" t="inlineStr"/>
+      <c r="L89" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M89" s="35" t="inlineStr"/>
     </row>
     <row r="90" ht="18" customHeight="1">
-      <c r="A90" s="33" t="inlineStr">
+      <c r="A90" s="34" t="inlineStr">
         <is>
           <t>4418169749</t>
         </is>
       </c>
-      <c r="B90" s="33" t="inlineStr">
+      <c r="B90" s="34" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6235,12 +6241,12 @@
           <t>AI/ML Engineering Intern</t>
         </is>
       </c>
-      <c r="D90" s="33" t="inlineStr">
+      <c r="D90" s="34" t="inlineStr">
         <is>
           <t>Daice Labs</t>
         </is>
       </c>
-      <c r="E90" s="33" t="inlineStr">
+      <c r="E90" s="34" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -6255,12 +6261,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H90" s="33" t="inlineStr">
+      <c r="H90" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I90" s="33" t="inlineStr">
+      <c r="I90" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6275,20 +6281,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L90" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M90" s="33" t="inlineStr"/>
+      <c r="L90" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M90" s="34" t="inlineStr"/>
     </row>
     <row r="91" ht="18" customHeight="1">
-      <c r="A91" s="32" t="inlineStr">
+      <c r="A91" s="35" t="inlineStr">
         <is>
           <t>4281120416</t>
         </is>
       </c>
-      <c r="B91" s="32" t="inlineStr">
+      <c r="B91" s="35" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6298,12 +6304,12 @@
           <t>Site Reliability Engineer Intern (Compute Platform) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D91" s="32" t="inlineStr">
+      <c r="D91" s="35" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E91" s="32" t="inlineStr">
+      <c r="E91" s="35" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6318,12 +6324,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H91" s="32" t="inlineStr">
+      <c r="H91" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I91" s="32" t="inlineStr">
+      <c r="I91" s="35" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -6338,20 +6344,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L91" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M91" s="32" t="inlineStr"/>
+      <c r="L91" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M91" s="35" t="inlineStr"/>
     </row>
     <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="33" t="inlineStr">
+      <c r="A92" s="34" t="inlineStr">
         <is>
           <t>4377549744</t>
         </is>
       </c>
-      <c r="B92" s="33" t="inlineStr">
+      <c r="B92" s="34" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6361,12 +6367,12 @@
           <t>Software Development Engineer Apprentice - Military Veterans</t>
         </is>
       </c>
-      <c r="D92" s="33" t="inlineStr">
+      <c r="D92" s="34" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E92" s="33" t="inlineStr">
+      <c r="E92" s="34" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -6381,12 +6387,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H92" s="33" t="inlineStr">
+      <c r="H92" s="34" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="I92" s="33" t="inlineStr">
+      <c r="I92" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6401,20 +6407,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L92" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M92" s="33" t="inlineStr"/>
+      <c r="L92" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M92" s="34" t="inlineStr"/>
     </row>
     <row r="93" ht="18" customHeight="1">
-      <c r="A93" s="32" t="inlineStr">
+      <c r="A93" s="35" t="inlineStr">
         <is>
           <t>4377564429</t>
         </is>
       </c>
-      <c r="B93" s="32" t="inlineStr">
+      <c r="B93" s="35" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6424,12 +6430,12 @@
           <t>Software Development Engineer Apprentice - Military Veterans</t>
         </is>
       </c>
-      <c r="D93" s="32" t="inlineStr">
+      <c r="D93" s="35" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E93" s="32" t="inlineStr">
+      <c r="E93" s="35" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6444,12 +6450,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H93" s="32" t="inlineStr">
+      <c r="H93" s="35" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="I93" s="32" t="inlineStr">
+      <c r="I93" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6464,20 +6470,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L93" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M93" s="32" t="inlineStr"/>
+      <c r="L93" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M93" s="35" t="inlineStr"/>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="A94" s="33" t="inlineStr">
+      <c r="A94" s="34" t="inlineStr">
         <is>
           <t>4413206046</t>
         </is>
       </c>
-      <c r="B94" s="33" t="inlineStr">
+      <c r="B94" s="34" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6487,12 +6493,12 @@
           <t>Software Development Engineer, Vendor Funding</t>
         </is>
       </c>
-      <c r="D94" s="33" t="inlineStr">
+      <c r="D94" s="34" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E94" s="33" t="inlineStr">
+      <c r="E94" s="34" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6507,12 +6513,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H94" s="33" t="inlineStr">
+      <c r="H94" s="34" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I94" s="33" t="inlineStr">
+      <c r="I94" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6527,20 +6533,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L94" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M94" s="33" t="inlineStr"/>
+      <c r="L94" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M94" s="34" t="inlineStr"/>
     </row>
     <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="32" t="inlineStr">
+      <c r="A95" s="35" t="inlineStr">
         <is>
           <t>4408778227</t>
         </is>
       </c>
-      <c r="B95" s="32" t="inlineStr">
+      <c r="B95" s="35" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6550,12 +6556,12 @@
           <t>Front-End Engineer Fall Internship – 2026 (US)</t>
         </is>
       </c>
-      <c r="D95" s="32" t="inlineStr">
+      <c r="D95" s="35" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E95" s="32" t="inlineStr">
+      <c r="E95" s="35" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6570,12 +6576,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H95" s="32" t="inlineStr">
+      <c r="H95" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I95" s="32" t="inlineStr">
+      <c r="I95" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6590,20 +6596,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L95" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M95" s="32" t="inlineStr"/>
+      <c r="L95" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M95" s="35" t="inlineStr"/>
     </row>
     <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="33" t="inlineStr">
+      <c r="A96" s="34" t="inlineStr">
         <is>
           <t>4281117648</t>
         </is>
       </c>
-      <c r="B96" s="33" t="inlineStr">
+      <c r="B96" s="34" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6613,12 +6619,12 @@
           <t>Data Engineer Intern (E-commerce) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D96" s="33" t="inlineStr">
+      <c r="D96" s="34" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E96" s="33" t="inlineStr">
+      <c r="E96" s="34" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6633,12 +6639,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H96" s="33" t="inlineStr">
+      <c r="H96" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I96" s="33" t="inlineStr">
+      <c r="I96" s="34" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -6653,20 +6659,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L96" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M96" s="33" t="inlineStr"/>
+      <c r="L96" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M96" s="34" t="inlineStr"/>
     </row>
     <row r="97" ht="18" customHeight="1">
-      <c r="A97" s="32" t="inlineStr">
+      <c r="A97" s="35" t="inlineStr">
         <is>
           <t>4407126060</t>
         </is>
       </c>
-      <c r="B97" s="32" t="inlineStr">
+      <c r="B97" s="35" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6676,12 +6682,12 @@
           <t>Site Reliability Engineer Intern (Data Infrastructure) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D97" s="32" t="inlineStr">
+      <c r="D97" s="35" t="inlineStr">
         <is>
           <t>ByteDance</t>
         </is>
       </c>
-      <c r="E97" s="32" t="inlineStr">
+      <c r="E97" s="35" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6696,12 +6702,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H97" s="32" t="inlineStr">
+      <c r="H97" s="35" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="I97" s="32" t="inlineStr">
+      <c r="I97" s="35" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -6716,20 +6722,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L97" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M97" s="32" t="inlineStr"/>
+      <c r="L97" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M97" s="35" t="inlineStr"/>
     </row>
     <row r="98" ht="18" customHeight="1">
-      <c r="A98" s="33" t="inlineStr">
+      <c r="A98" s="34" t="inlineStr">
         <is>
           <t>4392432360</t>
         </is>
       </c>
-      <c r="B98" s="33" t="inlineStr">
+      <c r="B98" s="34" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6739,12 +6745,12 @@
           <t>Software Engineer Intern (AI Model Optimization) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D98" s="33" t="inlineStr">
+      <c r="D98" s="34" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E98" s="33" t="inlineStr">
+      <c r="E98" s="34" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6759,12 +6765,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H98" s="33" t="inlineStr">
+      <c r="H98" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I98" s="33" t="inlineStr">
+      <c r="I98" s="34" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -6779,20 +6785,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L98" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M98" s="33" t="inlineStr"/>
+      <c r="L98" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M98" s="34" t="inlineStr"/>
     </row>
     <row r="99" ht="18" customHeight="1">
-      <c r="A99" s="32" t="inlineStr">
+      <c r="A99" s="35" t="inlineStr">
         <is>
           <t>4341279371</t>
         </is>
       </c>
-      <c r="B99" s="32" t="inlineStr">
+      <c r="B99" s="35" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6802,12 +6808,12 @@
           <t>Robotics - Software Development Engineer Intern/Co-op - 2026</t>
         </is>
       </c>
-      <c r="D99" s="32" t="inlineStr">
+      <c r="D99" s="35" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E99" s="32" t="inlineStr">
+      <c r="E99" s="35" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6822,12 +6828,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H99" s="32" t="inlineStr">
+      <c r="H99" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I99" s="32" t="inlineStr">
+      <c r="I99" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6842,20 +6848,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L99" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M99" s="32" t="inlineStr"/>
+      <c r="L99" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M99" s="35" t="inlineStr"/>
     </row>
     <row r="100" ht="18" customHeight="1">
-      <c r="A100" s="33" t="inlineStr">
+      <c r="A100" s="34" t="inlineStr">
         <is>
           <t>4417646890</t>
         </is>
       </c>
-      <c r="B100" s="33" t="inlineStr">
+      <c r="B100" s="34" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6865,12 +6871,12 @@
           <t>Software Engineer II</t>
         </is>
       </c>
-      <c r="D100" s="33" t="inlineStr">
+      <c r="D100" s="34" t="inlineStr">
         <is>
           <t>Compass</t>
         </is>
       </c>
-      <c r="E100" s="33" t="inlineStr">
+      <c r="E100" s="34" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6885,12 +6891,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H100" s="33" t="inlineStr">
+      <c r="H100" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I100" s="33" t="inlineStr">
+      <c r="I100" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6905,20 +6911,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L100" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M100" s="33" t="inlineStr"/>
+      <c r="L100" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M100" s="34" t="inlineStr"/>
     </row>
     <row r="101" ht="18" customHeight="1">
-      <c r="A101" s="32" t="inlineStr">
+      <c r="A101" s="35" t="inlineStr">
         <is>
           <t>4417565729</t>
         </is>
       </c>
-      <c r="B101" s="32" t="inlineStr">
+      <c r="B101" s="35" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6928,12 +6934,12 @@
           <t>software engineer- ST, Seattle, WA</t>
         </is>
       </c>
-      <c r="D101" s="32" t="inlineStr">
+      <c r="D101" s="35" t="inlineStr">
         <is>
           <t>Starbucks</t>
         </is>
       </c>
-      <c r="E101" s="32" t="inlineStr">
+      <c r="E101" s="35" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6948,12 +6954,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H101" s="32" t="inlineStr">
+      <c r="H101" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I101" s="32" t="inlineStr">
+      <c r="I101" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6968,20 +6974,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L101" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M101" s="32" t="inlineStr"/>
+      <c r="L101" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M101" s="35" t="inlineStr"/>
     </row>
     <row r="102" ht="18" customHeight="1">
-      <c r="A102" s="33" t="inlineStr">
+      <c r="A102" s="34" t="inlineStr">
         <is>
           <t>4420492781</t>
         </is>
       </c>
-      <c r="B102" s="33" t="inlineStr">
+      <c r="B102" s="34" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6991,12 +6997,12 @@
           <t>Software Engineer (Starlink Mobile)</t>
         </is>
       </c>
-      <c r="D102" s="33" t="inlineStr">
+      <c r="D102" s="34" t="inlineStr">
         <is>
           <t>SpaceX</t>
         </is>
       </c>
-      <c r="E102" s="33" t="inlineStr">
+      <c r="E102" s="34" t="inlineStr">
         <is>
           <t>Redmond, WA</t>
         </is>
@@ -7011,12 +7017,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H102" s="33" t="inlineStr">
+      <c r="H102" s="34" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="I102" s="33" t="inlineStr">
+      <c r="I102" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7031,20 +7037,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L102" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M102" s="33" t="inlineStr"/>
+      <c r="L102" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M102" s="34" t="inlineStr"/>
     </row>
     <row r="103" ht="18" customHeight="1">
-      <c r="A103" s="32" t="inlineStr">
+      <c r="A103" s="35" t="inlineStr">
         <is>
           <t>4418203886</t>
         </is>
       </c>
-      <c r="B103" s="32" t="inlineStr">
+      <c r="B103" s="35" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -7054,12 +7060,12 @@
           <t>System Software Engineer - Performance</t>
         </is>
       </c>
-      <c r="D103" s="32" t="inlineStr">
+      <c r="D103" s="35" t="inlineStr">
         <is>
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="E103" s="32" t="inlineStr">
+      <c r="E103" s="35" t="inlineStr">
         <is>
           <t>Redmond, WA</t>
         </is>
@@ -7074,12 +7080,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H103" s="32" t="inlineStr">
+      <c r="H103" s="35" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
-      <c r="I103" s="32" t="inlineStr">
+      <c r="I103" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7094,20 +7100,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L103" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M103" s="32" t="inlineStr"/>
+      <c r="L103" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M103" s="35" t="inlineStr"/>
     </row>
     <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="33" t="inlineStr">
+      <c r="A104" s="34" t="inlineStr">
         <is>
           <t>4332886298</t>
         </is>
       </c>
-      <c r="B104" s="33" t="inlineStr">
+      <c r="B104" s="34" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -7117,12 +7123,12 @@
           <t>Software Engineer - AI Travel Agent</t>
         </is>
       </c>
-      <c r="D104" s="33" t="inlineStr">
+      <c r="D104" s="34" t="inlineStr">
         <is>
           <t>Axel</t>
         </is>
       </c>
-      <c r="E104" s="33" t="inlineStr">
+      <c r="E104" s="34" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -7137,12 +7143,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H104" s="33" t="inlineStr">
+      <c r="H104" s="34" t="inlineStr">
         <is>
           <t>163</t>
         </is>
       </c>
-      <c r="I104" s="33" t="inlineStr">
+      <c r="I104" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7157,20 +7163,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L104" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M104" s="33" t="inlineStr"/>
+      <c r="L104" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M104" s="34" t="inlineStr"/>
     </row>
     <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="32" t="inlineStr">
+      <c r="A105" s="35" t="inlineStr">
         <is>
           <t>4388596468</t>
         </is>
       </c>
-      <c r="B105" s="32" t="inlineStr">
+      <c r="B105" s="35" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -7180,12 +7186,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D105" s="32" t="inlineStr">
+      <c r="D105" s="35" t="inlineStr">
         <is>
           <t>Capgemini</t>
         </is>
       </c>
-      <c r="E105" s="32" t="inlineStr">
+      <c r="E105" s="35" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -7200,12 +7206,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H105" s="32" t="inlineStr">
+      <c r="H105" s="35" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="I105" s="32" t="inlineStr">
+      <c r="I105" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7220,20 +7226,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L105" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M105" s="32" t="inlineStr"/>
+      <c r="L105" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M105" s="35" t="inlineStr"/>
     </row>
     <row r="106" ht="18" customHeight="1">
-      <c r="A106" s="33" t="inlineStr">
+      <c r="A106" s="34" t="inlineStr">
         <is>
           <t>4419517103</t>
         </is>
       </c>
-      <c r="B106" s="33" t="inlineStr">
+      <c r="B106" s="34" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -7243,12 +7249,12 @@
           <t>Software Engineer II</t>
         </is>
       </c>
-      <c r="D106" s="33" t="inlineStr">
+      <c r="D106" s="34" t="inlineStr">
         <is>
           <t>Chewy</t>
         </is>
       </c>
-      <c r="E106" s="33" t="inlineStr">
+      <c r="E106" s="34" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -7263,12 +7269,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H106" s="33" t="inlineStr">
+      <c r="H106" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I106" s="33" t="inlineStr">
+      <c r="I106" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7283,20 +7289,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L106" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M106" s="33" t="inlineStr"/>
+      <c r="L106" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M106" s="34" t="inlineStr"/>
     </row>
     <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="32" t="inlineStr">
+      <c r="A107" s="35" t="inlineStr">
         <is>
           <t>4395225418</t>
         </is>
       </c>
-      <c r="B107" s="32" t="inlineStr">
+      <c r="B107" s="35" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -7306,12 +7312,12 @@
           <t>Software Engineer - Backend</t>
         </is>
       </c>
-      <c r="D107" s="32" t="inlineStr">
+      <c r="D107" s="35" t="inlineStr">
         <is>
           <t>MotherDuck</t>
         </is>
       </c>
-      <c r="E107" s="32" t="inlineStr">
+      <c r="E107" s="35" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -7326,12 +7332,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H107" s="32" t="inlineStr">
+      <c r="H107" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I107" s="32" t="inlineStr">
+      <c r="I107" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7346,20 +7352,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L107" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M107" s="32" t="inlineStr"/>
+      <c r="L107" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M107" s="35" t="inlineStr"/>
     </row>
     <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="33" t="inlineStr">
+      <c r="A108" s="34" t="inlineStr">
         <is>
           <t>4417163235</t>
         </is>
       </c>
-      <c r="B108" s="33" t="inlineStr">
+      <c r="B108" s="34" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -7369,12 +7375,12 @@
           <t>Software Engineer, Cloud SDK</t>
         </is>
       </c>
-      <c r="D108" s="33" t="inlineStr">
+      <c r="D108" s="34" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="E108" s="33" t="inlineStr">
+      <c r="E108" s="34" t="inlineStr">
         <is>
           <t>Kirkland, WA</t>
         </is>
@@ -7389,12 +7395,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H108" s="33" t="inlineStr">
+      <c r="H108" s="34" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="I108" s="33" t="inlineStr">
+      <c r="I108" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7409,20 +7415,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L108" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M108" s="33" t="inlineStr"/>
+      <c r="L108" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M108" s="34" t="inlineStr"/>
     </row>
     <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="32" t="inlineStr">
+      <c r="A109" s="35" t="inlineStr">
         <is>
           <t>4412210123</t>
         </is>
       </c>
-      <c r="B109" s="32" t="inlineStr">
+      <c r="B109" s="35" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7432,12 +7438,12 @@
           <t>Summer Intern - Software Engineer</t>
         </is>
       </c>
-      <c r="D109" s="32" t="inlineStr">
+      <c r="D109" s="35" t="inlineStr">
         <is>
           <t>Allegion (Southeast Asia) Pte. Ltd.</t>
         </is>
       </c>
-      <c r="E109" s="32" t="inlineStr">
+      <c r="E109" s="35" t="inlineStr">
         <is>
           <t>Carmel, IN</t>
         </is>
@@ -7452,12 +7458,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H109" s="32" t="inlineStr">
+      <c r="H109" s="35" t="inlineStr">
         <is>
           <t>146</t>
         </is>
       </c>
-      <c r="I109" s="32" t="inlineStr">
+      <c r="I109" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7472,20 +7478,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L109" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M109" s="32" t="inlineStr"/>
+      <c r="L109" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M109" s="35" t="inlineStr"/>
     </row>
     <row r="110" ht="18" customHeight="1">
-      <c r="A110" s="33" t="inlineStr">
+      <c r="A110" s="34" t="inlineStr">
         <is>
           <t>4414924766</t>
         </is>
       </c>
-      <c r="B110" s="33" t="inlineStr">
+      <c r="B110" s="34" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7495,12 +7501,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D110" s="33" t="inlineStr">
+      <c r="D110" s="34" t="inlineStr">
         <is>
           <t>Uneek Global</t>
         </is>
       </c>
-      <c r="E110" s="33" t="inlineStr">
+      <c r="E110" s="34" t="inlineStr">
         <is>
           <t>Texas, United States</t>
         </is>
@@ -7515,12 +7521,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H110" s="33" t="inlineStr">
+      <c r="H110" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I110" s="33" t="inlineStr">
+      <c r="I110" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7535,20 +7541,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L110" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M110" s="33" t="inlineStr"/>
+      <c r="L110" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M110" s="34" t="inlineStr"/>
     </row>
     <row r="111" ht="18" customHeight="1">
-      <c r="A111" s="32" t="inlineStr">
+      <c r="A111" s="35" t="inlineStr">
         <is>
           <t>4411278313</t>
         </is>
       </c>
-      <c r="B111" s="32" t="inlineStr">
+      <c r="B111" s="35" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7558,12 +7564,12 @@
           <t>Junior Software Engineer (.NET)</t>
         </is>
       </c>
-      <c r="D111" s="32" t="inlineStr">
+      <c r="D111" s="35" t="inlineStr">
         <is>
           <t>Quintrix, by Mindlance</t>
         </is>
       </c>
-      <c r="E111" s="32" t="inlineStr">
+      <c r="E111" s="35" t="inlineStr">
         <is>
           <t>Austin, Texas Metropolitan Area</t>
         </is>
@@ -7578,12 +7584,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H111" s="32" t="inlineStr">
+      <c r="H111" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I111" s="32" t="inlineStr">
+      <c r="I111" s="35" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
@@ -7598,20 +7604,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L111" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M111" s="32" t="inlineStr"/>
+      <c r="L111" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M111" s="35" t="inlineStr"/>
     </row>
     <row r="112" ht="18" customHeight="1">
-      <c r="A112" s="33" t="inlineStr">
+      <c r="A112" s="34" t="inlineStr">
         <is>
           <t>4340327286</t>
         </is>
       </c>
-      <c r="B112" s="33" t="inlineStr">
+      <c r="B112" s="34" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7621,12 +7627,12 @@
           <t>IT Services - SOFTWARE DEVELOPERS</t>
         </is>
       </c>
-      <c r="D112" s="33" t="inlineStr">
+      <c r="D112" s="34" t="inlineStr">
         <is>
           <t>Fuge Technologies Inc</t>
         </is>
       </c>
-      <c r="E112" s="33" t="inlineStr">
+      <c r="E112" s="34" t="inlineStr">
         <is>
           <t>Irving, TX</t>
         </is>
@@ -7641,12 +7647,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H112" s="33" t="inlineStr">
+      <c r="H112" s="34" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="I112" s="33" t="inlineStr">
+      <c r="I112" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7661,20 +7667,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L112" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M112" s="33" t="inlineStr"/>
+      <c r="L112" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M112" s="34" t="inlineStr"/>
     </row>
     <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="32" t="inlineStr">
+      <c r="A113" s="35" t="inlineStr">
         <is>
           <t>4243859384</t>
         </is>
       </c>
-      <c r="B113" s="32" t="inlineStr">
+      <c r="B113" s="35" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7684,12 +7690,12 @@
           <t>Test analyst</t>
         </is>
       </c>
-      <c r="D113" s="32" t="inlineStr">
+      <c r="D113" s="35" t="inlineStr">
         <is>
           <t>ADP WFN Test Company 3</t>
         </is>
       </c>
-      <c r="E113" s="32" t="inlineStr">
+      <c r="E113" s="35" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
@@ -7704,12 +7710,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H113" s="32" t="inlineStr">
+      <c r="H113" s="35" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="I113" s="32" t="inlineStr">
+      <c r="I113" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7724,20 +7730,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L113" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M113" s="32" t="inlineStr"/>
+      <c r="L113" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M113" s="35" t="inlineStr"/>
     </row>
     <row r="114" ht="18" customHeight="1">
-      <c r="A114" s="33" t="inlineStr">
+      <c r="A114" s="34" t="inlineStr">
         <is>
           <t>4407894427</t>
         </is>
       </c>
-      <c r="B114" s="33" t="inlineStr">
+      <c r="B114" s="34" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7747,12 +7753,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D114" s="33" t="inlineStr">
+      <c r="D114" s="34" t="inlineStr">
         <is>
           <t>Meriplex</t>
         </is>
       </c>
-      <c r="E114" s="33" t="inlineStr">
+      <c r="E114" s="34" t="inlineStr">
         <is>
           <t>Houston, TX</t>
         </is>
@@ -7767,12 +7773,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H114" s="33" t="inlineStr">
+      <c r="H114" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I114" s="33" t="inlineStr">
+      <c r="I114" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7787,20 +7793,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L114" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M114" s="33" t="inlineStr"/>
+      <c r="L114" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M114" s="34" t="inlineStr"/>
     </row>
     <row r="115" ht="18" customHeight="1">
-      <c r="A115" s="32" t="inlineStr">
+      <c r="A115" s="35" t="inlineStr">
         <is>
           <t>4414252424</t>
         </is>
       </c>
-      <c r="B115" s="32" t="inlineStr">
+      <c r="B115" s="35" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7810,12 +7816,12 @@
           <t>Junior Developer</t>
         </is>
       </c>
-      <c r="D115" s="32" t="inlineStr">
+      <c r="D115" s="35" t="inlineStr">
         <is>
           <t>Joyce Meyer Ministries</t>
         </is>
       </c>
-      <c r="E115" s="32" t="inlineStr">
+      <c r="E115" s="35" t="inlineStr">
         <is>
           <t>Fenton, MO</t>
         </is>
@@ -7830,12 +7836,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H115" s="32" t="inlineStr">
+      <c r="H115" s="35" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="I115" s="32" t="inlineStr">
+      <c r="I115" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7850,20 +7856,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L115" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M115" s="32" t="inlineStr"/>
+      <c r="L115" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M115" s="35" t="inlineStr"/>
     </row>
     <row r="116" ht="18" customHeight="1">
-      <c r="A116" s="33" t="inlineStr">
+      <c r="A116" s="34" t="inlineStr">
         <is>
           <t>4401782778</t>
         </is>
       </c>
-      <c r="B116" s="33" t="inlineStr">
+      <c r="B116" s="34" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7873,12 +7879,12 @@
           <t>Junior Full-Stack Software Developer</t>
         </is>
       </c>
-      <c r="D116" s="33" t="inlineStr">
+      <c r="D116" s="34" t="inlineStr">
         <is>
           <t>Visionist, Inc.</t>
         </is>
       </c>
-      <c r="E116" s="33" t="inlineStr">
+      <c r="E116" s="34" t="inlineStr">
         <is>
           <t>Columbia, MD</t>
         </is>
@@ -7893,12 +7899,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H116" s="33" t="inlineStr">
+      <c r="H116" s="34" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="I116" s="33" t="inlineStr">
+      <c r="I116" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7913,20 +7919,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L116" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M116" s="33" t="inlineStr"/>
+      <c r="L116" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M116" s="34" t="inlineStr"/>
     </row>
     <row r="117" ht="18" customHeight="1">
-      <c r="A117" s="32" t="inlineStr">
+      <c r="A117" s="35" t="inlineStr">
         <is>
           <t>4411523361</t>
         </is>
       </c>
-      <c r="B117" s="32" t="inlineStr">
+      <c r="B117" s="35" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7936,12 +7942,12 @@
           <t>Junior Application Developer</t>
         </is>
       </c>
-      <c r="D117" s="32" t="inlineStr">
+      <c r="D117" s="35" t="inlineStr">
         <is>
           <t>HCL Global Systems Inc</t>
         </is>
       </c>
-      <c r="E117" s="32" t="inlineStr">
+      <c r="E117" s="35" t="inlineStr">
         <is>
           <t>Georgia, United States</t>
         </is>
@@ -7956,12 +7962,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H117" s="32" t="inlineStr">
+      <c r="H117" s="35" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="I117" s="32" t="inlineStr">
+      <c r="I117" s="35" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
@@ -7976,20 +7982,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L117" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M117" s="32" t="inlineStr"/>
+      <c r="L117" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M117" s="35" t="inlineStr"/>
     </row>
     <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="33" t="inlineStr">
+      <c r="A118" s="34" t="inlineStr">
         <is>
           <t>4261490006</t>
         </is>
       </c>
-      <c r="B118" s="33" t="inlineStr">
+      <c r="B118" s="34" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7999,12 +8005,12 @@
           <t>**</t>
         </is>
       </c>
-      <c r="D118" s="33" t="inlineStr">
+      <c r="D118" s="34" t="inlineStr">
         <is>
           <t>ADP WFN Test Company 3</t>
         </is>
       </c>
-      <c r="E118" s="33" t="inlineStr">
+      <c r="E118" s="34" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
@@ -8019,12 +8025,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H118" s="33" t="inlineStr">
+      <c r="H118" s="34" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I118" s="33" t="inlineStr">
+      <c r="I118" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8039,20 +8045,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L118" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M118" s="33" t="inlineStr"/>
+      <c r="L118" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M118" s="34" t="inlineStr"/>
     </row>
     <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="32" t="inlineStr">
+      <c r="A119" s="35" t="inlineStr">
         <is>
           <t>4422878758</t>
         </is>
       </c>
-      <c r="B119" s="32" t="inlineStr">
+      <c r="B119" s="35" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -8062,12 +8068,12 @@
           <t>Junior Software Engineer</t>
         </is>
       </c>
-      <c r="D119" s="32" t="inlineStr">
+      <c r="D119" s="35" t="inlineStr">
         <is>
           <t>Brooksource</t>
         </is>
       </c>
-      <c r="E119" s="32" t="inlineStr">
+      <c r="E119" s="35" t="inlineStr">
         <is>
           <t>Lansing, MI</t>
         </is>
@@ -8082,12 +8088,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H119" s="32" t="inlineStr">
+      <c r="H119" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I119" s="32" t="inlineStr">
+      <c r="I119" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8102,20 +8108,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L119" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M119" s="32" t="inlineStr"/>
+      <c r="L119" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M119" s="35" t="inlineStr"/>
     </row>
     <row r="120" ht="18" customHeight="1">
-      <c r="A120" s="33" t="inlineStr">
+      <c r="A120" s="34" t="inlineStr">
         <is>
           <t>4419071723</t>
         </is>
       </c>
-      <c r="B120" s="33" t="inlineStr">
+      <c r="B120" s="34" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -8125,12 +8131,12 @@
           <t>Junior Software Developer</t>
         </is>
       </c>
-      <c r="D120" s="33" t="inlineStr">
+      <c r="D120" s="34" t="inlineStr">
         <is>
           <t>IPTA</t>
         </is>
       </c>
-      <c r="E120" s="33" t="inlineStr">
+      <c r="E120" s="34" t="inlineStr">
         <is>
           <t>Layton, UT</t>
         </is>
@@ -8145,12 +8151,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H120" s="33" t="inlineStr">
+      <c r="H120" s="34" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="I120" s="33" t="inlineStr">
+      <c r="I120" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8165,20 +8171,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L120" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M120" s="33" t="inlineStr"/>
+      <c r="L120" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M120" s="34" t="inlineStr"/>
     </row>
     <row r="121" ht="18" customHeight="1">
-      <c r="A121" s="32" t="inlineStr">
+      <c r="A121" s="35" t="inlineStr">
         <is>
           <t>4420988356</t>
         </is>
       </c>
-      <c r="B121" s="32" t="inlineStr">
+      <c r="B121" s="35" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -8188,12 +8194,12 @@
           <t>Junior Software Engineer</t>
         </is>
       </c>
-      <c r="D121" s="32" t="inlineStr">
+      <c r="D121" s="35" t="inlineStr">
         <is>
           <t>Switchboard</t>
         </is>
       </c>
-      <c r="E121" s="32" t="inlineStr">
+      <c r="E121" s="35" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
@@ -8208,12 +8214,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H121" s="32" t="inlineStr">
+      <c r="H121" s="35" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I121" s="32" t="inlineStr">
+      <c r="I121" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8228,20 +8234,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L121" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M121" s="32" t="inlineStr"/>
+      <c r="L121" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M121" s="35" t="inlineStr"/>
     </row>
     <row r="122" ht="18" customHeight="1">
-      <c r="A122" s="33" t="inlineStr">
+      <c r="A122" s="34" t="inlineStr">
         <is>
           <t>4419072850</t>
         </is>
       </c>
-      <c r="B122" s="33" t="inlineStr">
+      <c r="B122" s="34" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -8251,12 +8257,12 @@
           <t>junior software engineer analyst</t>
         </is>
       </c>
-      <c r="D122" s="33" t="inlineStr">
+      <c r="D122" s="34" t="inlineStr">
         <is>
           <t>Altamira Technologies Corporation</t>
         </is>
       </c>
-      <c r="E122" s="33" t="inlineStr">
+      <c r="E122" s="34" t="inlineStr">
         <is>
           <t>State College, PA</t>
         </is>
@@ -8271,12 +8277,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H122" s="33" t="inlineStr">
+      <c r="H122" s="34" t="inlineStr">
         <is>
           <t>137</t>
         </is>
       </c>
-      <c r="I122" s="33" t="inlineStr">
+      <c r="I122" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8291,20 +8297,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L122" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M122" s="33" t="inlineStr"/>
+      <c r="L122" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M122" s="34" t="inlineStr"/>
     </row>
     <row r="123" ht="18" customHeight="1">
-      <c r="A123" s="32" t="inlineStr">
+      <c r="A123" s="35" t="inlineStr">
         <is>
           <t>4406854247</t>
         </is>
       </c>
-      <c r="B123" s="32" t="inlineStr">
+      <c r="B123" s="35" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -8314,12 +8320,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D123" s="32" t="inlineStr">
+      <c r="D123" s="35" t="inlineStr">
         <is>
           <t>The Anywhere Company</t>
         </is>
       </c>
-      <c r="E123" s="32" t="inlineStr">
+      <c r="E123" s="35" t="inlineStr">
         <is>
           <t>Hilton Head Island, SC</t>
         </is>
@@ -8334,12 +8340,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H123" s="32" t="inlineStr">
+      <c r="H123" s="35" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I123" s="32" t="inlineStr">
+      <c r="I123" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8354,20 +8360,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L123" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M123" s="32" t="inlineStr"/>
+      <c r="L123" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M123" s="35" t="inlineStr"/>
     </row>
     <row r="124" ht="18" customHeight="1">
-      <c r="A124" s="33" t="inlineStr">
+      <c r="A124" s="34" t="inlineStr">
         <is>
           <t>4394719485</t>
         </is>
       </c>
-      <c r="B124" s="33" t="inlineStr">
+      <c r="B124" s="34" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -8377,12 +8383,12 @@
           <t>Software Developer I, II (Days 8am to 5pm) *On-Site Victor, NY*</t>
         </is>
       </c>
-      <c r="D124" s="33" t="inlineStr">
+      <c r="D124" s="34" t="inlineStr">
         <is>
           <t>LSI SOLUTIONS®</t>
         </is>
       </c>
-      <c r="E124" s="33" t="inlineStr">
+      <c r="E124" s="34" t="inlineStr">
         <is>
           <t>Victor, NY</t>
         </is>
@@ -8397,12 +8403,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H124" s="33" t="inlineStr">
+      <c r="H124" s="34" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I124" s="33" t="inlineStr">
+      <c r="I124" s="34" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8417,20 +8423,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L124" s="33" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M124" s="33" t="inlineStr"/>
+      <c r="L124" s="34" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M124" s="34" t="inlineStr"/>
     </row>
     <row r="125" ht="18" customHeight="1">
-      <c r="A125" s="32" t="inlineStr">
+      <c r="A125" s="35" t="inlineStr">
         <is>
           <t>4367493426</t>
         </is>
       </c>
-      <c r="B125" s="32" t="inlineStr">
+      <c r="B125" s="35" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -8440,12 +8446,12 @@
           <t>Junior Software Developer</t>
         </is>
       </c>
-      <c r="D125" s="32" t="inlineStr">
+      <c r="D125" s="35" t="inlineStr">
         <is>
           <t>KIHOMAC</t>
         </is>
       </c>
-      <c r="E125" s="32" t="inlineStr">
+      <c r="E125" s="35" t="inlineStr">
         <is>
           <t>Colorado Springs, CO</t>
         </is>
@@ -8460,12 +8466,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H125" s="32" t="inlineStr">
+      <c r="H125" s="35" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="I125" s="32" t="inlineStr">
+      <c r="I125" s="35" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8480,12 +8486,12 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L125" s="32" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M125" s="32" t="inlineStr"/>
+      <c r="L125" s="35" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M125" s="35" t="inlineStr"/>
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="34" t="inlineStr">
@@ -8739,8 +8745,1331 @@
       </c>
       <c r="M129" s="35" t="inlineStr"/>
     </row>
+    <row r="130" ht="18" customHeight="1">
+      <c r="A130" s="36" t="inlineStr">
+        <is>
+          <t>4413774877</t>
+        </is>
+      </c>
+      <c r="B130" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>Network Engineering Intern (Summer 2026)</t>
+        </is>
+      </c>
+      <c r="D130" s="36" t="inlineStr">
+        <is>
+          <t>Cloudflare Area 1 Security</t>
+        </is>
+      </c>
+      <c r="E130" s="36" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="G130" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H130" s="36" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I130" s="36" t="inlineStr">
+        <is>
+          <t>Volunteer</t>
+        </is>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, aws, c, express, Location: Austin, TX, Title match: Network Engineering Intern (Summer 2026)</t>
+        </is>
+      </c>
+      <c r="K130" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L130" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M130" s="36" t="inlineStr"/>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="A131" s="37" t="inlineStr">
+        <is>
+          <t>4415577033</t>
+        </is>
+      </c>
+      <c r="B131" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C131" s="8" t="inlineStr">
+        <is>
+          <t>Summer Intern - Software Engineer</t>
+        </is>
+      </c>
+      <c r="D131" s="37" t="inlineStr">
+        <is>
+          <t>Allegion</t>
+        </is>
+      </c>
+      <c r="E131" s="37" t="inlineStr">
+        <is>
+          <t>Carmel, IN</t>
+        </is>
+      </c>
+      <c r="F131" s="18" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="G131" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H131" s="37" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I131" s="37" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J131" s="8" t="inlineStr">
+        <is>
+          <t>Skills: c, agile, Title match: Summer Intern - Software Engineer</t>
+        </is>
+      </c>
+      <c r="K131" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L131" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M131" s="37" t="inlineStr"/>
+    </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="A132" s="36" t="inlineStr">
+        <is>
+          <t>4407221528</t>
+        </is>
+      </c>
+      <c r="B132" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="D132" s="36" t="inlineStr">
+        <is>
+          <t>Saronic Technologies</t>
+        </is>
+      </c>
+      <c r="E132" s="36" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="G132" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H132" s="36" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I132" s="36" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>Skills: javascript, react, node, mongodb, api, git, Location: Austin, TX, Title match: Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="K132" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L132" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M132" s="36" t="inlineStr"/>
+    </row>
+    <row r="133" ht="18" customHeight="1">
+      <c r="A133" s="37" t="inlineStr">
+        <is>
+          <t>4413657345</t>
+        </is>
+      </c>
+      <c r="B133" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D133" s="37" t="inlineStr">
+        <is>
+          <t>Streamline Healthcare Solutions</t>
+        </is>
+      </c>
+      <c r="E133" s="37" t="inlineStr">
+        <is>
+          <t>Texas, United States</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H133" s="37" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I133" s="37" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J133" s="8" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, sql, c, Location: Texas, United States, Title match: Software Engineer</t>
+        </is>
+      </c>
+      <c r="K133" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L133" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M133" s="37" t="inlineStr"/>
+    </row>
+    <row r="134" ht="18" customHeight="1">
+      <c r="A134" s="36" t="inlineStr">
+        <is>
+          <t>4390738582</t>
+        </is>
+      </c>
+      <c r="B134" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D134" s="36" t="inlineStr">
+        <is>
+          <t>Pushnami</t>
+        </is>
+      </c>
+      <c r="E134" s="36" t="inlineStr">
+        <is>
+          <t>Austin, Texas Metropolitan Area</t>
+        </is>
+      </c>
+      <c r="F134" s="9" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="G134" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H134" s="36" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I134" s="36" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, aws, rest, api, full stack, c, Location: Austin, Texas Metropolitan Area, Title match: Software Engineer</t>
+        </is>
+      </c>
+      <c r="K134" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L134" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M134" s="36" t="inlineStr"/>
+    </row>
+    <row r="135" ht="18" customHeight="1">
+      <c r="A135" s="37" t="inlineStr">
+        <is>
+          <t>4304447681</t>
+        </is>
+      </c>
+      <c r="B135" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C135" s="8" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="D135" s="37" t="inlineStr">
+        <is>
+          <t>DataAnnotation</t>
+        </is>
+      </c>
+      <c r="E135" s="37" t="inlineStr">
+        <is>
+          <t>Texas, United States</t>
+        </is>
+      </c>
+      <c r="F135" s="9" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="G135" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H135" s="37" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I135" s="37" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J135" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, html, sql, c++, c, Location: Texas, United States, Title match: Software Developer</t>
+        </is>
+      </c>
+      <c r="K135" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L135" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M135" s="37" t="inlineStr"/>
+    </row>
+    <row r="136" ht="18" customHeight="1">
+      <c r="A136" s="36" t="inlineStr">
+        <is>
+          <t>4387731381</t>
+        </is>
+      </c>
+      <c r="B136" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>Software Development Engineer I</t>
+        </is>
+      </c>
+      <c r="D136" s="36" t="inlineStr">
+        <is>
+          <t>GM Financial</t>
+        </is>
+      </c>
+      <c r="E136" s="36" t="inlineStr">
+        <is>
+          <t>Irving, TX</t>
+        </is>
+      </c>
+      <c r="F136" s="18" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="G136" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H136" s="36" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I136" s="36" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>Skills: javascript, node, api, css, docker, git</t>
+        </is>
+      </c>
+      <c r="K136" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L136" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M136" s="36" t="inlineStr"/>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="A137" s="37" t="inlineStr">
+        <is>
+          <t>4420489886</t>
+        </is>
+      </c>
+      <c r="B137" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C137" s="8" t="inlineStr">
+        <is>
+          <t>Junior Java full stack developer/Data analyst</t>
+        </is>
+      </c>
+      <c r="D137" s="37" t="inlineStr">
+        <is>
+          <t>SynergisticIT</t>
+        </is>
+      </c>
+      <c r="E137" s="37" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="F137" s="9" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="G137" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H137" s="37" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I137" s="37" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="J137" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, rest, api, sql, machine learning, full stack, Location: Austin, TX, Title match: Junior Java full stack developer/Data analyst</t>
+        </is>
+      </c>
+      <c r="K137" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L137" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M137" s="37" t="inlineStr"/>
+    </row>
+    <row r="138" ht="18" customHeight="1">
+      <c r="A138" s="36" t="inlineStr">
+        <is>
+          <t>4419113430</t>
+        </is>
+      </c>
+      <c r="B138" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer, Factory Software</t>
+        </is>
+      </c>
+      <c r="D138" s="36" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="E138" s="36" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="F138" s="9" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="G138" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H138" s="36" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I138" s="36" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, react, mongodb, rest, api, docker, Location: Austin, TX, Title match: Software Engineer, Factory Software</t>
+        </is>
+      </c>
+      <c r="K138" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L138" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M138" s="36" t="inlineStr"/>
+    </row>
+    <row r="139" ht="18" customHeight="1">
+      <c r="A139" s="37" t="inlineStr">
+        <is>
+          <t>4358267222</t>
+        </is>
+      </c>
+      <c r="B139" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C139" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D139" s="37" t="inlineStr">
+        <is>
+          <t>iHeartMedia</t>
+        </is>
+      </c>
+      <c r="E139" s="37" t="inlineStr">
+        <is>
+          <t>San Antonio, TX</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="G139" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H139" s="37" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I139" s="37" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J139" s="8" t="inlineStr">
+        <is>
+          <t>Skills: aws, rest, api, git, backend, c, Title match: Software Engineer</t>
+        </is>
+      </c>
+      <c r="K139" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L139" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M139" s="37" t="inlineStr"/>
+    </row>
+    <row r="140" ht="18" customHeight="1">
+      <c r="A140" s="36" t="inlineStr">
+        <is>
+          <t>4414766348</t>
+        </is>
+      </c>
+      <c r="B140" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>Intern - Software Engineer Backend - Remote - Nationwide</t>
+        </is>
+      </c>
+      <c r="D140" s="36" t="inlineStr">
+        <is>
+          <t>Vituity</t>
+        </is>
+      </c>
+      <c r="E140" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="G140" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H140" s="36" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I140" s="36" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, aws, rest, api, git, backend, Title match: Intern - Software Engineer Backend - Remote - Nationwide</t>
+        </is>
+      </c>
+      <c r="K140" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L140" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M140" s="36" t="inlineStr"/>
+    </row>
+    <row r="141" ht="18" customHeight="1">
+      <c r="A141" s="37" t="inlineStr">
+        <is>
+          <t>4404102169</t>
+        </is>
+      </c>
+      <c r="B141" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C141" s="8" t="inlineStr">
+        <is>
+          <t>Software Development Engineer I</t>
+        </is>
+      </c>
+      <c r="D141" s="37" t="inlineStr">
+        <is>
+          <t>GM Financial</t>
+        </is>
+      </c>
+      <c r="E141" s="37" t="inlineStr">
+        <is>
+          <t>Irving, TX</t>
+        </is>
+      </c>
+      <c r="F141" s="18" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="G141" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H141" s="37" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I141" s="37" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J141" s="8" t="inlineStr">
+        <is>
+          <t>Skills: javascript, node, api, css, docker, git</t>
+        </is>
+      </c>
+      <c r="K141" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L141" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M141" s="37" t="inlineStr"/>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="A142" s="36" t="inlineStr">
+        <is>
+          <t>4415891077</t>
+        </is>
+      </c>
+      <c r="B142" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D142" s="36" t="inlineStr">
+        <is>
+          <t>Acrisure Innovation</t>
+        </is>
+      </c>
+      <c r="E142" s="36" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="G142" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H142" s="36" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="I142" s="36" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, react, api, full stack, c, Location: Austin, TX, Title match: Software Engineer</t>
+        </is>
+      </c>
+      <c r="K142" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L142" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M142" s="36" t="inlineStr"/>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="A143" s="37" t="inlineStr">
+        <is>
+          <t>4422883837</t>
+        </is>
+      </c>
+      <c r="B143" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C143" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D143" s="37" t="inlineStr">
+        <is>
+          <t>Emonics LLC</t>
+        </is>
+      </c>
+      <c r="E143" s="37" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="F143" s="9" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="G143" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H143" s="37" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I143" s="37" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J143" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, git, sql, c++, c, data structures, Location: Austin, TX, Title match: Software Engineer</t>
+        </is>
+      </c>
+      <c r="K143" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L143" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M143" s="37" t="inlineStr"/>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="A144" s="36" t="inlineStr">
+        <is>
+          <t>4313403973</t>
+        </is>
+      </c>
+      <c r="B144" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D144" s="36" t="inlineStr">
+        <is>
+          <t>BuildBuddy</t>
+        </is>
+      </c>
+      <c r="E144" s="36" t="inlineStr">
+        <is>
+          <t>San Angelo Area</t>
+        </is>
+      </c>
+      <c r="F144" s="18" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="G144" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H144" s="36" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="I144" s="36" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>Skills: react, rest, git, c, typescript, Title match: Software Engineer</t>
+        </is>
+      </c>
+      <c r="K144" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L144" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M144" s="36" t="inlineStr"/>
+    </row>
+    <row r="145" ht="18" customHeight="1">
+      <c r="A145" s="37" t="inlineStr">
+        <is>
+          <t>4414222508</t>
+        </is>
+      </c>
+      <c r="B145" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C145" s="8" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D145" s="37" t="inlineStr">
+        <is>
+          <t>Winaxis LLC</t>
+        </is>
+      </c>
+      <c r="E145" s="37" t="inlineStr">
+        <is>
+          <t>Dallas, TX</t>
+        </is>
+      </c>
+      <c r="F145" s="9" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="G145" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H145" s="37" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I145" s="37" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J145" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, react, node, aws, mongodb, rest, Location: Dallas, TX, Title match: Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="K145" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L145" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M145" s="37" t="inlineStr"/>
+    </row>
+    <row r="146" ht="18" customHeight="1">
+      <c r="A146" s="36" t="inlineStr">
+        <is>
+          <t>4419658058</t>
+        </is>
+      </c>
+      <c r="B146" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>Early Career Software Engineer</t>
+        </is>
+      </c>
+      <c r="D146" s="36" t="inlineStr">
+        <is>
+          <t>Gainwell Technologies</t>
+        </is>
+      </c>
+      <c r="E146" s="36" t="inlineStr">
+        <is>
+          <t>Texas, United States</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="G146" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H146" s="36" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I146" s="36" t="inlineStr">
+        <is>
+          <t>Volunteer</t>
+        </is>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>Skills: aws, c, Location: Texas, United States, Title match: Early Career Software Engineer</t>
+        </is>
+      </c>
+      <c r="K146" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L146" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M146" s="36" t="inlineStr"/>
+    </row>
+    <row r="147" ht="18" customHeight="1">
+      <c r="A147" s="37" t="inlineStr">
+        <is>
+          <t>4421341648</t>
+        </is>
+      </c>
+      <c r="B147" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C147" s="8" t="inlineStr">
+        <is>
+          <t>Entry level full stack developer/Machine learning /AI engineer</t>
+        </is>
+      </c>
+      <c r="D147" s="37" t="inlineStr">
+        <is>
+          <t>SynergisticIT</t>
+        </is>
+      </c>
+      <c r="E147" s="37" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="G147" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H147" s="37" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I147" s="37" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="J147" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, machine learning, full stack, c, Location: Austin, TX, Title match: Entry level full stack developer/Machine learning /AI engineer</t>
+        </is>
+      </c>
+      <c r="K147" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L147" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M147" s="37" t="inlineStr"/>
+    </row>
+    <row r="148" ht="18" customHeight="1">
+      <c r="A148" s="36" t="inlineStr">
+        <is>
+          <t>4413445271</t>
+        </is>
+      </c>
+      <c r="B148" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>Associate Software Engineer</t>
+        </is>
+      </c>
+      <c r="D148" s="36" t="inlineStr">
+        <is>
+          <t>SquareTrade</t>
+        </is>
+      </c>
+      <c r="E148" s="36" t="inlineStr">
+        <is>
+          <t>Dallas, TX</t>
+        </is>
+      </c>
+      <c r="F148" s="9" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="G148" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H148" s="36" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I148" s="36" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>Skills: aws, rest, git, sql, c, express, Location: Dallas, TX, Title match: Associate Software Engineer</t>
+        </is>
+      </c>
+      <c r="K148" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L148" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M148" s="36" t="inlineStr"/>
+    </row>
+    <row r="149" ht="18" customHeight="1">
+      <c r="A149" s="37" t="inlineStr">
+        <is>
+          <t>4418784522</t>
+        </is>
+      </c>
+      <c r="B149" s="37" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C149" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D149" s="37" t="inlineStr">
+        <is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="E149" s="37" t="inlineStr">
+        <is>
+          <t>Greater Houston</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="G149" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H149" s="37" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I149" s="37" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J149" s="8" t="inlineStr">
+        <is>
+          <t>Skills: c, express, Location: Greater Houston, Title match: Software Engineer</t>
+        </is>
+      </c>
+      <c r="K149" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L149" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M149" s="37" t="inlineStr"/>
+    </row>
+    <row r="150" ht="18" customHeight="1">
+      <c r="A150" s="36" t="inlineStr">
+        <is>
+          <t>4397591181</t>
+        </is>
+      </c>
+      <c r="B150" s="36" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer - New Grad (Summer 2026)</t>
+        </is>
+      </c>
+      <c r="D150" s="36" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="E150" s="36" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="G150" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H150" s="36" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I150" s="36" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>Skills: react, rest, api, c, Location: Austin, TX, Title match: Software Engineer - New Grad (Summer 2026)</t>
+        </is>
+      </c>
+      <c r="K150" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L150" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M150" s="36" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M129"/>
+  <autoFilter ref="A1:M150"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -8870,6 +10199,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K128" r:id="rId127"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K150" r:id="rId149"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Job Matches" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Matches'!$A$1:$M$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Matches'!$A$1:$M$159</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -229,6 +229,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -596,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M150"/>
+  <dimension ref="A1:M159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -682,12 +688,12 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="34" t="inlineStr">
+      <c r="A2" s="36" t="inlineStr">
         <is>
           <t>4406952064</t>
         </is>
       </c>
-      <c r="B2" s="34" t="inlineStr">
+      <c r="B2" s="36" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -697,12 +703,12 @@
           <t>DevSecOps Intern</t>
         </is>
       </c>
-      <c r="D2" s="34" t="inlineStr">
+      <c r="D2" s="36" t="inlineStr">
         <is>
           <t>Modern Technology Solutions, Inc. (MTSI)</t>
         </is>
       </c>
-      <c r="E2" s="34" t="inlineStr">
+      <c r="E2" s="36" t="inlineStr">
         <is>
           <t>Huntsville, AL</t>
         </is>
@@ -717,12 +723,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H2" s="34" t="inlineStr">
+      <c r="H2" s="36" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="I2" s="34" t="inlineStr">
+      <c r="I2" s="36" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -737,20 +743,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L2" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M2" s="34" t="inlineStr"/>
+      <c r="L2" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M2" s="36" t="inlineStr"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="37" t="inlineStr">
         <is>
           <t>4405630173</t>
         </is>
       </c>
-      <c r="B3" s="35" t="inlineStr">
+      <c r="B3" s="37" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -760,12 +766,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D3" s="35" t="inlineStr">
+      <c r="D3" s="37" t="inlineStr">
         <is>
           <t>DLRdmv®</t>
         </is>
       </c>
-      <c r="E3" s="35" t="inlineStr">
+      <c r="E3" s="37" t="inlineStr">
         <is>
           <t>Dallas, TX</t>
         </is>
@@ -780,12 +786,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H3" s="35" t="inlineStr">
+      <c r="H3" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I3" s="35" t="inlineStr">
+      <c r="I3" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -800,20 +806,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L3" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M3" s="35" t="inlineStr"/>
+      <c r="L3" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M3" s="37" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="34" t="inlineStr">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t>4287414862</t>
         </is>
       </c>
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="36" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -823,12 +829,12 @@
           <t>[Online Assessment]Software Development Engineer Intern (Network Automation)- 2026 Summer (BS/ MS)</t>
         </is>
       </c>
-      <c r="D4" s="34" t="inlineStr">
+      <c r="D4" s="36" t="inlineStr">
         <is>
           <t>ByteDance</t>
         </is>
       </c>
-      <c r="E4" s="34" t="inlineStr">
+      <c r="E4" s="36" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -843,12 +849,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H4" s="34" t="inlineStr">
+      <c r="H4" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I4" s="34" t="inlineStr">
+      <c r="I4" s="36" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -863,20 +869,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L4" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M4" s="34" t="inlineStr"/>
+      <c r="L4" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M4" s="36" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>4309805269</t>
         </is>
       </c>
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -886,12 +892,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="D5" s="37" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E5" s="35" t="inlineStr">
+      <c r="E5" s="37" t="inlineStr">
         <is>
           <t>Delaware, United States</t>
         </is>
@@ -906,12 +912,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H5" s="35" t="inlineStr">
+      <c r="H5" s="37" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="I5" s="35" t="inlineStr">
+      <c r="I5" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -926,20 +932,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L5" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M5" s="35" t="inlineStr"/>
+      <c r="L5" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M5" s="37" t="inlineStr"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>4371812987</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -949,12 +955,12 @@
           <t>Software Development Engineer Fall Intern - Military Veteran</t>
         </is>
       </c>
-      <c r="D6" s="34" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E6" s="34" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -969,12 +975,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H6" s="34" t="inlineStr">
+      <c r="H6" s="36" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="I6" s="34" t="inlineStr">
+      <c r="I6" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -989,20 +995,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L6" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M6" s="34" t="inlineStr"/>
+      <c r="L6" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M6" s="36" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>4274682122</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1012,12 +1018,12 @@
           <t>Software Engineer Intern (Data Ecosystem) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D7" s="35" t="inlineStr">
+      <c r="D7" s="37" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E7" s="35" t="inlineStr">
+      <c r="E7" s="37" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1032,12 +1038,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H7" s="35" t="inlineStr">
+      <c r="H7" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I7" s="35" t="inlineStr">
+      <c r="I7" s="37" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1052,20 +1058,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L7" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M7" s="35" t="inlineStr"/>
+      <c r="L7" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M7" s="37" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>4283848614</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1075,12 +1081,12 @@
           <t>[Online Assessment] Software Engineer Intern (Recommendation Infrastructure) - 2026 Fall (BS/ MS)</t>
         </is>
       </c>
-      <c r="D8" s="34" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E8" s="34" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1095,12 +1101,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H8" s="34" t="inlineStr">
+      <c r="H8" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I8" s="34" t="inlineStr">
+      <c r="I8" s="36" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1115,20 +1121,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L8" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M8" s="34" t="inlineStr"/>
+      <c r="L8" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M8" s="36" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>4411790844</t>
         </is>
       </c>
-      <c r="B9" s="35" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1138,12 +1144,12 @@
           <t>Software Engineer Intern (Infrastructure Automation) - Fall 2026</t>
         </is>
       </c>
-      <c r="D9" s="35" t="inlineStr">
+      <c r="D9" s="37" t="inlineStr">
         <is>
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="E9" s="35" t="inlineStr">
+      <c r="E9" s="37" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -1158,12 +1164,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H9" s="35" t="inlineStr">
+      <c r="H9" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I9" s="35" t="inlineStr">
+      <c r="I9" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1178,20 +1184,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L9" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M9" s="35" t="inlineStr"/>
+      <c r="L9" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M9" s="37" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>4332425058</t>
         </is>
       </c>
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1201,12 +1207,12 @@
           <t>Software Development Engineer Internship - Fall 2026 (US)</t>
         </is>
       </c>
-      <c r="D10" s="34" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E10" s="34" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1221,12 +1227,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H10" s="34" t="inlineStr">
+      <c r="H10" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I10" s="34" t="inlineStr">
+      <c r="I10" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1241,20 +1247,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L10" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M10" s="34" t="inlineStr"/>
+      <c r="L10" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M10" s="36" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="35" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>4323643644</t>
         </is>
       </c>
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1264,12 +1270,12 @@
           <t>[Online Assessment] Software Engineer Intern (Recommendation Infrastructure) - 2026 Summer (BS/ MS)</t>
         </is>
       </c>
-      <c r="D11" s="35" t="inlineStr">
+      <c r="D11" s="37" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E11" s="35" t="inlineStr">
+      <c r="E11" s="37" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1284,12 +1290,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H11" s="35" t="inlineStr">
+      <c r="H11" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I11" s="35" t="inlineStr">
+      <c r="I11" s="37" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1304,20 +1310,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L11" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M11" s="35" t="inlineStr"/>
+      <c r="L11" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M11" s="37" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>4320849104</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1327,12 +1333,12 @@
           <t>Software Engineer Intern (Commerce Ads) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D12" s="34" t="inlineStr">
+      <c r="D12" s="36" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E12" s="34" t="inlineStr">
+      <c r="E12" s="36" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1347,12 +1353,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H12" s="34" t="inlineStr">
+      <c r="H12" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I12" s="34" t="inlineStr">
+      <c r="I12" s="36" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1367,20 +1373,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L12" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M12" s="34" t="inlineStr"/>
+      <c r="L12" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M12" s="36" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="35" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>4401686051</t>
         </is>
       </c>
-      <c r="B13" s="35" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1390,12 +1396,12 @@
           <t>Front End Software Engineer</t>
         </is>
       </c>
-      <c r="D13" s="35" t="inlineStr">
+      <c r="D13" s="37" t="inlineStr">
         <is>
           <t>Saronic Technologies</t>
         </is>
       </c>
-      <c r="E13" s="35" t="inlineStr">
+      <c r="E13" s="37" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -1410,12 +1416,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H13" s="35" t="inlineStr">
+      <c r="H13" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I13" s="35" t="inlineStr">
+      <c r="I13" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1430,20 +1436,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L13" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M13" s="35" t="inlineStr"/>
+      <c r="L13" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M13" s="37" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>4309696652</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1453,12 +1459,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D14" s="34" t="inlineStr">
+      <c r="D14" s="36" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E14" s="34" t="inlineStr">
+      <c r="E14" s="36" t="inlineStr">
         <is>
           <t>Rhode Island, United States</t>
         </is>
@@ -1473,12 +1479,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H14" s="34" t="inlineStr">
+      <c r="H14" s="36" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="I14" s="34" t="inlineStr">
+      <c r="I14" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1493,20 +1499,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L14" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M14" s="34" t="inlineStr"/>
+      <c r="L14" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M14" s="36" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="35" t="inlineStr">
+      <c r="A15" s="37" t="inlineStr">
         <is>
           <t>4309804319</t>
         </is>
       </c>
-      <c r="B15" s="35" t="inlineStr">
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1516,12 +1522,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D15" s="35" t="inlineStr">
+      <c r="D15" s="37" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E15" s="35" t="inlineStr">
+      <c r="E15" s="37" t="inlineStr">
         <is>
           <t>Colorado, United States</t>
         </is>
@@ -1536,12 +1542,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H15" s="35" t="inlineStr">
+      <c r="H15" s="37" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="I15" s="35" t="inlineStr">
+      <c r="I15" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1556,20 +1562,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L15" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M15" s="35" t="inlineStr"/>
+      <c r="L15" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M15" s="37" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>4410271532</t>
         </is>
       </c>
-      <c r="B16" s="34" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1579,12 +1585,12 @@
           <t>Associate Developer</t>
         </is>
       </c>
-      <c r="D16" s="34" t="inlineStr">
+      <c r="D16" s="36" t="inlineStr">
         <is>
           <t>HealthStream</t>
         </is>
       </c>
-      <c r="E16" s="34" t="inlineStr">
+      <c r="E16" s="36" t="inlineStr">
         <is>
           <t>Nashville, TN</t>
         </is>
@@ -1599,12 +1605,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H16" s="34" t="inlineStr">
+      <c r="H16" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I16" s="34" t="inlineStr">
+      <c r="I16" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1619,20 +1625,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L16" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M16" s="34" t="inlineStr"/>
+      <c r="L16" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M16" s="36" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="35" t="inlineStr">
+      <c r="A17" s="37" t="inlineStr">
         <is>
           <t>4304445726</t>
         </is>
       </c>
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B17" s="37" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1642,12 +1648,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D17" s="35" t="inlineStr">
+      <c r="D17" s="37" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E17" s="35" t="inlineStr">
+      <c r="E17" s="37" t="inlineStr">
         <is>
           <t>Oregon, United States</t>
         </is>
@@ -1662,12 +1668,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H17" s="35" t="inlineStr">
+      <c r="H17" s="37" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="I17" s="35" t="inlineStr">
+      <c r="I17" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1682,20 +1688,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L17" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M17" s="35" t="inlineStr"/>
+      <c r="L17" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M17" s="37" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>4342036151</t>
         </is>
       </c>
-      <c r="B18" s="34" t="inlineStr">
+      <c r="B18" s="36" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1705,12 +1711,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D18" s="34" t="inlineStr">
+      <c r="D18" s="36" t="inlineStr">
         <is>
           <t>Modern Treasury</t>
         </is>
       </c>
-      <c r="E18" s="34" t="inlineStr">
+      <c r="E18" s="36" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
@@ -1725,12 +1731,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H18" s="34" t="inlineStr">
+      <c r="H18" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I18" s="34" t="inlineStr">
+      <c r="I18" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1745,20 +1751,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L18" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M18" s="34" t="inlineStr"/>
+      <c r="L18" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M18" s="36" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A19" s="37" t="inlineStr">
         <is>
           <t>4304441843</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1768,12 +1774,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D19" s="35" t="inlineStr">
+      <c r="D19" s="37" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E19" s="35" t="inlineStr">
+      <c r="E19" s="37" t="inlineStr">
         <is>
           <t>Idaho, United States</t>
         </is>
@@ -1788,12 +1794,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H19" s="35" t="inlineStr">
+      <c r="H19" s="37" t="inlineStr">
         <is>
           <t>157</t>
         </is>
       </c>
-      <c r="I19" s="35" t="inlineStr">
+      <c r="I19" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1808,20 +1814,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L19" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M19" s="35" t="inlineStr"/>
+      <c r="L19" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M19" s="37" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="34" t="inlineStr">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>4408047047</t>
         </is>
       </c>
-      <c r="B20" s="34" t="inlineStr">
+      <c r="B20" s="36" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1831,12 +1837,12 @@
           <t>Computer Sciences - Graduates - AI Training - Las Vegas, US</t>
         </is>
       </c>
-      <c r="D20" s="34" t="inlineStr">
+      <c r="D20" s="36" t="inlineStr">
         <is>
           <t>Prolific</t>
         </is>
       </c>
-      <c r="E20" s="34" t="inlineStr">
+      <c r="E20" s="36" t="inlineStr">
         <is>
           <t>Las Vegas, NV</t>
         </is>
@@ -1851,12 +1857,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H20" s="34" t="inlineStr">
+      <c r="H20" s="36" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I20" s="34" t="inlineStr">
+      <c r="I20" s="36" t="inlineStr">
         <is>
           <t>Temporary</t>
         </is>
@@ -1871,20 +1877,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L20" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M20" s="34" t="inlineStr"/>
+      <c r="L20" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M20" s="36" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="35" t="inlineStr">
+      <c r="A21" s="37" t="inlineStr">
         <is>
           <t>4304444837</t>
         </is>
       </c>
-      <c r="B21" s="35" t="inlineStr">
+      <c r="B21" s="37" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1894,12 +1900,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D21" s="35" t="inlineStr">
+      <c r="D21" s="37" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E21" s="35" t="inlineStr">
+      <c r="E21" s="37" t="inlineStr">
         <is>
           <t>New Jersey, United States</t>
         </is>
@@ -1914,12 +1920,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H21" s="35" t="inlineStr">
+      <c r="H21" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I21" s="35" t="inlineStr">
+      <c r="I21" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1934,20 +1940,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L21" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M21" s="35" t="inlineStr"/>
+      <c r="L21" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M21" s="37" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="34" t="inlineStr">
+      <c r="A22" s="36" t="inlineStr">
         <is>
           <t>4405641326</t>
         </is>
       </c>
-      <c r="B22" s="34" t="inlineStr">
+      <c r="B22" s="36" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1957,12 +1963,12 @@
           <t>Full-stack Engineer</t>
         </is>
       </c>
-      <c r="D22" s="34" t="inlineStr">
+      <c r="D22" s="36" t="inlineStr">
         <is>
           <t>PartnerTap</t>
         </is>
       </c>
-      <c r="E22" s="34" t="inlineStr">
+      <c r="E22" s="36" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1977,12 +1983,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H22" s="34" t="inlineStr">
+      <c r="H22" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I22" s="34" t="inlineStr">
+      <c r="I22" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1997,20 +2003,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L22" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M22" s="34" t="inlineStr"/>
+      <c r="L22" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M22" s="36" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="35" t="inlineStr">
+      <c r="A23" s="37" t="inlineStr">
         <is>
           <t>4341020900</t>
         </is>
       </c>
-      <c r="B23" s="35" t="inlineStr">
+      <c r="B23" s="37" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2020,12 +2026,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D23" s="35" t="inlineStr">
+      <c r="D23" s="37" t="inlineStr">
         <is>
           <t>PlanIT Group, LLC</t>
         </is>
       </c>
-      <c r="E23" s="35" t="inlineStr">
+      <c r="E23" s="37" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -2040,12 +2046,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H23" s="35" t="inlineStr">
+      <c r="H23" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I23" s="35" t="inlineStr">
+      <c r="I23" s="37" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
@@ -2060,20 +2066,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L23" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M23" s="35" t="inlineStr"/>
+      <c r="L23" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M23" s="37" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="34" t="inlineStr">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>4304450637</t>
         </is>
       </c>
-      <c r="B24" s="34" t="inlineStr">
+      <c r="B24" s="36" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2083,12 +2089,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D24" s="34" t="inlineStr">
+      <c r="D24" s="36" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E24" s="34" t="inlineStr">
+      <c r="E24" s="36" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -2103,12 +2109,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H24" s="34" t="inlineStr">
+      <c r="H24" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I24" s="34" t="inlineStr">
+      <c r="I24" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2123,20 +2129,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L24" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M24" s="34" t="inlineStr"/>
+      <c r="L24" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M24" s="36" t="inlineStr"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="35" t="inlineStr">
+      <c r="A25" s="37" t="inlineStr">
         <is>
           <t>4304451654</t>
         </is>
       </c>
-      <c r="B25" s="35" t="inlineStr">
+      <c r="B25" s="37" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2146,12 +2152,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D25" s="35" t="inlineStr">
+      <c r="D25" s="37" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E25" s="35" t="inlineStr">
+      <c r="E25" s="37" t="inlineStr">
         <is>
           <t>Utah, United States</t>
         </is>
@@ -2166,12 +2172,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H25" s="35" t="inlineStr">
+      <c r="H25" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I25" s="35" t="inlineStr">
+      <c r="I25" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2186,20 +2192,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L25" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M25" s="35" t="inlineStr"/>
+      <c r="L25" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M25" s="37" t="inlineStr"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="34" t="inlineStr">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>4413745880</t>
         </is>
       </c>
-      <c r="B26" s="34" t="inlineStr">
+      <c r="B26" s="36" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2209,12 +2215,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D26" s="34" t="inlineStr">
+      <c r="D26" s="36" t="inlineStr">
         <is>
           <t>Crate &amp; Barrel</t>
         </is>
       </c>
-      <c r="E26" s="34" t="inlineStr">
+      <c r="E26" s="36" t="inlineStr">
         <is>
           <t>Northbrook, IL</t>
         </is>
@@ -2229,12 +2235,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H26" s="34" t="inlineStr">
+      <c r="H26" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I26" s="34" t="inlineStr">
+      <c r="I26" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2249,20 +2255,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L26" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M26" s="34" t="inlineStr"/>
+      <c r="L26" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M26" s="36" t="inlineStr"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="35" t="inlineStr">
+      <c r="A27" s="37" t="inlineStr">
         <is>
           <t>4304438841</t>
         </is>
       </c>
-      <c r="B27" s="35" t="inlineStr">
+      <c r="B27" s="37" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2272,12 +2278,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D27" s="35" t="inlineStr">
+      <c r="D27" s="37" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E27" s="35" t="inlineStr">
+      <c r="E27" s="37" t="inlineStr">
         <is>
           <t>Connecticut, United States</t>
         </is>
@@ -2292,12 +2298,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H27" s="35" t="inlineStr">
+      <c r="H27" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I27" s="35" t="inlineStr">
+      <c r="I27" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2312,20 +2318,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L27" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M27" s="35" t="inlineStr"/>
+      <c r="L27" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M27" s="37" t="inlineStr"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="34" t="inlineStr">
+      <c r="A28" s="36" t="inlineStr">
         <is>
           <t>4393215930</t>
         </is>
       </c>
-      <c r="B28" s="34" t="inlineStr">
+      <c r="B28" s="36" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2335,12 +2341,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D28" s="34" t="inlineStr">
+      <c r="D28" s="36" t="inlineStr">
         <is>
           <t>Transcend</t>
         </is>
       </c>
-      <c r="E28" s="34" t="inlineStr">
+      <c r="E28" s="36" t="inlineStr">
         <is>
           <t>California, United States</t>
         </is>
@@ -2355,12 +2361,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H28" s="34" t="inlineStr">
+      <c r="H28" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I28" s="34" t="inlineStr">
+      <c r="I28" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2375,20 +2381,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L28" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M28" s="34" t="inlineStr"/>
+      <c r="L28" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M28" s="36" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="35" t="inlineStr">
+      <c r="A29" s="37" t="inlineStr">
         <is>
           <t>4304445723</t>
         </is>
       </c>
-      <c r="B29" s="35" t="inlineStr">
+      <c r="B29" s="37" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2398,12 +2404,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D29" s="35" t="inlineStr">
+      <c r="D29" s="37" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E29" s="35" t="inlineStr">
+      <c r="E29" s="37" t="inlineStr">
         <is>
           <t>Illinois, United States</t>
         </is>
@@ -2418,12 +2424,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H29" s="35" t="inlineStr">
+      <c r="H29" s="37" t="inlineStr">
         <is>
           <t>198</t>
         </is>
       </c>
-      <c r="I29" s="35" t="inlineStr">
+      <c r="I29" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2438,20 +2444,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L29" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M29" s="35" t="inlineStr"/>
+      <c r="L29" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M29" s="37" t="inlineStr"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="34" t="inlineStr">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>4396380649</t>
         </is>
       </c>
-      <c r="B30" s="34" t="inlineStr">
+      <c r="B30" s="36" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2461,12 +2467,12 @@
           <t>Full-Stack Developer Intern, Music &amp; Audio</t>
         </is>
       </c>
-      <c r="D30" s="34" t="inlineStr">
+      <c r="D30" s="36" t="inlineStr">
         <is>
           <t>Melotech</t>
         </is>
       </c>
-      <c r="E30" s="34" t="inlineStr">
+      <c r="E30" s="36" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
@@ -2481,12 +2487,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H30" s="34" t="inlineStr">
+      <c r="H30" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I30" s="34" t="inlineStr">
+      <c r="I30" s="36" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -2501,20 +2507,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L30" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M30" s="34" t="inlineStr"/>
+      <c r="L30" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M30" s="36" t="inlineStr"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="35" t="inlineStr">
+      <c r="A31" s="37" t="inlineStr">
         <is>
           <t>4304454025</t>
         </is>
       </c>
-      <c r="B31" s="35" t="inlineStr">
+      <c r="B31" s="37" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2524,12 +2530,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D31" s="35" t="inlineStr">
+      <c r="D31" s="37" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E31" s="35" t="inlineStr">
+      <c r="E31" s="37" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -2544,12 +2550,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H31" s="35" t="inlineStr">
+      <c r="H31" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I31" s="35" t="inlineStr">
+      <c r="I31" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2564,20 +2570,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L31" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M31" s="35" t="inlineStr"/>
+      <c r="L31" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M31" s="37" t="inlineStr"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="34" t="inlineStr">
+      <c r="A32" s="36" t="inlineStr">
         <is>
           <t>4309802287</t>
         </is>
       </c>
-      <c r="B32" s="34" t="inlineStr">
+      <c r="B32" s="36" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2587,12 +2593,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D32" s="34" t="inlineStr">
+      <c r="D32" s="36" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E32" s="34" t="inlineStr">
+      <c r="E32" s="36" t="inlineStr">
         <is>
           <t>New Jersey, United States</t>
         </is>
@@ -2607,12 +2613,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H32" s="34" t="inlineStr">
+      <c r="H32" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I32" s="34" t="inlineStr">
+      <c r="I32" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2627,20 +2633,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L32" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M32" s="34" t="inlineStr"/>
+      <c r="L32" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M32" s="36" t="inlineStr"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="35" t="inlineStr">
+      <c r="A33" s="37" t="inlineStr">
         <is>
           <t>4309694880</t>
         </is>
       </c>
-      <c r="B33" s="35" t="inlineStr">
+      <c r="B33" s="37" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2650,12 +2656,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D33" s="35" t="inlineStr">
+      <c r="D33" s="37" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E33" s="35" t="inlineStr">
+      <c r="E33" s="37" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -2670,12 +2676,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H33" s="35" t="inlineStr">
+      <c r="H33" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I33" s="35" t="inlineStr">
+      <c r="I33" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2690,20 +2696,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L33" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M33" s="35" t="inlineStr"/>
+      <c r="L33" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M33" s="37" t="inlineStr"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="34" t="inlineStr">
+      <c r="A34" s="36" t="inlineStr">
         <is>
           <t>4411274012</t>
         </is>
       </c>
-      <c r="B34" s="34" t="inlineStr">
+      <c r="B34" s="36" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2713,12 +2719,12 @@
           <t>Junior UI Developer</t>
         </is>
       </c>
-      <c r="D34" s="34" t="inlineStr">
+      <c r="D34" s="36" t="inlineStr">
         <is>
           <t>General Dynamics Information Technology</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
+      <c r="E34" s="36" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -2733,12 +2739,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H34" s="34" t="inlineStr">
+      <c r="H34" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I34" s="34" t="inlineStr">
+      <c r="I34" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2753,20 +2759,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L34" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M34" s="34" t="inlineStr"/>
+      <c r="L34" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M34" s="36" t="inlineStr"/>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="35" t="inlineStr">
+      <c r="A35" s="37" t="inlineStr">
         <is>
           <t>4264562292</t>
         </is>
       </c>
-      <c r="B35" s="35" t="inlineStr">
+      <c r="B35" s="37" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2776,12 +2782,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D35" s="35" t="inlineStr">
+      <c r="D35" s="37" t="inlineStr">
         <is>
           <t>Cymertek Corporation</t>
         </is>
       </c>
-      <c r="E35" s="35" t="inlineStr">
+      <c r="E35" s="37" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
@@ -2796,12 +2802,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H35" s="35" t="inlineStr">
+      <c r="H35" s="37" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="I35" s="35" t="inlineStr">
+      <c r="I35" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2816,20 +2822,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L35" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M35" s="35" t="inlineStr"/>
+      <c r="L35" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M35" s="37" t="inlineStr"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="34" t="inlineStr">
+      <c r="A36" s="36" t="inlineStr">
         <is>
           <t>4417482675</t>
         </is>
       </c>
-      <c r="B36" s="34" t="inlineStr">
+      <c r="B36" s="36" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2839,12 +2845,12 @@
           <t>Software Developer I</t>
         </is>
       </c>
-      <c r="D36" s="34" t="inlineStr">
+      <c r="D36" s="36" t="inlineStr">
         <is>
           <t>El Paso Water</t>
         </is>
       </c>
-      <c r="E36" s="34" t="inlineStr">
+      <c r="E36" s="36" t="inlineStr">
         <is>
           <t>El Paso, TX</t>
         </is>
@@ -2859,12 +2865,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H36" s="34" t="inlineStr">
+      <c r="H36" s="36" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="I36" s="34" t="inlineStr">
+      <c r="I36" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2879,20 +2885,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L36" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M36" s="34" t="inlineStr"/>
+      <c r="L36" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M36" s="36" t="inlineStr"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="35" t="inlineStr">
+      <c r="A37" s="37" t="inlineStr">
         <is>
           <t>4416508200</t>
         </is>
       </c>
-      <c r="B37" s="35" t="inlineStr">
+      <c r="B37" s="37" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2902,12 +2908,12 @@
           <t>Software Development Engineer in Test Intern (Global E-Commerce) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D37" s="35" t="inlineStr">
+      <c r="D37" s="37" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E37" s="35" t="inlineStr">
+      <c r="E37" s="37" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -2922,12 +2928,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H37" s="35" t="inlineStr">
+      <c r="H37" s="37" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I37" s="35" t="inlineStr">
+      <c r="I37" s="37" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -2942,20 +2948,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L37" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M37" s="35" t="inlineStr"/>
+      <c r="L37" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M37" s="37" t="inlineStr"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="34" t="inlineStr">
+      <c r="A38" s="36" t="inlineStr">
         <is>
           <t>4309809191</t>
         </is>
       </c>
-      <c r="B38" s="34" t="inlineStr">
+      <c r="B38" s="36" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
@@ -2965,12 +2971,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D38" s="34" t="inlineStr">
+      <c r="D38" s="36" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E38" s="34" t="inlineStr">
+      <c r="E38" s="36" t="inlineStr">
         <is>
           <t>Ohio, United States</t>
         </is>
@@ -2985,12 +2991,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H38" s="34" t="inlineStr">
+      <c r="H38" s="36" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="I38" s="34" t="inlineStr">
+      <c r="I38" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3005,20 +3011,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L38" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M38" s="34" t="inlineStr"/>
+      <c r="L38" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M38" s="36" t="inlineStr"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="35" t="inlineStr">
+      <c r="A39" s="37" t="inlineStr">
         <is>
           <t>3986118096</t>
         </is>
       </c>
-      <c r="B39" s="35" t="inlineStr">
+      <c r="B39" s="37" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
@@ -3028,12 +3034,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D39" s="35" t="inlineStr">
+      <c r="D39" s="37" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E39" s="35" t="inlineStr">
+      <c r="E39" s="37" t="inlineStr">
         <is>
           <t>Irving, TX</t>
         </is>
@@ -3048,12 +3054,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H39" s="35" t="inlineStr">
+      <c r="H39" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I39" s="35" t="inlineStr">
+      <c r="I39" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3068,20 +3074,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L39" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M39" s="35" t="inlineStr"/>
+      <c r="L39" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M39" s="37" t="inlineStr"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="34" t="inlineStr">
+      <c r="A40" s="36" t="inlineStr">
         <is>
           <t>4309808244</t>
         </is>
       </c>
-      <c r="B40" s="34" t="inlineStr">
+      <c r="B40" s="36" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3091,12 +3097,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D40" s="34" t="inlineStr">
+      <c r="D40" s="36" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E40" s="34" t="inlineStr">
+      <c r="E40" s="36" t="inlineStr">
         <is>
           <t>Massachusetts, United States</t>
         </is>
@@ -3111,12 +3117,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H40" s="34" t="inlineStr">
+      <c r="H40" s="36" t="inlineStr">
         <is>
           <t>166</t>
         </is>
       </c>
-      <c r="I40" s="34" t="inlineStr">
+      <c r="I40" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3131,20 +3137,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L40" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M40" s="34" t="inlineStr"/>
+      <c r="L40" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M40" s="36" t="inlineStr"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="35" t="inlineStr">
+      <c r="A41" s="37" t="inlineStr">
         <is>
           <t>4362173625</t>
         </is>
       </c>
-      <c r="B41" s="35" t="inlineStr">
+      <c r="B41" s="37" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3154,12 +3160,12 @@
           <t>Full Stack Engineer</t>
         </is>
       </c>
-      <c r="D41" s="35" t="inlineStr">
+      <c r="D41" s="37" t="inlineStr">
         <is>
           <t>Empower Sleep</t>
         </is>
       </c>
-      <c r="E41" s="35" t="inlineStr">
+      <c r="E41" s="37" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3174,12 +3180,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H41" s="35" t="inlineStr">
+      <c r="H41" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I41" s="35" t="inlineStr">
+      <c r="I41" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3194,20 +3200,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L41" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M41" s="35" t="inlineStr"/>
+      <c r="L41" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M41" s="37" t="inlineStr"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="34" t="inlineStr">
+      <c r="A42" s="36" t="inlineStr">
         <is>
           <t>4309812093</t>
         </is>
       </c>
-      <c r="B42" s="34" t="inlineStr">
+      <c r="B42" s="36" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3217,12 +3223,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D42" s="34" t="inlineStr">
+      <c r="D42" s="36" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E42" s="34" t="inlineStr">
+      <c r="E42" s="36" t="inlineStr">
         <is>
           <t>Florida, United States</t>
         </is>
@@ -3237,12 +3243,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H42" s="34" t="inlineStr">
+      <c r="H42" s="36" t="inlineStr">
         <is>
           <t>158</t>
         </is>
       </c>
-      <c r="I42" s="34" t="inlineStr">
+      <c r="I42" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3257,20 +3263,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L42" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M42" s="34" t="inlineStr"/>
+      <c r="L42" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M42" s="36" t="inlineStr"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="35" t="inlineStr">
+      <c r="A43" s="37" t="inlineStr">
         <is>
           <t>4391759914</t>
         </is>
       </c>
-      <c r="B43" s="35" t="inlineStr">
+      <c r="B43" s="37" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3280,12 +3286,12 @@
           <t>QA Engineering Internship</t>
         </is>
       </c>
-      <c r="D43" s="35" t="inlineStr">
+      <c r="D43" s="37" t="inlineStr">
         <is>
           <t>Chartbeat</t>
         </is>
       </c>
-      <c r="E43" s="35" t="inlineStr">
+      <c r="E43" s="37" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -3300,12 +3306,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H43" s="35" t="inlineStr">
+      <c r="H43" s="37" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="I43" s="35" t="inlineStr">
+      <c r="I43" s="37" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3320,20 +3326,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L43" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M43" s="35" t="inlineStr"/>
+      <c r="L43" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M43" s="37" t="inlineStr"/>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="34" t="inlineStr">
+      <c r="A44" s="36" t="inlineStr">
         <is>
           <t>4412855678</t>
         </is>
       </c>
-      <c r="B44" s="34" t="inlineStr">
+      <c r="B44" s="36" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3343,12 +3349,12 @@
           <t>AI Integration Engineer</t>
         </is>
       </c>
-      <c r="D44" s="34" t="inlineStr">
+      <c r="D44" s="36" t="inlineStr">
         <is>
           <t>UST</t>
         </is>
       </c>
-      <c r="E44" s="34" t="inlineStr">
+      <c r="E44" s="36" t="inlineStr">
         <is>
           <t>Santa Clara, CA</t>
         </is>
@@ -3363,12 +3369,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H44" s="34" t="inlineStr">
+      <c r="H44" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I44" s="34" t="inlineStr">
+      <c r="I44" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3383,20 +3389,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L44" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M44" s="34" t="inlineStr"/>
+      <c r="L44" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M44" s="36" t="inlineStr"/>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="35" t="inlineStr">
+      <c r="A45" s="37" t="inlineStr">
         <is>
           <t>4309805219</t>
         </is>
       </c>
-      <c r="B45" s="35" t="inlineStr">
+      <c r="B45" s="37" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3406,12 +3412,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D45" s="35" t="inlineStr">
+      <c r="D45" s="37" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E45" s="35" t="inlineStr">
+      <c r="E45" s="37" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -3426,12 +3432,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H45" s="35" t="inlineStr">
+      <c r="H45" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I45" s="35" t="inlineStr">
+      <c r="I45" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3446,20 +3452,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L45" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M45" s="35" t="inlineStr"/>
+      <c r="L45" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M45" s="37" t="inlineStr"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="34" t="inlineStr">
+      <c r="A46" s="36" t="inlineStr">
         <is>
           <t>4409726429</t>
         </is>
       </c>
-      <c r="B46" s="34" t="inlineStr">
+      <c r="B46" s="36" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3469,12 +3475,12 @@
           <t>Data Science Intern</t>
         </is>
       </c>
-      <c r="D46" s="34" t="inlineStr">
+      <c r="D46" s="36" t="inlineStr">
         <is>
           <t>Rundoo</t>
         </is>
       </c>
-      <c r="E46" s="34" t="inlineStr">
+      <c r="E46" s="36" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3489,12 +3495,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H46" s="34" t="inlineStr">
+      <c r="H46" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I46" s="34" t="inlineStr">
+      <c r="I46" s="36" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3509,20 +3515,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L46" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M46" s="34" t="inlineStr"/>
+      <c r="L46" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M46" s="36" t="inlineStr"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="35" t="inlineStr">
+      <c r="A47" s="37" t="inlineStr">
         <is>
           <t>4305671729</t>
         </is>
       </c>
-      <c r="B47" s="35" t="inlineStr">
+      <c r="B47" s="37" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3532,12 +3538,12 @@
           <t>DoD SkillBridge Internship/Fellowship Opportunity Application (U.S. Military Only)</t>
         </is>
       </c>
-      <c r="D47" s="35" t="inlineStr">
+      <c r="D47" s="37" t="inlineStr">
         <is>
           <t>Onsights</t>
         </is>
       </c>
-      <c r="E47" s="35" t="inlineStr">
+      <c r="E47" s="37" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -3552,12 +3558,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H47" s="35" t="inlineStr">
+      <c r="H47" s="37" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I47" s="35" t="inlineStr">
+      <c r="I47" s="37" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3572,20 +3578,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L47" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M47" s="35" t="inlineStr"/>
+      <c r="L47" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M47" s="37" t="inlineStr"/>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="34" t="inlineStr">
+      <c r="A48" s="36" t="inlineStr">
         <is>
           <t>4414096220</t>
         </is>
       </c>
-      <c r="B48" s="34" t="inlineStr">
+      <c r="B48" s="36" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3595,12 +3601,12 @@
           <t>Visualization Engineer Intern</t>
         </is>
       </c>
-      <c r="D48" s="34" t="inlineStr">
+      <c r="D48" s="36" t="inlineStr">
         <is>
           <t>Leidos</t>
         </is>
       </c>
-      <c r="E48" s="34" t="inlineStr">
+      <c r="E48" s="36" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3615,12 +3621,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H48" s="34" t="inlineStr">
+      <c r="H48" s="36" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="I48" s="34" t="inlineStr">
+      <c r="I48" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3635,20 +3641,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L48" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M48" s="34" t="inlineStr"/>
+      <c r="L48" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M48" s="36" t="inlineStr"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="35" t="inlineStr">
+      <c r="A49" s="37" t="inlineStr">
         <is>
           <t>4361076044</t>
         </is>
       </c>
-      <c r="B49" s="35" t="inlineStr">
+      <c r="B49" s="37" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3658,12 +3664,12 @@
           <t>GenAI Engineering Intern  - SkillBridge (Remote)</t>
         </is>
       </c>
-      <c r="D49" s="35" t="inlineStr">
+      <c r="D49" s="37" t="inlineStr">
         <is>
           <t>CrowdStrike</t>
         </is>
       </c>
-      <c r="E49" s="35" t="inlineStr">
+      <c r="E49" s="37" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3678,12 +3684,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H49" s="35" t="inlineStr">
+      <c r="H49" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I49" s="35" t="inlineStr">
+      <c r="I49" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3698,20 +3704,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L49" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M49" s="35" t="inlineStr"/>
+      <c r="L49" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M49" s="37" t="inlineStr"/>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="34" t="inlineStr">
+      <c r="A50" s="36" t="inlineStr">
         <is>
           <t>4417553585</t>
         </is>
       </c>
-      <c r="B50" s="34" t="inlineStr">
+      <c r="B50" s="36" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3721,12 +3727,12 @@
           <t>Entry-Level Software Engineer | Remote</t>
         </is>
       </c>
-      <c r="D50" s="34" t="inlineStr">
+      <c r="D50" s="36" t="inlineStr">
         <is>
           <t>Crossing Hurdles</t>
         </is>
       </c>
-      <c r="E50" s="34" t="inlineStr">
+      <c r="E50" s="36" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3741,12 +3747,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H50" s="34" t="inlineStr">
+      <c r="H50" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I50" s="34" t="inlineStr">
+      <c r="I50" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3761,20 +3767,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L50" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M50" s="34" t="inlineStr"/>
+      <c r="L50" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M50" s="36" t="inlineStr"/>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="35" t="inlineStr">
+      <c r="A51" s="37" t="inlineStr">
         <is>
           <t>4309699451</t>
         </is>
       </c>
-      <c r="B51" s="35" t="inlineStr">
+      <c r="B51" s="37" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3784,12 +3790,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D51" s="35" t="inlineStr">
+      <c r="D51" s="37" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E51" s="35" t="inlineStr">
+      <c r="E51" s="37" t="inlineStr">
         <is>
           <t>Washington, United States</t>
         </is>
@@ -3804,12 +3810,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H51" s="35" t="inlineStr">
+      <c r="H51" s="37" t="inlineStr">
         <is>
           <t>109</t>
         </is>
       </c>
-      <c r="I51" s="35" t="inlineStr">
+      <c r="I51" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3824,20 +3830,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L51" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M51" s="35" t="inlineStr"/>
+      <c r="L51" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M51" s="37" t="inlineStr"/>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="34" t="inlineStr">
+      <c r="A52" s="36" t="inlineStr">
         <is>
           <t>4406945262</t>
         </is>
       </c>
-      <c r="B52" s="34" t="inlineStr">
+      <c r="B52" s="36" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3847,12 +3853,12 @@
           <t>DevSecOps Intern</t>
         </is>
       </c>
-      <c r="D52" s="34" t="inlineStr">
+      <c r="D52" s="36" t="inlineStr">
         <is>
           <t>Modern Technology Solutions, Inc. (MTSI)</t>
         </is>
       </c>
-      <c r="E52" s="34" t="inlineStr">
+      <c r="E52" s="36" t="inlineStr">
         <is>
           <t>Niceville, FL</t>
         </is>
@@ -3867,12 +3873,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H52" s="34" t="inlineStr">
+      <c r="H52" s="36" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="I52" s="34" t="inlineStr">
+      <c r="I52" s="36" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3887,20 +3893,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L52" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M52" s="34" t="inlineStr"/>
+      <c r="L52" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M52" s="36" t="inlineStr"/>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="35" t="inlineStr">
+      <c r="A53" s="37" t="inlineStr">
         <is>
           <t>4407937810</t>
         </is>
       </c>
-      <c r="B53" s="35" t="inlineStr">
+      <c r="B53" s="37" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3910,12 +3916,12 @@
           <t>Temporary Intern - Agentic AI &amp; Neural-Symbolic Systems (Healthcare)</t>
         </is>
       </c>
-      <c r="D53" s="35" t="inlineStr">
+      <c r="D53" s="37" t="inlineStr">
         <is>
           <t>Cotiviti</t>
         </is>
       </c>
-      <c r="E53" s="35" t="inlineStr">
+      <c r="E53" s="37" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3930,12 +3936,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H53" s="35" t="inlineStr">
+      <c r="H53" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I53" s="35" t="inlineStr">
+      <c r="I53" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3950,20 +3956,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L53" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M53" s="35" t="inlineStr"/>
+      <c r="L53" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M53" s="37" t="inlineStr"/>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="34" t="inlineStr">
+      <c r="A54" s="36" t="inlineStr">
         <is>
           <t>4414089997</t>
         </is>
       </c>
-      <c r="B54" s="34" t="inlineStr">
+      <c r="B54" s="36" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3973,12 +3979,12 @@
           <t>Visualization Engineer Intern</t>
         </is>
       </c>
-      <c r="D54" s="34" t="inlineStr">
+      <c r="D54" s="36" t="inlineStr">
         <is>
           <t>Leidos</t>
         </is>
       </c>
-      <c r="E54" s="34" t="inlineStr">
+      <c r="E54" s="36" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3993,12 +3999,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H54" s="34" t="inlineStr">
+      <c r="H54" s="36" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="I54" s="34" t="inlineStr">
+      <c r="I54" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4013,20 +4019,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L54" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M54" s="34" t="inlineStr"/>
+      <c r="L54" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M54" s="36" t="inlineStr"/>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="35" t="inlineStr">
+      <c r="A55" s="37" t="inlineStr">
         <is>
           <t>4387443129</t>
         </is>
       </c>
-      <c r="B55" s="35" t="inlineStr">
+      <c r="B55" s="37" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4036,12 +4042,12 @@
           <t>2026 Interns</t>
         </is>
       </c>
-      <c r="D55" s="35" t="inlineStr">
+      <c r="D55" s="37" t="inlineStr">
         <is>
           <t>Givelify</t>
         </is>
       </c>
-      <c r="E55" s="35" t="inlineStr">
+      <c r="E55" s="37" t="inlineStr">
         <is>
           <t>Dallas, TX</t>
         </is>
@@ -4056,12 +4062,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H55" s="35" t="inlineStr">
+      <c r="H55" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I55" s="35" t="inlineStr">
+      <c r="I55" s="37" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -4076,20 +4082,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L55" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M55" s="35" t="inlineStr"/>
+      <c r="L55" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M55" s="37" t="inlineStr"/>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="34" t="inlineStr">
+      <c r="A56" s="36" t="inlineStr">
         <is>
           <t>4337980765</t>
         </is>
       </c>
-      <c r="B56" s="34" t="inlineStr">
+      <c r="B56" s="36" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4099,12 +4105,12 @@
           <t>Submitting for a General Internship Application</t>
         </is>
       </c>
-      <c r="D56" s="34" t="inlineStr">
+      <c r="D56" s="36" t="inlineStr">
         <is>
           <t>Chainguard</t>
         </is>
       </c>
-      <c r="E56" s="34" t="inlineStr">
+      <c r="E56" s="36" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4119,12 +4125,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H56" s="34" t="inlineStr">
+      <c r="H56" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I56" s="34" t="inlineStr">
+      <c r="I56" s="36" t="inlineStr">
         <is>
           <t>Volunteer</t>
         </is>
@@ -4139,20 +4145,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L56" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M56" s="34" t="inlineStr"/>
+      <c r="L56" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M56" s="36" t="inlineStr"/>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="35" t="inlineStr">
+      <c r="A57" s="37" t="inlineStr">
         <is>
           <t>4417030460</t>
         </is>
       </c>
-      <c r="B57" s="35" t="inlineStr">
+      <c r="B57" s="37" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4162,12 +4168,12 @@
           <t>AI Researcher Intern</t>
         </is>
       </c>
-      <c r="D57" s="35" t="inlineStr">
+      <c r="D57" s="37" t="inlineStr">
         <is>
           <t>BioSpace</t>
         </is>
       </c>
-      <c r="E57" s="35" t="inlineStr">
+      <c r="E57" s="37" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4182,12 +4188,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H57" s="35" t="inlineStr">
+      <c r="H57" s="37" t="inlineStr">
         <is>
           <t>151</t>
         </is>
       </c>
-      <c r="I57" s="35" t="inlineStr">
+      <c r="I57" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4202,20 +4208,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L57" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M57" s="35" t="inlineStr"/>
+      <c r="L57" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M57" s="37" t="inlineStr"/>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="34" t="inlineStr">
+      <c r="A58" s="36" t="inlineStr">
         <is>
           <t>4406930916</t>
         </is>
       </c>
-      <c r="B58" s="34" t="inlineStr">
+      <c r="B58" s="36" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4225,12 +4231,12 @@
           <t>DevSecOps Intern</t>
         </is>
       </c>
-      <c r="D58" s="34" t="inlineStr">
+      <c r="D58" s="36" t="inlineStr">
         <is>
           <t>Modern Technology Solutions, Inc. (MTSI)</t>
         </is>
       </c>
-      <c r="E58" s="34" t="inlineStr">
+      <c r="E58" s="36" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4245,12 +4251,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H58" s="34" t="inlineStr">
+      <c r="H58" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I58" s="34" t="inlineStr">
+      <c r="I58" s="36" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -4265,20 +4271,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L58" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M58" s="34" t="inlineStr"/>
+      <c r="L58" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M58" s="36" t="inlineStr"/>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="35" t="inlineStr">
+      <c r="A59" s="37" t="inlineStr">
         <is>
           <t>4385798937</t>
         </is>
       </c>
-      <c r="B59" s="35" t="inlineStr">
+      <c r="B59" s="37" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4288,12 +4294,12 @@
           <t>Research Intern on Generative and Protective AI for Content Creation</t>
         </is>
       </c>
-      <c r="D59" s="35" t="inlineStr">
+      <c r="D59" s="37" t="inlineStr">
         <is>
           <t>SonyAI</t>
         </is>
       </c>
-      <c r="E59" s="35" t="inlineStr">
+      <c r="E59" s="37" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -4308,12 +4314,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H59" s="35" t="inlineStr">
+      <c r="H59" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I59" s="35" t="inlineStr">
+      <c r="I59" s="37" t="inlineStr">
         <is>
           <t>Part-time</t>
         </is>
@@ -4328,20 +4334,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L59" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M59" s="35" t="inlineStr"/>
+      <c r="L59" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M59" s="37" t="inlineStr"/>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="34" t="inlineStr">
+      <c r="A60" s="36" t="inlineStr">
         <is>
           <t>4414396950</t>
         </is>
       </c>
-      <c r="B60" s="34" t="inlineStr">
+      <c r="B60" s="36" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4351,12 +4357,12 @@
           <t>Power Platform Intern</t>
         </is>
       </c>
-      <c r="D60" s="34" t="inlineStr">
+      <c r="D60" s="36" t="inlineStr">
         <is>
           <t>Leidos</t>
         </is>
       </c>
-      <c r="E60" s="34" t="inlineStr">
+      <c r="E60" s="36" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4371,12 +4377,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H60" s="34" t="inlineStr">
+      <c r="H60" s="36" t="inlineStr">
         <is>
           <t>135</t>
         </is>
       </c>
-      <c r="I60" s="34" t="inlineStr">
+      <c r="I60" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4391,20 +4397,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L60" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M60" s="34" t="inlineStr"/>
+      <c r="L60" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M60" s="36" t="inlineStr"/>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="35" t="inlineStr">
+      <c r="A61" s="37" t="inlineStr">
         <is>
           <t>4413699205</t>
         </is>
       </c>
-      <c r="B61" s="35" t="inlineStr">
+      <c r="B61" s="37" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4414,12 +4420,12 @@
           <t>Junior Software Engineer - Automation &amp; Integration</t>
         </is>
       </c>
-      <c r="D61" s="35" t="inlineStr">
+      <c r="D61" s="37" t="inlineStr">
         <is>
           <t>Fletcher Development LLC</t>
         </is>
       </c>
-      <c r="E61" s="35" t="inlineStr">
+      <c r="E61" s="37" t="inlineStr">
         <is>
           <t>Redding, CT</t>
         </is>
@@ -4434,12 +4440,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H61" s="35" t="inlineStr">
+      <c r="H61" s="37" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="I61" s="35" t="inlineStr">
+      <c r="I61" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4454,20 +4460,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L61" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M61" s="35" t="inlineStr"/>
+      <c r="L61" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M61" s="37" t="inlineStr"/>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="34" t="inlineStr">
+      <c r="A62" s="36" t="inlineStr">
         <is>
           <t>4416171988</t>
         </is>
       </c>
-      <c r="B62" s="34" t="inlineStr">
+      <c r="B62" s="36" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4477,12 +4483,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D62" s="34" t="inlineStr">
+      <c r="D62" s="36" t="inlineStr">
         <is>
           <t>Altec</t>
         </is>
       </c>
-      <c r="E62" s="34" t="inlineStr">
+      <c r="E62" s="36" t="inlineStr">
         <is>
           <t>Birmingham, AL</t>
         </is>
@@ -4497,12 +4503,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H62" s="34" t="inlineStr">
+      <c r="H62" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I62" s="34" t="inlineStr">
+      <c r="I62" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4517,20 +4523,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L62" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M62" s="34" t="inlineStr"/>
+      <c r="L62" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M62" s="36" t="inlineStr"/>
     </row>
     <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="35" t="inlineStr">
+      <c r="A63" s="37" t="inlineStr">
         <is>
           <t>4403444963</t>
         </is>
       </c>
-      <c r="B63" s="35" t="inlineStr">
+      <c r="B63" s="37" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4540,12 +4546,12 @@
           <t>Junior Applications Developer (NY HELPS) #2026-252</t>
         </is>
       </c>
-      <c r="D63" s="35" t="inlineStr">
+      <c r="D63" s="37" t="inlineStr">
         <is>
           <t>Capital Region BOCES</t>
         </is>
       </c>
-      <c r="E63" s="35" t="inlineStr">
+      <c r="E63" s="37" t="inlineStr">
         <is>
           <t>Albany, NY</t>
         </is>
@@ -4560,12 +4566,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H63" s="35" t="inlineStr">
+      <c r="H63" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I63" s="35" t="inlineStr">
+      <c r="I63" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4580,20 +4586,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L63" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M63" s="35" t="inlineStr"/>
+      <c r="L63" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M63" s="37" t="inlineStr"/>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="34" t="inlineStr">
+      <c r="A64" s="36" t="inlineStr">
         <is>
           <t>4418506121</t>
         </is>
       </c>
-      <c r="B64" s="34" t="inlineStr">
+      <c r="B64" s="36" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4603,12 +4609,12 @@
           <t>Core System Junior Developer</t>
         </is>
       </c>
-      <c r="D64" s="34" t="inlineStr">
+      <c r="D64" s="36" t="inlineStr">
         <is>
           <t>Cyprus Federal Credit Union</t>
         </is>
       </c>
-      <c r="E64" s="34" t="inlineStr">
+      <c r="E64" s="36" t="inlineStr">
         <is>
           <t>West Jordan, UT</t>
         </is>
@@ -4623,12 +4629,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H64" s="34" t="inlineStr">
+      <c r="H64" s="36" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="I64" s="34" t="inlineStr">
+      <c r="I64" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4643,20 +4649,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L64" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M64" s="34" t="inlineStr"/>
+      <c r="L64" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M64" s="36" t="inlineStr"/>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="35" t="inlineStr">
+      <c r="A65" s="37" t="inlineStr">
         <is>
           <t>4413905706</t>
         </is>
       </c>
-      <c r="B65" s="35" t="inlineStr">
+      <c r="B65" s="37" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4666,12 +4672,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D65" s="35" t="inlineStr">
+      <c r="D65" s="37" t="inlineStr">
         <is>
           <t>Arnex Solutions LLC</t>
         </is>
       </c>
-      <c r="E65" s="35" t="inlineStr">
+      <c r="E65" s="37" t="inlineStr">
         <is>
           <t>Princeton, NJ</t>
         </is>
@@ -4686,12 +4692,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H65" s="35" t="inlineStr">
+      <c r="H65" s="37" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I65" s="35" t="inlineStr">
+      <c r="I65" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4706,20 +4712,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L65" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M65" s="35" t="inlineStr"/>
+      <c r="L65" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M65" s="37" t="inlineStr"/>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="34" t="inlineStr">
+      <c r="A66" s="36" t="inlineStr">
         <is>
           <t>4418963446</t>
         </is>
       </c>
-      <c r="B66" s="34" t="inlineStr">
+      <c r="B66" s="36" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4729,12 +4735,12 @@
           <t>Junior Software Engineer - Automation &amp; Integration</t>
         </is>
       </c>
-      <c r="D66" s="34" t="inlineStr">
+      <c r="D66" s="36" t="inlineStr">
         <is>
           <t>Vibrant Building Technologies</t>
         </is>
       </c>
-      <c r="E66" s="34" t="inlineStr">
+      <c r="E66" s="36" t="inlineStr">
         <is>
           <t>Ridgefield, CT</t>
         </is>
@@ -4749,12 +4755,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H66" s="34" t="inlineStr">
+      <c r="H66" s="36" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="I66" s="34" t="inlineStr">
+      <c r="I66" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4769,20 +4775,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L66" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M66" s="34" t="inlineStr"/>
+      <c r="L66" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M66" s="36" t="inlineStr"/>
     </row>
     <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="35" t="inlineStr">
+      <c r="A67" s="37" t="inlineStr">
         <is>
           <t>4413759052</t>
         </is>
       </c>
-      <c r="B67" s="35" t="inlineStr">
+      <c r="B67" s="37" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4792,12 +4798,12 @@
           <t>Junior Full Stack Developer</t>
         </is>
       </c>
-      <c r="D67" s="35" t="inlineStr">
+      <c r="D67" s="37" t="inlineStr">
         <is>
           <t>Allied World Reinsurance Company</t>
         </is>
       </c>
-      <c r="E67" s="35" t="inlineStr">
+      <c r="E67" s="37" t="inlineStr">
         <is>
           <t>Iselin, NJ</t>
         </is>
@@ -4812,12 +4818,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H67" s="35" t="inlineStr">
+      <c r="H67" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I67" s="35" t="inlineStr">
+      <c r="I67" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4832,20 +4838,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L67" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M67" s="35" t="inlineStr"/>
+      <c r="L67" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M67" s="37" t="inlineStr"/>
     </row>
     <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="34" t="inlineStr">
+      <c r="A68" s="36" t="inlineStr">
         <is>
           <t>4417542502</t>
         </is>
       </c>
-      <c r="B68" s="34" t="inlineStr">
+      <c r="B68" s="36" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4855,12 +4861,12 @@
           <t>Junior Developer</t>
         </is>
       </c>
-      <c r="D68" s="34" t="inlineStr">
+      <c r="D68" s="36" t="inlineStr">
         <is>
           <t>CloudMasonry</t>
         </is>
       </c>
-      <c r="E68" s="34" t="inlineStr">
+      <c r="E68" s="36" t="inlineStr">
         <is>
           <t>Indianapolis, IN</t>
         </is>
@@ -4875,12 +4881,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H68" s="34" t="inlineStr">
+      <c r="H68" s="36" t="inlineStr">
         <is>
           <t>154</t>
         </is>
       </c>
-      <c r="I68" s="34" t="inlineStr">
+      <c r="I68" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4895,20 +4901,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L68" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M68" s="34" t="inlineStr"/>
+      <c r="L68" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M68" s="36" t="inlineStr"/>
     </row>
     <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="35" t="inlineStr">
+      <c r="A69" s="37" t="inlineStr">
         <is>
           <t>4374856035</t>
         </is>
       </c>
-      <c r="B69" s="35" t="inlineStr">
+      <c r="B69" s="37" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4918,12 +4924,12 @@
           <t>Programmer II</t>
         </is>
       </c>
-      <c r="D69" s="35" t="inlineStr">
+      <c r="D69" s="37" t="inlineStr">
         <is>
           <t>Willis Knighton Health</t>
         </is>
       </c>
-      <c r="E69" s="35" t="inlineStr">
+      <c r="E69" s="37" t="inlineStr">
         <is>
           <t>Louisiana, United States</t>
         </is>
@@ -4938,12 +4944,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H69" s="35" t="inlineStr">
+      <c r="H69" s="37" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="I69" s="35" t="inlineStr">
+      <c r="I69" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4958,20 +4964,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L69" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M69" s="35" t="inlineStr"/>
+      <c r="L69" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M69" s="37" t="inlineStr"/>
     </row>
     <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="34" t="inlineStr">
+      <c r="A70" s="36" t="inlineStr">
         <is>
           <t>4416302564</t>
         </is>
       </c>
-      <c r="B70" s="34" t="inlineStr">
+      <c r="B70" s="36" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4981,12 +4987,12 @@
           <t>Software Engineer I</t>
         </is>
       </c>
-      <c r="D70" s="34" t="inlineStr">
+      <c r="D70" s="36" t="inlineStr">
         <is>
           <t>American Express</t>
         </is>
       </c>
-      <c r="E70" s="34" t="inlineStr">
+      <c r="E70" s="36" t="inlineStr">
         <is>
           <t>Sunrise, FL</t>
         </is>
@@ -5001,12 +5007,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H70" s="34" t="inlineStr">
+      <c r="H70" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I70" s="34" t="inlineStr">
+      <c r="I70" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5021,20 +5027,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L70" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M70" s="34" t="inlineStr"/>
+      <c r="L70" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M70" s="36" t="inlineStr"/>
     </row>
     <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="35" t="inlineStr">
+      <c r="A71" s="37" t="inlineStr">
         <is>
           <t>4417014137</t>
         </is>
       </c>
-      <c r="B71" s="35" t="inlineStr">
+      <c r="B71" s="37" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5044,12 +5050,12 @@
           <t>Junior Software Developer, Applications</t>
         </is>
       </c>
-      <c r="D71" s="35" t="inlineStr">
+      <c r="D71" s="37" t="inlineStr">
         <is>
           <t>ECS</t>
         </is>
       </c>
-      <c r="E71" s="35" t="inlineStr">
+      <c r="E71" s="37" t="inlineStr">
         <is>
           <t>O'Fallon, IL</t>
         </is>
@@ -5064,12 +5070,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H71" s="35" t="inlineStr">
+      <c r="H71" s="37" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="I71" s="35" t="inlineStr">
+      <c r="I71" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5084,20 +5090,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L71" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M71" s="35" t="inlineStr"/>
+      <c r="L71" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M71" s="37" t="inlineStr"/>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="34" t="inlineStr">
+      <c r="A72" s="36" t="inlineStr">
         <is>
           <t>4381211472</t>
         </is>
       </c>
-      <c r="B72" s="34" t="inlineStr">
+      <c r="B72" s="36" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5107,12 +5113,12 @@
           <t>Programmer</t>
         </is>
       </c>
-      <c r="D72" s="34" t="inlineStr">
+      <c r="D72" s="36" t="inlineStr">
         <is>
           <t>City of New York</t>
         </is>
       </c>
-      <c r="E72" s="34" t="inlineStr">
+      <c r="E72" s="36" t="inlineStr">
         <is>
           <t>Bronx, NY</t>
         </is>
@@ -5127,12 +5133,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H72" s="34" t="inlineStr">
+      <c r="H72" s="36" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="I72" s="34" t="inlineStr">
+      <c r="I72" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5147,20 +5153,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L72" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M72" s="34" t="inlineStr"/>
+      <c r="L72" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M72" s="36" t="inlineStr"/>
     </row>
     <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="35" t="inlineStr">
+      <c r="A73" s="37" t="inlineStr">
         <is>
           <t>4168416236</t>
         </is>
       </c>
-      <c r="B73" s="35" t="inlineStr">
+      <c r="B73" s="37" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5170,12 +5176,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D73" s="35" t="inlineStr">
+      <c r="D73" s="37" t="inlineStr">
         <is>
           <t>Interclypse</t>
         </is>
       </c>
-      <c r="E73" s="35" t="inlineStr">
+      <c r="E73" s="37" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
@@ -5190,12 +5196,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H73" s="35" t="inlineStr">
+      <c r="H73" s="37" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I73" s="35" t="inlineStr">
+      <c r="I73" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5210,20 +5216,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L73" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M73" s="35" t="inlineStr"/>
+      <c r="L73" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M73" s="37" t="inlineStr"/>
     </row>
     <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="34" t="inlineStr">
+      <c r="A74" s="36" t="inlineStr">
         <is>
           <t>4403507357</t>
         </is>
       </c>
-      <c r="B74" s="34" t="inlineStr">
+      <c r="B74" s="36" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5233,12 +5239,12 @@
           <t>Software Developer:</t>
         </is>
       </c>
-      <c r="D74" s="34" t="inlineStr">
+      <c r="D74" s="36" t="inlineStr">
         <is>
           <t>IQuest Solutions Corporation</t>
         </is>
       </c>
-      <c r="E74" s="34" t="inlineStr">
+      <c r="E74" s="36" t="inlineStr">
         <is>
           <t>Plano, TX</t>
         </is>
@@ -5253,12 +5259,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H74" s="34" t="inlineStr">
+      <c r="H74" s="36" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I74" s="34" t="inlineStr">
+      <c r="I74" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5273,20 +5279,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L74" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M74" s="34" t="inlineStr"/>
+      <c r="L74" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M74" s="36" t="inlineStr"/>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="35" t="inlineStr">
+      <c r="A75" s="37" t="inlineStr">
         <is>
           <t>4309800238</t>
         </is>
       </c>
-      <c r="B75" s="35" t="inlineStr">
+      <c r="B75" s="37" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5296,12 +5302,12 @@
           <t>Backend Software Engineer</t>
         </is>
       </c>
-      <c r="D75" s="35" t="inlineStr">
+      <c r="D75" s="37" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E75" s="35" t="inlineStr">
+      <c r="E75" s="37" t="inlineStr">
         <is>
           <t>Texas, United States</t>
         </is>
@@ -5316,12 +5322,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H75" s="35" t="inlineStr">
+      <c r="H75" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I75" s="35" t="inlineStr">
+      <c r="I75" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5336,20 +5342,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L75" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M75" s="35" t="inlineStr"/>
+      <c r="L75" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M75" s="37" t="inlineStr"/>
     </row>
     <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="34" t="inlineStr">
+      <c r="A76" s="36" t="inlineStr">
         <is>
           <t>4404109089</t>
         </is>
       </c>
-      <c r="B76" s="34" t="inlineStr">
+      <c r="B76" s="36" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5359,12 +5365,12 @@
           <t>Software Development Engineer I</t>
         </is>
       </c>
-      <c r="D76" s="34" t="inlineStr">
+      <c r="D76" s="36" t="inlineStr">
         <is>
           <t>GM Financial</t>
         </is>
       </c>
-      <c r="E76" s="34" t="inlineStr">
+      <c r="E76" s="36" t="inlineStr">
         <is>
           <t>Arlington, TX</t>
         </is>
@@ -5379,12 +5385,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H76" s="34" t="inlineStr">
+      <c r="H76" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I76" s="34" t="inlineStr">
+      <c r="I76" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5399,20 +5405,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L76" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M76" s="34" t="inlineStr"/>
+      <c r="L76" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M76" s="36" t="inlineStr"/>
     </row>
     <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="35" t="inlineStr">
+      <c r="A77" s="37" t="inlineStr">
         <is>
           <t>3986116411</t>
         </is>
       </c>
-      <c r="B77" s="35" t="inlineStr">
+      <c r="B77" s="37" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5422,12 +5428,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D77" s="35" t="inlineStr">
+      <c r="D77" s="37" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E77" s="35" t="inlineStr">
+      <c r="E77" s="37" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -5442,12 +5448,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H77" s="35" t="inlineStr">
+      <c r="H77" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I77" s="35" t="inlineStr">
+      <c r="I77" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5462,20 +5468,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L77" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M77" s="35" t="inlineStr"/>
+      <c r="L77" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M77" s="37" t="inlineStr"/>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="34" t="inlineStr">
+      <c r="A78" s="36" t="inlineStr">
         <is>
           <t>4418051524</t>
         </is>
       </c>
-      <c r="B78" s="34" t="inlineStr">
+      <c r="B78" s="36" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5485,12 +5491,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D78" s="34" t="inlineStr">
+      <c r="D78" s="36" t="inlineStr">
         <is>
           <t>Relativity</t>
         </is>
       </c>
-      <c r="E78" s="34" t="inlineStr">
+      <c r="E78" s="36" t="inlineStr">
         <is>
           <t>Texas, United States</t>
         </is>
@@ -5505,12 +5511,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H78" s="34" t="inlineStr">
+      <c r="H78" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I78" s="34" t="inlineStr">
+      <c r="I78" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5525,20 +5531,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L78" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M78" s="34" t="inlineStr"/>
+      <c r="L78" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M78" s="36" t="inlineStr"/>
     </row>
     <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="35" t="inlineStr">
+      <c r="A79" s="37" t="inlineStr">
         <is>
           <t>4409856693</t>
         </is>
       </c>
-      <c r="B79" s="35" t="inlineStr">
+      <c r="B79" s="37" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5548,12 +5554,12 @@
           <t>Software Engineer - Payments</t>
         </is>
       </c>
-      <c r="D79" s="35" t="inlineStr">
+      <c r="D79" s="37" t="inlineStr">
         <is>
           <t>Cloudbeds</t>
         </is>
       </c>
-      <c r="E79" s="35" t="inlineStr">
+      <c r="E79" s="37" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -5568,12 +5574,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H79" s="35" t="inlineStr">
+      <c r="H79" s="37" t="inlineStr">
         <is>
           <t>177</t>
         </is>
       </c>
-      <c r="I79" s="35" t="inlineStr">
+      <c r="I79" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5588,20 +5594,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L79" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M79" s="35" t="inlineStr"/>
+      <c r="L79" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M79" s="37" t="inlineStr"/>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="34" t="inlineStr">
+      <c r="A80" s="36" t="inlineStr">
         <is>
           <t>3986111771</t>
         </is>
       </c>
-      <c r="B80" s="34" t="inlineStr">
+      <c r="B80" s="36" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5611,12 +5617,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D80" s="34" t="inlineStr">
+      <c r="D80" s="36" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E80" s="34" t="inlineStr">
+      <c r="E80" s="36" t="inlineStr">
         <is>
           <t>Carrollton, TX</t>
         </is>
@@ -5631,12 +5637,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H80" s="34" t="inlineStr">
+      <c r="H80" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I80" s="34" t="inlineStr">
+      <c r="I80" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5651,20 +5657,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L80" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M80" s="34" t="inlineStr"/>
+      <c r="L80" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M80" s="36" t="inlineStr"/>
     </row>
     <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="35" t="inlineStr">
+      <c r="A81" s="37" t="inlineStr">
         <is>
           <t>4417160720</t>
         </is>
       </c>
-      <c r="B81" s="35" t="inlineStr">
+      <c r="B81" s="37" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5674,12 +5680,12 @@
           <t>Full-Stack AI Developer</t>
         </is>
       </c>
-      <c r="D81" s="35" t="inlineStr">
+      <c r="D81" s="37" t="inlineStr">
         <is>
           <t>AnswerMyQ</t>
         </is>
       </c>
-      <c r="E81" s="35" t="inlineStr">
+      <c r="E81" s="37" t="inlineStr">
         <is>
           <t>Austin, Texas Metropolitan Area</t>
         </is>
@@ -5694,12 +5700,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H81" s="35" t="inlineStr">
+      <c r="H81" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I81" s="35" t="inlineStr">
+      <c r="I81" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5714,20 +5720,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L81" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M81" s="35" t="inlineStr"/>
+      <c r="L81" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M81" s="37" t="inlineStr"/>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="34" t="inlineStr">
+      <c r="A82" s="36" t="inlineStr">
         <is>
           <t>4418507307</t>
         </is>
       </c>
-      <c r="B82" s="34" t="inlineStr">
+      <c r="B82" s="36" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -5737,12 +5743,12 @@
           <t>Entry Level Software Engineer Intern</t>
         </is>
       </c>
-      <c r="D82" s="34" t="inlineStr">
+      <c r="D82" s="36" t="inlineStr">
         <is>
           <t>CORMAC</t>
         </is>
       </c>
-      <c r="E82" s="34" t="inlineStr">
+      <c r="E82" s="36" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -5757,12 +5763,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H82" s="34" t="inlineStr">
+      <c r="H82" s="36" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="I82" s="34" t="inlineStr">
+      <c r="I82" s="36" t="inlineStr">
         <is>
           <t>Volunteer</t>
         </is>
@@ -5777,20 +5783,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L82" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M82" s="34" t="inlineStr"/>
+      <c r="L82" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M82" s="36" t="inlineStr"/>
     </row>
     <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="35" t="inlineStr">
+      <c r="A83" s="37" t="inlineStr">
         <is>
           <t>4413360938</t>
         </is>
       </c>
-      <c r="B83" s="35" t="inlineStr">
+      <c r="B83" s="37" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -5800,12 +5806,12 @@
           <t>Software Engineer Internship (Remote)</t>
         </is>
       </c>
-      <c r="D83" s="35" t="inlineStr">
+      <c r="D83" s="37" t="inlineStr">
         <is>
           <t>Orange Trail</t>
         </is>
       </c>
-      <c r="E83" s="35" t="inlineStr">
+      <c r="E83" s="37" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -5820,12 +5826,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H83" s="35" t="inlineStr">
+      <c r="H83" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I83" s="35" t="inlineStr">
+      <c r="I83" s="37" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -5840,20 +5846,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L83" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M83" s="35" t="inlineStr"/>
+      <c r="L83" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M83" s="37" t="inlineStr"/>
     </row>
     <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="34" t="inlineStr">
+      <c r="A84" s="36" t="inlineStr">
         <is>
           <t>4348111641</t>
         </is>
       </c>
-      <c r="B84" s="34" t="inlineStr">
+      <c r="B84" s="36" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -5863,12 +5869,12 @@
           <t>Software Engineer Intern</t>
         </is>
       </c>
-      <c r="D84" s="34" t="inlineStr">
+      <c r="D84" s="36" t="inlineStr">
         <is>
           <t>Simular</t>
         </is>
       </c>
-      <c r="E84" s="34" t="inlineStr">
+      <c r="E84" s="36" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -5883,12 +5889,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H84" s="34" t="inlineStr">
+      <c r="H84" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I84" s="34" t="inlineStr">
+      <c r="I84" s="36" t="inlineStr">
         <is>
           <t>Volunteer</t>
         </is>
@@ -5903,20 +5909,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L84" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M84" s="34" t="inlineStr"/>
+      <c r="L84" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M84" s="36" t="inlineStr"/>
     </row>
     <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="35" t="inlineStr">
+      <c r="A85" s="37" t="inlineStr">
         <is>
           <t>4411853543</t>
         </is>
       </c>
-      <c r="B85" s="35" t="inlineStr">
+      <c r="B85" s="37" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -5926,12 +5932,12 @@
           <t>Intern, Software Engineer</t>
         </is>
       </c>
-      <c r="D85" s="35" t="inlineStr">
+      <c r="D85" s="37" t="inlineStr">
         <is>
           <t>Accelerate Learning</t>
         </is>
       </c>
-      <c r="E85" s="35" t="inlineStr">
+      <c r="E85" s="37" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -5946,12 +5952,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H85" s="35" t="inlineStr">
+      <c r="H85" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I85" s="35" t="inlineStr">
+      <c r="I85" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5966,20 +5972,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L85" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M85" s="35" t="inlineStr"/>
+      <c r="L85" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M85" s="37" t="inlineStr"/>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="34" t="inlineStr">
+      <c r="A86" s="36" t="inlineStr">
         <is>
           <t>4408586245</t>
         </is>
       </c>
-      <c r="B86" s="34" t="inlineStr">
+      <c r="B86" s="36" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -5989,12 +5995,12 @@
           <t>Junior Software Engineer Intern</t>
         </is>
       </c>
-      <c r="D86" s="34" t="inlineStr">
+      <c r="D86" s="36" t="inlineStr">
         <is>
           <t>Cantaloupe Inc</t>
         </is>
       </c>
-      <c r="E86" s="34" t="inlineStr">
+      <c r="E86" s="36" t="inlineStr">
         <is>
           <t>Atlanta, GA</t>
         </is>
@@ -6009,12 +6015,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H86" s="34" t="inlineStr">
+      <c r="H86" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I86" s="34" t="inlineStr">
+      <c r="I86" s="36" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -6029,20 +6035,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L86" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M86" s="34" t="inlineStr"/>
+      <c r="L86" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M86" s="36" t="inlineStr"/>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="35" t="inlineStr">
+      <c r="A87" s="37" t="inlineStr">
         <is>
           <t>4364536992</t>
         </is>
       </c>
-      <c r="B87" s="35" t="inlineStr">
+      <c r="B87" s="37" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -6052,12 +6058,12 @@
           <t>Summer Internship - Measurement, Research and Development - Academic Measurement</t>
         </is>
       </c>
-      <c r="D87" s="35" t="inlineStr">
+      <c r="D87" s="37" t="inlineStr">
         <is>
           <t>ChatGPT Jobs</t>
         </is>
       </c>
-      <c r="E87" s="35" t="inlineStr">
+      <c r="E87" s="37" t="inlineStr">
         <is>
           <t>Iowa City, IA</t>
         </is>
@@ -6072,12 +6078,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H87" s="35" t="inlineStr">
+      <c r="H87" s="37" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I87" s="35" t="inlineStr">
+      <c r="I87" s="37" t="inlineStr">
         <is>
           <t>Volunteer</t>
         </is>
@@ -6092,20 +6098,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L87" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M87" s="35" t="inlineStr"/>
+      <c r="L87" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M87" s="37" t="inlineStr"/>
     </row>
     <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="34" t="inlineStr">
+      <c r="A88" s="36" t="inlineStr">
         <is>
           <t>4413206045</t>
         </is>
       </c>
-      <c r="B88" s="34" t="inlineStr">
+      <c r="B88" s="36" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6115,12 +6121,12 @@
           <t>Software Development Engineer, EC2 Nitro Specialized Instances</t>
         </is>
       </c>
-      <c r="D88" s="34" t="inlineStr">
+      <c r="D88" s="36" t="inlineStr">
         <is>
           <t>Amazon Web Services (AWS)</t>
         </is>
       </c>
-      <c r="E88" s="34" t="inlineStr">
+      <c r="E88" s="36" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6135,12 +6141,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H88" s="34" t="inlineStr">
+      <c r="H88" s="36" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I88" s="34" t="inlineStr">
+      <c r="I88" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6155,20 +6161,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L88" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M88" s="34" t="inlineStr"/>
+      <c r="L88" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M88" s="36" t="inlineStr"/>
     </row>
     <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="35" t="inlineStr">
+      <c r="A89" s="37" t="inlineStr">
         <is>
           <t>4383211797</t>
         </is>
       </c>
-      <c r="B89" s="35" t="inlineStr">
+      <c r="B89" s="37" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6178,12 +6184,12 @@
           <t>software development engineer</t>
         </is>
       </c>
-      <c r="D89" s="35" t="inlineStr">
+      <c r="D89" s="37" t="inlineStr">
         <is>
           <t>Abacus Business Computer</t>
         </is>
       </c>
-      <c r="E89" s="35" t="inlineStr">
+      <c r="E89" s="37" t="inlineStr">
         <is>
           <t>Queens, NY</t>
         </is>
@@ -6198,12 +6204,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H89" s="35" t="inlineStr">
+      <c r="H89" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I89" s="35" t="inlineStr">
+      <c r="I89" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6218,20 +6224,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L89" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M89" s="35" t="inlineStr"/>
+      <c r="L89" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M89" s="37" t="inlineStr"/>
     </row>
     <row r="90" ht="18" customHeight="1">
-      <c r="A90" s="34" t="inlineStr">
+      <c r="A90" s="36" t="inlineStr">
         <is>
           <t>4418169749</t>
         </is>
       </c>
-      <c r="B90" s="34" t="inlineStr">
+      <c r="B90" s="36" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6241,12 +6247,12 @@
           <t>AI/ML Engineering Intern</t>
         </is>
       </c>
-      <c r="D90" s="34" t="inlineStr">
+      <c r="D90" s="36" t="inlineStr">
         <is>
           <t>Daice Labs</t>
         </is>
       </c>
-      <c r="E90" s="34" t="inlineStr">
+      <c r="E90" s="36" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -6261,12 +6267,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H90" s="34" t="inlineStr">
+      <c r="H90" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I90" s="34" t="inlineStr">
+      <c r="I90" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6281,20 +6287,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L90" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M90" s="34" t="inlineStr"/>
+      <c r="L90" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M90" s="36" t="inlineStr"/>
     </row>
     <row r="91" ht="18" customHeight="1">
-      <c r="A91" s="35" t="inlineStr">
+      <c r="A91" s="37" t="inlineStr">
         <is>
           <t>4281120416</t>
         </is>
       </c>
-      <c r="B91" s="35" t="inlineStr">
+      <c r="B91" s="37" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6304,12 +6310,12 @@
           <t>Site Reliability Engineer Intern (Compute Platform) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D91" s="35" t="inlineStr">
+      <c r="D91" s="37" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E91" s="35" t="inlineStr">
+      <c r="E91" s="37" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6324,12 +6330,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H91" s="35" t="inlineStr">
+      <c r="H91" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I91" s="35" t="inlineStr">
+      <c r="I91" s="37" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -6344,20 +6350,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L91" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M91" s="35" t="inlineStr"/>
+      <c r="L91" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M91" s="37" t="inlineStr"/>
     </row>
     <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="34" t="inlineStr">
+      <c r="A92" s="36" t="inlineStr">
         <is>
           <t>4377549744</t>
         </is>
       </c>
-      <c r="B92" s="34" t="inlineStr">
+      <c r="B92" s="36" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6367,12 +6373,12 @@
           <t>Software Development Engineer Apprentice - Military Veterans</t>
         </is>
       </c>
-      <c r="D92" s="34" t="inlineStr">
+      <c r="D92" s="36" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E92" s="34" t="inlineStr">
+      <c r="E92" s="36" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -6387,12 +6393,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H92" s="34" t="inlineStr">
+      <c r="H92" s="36" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="I92" s="34" t="inlineStr">
+      <c r="I92" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6407,20 +6413,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L92" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M92" s="34" t="inlineStr"/>
+      <c r="L92" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M92" s="36" t="inlineStr"/>
     </row>
     <row r="93" ht="18" customHeight="1">
-      <c r="A93" s="35" t="inlineStr">
+      <c r="A93" s="37" t="inlineStr">
         <is>
           <t>4377564429</t>
         </is>
       </c>
-      <c r="B93" s="35" t="inlineStr">
+      <c r="B93" s="37" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6430,12 +6436,12 @@
           <t>Software Development Engineer Apprentice - Military Veterans</t>
         </is>
       </c>
-      <c r="D93" s="35" t="inlineStr">
+      <c r="D93" s="37" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E93" s="35" t="inlineStr">
+      <c r="E93" s="37" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6450,12 +6456,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H93" s="35" t="inlineStr">
+      <c r="H93" s="37" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="I93" s="35" t="inlineStr">
+      <c r="I93" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6470,20 +6476,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L93" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M93" s="35" t="inlineStr"/>
+      <c r="L93" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M93" s="37" t="inlineStr"/>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="A94" s="34" t="inlineStr">
+      <c r="A94" s="36" t="inlineStr">
         <is>
           <t>4413206046</t>
         </is>
       </c>
-      <c r="B94" s="34" t="inlineStr">
+      <c r="B94" s="36" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6493,12 +6499,12 @@
           <t>Software Development Engineer, Vendor Funding</t>
         </is>
       </c>
-      <c r="D94" s="34" t="inlineStr">
+      <c r="D94" s="36" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E94" s="34" t="inlineStr">
+      <c r="E94" s="36" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6513,12 +6519,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H94" s="34" t="inlineStr">
+      <c r="H94" s="36" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I94" s="34" t="inlineStr">
+      <c r="I94" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6533,20 +6539,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L94" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M94" s="34" t="inlineStr"/>
+      <c r="L94" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M94" s="36" t="inlineStr"/>
     </row>
     <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="35" t="inlineStr">
+      <c r="A95" s="37" t="inlineStr">
         <is>
           <t>4408778227</t>
         </is>
       </c>
-      <c r="B95" s="35" t="inlineStr">
+      <c r="B95" s="37" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6556,12 +6562,12 @@
           <t>Front-End Engineer Fall Internship – 2026 (US)</t>
         </is>
       </c>
-      <c r="D95" s="35" t="inlineStr">
+      <c r="D95" s="37" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E95" s="35" t="inlineStr">
+      <c r="E95" s="37" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6576,12 +6582,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H95" s="35" t="inlineStr">
+      <c r="H95" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I95" s="35" t="inlineStr">
+      <c r="I95" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6596,20 +6602,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L95" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M95" s="35" t="inlineStr"/>
+      <c r="L95" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M95" s="37" t="inlineStr"/>
     </row>
     <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="34" t="inlineStr">
+      <c r="A96" s="36" t="inlineStr">
         <is>
           <t>4281117648</t>
         </is>
       </c>
-      <c r="B96" s="34" t="inlineStr">
+      <c r="B96" s="36" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6619,12 +6625,12 @@
           <t>Data Engineer Intern (E-commerce) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D96" s="34" t="inlineStr">
+      <c r="D96" s="36" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E96" s="34" t="inlineStr">
+      <c r="E96" s="36" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6639,12 +6645,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H96" s="34" t="inlineStr">
+      <c r="H96" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I96" s="34" t="inlineStr">
+      <c r="I96" s="36" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -6659,20 +6665,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L96" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M96" s="34" t="inlineStr"/>
+      <c r="L96" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M96" s="36" t="inlineStr"/>
     </row>
     <row r="97" ht="18" customHeight="1">
-      <c r="A97" s="35" t="inlineStr">
+      <c r="A97" s="37" t="inlineStr">
         <is>
           <t>4407126060</t>
         </is>
       </c>
-      <c r="B97" s="35" t="inlineStr">
+      <c r="B97" s="37" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6682,12 +6688,12 @@
           <t>Site Reliability Engineer Intern (Data Infrastructure) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D97" s="35" t="inlineStr">
+      <c r="D97" s="37" t="inlineStr">
         <is>
           <t>ByteDance</t>
         </is>
       </c>
-      <c r="E97" s="35" t="inlineStr">
+      <c r="E97" s="37" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6702,12 +6708,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H97" s="35" t="inlineStr">
+      <c r="H97" s="37" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="I97" s="35" t="inlineStr">
+      <c r="I97" s="37" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -6722,20 +6728,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L97" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M97" s="35" t="inlineStr"/>
+      <c r="L97" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M97" s="37" t="inlineStr"/>
     </row>
     <row r="98" ht="18" customHeight="1">
-      <c r="A98" s="34" t="inlineStr">
+      <c r="A98" s="36" t="inlineStr">
         <is>
           <t>4392432360</t>
         </is>
       </c>
-      <c r="B98" s="34" t="inlineStr">
+      <c r="B98" s="36" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6745,12 +6751,12 @@
           <t>Software Engineer Intern (AI Model Optimization) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D98" s="34" t="inlineStr">
+      <c r="D98" s="36" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E98" s="34" t="inlineStr">
+      <c r="E98" s="36" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6765,12 +6771,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H98" s="34" t="inlineStr">
+      <c r="H98" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I98" s="34" t="inlineStr">
+      <c r="I98" s="36" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -6785,20 +6791,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L98" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M98" s="34" t="inlineStr"/>
+      <c r="L98" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M98" s="36" t="inlineStr"/>
     </row>
     <row r="99" ht="18" customHeight="1">
-      <c r="A99" s="35" t="inlineStr">
+      <c r="A99" s="37" t="inlineStr">
         <is>
           <t>4341279371</t>
         </is>
       </c>
-      <c r="B99" s="35" t="inlineStr">
+      <c r="B99" s="37" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6808,12 +6814,12 @@
           <t>Robotics - Software Development Engineer Intern/Co-op - 2026</t>
         </is>
       </c>
-      <c r="D99" s="35" t="inlineStr">
+      <c r="D99" s="37" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E99" s="35" t="inlineStr">
+      <c r="E99" s="37" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6828,12 +6834,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H99" s="35" t="inlineStr">
+      <c r="H99" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I99" s="35" t="inlineStr">
+      <c r="I99" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6848,20 +6854,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L99" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M99" s="35" t="inlineStr"/>
+      <c r="L99" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M99" s="37" t="inlineStr"/>
     </row>
     <row r="100" ht="18" customHeight="1">
-      <c r="A100" s="34" t="inlineStr">
+      <c r="A100" s="36" t="inlineStr">
         <is>
           <t>4417646890</t>
         </is>
       </c>
-      <c r="B100" s="34" t="inlineStr">
+      <c r="B100" s="36" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6871,12 +6877,12 @@
           <t>Software Engineer II</t>
         </is>
       </c>
-      <c r="D100" s="34" t="inlineStr">
+      <c r="D100" s="36" t="inlineStr">
         <is>
           <t>Compass</t>
         </is>
       </c>
-      <c r="E100" s="34" t="inlineStr">
+      <c r="E100" s="36" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6891,12 +6897,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H100" s="34" t="inlineStr">
+      <c r="H100" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I100" s="34" t="inlineStr">
+      <c r="I100" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6911,20 +6917,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L100" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M100" s="34" t="inlineStr"/>
+      <c r="L100" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M100" s="36" t="inlineStr"/>
     </row>
     <row r="101" ht="18" customHeight="1">
-      <c r="A101" s="35" t="inlineStr">
+      <c r="A101" s="37" t="inlineStr">
         <is>
           <t>4417565729</t>
         </is>
       </c>
-      <c r="B101" s="35" t="inlineStr">
+      <c r="B101" s="37" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6934,12 +6940,12 @@
           <t>software engineer- ST, Seattle, WA</t>
         </is>
       </c>
-      <c r="D101" s="35" t="inlineStr">
+      <c r="D101" s="37" t="inlineStr">
         <is>
           <t>Starbucks</t>
         </is>
       </c>
-      <c r="E101" s="35" t="inlineStr">
+      <c r="E101" s="37" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6954,12 +6960,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H101" s="35" t="inlineStr">
+      <c r="H101" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I101" s="35" t="inlineStr">
+      <c r="I101" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6974,20 +6980,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L101" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M101" s="35" t="inlineStr"/>
+      <c r="L101" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M101" s="37" t="inlineStr"/>
     </row>
     <row r="102" ht="18" customHeight="1">
-      <c r="A102" s="34" t="inlineStr">
+      <c r="A102" s="36" t="inlineStr">
         <is>
           <t>4420492781</t>
         </is>
       </c>
-      <c r="B102" s="34" t="inlineStr">
+      <c r="B102" s="36" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6997,12 +7003,12 @@
           <t>Software Engineer (Starlink Mobile)</t>
         </is>
       </c>
-      <c r="D102" s="34" t="inlineStr">
+      <c r="D102" s="36" t="inlineStr">
         <is>
           <t>SpaceX</t>
         </is>
       </c>
-      <c r="E102" s="34" t="inlineStr">
+      <c r="E102" s="36" t="inlineStr">
         <is>
           <t>Redmond, WA</t>
         </is>
@@ -7017,12 +7023,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H102" s="34" t="inlineStr">
+      <c r="H102" s="36" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="I102" s="34" t="inlineStr">
+      <c r="I102" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7037,20 +7043,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L102" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M102" s="34" t="inlineStr"/>
+      <c r="L102" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M102" s="36" t="inlineStr"/>
     </row>
     <row r="103" ht="18" customHeight="1">
-      <c r="A103" s="35" t="inlineStr">
+      <c r="A103" s="37" t="inlineStr">
         <is>
           <t>4418203886</t>
         </is>
       </c>
-      <c r="B103" s="35" t="inlineStr">
+      <c r="B103" s="37" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -7060,12 +7066,12 @@
           <t>System Software Engineer - Performance</t>
         </is>
       </c>
-      <c r="D103" s="35" t="inlineStr">
+      <c r="D103" s="37" t="inlineStr">
         <is>
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="E103" s="35" t="inlineStr">
+      <c r="E103" s="37" t="inlineStr">
         <is>
           <t>Redmond, WA</t>
         </is>
@@ -7080,12 +7086,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H103" s="35" t="inlineStr">
+      <c r="H103" s="37" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
-      <c r="I103" s="35" t="inlineStr">
+      <c r="I103" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7100,20 +7106,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L103" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M103" s="35" t="inlineStr"/>
+      <c r="L103" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M103" s="37" t="inlineStr"/>
     </row>
     <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="34" t="inlineStr">
+      <c r="A104" s="36" t="inlineStr">
         <is>
           <t>4332886298</t>
         </is>
       </c>
-      <c r="B104" s="34" t="inlineStr">
+      <c r="B104" s="36" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -7123,12 +7129,12 @@
           <t>Software Engineer - AI Travel Agent</t>
         </is>
       </c>
-      <c r="D104" s="34" t="inlineStr">
+      <c r="D104" s="36" t="inlineStr">
         <is>
           <t>Axel</t>
         </is>
       </c>
-      <c r="E104" s="34" t="inlineStr">
+      <c r="E104" s="36" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -7143,12 +7149,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H104" s="34" t="inlineStr">
+      <c r="H104" s="36" t="inlineStr">
         <is>
           <t>163</t>
         </is>
       </c>
-      <c r="I104" s="34" t="inlineStr">
+      <c r="I104" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7163,20 +7169,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L104" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M104" s="34" t="inlineStr"/>
+      <c r="L104" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M104" s="36" t="inlineStr"/>
     </row>
     <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="35" t="inlineStr">
+      <c r="A105" s="37" t="inlineStr">
         <is>
           <t>4388596468</t>
         </is>
       </c>
-      <c r="B105" s="35" t="inlineStr">
+      <c r="B105" s="37" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -7186,12 +7192,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D105" s="35" t="inlineStr">
+      <c r="D105" s="37" t="inlineStr">
         <is>
           <t>Capgemini</t>
         </is>
       </c>
-      <c r="E105" s="35" t="inlineStr">
+      <c r="E105" s="37" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -7206,12 +7212,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H105" s="35" t="inlineStr">
+      <c r="H105" s="37" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="I105" s="35" t="inlineStr">
+      <c r="I105" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7226,20 +7232,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L105" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M105" s="35" t="inlineStr"/>
+      <c r="L105" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M105" s="37" t="inlineStr"/>
     </row>
     <row r="106" ht="18" customHeight="1">
-      <c r="A106" s="34" t="inlineStr">
+      <c r="A106" s="36" t="inlineStr">
         <is>
           <t>4419517103</t>
         </is>
       </c>
-      <c r="B106" s="34" t="inlineStr">
+      <c r="B106" s="36" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -7249,12 +7255,12 @@
           <t>Software Engineer II</t>
         </is>
       </c>
-      <c r="D106" s="34" t="inlineStr">
+      <c r="D106" s="36" t="inlineStr">
         <is>
           <t>Chewy</t>
         </is>
       </c>
-      <c r="E106" s="34" t="inlineStr">
+      <c r="E106" s="36" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -7269,12 +7275,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H106" s="34" t="inlineStr">
+      <c r="H106" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I106" s="34" t="inlineStr">
+      <c r="I106" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7289,20 +7295,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L106" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M106" s="34" t="inlineStr"/>
+      <c r="L106" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M106" s="36" t="inlineStr"/>
     </row>
     <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="35" t="inlineStr">
+      <c r="A107" s="37" t="inlineStr">
         <is>
           <t>4395225418</t>
         </is>
       </c>
-      <c r="B107" s="35" t="inlineStr">
+      <c r="B107" s="37" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -7312,12 +7318,12 @@
           <t>Software Engineer - Backend</t>
         </is>
       </c>
-      <c r="D107" s="35" t="inlineStr">
+      <c r="D107" s="37" t="inlineStr">
         <is>
           <t>MotherDuck</t>
         </is>
       </c>
-      <c r="E107" s="35" t="inlineStr">
+      <c r="E107" s="37" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -7332,12 +7338,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H107" s="35" t="inlineStr">
+      <c r="H107" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I107" s="35" t="inlineStr">
+      <c r="I107" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7352,20 +7358,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L107" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M107" s="35" t="inlineStr"/>
+      <c r="L107" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M107" s="37" t="inlineStr"/>
     </row>
     <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="34" t="inlineStr">
+      <c r="A108" s="36" t="inlineStr">
         <is>
           <t>4417163235</t>
         </is>
       </c>
-      <c r="B108" s="34" t="inlineStr">
+      <c r="B108" s="36" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -7375,12 +7381,12 @@
           <t>Software Engineer, Cloud SDK</t>
         </is>
       </c>
-      <c r="D108" s="34" t="inlineStr">
+      <c r="D108" s="36" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="E108" s="34" t="inlineStr">
+      <c r="E108" s="36" t="inlineStr">
         <is>
           <t>Kirkland, WA</t>
         </is>
@@ -7395,12 +7401,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H108" s="34" t="inlineStr">
+      <c r="H108" s="36" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="I108" s="34" t="inlineStr">
+      <c r="I108" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7415,20 +7421,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L108" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M108" s="34" t="inlineStr"/>
+      <c r="L108" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M108" s="36" t="inlineStr"/>
     </row>
     <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="35" t="inlineStr">
+      <c r="A109" s="37" t="inlineStr">
         <is>
           <t>4412210123</t>
         </is>
       </c>
-      <c r="B109" s="35" t="inlineStr">
+      <c r="B109" s="37" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7438,12 +7444,12 @@
           <t>Summer Intern - Software Engineer</t>
         </is>
       </c>
-      <c r="D109" s="35" t="inlineStr">
+      <c r="D109" s="37" t="inlineStr">
         <is>
           <t>Allegion (Southeast Asia) Pte. Ltd.</t>
         </is>
       </c>
-      <c r="E109" s="35" t="inlineStr">
+      <c r="E109" s="37" t="inlineStr">
         <is>
           <t>Carmel, IN</t>
         </is>
@@ -7458,12 +7464,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H109" s="35" t="inlineStr">
+      <c r="H109" s="37" t="inlineStr">
         <is>
           <t>146</t>
         </is>
       </c>
-      <c r="I109" s="35" t="inlineStr">
+      <c r="I109" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7478,20 +7484,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L109" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M109" s="35" t="inlineStr"/>
+      <c r="L109" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M109" s="37" t="inlineStr"/>
     </row>
     <row r="110" ht="18" customHeight="1">
-      <c r="A110" s="34" t="inlineStr">
+      <c r="A110" s="36" t="inlineStr">
         <is>
           <t>4414924766</t>
         </is>
       </c>
-      <c r="B110" s="34" t="inlineStr">
+      <c r="B110" s="36" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7501,12 +7507,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D110" s="34" t="inlineStr">
+      <c r="D110" s="36" t="inlineStr">
         <is>
           <t>Uneek Global</t>
         </is>
       </c>
-      <c r="E110" s="34" t="inlineStr">
+      <c r="E110" s="36" t="inlineStr">
         <is>
           <t>Texas, United States</t>
         </is>
@@ -7521,12 +7527,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H110" s="34" t="inlineStr">
+      <c r="H110" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I110" s="34" t="inlineStr">
+      <c r="I110" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7541,20 +7547,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L110" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M110" s="34" t="inlineStr"/>
+      <c r="L110" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M110" s="36" t="inlineStr"/>
     </row>
     <row r="111" ht="18" customHeight="1">
-      <c r="A111" s="35" t="inlineStr">
+      <c r="A111" s="37" t="inlineStr">
         <is>
           <t>4411278313</t>
         </is>
       </c>
-      <c r="B111" s="35" t="inlineStr">
+      <c r="B111" s="37" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7564,12 +7570,12 @@
           <t>Junior Software Engineer (.NET)</t>
         </is>
       </c>
-      <c r="D111" s="35" t="inlineStr">
+      <c r="D111" s="37" t="inlineStr">
         <is>
           <t>Quintrix, by Mindlance</t>
         </is>
       </c>
-      <c r="E111" s="35" t="inlineStr">
+      <c r="E111" s="37" t="inlineStr">
         <is>
           <t>Austin, Texas Metropolitan Area</t>
         </is>
@@ -7584,12 +7590,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H111" s="35" t="inlineStr">
+      <c r="H111" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I111" s="35" t="inlineStr">
+      <c r="I111" s="37" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
@@ -7604,20 +7610,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L111" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M111" s="35" t="inlineStr"/>
+      <c r="L111" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M111" s="37" t="inlineStr"/>
     </row>
     <row r="112" ht="18" customHeight="1">
-      <c r="A112" s="34" t="inlineStr">
+      <c r="A112" s="36" t="inlineStr">
         <is>
           <t>4340327286</t>
         </is>
       </c>
-      <c r="B112" s="34" t="inlineStr">
+      <c r="B112" s="36" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7627,12 +7633,12 @@
           <t>IT Services - SOFTWARE DEVELOPERS</t>
         </is>
       </c>
-      <c r="D112" s="34" t="inlineStr">
+      <c r="D112" s="36" t="inlineStr">
         <is>
           <t>Fuge Technologies Inc</t>
         </is>
       </c>
-      <c r="E112" s="34" t="inlineStr">
+      <c r="E112" s="36" t="inlineStr">
         <is>
           <t>Irving, TX</t>
         </is>
@@ -7647,12 +7653,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H112" s="34" t="inlineStr">
+      <c r="H112" s="36" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="I112" s="34" t="inlineStr">
+      <c r="I112" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7667,20 +7673,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L112" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M112" s="34" t="inlineStr"/>
+      <c r="L112" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M112" s="36" t="inlineStr"/>
     </row>
     <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="35" t="inlineStr">
+      <c r="A113" s="37" t="inlineStr">
         <is>
           <t>4243859384</t>
         </is>
       </c>
-      <c r="B113" s="35" t="inlineStr">
+      <c r="B113" s="37" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7690,12 +7696,12 @@
           <t>Test analyst</t>
         </is>
       </c>
-      <c r="D113" s="35" t="inlineStr">
+      <c r="D113" s="37" t="inlineStr">
         <is>
           <t>ADP WFN Test Company 3</t>
         </is>
       </c>
-      <c r="E113" s="35" t="inlineStr">
+      <c r="E113" s="37" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
@@ -7710,12 +7716,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H113" s="35" t="inlineStr">
+      <c r="H113" s="37" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="I113" s="35" t="inlineStr">
+      <c r="I113" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7730,20 +7736,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L113" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M113" s="35" t="inlineStr"/>
+      <c r="L113" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M113" s="37" t="inlineStr"/>
     </row>
     <row r="114" ht="18" customHeight="1">
-      <c r="A114" s="34" t="inlineStr">
+      <c r="A114" s="36" t="inlineStr">
         <is>
           <t>4407894427</t>
         </is>
       </c>
-      <c r="B114" s="34" t="inlineStr">
+      <c r="B114" s="36" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7753,12 +7759,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D114" s="34" t="inlineStr">
+      <c r="D114" s="36" t="inlineStr">
         <is>
           <t>Meriplex</t>
         </is>
       </c>
-      <c r="E114" s="34" t="inlineStr">
+      <c r="E114" s="36" t="inlineStr">
         <is>
           <t>Houston, TX</t>
         </is>
@@ -7773,12 +7779,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H114" s="34" t="inlineStr">
+      <c r="H114" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I114" s="34" t="inlineStr">
+      <c r="I114" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7793,20 +7799,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L114" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M114" s="34" t="inlineStr"/>
+      <c r="L114" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M114" s="36" t="inlineStr"/>
     </row>
     <row r="115" ht="18" customHeight="1">
-      <c r="A115" s="35" t="inlineStr">
+      <c r="A115" s="37" t="inlineStr">
         <is>
           <t>4414252424</t>
         </is>
       </c>
-      <c r="B115" s="35" t="inlineStr">
+      <c r="B115" s="37" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7816,12 +7822,12 @@
           <t>Junior Developer</t>
         </is>
       </c>
-      <c r="D115" s="35" t="inlineStr">
+      <c r="D115" s="37" t="inlineStr">
         <is>
           <t>Joyce Meyer Ministries</t>
         </is>
       </c>
-      <c r="E115" s="35" t="inlineStr">
+      <c r="E115" s="37" t="inlineStr">
         <is>
           <t>Fenton, MO</t>
         </is>
@@ -7836,12 +7842,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H115" s="35" t="inlineStr">
+      <c r="H115" s="37" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="I115" s="35" t="inlineStr">
+      <c r="I115" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7856,20 +7862,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L115" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M115" s="35" t="inlineStr"/>
+      <c r="L115" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M115" s="37" t="inlineStr"/>
     </row>
     <row r="116" ht="18" customHeight="1">
-      <c r="A116" s="34" t="inlineStr">
+      <c r="A116" s="36" t="inlineStr">
         <is>
           <t>4401782778</t>
         </is>
       </c>
-      <c r="B116" s="34" t="inlineStr">
+      <c r="B116" s="36" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7879,12 +7885,12 @@
           <t>Junior Full-Stack Software Developer</t>
         </is>
       </c>
-      <c r="D116" s="34" t="inlineStr">
+      <c r="D116" s="36" t="inlineStr">
         <is>
           <t>Visionist, Inc.</t>
         </is>
       </c>
-      <c r="E116" s="34" t="inlineStr">
+      <c r="E116" s="36" t="inlineStr">
         <is>
           <t>Columbia, MD</t>
         </is>
@@ -7899,12 +7905,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H116" s="34" t="inlineStr">
+      <c r="H116" s="36" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="I116" s="34" t="inlineStr">
+      <c r="I116" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7919,20 +7925,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L116" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M116" s="34" t="inlineStr"/>
+      <c r="L116" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M116" s="36" t="inlineStr"/>
     </row>
     <row r="117" ht="18" customHeight="1">
-      <c r="A117" s="35" t="inlineStr">
+      <c r="A117" s="37" t="inlineStr">
         <is>
           <t>4411523361</t>
         </is>
       </c>
-      <c r="B117" s="35" t="inlineStr">
+      <c r="B117" s="37" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7942,12 +7948,12 @@
           <t>Junior Application Developer</t>
         </is>
       </c>
-      <c r="D117" s="35" t="inlineStr">
+      <c r="D117" s="37" t="inlineStr">
         <is>
           <t>HCL Global Systems Inc</t>
         </is>
       </c>
-      <c r="E117" s="35" t="inlineStr">
+      <c r="E117" s="37" t="inlineStr">
         <is>
           <t>Georgia, United States</t>
         </is>
@@ -7962,12 +7968,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H117" s="35" t="inlineStr">
+      <c r="H117" s="37" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="I117" s="35" t="inlineStr">
+      <c r="I117" s="37" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
@@ -7982,20 +7988,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L117" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M117" s="35" t="inlineStr"/>
+      <c r="L117" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M117" s="37" t="inlineStr"/>
     </row>
     <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="34" t="inlineStr">
+      <c r="A118" s="36" t="inlineStr">
         <is>
           <t>4261490006</t>
         </is>
       </c>
-      <c r="B118" s="34" t="inlineStr">
+      <c r="B118" s="36" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -8005,12 +8011,12 @@
           <t>**</t>
         </is>
       </c>
-      <c r="D118" s="34" t="inlineStr">
+      <c r="D118" s="36" t="inlineStr">
         <is>
           <t>ADP WFN Test Company 3</t>
         </is>
       </c>
-      <c r="E118" s="34" t="inlineStr">
+      <c r="E118" s="36" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
@@ -8025,12 +8031,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H118" s="34" t="inlineStr">
+      <c r="H118" s="36" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I118" s="34" t="inlineStr">
+      <c r="I118" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8045,20 +8051,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L118" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M118" s="34" t="inlineStr"/>
+      <c r="L118" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M118" s="36" t="inlineStr"/>
     </row>
     <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="35" t="inlineStr">
+      <c r="A119" s="37" t="inlineStr">
         <is>
           <t>4422878758</t>
         </is>
       </c>
-      <c r="B119" s="35" t="inlineStr">
+      <c r="B119" s="37" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -8068,12 +8074,12 @@
           <t>Junior Software Engineer</t>
         </is>
       </c>
-      <c r="D119" s="35" t="inlineStr">
+      <c r="D119" s="37" t="inlineStr">
         <is>
           <t>Brooksource</t>
         </is>
       </c>
-      <c r="E119" s="35" t="inlineStr">
+      <c r="E119" s="37" t="inlineStr">
         <is>
           <t>Lansing, MI</t>
         </is>
@@ -8088,12 +8094,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H119" s="35" t="inlineStr">
+      <c r="H119" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I119" s="35" t="inlineStr">
+      <c r="I119" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8108,20 +8114,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L119" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M119" s="35" t="inlineStr"/>
+      <c r="L119" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M119" s="37" t="inlineStr"/>
     </row>
     <row r="120" ht="18" customHeight="1">
-      <c r="A120" s="34" t="inlineStr">
+      <c r="A120" s="36" t="inlineStr">
         <is>
           <t>4419071723</t>
         </is>
       </c>
-      <c r="B120" s="34" t="inlineStr">
+      <c r="B120" s="36" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -8131,12 +8137,12 @@
           <t>Junior Software Developer</t>
         </is>
       </c>
-      <c r="D120" s="34" t="inlineStr">
+      <c r="D120" s="36" t="inlineStr">
         <is>
           <t>IPTA</t>
         </is>
       </c>
-      <c r="E120" s="34" t="inlineStr">
+      <c r="E120" s="36" t="inlineStr">
         <is>
           <t>Layton, UT</t>
         </is>
@@ -8151,12 +8157,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H120" s="34" t="inlineStr">
+      <c r="H120" s="36" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="I120" s="34" t="inlineStr">
+      <c r="I120" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8171,20 +8177,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L120" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M120" s="34" t="inlineStr"/>
+      <c r="L120" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M120" s="36" t="inlineStr"/>
     </row>
     <row r="121" ht="18" customHeight="1">
-      <c r="A121" s="35" t="inlineStr">
+      <c r="A121" s="37" t="inlineStr">
         <is>
           <t>4420988356</t>
         </is>
       </c>
-      <c r="B121" s="35" t="inlineStr">
+      <c r="B121" s="37" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -8194,12 +8200,12 @@
           <t>Junior Software Engineer</t>
         </is>
       </c>
-      <c r="D121" s="35" t="inlineStr">
+      <c r="D121" s="37" t="inlineStr">
         <is>
           <t>Switchboard</t>
         </is>
       </c>
-      <c r="E121" s="35" t="inlineStr">
+      <c r="E121" s="37" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
@@ -8214,12 +8220,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H121" s="35" t="inlineStr">
+      <c r="H121" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I121" s="35" t="inlineStr">
+      <c r="I121" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8234,20 +8240,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L121" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M121" s="35" t="inlineStr"/>
+      <c r="L121" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M121" s="37" t="inlineStr"/>
     </row>
     <row r="122" ht="18" customHeight="1">
-      <c r="A122" s="34" t="inlineStr">
+      <c r="A122" s="36" t="inlineStr">
         <is>
           <t>4419072850</t>
         </is>
       </c>
-      <c r="B122" s="34" t="inlineStr">
+      <c r="B122" s="36" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -8257,12 +8263,12 @@
           <t>junior software engineer analyst</t>
         </is>
       </c>
-      <c r="D122" s="34" t="inlineStr">
+      <c r="D122" s="36" t="inlineStr">
         <is>
           <t>Altamira Technologies Corporation</t>
         </is>
       </c>
-      <c r="E122" s="34" t="inlineStr">
+      <c r="E122" s="36" t="inlineStr">
         <is>
           <t>State College, PA</t>
         </is>
@@ -8277,12 +8283,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H122" s="34" t="inlineStr">
+      <c r="H122" s="36" t="inlineStr">
         <is>
           <t>137</t>
         </is>
       </c>
-      <c r="I122" s="34" t="inlineStr">
+      <c r="I122" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8297,20 +8303,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L122" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M122" s="34" t="inlineStr"/>
+      <c r="L122" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M122" s="36" t="inlineStr"/>
     </row>
     <row r="123" ht="18" customHeight="1">
-      <c r="A123" s="35" t="inlineStr">
+      <c r="A123" s="37" t="inlineStr">
         <is>
           <t>4406854247</t>
         </is>
       </c>
-      <c r="B123" s="35" t="inlineStr">
+      <c r="B123" s="37" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -8320,12 +8326,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D123" s="35" t="inlineStr">
+      <c r="D123" s="37" t="inlineStr">
         <is>
           <t>The Anywhere Company</t>
         </is>
       </c>
-      <c r="E123" s="35" t="inlineStr">
+      <c r="E123" s="37" t="inlineStr">
         <is>
           <t>Hilton Head Island, SC</t>
         </is>
@@ -8340,12 +8346,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H123" s="35" t="inlineStr">
+      <c r="H123" s="37" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I123" s="35" t="inlineStr">
+      <c r="I123" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8360,20 +8366,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L123" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M123" s="35" t="inlineStr"/>
+      <c r="L123" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M123" s="37" t="inlineStr"/>
     </row>
     <row r="124" ht="18" customHeight="1">
-      <c r="A124" s="34" t="inlineStr">
+      <c r="A124" s="36" t="inlineStr">
         <is>
           <t>4394719485</t>
         </is>
       </c>
-      <c r="B124" s="34" t="inlineStr">
+      <c r="B124" s="36" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -8383,12 +8389,12 @@
           <t>Software Developer I, II (Days 8am to 5pm) *On-Site Victor, NY*</t>
         </is>
       </c>
-      <c r="D124" s="34" t="inlineStr">
+      <c r="D124" s="36" t="inlineStr">
         <is>
           <t>LSI SOLUTIONS®</t>
         </is>
       </c>
-      <c r="E124" s="34" t="inlineStr">
+      <c r="E124" s="36" t="inlineStr">
         <is>
           <t>Victor, NY</t>
         </is>
@@ -8403,12 +8409,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H124" s="34" t="inlineStr">
+      <c r="H124" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I124" s="34" t="inlineStr">
+      <c r="I124" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8423,20 +8429,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L124" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M124" s="34" t="inlineStr"/>
+      <c r="L124" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M124" s="36" t="inlineStr"/>
     </row>
     <row r="125" ht="18" customHeight="1">
-      <c r="A125" s="35" t="inlineStr">
+      <c r="A125" s="37" t="inlineStr">
         <is>
           <t>4367493426</t>
         </is>
       </c>
-      <c r="B125" s="35" t="inlineStr">
+      <c r="B125" s="37" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -8446,12 +8452,12 @@
           <t>Junior Software Developer</t>
         </is>
       </c>
-      <c r="D125" s="35" t="inlineStr">
+      <c r="D125" s="37" t="inlineStr">
         <is>
           <t>KIHOMAC</t>
         </is>
       </c>
-      <c r="E125" s="35" t="inlineStr">
+      <c r="E125" s="37" t="inlineStr">
         <is>
           <t>Colorado Springs, CO</t>
         </is>
@@ -8466,12 +8472,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H125" s="35" t="inlineStr">
+      <c r="H125" s="37" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="I125" s="35" t="inlineStr">
+      <c r="I125" s="37" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8486,20 +8492,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L125" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M125" s="35" t="inlineStr"/>
+      <c r="L125" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M125" s="37" t="inlineStr"/>
     </row>
     <row r="126" ht="18" customHeight="1">
-      <c r="A126" s="34" t="inlineStr">
+      <c r="A126" s="36" t="inlineStr">
         <is>
           <t>4304448690</t>
         </is>
       </c>
-      <c r="B126" s="34" t="inlineStr">
+      <c r="B126" s="36" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
@@ -8509,12 +8515,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D126" s="34" t="inlineStr">
+      <c r="D126" s="36" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E126" s="34" t="inlineStr">
+      <c r="E126" s="36" t="inlineStr">
         <is>
           <t>Pennsylvania, United States</t>
         </is>
@@ -8529,12 +8535,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H126" s="34" t="inlineStr">
+      <c r="H126" s="36" t="inlineStr">
         <is>
           <t>151</t>
         </is>
       </c>
-      <c r="I126" s="34" t="inlineStr">
+      <c r="I126" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8549,20 +8555,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L126" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M126" s="34" t="inlineStr"/>
+      <c r="L126" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M126" s="36" t="inlineStr"/>
     </row>
     <row r="127" ht="18" customHeight="1">
-      <c r="A127" s="35" t="inlineStr">
+      <c r="A127" s="37" t="inlineStr">
         <is>
           <t>4305126185</t>
         </is>
       </c>
-      <c r="B127" s="35" t="inlineStr">
+      <c r="B127" s="37" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
@@ -8572,12 +8578,12 @@
           <t>Software Engineer Intern (Payment Network) - Global Payment - 2026 Summer(BS/MS)</t>
         </is>
       </c>
-      <c r="D127" s="35" t="inlineStr">
+      <c r="D127" s="37" t="inlineStr">
         <is>
           <t>ByteDance</t>
         </is>
       </c>
-      <c r="E127" s="35" t="inlineStr">
+      <c r="E127" s="37" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -8592,12 +8598,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H127" s="35" t="inlineStr">
+      <c r="H127" s="37" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I127" s="35" t="inlineStr">
+      <c r="I127" s="37" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -8612,20 +8618,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L127" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M127" s="35" t="inlineStr"/>
+      <c r="L127" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M127" s="37" t="inlineStr"/>
     </row>
     <row r="128" ht="18" customHeight="1">
-      <c r="A128" s="34" t="inlineStr">
+      <c r="A128" s="36" t="inlineStr">
         <is>
           <t>4418276914</t>
         </is>
       </c>
-      <c r="B128" s="34" t="inlineStr">
+      <c r="B128" s="36" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
@@ -8635,12 +8641,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D128" s="34" t="inlineStr">
+      <c r="D128" s="36" t="inlineStr">
         <is>
           <t>fieldd</t>
         </is>
       </c>
-      <c r="E128" s="34" t="inlineStr">
+      <c r="E128" s="36" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -8655,12 +8661,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H128" s="34" t="inlineStr">
+      <c r="H128" s="36" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I128" s="34" t="inlineStr">
+      <c r="I128" s="36" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8675,20 +8681,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L128" s="34" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M128" s="34" t="inlineStr"/>
+      <c r="L128" s="36" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M128" s="36" t="inlineStr"/>
     </row>
     <row r="129" ht="18" customHeight="1">
-      <c r="A129" s="35" t="inlineStr">
+      <c r="A129" s="37" t="inlineStr">
         <is>
           <t>4420219582</t>
         </is>
       </c>
-      <c r="B129" s="35" t="inlineStr">
+      <c r="B129" s="37" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
@@ -8698,12 +8704,12 @@
           <t>Internship, Software Engineer, Information Security (Fall 2026)</t>
         </is>
       </c>
-      <c r="D129" s="35" t="inlineStr">
+      <c r="D129" s="37" t="inlineStr">
         <is>
           <t>Tesla</t>
         </is>
       </c>
-      <c r="E129" s="35" t="inlineStr">
+      <c r="E129" s="37" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -8718,12 +8724,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H129" s="35" t="inlineStr">
+      <c r="H129" s="37" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="I129" s="35" t="inlineStr">
+      <c r="I129" s="37" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -8738,12 +8744,12 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L129" s="35" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M129" s="35" t="inlineStr"/>
+      <c r="L129" s="37" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M129" s="37" t="inlineStr"/>
     </row>
     <row r="130" ht="18" customHeight="1">
       <c r="A130" s="36" t="inlineStr">
@@ -10068,8 +10074,575 @@
       </c>
       <c r="M150" s="36" t="inlineStr"/>
     </row>
+    <row r="151" ht="18" customHeight="1">
+      <c r="A151" s="38" t="inlineStr">
+        <is>
+          <t>4424293195</t>
+        </is>
+      </c>
+      <c r="B151" s="38" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C151" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D151" s="38" t="inlineStr">
+        <is>
+          <t>Jobs via Dice</t>
+        </is>
+      </c>
+      <c r="E151" s="38" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="G151" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H151" s="38" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="I151" s="38" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="J151" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, react, node, aws, mongodb, Title match: Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="K151" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L151" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M151" s="38" t="inlineStr"/>
+    </row>
+    <row r="152" ht="18" customHeight="1">
+      <c r="A152" s="39" t="inlineStr">
+        <is>
+          <t>4420722011</t>
+        </is>
+      </c>
+      <c r="B152" s="39" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer</t>
+        </is>
+      </c>
+      <c r="D152" s="39" t="inlineStr">
+        <is>
+          <t>Siyata.AI</t>
+        </is>
+      </c>
+      <c r="E152" s="39" t="inlineStr">
+        <is>
+          <t>Texas, United States</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="G152" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H152" s="39" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I152" s="39" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, rest, c, llm, typescript, Location: Texas, United States, Title match: Junior Software Engineer</t>
+        </is>
+      </c>
+      <c r="K152" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L152" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M152" s="39" t="inlineStr"/>
+    </row>
+    <row r="153" ht="18" customHeight="1">
+      <c r="A153" s="38" t="inlineStr">
+        <is>
+          <t>4420654994</t>
+        </is>
+      </c>
+      <c r="B153" s="38" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C153" s="8" t="inlineStr">
+        <is>
+          <t>Junior data analyst/Java Developer</t>
+        </is>
+      </c>
+      <c r="D153" s="38" t="inlineStr">
+        <is>
+          <t>SynergisticIT</t>
+        </is>
+      </c>
+      <c r="E153" s="38" t="inlineStr">
+        <is>
+          <t>Irving, TX</t>
+        </is>
+      </c>
+      <c r="F153" s="18" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="G153" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H153" s="38" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I153" s="38" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="J153" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, api, machine learning, full stack, backend, c</t>
+        </is>
+      </c>
+      <c r="K153" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L153" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M153" s="38" t="inlineStr"/>
+    </row>
+    <row r="154" ht="18" customHeight="1">
+      <c r="A154" s="39" t="inlineStr">
+        <is>
+          <t>4418523832</t>
+        </is>
+      </c>
+      <c r="B154" s="39" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>Compiler Engineer, Compute Front-End - New College Grad 2026</t>
+        </is>
+      </c>
+      <c r="D154" s="39" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="E154" s="39" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="F154" s="18" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="G154" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H154" s="39" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="I154" s="39" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>Skills: api, c++, c, express, Location: Austin, TX</t>
+        </is>
+      </c>
+      <c r="K154" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L154" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M154" s="39" t="inlineStr"/>
+    </row>
+    <row r="155" ht="18" customHeight="1">
+      <c r="A155" s="38" t="inlineStr">
+        <is>
+          <t>3815119724</t>
+        </is>
+      </c>
+      <c r="B155" s="38" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C155" s="8" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="D155" s="38" t="inlineStr">
+        <is>
+          <t>Bay Mortgage Services</t>
+        </is>
+      </c>
+      <c r="E155" s="38" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="F155" s="18" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="G155" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H155" s="38" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I155" s="38" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J155" s="8" t="inlineStr">
+        <is>
+          <t>Skills: sql, c++, c, Location: Austin, TX</t>
+        </is>
+      </c>
+      <c r="K155" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L155" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M155" s="38" t="inlineStr"/>
+    </row>
+    <row r="156" ht="18" customHeight="1">
+      <c r="A156" s="39" t="inlineStr">
+        <is>
+          <t>4418158932</t>
+        </is>
+      </c>
+      <c r="B156" s="39" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D156" s="39" t="inlineStr">
+        <is>
+          <t>Teero</t>
+        </is>
+      </c>
+      <c r="E156" s="39" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="F156" s="9" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="G156" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H156" s="39" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I156" s="39" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>Skills: react, api, sql, full stack, backend, frontend, Location: Austin, TX, Title match: Software Engineer</t>
+        </is>
+      </c>
+      <c r="K156" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L156" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M156" s="39" t="inlineStr"/>
+    </row>
+    <row r="157" ht="18" customHeight="1">
+      <c r="A157" s="38" t="inlineStr">
+        <is>
+          <t>4411533644</t>
+        </is>
+      </c>
+      <c r="B157" s="38" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C157" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D157" s="38" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="E157" s="38" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="F157" s="9" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="G157" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H157" s="38" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="I157" s="38" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J157" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, react, api, html, css, Location: Austin, TX, Title match: Software Engineer</t>
+        </is>
+      </c>
+      <c r="K157" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L157" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M157" s="38" t="inlineStr"/>
+    </row>
+    <row r="158" ht="18" customHeight="1">
+      <c r="A158" s="39" t="inlineStr">
+        <is>
+          <t>4196899187</t>
+        </is>
+      </c>
+      <c r="B158" s="39" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>Exploit Developer - All Levels</t>
+        </is>
+      </c>
+      <c r="D158" s="39" t="inlineStr">
+        <is>
+          <t>Interclypse</t>
+        </is>
+      </c>
+      <c r="E158" s="39" t="inlineStr">
+        <is>
+          <t>San Antonio, TX</t>
+        </is>
+      </c>
+      <c r="F158" s="14" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="G158" s="15" t="inlineStr">
+        <is>
+          <t>Very Low</t>
+        </is>
+      </c>
+      <c r="H158" s="39" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I158" s="39" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, c++, c, agile</t>
+        </is>
+      </c>
+      <c r="K158" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L158" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M158" s="39" t="inlineStr"/>
+    </row>
+    <row r="159" ht="18" customHeight="1">
+      <c r="A159" s="38" t="inlineStr">
+        <is>
+          <t>4423075890</t>
+        </is>
+      </c>
+      <c r="B159" s="38" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="C159" s="8" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="D159" s="38" t="inlineStr">
+        <is>
+          <t>2INgage</t>
+        </is>
+      </c>
+      <c r="E159" s="38" t="inlineStr">
+        <is>
+          <t>Allen, TX</t>
+        </is>
+      </c>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="G159" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H159" s="38" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I159" s="38" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J159" s="8" t="inlineStr">
+        <is>
+          <t>Skills: javascript, react, aws, rest, sql, c, Title match: Software Developer</t>
+        </is>
+      </c>
+      <c r="K159" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L159" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M159" s="38" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M150"/>
+  <autoFilter ref="A1:M159"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -10220,6 +10793,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K148" r:id="rId147"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K149" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K159" r:id="rId158"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Job Matches" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Matches'!$A$1:$M$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Matches'!$A$1:$M$164</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -235,6 +235,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -602,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M159"/>
+  <dimension ref="A1:M164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -688,12 +694,12 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="36" t="inlineStr">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>4406952064</t>
         </is>
       </c>
-      <c r="B2" s="36" t="inlineStr">
+      <c r="B2" s="39" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -703,12 +709,12 @@
           <t>DevSecOps Intern</t>
         </is>
       </c>
-      <c r="D2" s="36" t="inlineStr">
+      <c r="D2" s="39" t="inlineStr">
         <is>
           <t>Modern Technology Solutions, Inc. (MTSI)</t>
         </is>
       </c>
-      <c r="E2" s="36" t="inlineStr">
+      <c r="E2" s="39" t="inlineStr">
         <is>
           <t>Huntsville, AL</t>
         </is>
@@ -723,12 +729,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H2" s="36" t="inlineStr">
+      <c r="H2" s="39" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="I2" s="36" t="inlineStr">
+      <c r="I2" s="39" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -743,20 +749,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L2" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M2" s="36" t="inlineStr"/>
+      <c r="L2" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M2" s="39" t="inlineStr"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="A3" s="38" t="inlineStr">
         <is>
           <t>4405630173</t>
         </is>
       </c>
-      <c r="B3" s="37" t="inlineStr">
+      <c r="B3" s="38" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -766,12 +772,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D3" s="37" t="inlineStr">
+      <c r="D3" s="38" t="inlineStr">
         <is>
           <t>DLRdmv®</t>
         </is>
       </c>
-      <c r="E3" s="37" t="inlineStr">
+      <c r="E3" s="38" t="inlineStr">
         <is>
           <t>Dallas, TX</t>
         </is>
@@ -786,12 +792,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H3" s="37" t="inlineStr">
+      <c r="H3" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I3" s="37" t="inlineStr">
+      <c r="I3" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -806,20 +812,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L3" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M3" s="37" t="inlineStr"/>
+      <c r="L3" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M3" s="38" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>4287414862</t>
         </is>
       </c>
-      <c r="B4" s="36" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -829,12 +835,12 @@
           <t>[Online Assessment]Software Development Engineer Intern (Network Automation)- 2026 Summer (BS/ MS)</t>
         </is>
       </c>
-      <c r="D4" s="36" t="inlineStr">
+      <c r="D4" s="39" t="inlineStr">
         <is>
           <t>ByteDance</t>
         </is>
       </c>
-      <c r="E4" s="36" t="inlineStr">
+      <c r="E4" s="39" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -849,12 +855,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H4" s="36" t="inlineStr">
+      <c r="H4" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I4" s="36" t="inlineStr">
+      <c r="I4" s="39" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -869,20 +875,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L4" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M4" s="36" t="inlineStr"/>
+      <c r="L4" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M4" s="39" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>4309805269</t>
         </is>
       </c>
-      <c r="B5" s="37" t="inlineStr">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -892,12 +898,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D5" s="37" t="inlineStr">
+      <c r="D5" s="38" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E5" s="37" t="inlineStr">
+      <c r="E5" s="38" t="inlineStr">
         <is>
           <t>Delaware, United States</t>
         </is>
@@ -912,12 +918,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H5" s="37" t="inlineStr">
+      <c r="H5" s="38" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="I5" s="37" t="inlineStr">
+      <c r="I5" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -932,20 +938,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L5" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M5" s="37" t="inlineStr"/>
+      <c r="L5" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M5" s="38" t="inlineStr"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="A6" s="39" t="inlineStr">
         <is>
           <t>4371812987</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="39" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -955,12 +961,12 @@
           <t>Software Development Engineer Fall Intern - Military Veteran</t>
         </is>
       </c>
-      <c r="D6" s="36" t="inlineStr">
+      <c r="D6" s="39" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E6" s="36" t="inlineStr">
+      <c r="E6" s="39" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -975,12 +981,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H6" s="36" t="inlineStr">
+      <c r="H6" s="39" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="I6" s="36" t="inlineStr">
+      <c r="I6" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -995,20 +1001,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L6" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M6" s="36" t="inlineStr"/>
+      <c r="L6" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M6" s="39" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="38" t="inlineStr">
         <is>
           <t>4274682122</t>
         </is>
       </c>
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B7" s="38" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1018,12 +1024,12 @@
           <t>Software Engineer Intern (Data Ecosystem) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D7" s="37" t="inlineStr">
+      <c r="D7" s="38" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E7" s="37" t="inlineStr">
+      <c r="E7" s="38" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1038,12 +1044,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H7" s="37" t="inlineStr">
+      <c r="H7" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I7" s="37" t="inlineStr">
+      <c r="I7" s="38" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1058,20 +1064,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L7" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M7" s="37" t="inlineStr"/>
+      <c r="L7" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M7" s="38" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>4283848614</t>
         </is>
       </c>
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1081,12 +1087,12 @@
           <t>[Online Assessment] Software Engineer Intern (Recommendation Infrastructure) - 2026 Fall (BS/ MS)</t>
         </is>
       </c>
-      <c r="D8" s="36" t="inlineStr">
+      <c r="D8" s="39" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E8" s="36" t="inlineStr">
+      <c r="E8" s="39" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1101,12 +1107,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H8" s="36" t="inlineStr">
+      <c r="H8" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I8" s="36" t="inlineStr">
+      <c r="I8" s="39" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1121,20 +1127,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L8" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M8" s="36" t="inlineStr"/>
+      <c r="L8" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M8" s="39" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="A9" s="38" t="inlineStr">
         <is>
           <t>4411790844</t>
         </is>
       </c>
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B9" s="38" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1144,12 +1150,12 @@
           <t>Software Engineer Intern (Infrastructure Automation) - Fall 2026</t>
         </is>
       </c>
-      <c r="D9" s="37" t="inlineStr">
+      <c r="D9" s="38" t="inlineStr">
         <is>
           <t>Snowflake</t>
         </is>
       </c>
-      <c r="E9" s="37" t="inlineStr">
+      <c r="E9" s="38" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -1164,12 +1170,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H9" s="37" t="inlineStr">
+      <c r="H9" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I9" s="37" t="inlineStr">
+      <c r="I9" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1184,20 +1190,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L9" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M9" s="37" t="inlineStr"/>
+      <c r="L9" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M9" s="38" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="39" t="inlineStr">
         <is>
           <t>4332425058</t>
         </is>
       </c>
-      <c r="B10" s="36" t="inlineStr">
+      <c r="B10" s="39" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1207,12 +1213,12 @@
           <t>Software Development Engineer Internship - Fall 2026 (US)</t>
         </is>
       </c>
-      <c r="D10" s="36" t="inlineStr">
+      <c r="D10" s="39" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E10" s="36" t="inlineStr">
+      <c r="E10" s="39" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1227,12 +1233,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H10" s="36" t="inlineStr">
+      <c r="H10" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I10" s="36" t="inlineStr">
+      <c r="I10" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1247,20 +1253,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L10" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M10" s="36" t="inlineStr"/>
+      <c r="L10" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M10" s="39" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="37" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>4323643644</t>
         </is>
       </c>
-      <c r="B11" s="37" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1270,12 +1276,12 @@
           <t>[Online Assessment] Software Engineer Intern (Recommendation Infrastructure) - 2026 Summer (BS/ MS)</t>
         </is>
       </c>
-      <c r="D11" s="37" t="inlineStr">
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E11" s="37" t="inlineStr">
+      <c r="E11" s="38" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1290,12 +1296,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H11" s="37" t="inlineStr">
+      <c r="H11" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I11" s="37" t="inlineStr">
+      <c r="I11" s="38" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1310,20 +1316,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L11" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M11" s="37" t="inlineStr"/>
+      <c r="L11" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M11" s="38" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="A12" s="39" t="inlineStr">
         <is>
           <t>4320849104</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="39" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1333,12 +1339,12 @@
           <t>Software Engineer Intern (Commerce Ads) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D12" s="36" t="inlineStr">
+      <c r="D12" s="39" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E12" s="36" t="inlineStr">
+      <c r="E12" s="39" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1353,12 +1359,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H12" s="36" t="inlineStr">
+      <c r="H12" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I12" s="36" t="inlineStr">
+      <c r="I12" s="39" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -1373,20 +1379,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L12" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M12" s="36" t="inlineStr"/>
+      <c r="L12" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M12" s="39" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="37" t="inlineStr">
+      <c r="A13" s="38" t="inlineStr">
         <is>
           <t>4401686051</t>
         </is>
       </c>
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B13" s="38" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1396,12 +1402,12 @@
           <t>Front End Software Engineer</t>
         </is>
       </c>
-      <c r="D13" s="37" t="inlineStr">
+      <c r="D13" s="38" t="inlineStr">
         <is>
           <t>Saronic Technologies</t>
         </is>
       </c>
-      <c r="E13" s="37" t="inlineStr">
+      <c r="E13" s="38" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -1416,12 +1422,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H13" s="37" t="inlineStr">
+      <c r="H13" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I13" s="37" t="inlineStr">
+      <c r="I13" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1436,20 +1442,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L13" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M13" s="37" t="inlineStr"/>
+      <c r="L13" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M13" s="38" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="36" t="inlineStr">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>4309696652</t>
         </is>
       </c>
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1459,12 +1465,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D14" s="36" t="inlineStr">
+      <c r="D14" s="39" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E14" s="36" t="inlineStr">
+      <c r="E14" s="39" t="inlineStr">
         <is>
           <t>Rhode Island, United States</t>
         </is>
@@ -1479,12 +1485,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H14" s="36" t="inlineStr">
+      <c r="H14" s="39" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="I14" s="36" t="inlineStr">
+      <c r="I14" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1499,20 +1505,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L14" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M14" s="36" t="inlineStr"/>
+      <c r="L14" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M14" s="39" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="37" t="inlineStr">
+      <c r="A15" s="38" t="inlineStr">
         <is>
           <t>4309804319</t>
         </is>
       </c>
-      <c r="B15" s="37" t="inlineStr">
+      <c r="B15" s="38" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1522,12 +1528,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D15" s="37" t="inlineStr">
+      <c r="D15" s="38" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E15" s="37" t="inlineStr">
+      <c r="E15" s="38" t="inlineStr">
         <is>
           <t>Colorado, United States</t>
         </is>
@@ -1542,12 +1548,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H15" s="37" t="inlineStr">
+      <c r="H15" s="38" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="I15" s="37" t="inlineStr">
+      <c r="I15" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1562,20 +1568,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L15" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M15" s="37" t="inlineStr"/>
+      <c r="L15" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M15" s="38" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="36" t="inlineStr">
+      <c r="A16" s="39" t="inlineStr">
         <is>
           <t>4410271532</t>
         </is>
       </c>
-      <c r="B16" s="36" t="inlineStr">
+      <c r="B16" s="39" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1585,12 +1591,12 @@
           <t>Associate Developer</t>
         </is>
       </c>
-      <c r="D16" s="36" t="inlineStr">
+      <c r="D16" s="39" t="inlineStr">
         <is>
           <t>HealthStream</t>
         </is>
       </c>
-      <c r="E16" s="36" t="inlineStr">
+      <c r="E16" s="39" t="inlineStr">
         <is>
           <t>Nashville, TN</t>
         </is>
@@ -1605,12 +1611,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H16" s="36" t="inlineStr">
+      <c r="H16" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I16" s="36" t="inlineStr">
+      <c r="I16" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1625,20 +1631,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L16" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M16" s="36" t="inlineStr"/>
+      <c r="L16" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M16" s="39" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="37" t="inlineStr">
+      <c r="A17" s="38" t="inlineStr">
         <is>
           <t>4304445726</t>
         </is>
       </c>
-      <c r="B17" s="37" t="inlineStr">
+      <c r="B17" s="38" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1648,12 +1654,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D17" s="37" t="inlineStr">
+      <c r="D17" s="38" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E17" s="37" t="inlineStr">
+      <c r="E17" s="38" t="inlineStr">
         <is>
           <t>Oregon, United States</t>
         </is>
@@ -1668,12 +1674,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H17" s="37" t="inlineStr">
+      <c r="H17" s="38" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="I17" s="37" t="inlineStr">
+      <c r="I17" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1688,20 +1694,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L17" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M17" s="37" t="inlineStr"/>
+      <c r="L17" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M17" s="38" t="inlineStr"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="36" t="inlineStr">
+      <c r="A18" s="39" t="inlineStr">
         <is>
           <t>4342036151</t>
         </is>
       </c>
-      <c r="B18" s="36" t="inlineStr">
+      <c r="B18" s="39" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1711,12 +1717,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D18" s="36" t="inlineStr">
+      <c r="D18" s="39" t="inlineStr">
         <is>
           <t>Modern Treasury</t>
         </is>
       </c>
-      <c r="E18" s="36" t="inlineStr">
+      <c r="E18" s="39" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
@@ -1731,12 +1737,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H18" s="36" t="inlineStr">
+      <c r="H18" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I18" s="36" t="inlineStr">
+      <c r="I18" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1751,20 +1757,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L18" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M18" s="36" t="inlineStr"/>
+      <c r="L18" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M18" s="39" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="37" t="inlineStr">
+      <c r="A19" s="38" t="inlineStr">
         <is>
           <t>4304441843</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="38" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1774,12 +1780,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D19" s="37" t="inlineStr">
+      <c r="D19" s="38" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E19" s="37" t="inlineStr">
+      <c r="E19" s="38" t="inlineStr">
         <is>
           <t>Idaho, United States</t>
         </is>
@@ -1794,12 +1800,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H19" s="37" t="inlineStr">
+      <c r="H19" s="38" t="inlineStr">
         <is>
           <t>157</t>
         </is>
       </c>
-      <c r="I19" s="37" t="inlineStr">
+      <c r="I19" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1814,20 +1820,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L19" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M19" s="37" t="inlineStr"/>
+      <c r="L19" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M19" s="38" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="36" t="inlineStr">
+      <c r="A20" s="39" t="inlineStr">
         <is>
           <t>4408047047</t>
         </is>
       </c>
-      <c r="B20" s="36" t="inlineStr">
+      <c r="B20" s="39" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1837,12 +1843,12 @@
           <t>Computer Sciences - Graduates - AI Training - Las Vegas, US</t>
         </is>
       </c>
-      <c r="D20" s="36" t="inlineStr">
+      <c r="D20" s="39" t="inlineStr">
         <is>
           <t>Prolific</t>
         </is>
       </c>
-      <c r="E20" s="36" t="inlineStr">
+      <c r="E20" s="39" t="inlineStr">
         <is>
           <t>Las Vegas, NV</t>
         </is>
@@ -1857,12 +1863,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H20" s="36" t="inlineStr">
+      <c r="H20" s="39" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I20" s="36" t="inlineStr">
+      <c r="I20" s="39" t="inlineStr">
         <is>
           <t>Temporary</t>
         </is>
@@ -1877,20 +1883,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L20" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M20" s="36" t="inlineStr"/>
+      <c r="L20" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M20" s="39" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="37" t="inlineStr">
+      <c r="A21" s="38" t="inlineStr">
         <is>
           <t>4304444837</t>
         </is>
       </c>
-      <c r="B21" s="37" t="inlineStr">
+      <c r="B21" s="38" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1900,12 +1906,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D21" s="37" t="inlineStr">
+      <c r="D21" s="38" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E21" s="37" t="inlineStr">
+      <c r="E21" s="38" t="inlineStr">
         <is>
           <t>New Jersey, United States</t>
         </is>
@@ -1920,12 +1926,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H21" s="37" t="inlineStr">
+      <c r="H21" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I21" s="37" t="inlineStr">
+      <c r="I21" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -1940,20 +1946,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L21" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M21" s="37" t="inlineStr"/>
+      <c r="L21" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M21" s="38" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="36" t="inlineStr">
+      <c r="A22" s="39" t="inlineStr">
         <is>
           <t>4405641326</t>
         </is>
       </c>
-      <c r="B22" s="36" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -1963,12 +1969,12 @@
           <t>Full-stack Engineer</t>
         </is>
       </c>
-      <c r="D22" s="36" t="inlineStr">
+      <c r="D22" s="39" t="inlineStr">
         <is>
           <t>PartnerTap</t>
         </is>
       </c>
-      <c r="E22" s="36" t="inlineStr">
+      <c r="E22" s="39" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -1983,12 +1989,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H22" s="36" t="inlineStr">
+      <c r="H22" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I22" s="36" t="inlineStr">
+      <c r="I22" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2003,20 +2009,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L22" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M22" s="36" t="inlineStr"/>
+      <c r="L22" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M22" s="39" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="37" t="inlineStr">
+      <c r="A23" s="38" t="inlineStr">
         <is>
           <t>4341020900</t>
         </is>
       </c>
-      <c r="B23" s="37" t="inlineStr">
+      <c r="B23" s="38" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2026,12 +2032,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D23" s="37" t="inlineStr">
+      <c r="D23" s="38" t="inlineStr">
         <is>
           <t>PlanIT Group, LLC</t>
         </is>
       </c>
-      <c r="E23" s="37" t="inlineStr">
+      <c r="E23" s="38" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -2046,12 +2052,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H23" s="37" t="inlineStr">
+      <c r="H23" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I23" s="37" t="inlineStr">
+      <c r="I23" s="38" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
@@ -2066,20 +2072,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L23" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M23" s="37" t="inlineStr"/>
+      <c r="L23" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M23" s="38" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="36" t="inlineStr">
+      <c r="A24" s="39" t="inlineStr">
         <is>
           <t>4304450637</t>
         </is>
       </c>
-      <c r="B24" s="36" t="inlineStr">
+      <c r="B24" s="39" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2089,12 +2095,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D24" s="36" t="inlineStr">
+      <c r="D24" s="39" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E24" s="36" t="inlineStr">
+      <c r="E24" s="39" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -2109,12 +2115,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H24" s="36" t="inlineStr">
+      <c r="H24" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I24" s="36" t="inlineStr">
+      <c r="I24" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2129,20 +2135,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L24" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M24" s="36" t="inlineStr"/>
+      <c r="L24" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M24" s="39" t="inlineStr"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="37" t="inlineStr">
+      <c r="A25" s="38" t="inlineStr">
         <is>
           <t>4304451654</t>
         </is>
       </c>
-      <c r="B25" s="37" t="inlineStr">
+      <c r="B25" s="38" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2152,12 +2158,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D25" s="37" t="inlineStr">
+      <c r="D25" s="38" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E25" s="37" t="inlineStr">
+      <c r="E25" s="38" t="inlineStr">
         <is>
           <t>Utah, United States</t>
         </is>
@@ -2172,12 +2178,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H25" s="37" t="inlineStr">
+      <c r="H25" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I25" s="37" t="inlineStr">
+      <c r="I25" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2192,20 +2198,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L25" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M25" s="37" t="inlineStr"/>
+      <c r="L25" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M25" s="38" t="inlineStr"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="36" t="inlineStr">
+      <c r="A26" s="39" t="inlineStr">
         <is>
           <t>4413745880</t>
         </is>
       </c>
-      <c r="B26" s="36" t="inlineStr">
+      <c r="B26" s="39" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2215,12 +2221,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D26" s="36" t="inlineStr">
+      <c r="D26" s="39" t="inlineStr">
         <is>
           <t>Crate &amp; Barrel</t>
         </is>
       </c>
-      <c r="E26" s="36" t="inlineStr">
+      <c r="E26" s="39" t="inlineStr">
         <is>
           <t>Northbrook, IL</t>
         </is>
@@ -2235,12 +2241,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H26" s="36" t="inlineStr">
+      <c r="H26" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I26" s="36" t="inlineStr">
+      <c r="I26" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2255,20 +2261,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L26" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M26" s="36" t="inlineStr"/>
+      <c r="L26" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M26" s="39" t="inlineStr"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="37" t="inlineStr">
+      <c r="A27" s="38" t="inlineStr">
         <is>
           <t>4304438841</t>
         </is>
       </c>
-      <c r="B27" s="37" t="inlineStr">
+      <c r="B27" s="38" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2278,12 +2284,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D27" s="37" t="inlineStr">
+      <c r="D27" s="38" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E27" s="37" t="inlineStr">
+      <c r="E27" s="38" t="inlineStr">
         <is>
           <t>Connecticut, United States</t>
         </is>
@@ -2298,12 +2304,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H27" s="37" t="inlineStr">
+      <c r="H27" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I27" s="37" t="inlineStr">
+      <c r="I27" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2318,20 +2324,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L27" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M27" s="37" t="inlineStr"/>
+      <c r="L27" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M27" s="38" t="inlineStr"/>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="36" t="inlineStr">
+      <c r="A28" s="39" t="inlineStr">
         <is>
           <t>4393215930</t>
         </is>
       </c>
-      <c r="B28" s="36" t="inlineStr">
+      <c r="B28" s="39" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2341,12 +2347,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D28" s="36" t="inlineStr">
+      <c r="D28" s="39" t="inlineStr">
         <is>
           <t>Transcend</t>
         </is>
       </c>
-      <c r="E28" s="36" t="inlineStr">
+      <c r="E28" s="39" t="inlineStr">
         <is>
           <t>California, United States</t>
         </is>
@@ -2361,12 +2367,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H28" s="36" t="inlineStr">
+      <c r="H28" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I28" s="36" t="inlineStr">
+      <c r="I28" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2381,20 +2387,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L28" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M28" s="36" t="inlineStr"/>
+      <c r="L28" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M28" s="39" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="37" t="inlineStr">
+      <c r="A29" s="38" t="inlineStr">
         <is>
           <t>4304445723</t>
         </is>
       </c>
-      <c r="B29" s="37" t="inlineStr">
+      <c r="B29" s="38" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2404,12 +2410,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D29" s="37" t="inlineStr">
+      <c r="D29" s="38" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E29" s="37" t="inlineStr">
+      <c r="E29" s="38" t="inlineStr">
         <is>
           <t>Illinois, United States</t>
         </is>
@@ -2424,12 +2430,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H29" s="37" t="inlineStr">
+      <c r="H29" s="38" t="inlineStr">
         <is>
           <t>198</t>
         </is>
       </c>
-      <c r="I29" s="37" t="inlineStr">
+      <c r="I29" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2444,20 +2450,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L29" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M29" s="37" t="inlineStr"/>
+      <c r="L29" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M29" s="38" t="inlineStr"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="36" t="inlineStr">
+      <c r="A30" s="39" t="inlineStr">
         <is>
           <t>4396380649</t>
         </is>
       </c>
-      <c r="B30" s="36" t="inlineStr">
+      <c r="B30" s="39" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2467,12 +2473,12 @@
           <t>Full-Stack Developer Intern, Music &amp; Audio</t>
         </is>
       </c>
-      <c r="D30" s="36" t="inlineStr">
+      <c r="D30" s="39" t="inlineStr">
         <is>
           <t>Melotech</t>
         </is>
       </c>
-      <c r="E30" s="36" t="inlineStr">
+      <c r="E30" s="39" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
@@ -2487,12 +2493,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H30" s="36" t="inlineStr">
+      <c r="H30" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I30" s="36" t="inlineStr">
+      <c r="I30" s="39" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -2507,20 +2513,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L30" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M30" s="36" t="inlineStr"/>
+      <c r="L30" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M30" s="39" t="inlineStr"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="37" t="inlineStr">
+      <c r="A31" s="38" t="inlineStr">
         <is>
           <t>4304454025</t>
         </is>
       </c>
-      <c r="B31" s="37" t="inlineStr">
+      <c r="B31" s="38" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2530,12 +2536,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D31" s="37" t="inlineStr">
+      <c r="D31" s="38" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E31" s="37" t="inlineStr">
+      <c r="E31" s="38" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -2550,12 +2556,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H31" s="37" t="inlineStr">
+      <c r="H31" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I31" s="37" t="inlineStr">
+      <c r="I31" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2570,20 +2576,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L31" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M31" s="37" t="inlineStr"/>
+      <c r="L31" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M31" s="38" t="inlineStr"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="36" t="inlineStr">
+      <c r="A32" s="39" t="inlineStr">
         <is>
           <t>4309802287</t>
         </is>
       </c>
-      <c r="B32" s="36" t="inlineStr">
+      <c r="B32" s="39" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2593,12 +2599,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D32" s="36" t="inlineStr">
+      <c r="D32" s="39" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E32" s="36" t="inlineStr">
+      <c r="E32" s="39" t="inlineStr">
         <is>
           <t>New Jersey, United States</t>
         </is>
@@ -2613,12 +2619,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H32" s="36" t="inlineStr">
+      <c r="H32" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I32" s="36" t="inlineStr">
+      <c r="I32" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2633,20 +2639,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L32" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M32" s="36" t="inlineStr"/>
+      <c r="L32" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M32" s="39" t="inlineStr"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="37" t="inlineStr">
+      <c r="A33" s="38" t="inlineStr">
         <is>
           <t>4309694880</t>
         </is>
       </c>
-      <c r="B33" s="37" t="inlineStr">
+      <c r="B33" s="38" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2656,12 +2662,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D33" s="37" t="inlineStr">
+      <c r="D33" s="38" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E33" s="37" t="inlineStr">
+      <c r="E33" s="38" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -2676,12 +2682,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H33" s="37" t="inlineStr">
+      <c r="H33" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I33" s="37" t="inlineStr">
+      <c r="I33" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2696,20 +2702,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L33" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M33" s="37" t="inlineStr"/>
+      <c r="L33" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M33" s="38" t="inlineStr"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="36" t="inlineStr">
+      <c r="A34" s="39" t="inlineStr">
         <is>
           <t>4411274012</t>
         </is>
       </c>
-      <c r="B34" s="36" t="inlineStr">
+      <c r="B34" s="39" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
@@ -2719,12 +2725,12 @@
           <t>Junior UI Developer</t>
         </is>
       </c>
-      <c r="D34" s="36" t="inlineStr">
+      <c r="D34" s="39" t="inlineStr">
         <is>
           <t>General Dynamics Information Technology</t>
         </is>
       </c>
-      <c r="E34" s="36" t="inlineStr">
+      <c r="E34" s="39" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -2739,12 +2745,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H34" s="36" t="inlineStr">
+      <c r="H34" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I34" s="36" t="inlineStr">
+      <c r="I34" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2759,20 +2765,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L34" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M34" s="36" t="inlineStr"/>
+      <c r="L34" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M34" s="39" t="inlineStr"/>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="37" t="inlineStr">
+      <c r="A35" s="38" t="inlineStr">
         <is>
           <t>4264562292</t>
         </is>
       </c>
-      <c r="B35" s="37" t="inlineStr">
+      <c r="B35" s="38" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2782,12 +2788,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D35" s="37" t="inlineStr">
+      <c r="D35" s="38" t="inlineStr">
         <is>
           <t>Cymertek Corporation</t>
         </is>
       </c>
-      <c r="E35" s="37" t="inlineStr">
+      <c r="E35" s="38" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
@@ -2802,12 +2808,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H35" s="37" t="inlineStr">
+      <c r="H35" s="38" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="I35" s="37" t="inlineStr">
+      <c r="I35" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2822,20 +2828,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L35" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M35" s="37" t="inlineStr"/>
+      <c r="L35" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M35" s="38" t="inlineStr"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="36" t="inlineStr">
+      <c r="A36" s="39" t="inlineStr">
         <is>
           <t>4417482675</t>
         </is>
       </c>
-      <c r="B36" s="36" t="inlineStr">
+      <c r="B36" s="39" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2845,12 +2851,12 @@
           <t>Software Developer I</t>
         </is>
       </c>
-      <c r="D36" s="36" t="inlineStr">
+      <c r="D36" s="39" t="inlineStr">
         <is>
           <t>El Paso Water</t>
         </is>
       </c>
-      <c r="E36" s="36" t="inlineStr">
+      <c r="E36" s="39" t="inlineStr">
         <is>
           <t>El Paso, TX</t>
         </is>
@@ -2865,12 +2871,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H36" s="36" t="inlineStr">
+      <c r="H36" s="39" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="I36" s="36" t="inlineStr">
+      <c r="I36" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -2885,20 +2891,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L36" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M36" s="36" t="inlineStr"/>
+      <c r="L36" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M36" s="39" t="inlineStr"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="37" t="inlineStr">
+      <c r="A37" s="38" t="inlineStr">
         <is>
           <t>4416508200</t>
         </is>
       </c>
-      <c r="B37" s="37" t="inlineStr">
+      <c r="B37" s="38" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
@@ -2908,12 +2914,12 @@
           <t>Software Development Engineer in Test Intern (Global E-Commerce) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D37" s="37" t="inlineStr">
+      <c r="D37" s="38" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E37" s="37" t="inlineStr">
+      <c r="E37" s="38" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -2928,12 +2934,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H37" s="37" t="inlineStr">
+      <c r="H37" s="38" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I37" s="37" t="inlineStr">
+      <c r="I37" s="38" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -2948,20 +2954,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L37" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M37" s="37" t="inlineStr"/>
+      <c r="L37" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M37" s="38" t="inlineStr"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="36" t="inlineStr">
+      <c r="A38" s="39" t="inlineStr">
         <is>
           <t>4309809191</t>
         </is>
       </c>
-      <c r="B38" s="36" t="inlineStr">
+      <c r="B38" s="39" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
@@ -2971,12 +2977,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D38" s="36" t="inlineStr">
+      <c r="D38" s="39" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E38" s="36" t="inlineStr">
+      <c r="E38" s="39" t="inlineStr">
         <is>
           <t>Ohio, United States</t>
         </is>
@@ -2991,12 +2997,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H38" s="36" t="inlineStr">
+      <c r="H38" s="39" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="I38" s="36" t="inlineStr">
+      <c r="I38" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3011,20 +3017,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L38" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M38" s="36" t="inlineStr"/>
+      <c r="L38" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M38" s="39" t="inlineStr"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="37" t="inlineStr">
+      <c r="A39" s="38" t="inlineStr">
         <is>
           <t>3986118096</t>
         </is>
       </c>
-      <c r="B39" s="37" t="inlineStr">
+      <c r="B39" s="38" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
@@ -3034,12 +3040,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D39" s="37" t="inlineStr">
+      <c r="D39" s="38" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E39" s="37" t="inlineStr">
+      <c r="E39" s="38" t="inlineStr">
         <is>
           <t>Irving, TX</t>
         </is>
@@ -3054,12 +3060,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H39" s="37" t="inlineStr">
+      <c r="H39" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I39" s="37" t="inlineStr">
+      <c r="I39" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3074,20 +3080,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L39" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M39" s="37" t="inlineStr"/>
+      <c r="L39" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M39" s="38" t="inlineStr"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="36" t="inlineStr">
+      <c r="A40" s="39" t="inlineStr">
         <is>
           <t>4309808244</t>
         </is>
       </c>
-      <c r="B40" s="36" t="inlineStr">
+      <c r="B40" s="39" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3097,12 +3103,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D40" s="36" t="inlineStr">
+      <c r="D40" s="39" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E40" s="36" t="inlineStr">
+      <c r="E40" s="39" t="inlineStr">
         <is>
           <t>Massachusetts, United States</t>
         </is>
@@ -3117,12 +3123,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H40" s="36" t="inlineStr">
+      <c r="H40" s="39" t="inlineStr">
         <is>
           <t>166</t>
         </is>
       </c>
-      <c r="I40" s="36" t="inlineStr">
+      <c r="I40" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3137,20 +3143,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L40" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M40" s="36" t="inlineStr"/>
+      <c r="L40" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M40" s="39" t="inlineStr"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="37" t="inlineStr">
+      <c r="A41" s="38" t="inlineStr">
         <is>
           <t>4362173625</t>
         </is>
       </c>
-      <c r="B41" s="37" t="inlineStr">
+      <c r="B41" s="38" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3160,12 +3166,12 @@
           <t>Full Stack Engineer</t>
         </is>
       </c>
-      <c r="D41" s="37" t="inlineStr">
+      <c r="D41" s="38" t="inlineStr">
         <is>
           <t>Empower Sleep</t>
         </is>
       </c>
-      <c r="E41" s="37" t="inlineStr">
+      <c r="E41" s="38" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3180,12 +3186,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H41" s="37" t="inlineStr">
+      <c r="H41" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I41" s="37" t="inlineStr">
+      <c r="I41" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3200,20 +3206,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L41" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M41" s="37" t="inlineStr"/>
+      <c r="L41" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M41" s="38" t="inlineStr"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="36" t="inlineStr">
+      <c r="A42" s="39" t="inlineStr">
         <is>
           <t>4309812093</t>
         </is>
       </c>
-      <c r="B42" s="36" t="inlineStr">
+      <c r="B42" s="39" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3223,12 +3229,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D42" s="36" t="inlineStr">
+      <c r="D42" s="39" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E42" s="36" t="inlineStr">
+      <c r="E42" s="39" t="inlineStr">
         <is>
           <t>Florida, United States</t>
         </is>
@@ -3243,12 +3249,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H42" s="36" t="inlineStr">
+      <c r="H42" s="39" t="inlineStr">
         <is>
           <t>158</t>
         </is>
       </c>
-      <c r="I42" s="36" t="inlineStr">
+      <c r="I42" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3263,20 +3269,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L42" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M42" s="36" t="inlineStr"/>
+      <c r="L42" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M42" s="39" t="inlineStr"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="37" t="inlineStr">
+      <c r="A43" s="38" t="inlineStr">
         <is>
           <t>4391759914</t>
         </is>
       </c>
-      <c r="B43" s="37" t="inlineStr">
+      <c r="B43" s="38" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3286,12 +3292,12 @@
           <t>QA Engineering Internship</t>
         </is>
       </c>
-      <c r="D43" s="37" t="inlineStr">
+      <c r="D43" s="38" t="inlineStr">
         <is>
           <t>Chartbeat</t>
         </is>
       </c>
-      <c r="E43" s="37" t="inlineStr">
+      <c r="E43" s="38" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -3306,12 +3312,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H43" s="37" t="inlineStr">
+      <c r="H43" s="38" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="I43" s="37" t="inlineStr">
+      <c r="I43" s="38" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3326,20 +3332,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L43" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M43" s="37" t="inlineStr"/>
+      <c r="L43" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M43" s="38" t="inlineStr"/>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="36" t="inlineStr">
+      <c r="A44" s="39" t="inlineStr">
         <is>
           <t>4412855678</t>
         </is>
       </c>
-      <c r="B44" s="36" t="inlineStr">
+      <c r="B44" s="39" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3349,12 +3355,12 @@
           <t>AI Integration Engineer</t>
         </is>
       </c>
-      <c r="D44" s="36" t="inlineStr">
+      <c r="D44" s="39" t="inlineStr">
         <is>
           <t>UST</t>
         </is>
       </c>
-      <c r="E44" s="36" t="inlineStr">
+      <c r="E44" s="39" t="inlineStr">
         <is>
           <t>Santa Clara, CA</t>
         </is>
@@ -3369,12 +3375,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H44" s="36" t="inlineStr">
+      <c r="H44" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I44" s="36" t="inlineStr">
+      <c r="I44" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3389,20 +3395,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L44" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M44" s="36" t="inlineStr"/>
+      <c r="L44" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M44" s="39" t="inlineStr"/>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="37" t="inlineStr">
+      <c r="A45" s="38" t="inlineStr">
         <is>
           <t>4309805219</t>
         </is>
       </c>
-      <c r="B45" s="37" t="inlineStr">
+      <c r="B45" s="38" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3412,12 +3418,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D45" s="37" t="inlineStr">
+      <c r="D45" s="38" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E45" s="37" t="inlineStr">
+      <c r="E45" s="38" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -3432,12 +3438,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H45" s="37" t="inlineStr">
+      <c r="H45" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I45" s="37" t="inlineStr">
+      <c r="I45" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3452,20 +3458,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L45" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M45" s="37" t="inlineStr"/>
+      <c r="L45" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M45" s="38" t="inlineStr"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="36" t="inlineStr">
+      <c r="A46" s="39" t="inlineStr">
         <is>
           <t>4409726429</t>
         </is>
       </c>
-      <c r="B46" s="36" t="inlineStr">
+      <c r="B46" s="39" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3475,12 +3481,12 @@
           <t>Data Science Intern</t>
         </is>
       </c>
-      <c r="D46" s="36" t="inlineStr">
+      <c r="D46" s="39" t="inlineStr">
         <is>
           <t>Rundoo</t>
         </is>
       </c>
-      <c r="E46" s="36" t="inlineStr">
+      <c r="E46" s="39" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3495,12 +3501,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H46" s="36" t="inlineStr">
+      <c r="H46" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I46" s="36" t="inlineStr">
+      <c r="I46" s="39" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3515,20 +3521,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L46" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M46" s="36" t="inlineStr"/>
+      <c r="L46" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M46" s="39" t="inlineStr"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="37" t="inlineStr">
+      <c r="A47" s="38" t="inlineStr">
         <is>
           <t>4305671729</t>
         </is>
       </c>
-      <c r="B47" s="37" t="inlineStr">
+      <c r="B47" s="38" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3538,12 +3544,12 @@
           <t>DoD SkillBridge Internship/Fellowship Opportunity Application (U.S. Military Only)</t>
         </is>
       </c>
-      <c r="D47" s="37" t="inlineStr">
+      <c r="D47" s="38" t="inlineStr">
         <is>
           <t>Onsights</t>
         </is>
       </c>
-      <c r="E47" s="37" t="inlineStr">
+      <c r="E47" s="38" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -3558,12 +3564,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H47" s="37" t="inlineStr">
+      <c r="H47" s="38" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I47" s="37" t="inlineStr">
+      <c r="I47" s="38" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3578,20 +3584,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L47" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M47" s="37" t="inlineStr"/>
+      <c r="L47" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M47" s="38" t="inlineStr"/>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="36" t="inlineStr">
+      <c r="A48" s="39" t="inlineStr">
         <is>
           <t>4414096220</t>
         </is>
       </c>
-      <c r="B48" s="36" t="inlineStr">
+      <c r="B48" s="39" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3601,12 +3607,12 @@
           <t>Visualization Engineer Intern</t>
         </is>
       </c>
-      <c r="D48" s="36" t="inlineStr">
+      <c r="D48" s="39" t="inlineStr">
         <is>
           <t>Leidos</t>
         </is>
       </c>
-      <c r="E48" s="36" t="inlineStr">
+      <c r="E48" s="39" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3621,12 +3627,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H48" s="36" t="inlineStr">
+      <c r="H48" s="39" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="I48" s="36" t="inlineStr">
+      <c r="I48" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3641,20 +3647,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L48" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M48" s="36" t="inlineStr"/>
+      <c r="L48" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M48" s="39" t="inlineStr"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="37" t="inlineStr">
+      <c r="A49" s="38" t="inlineStr">
         <is>
           <t>4361076044</t>
         </is>
       </c>
-      <c r="B49" s="37" t="inlineStr">
+      <c r="B49" s="38" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
@@ -3664,12 +3670,12 @@
           <t>GenAI Engineering Intern  - SkillBridge (Remote)</t>
         </is>
       </c>
-      <c r="D49" s="37" t="inlineStr">
+      <c r="D49" s="38" t="inlineStr">
         <is>
           <t>CrowdStrike</t>
         </is>
       </c>
-      <c r="E49" s="37" t="inlineStr">
+      <c r="E49" s="38" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3684,12 +3690,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H49" s="37" t="inlineStr">
+      <c r="H49" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I49" s="37" t="inlineStr">
+      <c r="I49" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3704,20 +3710,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L49" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M49" s="37" t="inlineStr"/>
+      <c r="L49" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M49" s="38" t="inlineStr"/>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="36" t="inlineStr">
+      <c r="A50" s="39" t="inlineStr">
         <is>
           <t>4417553585</t>
         </is>
       </c>
-      <c r="B50" s="36" t="inlineStr">
+      <c r="B50" s="39" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3727,12 +3733,12 @@
           <t>Entry-Level Software Engineer | Remote</t>
         </is>
       </c>
-      <c r="D50" s="36" t="inlineStr">
+      <c r="D50" s="39" t="inlineStr">
         <is>
           <t>Crossing Hurdles</t>
         </is>
       </c>
-      <c r="E50" s="36" t="inlineStr">
+      <c r="E50" s="39" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3747,12 +3753,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H50" s="36" t="inlineStr">
+      <c r="H50" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I50" s="36" t="inlineStr">
+      <c r="I50" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3767,20 +3773,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L50" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M50" s="36" t="inlineStr"/>
+      <c r="L50" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M50" s="39" t="inlineStr"/>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="37" t="inlineStr">
+      <c r="A51" s="38" t="inlineStr">
         <is>
           <t>4309699451</t>
         </is>
       </c>
-      <c r="B51" s="37" t="inlineStr">
+      <c r="B51" s="38" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3790,12 +3796,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D51" s="37" t="inlineStr">
+      <c r="D51" s="38" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E51" s="37" t="inlineStr">
+      <c r="E51" s="38" t="inlineStr">
         <is>
           <t>Washington, United States</t>
         </is>
@@ -3810,12 +3816,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H51" s="37" t="inlineStr">
+      <c r="H51" s="38" t="inlineStr">
         <is>
           <t>109</t>
         </is>
       </c>
-      <c r="I51" s="37" t="inlineStr">
+      <c r="I51" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3830,20 +3836,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L51" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M51" s="37" t="inlineStr"/>
+      <c r="L51" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M51" s="38" t="inlineStr"/>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="36" t="inlineStr">
+      <c r="A52" s="39" t="inlineStr">
         <is>
           <t>4406945262</t>
         </is>
       </c>
-      <c r="B52" s="36" t="inlineStr">
+      <c r="B52" s="39" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3853,12 +3859,12 @@
           <t>DevSecOps Intern</t>
         </is>
       </c>
-      <c r="D52" s="36" t="inlineStr">
+      <c r="D52" s="39" t="inlineStr">
         <is>
           <t>Modern Technology Solutions, Inc. (MTSI)</t>
         </is>
       </c>
-      <c r="E52" s="36" t="inlineStr">
+      <c r="E52" s="39" t="inlineStr">
         <is>
           <t>Niceville, FL</t>
         </is>
@@ -3873,12 +3879,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H52" s="36" t="inlineStr">
+      <c r="H52" s="39" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="I52" s="36" t="inlineStr">
+      <c r="I52" s="39" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -3893,20 +3899,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L52" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M52" s="36" t="inlineStr"/>
+      <c r="L52" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M52" s="39" t="inlineStr"/>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="37" t="inlineStr">
+      <c r="A53" s="38" t="inlineStr">
         <is>
           <t>4407937810</t>
         </is>
       </c>
-      <c r="B53" s="37" t="inlineStr">
+      <c r="B53" s="38" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3916,12 +3922,12 @@
           <t>Temporary Intern - Agentic AI &amp; Neural-Symbolic Systems (Healthcare)</t>
         </is>
       </c>
-      <c r="D53" s="37" t="inlineStr">
+      <c r="D53" s="38" t="inlineStr">
         <is>
           <t>Cotiviti</t>
         </is>
       </c>
-      <c r="E53" s="37" t="inlineStr">
+      <c r="E53" s="38" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3936,12 +3942,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H53" s="37" t="inlineStr">
+      <c r="H53" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I53" s="37" t="inlineStr">
+      <c r="I53" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -3956,20 +3962,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L53" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M53" s="37" t="inlineStr"/>
+      <c r="L53" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M53" s="38" t="inlineStr"/>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="36" t="inlineStr">
+      <c r="A54" s="39" t="inlineStr">
         <is>
           <t>4414089997</t>
         </is>
       </c>
-      <c r="B54" s="36" t="inlineStr">
+      <c r="B54" s="39" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -3979,12 +3985,12 @@
           <t>Visualization Engineer Intern</t>
         </is>
       </c>
-      <c r="D54" s="36" t="inlineStr">
+      <c r="D54" s="39" t="inlineStr">
         <is>
           <t>Leidos</t>
         </is>
       </c>
-      <c r="E54" s="36" t="inlineStr">
+      <c r="E54" s="39" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -3999,12 +4005,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H54" s="36" t="inlineStr">
+      <c r="H54" s="39" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="I54" s="36" t="inlineStr">
+      <c r="I54" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4019,20 +4025,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L54" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M54" s="36" t="inlineStr"/>
+      <c r="L54" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M54" s="39" t="inlineStr"/>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="37" t="inlineStr">
+      <c r="A55" s="38" t="inlineStr">
         <is>
           <t>4387443129</t>
         </is>
       </c>
-      <c r="B55" s="37" t="inlineStr">
+      <c r="B55" s="38" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4042,12 +4048,12 @@
           <t>2026 Interns</t>
         </is>
       </c>
-      <c r="D55" s="37" t="inlineStr">
+      <c r="D55" s="38" t="inlineStr">
         <is>
           <t>Givelify</t>
         </is>
       </c>
-      <c r="E55" s="37" t="inlineStr">
+      <c r="E55" s="38" t="inlineStr">
         <is>
           <t>Dallas, TX</t>
         </is>
@@ -4062,12 +4068,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H55" s="37" t="inlineStr">
+      <c r="H55" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I55" s="37" t="inlineStr">
+      <c r="I55" s="38" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -4082,20 +4088,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L55" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M55" s="37" t="inlineStr"/>
+      <c r="L55" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M55" s="38" t="inlineStr"/>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="36" t="inlineStr">
+      <c r="A56" s="39" t="inlineStr">
         <is>
           <t>4337980765</t>
         </is>
       </c>
-      <c r="B56" s="36" t="inlineStr">
+      <c r="B56" s="39" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4105,12 +4111,12 @@
           <t>Submitting for a General Internship Application</t>
         </is>
       </c>
-      <c r="D56" s="36" t="inlineStr">
+      <c r="D56" s="39" t="inlineStr">
         <is>
           <t>Chainguard</t>
         </is>
       </c>
-      <c r="E56" s="36" t="inlineStr">
+      <c r="E56" s="39" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4125,12 +4131,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H56" s="36" t="inlineStr">
+      <c r="H56" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I56" s="36" t="inlineStr">
+      <c r="I56" s="39" t="inlineStr">
         <is>
           <t>Volunteer</t>
         </is>
@@ -4145,20 +4151,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L56" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M56" s="36" t="inlineStr"/>
+      <c r="L56" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M56" s="39" t="inlineStr"/>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="37" t="inlineStr">
+      <c r="A57" s="38" t="inlineStr">
         <is>
           <t>4417030460</t>
         </is>
       </c>
-      <c r="B57" s="37" t="inlineStr">
+      <c r="B57" s="38" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4168,12 +4174,12 @@
           <t>AI Researcher Intern</t>
         </is>
       </c>
-      <c r="D57" s="37" t="inlineStr">
+      <c r="D57" s="38" t="inlineStr">
         <is>
           <t>BioSpace</t>
         </is>
       </c>
-      <c r="E57" s="37" t="inlineStr">
+      <c r="E57" s="38" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4188,12 +4194,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H57" s="37" t="inlineStr">
+      <c r="H57" s="38" t="inlineStr">
         <is>
           <t>151</t>
         </is>
       </c>
-      <c r="I57" s="37" t="inlineStr">
+      <c r="I57" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4208,20 +4214,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L57" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M57" s="37" t="inlineStr"/>
+      <c r="L57" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M57" s="38" t="inlineStr"/>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="36" t="inlineStr">
+      <c r="A58" s="39" t="inlineStr">
         <is>
           <t>4406930916</t>
         </is>
       </c>
-      <c r="B58" s="36" t="inlineStr">
+      <c r="B58" s="39" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4231,12 +4237,12 @@
           <t>DevSecOps Intern</t>
         </is>
       </c>
-      <c r="D58" s="36" t="inlineStr">
+      <c r="D58" s="39" t="inlineStr">
         <is>
           <t>Modern Technology Solutions, Inc. (MTSI)</t>
         </is>
       </c>
-      <c r="E58" s="36" t="inlineStr">
+      <c r="E58" s="39" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4251,12 +4257,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H58" s="36" t="inlineStr">
+      <c r="H58" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I58" s="36" t="inlineStr">
+      <c r="I58" s="39" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -4271,20 +4277,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L58" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M58" s="36" t="inlineStr"/>
+      <c r="L58" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M58" s="39" t="inlineStr"/>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="37" t="inlineStr">
+      <c r="A59" s="38" t="inlineStr">
         <is>
           <t>4385798937</t>
         </is>
       </c>
-      <c r="B59" s="37" t="inlineStr">
+      <c r="B59" s="38" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4294,12 +4300,12 @@
           <t>Research Intern on Generative and Protective AI for Content Creation</t>
         </is>
       </c>
-      <c r="D59" s="37" t="inlineStr">
+      <c r="D59" s="38" t="inlineStr">
         <is>
           <t>SonyAI</t>
         </is>
       </c>
-      <c r="E59" s="37" t="inlineStr">
+      <c r="E59" s="38" t="inlineStr">
         <is>
           <t>New York, United States</t>
         </is>
@@ -4314,12 +4320,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H59" s="37" t="inlineStr">
+      <c r="H59" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I59" s="37" t="inlineStr">
+      <c r="I59" s="38" t="inlineStr">
         <is>
           <t>Part-time</t>
         </is>
@@ -4334,20 +4340,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L59" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M59" s="37" t="inlineStr"/>
+      <c r="L59" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M59" s="38" t="inlineStr"/>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="36" t="inlineStr">
+      <c r="A60" s="39" t="inlineStr">
         <is>
           <t>4414396950</t>
         </is>
       </c>
-      <c r="B60" s="36" t="inlineStr">
+      <c r="B60" s="39" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
@@ -4357,12 +4363,12 @@
           <t>Power Platform Intern</t>
         </is>
       </c>
-      <c r="D60" s="36" t="inlineStr">
+      <c r="D60" s="39" t="inlineStr">
         <is>
           <t>Leidos</t>
         </is>
       </c>
-      <c r="E60" s="36" t="inlineStr">
+      <c r="E60" s="39" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -4377,12 +4383,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H60" s="36" t="inlineStr">
+      <c r="H60" s="39" t="inlineStr">
         <is>
           <t>135</t>
         </is>
       </c>
-      <c r="I60" s="36" t="inlineStr">
+      <c r="I60" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4397,20 +4403,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L60" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M60" s="36" t="inlineStr"/>
+      <c r="L60" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M60" s="39" t="inlineStr"/>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="37" t="inlineStr">
+      <c r="A61" s="38" t="inlineStr">
         <is>
           <t>4413699205</t>
         </is>
       </c>
-      <c r="B61" s="37" t="inlineStr">
+      <c r="B61" s="38" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4420,12 +4426,12 @@
           <t>Junior Software Engineer - Automation &amp; Integration</t>
         </is>
       </c>
-      <c r="D61" s="37" t="inlineStr">
+      <c r="D61" s="38" t="inlineStr">
         <is>
           <t>Fletcher Development LLC</t>
         </is>
       </c>
-      <c r="E61" s="37" t="inlineStr">
+      <c r="E61" s="38" t="inlineStr">
         <is>
           <t>Redding, CT</t>
         </is>
@@ -4440,12 +4446,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H61" s="37" t="inlineStr">
+      <c r="H61" s="38" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="I61" s="37" t="inlineStr">
+      <c r="I61" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4460,20 +4466,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L61" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M61" s="37" t="inlineStr"/>
+      <c r="L61" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M61" s="38" t="inlineStr"/>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="36" t="inlineStr">
+      <c r="A62" s="39" t="inlineStr">
         <is>
           <t>4416171988</t>
         </is>
       </c>
-      <c r="B62" s="36" t="inlineStr">
+      <c r="B62" s="39" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4483,12 +4489,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D62" s="36" t="inlineStr">
+      <c r="D62" s="39" t="inlineStr">
         <is>
           <t>Altec</t>
         </is>
       </c>
-      <c r="E62" s="36" t="inlineStr">
+      <c r="E62" s="39" t="inlineStr">
         <is>
           <t>Birmingham, AL</t>
         </is>
@@ -4503,12 +4509,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H62" s="36" t="inlineStr">
+      <c r="H62" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I62" s="36" t="inlineStr">
+      <c r="I62" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4523,20 +4529,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L62" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M62" s="36" t="inlineStr"/>
+      <c r="L62" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M62" s="39" t="inlineStr"/>
     </row>
     <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="37" t="inlineStr">
+      <c r="A63" s="38" t="inlineStr">
         <is>
           <t>4403444963</t>
         </is>
       </c>
-      <c r="B63" s="37" t="inlineStr">
+      <c r="B63" s="38" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4546,12 +4552,12 @@
           <t>Junior Applications Developer (NY HELPS) #2026-252</t>
         </is>
       </c>
-      <c r="D63" s="37" t="inlineStr">
+      <c r="D63" s="38" t="inlineStr">
         <is>
           <t>Capital Region BOCES</t>
         </is>
       </c>
-      <c r="E63" s="37" t="inlineStr">
+      <c r="E63" s="38" t="inlineStr">
         <is>
           <t>Albany, NY</t>
         </is>
@@ -4566,12 +4572,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H63" s="37" t="inlineStr">
+      <c r="H63" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I63" s="37" t="inlineStr">
+      <c r="I63" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4586,20 +4592,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L63" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M63" s="37" t="inlineStr"/>
+      <c r="L63" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M63" s="38" t="inlineStr"/>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="36" t="inlineStr">
+      <c r="A64" s="39" t="inlineStr">
         <is>
           <t>4418506121</t>
         </is>
       </c>
-      <c r="B64" s="36" t="inlineStr">
+      <c r="B64" s="39" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4609,12 +4615,12 @@
           <t>Core System Junior Developer</t>
         </is>
       </c>
-      <c r="D64" s="36" t="inlineStr">
+      <c r="D64" s="39" t="inlineStr">
         <is>
           <t>Cyprus Federal Credit Union</t>
         </is>
       </c>
-      <c r="E64" s="36" t="inlineStr">
+      <c r="E64" s="39" t="inlineStr">
         <is>
           <t>West Jordan, UT</t>
         </is>
@@ -4629,12 +4635,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H64" s="36" t="inlineStr">
+      <c r="H64" s="39" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="I64" s="36" t="inlineStr">
+      <c r="I64" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4649,20 +4655,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L64" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M64" s="36" t="inlineStr"/>
+      <c r="L64" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M64" s="39" t="inlineStr"/>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="37" t="inlineStr">
+      <c r="A65" s="38" t="inlineStr">
         <is>
           <t>4413905706</t>
         </is>
       </c>
-      <c r="B65" s="37" t="inlineStr">
+      <c r="B65" s="38" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4672,12 +4678,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D65" s="37" t="inlineStr">
+      <c r="D65" s="38" t="inlineStr">
         <is>
           <t>Arnex Solutions LLC</t>
         </is>
       </c>
-      <c r="E65" s="37" t="inlineStr">
+      <c r="E65" s="38" t="inlineStr">
         <is>
           <t>Princeton, NJ</t>
         </is>
@@ -4692,12 +4698,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H65" s="37" t="inlineStr">
+      <c r="H65" s="38" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I65" s="37" t="inlineStr">
+      <c r="I65" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4712,20 +4718,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L65" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M65" s="37" t="inlineStr"/>
+      <c r="L65" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M65" s="38" t="inlineStr"/>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="36" t="inlineStr">
+      <c r="A66" s="39" t="inlineStr">
         <is>
           <t>4418963446</t>
         </is>
       </c>
-      <c r="B66" s="36" t="inlineStr">
+      <c r="B66" s="39" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4735,12 +4741,12 @@
           <t>Junior Software Engineer - Automation &amp; Integration</t>
         </is>
       </c>
-      <c r="D66" s="36" t="inlineStr">
+      <c r="D66" s="39" t="inlineStr">
         <is>
           <t>Vibrant Building Technologies</t>
         </is>
       </c>
-      <c r="E66" s="36" t="inlineStr">
+      <c r="E66" s="39" t="inlineStr">
         <is>
           <t>Ridgefield, CT</t>
         </is>
@@ -4755,12 +4761,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H66" s="36" t="inlineStr">
+      <c r="H66" s="39" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="I66" s="36" t="inlineStr">
+      <c r="I66" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4775,20 +4781,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L66" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M66" s="36" t="inlineStr"/>
+      <c r="L66" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M66" s="39" t="inlineStr"/>
     </row>
     <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="37" t="inlineStr">
+      <c r="A67" s="38" t="inlineStr">
         <is>
           <t>4413759052</t>
         </is>
       </c>
-      <c r="B67" s="37" t="inlineStr">
+      <c r="B67" s="38" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4798,12 +4804,12 @@
           <t>Junior Full Stack Developer</t>
         </is>
       </c>
-      <c r="D67" s="37" t="inlineStr">
+      <c r="D67" s="38" t="inlineStr">
         <is>
           <t>Allied World Reinsurance Company</t>
         </is>
       </c>
-      <c r="E67" s="37" t="inlineStr">
+      <c r="E67" s="38" t="inlineStr">
         <is>
           <t>Iselin, NJ</t>
         </is>
@@ -4818,12 +4824,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H67" s="37" t="inlineStr">
+      <c r="H67" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I67" s="37" t="inlineStr">
+      <c r="I67" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4838,20 +4844,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L67" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M67" s="37" t="inlineStr"/>
+      <c r="L67" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M67" s="38" t="inlineStr"/>
     </row>
     <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="36" t="inlineStr">
+      <c r="A68" s="39" t="inlineStr">
         <is>
           <t>4417542502</t>
         </is>
       </c>
-      <c r="B68" s="36" t="inlineStr">
+      <c r="B68" s="39" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4861,12 +4867,12 @@
           <t>Junior Developer</t>
         </is>
       </c>
-      <c r="D68" s="36" t="inlineStr">
+      <c r="D68" s="39" t="inlineStr">
         <is>
           <t>CloudMasonry</t>
         </is>
       </c>
-      <c r="E68" s="36" t="inlineStr">
+      <c r="E68" s="39" t="inlineStr">
         <is>
           <t>Indianapolis, IN</t>
         </is>
@@ -4881,12 +4887,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H68" s="36" t="inlineStr">
+      <c r="H68" s="39" t="inlineStr">
         <is>
           <t>154</t>
         </is>
       </c>
-      <c r="I68" s="36" t="inlineStr">
+      <c r="I68" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4901,20 +4907,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L68" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M68" s="36" t="inlineStr"/>
+      <c r="L68" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M68" s="39" t="inlineStr"/>
     </row>
     <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="37" t="inlineStr">
+      <c r="A69" s="38" t="inlineStr">
         <is>
           <t>4374856035</t>
         </is>
       </c>
-      <c r="B69" s="37" t="inlineStr">
+      <c r="B69" s="38" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4924,12 +4930,12 @@
           <t>Programmer II</t>
         </is>
       </c>
-      <c r="D69" s="37" t="inlineStr">
+      <c r="D69" s="38" t="inlineStr">
         <is>
           <t>Willis Knighton Health</t>
         </is>
       </c>
-      <c r="E69" s="37" t="inlineStr">
+      <c r="E69" s="38" t="inlineStr">
         <is>
           <t>Louisiana, United States</t>
         </is>
@@ -4944,12 +4950,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H69" s="37" t="inlineStr">
+      <c r="H69" s="38" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="I69" s="37" t="inlineStr">
+      <c r="I69" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -4964,20 +4970,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L69" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M69" s="37" t="inlineStr"/>
+      <c r="L69" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M69" s="38" t="inlineStr"/>
     </row>
     <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="36" t="inlineStr">
+      <c r="A70" s="39" t="inlineStr">
         <is>
           <t>4416302564</t>
         </is>
       </c>
-      <c r="B70" s="36" t="inlineStr">
+      <c r="B70" s="39" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -4987,12 +4993,12 @@
           <t>Software Engineer I</t>
         </is>
       </c>
-      <c r="D70" s="36" t="inlineStr">
+      <c r="D70" s="39" t="inlineStr">
         <is>
           <t>American Express</t>
         </is>
       </c>
-      <c r="E70" s="36" t="inlineStr">
+      <c r="E70" s="39" t="inlineStr">
         <is>
           <t>Sunrise, FL</t>
         </is>
@@ -5007,12 +5013,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H70" s="36" t="inlineStr">
+      <c r="H70" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I70" s="36" t="inlineStr">
+      <c r="I70" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5027,20 +5033,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L70" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M70" s="36" t="inlineStr"/>
+      <c r="L70" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M70" s="39" t="inlineStr"/>
     </row>
     <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="37" t="inlineStr">
+      <c r="A71" s="38" t="inlineStr">
         <is>
           <t>4417014137</t>
         </is>
       </c>
-      <c r="B71" s="37" t="inlineStr">
+      <c r="B71" s="38" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5050,12 +5056,12 @@
           <t>Junior Software Developer, Applications</t>
         </is>
       </c>
-      <c r="D71" s="37" t="inlineStr">
+      <c r="D71" s="38" t="inlineStr">
         <is>
           <t>ECS</t>
         </is>
       </c>
-      <c r="E71" s="37" t="inlineStr">
+      <c r="E71" s="38" t="inlineStr">
         <is>
           <t>O'Fallon, IL</t>
         </is>
@@ -5070,12 +5076,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H71" s="37" t="inlineStr">
+      <c r="H71" s="38" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="I71" s="37" t="inlineStr">
+      <c r="I71" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5090,20 +5096,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L71" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M71" s="37" t="inlineStr"/>
+      <c r="L71" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M71" s="38" t="inlineStr"/>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="36" t="inlineStr">
+      <c r="A72" s="39" t="inlineStr">
         <is>
           <t>4381211472</t>
         </is>
       </c>
-      <c r="B72" s="36" t="inlineStr">
+      <c r="B72" s="39" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5113,12 +5119,12 @@
           <t>Programmer</t>
         </is>
       </c>
-      <c r="D72" s="36" t="inlineStr">
+      <c r="D72" s="39" t="inlineStr">
         <is>
           <t>City of New York</t>
         </is>
       </c>
-      <c r="E72" s="36" t="inlineStr">
+      <c r="E72" s="39" t="inlineStr">
         <is>
           <t>Bronx, NY</t>
         </is>
@@ -5133,12 +5139,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H72" s="36" t="inlineStr">
+      <c r="H72" s="39" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="I72" s="36" t="inlineStr">
+      <c r="I72" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5153,20 +5159,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L72" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M72" s="36" t="inlineStr"/>
+      <c r="L72" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M72" s="39" t="inlineStr"/>
     </row>
     <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="37" t="inlineStr">
+      <c r="A73" s="38" t="inlineStr">
         <is>
           <t>4168416236</t>
         </is>
       </c>
-      <c r="B73" s="37" t="inlineStr">
+      <c r="B73" s="38" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5176,12 +5182,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D73" s="37" t="inlineStr">
+      <c r="D73" s="38" t="inlineStr">
         <is>
           <t>Interclypse</t>
         </is>
       </c>
-      <c r="E73" s="37" t="inlineStr">
+      <c r="E73" s="38" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
@@ -5196,12 +5202,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H73" s="37" t="inlineStr">
+      <c r="H73" s="38" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I73" s="37" t="inlineStr">
+      <c r="I73" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5216,20 +5222,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L73" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M73" s="37" t="inlineStr"/>
+      <c r="L73" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M73" s="38" t="inlineStr"/>
     </row>
     <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="36" t="inlineStr">
+      <c r="A74" s="39" t="inlineStr">
         <is>
           <t>4403507357</t>
         </is>
       </c>
-      <c r="B74" s="36" t="inlineStr">
+      <c r="B74" s="39" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5239,12 +5245,12 @@
           <t>Software Developer:</t>
         </is>
       </c>
-      <c r="D74" s="36" t="inlineStr">
+      <c r="D74" s="39" t="inlineStr">
         <is>
           <t>IQuest Solutions Corporation</t>
         </is>
       </c>
-      <c r="E74" s="36" t="inlineStr">
+      <c r="E74" s="39" t="inlineStr">
         <is>
           <t>Plano, TX</t>
         </is>
@@ -5259,12 +5265,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H74" s="36" t="inlineStr">
+      <c r="H74" s="39" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I74" s="36" t="inlineStr">
+      <c r="I74" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5279,20 +5285,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L74" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M74" s="36" t="inlineStr"/>
+      <c r="L74" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M74" s="39" t="inlineStr"/>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="37" t="inlineStr">
+      <c r="A75" s="38" t="inlineStr">
         <is>
           <t>4309800238</t>
         </is>
       </c>
-      <c r="B75" s="37" t="inlineStr">
+      <c r="B75" s="38" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5302,12 +5308,12 @@
           <t>Backend Software Engineer</t>
         </is>
       </c>
-      <c r="D75" s="37" t="inlineStr">
+      <c r="D75" s="38" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E75" s="37" t="inlineStr">
+      <c r="E75" s="38" t="inlineStr">
         <is>
           <t>Texas, United States</t>
         </is>
@@ -5322,12 +5328,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H75" s="37" t="inlineStr">
+      <c r="H75" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I75" s="37" t="inlineStr">
+      <c r="I75" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5342,20 +5348,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L75" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M75" s="37" t="inlineStr"/>
+      <c r="L75" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M75" s="38" t="inlineStr"/>
     </row>
     <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="36" t="inlineStr">
+      <c r="A76" s="39" t="inlineStr">
         <is>
           <t>4404109089</t>
         </is>
       </c>
-      <c r="B76" s="36" t="inlineStr">
+      <c r="B76" s="39" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5365,12 +5371,12 @@
           <t>Software Development Engineer I</t>
         </is>
       </c>
-      <c r="D76" s="36" t="inlineStr">
+      <c r="D76" s="39" t="inlineStr">
         <is>
           <t>GM Financial</t>
         </is>
       </c>
-      <c r="E76" s="36" t="inlineStr">
+      <c r="E76" s="39" t="inlineStr">
         <is>
           <t>Arlington, TX</t>
         </is>
@@ -5385,12 +5391,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H76" s="36" t="inlineStr">
+      <c r="H76" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I76" s="36" t="inlineStr">
+      <c r="I76" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5405,20 +5411,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L76" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M76" s="36" t="inlineStr"/>
+      <c r="L76" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M76" s="39" t="inlineStr"/>
     </row>
     <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="37" t="inlineStr">
+      <c r="A77" s="38" t="inlineStr">
         <is>
           <t>3986116411</t>
         </is>
       </c>
-      <c r="B77" s="37" t="inlineStr">
+      <c r="B77" s="38" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5428,12 +5434,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D77" s="37" t="inlineStr">
+      <c r="D77" s="38" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E77" s="37" t="inlineStr">
+      <c r="E77" s="38" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -5448,12 +5454,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H77" s="37" t="inlineStr">
+      <c r="H77" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I77" s="37" t="inlineStr">
+      <c r="I77" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5468,20 +5474,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L77" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M77" s="37" t="inlineStr"/>
+      <c r="L77" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M77" s="38" t="inlineStr"/>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="36" t="inlineStr">
+      <c r="A78" s="39" t="inlineStr">
         <is>
           <t>4418051524</t>
         </is>
       </c>
-      <c r="B78" s="36" t="inlineStr">
+      <c r="B78" s="39" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5491,12 +5497,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D78" s="36" t="inlineStr">
+      <c r="D78" s="39" t="inlineStr">
         <is>
           <t>Relativity</t>
         </is>
       </c>
-      <c r="E78" s="36" t="inlineStr">
+      <c r="E78" s="39" t="inlineStr">
         <is>
           <t>Texas, United States</t>
         </is>
@@ -5511,12 +5517,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H78" s="36" t="inlineStr">
+      <c r="H78" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I78" s="36" t="inlineStr">
+      <c r="I78" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5531,20 +5537,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L78" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M78" s="36" t="inlineStr"/>
+      <c r="L78" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M78" s="39" t="inlineStr"/>
     </row>
     <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="37" t="inlineStr">
+      <c r="A79" s="38" t="inlineStr">
         <is>
           <t>4409856693</t>
         </is>
       </c>
-      <c r="B79" s="37" t="inlineStr">
+      <c r="B79" s="38" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5554,12 +5560,12 @@
           <t>Software Engineer - Payments</t>
         </is>
       </c>
-      <c r="D79" s="37" t="inlineStr">
+      <c r="D79" s="38" t="inlineStr">
         <is>
           <t>Cloudbeds</t>
         </is>
       </c>
-      <c r="E79" s="37" t="inlineStr">
+      <c r="E79" s="38" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -5574,12 +5580,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H79" s="37" t="inlineStr">
+      <c r="H79" s="38" t="inlineStr">
         <is>
           <t>177</t>
         </is>
       </c>
-      <c r="I79" s="37" t="inlineStr">
+      <c r="I79" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5594,20 +5600,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L79" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M79" s="37" t="inlineStr"/>
+      <c r="L79" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M79" s="38" t="inlineStr"/>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="36" t="inlineStr">
+      <c r="A80" s="39" t="inlineStr">
         <is>
           <t>3986111771</t>
         </is>
       </c>
-      <c r="B80" s="36" t="inlineStr">
+      <c r="B80" s="39" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5617,12 +5623,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D80" s="36" t="inlineStr">
+      <c r="D80" s="39" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="E80" s="36" t="inlineStr">
+      <c r="E80" s="39" t="inlineStr">
         <is>
           <t>Carrollton, TX</t>
         </is>
@@ -5637,12 +5643,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H80" s="36" t="inlineStr">
+      <c r="H80" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I80" s="36" t="inlineStr">
+      <c r="I80" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5657,20 +5663,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L80" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M80" s="36" t="inlineStr"/>
+      <c r="L80" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M80" s="39" t="inlineStr"/>
     </row>
     <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="37" t="inlineStr">
+      <c r="A81" s="38" t="inlineStr">
         <is>
           <t>4417160720</t>
         </is>
       </c>
-      <c r="B81" s="37" t="inlineStr">
+      <c r="B81" s="38" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
@@ -5680,12 +5686,12 @@
           <t>Full-Stack AI Developer</t>
         </is>
       </c>
-      <c r="D81" s="37" t="inlineStr">
+      <c r="D81" s="38" t="inlineStr">
         <is>
           <t>AnswerMyQ</t>
         </is>
       </c>
-      <c r="E81" s="37" t="inlineStr">
+      <c r="E81" s="38" t="inlineStr">
         <is>
           <t>Austin, Texas Metropolitan Area</t>
         </is>
@@ -5700,12 +5706,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H81" s="37" t="inlineStr">
+      <c r="H81" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I81" s="37" t="inlineStr">
+      <c r="I81" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5720,20 +5726,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L81" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M81" s="37" t="inlineStr"/>
+      <c r="L81" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M81" s="38" t="inlineStr"/>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="36" t="inlineStr">
+      <c r="A82" s="39" t="inlineStr">
         <is>
           <t>4418507307</t>
         </is>
       </c>
-      <c r="B82" s="36" t="inlineStr">
+      <c r="B82" s="39" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -5743,12 +5749,12 @@
           <t>Entry Level Software Engineer Intern</t>
         </is>
       </c>
-      <c r="D82" s="36" t="inlineStr">
+      <c r="D82" s="39" t="inlineStr">
         <is>
           <t>CORMAC</t>
         </is>
       </c>
-      <c r="E82" s="36" t="inlineStr">
+      <c r="E82" s="39" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -5763,12 +5769,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H82" s="36" t="inlineStr">
+      <c r="H82" s="39" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="I82" s="36" t="inlineStr">
+      <c r="I82" s="39" t="inlineStr">
         <is>
           <t>Volunteer</t>
         </is>
@@ -5783,20 +5789,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L82" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M82" s="36" t="inlineStr"/>
+      <c r="L82" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M82" s="39" t="inlineStr"/>
     </row>
     <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="37" t="inlineStr">
+      <c r="A83" s="38" t="inlineStr">
         <is>
           <t>4413360938</t>
         </is>
       </c>
-      <c r="B83" s="37" t="inlineStr">
+      <c r="B83" s="38" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -5806,12 +5812,12 @@
           <t>Software Engineer Internship (Remote)</t>
         </is>
       </c>
-      <c r="D83" s="37" t="inlineStr">
+      <c r="D83" s="38" t="inlineStr">
         <is>
           <t>Orange Trail</t>
         </is>
       </c>
-      <c r="E83" s="37" t="inlineStr">
+      <c r="E83" s="38" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -5826,12 +5832,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H83" s="37" t="inlineStr">
+      <c r="H83" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I83" s="37" t="inlineStr">
+      <c r="I83" s="38" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -5846,20 +5852,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L83" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M83" s="37" t="inlineStr"/>
+      <c r="L83" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M83" s="38" t="inlineStr"/>
     </row>
     <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="36" t="inlineStr">
+      <c r="A84" s="39" t="inlineStr">
         <is>
           <t>4348111641</t>
         </is>
       </c>
-      <c r="B84" s="36" t="inlineStr">
+      <c r="B84" s="39" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -5869,12 +5875,12 @@
           <t>Software Engineer Intern</t>
         </is>
       </c>
-      <c r="D84" s="36" t="inlineStr">
+      <c r="D84" s="39" t="inlineStr">
         <is>
           <t>Simular</t>
         </is>
       </c>
-      <c r="E84" s="36" t="inlineStr">
+      <c r="E84" s="39" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -5889,12 +5895,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H84" s="36" t="inlineStr">
+      <c r="H84" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I84" s="36" t="inlineStr">
+      <c r="I84" s="39" t="inlineStr">
         <is>
           <t>Volunteer</t>
         </is>
@@ -5909,20 +5915,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L84" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M84" s="36" t="inlineStr"/>
+      <c r="L84" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M84" s="39" t="inlineStr"/>
     </row>
     <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="37" t="inlineStr">
+      <c r="A85" s="38" t="inlineStr">
         <is>
           <t>4411853543</t>
         </is>
       </c>
-      <c r="B85" s="37" t="inlineStr">
+      <c r="B85" s="38" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -5932,12 +5938,12 @@
           <t>Intern, Software Engineer</t>
         </is>
       </c>
-      <c r="D85" s="37" t="inlineStr">
+      <c r="D85" s="38" t="inlineStr">
         <is>
           <t>Accelerate Learning</t>
         </is>
       </c>
-      <c r="E85" s="37" t="inlineStr">
+      <c r="E85" s="38" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -5952,12 +5958,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H85" s="37" t="inlineStr">
+      <c r="H85" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I85" s="37" t="inlineStr">
+      <c r="I85" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -5972,20 +5978,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L85" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M85" s="37" t="inlineStr"/>
+      <c r="L85" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M85" s="38" t="inlineStr"/>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="36" t="inlineStr">
+      <c r="A86" s="39" t="inlineStr">
         <is>
           <t>4408586245</t>
         </is>
       </c>
-      <c r="B86" s="36" t="inlineStr">
+      <c r="B86" s="39" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -5995,12 +6001,12 @@
           <t>Junior Software Engineer Intern</t>
         </is>
       </c>
-      <c r="D86" s="36" t="inlineStr">
+      <c r="D86" s="39" t="inlineStr">
         <is>
           <t>Cantaloupe Inc</t>
         </is>
       </c>
-      <c r="E86" s="36" t="inlineStr">
+      <c r="E86" s="39" t="inlineStr">
         <is>
           <t>Atlanta, GA</t>
         </is>
@@ -6015,12 +6021,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H86" s="36" t="inlineStr">
+      <c r="H86" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I86" s="36" t="inlineStr">
+      <c r="I86" s="39" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -6035,20 +6041,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L86" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M86" s="36" t="inlineStr"/>
+      <c r="L86" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M86" s="39" t="inlineStr"/>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="37" t="inlineStr">
+      <c r="A87" s="38" t="inlineStr">
         <is>
           <t>4364536992</t>
         </is>
       </c>
-      <c r="B87" s="37" t="inlineStr">
+      <c r="B87" s="38" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
@@ -6058,12 +6064,12 @@
           <t>Summer Internship - Measurement, Research and Development - Academic Measurement</t>
         </is>
       </c>
-      <c r="D87" s="37" t="inlineStr">
+      <c r="D87" s="38" t="inlineStr">
         <is>
           <t>ChatGPT Jobs</t>
         </is>
       </c>
-      <c r="E87" s="37" t="inlineStr">
+      <c r="E87" s="38" t="inlineStr">
         <is>
           <t>Iowa City, IA</t>
         </is>
@@ -6078,12 +6084,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H87" s="37" t="inlineStr">
+      <c r="H87" s="38" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I87" s="37" t="inlineStr">
+      <c r="I87" s="38" t="inlineStr">
         <is>
           <t>Volunteer</t>
         </is>
@@ -6098,20 +6104,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L87" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M87" s="37" t="inlineStr"/>
+      <c r="L87" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M87" s="38" t="inlineStr"/>
     </row>
     <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="36" t="inlineStr">
+      <c r="A88" s="39" t="inlineStr">
         <is>
           <t>4413206045</t>
         </is>
       </c>
-      <c r="B88" s="36" t="inlineStr">
+      <c r="B88" s="39" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6121,12 +6127,12 @@
           <t>Software Development Engineer, EC2 Nitro Specialized Instances</t>
         </is>
       </c>
-      <c r="D88" s="36" t="inlineStr">
+      <c r="D88" s="39" t="inlineStr">
         <is>
           <t>Amazon Web Services (AWS)</t>
         </is>
       </c>
-      <c r="E88" s="36" t="inlineStr">
+      <c r="E88" s="39" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6141,12 +6147,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H88" s="36" t="inlineStr">
+      <c r="H88" s="39" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I88" s="36" t="inlineStr">
+      <c r="I88" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6161,20 +6167,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L88" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M88" s="36" t="inlineStr"/>
+      <c r="L88" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M88" s="39" t="inlineStr"/>
     </row>
     <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="37" t="inlineStr">
+      <c r="A89" s="38" t="inlineStr">
         <is>
           <t>4383211797</t>
         </is>
       </c>
-      <c r="B89" s="37" t="inlineStr">
+      <c r="B89" s="38" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6184,12 +6190,12 @@
           <t>software development engineer</t>
         </is>
       </c>
-      <c r="D89" s="37" t="inlineStr">
+      <c r="D89" s="38" t="inlineStr">
         <is>
           <t>Abacus Business Computer</t>
         </is>
       </c>
-      <c r="E89" s="37" t="inlineStr">
+      <c r="E89" s="38" t="inlineStr">
         <is>
           <t>Queens, NY</t>
         </is>
@@ -6204,12 +6210,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H89" s="37" t="inlineStr">
+      <c r="H89" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I89" s="37" t="inlineStr">
+      <c r="I89" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6224,20 +6230,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L89" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M89" s="37" t="inlineStr"/>
+      <c r="L89" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M89" s="38" t="inlineStr"/>
     </row>
     <row r="90" ht="18" customHeight="1">
-      <c r="A90" s="36" t="inlineStr">
+      <c r="A90" s="39" t="inlineStr">
         <is>
           <t>4418169749</t>
         </is>
       </c>
-      <c r="B90" s="36" t="inlineStr">
+      <c r="B90" s="39" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6247,12 +6253,12 @@
           <t>AI/ML Engineering Intern</t>
         </is>
       </c>
-      <c r="D90" s="36" t="inlineStr">
+      <c r="D90" s="39" t="inlineStr">
         <is>
           <t>Daice Labs</t>
         </is>
       </c>
-      <c r="E90" s="36" t="inlineStr">
+      <c r="E90" s="39" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -6267,12 +6273,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H90" s="36" t="inlineStr">
+      <c r="H90" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I90" s="36" t="inlineStr">
+      <c r="I90" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6287,20 +6293,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L90" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M90" s="36" t="inlineStr"/>
+      <c r="L90" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M90" s="39" t="inlineStr"/>
     </row>
     <row r="91" ht="18" customHeight="1">
-      <c r="A91" s="37" t="inlineStr">
+      <c r="A91" s="38" t="inlineStr">
         <is>
           <t>4281120416</t>
         </is>
       </c>
-      <c r="B91" s="37" t="inlineStr">
+      <c r="B91" s="38" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6310,12 +6316,12 @@
           <t>Site Reliability Engineer Intern (Compute Platform) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D91" s="37" t="inlineStr">
+      <c r="D91" s="38" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E91" s="37" t="inlineStr">
+      <c r="E91" s="38" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6330,12 +6336,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H91" s="37" t="inlineStr">
+      <c r="H91" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I91" s="37" t="inlineStr">
+      <c r="I91" s="38" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -6350,20 +6356,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L91" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M91" s="37" t="inlineStr"/>
+      <c r="L91" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M91" s="38" t="inlineStr"/>
     </row>
     <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="36" t="inlineStr">
+      <c r="A92" s="39" t="inlineStr">
         <is>
           <t>4377549744</t>
         </is>
       </c>
-      <c r="B92" s="36" t="inlineStr">
+      <c r="B92" s="39" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6373,12 +6379,12 @@
           <t>Software Development Engineer Apprentice - Military Veterans</t>
         </is>
       </c>
-      <c r="D92" s="36" t="inlineStr">
+      <c r="D92" s="39" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E92" s="36" t="inlineStr">
+      <c r="E92" s="39" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -6393,12 +6399,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H92" s="36" t="inlineStr">
+      <c r="H92" s="39" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="I92" s="36" t="inlineStr">
+      <c r="I92" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6413,20 +6419,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L92" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M92" s="36" t="inlineStr"/>
+      <c r="L92" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M92" s="39" t="inlineStr"/>
     </row>
     <row r="93" ht="18" customHeight="1">
-      <c r="A93" s="37" t="inlineStr">
+      <c r="A93" s="38" t="inlineStr">
         <is>
           <t>4377564429</t>
         </is>
       </c>
-      <c r="B93" s="37" t="inlineStr">
+      <c r="B93" s="38" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6436,12 +6442,12 @@
           <t>Software Development Engineer Apprentice - Military Veterans</t>
         </is>
       </c>
-      <c r="D93" s="37" t="inlineStr">
+      <c r="D93" s="38" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E93" s="37" t="inlineStr">
+      <c r="E93" s="38" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6456,12 +6462,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H93" s="37" t="inlineStr">
+      <c r="H93" s="38" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="I93" s="37" t="inlineStr">
+      <c r="I93" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6476,20 +6482,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L93" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M93" s="37" t="inlineStr"/>
+      <c r="L93" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M93" s="38" t="inlineStr"/>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="A94" s="36" t="inlineStr">
+      <c r="A94" s="39" t="inlineStr">
         <is>
           <t>4413206046</t>
         </is>
       </c>
-      <c r="B94" s="36" t="inlineStr">
+      <c r="B94" s="39" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6499,12 +6505,12 @@
           <t>Software Development Engineer, Vendor Funding</t>
         </is>
       </c>
-      <c r="D94" s="36" t="inlineStr">
+      <c r="D94" s="39" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E94" s="36" t="inlineStr">
+      <c r="E94" s="39" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6519,12 +6525,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H94" s="36" t="inlineStr">
+      <c r="H94" s="39" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I94" s="36" t="inlineStr">
+      <c r="I94" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6539,20 +6545,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L94" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M94" s="36" t="inlineStr"/>
+      <c r="L94" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M94" s="39" t="inlineStr"/>
     </row>
     <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="37" t="inlineStr">
+      <c r="A95" s="38" t="inlineStr">
         <is>
           <t>4408778227</t>
         </is>
       </c>
-      <c r="B95" s="37" t="inlineStr">
+      <c r="B95" s="38" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6562,12 +6568,12 @@
           <t>Front-End Engineer Fall Internship – 2026 (US)</t>
         </is>
       </c>
-      <c r="D95" s="37" t="inlineStr">
+      <c r="D95" s="38" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E95" s="37" t="inlineStr">
+      <c r="E95" s="38" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6582,12 +6588,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H95" s="37" t="inlineStr">
+      <c r="H95" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I95" s="37" t="inlineStr">
+      <c r="I95" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6602,20 +6608,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L95" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M95" s="37" t="inlineStr"/>
+      <c r="L95" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M95" s="38" t="inlineStr"/>
     </row>
     <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="36" t="inlineStr">
+      <c r="A96" s="39" t="inlineStr">
         <is>
           <t>4281117648</t>
         </is>
       </c>
-      <c r="B96" s="36" t="inlineStr">
+      <c r="B96" s="39" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6625,12 +6631,12 @@
           <t>Data Engineer Intern (E-commerce) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D96" s="36" t="inlineStr">
+      <c r="D96" s="39" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E96" s="36" t="inlineStr">
+      <c r="E96" s="39" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6645,12 +6651,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H96" s="36" t="inlineStr">
+      <c r="H96" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I96" s="36" t="inlineStr">
+      <c r="I96" s="39" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -6665,20 +6671,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L96" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M96" s="36" t="inlineStr"/>
+      <c r="L96" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M96" s="39" t="inlineStr"/>
     </row>
     <row r="97" ht="18" customHeight="1">
-      <c r="A97" s="37" t="inlineStr">
+      <c r="A97" s="38" t="inlineStr">
         <is>
           <t>4407126060</t>
         </is>
       </c>
-      <c r="B97" s="37" t="inlineStr">
+      <c r="B97" s="38" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6688,12 +6694,12 @@
           <t>Site Reliability Engineer Intern (Data Infrastructure) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D97" s="37" t="inlineStr">
+      <c r="D97" s="38" t="inlineStr">
         <is>
           <t>ByteDance</t>
         </is>
       </c>
-      <c r="E97" s="37" t="inlineStr">
+      <c r="E97" s="38" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6708,12 +6714,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H97" s="37" t="inlineStr">
+      <c r="H97" s="38" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="I97" s="37" t="inlineStr">
+      <c r="I97" s="38" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -6728,20 +6734,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L97" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M97" s="37" t="inlineStr"/>
+      <c r="L97" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M97" s="38" t="inlineStr"/>
     </row>
     <row r="98" ht="18" customHeight="1">
-      <c r="A98" s="36" t="inlineStr">
+      <c r="A98" s="39" t="inlineStr">
         <is>
           <t>4392432360</t>
         </is>
       </c>
-      <c r="B98" s="36" t="inlineStr">
+      <c r="B98" s="39" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6751,12 +6757,12 @@
           <t>Software Engineer Intern (AI Model Optimization) - 2026 Summer (BS/MS)</t>
         </is>
       </c>
-      <c r="D98" s="36" t="inlineStr">
+      <c r="D98" s="39" t="inlineStr">
         <is>
           <t>TikTok</t>
         </is>
       </c>
-      <c r="E98" s="36" t="inlineStr">
+      <c r="E98" s="39" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6771,12 +6777,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H98" s="36" t="inlineStr">
+      <c r="H98" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I98" s="36" t="inlineStr">
+      <c r="I98" s="39" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -6791,20 +6797,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L98" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M98" s="36" t="inlineStr"/>
+      <c r="L98" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M98" s="39" t="inlineStr"/>
     </row>
     <row r="99" ht="18" customHeight="1">
-      <c r="A99" s="37" t="inlineStr">
+      <c r="A99" s="38" t="inlineStr">
         <is>
           <t>4341279371</t>
         </is>
       </c>
-      <c r="B99" s="37" t="inlineStr">
+      <c r="B99" s="38" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6814,12 +6820,12 @@
           <t>Robotics - Software Development Engineer Intern/Co-op - 2026</t>
         </is>
       </c>
-      <c r="D99" s="37" t="inlineStr">
+      <c r="D99" s="38" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E99" s="37" t="inlineStr">
+      <c r="E99" s="38" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6834,12 +6840,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H99" s="37" t="inlineStr">
+      <c r="H99" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I99" s="37" t="inlineStr">
+      <c r="I99" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6854,20 +6860,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L99" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M99" s="37" t="inlineStr"/>
+      <c r="L99" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M99" s="38" t="inlineStr"/>
     </row>
     <row r="100" ht="18" customHeight="1">
-      <c r="A100" s="36" t="inlineStr">
+      <c r="A100" s="39" t="inlineStr">
         <is>
           <t>4417646890</t>
         </is>
       </c>
-      <c r="B100" s="36" t="inlineStr">
+      <c r="B100" s="39" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6877,12 +6883,12 @@
           <t>Software Engineer II</t>
         </is>
       </c>
-      <c r="D100" s="36" t="inlineStr">
+      <c r="D100" s="39" t="inlineStr">
         <is>
           <t>Compass</t>
         </is>
       </c>
-      <c r="E100" s="36" t="inlineStr">
+      <c r="E100" s="39" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6897,12 +6903,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H100" s="36" t="inlineStr">
+      <c r="H100" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I100" s="36" t="inlineStr">
+      <c r="I100" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6917,20 +6923,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L100" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M100" s="36" t="inlineStr"/>
+      <c r="L100" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M100" s="39" t="inlineStr"/>
     </row>
     <row r="101" ht="18" customHeight="1">
-      <c r="A101" s="37" t="inlineStr">
+      <c r="A101" s="38" t="inlineStr">
         <is>
           <t>4417565729</t>
         </is>
       </c>
-      <c r="B101" s="37" t="inlineStr">
+      <c r="B101" s="38" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -6940,12 +6946,12 @@
           <t>software engineer- ST, Seattle, WA</t>
         </is>
       </c>
-      <c r="D101" s="37" t="inlineStr">
+      <c r="D101" s="38" t="inlineStr">
         <is>
           <t>Starbucks</t>
         </is>
       </c>
-      <c r="E101" s="37" t="inlineStr">
+      <c r="E101" s="38" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -6960,12 +6966,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H101" s="37" t="inlineStr">
+      <c r="H101" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I101" s="37" t="inlineStr">
+      <c r="I101" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -6980,20 +6986,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L101" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M101" s="37" t="inlineStr"/>
+      <c r="L101" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M101" s="38" t="inlineStr"/>
     </row>
     <row r="102" ht="18" customHeight="1">
-      <c r="A102" s="36" t="inlineStr">
+      <c r="A102" s="39" t="inlineStr">
         <is>
           <t>4420492781</t>
         </is>
       </c>
-      <c r="B102" s="36" t="inlineStr">
+      <c r="B102" s="39" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -7003,12 +7009,12 @@
           <t>Software Engineer (Starlink Mobile)</t>
         </is>
       </c>
-      <c r="D102" s="36" t="inlineStr">
+      <c r="D102" s="39" t="inlineStr">
         <is>
           <t>SpaceX</t>
         </is>
       </c>
-      <c r="E102" s="36" t="inlineStr">
+      <c r="E102" s="39" t="inlineStr">
         <is>
           <t>Redmond, WA</t>
         </is>
@@ -7023,12 +7029,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H102" s="36" t="inlineStr">
+      <c r="H102" s="39" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="I102" s="36" t="inlineStr">
+      <c r="I102" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7043,20 +7049,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L102" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M102" s="36" t="inlineStr"/>
+      <c r="L102" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M102" s="39" t="inlineStr"/>
     </row>
     <row r="103" ht="18" customHeight="1">
-      <c r="A103" s="37" t="inlineStr">
+      <c r="A103" s="38" t="inlineStr">
         <is>
           <t>4418203886</t>
         </is>
       </c>
-      <c r="B103" s="37" t="inlineStr">
+      <c r="B103" s="38" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -7066,12 +7072,12 @@
           <t>System Software Engineer - Performance</t>
         </is>
       </c>
-      <c r="D103" s="37" t="inlineStr">
+      <c r="D103" s="38" t="inlineStr">
         <is>
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="E103" s="37" t="inlineStr">
+      <c r="E103" s="38" t="inlineStr">
         <is>
           <t>Redmond, WA</t>
         </is>
@@ -7086,12 +7092,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H103" s="37" t="inlineStr">
+      <c r="H103" s="38" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
-      <c r="I103" s="37" t="inlineStr">
+      <c r="I103" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7106,20 +7112,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L103" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M103" s="37" t="inlineStr"/>
+      <c r="L103" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M103" s="38" t="inlineStr"/>
     </row>
     <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="36" t="inlineStr">
+      <c r="A104" s="39" t="inlineStr">
         <is>
           <t>4332886298</t>
         </is>
       </c>
-      <c r="B104" s="36" t="inlineStr">
+      <c r="B104" s="39" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -7129,12 +7135,12 @@
           <t>Software Engineer - AI Travel Agent</t>
         </is>
       </c>
-      <c r="D104" s="36" t="inlineStr">
+      <c r="D104" s="39" t="inlineStr">
         <is>
           <t>Axel</t>
         </is>
       </c>
-      <c r="E104" s="36" t="inlineStr">
+      <c r="E104" s="39" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -7149,12 +7155,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H104" s="36" t="inlineStr">
+      <c r="H104" s="39" t="inlineStr">
         <is>
           <t>163</t>
         </is>
       </c>
-      <c r="I104" s="36" t="inlineStr">
+      <c r="I104" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7169,20 +7175,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L104" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M104" s="36" t="inlineStr"/>
+      <c r="L104" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M104" s="39" t="inlineStr"/>
     </row>
     <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="37" t="inlineStr">
+      <c r="A105" s="38" t="inlineStr">
         <is>
           <t>4388596468</t>
         </is>
       </c>
-      <c r="B105" s="37" t="inlineStr">
+      <c r="B105" s="38" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -7192,12 +7198,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D105" s="37" t="inlineStr">
+      <c r="D105" s="38" t="inlineStr">
         <is>
           <t>Capgemini</t>
         </is>
       </c>
-      <c r="E105" s="37" t="inlineStr">
+      <c r="E105" s="38" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -7212,12 +7218,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H105" s="37" t="inlineStr">
+      <c r="H105" s="38" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="I105" s="37" t="inlineStr">
+      <c r="I105" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7232,20 +7238,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L105" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M105" s="37" t="inlineStr"/>
+      <c r="L105" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M105" s="38" t="inlineStr"/>
     </row>
     <row r="106" ht="18" customHeight="1">
-      <c r="A106" s="36" t="inlineStr">
+      <c r="A106" s="39" t="inlineStr">
         <is>
           <t>4419517103</t>
         </is>
       </c>
-      <c r="B106" s="36" t="inlineStr">
+      <c r="B106" s="39" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -7255,12 +7261,12 @@
           <t>Software Engineer II</t>
         </is>
       </c>
-      <c r="D106" s="36" t="inlineStr">
+      <c r="D106" s="39" t="inlineStr">
         <is>
           <t>Chewy</t>
         </is>
       </c>
-      <c r="E106" s="36" t="inlineStr">
+      <c r="E106" s="39" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -7275,12 +7281,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H106" s="36" t="inlineStr">
+      <c r="H106" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I106" s="36" t="inlineStr">
+      <c r="I106" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7295,20 +7301,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L106" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M106" s="36" t="inlineStr"/>
+      <c r="L106" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M106" s="39" t="inlineStr"/>
     </row>
     <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="37" t="inlineStr">
+      <c r="A107" s="38" t="inlineStr">
         <is>
           <t>4395225418</t>
         </is>
       </c>
-      <c r="B107" s="37" t="inlineStr">
+      <c r="B107" s="38" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -7318,12 +7324,12 @@
           <t>Software Engineer - Backend</t>
         </is>
       </c>
-      <c r="D107" s="37" t="inlineStr">
+      <c r="D107" s="38" t="inlineStr">
         <is>
           <t>MotherDuck</t>
         </is>
       </c>
-      <c r="E107" s="37" t="inlineStr">
+      <c r="E107" s="38" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -7338,12 +7344,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H107" s="37" t="inlineStr">
+      <c r="H107" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I107" s="37" t="inlineStr">
+      <c r="I107" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7358,20 +7364,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L107" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M107" s="37" t="inlineStr"/>
+      <c r="L107" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M107" s="38" t="inlineStr"/>
     </row>
     <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="36" t="inlineStr">
+      <c r="A108" s="39" t="inlineStr">
         <is>
           <t>4417163235</t>
         </is>
       </c>
-      <c r="B108" s="36" t="inlineStr">
+      <c r="B108" s="39" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
@@ -7381,12 +7387,12 @@
           <t>Software Engineer, Cloud SDK</t>
         </is>
       </c>
-      <c r="D108" s="36" t="inlineStr">
+      <c r="D108" s="39" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="E108" s="36" t="inlineStr">
+      <c r="E108" s="39" t="inlineStr">
         <is>
           <t>Kirkland, WA</t>
         </is>
@@ -7401,12 +7407,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H108" s="36" t="inlineStr">
+      <c r="H108" s="39" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="I108" s="36" t="inlineStr">
+      <c r="I108" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7421,20 +7427,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L108" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M108" s="36" t="inlineStr"/>
+      <c r="L108" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M108" s="39" t="inlineStr"/>
     </row>
     <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="37" t="inlineStr">
+      <c r="A109" s="38" t="inlineStr">
         <is>
           <t>4412210123</t>
         </is>
       </c>
-      <c r="B109" s="37" t="inlineStr">
+      <c r="B109" s="38" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7444,12 +7450,12 @@
           <t>Summer Intern - Software Engineer</t>
         </is>
       </c>
-      <c r="D109" s="37" t="inlineStr">
+      <c r="D109" s="38" t="inlineStr">
         <is>
           <t>Allegion (Southeast Asia) Pte. Ltd.</t>
         </is>
       </c>
-      <c r="E109" s="37" t="inlineStr">
+      <c r="E109" s="38" t="inlineStr">
         <is>
           <t>Carmel, IN</t>
         </is>
@@ -7464,12 +7470,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H109" s="37" t="inlineStr">
+      <c r="H109" s="38" t="inlineStr">
         <is>
           <t>146</t>
         </is>
       </c>
-      <c r="I109" s="37" t="inlineStr">
+      <c r="I109" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7484,20 +7490,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L109" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M109" s="37" t="inlineStr"/>
+      <c r="L109" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M109" s="38" t="inlineStr"/>
     </row>
     <row r="110" ht="18" customHeight="1">
-      <c r="A110" s="36" t="inlineStr">
+      <c r="A110" s="39" t="inlineStr">
         <is>
           <t>4414924766</t>
         </is>
       </c>
-      <c r="B110" s="36" t="inlineStr">
+      <c r="B110" s="39" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7507,12 +7513,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D110" s="36" t="inlineStr">
+      <c r="D110" s="39" t="inlineStr">
         <is>
           <t>Uneek Global</t>
         </is>
       </c>
-      <c r="E110" s="36" t="inlineStr">
+      <c r="E110" s="39" t="inlineStr">
         <is>
           <t>Texas, United States</t>
         </is>
@@ -7527,12 +7533,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H110" s="36" t="inlineStr">
+      <c r="H110" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I110" s="36" t="inlineStr">
+      <c r="I110" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7547,20 +7553,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L110" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M110" s="36" t="inlineStr"/>
+      <c r="L110" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M110" s="39" t="inlineStr"/>
     </row>
     <row r="111" ht="18" customHeight="1">
-      <c r="A111" s="37" t="inlineStr">
+      <c r="A111" s="38" t="inlineStr">
         <is>
           <t>4411278313</t>
         </is>
       </c>
-      <c r="B111" s="37" t="inlineStr">
+      <c r="B111" s="38" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7570,12 +7576,12 @@
           <t>Junior Software Engineer (.NET)</t>
         </is>
       </c>
-      <c r="D111" s="37" t="inlineStr">
+      <c r="D111" s="38" t="inlineStr">
         <is>
           <t>Quintrix, by Mindlance</t>
         </is>
       </c>
-      <c r="E111" s="37" t="inlineStr">
+      <c r="E111" s="38" t="inlineStr">
         <is>
           <t>Austin, Texas Metropolitan Area</t>
         </is>
@@ -7590,12 +7596,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H111" s="37" t="inlineStr">
+      <c r="H111" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I111" s="37" t="inlineStr">
+      <c r="I111" s="38" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
@@ -7610,20 +7616,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L111" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M111" s="37" t="inlineStr"/>
+      <c r="L111" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M111" s="38" t="inlineStr"/>
     </row>
     <row r="112" ht="18" customHeight="1">
-      <c r="A112" s="36" t="inlineStr">
+      <c r="A112" s="39" t="inlineStr">
         <is>
           <t>4340327286</t>
         </is>
       </c>
-      <c r="B112" s="36" t="inlineStr">
+      <c r="B112" s="39" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7633,12 +7639,12 @@
           <t>IT Services - SOFTWARE DEVELOPERS</t>
         </is>
       </c>
-      <c r="D112" s="36" t="inlineStr">
+      <c r="D112" s="39" t="inlineStr">
         <is>
           <t>Fuge Technologies Inc</t>
         </is>
       </c>
-      <c r="E112" s="36" t="inlineStr">
+      <c r="E112" s="39" t="inlineStr">
         <is>
           <t>Irving, TX</t>
         </is>
@@ -7653,12 +7659,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H112" s="36" t="inlineStr">
+      <c r="H112" s="39" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="I112" s="36" t="inlineStr">
+      <c r="I112" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7673,20 +7679,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L112" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M112" s="36" t="inlineStr"/>
+      <c r="L112" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M112" s="39" t="inlineStr"/>
     </row>
     <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="37" t="inlineStr">
+      <c r="A113" s="38" t="inlineStr">
         <is>
           <t>4243859384</t>
         </is>
       </c>
-      <c r="B113" s="37" t="inlineStr">
+      <c r="B113" s="38" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7696,12 +7702,12 @@
           <t>Test analyst</t>
         </is>
       </c>
-      <c r="D113" s="37" t="inlineStr">
+      <c r="D113" s="38" t="inlineStr">
         <is>
           <t>ADP WFN Test Company 3</t>
         </is>
       </c>
-      <c r="E113" s="37" t="inlineStr">
+      <c r="E113" s="38" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
@@ -7716,12 +7722,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H113" s="37" t="inlineStr">
+      <c r="H113" s="38" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="I113" s="37" t="inlineStr">
+      <c r="I113" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7736,20 +7742,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L113" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M113" s="37" t="inlineStr"/>
+      <c r="L113" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M113" s="38" t="inlineStr"/>
     </row>
     <row r="114" ht="18" customHeight="1">
-      <c r="A114" s="36" t="inlineStr">
+      <c r="A114" s="39" t="inlineStr">
         <is>
           <t>4407894427</t>
         </is>
       </c>
-      <c r="B114" s="36" t="inlineStr">
+      <c r="B114" s="39" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7759,12 +7765,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D114" s="36" t="inlineStr">
+      <c r="D114" s="39" t="inlineStr">
         <is>
           <t>Meriplex</t>
         </is>
       </c>
-      <c r="E114" s="36" t="inlineStr">
+      <c r="E114" s="39" t="inlineStr">
         <is>
           <t>Houston, TX</t>
         </is>
@@ -7779,12 +7785,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H114" s="36" t="inlineStr">
+      <c r="H114" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I114" s="36" t="inlineStr">
+      <c r="I114" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7799,20 +7805,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L114" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M114" s="36" t="inlineStr"/>
+      <c r="L114" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M114" s="39" t="inlineStr"/>
     </row>
     <row r="115" ht="18" customHeight="1">
-      <c r="A115" s="37" t="inlineStr">
+      <c r="A115" s="38" t="inlineStr">
         <is>
           <t>4414252424</t>
         </is>
       </c>
-      <c r="B115" s="37" t="inlineStr">
+      <c r="B115" s="38" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7822,12 +7828,12 @@
           <t>Junior Developer</t>
         </is>
       </c>
-      <c r="D115" s="37" t="inlineStr">
+      <c r="D115" s="38" t="inlineStr">
         <is>
           <t>Joyce Meyer Ministries</t>
         </is>
       </c>
-      <c r="E115" s="37" t="inlineStr">
+      <c r="E115" s="38" t="inlineStr">
         <is>
           <t>Fenton, MO</t>
         </is>
@@ -7842,12 +7848,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H115" s="37" t="inlineStr">
+      <c r="H115" s="38" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="I115" s="37" t="inlineStr">
+      <c r="I115" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7862,20 +7868,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L115" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M115" s="37" t="inlineStr"/>
+      <c r="L115" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M115" s="38" t="inlineStr"/>
     </row>
     <row r="116" ht="18" customHeight="1">
-      <c r="A116" s="36" t="inlineStr">
+      <c r="A116" s="39" t="inlineStr">
         <is>
           <t>4401782778</t>
         </is>
       </c>
-      <c r="B116" s="36" t="inlineStr">
+      <c r="B116" s="39" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7885,12 +7891,12 @@
           <t>Junior Full-Stack Software Developer</t>
         </is>
       </c>
-      <c r="D116" s="36" t="inlineStr">
+      <c r="D116" s="39" t="inlineStr">
         <is>
           <t>Visionist, Inc.</t>
         </is>
       </c>
-      <c r="E116" s="36" t="inlineStr">
+      <c r="E116" s="39" t="inlineStr">
         <is>
           <t>Columbia, MD</t>
         </is>
@@ -7905,12 +7911,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H116" s="36" t="inlineStr">
+      <c r="H116" s="39" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="I116" s="36" t="inlineStr">
+      <c r="I116" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -7925,20 +7931,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L116" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M116" s="36" t="inlineStr"/>
+      <c r="L116" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M116" s="39" t="inlineStr"/>
     </row>
     <row r="117" ht="18" customHeight="1">
-      <c r="A117" s="37" t="inlineStr">
+      <c r="A117" s="38" t="inlineStr">
         <is>
           <t>4411523361</t>
         </is>
       </c>
-      <c r="B117" s="37" t="inlineStr">
+      <c r="B117" s="38" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -7948,12 +7954,12 @@
           <t>Junior Application Developer</t>
         </is>
       </c>
-      <c r="D117" s="37" t="inlineStr">
+      <c r="D117" s="38" t="inlineStr">
         <is>
           <t>HCL Global Systems Inc</t>
         </is>
       </c>
-      <c r="E117" s="37" t="inlineStr">
+      <c r="E117" s="38" t="inlineStr">
         <is>
           <t>Georgia, United States</t>
         </is>
@@ -7968,12 +7974,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H117" s="37" t="inlineStr">
+      <c r="H117" s="38" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="I117" s="37" t="inlineStr">
+      <c r="I117" s="38" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
@@ -7988,20 +7994,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L117" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M117" s="37" t="inlineStr"/>
+      <c r="L117" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M117" s="38" t="inlineStr"/>
     </row>
     <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="36" t="inlineStr">
+      <c r="A118" s="39" t="inlineStr">
         <is>
           <t>4261490006</t>
         </is>
       </c>
-      <c r="B118" s="36" t="inlineStr">
+      <c r="B118" s="39" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -8011,12 +8017,12 @@
           <t>**</t>
         </is>
       </c>
-      <c r="D118" s="36" t="inlineStr">
+      <c r="D118" s="39" t="inlineStr">
         <is>
           <t>ADP WFN Test Company 3</t>
         </is>
       </c>
-      <c r="E118" s="36" t="inlineStr">
+      <c r="E118" s="39" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
@@ -8031,12 +8037,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H118" s="36" t="inlineStr">
+      <c r="H118" s="39" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I118" s="36" t="inlineStr">
+      <c r="I118" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8051,20 +8057,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L118" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M118" s="36" t="inlineStr"/>
+      <c r="L118" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M118" s="39" t="inlineStr"/>
     </row>
     <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="37" t="inlineStr">
+      <c r="A119" s="38" t="inlineStr">
         <is>
           <t>4422878758</t>
         </is>
       </c>
-      <c r="B119" s="37" t="inlineStr">
+      <c r="B119" s="38" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -8074,12 +8080,12 @@
           <t>Junior Software Engineer</t>
         </is>
       </c>
-      <c r="D119" s="37" t="inlineStr">
+      <c r="D119" s="38" t="inlineStr">
         <is>
           <t>Brooksource</t>
         </is>
       </c>
-      <c r="E119" s="37" t="inlineStr">
+      <c r="E119" s="38" t="inlineStr">
         <is>
           <t>Lansing, MI</t>
         </is>
@@ -8094,12 +8100,12 @@
           <t>Very Low</t>
         </is>
       </c>
-      <c r="H119" s="37" t="inlineStr">
+      <c r="H119" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I119" s="37" t="inlineStr">
+      <c r="I119" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8114,20 +8120,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L119" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M119" s="37" t="inlineStr"/>
+      <c r="L119" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M119" s="38" t="inlineStr"/>
     </row>
     <row r="120" ht="18" customHeight="1">
-      <c r="A120" s="36" t="inlineStr">
+      <c r="A120" s="39" t="inlineStr">
         <is>
           <t>4419071723</t>
         </is>
       </c>
-      <c r="B120" s="36" t="inlineStr">
+      <c r="B120" s="39" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -8137,12 +8143,12 @@
           <t>Junior Software Developer</t>
         </is>
       </c>
-      <c r="D120" s="36" t="inlineStr">
+      <c r="D120" s="39" t="inlineStr">
         <is>
           <t>IPTA</t>
         </is>
       </c>
-      <c r="E120" s="36" t="inlineStr">
+      <c r="E120" s="39" t="inlineStr">
         <is>
           <t>Layton, UT</t>
         </is>
@@ -8157,12 +8163,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H120" s="36" t="inlineStr">
+      <c r="H120" s="39" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="I120" s="36" t="inlineStr">
+      <c r="I120" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8177,20 +8183,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L120" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M120" s="36" t="inlineStr"/>
+      <c r="L120" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M120" s="39" t="inlineStr"/>
     </row>
     <row r="121" ht="18" customHeight="1">
-      <c r="A121" s="37" t="inlineStr">
+      <c r="A121" s="38" t="inlineStr">
         <is>
           <t>4420988356</t>
         </is>
       </c>
-      <c r="B121" s="37" t="inlineStr">
+      <c r="B121" s="38" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -8200,12 +8206,12 @@
           <t>Junior Software Engineer</t>
         </is>
       </c>
-      <c r="D121" s="37" t="inlineStr">
+      <c r="D121" s="38" t="inlineStr">
         <is>
           <t>Switchboard</t>
         </is>
       </c>
-      <c r="E121" s="37" t="inlineStr">
+      <c r="E121" s="38" t="inlineStr">
         <is>
           <t>New York, NY</t>
         </is>
@@ -8220,12 +8226,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H121" s="37" t="inlineStr">
+      <c r="H121" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I121" s="37" t="inlineStr">
+      <c r="I121" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8240,20 +8246,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L121" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M121" s="37" t="inlineStr"/>
+      <c r="L121" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M121" s="38" t="inlineStr"/>
     </row>
     <row r="122" ht="18" customHeight="1">
-      <c r="A122" s="36" t="inlineStr">
+      <c r="A122" s="39" t="inlineStr">
         <is>
           <t>4419072850</t>
         </is>
       </c>
-      <c r="B122" s="36" t="inlineStr">
+      <c r="B122" s="39" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -8263,12 +8269,12 @@
           <t>junior software engineer analyst</t>
         </is>
       </c>
-      <c r="D122" s="36" t="inlineStr">
+      <c r="D122" s="39" t="inlineStr">
         <is>
           <t>Altamira Technologies Corporation</t>
         </is>
       </c>
-      <c r="E122" s="36" t="inlineStr">
+      <c r="E122" s="39" t="inlineStr">
         <is>
           <t>State College, PA</t>
         </is>
@@ -8283,12 +8289,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H122" s="36" t="inlineStr">
+      <c r="H122" s="39" t="inlineStr">
         <is>
           <t>137</t>
         </is>
       </c>
-      <c r="I122" s="36" t="inlineStr">
+      <c r="I122" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8303,20 +8309,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L122" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M122" s="36" t="inlineStr"/>
+      <c r="L122" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M122" s="39" t="inlineStr"/>
     </row>
     <row r="123" ht="18" customHeight="1">
-      <c r="A123" s="37" t="inlineStr">
+      <c r="A123" s="38" t="inlineStr">
         <is>
           <t>4406854247</t>
         </is>
       </c>
-      <c r="B123" s="37" t="inlineStr">
+      <c r="B123" s="38" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -8326,12 +8332,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D123" s="37" t="inlineStr">
+      <c r="D123" s="38" t="inlineStr">
         <is>
           <t>The Anywhere Company</t>
         </is>
       </c>
-      <c r="E123" s="37" t="inlineStr">
+      <c r="E123" s="38" t="inlineStr">
         <is>
           <t>Hilton Head Island, SC</t>
         </is>
@@ -8346,12 +8352,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H123" s="37" t="inlineStr">
+      <c r="H123" s="38" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I123" s="37" t="inlineStr">
+      <c r="I123" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8366,20 +8372,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L123" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M123" s="37" t="inlineStr"/>
+      <c r="L123" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M123" s="38" t="inlineStr"/>
     </row>
     <row r="124" ht="18" customHeight="1">
-      <c r="A124" s="36" t="inlineStr">
+      <c r="A124" s="39" t="inlineStr">
         <is>
           <t>4394719485</t>
         </is>
       </c>
-      <c r="B124" s="36" t="inlineStr">
+      <c r="B124" s="39" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -8389,12 +8395,12 @@
           <t>Software Developer I, II (Days 8am to 5pm) *On-Site Victor, NY*</t>
         </is>
       </c>
-      <c r="D124" s="36" t="inlineStr">
+      <c r="D124" s="39" t="inlineStr">
         <is>
           <t>LSI SOLUTIONS®</t>
         </is>
       </c>
-      <c r="E124" s="36" t="inlineStr">
+      <c r="E124" s="39" t="inlineStr">
         <is>
           <t>Victor, NY</t>
         </is>
@@ -8409,12 +8415,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H124" s="36" t="inlineStr">
+      <c r="H124" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I124" s="36" t="inlineStr">
+      <c r="I124" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8429,20 +8435,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L124" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M124" s="36" t="inlineStr"/>
+      <c r="L124" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M124" s="39" t="inlineStr"/>
     </row>
     <row r="125" ht="18" customHeight="1">
-      <c r="A125" s="37" t="inlineStr">
+      <c r="A125" s="38" t="inlineStr">
         <is>
           <t>4367493426</t>
         </is>
       </c>
-      <c r="B125" s="37" t="inlineStr">
+      <c r="B125" s="38" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -8452,12 +8458,12 @@
           <t>Junior Software Developer</t>
         </is>
       </c>
-      <c r="D125" s="37" t="inlineStr">
+      <c r="D125" s="38" t="inlineStr">
         <is>
           <t>KIHOMAC</t>
         </is>
       </c>
-      <c r="E125" s="37" t="inlineStr">
+      <c r="E125" s="38" t="inlineStr">
         <is>
           <t>Colorado Springs, CO</t>
         </is>
@@ -8472,12 +8478,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H125" s="37" t="inlineStr">
+      <c r="H125" s="38" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="I125" s="37" t="inlineStr">
+      <c r="I125" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8492,20 +8498,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L125" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M125" s="37" t="inlineStr"/>
+      <c r="L125" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M125" s="38" t="inlineStr"/>
     </row>
     <row r="126" ht="18" customHeight="1">
-      <c r="A126" s="36" t="inlineStr">
+      <c r="A126" s="39" t="inlineStr">
         <is>
           <t>4304448690</t>
         </is>
       </c>
-      <c r="B126" s="36" t="inlineStr">
+      <c r="B126" s="39" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
@@ -8515,12 +8521,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D126" s="36" t="inlineStr">
+      <c r="D126" s="39" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E126" s="36" t="inlineStr">
+      <c r="E126" s="39" t="inlineStr">
         <is>
           <t>Pennsylvania, United States</t>
         </is>
@@ -8535,12 +8541,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H126" s="36" t="inlineStr">
+      <c r="H126" s="39" t="inlineStr">
         <is>
           <t>151</t>
         </is>
       </c>
-      <c r="I126" s="36" t="inlineStr">
+      <c r="I126" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8555,20 +8561,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L126" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M126" s="36" t="inlineStr"/>
+      <c r="L126" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M126" s="39" t="inlineStr"/>
     </row>
     <row r="127" ht="18" customHeight="1">
-      <c r="A127" s="37" t="inlineStr">
+      <c r="A127" s="38" t="inlineStr">
         <is>
           <t>4305126185</t>
         </is>
       </c>
-      <c r="B127" s="37" t="inlineStr">
+      <c r="B127" s="38" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
@@ -8578,12 +8584,12 @@
           <t>Software Engineer Intern (Payment Network) - Global Payment - 2026 Summer(BS/MS)</t>
         </is>
       </c>
-      <c r="D127" s="37" t="inlineStr">
+      <c r="D127" s="38" t="inlineStr">
         <is>
           <t>ByteDance</t>
         </is>
       </c>
-      <c r="E127" s="37" t="inlineStr">
+      <c r="E127" s="38" t="inlineStr">
         <is>
           <t>Seattle, WA</t>
         </is>
@@ -8598,12 +8604,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H127" s="37" t="inlineStr">
+      <c r="H127" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I127" s="37" t="inlineStr">
+      <c r="I127" s="38" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -8618,20 +8624,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L127" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M127" s="37" t="inlineStr"/>
+      <c r="L127" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M127" s="38" t="inlineStr"/>
     </row>
     <row r="128" ht="18" customHeight="1">
-      <c r="A128" s="36" t="inlineStr">
+      <c r="A128" s="39" t="inlineStr">
         <is>
           <t>4418276914</t>
         </is>
       </c>
-      <c r="B128" s="36" t="inlineStr">
+      <c r="B128" s="39" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
@@ -8641,12 +8647,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D128" s="36" t="inlineStr">
+      <c r="D128" s="39" t="inlineStr">
         <is>
           <t>fieldd</t>
         </is>
       </c>
-      <c r="E128" s="36" t="inlineStr">
+      <c r="E128" s="39" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -8661,12 +8667,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H128" s="36" t="inlineStr">
+      <c r="H128" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I128" s="36" t="inlineStr">
+      <c r="I128" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8681,20 +8687,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L128" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M128" s="36" t="inlineStr"/>
+      <c r="L128" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M128" s="39" t="inlineStr"/>
     </row>
     <row r="129" ht="18" customHeight="1">
-      <c r="A129" s="37" t="inlineStr">
+      <c r="A129" s="38" t="inlineStr">
         <is>
           <t>4420219582</t>
         </is>
       </c>
-      <c r="B129" s="37" t="inlineStr">
+      <c r="B129" s="38" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
@@ -8704,12 +8710,12 @@
           <t>Internship, Software Engineer, Information Security (Fall 2026)</t>
         </is>
       </c>
-      <c r="D129" s="37" t="inlineStr">
+      <c r="D129" s="38" t="inlineStr">
         <is>
           <t>Tesla</t>
         </is>
       </c>
-      <c r="E129" s="37" t="inlineStr">
+      <c r="E129" s="38" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
@@ -8724,12 +8730,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H129" s="37" t="inlineStr">
+      <c r="H129" s="38" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="I129" s="37" t="inlineStr">
+      <c r="I129" s="38" t="inlineStr">
         <is>
           <t>Internship</t>
         </is>
@@ -8744,20 +8750,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L129" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M129" s="37" t="inlineStr"/>
+      <c r="L129" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M129" s="38" t="inlineStr"/>
     </row>
     <row r="130" ht="18" customHeight="1">
-      <c r="A130" s="36" t="inlineStr">
+      <c r="A130" s="39" t="inlineStr">
         <is>
           <t>4413774877</t>
         </is>
       </c>
-      <c r="B130" s="36" t="inlineStr">
+      <c r="B130" s="39" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
@@ -8767,12 +8773,12 @@
           <t>Network Engineering Intern (Summer 2026)</t>
         </is>
       </c>
-      <c r="D130" s="36" t="inlineStr">
+      <c r="D130" s="39" t="inlineStr">
         <is>
           <t>Cloudflare Area 1 Security</t>
         </is>
       </c>
-      <c r="E130" s="36" t="inlineStr">
+      <c r="E130" s="39" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -8787,12 +8793,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H130" s="36" t="inlineStr">
+      <c r="H130" s="39" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="I130" s="36" t="inlineStr">
+      <c r="I130" s="39" t="inlineStr">
         <is>
           <t>Volunteer</t>
         </is>
@@ -8807,20 +8813,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L130" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M130" s="36" t="inlineStr"/>
+      <c r="L130" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M130" s="39" t="inlineStr"/>
     </row>
     <row r="131" ht="18" customHeight="1">
-      <c r="A131" s="37" t="inlineStr">
+      <c r="A131" s="38" t="inlineStr">
         <is>
           <t>4415577033</t>
         </is>
       </c>
-      <c r="B131" s="37" t="inlineStr">
+      <c r="B131" s="38" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
@@ -8830,12 +8836,12 @@
           <t>Summer Intern - Software Engineer</t>
         </is>
       </c>
-      <c r="D131" s="37" t="inlineStr">
+      <c r="D131" s="38" t="inlineStr">
         <is>
           <t>Allegion</t>
         </is>
       </c>
-      <c r="E131" s="37" t="inlineStr">
+      <c r="E131" s="38" t="inlineStr">
         <is>
           <t>Carmel, IN</t>
         </is>
@@ -8850,12 +8856,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H131" s="37" t="inlineStr">
+      <c r="H131" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I131" s="37" t="inlineStr">
+      <c r="I131" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8870,20 +8876,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L131" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M131" s="37" t="inlineStr"/>
+      <c r="L131" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M131" s="38" t="inlineStr"/>
     </row>
     <row r="132" ht="18" customHeight="1">
-      <c r="A132" s="36" t="inlineStr">
+      <c r="A132" s="39" t="inlineStr">
         <is>
           <t>4407221528</t>
         </is>
       </c>
-      <c r="B132" s="36" t="inlineStr">
+      <c r="B132" s="39" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
@@ -8893,12 +8899,12 @@
           <t>Full Stack Engineer</t>
         </is>
       </c>
-      <c r="D132" s="36" t="inlineStr">
+      <c r="D132" s="39" t="inlineStr">
         <is>
           <t>Saronic Technologies</t>
         </is>
       </c>
-      <c r="E132" s="36" t="inlineStr">
+      <c r="E132" s="39" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -8913,12 +8919,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H132" s="36" t="inlineStr">
+      <c r="H132" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I132" s="36" t="inlineStr">
+      <c r="I132" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8933,20 +8939,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L132" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M132" s="36" t="inlineStr"/>
+      <c r="L132" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M132" s="39" t="inlineStr"/>
     </row>
     <row r="133" ht="18" customHeight="1">
-      <c r="A133" s="37" t="inlineStr">
+      <c r="A133" s="38" t="inlineStr">
         <is>
           <t>4413657345</t>
         </is>
       </c>
-      <c r="B133" s="37" t="inlineStr">
+      <c r="B133" s="38" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
@@ -8956,12 +8962,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D133" s="37" t="inlineStr">
+      <c r="D133" s="38" t="inlineStr">
         <is>
           <t>Streamline Healthcare Solutions</t>
         </is>
       </c>
-      <c r="E133" s="37" t="inlineStr">
+      <c r="E133" s="38" t="inlineStr">
         <is>
           <t>Texas, United States</t>
         </is>
@@ -8976,12 +8982,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H133" s="37" t="inlineStr">
+      <c r="H133" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I133" s="37" t="inlineStr">
+      <c r="I133" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -8996,20 +9002,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L133" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M133" s="37" t="inlineStr"/>
+      <c r="L133" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M133" s="38" t="inlineStr"/>
     </row>
     <row r="134" ht="18" customHeight="1">
-      <c r="A134" s="36" t="inlineStr">
+      <c r="A134" s="39" t="inlineStr">
         <is>
           <t>4390738582</t>
         </is>
       </c>
-      <c r="B134" s="36" t="inlineStr">
+      <c r="B134" s="39" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
@@ -9019,12 +9025,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D134" s="36" t="inlineStr">
+      <c r="D134" s="39" t="inlineStr">
         <is>
           <t>Pushnami</t>
         </is>
       </c>
-      <c r="E134" s="36" t="inlineStr">
+      <c r="E134" s="39" t="inlineStr">
         <is>
           <t>Austin, Texas Metropolitan Area</t>
         </is>
@@ -9039,12 +9045,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H134" s="36" t="inlineStr">
+      <c r="H134" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I134" s="36" t="inlineStr">
+      <c r="I134" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -9059,20 +9065,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L134" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M134" s="36" t="inlineStr"/>
+      <c r="L134" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M134" s="39" t="inlineStr"/>
     </row>
     <row r="135" ht="18" customHeight="1">
-      <c r="A135" s="37" t="inlineStr">
+      <c r="A135" s="38" t="inlineStr">
         <is>
           <t>4304447681</t>
         </is>
       </c>
-      <c r="B135" s="37" t="inlineStr">
+      <c r="B135" s="38" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
@@ -9082,12 +9088,12 @@
           <t>Software Developer</t>
         </is>
       </c>
-      <c r="D135" s="37" t="inlineStr">
+      <c r="D135" s="38" t="inlineStr">
         <is>
           <t>DataAnnotation</t>
         </is>
       </c>
-      <c r="E135" s="37" t="inlineStr">
+      <c r="E135" s="38" t="inlineStr">
         <is>
           <t>Texas, United States</t>
         </is>
@@ -9102,12 +9108,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H135" s="37" t="inlineStr">
+      <c r="H135" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I135" s="37" t="inlineStr">
+      <c r="I135" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -9122,20 +9128,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L135" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M135" s="37" t="inlineStr"/>
+      <c r="L135" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M135" s="38" t="inlineStr"/>
     </row>
     <row r="136" ht="18" customHeight="1">
-      <c r="A136" s="36" t="inlineStr">
+      <c r="A136" s="39" t="inlineStr">
         <is>
           <t>4387731381</t>
         </is>
       </c>
-      <c r="B136" s="36" t="inlineStr">
+      <c r="B136" s="39" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
@@ -9145,12 +9151,12 @@
           <t>Software Development Engineer I</t>
         </is>
       </c>
-      <c r="D136" s="36" t="inlineStr">
+      <c r="D136" s="39" t="inlineStr">
         <is>
           <t>GM Financial</t>
         </is>
       </c>
-      <c r="E136" s="36" t="inlineStr">
+      <c r="E136" s="39" t="inlineStr">
         <is>
           <t>Irving, TX</t>
         </is>
@@ -9165,12 +9171,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H136" s="36" t="inlineStr">
+      <c r="H136" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I136" s="36" t="inlineStr">
+      <c r="I136" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -9185,20 +9191,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L136" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M136" s="36" t="inlineStr"/>
+      <c r="L136" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M136" s="39" t="inlineStr"/>
     </row>
     <row r="137" ht="18" customHeight="1">
-      <c r="A137" s="37" t="inlineStr">
+      <c r="A137" s="38" t="inlineStr">
         <is>
           <t>4420489886</t>
         </is>
       </c>
-      <c r="B137" s="37" t="inlineStr">
+      <c r="B137" s="38" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
@@ -9208,12 +9214,12 @@
           <t>Junior Java full stack developer/Data analyst</t>
         </is>
       </c>
-      <c r="D137" s="37" t="inlineStr">
+      <c r="D137" s="38" t="inlineStr">
         <is>
           <t>SynergisticIT</t>
         </is>
       </c>
-      <c r="E137" s="37" t="inlineStr">
+      <c r="E137" s="38" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -9228,12 +9234,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H137" s="37" t="inlineStr">
+      <c r="H137" s="38" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I137" s="37" t="inlineStr">
+      <c r="I137" s="38" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
@@ -9248,20 +9254,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L137" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M137" s="37" t="inlineStr"/>
+      <c r="L137" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M137" s="38" t="inlineStr"/>
     </row>
     <row r="138" ht="18" customHeight="1">
-      <c r="A138" s="36" t="inlineStr">
+      <c r="A138" s="39" t="inlineStr">
         <is>
           <t>4419113430</t>
         </is>
       </c>
-      <c r="B138" s="36" t="inlineStr">
+      <c r="B138" s="39" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
@@ -9271,12 +9277,12 @@
           <t>Software Engineer, Factory Software</t>
         </is>
       </c>
-      <c r="D138" s="36" t="inlineStr">
+      <c r="D138" s="39" t="inlineStr">
         <is>
           <t>Tesla</t>
         </is>
       </c>
-      <c r="E138" s="36" t="inlineStr">
+      <c r="E138" s="39" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -9291,12 +9297,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H138" s="36" t="inlineStr">
+      <c r="H138" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I138" s="36" t="inlineStr">
+      <c r="I138" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -9311,20 +9317,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L138" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M138" s="36" t="inlineStr"/>
+      <c r="L138" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M138" s="39" t="inlineStr"/>
     </row>
     <row r="139" ht="18" customHeight="1">
-      <c r="A139" s="37" t="inlineStr">
+      <c r="A139" s="38" t="inlineStr">
         <is>
           <t>4358267222</t>
         </is>
       </c>
-      <c r="B139" s="37" t="inlineStr">
+      <c r="B139" s="38" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
@@ -9334,12 +9340,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D139" s="37" t="inlineStr">
+      <c r="D139" s="38" t="inlineStr">
         <is>
           <t>iHeartMedia</t>
         </is>
       </c>
-      <c r="E139" s="37" t="inlineStr">
+      <c r="E139" s="38" t="inlineStr">
         <is>
           <t>San Antonio, TX</t>
         </is>
@@ -9354,12 +9360,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H139" s="37" t="inlineStr">
+      <c r="H139" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I139" s="37" t="inlineStr">
+      <c r="I139" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -9374,20 +9380,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L139" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M139" s="37" t="inlineStr"/>
+      <c r="L139" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M139" s="38" t="inlineStr"/>
     </row>
     <row r="140" ht="18" customHeight="1">
-      <c r="A140" s="36" t="inlineStr">
+      <c r="A140" s="39" t="inlineStr">
         <is>
           <t>4414766348</t>
         </is>
       </c>
-      <c r="B140" s="36" t="inlineStr">
+      <c r="B140" s="39" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
@@ -9397,12 +9403,12 @@
           <t>Intern - Software Engineer Backend - Remote - Nationwide</t>
         </is>
       </c>
-      <c r="D140" s="36" t="inlineStr">
+      <c r="D140" s="39" t="inlineStr">
         <is>
           <t>Vituity</t>
         </is>
       </c>
-      <c r="E140" s="36" t="inlineStr">
+      <c r="E140" s="39" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -9417,12 +9423,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H140" s="36" t="inlineStr">
+      <c r="H140" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I140" s="36" t="inlineStr">
+      <c r="I140" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -9437,20 +9443,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L140" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M140" s="36" t="inlineStr"/>
+      <c r="L140" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M140" s="39" t="inlineStr"/>
     </row>
     <row r="141" ht="18" customHeight="1">
-      <c r="A141" s="37" t="inlineStr">
+      <c r="A141" s="38" t="inlineStr">
         <is>
           <t>4404102169</t>
         </is>
       </c>
-      <c r="B141" s="37" t="inlineStr">
+      <c r="B141" s="38" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
@@ -9460,12 +9466,12 @@
           <t>Software Development Engineer I</t>
         </is>
       </c>
-      <c r="D141" s="37" t="inlineStr">
+      <c r="D141" s="38" t="inlineStr">
         <is>
           <t>GM Financial</t>
         </is>
       </c>
-      <c r="E141" s="37" t="inlineStr">
+      <c r="E141" s="38" t="inlineStr">
         <is>
           <t>Irving, TX</t>
         </is>
@@ -9480,12 +9486,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H141" s="37" t="inlineStr">
+      <c r="H141" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I141" s="37" t="inlineStr">
+      <c r="I141" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -9500,20 +9506,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L141" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M141" s="37" t="inlineStr"/>
+      <c r="L141" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M141" s="38" t="inlineStr"/>
     </row>
     <row r="142" ht="18" customHeight="1">
-      <c r="A142" s="36" t="inlineStr">
+      <c r="A142" s="39" t="inlineStr">
         <is>
           <t>4415891077</t>
         </is>
       </c>
-      <c r="B142" s="36" t="inlineStr">
+      <c r="B142" s="39" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
@@ -9523,12 +9529,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D142" s="36" t="inlineStr">
+      <c r="D142" s="39" t="inlineStr">
         <is>
           <t>Acrisure Innovation</t>
         </is>
       </c>
-      <c r="E142" s="36" t="inlineStr">
+      <c r="E142" s="39" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -9543,12 +9549,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H142" s="36" t="inlineStr">
+      <c r="H142" s="39" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="I142" s="36" t="inlineStr">
+      <c r="I142" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -9563,20 +9569,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L142" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M142" s="36" t="inlineStr"/>
+      <c r="L142" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M142" s="39" t="inlineStr"/>
     </row>
     <row r="143" ht="18" customHeight="1">
-      <c r="A143" s="37" t="inlineStr">
+      <c r="A143" s="38" t="inlineStr">
         <is>
           <t>4422883837</t>
         </is>
       </c>
-      <c r="B143" s="37" t="inlineStr">
+      <c r="B143" s="38" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
@@ -9586,12 +9592,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D143" s="37" t="inlineStr">
+      <c r="D143" s="38" t="inlineStr">
         <is>
           <t>Emonics LLC</t>
         </is>
       </c>
-      <c r="E143" s="37" t="inlineStr">
+      <c r="E143" s="38" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -9606,12 +9612,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H143" s="37" t="inlineStr">
+      <c r="H143" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I143" s="37" t="inlineStr">
+      <c r="I143" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -9626,20 +9632,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L143" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M143" s="37" t="inlineStr"/>
+      <c r="L143" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M143" s="38" t="inlineStr"/>
     </row>
     <row r="144" ht="18" customHeight="1">
-      <c r="A144" s="36" t="inlineStr">
+      <c r="A144" s="39" t="inlineStr">
         <is>
           <t>4313403973</t>
         </is>
       </c>
-      <c r="B144" s="36" t="inlineStr">
+      <c r="B144" s="39" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
@@ -9649,12 +9655,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D144" s="36" t="inlineStr">
+      <c r="D144" s="39" t="inlineStr">
         <is>
           <t>BuildBuddy</t>
         </is>
       </c>
-      <c r="E144" s="36" t="inlineStr">
+      <c r="E144" s="39" t="inlineStr">
         <is>
           <t>San Angelo Area</t>
         </is>
@@ -9669,12 +9675,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="H144" s="36" t="inlineStr">
+      <c r="H144" s="39" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="I144" s="36" t="inlineStr">
+      <c r="I144" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -9689,20 +9695,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L144" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M144" s="36" t="inlineStr"/>
+      <c r="L144" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M144" s="39" t="inlineStr"/>
     </row>
     <row r="145" ht="18" customHeight="1">
-      <c r="A145" s="37" t="inlineStr">
+      <c r="A145" s="38" t="inlineStr">
         <is>
           <t>4414222508</t>
         </is>
       </c>
-      <c r="B145" s="37" t="inlineStr">
+      <c r="B145" s="38" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
@@ -9712,12 +9718,12 @@
           <t>Full Stack Developer</t>
         </is>
       </c>
-      <c r="D145" s="37" t="inlineStr">
+      <c r="D145" s="38" t="inlineStr">
         <is>
           <t>Winaxis LLC</t>
         </is>
       </c>
-      <c r="E145" s="37" t="inlineStr">
+      <c r="E145" s="38" t="inlineStr">
         <is>
           <t>Dallas, TX</t>
         </is>
@@ -9732,12 +9738,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H145" s="37" t="inlineStr">
+      <c r="H145" s="38" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I145" s="37" t="inlineStr">
+      <c r="I145" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -9752,20 +9758,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L145" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M145" s="37" t="inlineStr"/>
+      <c r="L145" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M145" s="38" t="inlineStr"/>
     </row>
     <row r="146" ht="18" customHeight="1">
-      <c r="A146" s="36" t="inlineStr">
+      <c r="A146" s="39" t="inlineStr">
         <is>
           <t>4419658058</t>
         </is>
       </c>
-      <c r="B146" s="36" t="inlineStr">
+      <c r="B146" s="39" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
@@ -9775,12 +9781,12 @@
           <t>Early Career Software Engineer</t>
         </is>
       </c>
-      <c r="D146" s="36" t="inlineStr">
+      <c r="D146" s="39" t="inlineStr">
         <is>
           <t>Gainwell Technologies</t>
         </is>
       </c>
-      <c r="E146" s="36" t="inlineStr">
+      <c r="E146" s="39" t="inlineStr">
         <is>
           <t>Texas, United States</t>
         </is>
@@ -9795,12 +9801,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H146" s="36" t="inlineStr">
+      <c r="H146" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I146" s="36" t="inlineStr">
+      <c r="I146" s="39" t="inlineStr">
         <is>
           <t>Volunteer</t>
         </is>
@@ -9815,20 +9821,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L146" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M146" s="36" t="inlineStr"/>
+      <c r="L146" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M146" s="39" t="inlineStr"/>
     </row>
     <row r="147" ht="18" customHeight="1">
-      <c r="A147" s="37" t="inlineStr">
+      <c r="A147" s="38" t="inlineStr">
         <is>
           <t>4421341648</t>
         </is>
       </c>
-      <c r="B147" s="37" t="inlineStr">
+      <c r="B147" s="38" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
@@ -9838,12 +9844,12 @@
           <t>Entry level full stack developer/Machine learning /AI engineer</t>
         </is>
       </c>
-      <c r="D147" s="37" t="inlineStr">
+      <c r="D147" s="38" t="inlineStr">
         <is>
           <t>SynergisticIT</t>
         </is>
       </c>
-      <c r="E147" s="37" t="inlineStr">
+      <c r="E147" s="38" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -9858,12 +9864,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H147" s="37" t="inlineStr">
+      <c r="H147" s="38" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="I147" s="37" t="inlineStr">
+      <c r="I147" s="38" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
@@ -9878,20 +9884,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L147" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M147" s="37" t="inlineStr"/>
+      <c r="L147" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M147" s="38" t="inlineStr"/>
     </row>
     <row r="148" ht="18" customHeight="1">
-      <c r="A148" s="36" t="inlineStr">
+      <c r="A148" s="39" t="inlineStr">
         <is>
           <t>4413445271</t>
         </is>
       </c>
-      <c r="B148" s="36" t="inlineStr">
+      <c r="B148" s="39" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
@@ -9901,12 +9907,12 @@
           <t>Associate Software Engineer</t>
         </is>
       </c>
-      <c r="D148" s="36" t="inlineStr">
+      <c r="D148" s="39" t="inlineStr">
         <is>
           <t>SquareTrade</t>
         </is>
       </c>
-      <c r="E148" s="36" t="inlineStr">
+      <c r="E148" s="39" t="inlineStr">
         <is>
           <t>Dallas, TX</t>
         </is>
@@ -9921,12 +9927,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H148" s="36" t="inlineStr">
+      <c r="H148" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I148" s="36" t="inlineStr">
+      <c r="I148" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -9941,20 +9947,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L148" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M148" s="36" t="inlineStr"/>
+      <c r="L148" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M148" s="39" t="inlineStr"/>
     </row>
     <row r="149" ht="18" customHeight="1">
-      <c r="A149" s="37" t="inlineStr">
+      <c r="A149" s="38" t="inlineStr">
         <is>
           <t>4418784522</t>
         </is>
       </c>
-      <c r="B149" s="37" t="inlineStr">
+      <c r="B149" s="38" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
@@ -9964,12 +9970,12 @@
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="D149" s="37" t="inlineStr">
+      <c r="D149" s="38" t="inlineStr">
         <is>
           <t>LTM</t>
         </is>
       </c>
-      <c r="E149" s="37" t="inlineStr">
+      <c r="E149" s="38" t="inlineStr">
         <is>
           <t>Greater Houston</t>
         </is>
@@ -9984,12 +9990,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H149" s="37" t="inlineStr">
+      <c r="H149" s="38" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I149" s="37" t="inlineStr">
+      <c r="I149" s="38" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -10004,20 +10010,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L149" s="37" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M149" s="37" t="inlineStr"/>
+      <c r="L149" s="38" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M149" s="38" t="inlineStr"/>
     </row>
     <row r="150" ht="18" customHeight="1">
-      <c r="A150" s="36" t="inlineStr">
+      <c r="A150" s="39" t="inlineStr">
         <is>
           <t>4397591181</t>
         </is>
       </c>
-      <c r="B150" s="36" t="inlineStr">
+      <c r="B150" s="39" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
@@ -10027,12 +10033,12 @@
           <t>Software Engineer - New Grad (Summer 2026)</t>
         </is>
       </c>
-      <c r="D150" s="36" t="inlineStr">
+      <c r="D150" s="39" t="inlineStr">
         <is>
           <t>Nominal</t>
         </is>
       </c>
-      <c r="E150" s="36" t="inlineStr">
+      <c r="E150" s="39" t="inlineStr">
         <is>
           <t>Austin, TX</t>
         </is>
@@ -10047,12 +10053,12 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="H150" s="36" t="inlineStr">
+      <c r="H150" s="39" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I150" s="36" t="inlineStr">
+      <c r="I150" s="39" t="inlineStr">
         <is>
           <t>Full-time</t>
         </is>
@@ -10067,12 +10073,12 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="L150" s="36" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="M150" s="36" t="inlineStr"/>
+      <c r="L150" s="39" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M150" s="39" t="inlineStr"/>
     </row>
     <row r="151" ht="18" customHeight="1">
       <c r="A151" s="38" t="inlineStr">
@@ -10641,8 +10647,323 @@
       </c>
       <c r="M159" s="38" t="inlineStr"/>
     </row>
+    <row r="160" ht="18" customHeight="1">
+      <c r="A160" s="40" t="inlineStr">
+        <is>
+          <t>4424750681</t>
+        </is>
+      </c>
+      <c r="B160" s="40" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D160" s="40" t="inlineStr">
+        <is>
+          <t>MeeBoss</t>
+        </is>
+      </c>
+      <c r="E160" s="40" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F160" s="18" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="G160" s="19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H160" s="40" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="I160" s="40" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, c++, c, data structures, algorithms, Title match: Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="K160" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L160" s="40" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M160" s="40" t="inlineStr"/>
+    </row>
+    <row r="161" ht="18" customHeight="1">
+      <c r="A161" s="41" t="inlineStr">
+        <is>
+          <t>4423332981</t>
+        </is>
+      </c>
+      <c r="B161" s="41" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C161" s="8" t="inlineStr">
+        <is>
+          <t>Junior Full Stack Developer (Python/React.js)</t>
+        </is>
+      </c>
+      <c r="D161" s="41" t="inlineStr">
+        <is>
+          <t>Inadev</t>
+        </is>
+      </c>
+      <c r="E161" s="41" t="inlineStr">
+        <is>
+          <t>Reston, VA</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="G161" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H161" s="41" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="I161" s="41" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J161" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, react, node, aws, mongodb, Title match: Junior Full Stack Developer (Python/React.js)</t>
+        </is>
+      </c>
+      <c r="K161" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L161" s="41" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M161" s="41" t="inlineStr"/>
+    </row>
+    <row r="162" ht="18" customHeight="1">
+      <c r="A162" s="40" t="inlineStr">
+        <is>
+          <t>4420669323</t>
+        </is>
+      </c>
+      <c r="B162" s="40" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>Jr. Java Full stack Developer/AI engineer</t>
+        </is>
+      </c>
+      <c r="D162" s="40" t="inlineStr">
+        <is>
+          <t>SynergisticIT</t>
+        </is>
+      </c>
+      <c r="E162" s="40" t="inlineStr">
+        <is>
+          <t>Dallas, TX</t>
+        </is>
+      </c>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="G162" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H162" s="40" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I162" s="40" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, machine learning, full stack, backend, c, Location: Dallas, TX, Title match: Jr. Java Full stack Developer/AI engineer</t>
+        </is>
+      </c>
+      <c r="K162" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L162" s="40" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M162" s="40" t="inlineStr"/>
+    </row>
+    <row r="163" ht="18" customHeight="1">
+      <c r="A163" s="41" t="inlineStr">
+        <is>
+          <t>4411531916</t>
+        </is>
+      </c>
+      <c r="B163" s="41" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C163" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D163" s="41" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="E163" s="41" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="F163" s="9" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="G163" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H163" s="41" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I163" s="41" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J163" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, react, css, git, sql, Location: Austin, TX, Title match: Software Engineer</t>
+        </is>
+      </c>
+      <c r="K163" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L163" s="41" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M163" s="41" t="inlineStr"/>
+    </row>
+    <row r="164" ht="18" customHeight="1">
+      <c r="A164" s="40" t="inlineStr">
+        <is>
+          <t>4423520762</t>
+        </is>
+      </c>
+      <c r="B164" s="40" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="D164" s="40" t="inlineStr">
+        <is>
+          <t>Loombotic</t>
+        </is>
+      </c>
+      <c r="E164" s="40" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="F164" s="9" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="G164" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H164" s="40" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I164" s="40" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, rest, git, full-stack, c, oop, Location: Austin, TX, Title match: Software Engineer</t>
+        </is>
+      </c>
+      <c r="K164" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L164" s="40" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="M164" s="40" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M159"/>
+  <autoFilter ref="A1:M164"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -10802,6 +11123,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K157" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K158" r:id="rId157"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K164" r:id="rId163"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship Matches" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Internship Matches" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internship Matches'!$A$1:$L$9</definedName>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Internship Matches" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internship Matches'!$A$1:$L$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internship Matches'!$A$1:$L$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -113,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -153,6 +153,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -519,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1062,8 +1068,124 @@
       </c>
       <c r="L9" s="7" t="inlineStr"/>
     </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>gh:togetherai:5157380007</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Frontier Agents Intern (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>Together AI</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>Gh</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, pytorch, nlp, machine learning, deep learning, algorithms, Internship title, Posted &lt;7d ago, Flags: PhD-oriented role</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K10" s="14" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>gh:togetherai:5157559007</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Systems Research Engineer Intern - GPU Programming (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Together AI</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>Gh</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>Skills: algorithms, artificial intelligence, Internship title, Posted &lt;7d ago</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K11" s="15" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L11" s="15" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L9"/>
+  <autoFilter ref="A1:L11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
@@ -1073,6 +1195,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Internship Matches" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internship Matches'!$A$1:$L$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internship Matches'!$A$1:$L$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -113,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -158,6 +158,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -525,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -605,12 +608,12 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>ashby:baseten:58d7d8e6-86ee-43a1-baec-3dddcb661d51</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
@@ -620,12 +623,12 @@
           <t>Base Labs Fellowship</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>Baseten</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>San Francisco (Remote)</t>
         </is>
@@ -640,7 +643,7 @@
           <t>Possible Fit</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="14" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
@@ -655,20 +658,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="14" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="L2" s="14" t="inlineStr"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>ashby:notion:297b4ece-765f-4eea-b1b8-46057cb6501f</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
@@ -678,12 +681,12 @@
           <t>Software Engineer, Early Career</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>Notion</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>San Francisco, California</t>
         </is>
@@ -698,7 +701,7 @@
           <t>Possible Fit</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="15" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
@@ -713,20 +716,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K3" s="7" t="inlineStr">
+      <c r="K3" s="15" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L3" s="7" t="inlineStr"/>
+      <c r="L3" s="15" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>ashby:notion:5b15697c-fa91-4511-9482-c98a6ff29f90</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
@@ -736,12 +739,12 @@
           <t>Software Engineer Intern (Fall 2026)</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>Notion</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>San Francisco, California (Remote)</t>
         </is>
@@ -756,7 +759,7 @@
           <t>Good Fit</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="14" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
@@ -771,20 +774,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="14" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="L4" s="14" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>ashby:notion:7e6dc7fe-7ddd-42c1-8928-13f7bddb9ec9</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
@@ -794,12 +797,12 @@
           <t>Software Engineer, New Grad (AI)</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>Notion</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>San Francisco, California (Remote)</t>
         </is>
@@ -814,7 +817,7 @@
           <t>Possible Fit</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="15" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
@@ -829,20 +832,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="K5" s="15" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr"/>
+      <c r="L5" s="15" t="inlineStr"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>ashby:notion:85947779-6b87-466a-98bc-30a640448c28</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
@@ -852,12 +855,12 @@
           <t>Software Engineer, Early Career (AI)</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>Notion</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>San Francisco, California (Remote)</t>
         </is>
@@ -872,7 +875,7 @@
           <t>Strong Fit</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
@@ -887,20 +890,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="14" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
+      <c r="L6" s="14" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>ashby:notion:a6311f97-4850-4674-a5f3-d9fe5f6f2555</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
@@ -910,12 +913,12 @@
           <t>Software Engineer, New Grad</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>Notion</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>San Francisco, California (Remote)</t>
         </is>
@@ -930,7 +933,7 @@
           <t>Good Fit</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
@@ -945,20 +948,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="K7" s="15" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr"/>
+      <c r="L7" s="15" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>ashby:ramp:67fadb77-43d8-4449-954b-d4cf2c6d3b8b</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
@@ -968,12 +971,12 @@
           <t xml:space="preserve">Software Engineer Internship, Android </t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>Ramp</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>New York, NY (HQ) (Remote)</t>
         </is>
@@ -988,7 +991,7 @@
           <t>Good Fit</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
@@ -1003,20 +1006,20 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="14" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
+      <c r="L8" s="14" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>gh:scaleai:4703343005</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
@@ -1026,12 +1029,12 @@
           <t>AI Builder Intern</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>Scale AI</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>San Francisco, CA; New York, NY</t>
         </is>
@@ -1046,7 +1049,7 @@
           <t>Good Fit</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="15" t="inlineStr">
         <is>
           <t>Gh</t>
         </is>
@@ -1061,12 +1064,12 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr">
+      <c r="K9" s="15" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L9" s="7" t="inlineStr"/>
+      <c r="L9" s="15" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
@@ -1184,8 +1187,66 @@
       </c>
       <c r="L11" s="15" t="inlineStr"/>
     </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>gh:scaleai:4660340005</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Machine Learning Fellow - Human Frontier Collective (US)</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>Scale AI</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>Gh</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, docker, aws, tensorflow, pytorch, langchain, Fellowship title, Posted &lt;7d ago, Flags: PhD-oriented role</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K12" s="16" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L12" s="16" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L11"/>
+  <autoFilter ref="A1:L12"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
@@ -1197,6 +1258,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -608,12 +608,12 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>ashby:baseten:58d7d8e6-86ee-43a1-baec-3dddcb661d51</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
@@ -623,12 +623,12 @@
           <t>Base Labs Fellowship</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>Baseten</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>San Francisco (Remote)</t>
         </is>
@@ -643,7 +643,7 @@
           <t>Possible Fit</t>
         </is>
       </c>
-      <c r="H2" s="14" t="inlineStr">
+      <c r="H2" s="16" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
@@ -658,12 +658,12 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K2" s="14" t="inlineStr">
+      <c r="K2" s="16" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L2" s="14" t="inlineStr"/>
+      <c r="L2" s="16" t="inlineStr"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
@@ -724,12 +724,12 @@
       <c r="L3" s="15" t="inlineStr"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>ashby:notion:5b15697c-fa91-4511-9482-c98a6ff29f90</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
@@ -739,12 +739,12 @@
           <t>Software Engineer Intern (Fall 2026)</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>Notion</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>San Francisco, California (Remote)</t>
         </is>
@@ -759,7 +759,7 @@
           <t>Good Fit</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="16" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
@@ -774,12 +774,12 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="K4" s="16" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L4" s="14" t="inlineStr"/>
+      <c r="L4" s="16" t="inlineStr"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="15" t="inlineStr">
@@ -840,12 +840,12 @@
       <c r="L5" s="15" t="inlineStr"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>ashby:notion:85947779-6b87-466a-98bc-30a640448c28</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
@@ -855,12 +855,12 @@
           <t>Software Engineer, Early Career (AI)</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>Notion</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>San Francisco, California (Remote)</t>
         </is>
@@ -875,7 +875,7 @@
           <t>Strong Fit</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="16" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
@@ -890,12 +890,12 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K6" s="14" t="inlineStr">
+      <c r="K6" s="16" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L6" s="14" t="inlineStr"/>
+      <c r="L6" s="16" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
@@ -956,12 +956,12 @@
       <c r="L7" s="15" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>ashby:ramp:67fadb77-43d8-4449-954b-d4cf2c6d3b8b</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
@@ -971,12 +971,12 @@
           <t xml:space="preserve">Software Engineer Internship, Android </t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Ramp</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>New York, NY (HQ) (Remote)</t>
         </is>
@@ -991,7 +991,7 @@
           <t>Good Fit</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
@@ -1006,12 +1006,12 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K8" s="14" t="inlineStr">
+      <c r="K8" s="16" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L8" s="14" t="inlineStr"/>
+      <c r="L8" s="16" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
@@ -1072,12 +1072,12 @@
       <c r="L9" s="15" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>gh:togetherai:5157380007</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
@@ -1087,12 +1087,12 @@
           <t>Frontier Agents Intern (Fall 2026)</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>Together AI</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>San Francisco</t>
         </is>
@@ -1107,7 +1107,7 @@
           <t>Possible Fit</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr">
+      <c r="H10" s="16" t="inlineStr">
         <is>
           <t>Gh</t>
         </is>
@@ -1122,12 +1122,12 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K10" s="14" t="inlineStr">
+      <c r="K10" s="16" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L10" s="14" t="inlineStr"/>
+      <c r="L10" s="16" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="15" t="inlineStr">

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Internship Matches" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship Matches" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Startups" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internship Matches'!$A$1:$L$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internship Matches'!$A$1:$L$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Startups'!$A$1:$L$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -113,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -139,13 +141,13 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -153,15 +155,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -528,6 +521,1102 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Job ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Date Found</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Match %</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Why It Matched</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ashby:baseten:58d7d8e6-86ee-43a1-baec-3dddcb661d51</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Base Labs Fellowship</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Baseten</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>San Francisco (Remote)</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Ashby</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Skills: machine learning, statistics, Fellowship title, Location: San Francisco (Remote), Posted &lt;7d ago</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>ashby:notion:a6311f97-4850-4674-a5f3-d9fe5f6f2555</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer, New Grad</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Notion</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>San Francisco, California (Remote)</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Ashby</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, typescript, react, node, node.js, New-grad title, Location: San Francisco, California (Remote)</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ashby:notion:5b15697c-fa91-4511-9482-c98a6ff29f90</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Notion</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>San Francisco, California (Remote)</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Ashby</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, typescript, react, node, node.js, embeddings, Internship title, Location: San Francisco, California (Remote)</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>ashby:notion:7e6dc7fe-7ddd-42c1-8928-13f7bddb9ec9</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer, New Grad (AI)</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Notion</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>San Francisco, California (Remote)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Ashby</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, typescript, react, node, node.js, embeddings, New-grad title, Location: San Francisco, California (Remote)</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ashby:notion:85947779-6b87-466a-98bc-30a640448c28</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer, Early Career (AI)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Notion</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>San Francisco, California (Remote)</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>Strong Fit</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Ashby</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Skills: typescript, react, node, node.js, embeddings, data structures, New-grad title, Location: San Francisco, California (Remote), Posted &lt;7d ago</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>ashby:notion:297b4ece-765f-4eea-b1b8-46057cb6501f</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer, Early Career</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Notion</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>San Francisco, California</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Ashby</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>Skills: typescript, react, node, node.js, backend, data structures, New-grad title, Posted &lt;7d ago</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ashby:ramp:67fadb77-43d8-4449-954b-d4cf2c6d3b8b</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Software Engineer Internship, Android </t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>New York, NY (HQ) (Remote)</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Ashby</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, typescript, react, flask, sql, backend, Internship title, Location: New York, NY (HQ) (Remote)</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>gh:togetherai:5157380007</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Frontier Agents Intern (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Together AI</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Gh</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, pytorch, nlp, machine learning, deep learning, algorithms, Internship title, Posted &lt;7d ago, Flags: PhD-oriented role</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>gh:togetherai:5157559007</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Systems Research Engineer Intern - GPU Programming (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Together AI</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Gh</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Skills: algorithms, artificial intelligence, Internship title, Posted &lt;7d ago</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>gh:scaleai:4703343005</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>AI Builder Intern</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Scale AI</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>San Francisco, CA; New York, NY</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>Strong Fit</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Gh</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, react, api, github, llm, Internship title, Posted &lt;7d ago</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>gh:scaleai:4660340005</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Machine Learning Fellow - Human Frontier Collective (US)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Scale AI</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Gh</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, docker, aws, tensorflow, pytorch, langchain, Fellowship title, Posted &lt;7d ago, Flags: PhD-oriented role</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>lever:palantir:f17e98d0-046a-4e6e-9d65-ed0b12dd0ff7</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer, Internship - Defense Tech</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Palantir</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Lever</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>Skills: typescript, react, github, backend, frontend, Internship title, Location: Washington, D.C.</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>gh:cloudflare:8031027</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Network Strategy Intern (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Cloudflare</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>In-Office</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Gh</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, sql, data analysis, excel, kpi, Internship title</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>gh:cloudflare:8013562</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Network Strategy Intern (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Cloudflare</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>In-Office</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Gh</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, sql, data analysis, excel, kpi, Internship title</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>gh:cloudflare:8041135</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Technical Support Engineer Intern (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Cloudflare</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>In-Office</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Gh</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, rest, git, Internship title, Posted &lt;7d ago</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>gh:imc:4907430101</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Research Intern - Summer 2027 - Chicago</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>IMC Trading</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Chicago, United States</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Gh</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, tensorflow, pytorch, machine learning, deep learning, algorithms, Internship title, Posted &lt;7d ago, Flags: PhD-oriented role</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>gh:imc:4907399101</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Quantitative Research Intern (BS/MS) - Summer 2027</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>IMC Trading</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Chicago, United States</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Gh</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, c++, statistics, Internship title, Posted &lt;7d ago</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L18"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId17"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -608,14 +1697,14 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>ashby:baseten:58d7d8e6-86ee-43a1-baec-3dddcb661d51</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -623,12 +1712,12 @@
           <t>Base Labs Fellowship</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Baseten</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>San Francisco (Remote)</t>
         </is>
@@ -643,7 +1732,7 @@
           <t>Possible Fit</t>
         </is>
       </c>
-      <c r="H2" s="16" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
@@ -658,576 +1747,576 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K2" s="16" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L2" s="16" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>ashby:notion:a6311f97-4850-4674-a5f3-d9fe5f6f2555</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer, New Grad</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Notion</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>San Francisco, California (Remote)</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Ashby</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, typescript, react, node, node.js, New-grad title, Location: San Francisco, California (Remote)</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ashby:notion:5b15697c-fa91-4511-9482-c98a6ff29f90</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Notion</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>San Francisco, California (Remote)</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Ashby</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, typescript, react, node, node.js, embeddings, Internship title, Location: San Francisco, California (Remote)</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>ashby:notion:7e6dc7fe-7ddd-42c1-8928-13f7bddb9ec9</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer, New Grad (AI)</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Notion</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>San Francisco, California (Remote)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Ashby</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, typescript, react, node, node.js, embeddings, New-grad title, Location: San Francisco, California (Remote)</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ashby:notion:85947779-6b87-466a-98bc-30a640448c28</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer, Early Career (AI)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Notion</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>San Francisco, California (Remote)</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>Strong Fit</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Ashby</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Skills: typescript, react, node, node.js, embeddings, data structures, New-grad title, Location: San Francisco, California (Remote), Posted &lt;7d ago</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>ashby:notion:297b4ece-765f-4eea-b1b8-46057cb6501f</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Software Engineer, Early Career</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Notion</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>San Francisco, California</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Possible Fit</t>
         </is>
       </c>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>Skills: typescript, react, node, node.js, backend, data structures, New-grad title, Posted &lt;7d ago</t>
         </is>
       </c>
-      <c r="J3" s="9" t="inlineStr">
-        <is>
-          <t>Apply →</t>
-        </is>
-      </c>
-      <c r="K3" s="15" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L3" s="15" t="inlineStr"/>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>ashby:notion:5b15697c-fa91-4511-9482-c98a6ff29f90</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Software Engineer Intern (Fall 2026)</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>Notion</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>San Francisco, California (Remote)</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>68%</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ashby:ramp:67fadb77-43d8-4449-954b-d4cf2c6d3b8b</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Software Engineer Internship, Android </t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>New York, NY (HQ) (Remote)</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>Good Fit</t>
         </is>
       </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Skills: python, typescript, react, node, node.js, embeddings, Internship title, Location: San Francisco, California (Remote)</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Apply →</t>
-        </is>
-      </c>
-      <c r="K4" s="16" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L4" s="16" t="inlineStr"/>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>ashby:notion:7e6dc7fe-7ddd-42c1-8928-13f7bddb9ec9</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Software Engineer, New Grad (AI)</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>Notion</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>San Francisco, California (Remote)</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>52%</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, typescript, react, flask, sql, backend, Internship title, Location: New York, NY (HQ) (Remote)</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>gh:togetherai:5157380007</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Frontier Agents Intern (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Together AI</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Possible Fit</t>
         </is>
       </c>
-      <c r="H5" s="15" t="inlineStr">
-        <is>
-          <t>Ashby</t>
-        </is>
-      </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>Skills: python, typescript, react, node, node.js, embeddings, New-grad title, Location: San Francisco, California (Remote)</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="inlineStr">
-        <is>
-          <t>Apply →</t>
-        </is>
-      </c>
-      <c r="K5" s="15" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L5" s="15" t="inlineStr"/>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>ashby:notion:85947779-6b87-466a-98bc-30a640448c28</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Software Engineer, Early Career (AI)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>Notion</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>San Francisco, California (Remote)</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>73%</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Gh</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, pytorch, nlp, machine learning, deep learning, algorithms, Internship title, Posted &lt;7d ago, Flags: PhD-oriented role</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>gh:togetherai:5157559007</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Systems Research Engineer Intern - GPU Programming (Fall 2026)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Together AI</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Gh</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Skills: algorithms, artificial intelligence, Internship title, Posted &lt;7d ago</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>gh:scaleai:4703343005</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>AI Builder Intern</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Scale AI</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>San Francisco, CA; New York, NY</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
         <is>
           <t>Strong Fit</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>Ashby</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>Skills: typescript, react, node, node.js, embeddings, data structures, New-grad title, Location: San Francisco, California (Remote), Posted &lt;7d ago</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>Apply →</t>
-        </is>
-      </c>
-      <c r="K6" s="16" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L6" s="16" t="inlineStr"/>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>ashby:notion:a6311f97-4850-4674-a5f3-d9fe5f6f2555</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Software Engineer, New Grad</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Notion</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>San Francisco, California (Remote)</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>64%</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Gh</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, javascript, react, api, github, llm, Internship title, Posted &lt;7d ago</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>gh:scaleai:4660340005</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Machine Learning Fellow - Human Frontier Collective (US)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Scale AI</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Good Fit</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
-        <is>
-          <t>Ashby</t>
-        </is>
-      </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>Skills: python, javascript, typescript, react, node, node.js, New-grad title, Location: San Francisco, California (Remote)</t>
-        </is>
-      </c>
-      <c r="J7" s="9" t="inlineStr">
-        <is>
-          <t>Apply →</t>
-        </is>
-      </c>
-      <c r="K7" s="15" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L7" s="15" t="inlineStr"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>ashby:ramp:67fadb77-43d8-4449-954b-d4cf2c6d3b8b</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Software Engineer Internship, Android </t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>Ramp</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>New York, NY (HQ) (Remote)</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>65%</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>Good Fit</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>Ashby</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Skills: python, typescript, react, flask, sql, backend, Internship title, Location: New York, NY (HQ) (Remote)</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>Apply →</t>
-        </is>
-      </c>
-      <c r="K8" s="16" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>gh:scaleai:4703343005</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>AI Builder Intern</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>Scale AI</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
-          <t>San Francisco, CA; New York, NY</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>66%</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>Good Fit</t>
-        </is>
-      </c>
-      <c r="H9" s="15" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Gh</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>Skills: python, javascript, react, api, github, llm, Internship title</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="inlineStr">
-        <is>
-          <t>Apply →</t>
-        </is>
-      </c>
-      <c r="K9" s="15" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L9" s="15" t="inlineStr"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>gh:togetherai:5157380007</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Frontier Agents Intern (Fall 2026)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>Together AI</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>51%</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>Possible Fit</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>Gh</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>Skills: python, pytorch, nlp, machine learning, deep learning, algorithms, Internship title, Posted &lt;7d ago, Flags: PhD-oriented role</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>Apply →</t>
-        </is>
-      </c>
-      <c r="K10" s="16" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>gh:togetherai:5157559007</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Systems Research Engineer Intern - GPU Programming (Fall 2026)</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>Together AI</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>51%</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Possible Fit</t>
-        </is>
-      </c>
-      <c r="H11" s="15" t="inlineStr">
-        <is>
-          <t>Gh</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>Skills: algorithms, artificial intelligence, Internship title, Posted &lt;7d ago</t>
-        </is>
-      </c>
-      <c r="J11" s="9" t="inlineStr">
-        <is>
-          <t>Apply →</t>
-        </is>
-      </c>
-      <c r="K11" s="15" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L11" s="15" t="inlineStr"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>gh:scaleai:4660340005</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Machine Learning Fellow - Human Frontier Collective (US)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>Scale AI</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>Good Fit</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>Gh</t>
-        </is>
-      </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
           <t>Skills: python, docker, aws, tensorflow, pytorch, langchain, Fellowship title, Posted &lt;7d ago, Flags: PhD-oriented role</t>
@@ -1238,12 +2327,12 @@
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K12" s="16" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L12" s="16" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L12"/>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship Matches" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Startups" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Internship Matches" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Startups" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internship Matches'!$A$1:$L$18</definedName>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Internship Matches" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Startups" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship Matches" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Startups" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internship Matches'!$A$1:$L$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Startups'!$A$1:$L$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internship Matches'!$A$1:$Q$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Startups'!$A$1:$Q$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -126,13 +126,13 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -141,13 +141,13 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -521,21 +521,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -561,46 +566,71 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Match %</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Fit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Why It Matched</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>WSU Alumni Search</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Recruiter Search</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LinkedIn Note Draft</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Email Draft</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
+    <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>ashby:baseten:58d7d8e6-86ee-43a1-baec-3dddcb661d51</t>
@@ -621,44 +651,76 @@
           <t>Baseten</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>San Francisco (Remote)</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>54%</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>Possible Fit</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Skills: machine learning, statistics, Fellowship title, Location: San Francisco (Remote), Posted &lt;7d ago</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Baseten is hiring for Base Labs Fellowship. I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Base Labs Fellowship role at Baseten
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Base Labs Fellowship opening at Baseten and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="18" customHeight="1">
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>ashby:notion:a6311f97-4850-4674-a5f3-d9fe5f6f2555</t>
@@ -679,44 +741,76 @@
           <t>Notion</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>San Francisco, California (Remote)</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="H3" s="11" t="inlineStr">
         <is>
           <t>Good Fit</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="J3" s="8" t="inlineStr">
         <is>
           <t>Skills: python, javascript, typescript, react, node, node.js, New-grad title, Location: San Francisco, California (Remote)</t>
         </is>
       </c>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K3" s="7" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M3" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N3" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Notion is hiring for Software Engineer, New Grad. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O3" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer, New Grad role at Notion
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer, New Grad opening at Notion and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P3" s="7" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L3" s="7" t="inlineStr"/>
+      <c r="Q3" s="7" t="inlineStr"/>
     </row>
-    <row r="4" ht="18" customHeight="1">
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>ashby:notion:5b15697c-fa91-4511-9482-c98a6ff29f90</t>
@@ -737,44 +831,76 @@
           <t>Notion</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>San Francisco, California (Remote)</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>68%</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
         <is>
           <t>Good Fit</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Skills: python, typescript, react, node, node.js, embeddings, Internship title, Location: San Francisco, California (Remote)</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Notion is hiring for Software Engineer Intern (Fall 2026). I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer Intern (Fall 2026) role at Notion
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer Intern (Fall 2026) opening at Notion and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>ashby:notion:7e6dc7fe-7ddd-42c1-8928-13f7bddb9ec9</t>
@@ -795,44 +921,76 @@
           <t>Notion</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>San Francisco, California (Remote)</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>52%</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Possible Fit</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="J5" s="8" t="inlineStr">
         <is>
           <t>Skills: python, typescript, react, node, node.js, embeddings, New-grad title, Location: San Francisco, California (Remote)</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N5" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Notion is hiring for Software Engineer, New Grad (AI). I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O5" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer, New Grad (AI) role at Notion
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer, New Grad (AI) opening at Notion and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr"/>
+      <c r="Q5" s="7" t="inlineStr"/>
     </row>
-    <row r="6" ht="18" customHeight="1">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>ashby:notion:85947779-6b87-466a-98bc-30a640448c28</t>
@@ -853,44 +1011,76 @@
           <t>Notion</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>San Francisco, California (Remote)</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>Strong Fit</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>Skills: typescript, react, node, node.js, embeddings, data structures, New-grad title, Location: San Francisco, California (Remote), Posted &lt;7d ago</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Notion is hiring for Software Engineer, Early Career (AI). I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer, Early Career (AI) role at Notion
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer, Early Career (AI) opening at Notion and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>ashby:notion:297b4ece-765f-4eea-b1b8-46057cb6501f</t>
@@ -911,44 +1101,76 @@
           <t>Notion</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>San Francisco, California</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Possible Fit</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="J7" s="8" t="inlineStr">
         <is>
           <t>Skills: typescript, react, node, node.js, backend, data structures, New-grad title, Posted &lt;7d ago</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="K7" s="9" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Notion is hiring for Software Engineer, Early Career. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O7" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer, Early Career role at Notion
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer, Early Career opening at Notion and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr"/>
+      <c r="Q7" s="7" t="inlineStr"/>
     </row>
-    <row r="8" ht="18" customHeight="1">
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>ashby:ramp:67fadb77-43d8-4449-954b-d4cf2c6d3b8b</t>
@@ -969,44 +1191,76 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>New York, NY (HQ) (Remote)</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
         <is>
           <t>Good Fit</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>Skills: python, typescript, react, flask, sql, backend, Internship title, Location: New York, NY (HQ) (Remote)</t>
         </is>
       </c>
-      <c r="J8" s="6" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Ramp is hiring for Software Engineer Internship, Android . I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer Internship, Android  role at Ramp
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer Internship, Android  opening at Ramp and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
     </row>
-    <row r="9" ht="18" customHeight="1">
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>gh:togetherai:5157380007</t>
@@ -1027,44 +1281,76 @@
           <t>Together AI</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Possible Fit</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Gh</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>Skills: python, pytorch, nlp, machine learning, deep learning, algorithms, Internship title, Posted &lt;7d ago, Flags: PhD-oriented role</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="K9" s="9" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr">
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N9" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Together AI is hiring for Frontier Agents Intern (Fall 2026). I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O9" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Frontier Agents Intern (Fall 2026) role at Together AI
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Frontier Agents Intern (Fall 2026) opening at Together AI and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L9" s="7" t="inlineStr"/>
+      <c r="Q9" s="7" t="inlineStr"/>
     </row>
-    <row r="10" ht="18" customHeight="1">
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>gh:togetherai:5157559007</t>
@@ -1085,44 +1371,76 @@
           <t>Together AI</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>Possible Fit</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Gh</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>Skills: algorithms, artificial intelligence, Internship title, Posted &lt;7d ago</t>
         </is>
       </c>
-      <c r="J10" s="6" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Together AI is hiring for Systems Research Engineer Intern - GPU Programming (Fall 2026). I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Systems Research Engineer Intern - GPU Programming (Fall 2026) role at Together AI
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Systems Research Engineer Intern - GPU Programming (Fall 2026) opening at Together AI and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
     </row>
-    <row r="11" ht="18" customHeight="1">
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>gh:scaleai:4703343005</t>
@@ -1143,44 +1461,76 @@
           <t>Scale AI</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>San Francisco, CA; New York, NY</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>72%</t>
         </is>
       </c>
-      <c r="G11" s="13" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t>Strong Fit</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>Gh</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>Skills: python, javascript, react, api, github, llm, Internship title, Posted &lt;7d ago</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="K11" s="9" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr">
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M11" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N11" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Scale AI is hiring for AI Builder Intern. I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O11" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the AI Builder Intern role at Scale AI
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the AI Builder Intern opening at Scale AI and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L11" s="7" t="inlineStr"/>
+      <c r="Q11" s="7" t="inlineStr"/>
     </row>
-    <row r="12" ht="18" customHeight="1">
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>gh:scaleai:4660340005</t>
@@ -1201,44 +1551,76 @@
           <t>Scale AI</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>Good Fit</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Gh</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>Skills: python, docker, aws, tensorflow, pytorch, langchain, Fellowship title, Posted &lt;7d ago, Flags: PhD-oriented role</t>
         </is>
       </c>
-      <c r="J12" s="6" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Scale AI is hiring for Machine Learning Fellow - Human Frontier Collective (US). I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Machine Learning Fellow - Human Frontier Collective (US) role at Scale AI
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Machine Learning Fellow - Human Frontier Collective (US) opening at Scale AI and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
     </row>
-    <row r="13" ht="18" customHeight="1">
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>lever:palantir:f17e98d0-046a-4e6e-9d65-ed0b12dd0ff7</t>
@@ -1259,44 +1641,76 @@
           <t>Palantir</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>Washington, D.C.</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="H13" s="11" t="inlineStr">
         <is>
           <t>Good Fit</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>Lever</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>Skills: typescript, react, github, backend, frontend, Internship title, Location: Washington, D.C.</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="K13" s="9" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr">
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M13" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N13" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Palantir is hiring for Software Engineer, Internship - Defense Tech. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O13" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer, Internship - Defense Tech role at Palantir
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer, Internship - Defense Tech opening at Palantir and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L13" s="7" t="inlineStr"/>
+      <c r="Q13" s="7" t="inlineStr"/>
     </row>
-    <row r="14" ht="18" customHeight="1">
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>gh:cloudflare:8031027</t>
@@ -1317,44 +1731,76 @@
           <t>Cloudflare</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>In-Office</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>54%</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>Possible Fit</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Gh</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>Skills: python, sql, data analysis, excel, kpi, Internship title</t>
         </is>
       </c>
-      <c r="J14" s="6" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Cloudflare is hiring for Network Strategy Intern (Fall 2026). I've built a couple of data-heavy projects, including an automated stock signal analyzer — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Network Strategy Intern (Fall 2026) role at Cloudflare
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Network Strategy Intern (Fall 2026) opening at Cloudflare and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've built a couple of data-focused projects — an automated stock analysis tool applying technical indicators to live market data, and an interactive trail-mapping app processing 200+ real-world datasets with Pandas.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
     </row>
-    <row r="15" ht="18" customHeight="1">
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>gh:cloudflare:8013562</t>
@@ -1375,44 +1821,76 @@
           <t>Cloudflare</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>In-Office</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>54%</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>Possible Fit</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>Gh</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>Skills: python, sql, data analysis, excel, kpi, Internship title</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr">
+      <c r="K15" s="9" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K15" s="7" t="inlineStr">
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M15" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N15" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Cloudflare is hiring for Network Strategy Intern (Fall 2026). I've built a couple of data-heavy projects, including an automated stock signal analyzer — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O15" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Network Strategy Intern (Fall 2026) role at Cloudflare
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Network Strategy Intern (Fall 2026) opening at Cloudflare and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've built a couple of data-focused projects — an automated stock analysis tool applying technical indicators to live market data, and an interactive trail-mapping app processing 200+ real-world datasets with Pandas.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L15" s="7" t="inlineStr"/>
+      <c r="Q15" s="7" t="inlineStr"/>
     </row>
-    <row r="16" ht="18" customHeight="1">
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>gh:cloudflare:8041135</t>
@@ -1433,44 +1911,76 @@
           <t>Cloudflare</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>In-Office</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>57%</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="H16" s="11" t="inlineStr">
         <is>
           <t>Good Fit</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>Gh</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>Skills: python, javascript, rest, git, Internship title, Posted &lt;7d ago</t>
         </is>
       </c>
-      <c r="J16" s="6" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Cloudflare is hiring for Technical Support Engineer Intern (Fall 2026). I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Technical Support Engineer Intern (Fall 2026) role at Cloudflare
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Technical Support Engineer Intern (Fall 2026) opening at Cloudflare and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
-    <row r="17" ht="18" customHeight="1">
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>gh:imc:4907430101</t>
@@ -1491,44 +2001,76 @@
           <t>IMC Trading</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>Chicago, United States</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>Possible Fit</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>Gh</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>Skills: python, tensorflow, pytorch, machine learning, deep learning, algorithms, Internship title, Posted &lt;7d ago, Flags: PhD-oriented role</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="K17" s="9" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr">
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M17" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N17" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw IMC Trading is hiring for Machine Learning Research Intern - Summer 2027 - Chicago. I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Machine Learning Research Intern - Summer 2027 - Chicago role at IMC Trading
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Machine Learning Research Intern - Summer 2027 - Chicago opening at IMC Trading and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L17" s="7" t="inlineStr"/>
+      <c r="Q17" s="7" t="inlineStr"/>
     </row>
-    <row r="18" ht="18" customHeight="1">
+    <row r="18" ht="60" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>gh:imc:4907399101</t>
@@ -1549,63 +2091,146 @@
           <t>IMC Trading</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Chicago, United States</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>54%</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>Possible Fit</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>Gh</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>Skills: python, c++, statistics, Internship title, Posted &lt;7d ago</t>
         </is>
       </c>
-      <c r="J18" s="6" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw IMC Trading is hiring for Quantitative Research Intern (BS/MS) - Summer 2027. I've built a couple of data-heavy projects, including an automated stock signal analyzer — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Quantitative Research Intern (BS/MS) - Summer 2027 role at IMC Trading
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Quantitative Research Intern (BS/MS) - Summer 2027 opening at IMC Trading and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've built a couple of data-focused projects — an automated stock analysis tool applying technical indicators to live market data, and an interactive trail-mapping app processing 200+ real-world datasets with Pandas.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L18"/>
+  <autoFilter ref="A1:Q18"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1617,21 +2242,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1657,46 +2287,71 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Company Website</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Match %</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Fit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Why It Matched</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>WSU Alumni Search</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Recruiter Search</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LinkedIn Note Draft</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Email Draft</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
+    <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>ashby:baseten:58d7d8e6-86ee-43a1-baec-3dddcb661d51</t>
@@ -1717,44 +2372,76 @@
           <t>Baseten</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>San Francisco (Remote)</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>54%</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>Possible Fit</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Skills: machine learning, statistics, Fellowship title, Location: San Francisco (Remote), Posted &lt;7d ago</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Baseten is hiring for Base Labs Fellowship. I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Base Labs Fellowship role at Baseten
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Base Labs Fellowship opening at Baseten and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="18" customHeight="1">
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>ashby:notion:a6311f97-4850-4674-a5f3-d9fe5f6f2555</t>
@@ -1775,44 +2462,76 @@
           <t>Notion</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>San Francisco, California (Remote)</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="H3" s="11" t="inlineStr">
         <is>
           <t>Good Fit</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="J3" s="8" t="inlineStr">
         <is>
           <t>Skills: python, javascript, typescript, react, node, node.js, New-grad title, Location: San Francisco, California (Remote)</t>
         </is>
       </c>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K3" s="7" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M3" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N3" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Notion is hiring for Software Engineer, New Grad. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O3" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer, New Grad role at Notion
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer, New Grad opening at Notion and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P3" s="7" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L3" s="7" t="inlineStr"/>
+      <c r="Q3" s="7" t="inlineStr"/>
     </row>
-    <row r="4" ht="18" customHeight="1">
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>ashby:notion:5b15697c-fa91-4511-9482-c98a6ff29f90</t>
@@ -1833,44 +2552,76 @@
           <t>Notion</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>San Francisco, California (Remote)</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>68%</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
         <is>
           <t>Good Fit</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Skills: python, typescript, react, node, node.js, embeddings, Internship title, Location: San Francisco, California (Remote)</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Notion is hiring for Software Engineer Intern (Fall 2026). I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer Intern (Fall 2026) role at Notion
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer Intern (Fall 2026) opening at Notion and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>ashby:notion:7e6dc7fe-7ddd-42c1-8928-13f7bddb9ec9</t>
@@ -1891,44 +2642,76 @@
           <t>Notion</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>San Francisco, California (Remote)</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>52%</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Possible Fit</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="J5" s="8" t="inlineStr">
         <is>
           <t>Skills: python, typescript, react, node, node.js, embeddings, New-grad title, Location: San Francisco, California (Remote)</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N5" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Notion is hiring for Software Engineer, New Grad (AI). I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O5" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer, New Grad (AI) role at Notion
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer, New Grad (AI) opening at Notion and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr"/>
+      <c r="Q5" s="7" t="inlineStr"/>
     </row>
-    <row r="6" ht="18" customHeight="1">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>ashby:notion:85947779-6b87-466a-98bc-30a640448c28</t>
@@ -1949,44 +2732,76 @@
           <t>Notion</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>San Francisco, California (Remote)</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>Strong Fit</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>Skills: typescript, react, node, node.js, embeddings, data structures, New-grad title, Location: San Francisco, California (Remote), Posted &lt;7d ago</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Notion is hiring for Software Engineer, Early Career (AI). I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer, Early Career (AI) role at Notion
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer, Early Career (AI) opening at Notion and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>ashby:notion:297b4ece-765f-4eea-b1b8-46057cb6501f</t>
@@ -2007,44 +2822,76 @@
           <t>Notion</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>San Francisco, California</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Possible Fit</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="J7" s="8" t="inlineStr">
         <is>
           <t>Skills: typescript, react, node, node.js, backend, data structures, New-grad title, Posted &lt;7d ago</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="K7" s="9" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Notion is hiring for Software Engineer, Early Career. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O7" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer, Early Career role at Notion
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer, Early Career opening at Notion and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr"/>
+      <c r="Q7" s="7" t="inlineStr"/>
     </row>
-    <row r="8" ht="18" customHeight="1">
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>ashby:ramp:67fadb77-43d8-4449-954b-d4cf2c6d3b8b</t>
@@ -2065,44 +2912,76 @@
           <t>Ramp</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>New York, NY (HQ) (Remote)</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
         <is>
           <t>Good Fit</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Ashby</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>Skills: python, typescript, react, flask, sql, backend, Internship title, Location: New York, NY (HQ) (Remote)</t>
         </is>
       </c>
-      <c r="J8" s="6" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Ramp is hiring for Software Engineer Internship, Android . I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer Internship, Android  role at Ramp
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer Internship, Android  opening at Ramp and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
     </row>
-    <row r="9" ht="18" customHeight="1">
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>gh:togetherai:5157380007</t>
@@ -2123,44 +3002,76 @@
           <t>Together AI</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Possible Fit</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Gh</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>Skills: python, pytorch, nlp, machine learning, deep learning, algorithms, Internship title, Posted &lt;7d ago, Flags: PhD-oriented role</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="K9" s="9" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr">
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N9" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Together AI is hiring for Frontier Agents Intern (Fall 2026). I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O9" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Frontier Agents Intern (Fall 2026) role at Together AI
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Frontier Agents Intern (Fall 2026) opening at Together AI and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L9" s="7" t="inlineStr"/>
+      <c r="Q9" s="7" t="inlineStr"/>
     </row>
-    <row r="10" ht="18" customHeight="1">
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>gh:togetherai:5157559007</t>
@@ -2181,44 +3092,76 @@
           <t>Together AI</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>San Francisco</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>Possible Fit</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Gh</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>Skills: algorithms, artificial intelligence, Internship title, Posted &lt;7d ago</t>
         </is>
       </c>
-      <c r="J10" s="6" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Together AI is hiring for Systems Research Engineer Intern - GPU Programming (Fall 2026). I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Systems Research Engineer Intern - GPU Programming (Fall 2026) role at Together AI
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Systems Research Engineer Intern - GPU Programming (Fall 2026) opening at Together AI and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
     </row>
-    <row r="11" ht="18" customHeight="1">
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>gh:scaleai:4703343005</t>
@@ -2239,115 +3182,118 @@
           <t>Scale AI</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>San Francisco, CA; New York, NY</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>72%</t>
         </is>
       </c>
-      <c r="G11" s="13" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t>Strong Fit</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>Gh</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>Skills: python, javascript, react, api, github, llm, Internship title, Posted &lt;7d ago</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="K11" s="9" t="inlineStr">
         <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr">
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M11" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N11" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Scale AI is hiring for AI Builder Intern. I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O11" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the AI Builder Intern role at Scale AI
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the AI Builder Intern opening at Scale AI and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
         <is>
           <t>Not Applied</t>
         </is>
       </c>
-      <c r="L11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>gh:scaleai:4660340005</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Machine Learning Fellow - Human Frontier Collective (US)</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Scale AI</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>Good Fit</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Gh</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>Skills: python, docker, aws, tensorflow, pytorch, langchain, Fellowship title, Posted &lt;7d ago, Flags: PhD-oriented role</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>Apply →</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Not Applied</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="Q11" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L12"/>
+  <autoFilter ref="A1:Q11"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship Matches" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Startups" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Internship Matches" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Startups" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internship Matches'!$A$1:$Q$18</definedName>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Internship Matches" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Startups" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship Matches" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Startups" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internship Matches'!$A$1:$Q$18</definedName>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Startups" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internship Matches'!$A$1:$Q$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internship Matches'!$A$1:$Q$121</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Startups'!$A$1:$Q$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2160,8 +2160,9250 @@
       </c>
       <c r="Q18" s="2" t="inlineStr"/>
     </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>simplify:55804513-4600-4ed2-98da-a5e607d5acdb</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern, Frontend</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Tessera Labs</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr"/>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Remote in USA</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title, Location: Remote in USA</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M19" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N19" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Tessera Labs is hiring for Software Engineering Intern, Frontend. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineering Intern, Frontend role at Tessera Labs
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineering Intern, Frontend opening at Tessera Labs and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>simplify:51bded9f-eacd-40b1-aac6-c782f03da04b</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Intern/New Grad Software Engineer</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Anima</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Remote in USA</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title, Location: Remote in USA</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Anima is hiring for Intern/New Grad Software Engineer. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Intern/New Grad Software Engineer role at Anima
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Intern/New Grad Software Engineer opening at Anima and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>simplify:e5045382-ee6d-4bcb-a35a-9d5d2d395276</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>AI Automation Intern</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Advantmed</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr"/>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Remote in USA</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, machine learning, data analysis, artificial intelligence, Internship title, Location: Remote in USA</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M21" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Advantmed is hiring for AI Automation Intern. I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the AI Automation Intern role at Advantmed
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the AI Automation Intern opening at Advantmed and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>simplify:5428a3c8-3c8c-496a-87c2-2afbd536b54f</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>MCG Health</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title, Location: Seattle, WA</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw MCG Health is hiring for Software Engineering Intern. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineering Intern role at MCG Health
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineering Intern opening at MCG Health and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>simplify:7cbf5e66-95b6-4b66-b41f-fa9cdeadcadc</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern - Commerce Ads - 2026 Summer</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title, Location: Seattle, WA</t>
+        </is>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M23" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N23" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw TikTok is hiring for Software Engineer Intern - Commerce Ads - 2026 Summer. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer Intern - Commerce Ads - 2026 Summer role at TikTok
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer Intern - Commerce Ads - 2026 Summer opening at TikTok and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>simplify:8cfec360-0de7-4099-97df-66400369c836</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Software Development Engineer Intern - Military Veteran</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>NYC; Culver City, CA; Santa Clara, CA; Boston, MA; Seattle, WA; Denver, CO; SF; Arlington, VA; Sunnyvale, CA; Brooklyn, NY; Williston Park, NY</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title, Location: NYC; Culver City, CA; Santa Clara, CA; Boston, MA; Seattle, WA; Denver, CO; SF; Arlington, VA; Sunnyvale, CA; Brooklyn, NY; Williston Park, NY</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Amazon is hiring for Software Development Engineer Intern - Military Veteran. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Development Engineer Intern - Military Veteran role at Amazon
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Development Engineer Intern - Military Veteran opening at Amazon and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>simplify:f9c3682d-25e0-42b3-aeb8-ae98854876fe</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern - Payment Network - Global Payment</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>ByteDance</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title, Location: Seattle, WA</t>
+        </is>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M25" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N25" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw ByteDance is hiring for Software Engineer Intern - Payment Network - Global Payment. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O25" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer Intern - Payment Network - Global Payment role at ByteDance
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer Intern - Payment Network - Global Payment opening at ByteDance and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>simplify:177690e4-6703-4698-a2bd-350db211f356</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern - AI Model Optimization</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title, Location: Seattle, WA</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw TikTok is hiring for Software Engineer Intern - AI Model Optimization. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer Intern - AI Model Optimization role at TikTok
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer Intern - AI Model Optimization opening at TikTok and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>simplify:7107711b-0874-460d-932c-0c0d7b729f42</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Year at Palantir Intern - Forward Deployed Software Engineer</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Palantir</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Washington, DC</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title, Location: Washington, DC</t>
+        </is>
+      </c>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M27" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N27" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Palantir is hiring for Year at Palantir Intern - Forward Deployed Software Engineer. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Year at Palantir Intern - Forward Deployed Software Engineer role at Palantir
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Year at Palantir Intern - Forward Deployed Software Engineer opening at Palantir and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>simplify:78ecf03f-56f1-4a4f-8ec9-e5b351b77080</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Docugami</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Kirkland, WA</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title, Location: Kirkland, WA</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Docugami is hiring for Software Engineer Intern. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer Intern role at Docugami
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer Intern opening at Docugami and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>simplify:6c56bd42-aaca-45b8-b770-128f543898e0</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Applied Scientist AI/ML Intern</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Wealth.com</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Remote in USA</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, machine learning, data analysis, artificial intelligence, Internship title, Location: Remote in USA</t>
+        </is>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M29" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N29" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Wealth.com is hiring for Applied Scientist AI/ML Intern. I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O29" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Applied Scientist AI/ML Intern role at Wealth.com
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Applied Scientist AI/ML Intern opening at Wealth.com and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>simplify:71f5d4c0-dc9d-4fe6-afcc-6d0735570374</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Clerkie</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Remote in USA</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title, Location: Remote in USA</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Clerkie is hiring for Software Engineer Intern. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer Intern role at Clerkie
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer Intern opening at Clerkie and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>simplify:8d981cf1-c610-41cc-84d1-800ea078fd37</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Software Development Engineer Intern - Network Automation</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>ByteDance</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title, Location: Seattle, WA</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M31" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N31" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw ByteDance is hiring for Software Development Engineer Intern - Network Automation. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O31" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Development Engineer Intern - Network Automation role at ByteDance
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Development Engineer Intern - Network Automation opening at ByteDance and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>simplify:77245ac7-931e-4d69-8030-18400e8793a2</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer Intern - E-commerce Governance Algorithms</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>ByteDance</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, machine learning, algorithms, data analysis, artificial intelligence, Internship title, Location: Seattle, WA</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw ByteDance is hiring for Machine Learning Engineer Intern - E-commerce Governance Algorithms. I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Machine Learning Engineer Intern - E-commerce Governance Algorithms role at ByteDance
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Machine Learning Engineer Intern - E-commerce Governance Algorithms opening at ByteDance and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>simplify:6bc3983c-65aa-4d29-9a3b-a08c3230a75a</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer Intern - E-Commerce Knowledge Graph - Computer Vision/Multimodal/Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>ByteDance</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, machine learning, data analysis, artificial intelligence, Internship title, Location: Seattle, WA</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M33" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N33" s="8" t="inlineStr">
+        <is>
+          <t>Hi! WSU CS student here, saw ByteDance is hiring for Machine Learning Engineer Intern - E-Commerce Knowledge Graph - Computer Vision/Multimodal/Natural Language Processing. I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect.</t>
+        </is>
+      </c>
+      <c r="O33" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Machine Learning Engineer Intern - E-Commerce Knowledge Graph - Computer Vision/Multimodal/Natural Language Processing role at ByteDance
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Machine Learning Engineer Intern - E-Commerce Knowledge Graph - Computer Vision/Multimodal/Natural Language Processing opening at ByteDance and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P33" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>simplify:38e9b155-826a-49f7-a431-a689d10c579e</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer Intern - Global E-commerce Risk Control</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>ByteDance</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, machine learning, data analysis, artificial intelligence, Internship title, Location: Seattle, WA</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw ByteDance is hiring for Machine Learning Engineer Intern - Global E-commerce Risk Control. I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Machine Learning Engineer Intern - Global E-commerce Risk Control role at ByteDance
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Machine Learning Engineer Intern - Global E-commerce Risk Control opening at ByteDance and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>simplify:0d8819e9-06a6-4bf6-9c18-a00012e17263</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Rippling</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Seattle, WA; SF; NYC</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title, Location: Seattle, WA; SF; NYC</t>
+        </is>
+      </c>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L35" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M35" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N35" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Rippling is hiring for Full Stack Software Engineer Intern. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O35" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Full Stack Software Engineer Intern role at Rippling
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Full Stack Software Engineer Intern opening at Rippling and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P35" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>simplify:7df6766d-b43b-464c-a03e-68387c5ffb37</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern - Backend Focused</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Rippling</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Seattle, WA; SF; NYC</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title, Location: Seattle, WA; SF; NYC</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Rippling is hiring for Software Engineer Intern - Backend Focused. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer Intern - Backend Focused role at Rippling
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer Intern - Backend Focused opening at Rippling and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>simplify:3fa70c31-5b5a-41e7-8aa4-3e415e17364f</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Data Science Intern</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>iSpot.tv</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>Bellevue, WA</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, machine learning, data analysis, artificial intelligence, Internship title, Location: Bellevue, WA</t>
+        </is>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L37" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M37" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N37" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw iSpot.tv is hiring for Data Science Intern. I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O37" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Data Science Intern role at iSpot.tv
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Data Science Intern opening at iSpot.tv and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P37" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>simplify:cc2fec71-d445-40e3-be3e-b8dd51184164</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>OfferUp</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Bellevue, WA</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title, Location: Bellevue, WA</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw OfferUp is hiring for Software Engineer Intern. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer Intern role at OfferUp
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer Intern opening at OfferUp and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>simplify:94896995-4fb6-4ac7-8f06-5ef16ac5ad82</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Data Scientist Intern</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J39" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, machine learning, data analysis, artificial intelligence, Internship title, Location: Seattle, WA</t>
+        </is>
+      </c>
+      <c r="K39" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M39" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N39" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw TikTok is hiring for Data Scientist Intern. I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O39" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Data Scientist Intern role at TikTok
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Data Scientist Intern opening at TikTok and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P39" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>simplify:75840089-9ab1-4f67-bb80-130b0082924b</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Data Analyst Intern - TikTok Shop AMS Data Science</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, machine learning, data analysis, data analyst, artificial intelligence, Internship title, Location: Seattle, WA</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw TikTok is hiring for Data Analyst Intern - TikTok Shop AMS Data Science. I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Data Analyst Intern - TikTok Shop AMS Data Science role at TikTok
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Data Analyst Intern - TikTok Shop AMS Data Science opening at TikTok and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>simplify:fe77f108-84fc-48fd-bc64-dfd8921d203f</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Forward Deployed Software Engineer Intern - Defense Tech</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Palantir</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>Washington, DC</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J41" s="8" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title, Location: Washington, DC</t>
+        </is>
+      </c>
+      <c r="K41" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L41" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M41" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N41" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Palantir is hiring for Forward Deployed Software Engineer Intern - Defense Tech. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O41" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Forward Deployed Software Engineer Intern - Defense Tech role at Palantir
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Forward Deployed Software Engineer Intern - Defense Tech opening at Palantir and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P41" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>simplify:e18b613e-4960-458a-950c-31a675aacf04</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Agentic AI Research Intern</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Cotiviti</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Remote in USA</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, machine learning, data analysis, artificial intelligence, Internship title, Location: Remote in USA</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Cotiviti is hiring for Agentic AI Research Intern. I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Agentic AI Research Intern role at Cotiviti
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Agentic AI Research Intern opening at Cotiviti and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>simplify:36e30f4d-f208-49e7-b220-df4872f5af7b</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Software Development Intern</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>iHerb</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>Remote in USA</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J43" s="8" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title, Location: Remote in USA</t>
+        </is>
+      </c>
+      <c r="K43" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L43" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M43" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N43" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw iHerb is hiring for Software Development Intern. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O43" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Development Intern role at iHerb
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Development Intern opening at iHerb and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P43" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>simplify:ac9a60d7-eb51-4cbb-af68-97f00839f454</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Full-Stack Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Muru</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, full-stack, backend, frontend, Internship title</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Muru is hiring for Full-Stack Software Engineer Intern. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Full-Stack Software Engineer Intern role at Muru
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Full-Stack Software Engineer Intern opening at Muru and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>simplify:c3e5404d-596e-4408-ba27-d60a17fb1680</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>AI Product Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>MyEmployment</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr"/>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>Remote in US</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J45" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, machine learning, data analysis, artificial intelligence, Internship title, Location: Remote in US</t>
+        </is>
+      </c>
+      <c r="K45" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M45" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N45" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw MyEmployment is hiring for AI Product Engineer Intern. I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O45" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the AI Product Engineer Intern role at MyEmployment
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the AI Product Engineer Intern opening at MyEmployment and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P45" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>simplify:3b16aba4-17cf-4636-b0fa-03bc53122db2</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Full Stack Developer Intern</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>VetsEZ</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Remote in US</t>
+        </is>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title, Location: Remote in US</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw VetsEZ is hiring for Full Stack Developer Intern. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Full Stack Developer Intern role at VetsEZ
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Full Stack Developer Intern opening at VetsEZ and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>simplify:70b45d75-a146-4733-a653-c4bce22c4e32</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer Intern - Global E-Commerce Content Recommendation</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="G47" s="10" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J47" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, machine learning, data analysis, artificial intelligence, Internship title, Location: Seattle, WA</t>
+        </is>
+      </c>
+      <c r="K47" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L47" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M47" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N47" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw TikTok is hiring for Machine Learning Engineer Intern - Global E-Commerce Content Recommendation. I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O47" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Machine Learning Engineer Intern - Global E-Commerce Content Recommendation role at TikTok
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Machine Learning Engineer Intern - Global E-Commerce Content Recommendation opening at TikTok and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P47" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>simplify:e1cb71b6-18fc-4d48-9c80-55c54bb62a50</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Palantir</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M48" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Palantir is hiring for Software Engineer Intern. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer Intern role at Palantir
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer Intern opening at Palantir and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>simplify:da1074aa-7344-4ad3-9b53-078f1dbd2edc</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Palantir</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>Denver, CO</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J49" s="8" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title</t>
+        </is>
+      </c>
+      <c r="K49" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L49" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M49" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N49" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Palantir is hiring for Software Engineer Intern. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O49" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer Intern role at Palantir
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer Intern opening at Palantir and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P49" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>simplify:4a30dd71-73a0-48c8-9e4a-9422a6952920</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern - Defense Tech</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Palantir</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Washington, DC</t>
+        </is>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="H50" s="13" t="inlineStr">
+        <is>
+          <t>Strong Fit</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title, Location: Washington, DC</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Palantir is hiring for Software Engineer Intern - Defense Tech. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer Intern - Defense Tech role at Palantir
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer Intern - Defense Tech opening at Palantir and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>simplify:0d20db7c-197a-4ec4-91c2-a72684374d51</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern - Production Infrastructure</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Palantir</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J51" s="8" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title</t>
+        </is>
+      </c>
+      <c r="K51" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L51" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M51" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N51" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Palantir is hiring for Software Engineer Intern - Production Infrastructure. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O51" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer Intern - Production Infrastructure role at Palantir
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer Intern - Production Infrastructure opening at Palantir and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P51" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>simplify:03866764-b942-4e9f-977f-9523a4647726</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Founding Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Clera</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M52" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Clera is hiring for Founding Engineer Intern. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Founding Engineer Intern role at Clera
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Founding Engineer Intern opening at Clera and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>simplify:57cd150e-48df-4c56-85b9-d5a32e55b32f</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>System Triage Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Torc Robotics</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>Blacksburg, VA; Ann Arbor, MI; Fort Worth, TX</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J53" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, machine learning, data analysis, artificial intelligence, Internship title</t>
+        </is>
+      </c>
+      <c r="K53" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L53" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M53" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N53" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Torc Robotics is hiring for System Triage Engineer Intern. I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O53" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the System Triage Engineer Intern role at Torc Robotics
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the System Triage Engineer Intern opening at Torc Robotics and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P53" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>simplify:9c647182-768d-410f-acf7-e162259bd5f2</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Undergraduate Intern - Technology and Analytics Department-Educate Pod</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>ACLU Kentucky</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M54" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>Hi! WSU CS student here, saw ACLU Kentucky is hiring for Undergraduate Intern - Technology and Analytics Department-Educate Pod. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect.</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Undergraduate Intern - Technology and Analytics Department-Educate Pod role at ACLU Kentucky
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Undergraduate Intern - Technology and Analytics Department-Educate Pod opening at ACLU Kentucky and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>simplify:38e6cb0e-9447-444b-8afd-ed10aa5c709d</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>AI Intern</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>PLS</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J55" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, machine learning, data analysis, artificial intelligence, Internship title</t>
+        </is>
+      </c>
+      <c r="K55" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L55" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M55" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N55" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw PLS is hiring for AI Intern. I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O55" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the AI Intern role at PLS
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the AI Intern opening at PLS and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P55" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>simplify:77fe355c-f71a-4b4f-8ac1-348d2b156c64</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer Intern - Machine Learning Engineer - Factory Software</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Fremont, CA</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, machine learning, data analysis, artificial intelligence, Internship title</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>Hi! WSU CS student here, saw Tesla is hiring for Machine Learning Engineer Intern - Machine Learning Engineer - Factory Software. I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect.</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Machine Learning Engineer Intern - Machine Learning Engineer - Factory Software role at Tesla
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Machine Learning Engineer Intern - Machine Learning Engineer - Factory Software opening at Tesla and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>simplify:7185eeaf-ca13-448b-9914-08c197b45f81</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>Analytics Intern</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>thyssenkrupp</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>Cleveland, OH</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J57" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, machine learning, data analysis, artificial intelligence, Internship title</t>
+        </is>
+      </c>
+      <c r="K57" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L57" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M57" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N57" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw thyssenkrupp is hiring for Analytics Intern. I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O57" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Analytics Intern role at thyssenkrupp
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Analytics Intern opening at thyssenkrupp and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P57" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>simplify:ffc1f08c-7dd5-4fce-986e-2e3b824aabb4</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Forward Deployed Software Engineer Intern - Commercial</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Palantir</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M58" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Palantir is hiring for Forward Deployed Software Engineer Intern - Commercial. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Forward Deployed Software Engineer Intern - Commercial role at Palantir
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Forward Deployed Software Engineer Intern - Commercial opening at Palantir and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>simplify:de258f68-480f-46d8-90eb-6a87d8ded565</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineer Intern - Applications Engineering</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>Fremont, CA</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J59" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, machine learning, data analysis, artificial intelligence, Internship title</t>
+        </is>
+      </c>
+      <c r="K59" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L59" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M59" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N59" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Tesla is hiring for Data Engineer Intern - Applications Engineering. I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O59" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Data Engineer Intern - Applications Engineering role at Tesla
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Data Engineer Intern - Applications Engineering opening at Tesla and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P59" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>simplify:3aadf7a9-d9ad-4c6e-a941-31641f852cdd</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>AI/ML Modeling Engineer Intern - ML Modeling Engineer - AI Hardware</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, machine learning, data analysis, artificial intelligence, Internship title</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M60" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Tesla is hiring for AI/ML Modeling Engineer Intern - ML Modeling Engineer - AI Hardware. I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the AI/ML Modeling Engineer Intern - ML Modeling Engineer - AI Hardware role at Tesla
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the AI/ML Modeling Engineer Intern - ML Modeling Engineer - AI Hardware opening at Tesla and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>simplify:9d5715d2-791b-4696-8b04-e80e30594e84</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>Project and Race Support Engineer Internship</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Hendrick Motorsports</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Charlotte, NC</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J61" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, machine learning, data analysis, artificial intelligence, Internship title</t>
+        </is>
+      </c>
+      <c r="K61" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L61" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M61" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N61" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Hendrick Motorsports is hiring for Project and Race Support Engineer Internship. I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O61" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Project and Race Support Engineer Internship role at Hendrick Motorsports
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Project and Race Support Engineer Internship opening at Hendrick Motorsports and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P61" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>simplify:dc2f3a9e-bfd2-4ade-a19a-e77dfdcd2301</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Copart</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Dallas, TX</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M62" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Copart is hiring for Software Engineer Intern. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer Intern role at Copart
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer Intern opening at Copart and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>simplify:9ef328e9-1153-41e5-a037-2d1748c0288c</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>Remote in USA</t>
+        </is>
+      </c>
+      <c r="G63" s="10" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="H63" s="11" t="inlineStr">
+        <is>
+          <t>Good Fit</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J63" s="8" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title, Location: Remote in USA</t>
+        </is>
+      </c>
+      <c r="K63" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L63" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M63" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N63" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Binance is hiring for Software Engineer Intern. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O63" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer Intern role at Binance
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer Intern opening at Binance and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P63" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>simplify:da228603-aa5d-4d28-94e6-89b4d8db92e7</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Maxima</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>San Mateo, CA</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M64" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Maxima is hiring for Software Engineer Intern. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer Intern role at Maxima
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer Intern opening at Maxima and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>simplify:b8c23e53-79db-45ab-a105-78a3d344b881</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>kos.ai</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J65" s="8" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title</t>
+        </is>
+      </c>
+      <c r="K65" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L65" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M65" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N65" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw kos.ai is hiring for Software Engineer Intern. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O65" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer Intern role at kos.ai
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer Intern opening at kos.ai and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P65" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>simplify:458415d1-7c6f-417e-9299-30a80dcdf88b</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Espa AI</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M66" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Espa AI is hiring for Software Engineer Intern. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O66" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer Intern role at Espa AI
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer Intern opening at Espa AI and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>simplify:2c1046a7-cf40-410a-bf96-843e6e4db629</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern - Production Infrastructure</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Palantir</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>Washington, DC</t>
+        </is>
+      </c>
+      <c r="G67" s="12" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="H67" s="13" t="inlineStr">
+        <is>
+          <t>Strong Fit</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J67" s="8" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title, Location: Washington, DC</t>
+        </is>
+      </c>
+      <c r="K67" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L67" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M67" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N67" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Palantir is hiring for Software Engineer Intern - Production Infrastructure. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O67" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer Intern - Production Infrastructure role at Palantir
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer Intern - Production Infrastructure opening at Palantir and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P67" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>simplify:eed44008-bc56-4a68-9f65-0b98b4876804</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Forward Deployed Software Engineer Intern - Commercial</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Palantir</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>NYC</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M68" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Palantir is hiring for Forward Deployed Software Engineer Intern - Commercial. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Forward Deployed Software Engineer Intern - Commercial role at Palantir
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Forward Deployed Software Engineer Intern - Commercial opening at Palantir and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>simplify:8f121dc0-1713-477e-834e-8e750c15465c</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>Vehicle Software Intern - Torque Path &amp; Chassis Controls</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J69" s="8" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title</t>
+        </is>
+      </c>
+      <c r="K69" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L69" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M69" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N69" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Tesla is hiring for Vehicle Software Intern - Torque Path &amp; Chassis Controls. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O69" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Vehicle Software Intern - Torque Path &amp; Chassis Controls role at Tesla
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Vehicle Software Intern - Torque Path &amp; Chassis Controls opening at Tesla and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P69" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q69" s="7" t="inlineStr"/>
+    </row>
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>simplify:904269e6-581d-458f-9376-a8c3d9e74a98</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>RL Engineer Intern - RL Engineer - Tesla AI</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, machine learning, data analysis, artificial intelligence, Internship title</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M70" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Tesla is hiring for RL Engineer Intern - RL Engineer - Tesla AI. I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O70" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the RL Engineer Intern - RL Engineer - Tesla AI role at Tesla
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the RL Engineer Intern - RL Engineer - Tesla AI opening at Tesla and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>simplify:f49b4766-f352-4e81-9cb2-0f42fb9fd101</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Optiver</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J71" s="8" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title</t>
+        </is>
+      </c>
+      <c r="K71" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L71" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M71" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N71" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Optiver is hiring for Software Engineer Intern. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O71" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer Intern role at Optiver
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer Intern opening at Optiver and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P71" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q71" s="7" t="inlineStr"/>
+    </row>
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>simplify:895ea579-0ca7-4aa8-82a2-db62cfeba95c</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Optiver</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M72" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Optiver is hiring for Software Engineer Intern. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O72" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer Intern role at Optiver
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer Intern opening at Optiver and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>simplify:87b3e2e9-6e48-46cf-a3ad-0144480aaea6</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern - Distributed Systems Software Engineer - Energy Engineering</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J73" s="8" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title</t>
+        </is>
+      </c>
+      <c r="K73" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L73" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M73" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N73" s="8" t="inlineStr">
+        <is>
+          <t>Hi! WSU CS student here, saw Tesla is hiring for Software Engineer Intern - Distributed Systems Software Engineer - Energy Engineering. I've shipped a few full-stack apps (Flask/React, deployed on AWS) including an AI travel planner — would love to connect.</t>
+        </is>
+      </c>
+      <c r="O73" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Software Engineer Intern - Distributed Systems Software Engineer - Energy Engineering role at Tesla
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Software Engineer Intern - Distributed Systems Software Engineer - Energy Engineering opening at Tesla and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+I've shipped several full-stack projects — including TravelBuddy, an AI-powered travel planner with a Flask backend and React frontend deployed on AWS, and a hackathon project integrating the Anthropic Claude API built in 24 hours.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P73" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>simplify:e0d4f452-a4bf-4b10-9618-15d2cfe12f9e</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>IT Intern</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Blue Cross Blue Shield of Michigan</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Detroit, MI</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>Skills: python, machine learning, data analysis, artificial intelligence, Internship title</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M74" s="4" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw Blue Cross Blue Shield of Michigan is hiring for IT Intern. I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O74" s="3" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the IT Intern role at Blue Cross Blue Shield of Michigan
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the IT Intern opening at Blue Cross Blue Shield of Michigan and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>simplify:340cf1d5-2f86-48ad-ba6d-24877471ebcf</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>Summer Internship Intern - Business Systems Analyst</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>The Wonderful Company</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>Bakersfield, CA</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J75" s="8" t="inlineStr">
+        <is>
+          <t>Skills: python, machine learning, data analysis, artificial intelligence, Internship title</t>
+        </is>
+      </c>
+      <c r="K75" s="9" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L75" s="9" t="inlineStr">
+        <is>
+          <t>WSU Alumni →</t>
+        </is>
+      </c>
+      <c r="M75" s="9" t="inlineStr">
+        <is>
+          <t>Recruiters →</t>
+        </is>
+      </c>
+      <c r="N75" s="8" t="inlineStr">
+        <is>
+          <t>Hi! I'm a CS student at Washington State University and saw The Wonderful Company is hiring for Summer Internship Intern - Business Systems Analyst. I recently built APEX, an ML-driven trading signal system with a self-retraining model — would love to connect and hear more about the team.</t>
+        </is>
+      </c>
+      <c r="O75" s="8" t="inlineStr">
+        <is>
+          <t>Subject: Interested in the Summer Internship Intern - Business Systems Analyst role at The Wonderful Company
+Hi,
+My name is Giri Vignesh, and I'm a Computer Science student at Washington State University (graduating May 2027). I came across the Summer Internship Intern - Business Systems Analyst opening at The Wonderful Company and wanted to reach out directly — I'm genuinely interested in the role and think my background lines up well.
+Most recently I built APEX, a full-stack system that combines a technical-analysis signal engine with a RandomForest model that retrains itself on live trading outcomes — deployed end-to-end on AWS.
+I'd love to learn more about the team and what you're looking for — happy to send my resume or hop on a quick call if you're open to it.
+Thanks so much for your time,
+Giri Vignesh
+(425) 362-2938 | girivignesh5@gmail.com | github.com/gvignesh286</t>
+        </is>
+      </c>
+      <c r="P75" s="7" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="Q75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>simplify:74ebbab0-9a8d-4399-aec0-07e5ad5f7337</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>IMC Trading</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>Website →</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>Possible Fit</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>Skills: rest, api, full stack, backend, frontend, Internship title</t>
+        </is>
+      </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="L76" s="4" t="inlineStr">
+        <is>
+          <t